--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="649">
   <si>
     <t>姓名</t>
   </si>
@@ -1016,6 +1016,18 @@
   </si>
   <si>
     <t>座号</t>
+  </si>
+  <si>
+    <t>25 12</t>
+  </si>
+  <si>
+    <t>26 01</t>
+  </si>
+  <si>
+    <t>26 02</t>
+  </si>
+  <si>
+    <t>26 03</t>
   </si>
   <si>
     <t>统计数据</t>
@@ -3287,7 +3299,7 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3302,14 +3314,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="华文仿宋"/>
+      <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="黑体"/>
+      <name val="华文仿宋"/>
       <charset val="134"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="57">
@@ -4075,7 +4087,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="232">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4616,6 +4628,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="57" fontId="24" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="24" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="24" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -5110,529 +5131,529 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="221" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="222" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="223" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="224"/>
+    <col min="1" max="1" width="7.59090909090909" style="224" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="225" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="226" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="227"/>
   </cols>
   <sheetData>
-    <row r="1" s="220" customFormat="1" spans="1:10">
-      <c r="A1" s="225" t="s">
+    <row r="1" s="223" customFormat="1" spans="1:10">
+      <c r="A1" s="228" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="226" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="226" t="s">
+      <c r="B1" s="229" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="226" t="s">
+      <c r="D1" s="229" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="226" t="s">
+      <c r="E1" s="229" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="226" t="s">
+      <c r="F1" s="229" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="226" t="s">
+      <c r="G1" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="227"/>
-      <c r="I1" s="227"/>
-      <c r="J1" s="227"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="228" t="s">
+      <c r="A2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="222" t="s">
+      <c r="B2" s="225" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="222" t="s">
+      <c r="C2" s="225" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="228" t="s">
+      <c r="A3" s="231" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="222" t="s">
+      <c r="C3" s="225" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="222" t="s">
+      <c r="D3" s="225" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="228" t="s">
+      <c r="A4" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="222" t="s">
+      <c r="D4" s="225" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="228" t="s">
+      <c r="A5" s="231" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="222" t="s">
+      <c r="C5" s="225" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="222" t="s">
+      <c r="D5" s="225" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="228" t="s">
+      <c r="A6" s="231" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="222" t="s">
+      <c r="C6" s="225" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="228" t="s">
+      <c r="A7" s="231" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="222" t="s">
+      <c r="B7" s="225" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="222" t="s">
+      <c r="C7" s="225" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="222" t="s">
+      <c r="D7" s="225" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="231" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="222" t="s">
+      <c r="D8" s="225" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="228" t="s">
+      <c r="A9" s="231" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="228" t="s">
+      <c r="A10" s="231" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="222" t="s">
+      <c r="B10" s="225" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="228" t="s">
+      <c r="A11" s="231" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="228" t="s">
+      <c r="A12" s="231" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="228" t="s">
+      <c r="A13" s="231" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="222" t="s">
+      <c r="D13" s="225" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="228" t="s">
+      <c r="A14" s="231" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="222" t="s">
+      <c r="B14" s="225" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="228" t="s">
+      <c r="A15" s="231" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="228" t="s">
+      <c r="A16" s="231" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="222" t="s">
+      <c r="C16" s="225" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="228" t="s">
+      <c r="A17" s="231" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="222" t="s">
+      <c r="C17" s="225" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="228" t="s">
+      <c r="A18" s="231" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="222" t="s">
+      <c r="D18" s="225" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:4">
-      <c r="A19" s="228" t="s">
+      <c r="A19" s="231" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="222" t="s">
+      <c r="D19" s="225" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="228" t="s">
+      <c r="A20" s="231" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="222" t="s">
+      <c r="B20" s="225" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="222" t="s">
+      <c r="C20" s="225" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:4">
-      <c r="A21" s="228" t="s">
+      <c r="A21" s="231" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="222" t="s">
+      <c r="B21" s="225" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="222" t="s">
+      <c r="C21" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="222" t="s">
+      <c r="D21" s="225" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="228" t="s">
+      <c r="A22" s="231" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="228" t="s">
+      <c r="A23" s="231" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="222" t="s">
+      <c r="B23" s="225" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="228" t="s">
+      <c r="A24" s="231" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="222" t="s">
+      <c r="B24" s="225" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="222" t="s">
+      <c r="C24" s="225" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="222" t="s">
+      <c r="D24" s="225" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="228" t="s">
+      <c r="A25" s="231" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="228" t="s">
+      <c r="A26" s="231" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="228" t="s">
+      <c r="A27" s="231" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="222" t="s">
+      <c r="B27" s="225" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="222" t="s">
+      <c r="C27" s="225" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="228" t="s">
+      <c r="A28" s="231" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="222" t="s">
+      <c r="B28" s="225" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="222" t="s">
+      <c r="C28" s="225" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="222" t="s">
+      <c r="D28" s="225" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="228" t="s">
+      <c r="A29" s="231" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="228" t="s">
+      <c r="A30" s="231" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="222" t="s">
+      <c r="B30" s="225" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="222" t="s">
+      <c r="C30" s="225" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="228" t="s">
+      <c r="A31" s="231" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="228" t="s">
+      <c r="A32" s="231" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="228" t="s">
+      <c r="A33" s="231" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="228" t="s">
+      <c r="A34" s="231" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="228" t="s">
+      <c r="A35" s="231" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="228" t="s">
+      <c r="A36" s="231" t="s">
         <v>76</v>
       </c>
-      <c r="B36" s="222" t="s">
+      <c r="B36" s="225" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="228" t="s">
+      <c r="A37" s="231" t="s">
         <v>78</v>
       </c>
-      <c r="C37" s="222" t="s">
+      <c r="C37" s="225" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="222" t="s">
+      <c r="D37" s="225" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="228" t="s">
+      <c r="A38" s="231" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="222" t="s">
+      <c r="B38" s="225" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="229"/>
-      <c r="D38" s="229"/>
-      <c r="E38" s="229"/>
-      <c r="F38" s="229"/>
-      <c r="G38" s="229"/>
+      <c r="C38" s="232"/>
+      <c r="D38" s="232"/>
+      <c r="E38" s="232"/>
+      <c r="F38" s="232"/>
+      <c r="G38" s="232"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="228" t="s">
+      <c r="A39" s="231" t="s">
         <v>83</v>
       </c>
-      <c r="C39" s="222" t="s">
+      <c r="C39" s="225" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="222" t="s">
+      <c r="D39" s="225" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="228" t="s">
+      <c r="A40" s="231" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="222" t="s">
+      <c r="B40" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="222" t="s">
+      <c r="C40" s="225" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="222" t="s">
+      <c r="D40" s="225" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="228" t="s">
+      <c r="A41" s="231" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="222" t="s">
+      <c r="C41" s="225" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="222" t="s">
+      <c r="D41" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="H41" s="223" t="s">
+      <c r="H41" s="226" t="s">
         <v>93</v>
       </c>
-      <c r="I41" s="223" t="s">
+      <c r="I41" s="226" t="s">
         <v>94</v>
       </c>
-      <c r="J41" s="223" t="s">
+      <c r="J41" s="226" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="228" t="s">
+      <c r="A42" s="231" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="228" t="s">
+      <c r="A43" s="231" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="222" t="s">
+      <c r="B43" s="225" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="223" t="s">
+      <c r="H43" s="226" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="228" t="s">
+      <c r="A44" s="231" t="s">
         <v>100</v>
       </c>
-      <c r="B44" s="222" t="s">
+      <c r="B44" s="225" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="228" t="s">
+      <c r="A45" s="231" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="222" t="s">
+      <c r="C45" s="225" t="s">
         <v>103</v>
       </c>
-      <c r="D45" s="222" t="s">
+      <c r="D45" s="225" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="228" t="s">
+      <c r="A46" s="231" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="228" t="s">
+      <c r="A47" s="231" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="222" t="s">
+      <c r="D47" s="225" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="228" t="s">
+      <c r="A48" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="222" t="s">
+      <c r="C48" s="225" t="s">
         <v>109</v>
       </c>
-      <c r="D48" s="222" t="s">
+      <c r="D48" s="225" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="228" t="s">
+      <c r="A49" s="231" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="228" t="s">
+      <c r="A50" s="231" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="222" t="s">
+      <c r="C50" s="225" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="228" t="s">
+      <c r="A51" s="231" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="228" t="s">
+      <c r="A52" s="231" t="s">
         <v>115</v>
       </c>
-      <c r="B52" s="222" t="s">
+      <c r="B52" s="225" t="s">
         <v>116</v>
       </c>
-      <c r="C52" s="222" t="s">
+      <c r="C52" s="225" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="221" t="s">
+      <c r="A53" s="224" t="s">
         <v>118</v>
       </c>
-      <c r="B53" s="222" t="s">
+      <c r="B53" s="225" t="s">
         <v>119</v>
       </c>
-      <c r="D53" s="229"/>
-      <c r="E53" s="229"/>
-      <c r="F53" s="229"/>
-      <c r="G53" s="229"/>
+      <c r="D53" s="232"/>
+      <c r="E53" s="232"/>
+      <c r="F53" s="232"/>
+      <c r="G53" s="232"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="221" t="s">
+      <c r="A54" s="224" t="s">
         <v>120</v>
       </c>
-      <c r="B54" s="222" t="s">
+      <c r="B54" s="225" t="s">
         <v>121</v>
       </c>
-      <c r="C54" s="222" t="s">
+      <c r="C54" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="D54" s="229"/>
-      <c r="E54" s="229"/>
-      <c r="F54" s="229"/>
-      <c r="G54" s="229"/>
+      <c r="D54" s="232"/>
+      <c r="E54" s="232"/>
+      <c r="F54" s="232"/>
+      <c r="G54" s="232"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="221" t="s">
+      <c r="A55" s="224" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="229"/>
-      <c r="C55" s="229"/>
-      <c r="D55" s="222" t="s">
+      <c r="B55" s="232"/>
+      <c r="C55" s="232"/>
+      <c r="D55" s="225" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="221" t="s">
+      <c r="A56" s="224" t="s">
         <v>125</v>
       </c>
       <c r="B56" s="78" t="s">
         <v>126</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="222" t="s">
+      <c r="D56" s="225" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="221" t="s">
+      <c r="A57" s="224" t="s">
         <v>128</v>
       </c>
       <c r="B57" s="78" t="s">
@@ -5641,73 +5662,73 @@
       <c r="C57" s="78" t="s">
         <v>130</v>
       </c>
-      <c r="D57" s="222" t="s">
+      <c r="D57" s="225" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="221" t="s">
+      <c r="A58" s="224" t="s">
         <v>132</v>
       </c>
-      <c r="B58" s="222" t="s">
+      <c r="B58" s="225" t="s">
         <v>133</v>
       </c>
-      <c r="C58" s="229"/>
-      <c r="D58" s="229"/>
-      <c r="E58" s="229"/>
-      <c r="F58" s="229"/>
-      <c r="G58" s="229"/>
+      <c r="C58" s="232"/>
+      <c r="D58" s="232"/>
+      <c r="E58" s="232"/>
+      <c r="F58" s="232"/>
+      <c r="G58" s="232"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="221" t="s">
+      <c r="A59" s="224" t="s">
         <v>134</v>
       </c>
-      <c r="B59" s="229"/>
-      <c r="C59" s="222" t="s">
+      <c r="B59" s="232"/>
+      <c r="C59" s="225" t="s">
         <v>135</v>
       </c>
-      <c r="D59" s="229"/>
-      <c r="E59" s="229"/>
-      <c r="F59" s="229"/>
-      <c r="G59" s="229"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
     </row>
     <row r="60" ht="52" spans="1:7">
-      <c r="A60" s="221" t="s">
+      <c r="A60" s="224" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="229" t="s">
+      <c r="B60" s="232" t="s">
         <v>137</v>
       </c>
-      <c r="C60" s="229"/>
-      <c r="D60" s="222" t="s">
+      <c r="C60" s="232"/>
+      <c r="D60" s="225" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="221" t="s">
+      <c r="A61" s="224" t="s">
         <v>139</v>
       </c>
       <c r="B61" s="78" t="s">
         <v>140</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="229"/>
-      <c r="E61" s="229"/>
-      <c r="F61" s="229"/>
-      <c r="G61" s="229"/>
+      <c r="D61" s="232"/>
+      <c r="E61" s="232"/>
+      <c r="F61" s="232"/>
+      <c r="G61" s="232"/>
     </row>
     <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="221" t="s">
+      <c r="A62" s="224" t="s">
         <v>141</v>
       </c>
-      <c r="B62" s="229"/>
-      <c r="C62" s="229"/>
-      <c r="D62" s="222" t="s">
+      <c r="B62" s="232"/>
+      <c r="C62" s="232"/>
+      <c r="D62" s="225" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="221" t="s">
+      <c r="A63" s="224" t="s">
         <v>143</v>
       </c>
       <c r="B63" s="78" t="s">
@@ -5716,66 +5737,66 @@
       <c r="C63" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="D63" s="229"/>
-      <c r="E63" s="229"/>
-      <c r="F63" s="229"/>
-      <c r="G63" s="229"/>
+      <c r="D63" s="232"/>
+      <c r="E63" s="232"/>
+      <c r="F63" s="232"/>
+      <c r="G63" s="232"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="221" t="s">
+      <c r="A64" s="224" t="s">
         <v>146</v>
       </c>
-      <c r="B64" s="229"/>
-      <c r="C64" s="229"/>
-      <c r="D64" s="222" t="s">
+      <c r="B64" s="232"/>
+      <c r="C64" s="232"/>
+      <c r="D64" s="225" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="221" t="s">
+      <c r="A65" s="224" t="s">
         <v>148</v>
       </c>
-      <c r="B65" s="230" t="s">
+      <c r="B65" s="233" t="s">
         <v>149</v>
       </c>
-      <c r="C65" s="229"/>
-      <c r="D65" s="229"/>
-      <c r="E65" s="229"/>
-      <c r="F65" s="229"/>
-      <c r="G65" s="229"/>
+      <c r="C65" s="232"/>
+      <c r="D65" s="232"/>
+      <c r="E65" s="232"/>
+      <c r="F65" s="232"/>
+      <c r="G65" s="232"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="221" t="s">
+      <c r="A66" s="224" t="s">
         <v>150</v>
       </c>
-      <c r="B66" s="229"/>
-      <c r="C66" s="222" t="s">
+      <c r="B66" s="232"/>
+      <c r="C66" s="225" t="s">
         <v>151</v>
       </c>
-      <c r="D66" s="229"/>
-      <c r="E66" s="229"/>
-      <c r="F66" s="229"/>
-      <c r="G66" s="229"/>
+      <c r="D66" s="232"/>
+      <c r="E66" s="232"/>
+      <c r="F66" s="232"/>
+      <c r="G66" s="232"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="221" t="s">
+      <c r="A67" s="224" t="s">
         <v>152</v>
       </c>
-      <c r="B67" s="229"/>
-      <c r="C67" s="229"/>
+      <c r="B67" s="232"/>
+      <c r="C67" s="232"/>
     </row>
     <row r="68" ht="65" spans="1:7">
-      <c r="A68" s="221" t="s">
+      <c r="A68" s="224" t="s">
         <v>153</v>
       </c>
-      <c r="B68" s="229"/>
-      <c r="C68" s="229"/>
-      <c r="D68" s="222" t="s">
+      <c r="B68" s="232"/>
+      <c r="C68" s="232"/>
+      <c r="D68" s="225" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="221" t="s">
+      <c r="A69" s="224" t="s">
         <v>155</v>
       </c>
       <c r="B69" s="78" t="s">
@@ -5784,89 +5805,89 @@
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="221" t="s">
+      <c r="A70" s="224" t="s">
         <v>157</v>
       </c>
       <c r="B70" s="78" t="s">
         <v>158</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="229"/>
-      <c r="E70" s="229"/>
-      <c r="F70" s="229"/>
-      <c r="G70" s="229"/>
+      <c r="D70" s="232"/>
+      <c r="E70" s="232"/>
+      <c r="F70" s="232"/>
+      <c r="G70" s="232"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="221" t="s">
+      <c r="A71" s="224" t="s">
         <v>159</v>
       </c>
-      <c r="B71" s="229"/>
-      <c r="C71" s="229"/>
+      <c r="B71" s="232"/>
+      <c r="C71" s="232"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="221" t="s">
+      <c r="A72" s="224" t="s">
         <v>160</v>
       </c>
-      <c r="B72" s="222" t="s">
+      <c r="B72" s="225" t="s">
         <v>161</v>
       </c>
-      <c r="C72" s="222" t="s">
+      <c r="C72" s="225" t="s">
         <v>162</v>
       </c>
-      <c r="D72" s="229"/>
-      <c r="E72" s="229"/>
-      <c r="F72" s="229"/>
-      <c r="G72" s="229"/>
+      <c r="D72" s="232"/>
+      <c r="E72" s="232"/>
+      <c r="F72" s="232"/>
+      <c r="G72" s="232"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="221" t="s">
+      <c r="A73" s="224" t="s">
         <v>163</v>
       </c>
-      <c r="B73" s="229"/>
-      <c r="C73" s="222" t="s">
+      <c r="B73" s="232"/>
+      <c r="C73" s="225" t="s">
         <v>164</v>
       </c>
-      <c r="D73" s="229"/>
-      <c r="E73" s="229"/>
-      <c r="F73" s="229"/>
-      <c r="G73" s="229"/>
+      <c r="D73" s="232"/>
+      <c r="E73" s="232"/>
+      <c r="F73" s="232"/>
+      <c r="G73" s="232"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="221" t="s">
+      <c r="A74" s="224" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="221" t="s">
+      <c r="A75" s="224" t="s">
         <v>166</v>
       </c>
-      <c r="D75" s="229"/>
-      <c r="E75" s="229"/>
-      <c r="F75" s="229"/>
-      <c r="G75" s="229"/>
+      <c r="D75" s="232"/>
+      <c r="E75" s="232"/>
+      <c r="F75" s="232"/>
+      <c r="G75" s="232"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="221" t="s">
+      <c r="A76" s="224" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="229"/>
-      <c r="C76" s="229"/>
-      <c r="D76" s="222" t="s">
+      <c r="B76" s="232"/>
+      <c r="C76" s="232"/>
+      <c r="D76" s="225" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="221" t="s">
+      <c r="A77" s="224" t="s">
         <v>169</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="231" t="s">
+      <c r="A78" s="234" t="s">
         <v>170</v>
       </c>
-      <c r="B78" s="222" t="s">
+      <c r="B78" s="225" t="s">
         <v>171</v>
       </c>
     </row>
@@ -5926,10 +5947,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5943,7 +5964,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5957,7 +5978,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5971,7 +5992,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -5999,7 +6020,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6013,7 +6034,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6027,7 +6048,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6041,7 +6062,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6055,7 +6076,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6081,7 +6102,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6095,7 +6116,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6109,7 +6130,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6135,7 +6156,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6149,7 +6170,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6187,7 +6208,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6201,7 +6222,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6227,7 +6248,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6241,7 +6262,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6255,7 +6276,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6269,7 +6290,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6283,7 +6304,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6297,7 +6318,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6323,7 +6344,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6337,7 +6358,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6351,7 +6372,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6377,7 +6398,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6403,7 +6424,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6417,7 +6438,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6431,10 +6452,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E38" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6448,7 +6469,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6462,7 +6483,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6476,10 +6497,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="E41" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6505,7 +6526,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6531,7 +6552,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6557,10 +6578,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E47" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6574,7 +6595,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6600,7 +6621,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6626,7 +6647,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -6659,34 +6680,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>252</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6694,10 +6715,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6705,10 +6726,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6716,10 +6737,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6727,23 +6748,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6751,10 +6772,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6762,10 +6783,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6773,10 +6794,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6784,10 +6805,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6795,50 +6816,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6847,24 +6868,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6872,17 +6893,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6891,22 +6912,22 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
@@ -6917,35 +6938,35 @@
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6953,10 +6974,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6964,10 +6985,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -6975,27 +6996,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7003,10 +7024,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7014,10 +7035,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7025,53 +7046,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7082,42 +7103,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7125,64 +7146,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7192,16 +7213,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7210,7 +7231,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7219,42 +7240,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7264,10 +7285,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7275,10 +7296,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7290,18 +7311,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>
@@ -7409,7 +7430,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7423,7 +7444,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7447,7 +7468,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7460,7 +7481,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7473,7 +7494,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7507,7 +7528,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7553,7 +7574,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7589,7 +7610,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7623,10 +7644,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7638,10 +7659,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7664,7 +7685,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7677,10 +7698,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7714,10 +7735,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7729,10 +7750,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7756,7 +7777,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7823,7 +7844,7 @@
         <v>76</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7837,7 +7858,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7849,7 +7870,7 @@
         <v>81</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7863,7 +7884,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7875,10 +7896,10 @@
         <v>86</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7891,7 +7912,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7914,7 +7935,7 @@
         <v>97</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7938,7 +7959,7 @@
         <v>102</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -7974,7 +7995,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -7998,7 +8019,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8021,10 +8042,10 @@
         <v>115</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8060,27 +8081,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8088,13 +8109,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8102,13 +8123,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8116,13 +8137,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8130,13 +8151,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8144,13 +8165,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8158,13 +8179,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8172,7 +8193,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8180,7 +8201,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8188,7 +8209,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8196,7 +8217,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8216,14 +8237,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="215" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="218" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="216"/>
+    <col min="8" max="16384" width="8.72727272727273" style="219"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="217"/>
+      <c r="A1" s="220"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8243,8 +8264,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="214" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="218" t="s">
+    <row r="2" s="217" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="221" t="s">
         <v>172</v>
       </c>
       <c r="B2" s="78"/>
@@ -8257,7 +8278,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="219" t="s">
+      <c r="A3" s="222" t="s">
         <v>174</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8265,7 +8286,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="219" t="s">
+      <c r="A4" s="222" t="s">
         <v>176</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8276,7 +8297,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="219" t="s">
+      <c r="A5" s="222" t="s">
         <v>179</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8287,7 +8308,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="219" t="s">
+      <c r="A6" s="222" t="s">
         <v>182</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8298,7 +8319,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="219" t="s">
+      <c r="A7" s="222" t="s">
         <v>185</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8306,124 +8327,124 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="219"/>
+      <c r="A8" s="222"/>
       <c r="D8" s="66" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="219"/>
+      <c r="A9" s="222"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="219"/>
+      <c r="A10" s="222"/>
       <c r="B10" s="66" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="219"/>
+      <c r="A11" s="222"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="219"/>
+      <c r="A12" s="222"/>
       <c r="B12" s="66" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="219"/>
+      <c r="A13" s="222"/>
       <c r="B13" s="66" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="219"/>
+      <c r="A14" s="222"/>
       <c r="B14" s="66" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="219"/>
+      <c r="A15" s="222"/>
       <c r="B15" s="66" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="219"/>
+      <c r="A16" s="222"/>
       <c r="B16" s="66" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="219"/>
+      <c r="A17" s="222"/>
       <c r="B17" s="66" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="219"/>
+      <c r="A18" s="222"/>
       <c r="B18" s="66" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="219"/>
+      <c r="A19" s="222"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="219"/>
+      <c r="A20" s="222"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="219"/>
+      <c r="A21" s="222"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="219"/>
+      <c r="A22" s="222"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="219"/>
+      <c r="A23" s="222"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="219"/>
+      <c r="A24" s="222"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="219"/>
+      <c r="A25" s="222"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="219"/>
+      <c r="A26" s="222"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="219"/>
+      <c r="A27" s="222"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="219"/>
+      <c r="A28" s="222"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="219"/>
+      <c r="A29" s="222"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="219"/>
+      <c r="A30" s="222"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="219"/>
+      <c r="A31" s="222"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="219"/>
+      <c r="A32" s="222"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="219"/>
+      <c r="A33" s="222"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="219"/>
+      <c r="A34" s="222"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="219"/>
+      <c r="A35" s="222"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="219"/>
+      <c r="A36" s="222"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="219"/>
+      <c r="A37" s="222"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="219"/>
+      <c r="A38" s="222"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8432,7 +8453,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="219"/>
+      <c r="A39" s="222"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8441,40 +8462,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="219"/>
+      <c r="A40" s="222"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="219"/>
+      <c r="A41" s="222"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="219"/>
+      <c r="A42" s="222"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="219"/>
+      <c r="A43" s="222"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="219"/>
+      <c r="A44" s="222"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="219"/>
+      <c r="A45" s="222"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="219"/>
+      <c r="A46" s="222"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="219"/>
+      <c r="A47" s="222"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="219"/>
+      <c r="A48" s="222"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="219"/>
+      <c r="A49" s="222"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="219"/>
+      <c r="A50" s="222"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="219"/>
+      <c r="A51" s="222"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8490,476 +8511,476 @@
   <dimension ref="A1:C47"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="205" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="205" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="205" customWidth="1"/>
+    <col min="1" max="1" width="24" style="208" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="208" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="208" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="204" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="206" t="s">
+    <row r="1" s="207" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="209" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="206" t="s">
+      <c r="B1" s="209" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="206" t="s">
+      <c r="C1" s="209" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="207" t="s">
+      <c r="A2" s="210" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="207" t="s">
+      <c r="B2" s="210" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="207" t="s">
+      <c r="C2" s="210" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="207" t="s">
+      <c r="A3" s="210" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="207" t="s">
+      <c r="B3" s="210" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="207" t="s">
+      <c r="C3" s="210" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="207" t="s">
+      <c r="A4" s="210" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="207" t="s">
+      <c r="B4" s="210" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="207" t="s">
+      <c r="C4" s="210" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="208" t="s">
+      <c r="A5" s="211" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="207" t="s">
+      <c r="B5" s="210" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="207" t="s">
+      <c r="C5" s="210" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="209"/>
-      <c r="B6" s="207" t="s">
+      <c r="A6" s="212"/>
+      <c r="B6" s="210" t="s">
         <v>210</v>
       </c>
-      <c r="C6" s="207" t="s">
+      <c r="C6" s="210" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="207" t="s">
+      <c r="A7" s="210" t="s">
         <v>212</v>
       </c>
-      <c r="B7" s="207" t="s">
+      <c r="B7" s="210" t="s">
         <v>213</v>
       </c>
-      <c r="C7" s="207" t="s">
+      <c r="C7" s="210" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="210" t="s">
+      <c r="A8" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="210" t="s">
         <v>215</v>
       </c>
-      <c r="C8" s="207" t="s">
+      <c r="C8" s="210" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="211"/>
-      <c r="B9" s="207" t="s">
+      <c r="A9" s="214"/>
+      <c r="B9" s="210" t="s">
         <v>217</v>
       </c>
-      <c r="C9" s="207" t="s">
+      <c r="C9" s="210" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="211"/>
-      <c r="B10" s="207" t="s">
+      <c r="A10" s="214"/>
+      <c r="B10" s="210" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="207" t="s">
+      <c r="C10" s="210" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="211"/>
-      <c r="B11" s="207" t="s">
+      <c r="A11" s="214"/>
+      <c r="B11" s="210" t="s">
         <v>219</v>
       </c>
-      <c r="C11" s="207" t="s">
+      <c r="C11" s="210" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="211"/>
-      <c r="B12" s="207" t="s">
+      <c r="A12" s="214"/>
+      <c r="B12" s="210" t="s">
         <v>222</v>
       </c>
-      <c r="C12" s="207" t="s">
+      <c r="C12" s="210" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="13" ht="140" spans="1:3">
-      <c r="A13" s="211"/>
-      <c r="B13" s="207" t="s">
+      <c r="A13" s="214"/>
+      <c r="B13" s="210" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="207" t="s">
+      <c r="C13" s="210" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="211"/>
-      <c r="B14" s="207" t="s">
+      <c r="A14" s="214"/>
+      <c r="B14" s="210" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="207" t="s">
+      <c r="C14" s="210" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="211"/>
-      <c r="B15" s="207" t="s">
+      <c r="A15" s="214"/>
+      <c r="B15" s="210" t="s">
         <v>228</v>
       </c>
-      <c r="C15" s="207" t="s">
+      <c r="C15" s="210" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="211"/>
-      <c r="B16" s="207" t="s">
+      <c r="A16" s="214"/>
+      <c r="B16" s="210" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="207" t="s">
+      <c r="C16" s="210" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="212"/>
-      <c r="B17" s="207"/>
-      <c r="C17" s="207"/>
+      <c r="A17" s="215"/>
+      <c r="B17" s="210"/>
+      <c r="C17" s="210"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="207" t="s">
+      <c r="A18" s="210" t="s">
         <v>232</v>
       </c>
-      <c r="B18" s="207" t="s">
+      <c r="B18" s="210" t="s">
         <v>233</v>
       </c>
-      <c r="C18" s="207" t="s">
+      <c r="C18" s="210" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="207" t="s">
+      <c r="A19" s="210" t="s">
         <v>235</v>
       </c>
-      <c r="B19" s="207" t="s">
+      <c r="B19" s="210" t="s">
         <v>236</v>
       </c>
-      <c r="C19" s="207" t="s">
+      <c r="C19" s="210" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="207" t="s">
+      <c r="A20" s="210" t="s">
         <v>238</v>
       </c>
-      <c r="B20" s="207" t="s">
+      <c r="B20" s="210" t="s">
         <v>239</v>
       </c>
-      <c r="C20" s="213">
+      <c r="C20" s="216">
         <v>0.440972222222222</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="210" t="s">
+      <c r="A21" s="213" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="207" t="s">
+      <c r="B21" s="210" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="207" t="s">
+      <c r="C21" s="210" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="211"/>
-      <c r="B22" s="207" t="s">
+      <c r="A22" s="214"/>
+      <c r="B22" s="210" t="s">
         <v>242</v>
       </c>
-      <c r="C22" s="207" t="s">
+      <c r="C22" s="210" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="211"/>
-      <c r="B23" s="207" t="s">
+      <c r="A23" s="214"/>
+      <c r="B23" s="210" t="s">
         <v>244</v>
       </c>
-      <c r="C23" s="207" t="s">
+      <c r="C23" s="210" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="24" ht="56" spans="1:3">
-      <c r="A24" s="211"/>
-      <c r="B24" s="207" t="s">
+      <c r="A24" s="214"/>
+      <c r="B24" s="210" t="s">
         <v>246</v>
       </c>
-      <c r="C24" s="207" t="s">
+      <c r="C24" s="210" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="208" t="s">
+      <c r="A25" s="211" t="s">
         <v>248</v>
       </c>
-      <c r="B25" s="207" t="s">
+      <c r="B25" s="210" t="s">
         <v>242</v>
       </c>
-      <c r="C25" s="207" t="s">
+      <c r="C25" s="210" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="209"/>
-      <c r="B26" s="207" t="s">
+      <c r="A26" s="212"/>
+      <c r="B26" s="210" t="s">
         <v>250</v>
       </c>
-      <c r="C26" s="207" t="s">
+      <c r="C26" s="210" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="27" ht="28" spans="1:3">
-      <c r="A27" s="210" t="s">
+      <c r="A27" s="213" t="s">
         <v>252</v>
       </c>
-      <c r="B27" s="207" t="s">
+      <c r="B27" s="210" t="s">
         <v>253</v>
       </c>
-      <c r="C27" s="207" t="s">
+      <c r="C27" s="210" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="211"/>
-      <c r="B28" s="207" t="s">
+      <c r="A28" s="214"/>
+      <c r="B28" s="210" t="s">
         <v>224</v>
       </c>
-      <c r="C28" s="207" t="s">
+      <c r="C28" s="210" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="211"/>
-      <c r="B29" s="207" t="s">
+      <c r="A29" s="214"/>
+      <c r="B29" s="210" t="s">
         <v>228</v>
       </c>
-      <c r="C29" s="207" t="s">
+      <c r="C29" s="210" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="211"/>
-      <c r="B30" s="207"/>
-      <c r="C30" s="207"/>
+      <c r="A30" s="214"/>
+      <c r="B30" s="210"/>
+      <c r="C30" s="210"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="208" t="s">
+      <c r="A31" s="211" t="s">
         <v>257</v>
       </c>
-      <c r="B31" s="207" t="s">
+      <c r="B31" s="210" t="s">
         <v>258</v>
       </c>
-      <c r="C31" s="207" t="s">
+      <c r="C31" s="210" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="209"/>
-      <c r="B32" s="207" t="s">
+      <c r="A32" s="212"/>
+      <c r="B32" s="210" t="s">
         <v>219</v>
       </c>
-      <c r="C32" s="207" t="s">
+      <c r="C32" s="210" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="33" ht="28" spans="1:3">
-      <c r="A33" s="210" t="s">
+      <c r="A33" s="213" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="207" t="s">
+      <c r="B33" s="210" t="s">
         <v>219</v>
       </c>
-      <c r="C33" s="207" t="s">
+      <c r="C33" s="210" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="212"/>
-      <c r="B34" s="205" t="s">
+      <c r="A34" s="215"/>
+      <c r="B34" s="208" t="s">
         <v>262</v>
       </c>
-      <c r="C34" s="205" t="s">
+      <c r="C34" s="208" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="35" ht="98" spans="1:3">
-      <c r="A35" s="210" t="s">
+      <c r="A35" s="213" t="s">
         <v>264</v>
       </c>
-      <c r="B35" s="205" t="s">
+      <c r="B35" s="208" t="s">
         <v>219</v>
       </c>
-      <c r="C35" s="205" t="s">
+      <c r="C35" s="208" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="36" ht="84" spans="1:3">
-      <c r="A36" s="212"/>
-      <c r="B36" s="205" t="s">
+      <c r="A36" s="215"/>
+      <c r="B36" s="208" t="s">
         <v>266</v>
       </c>
-      <c r="C36" s="205" t="s">
+      <c r="C36" s="208" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="205" t="s">
+      <c r="A37" s="208" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="205" t="s">
+      <c r="B37" s="208" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="205" t="s">
+      <c r="C37" s="208" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="38" ht="28" spans="1:3">
-      <c r="A38" s="205" t="s">
+      <c r="A38" s="208" t="s">
         <v>270</v>
       </c>
-      <c r="B38" s="205" t="s">
+      <c r="B38" s="208" t="s">
         <v>262</v>
       </c>
-      <c r="C38" s="205" t="s">
+      <c r="C38" s="208" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="210" t="s">
+      <c r="A39" s="213" t="s">
         <v>272</v>
       </c>
-      <c r="B39" s="205" t="s">
+      <c r="B39" s="208" t="s">
         <v>224</v>
       </c>
-      <c r="C39" s="205" t="s">
+      <c r="C39" s="208" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="212"/>
-      <c r="B40" s="205" t="s">
+      <c r="A40" s="215"/>
+      <c r="B40" s="208" t="s">
         <v>266</v>
       </c>
-      <c r="C40" s="205" t="s">
+      <c r="C40" s="208" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="205" t="s">
+      <c r="A41" s="208" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="205" t="s">
+      <c r="B41" s="208" t="s">
         <v>226</v>
       </c>
-      <c r="C41" s="205" t="s">
+      <c r="C41" s="208" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="205" t="s">
+      <c r="A42" s="208" t="s">
         <v>276</v>
       </c>
-      <c r="B42" s="205" t="s">
+      <c r="B42" s="208" t="s">
         <v>277</v>
       </c>
-      <c r="C42" s="205" t="s">
+      <c r="C42" s="208" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="205" t="s">
+      <c r="A43" s="208" t="s">
         <v>279</v>
       </c>
-      <c r="B43" s="205" t="s">
+      <c r="B43" s="208" t="s">
         <v>230</v>
       </c>
-      <c r="C43" s="205" t="s">
+      <c r="C43" s="208" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="205" t="s">
+      <c r="A44" s="208" t="s">
         <v>10</v>
       </c>
-      <c r="B44" s="205" t="s">
+      <c r="B44" s="208" t="s">
         <v>266</v>
       </c>
-      <c r="C44" s="205" t="s">
+      <c r="C44" s="208" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="205" t="s">
+      <c r="A45" s="208" t="s">
         <v>282</v>
       </c>
-      <c r="B45" s="205" t="s">
+      <c r="B45" s="208" t="s">
         <v>244</v>
       </c>
-      <c r="C45" s="205" t="s">
+      <c r="C45" s="208" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="205" t="s">
+      <c r="A46" s="208" t="s">
         <v>284</v>
       </c>
-      <c r="B46" s="205" t="s">
+      <c r="B46" s="208" t="s">
         <v>285</v>
       </c>
-      <c r="C46" s="205" t="s">
+      <c r="C46" s="208" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="205" t="s">
+      <c r="A47" s="208" t="s">
         <v>287</v>
       </c>
-      <c r="B47" s="205" t="s">
+      <c r="B47" s="208" t="s">
         <v>285</v>
       </c>
-      <c r="C47" s="205" t="s">
+      <c r="C47" s="208" t="s">
         <v>288</v>
       </c>
     </row>
@@ -8992,45 +9013,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="193"/>
+    <col min="5" max="5" width="8.72727272727273" style="196"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="191" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="194" t="s">
+    <row r="1" s="194" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="197" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="195"/>
-      <c r="C1" s="195"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="191" t="s">
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="194" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="2" s="192" customFormat="1" spans="1:7">
-      <c r="A2" s="198" t="s">
+    <row r="2" s="195" customFormat="1" spans="1:7">
+      <c r="A2" s="201" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="199"/>
-      <c r="C2" s="192" t="s">
+      <c r="B2" s="202"/>
+      <c r="C2" s="195" t="s">
         <v>291</v>
       </c>
-      <c r="D2" s="192" t="s">
+      <c r="D2" s="195" t="s">
         <v>292</v>
       </c>
       <c r="E2" s="141"/>
-      <c r="F2" s="192" t="s">
+      <c r="F2" s="195" t="s">
         <v>197</v>
       </c>
-      <c r="G2" s="192" t="s">
+      <c r="G2" s="195" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="200">
+      <c r="A3" s="203">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -9048,7 +9069,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="201"/>
+      <c r="A4" s="204"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -9064,7 +9085,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="201"/>
+      <c r="A5" s="204"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -9080,7 +9101,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="201"/>
+      <c r="A6" s="204"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9088,7 +9109,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="202" t="s">
+      <c r="F6" s="205" t="s">
         <v>300</v>
       </c>
       <c r="G6" s="119" t="s">
@@ -9096,7 +9117,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="201"/>
+      <c r="A7" s="204"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9104,13 +9125,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="203"/>
+      <c r="F7" s="206"/>
       <c r="G7" s="119" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="201"/>
+      <c r="A8" s="204"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9122,7 +9143,7 @@
       <c r="G8" s="119"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="203"/>
+      <c r="A9" s="206"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9134,7 +9155,7 @@
       <c r="G9" s="119"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="202">
+      <c r="A10" s="205">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9148,7 +9169,7 @@
       <c r="G10" s="119"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="201"/>
+      <c r="A11" s="204"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9160,7 +9181,7 @@
       <c r="G11" s="119"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="203"/>
+      <c r="A12" s="206"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9172,7 +9193,7 @@
       <c r="G12" s="119"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="202">
+      <c r="A13" s="205">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9188,7 +9209,7 @@
       <c r="G13" s="119"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="203"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -9236,8 +9257,8 @@
       <c r="A1" s="175" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="176">
-        <v>45992</v>
+      <c r="B1" s="176" t="s">
+        <v>304</v>
       </c>
       <c r="C1" s="177"/>
       <c r="D1" s="177"/>
@@ -9256,8 +9277,8 @@
       <c r="Q1" s="177"/>
       <c r="R1" s="177"/>
       <c r="S1" s="177"/>
-      <c r="T1" s="178">
-        <v>46023</v>
+      <c r="T1" s="178" t="s">
+        <v>305</v>
       </c>
       <c r="U1" s="179"/>
       <c r="V1" s="179"/>
@@ -9274,188 +9295,220 @@
       <c r="AG1" s="179"/>
       <c r="AH1" s="179"/>
       <c r="AI1" s="179"/>
-      <c r="AJ1" s="176">
-        <v>46054</v>
-      </c>
-      <c r="AK1" s="176"/>
-      <c r="AL1" s="176"/>
-      <c r="AM1" s="176"/>
-      <c r="AN1" s="176"/>
-      <c r="AO1" s="176"/>
-      <c r="AP1" s="176"/>
-      <c r="AQ1" s="176"/>
-      <c r="AR1" s="176"/>
-      <c r="AS1" s="176"/>
-      <c r="AT1" s="176"/>
-      <c r="AU1" s="176"/>
-      <c r="AV1" s="176"/>
-      <c r="AW1" s="176"/>
-      <c r="AX1" s="176"/>
-      <c r="AY1" s="176"/>
-      <c r="AZ1" s="176"/>
-      <c r="BA1" s="176"/>
-      <c r="BB1" s="176"/>
-      <c r="BC1" s="176"/>
-      <c r="BD1" s="180" t="s">
-        <v>304</v>
-      </c>
-      <c r="BE1" s="181"/>
-      <c r="BF1" s="181"/>
-      <c r="BG1" s="181"/>
-      <c r="BH1" s="181"/>
-      <c r="BI1" s="181"/>
-      <c r="BJ1" s="182"/>
+      <c r="AJ1" s="180" t="s">
+        <v>306</v>
+      </c>
+      <c r="AK1" s="181"/>
+      <c r="AL1" s="181"/>
+      <c r="AM1" s="180" t="s">
+        <v>307</v>
+      </c>
+      <c r="AN1" s="181"/>
+      <c r="AO1" s="181"/>
+      <c r="AP1" s="181"/>
+      <c r="AQ1" s="181"/>
+      <c r="AR1" s="181"/>
+      <c r="AS1" s="181"/>
+      <c r="AT1" s="181"/>
+      <c r="AU1" s="181"/>
+      <c r="AV1" s="181"/>
+      <c r="AW1" s="181"/>
+      <c r="AX1" s="181"/>
+      <c r="AY1" s="181"/>
+      <c r="AZ1" s="181"/>
+      <c r="BA1" s="181"/>
+      <c r="BB1" s="181"/>
+      <c r="BC1" s="182"/>
+      <c r="BD1" s="183" t="s">
+        <v>308</v>
+      </c>
+      <c r="BE1" s="184"/>
+      <c r="BF1" s="184"/>
+      <c r="BG1" s="184"/>
+      <c r="BH1" s="184"/>
+      <c r="BI1" s="184"/>
+      <c r="BJ1" s="185"/>
     </row>
     <row r="2" s="173" customFormat="1" ht="28" spans="1:62">
       <c r="A2" s="175"/>
-      <c r="B2" s="183">
+      <c r="B2" s="186">
         <v>5</v>
       </c>
-      <c r="C2" s="183">
+      <c r="C2" s="186">
         <v>6</v>
       </c>
-      <c r="D2" s="183">
+      <c r="D2" s="186">
         <v>9</v>
       </c>
-      <c r="E2" s="183">
+      <c r="E2" s="186">
         <v>10</v>
       </c>
-      <c r="F2" s="183">
+      <c r="F2" s="186">
         <v>11</v>
       </c>
-      <c r="G2" s="183">
+      <c r="G2" s="186">
         <v>12</v>
       </c>
-      <c r="H2" s="183">
+      <c r="H2" s="186">
         <v>15</v>
       </c>
-      <c r="I2" s="183">
+      <c r="I2" s="186">
         <v>16</v>
       </c>
-      <c r="J2" s="183">
+      <c r="J2" s="186">
         <v>17</v>
       </c>
-      <c r="K2" s="183">
+      <c r="K2" s="186">
         <v>18</v>
       </c>
-      <c r="L2" s="183">
+      <c r="L2" s="186">
         <v>19</v>
       </c>
-      <c r="M2" s="183">
+      <c r="M2" s="186">
         <v>22</v>
       </c>
-      <c r="N2" s="183">
+      <c r="N2" s="186">
         <v>23</v>
       </c>
-      <c r="O2" s="183">
+      <c r="O2" s="186">
         <v>25</v>
       </c>
-      <c r="P2" s="183">
+      <c r="P2" s="186">
         <v>26</v>
       </c>
-      <c r="Q2" s="183">
+      <c r="Q2" s="186">
         <v>29</v>
       </c>
-      <c r="R2" s="183">
+      <c r="R2" s="186">
         <v>30</v>
       </c>
-      <c r="S2" s="183">
+      <c r="S2" s="186">
         <v>31</v>
       </c>
-      <c r="T2" s="183">
+      <c r="T2" s="186">
         <v>4</v>
       </c>
-      <c r="U2" s="183">
+      <c r="U2" s="186">
         <v>5</v>
       </c>
-      <c r="V2" s="183">
+      <c r="V2" s="186">
         <v>6</v>
       </c>
-      <c r="W2" s="183">
+      <c r="W2" s="186">
         <v>7</v>
       </c>
-      <c r="X2" s="183">
+      <c r="X2" s="186">
         <v>8</v>
       </c>
-      <c r="Y2" s="183">
+      <c r="Y2" s="186">
         <v>11</v>
       </c>
-      <c r="Z2" s="183">
+      <c r="Z2" s="186">
         <v>12</v>
       </c>
-      <c r="AA2" s="183">
+      <c r="AA2" s="186">
         <v>13</v>
       </c>
-      <c r="AB2" s="183">
+      <c r="AB2" s="186">
         <v>14</v>
       </c>
-      <c r="AC2" s="183">
+      <c r="AC2" s="186">
         <v>15</v>
       </c>
-      <c r="AD2" s="183">
+      <c r="AD2" s="186">
         <v>16</v>
       </c>
-      <c r="AE2" s="183">
+      <c r="AE2" s="186">
         <v>19</v>
       </c>
-      <c r="AF2" s="183">
+      <c r="AF2" s="186">
         <v>20</v>
       </c>
-      <c r="AG2" s="183">
+      <c r="AG2" s="186">
         <v>21</v>
       </c>
-      <c r="AH2" s="183">
+      <c r="AH2" s="186">
         <v>22</v>
       </c>
-      <c r="AI2" s="183">
+      <c r="AI2" s="186">
         <v>23</v>
       </c>
-      <c r="AJ2" s="183">
+      <c r="AJ2" s="186">
         <v>26</v>
       </c>
-      <c r="AK2" s="183">
+      <c r="AK2" s="186">
         <v>27</v>
       </c>
-      <c r="AL2" s="183">
+      <c r="AL2" s="186">
         <v>28</v>
       </c>
-      <c r="AM2" s="183"/>
-      <c r="AN2" s="183"/>
-      <c r="AO2" s="183"/>
-      <c r="AP2" s="183"/>
-      <c r="AQ2" s="183"/>
-      <c r="AR2" s="183"/>
-      <c r="AS2" s="183"/>
-      <c r="AT2" s="183"/>
-      <c r="AU2" s="183"/>
-      <c r="AV2" s="183"/>
-      <c r="AW2" s="183"/>
-      <c r="AX2" s="183"/>
-      <c r="AY2" s="183"/>
-      <c r="AZ2" s="183"/>
-      <c r="BA2" s="183"/>
-      <c r="BB2" s="183"/>
-      <c r="BC2" s="183"/>
-      <c r="BD2" s="184" t="s">
-        <v>305</v>
-      </c>
-      <c r="BE2" s="184" t="s">
-        <v>306</v>
-      </c>
-      <c r="BF2" s="184" t="s">
-        <v>307</v>
-      </c>
-      <c r="BG2" s="184" t="s">
-        <v>308</v>
-      </c>
-      <c r="BH2" s="185" t="s">
+      <c r="AM2" s="186">
+        <v>2</v>
+      </c>
+      <c r="AN2" s="186">
+        <v>3</v>
+      </c>
+      <c r="AO2" s="186">
+        <v>4</v>
+      </c>
+      <c r="AP2" s="186">
+        <v>5</v>
+      </c>
+      <c r="AQ2" s="186">
+        <v>6</v>
+      </c>
+      <c r="AR2" s="186">
+        <v>9</v>
+      </c>
+      <c r="AS2" s="186">
+        <v>10</v>
+      </c>
+      <c r="AT2" s="186">
+        <v>11</v>
+      </c>
+      <c r="AU2" s="186">
+        <v>12</v>
+      </c>
+      <c r="AV2" s="186">
+        <v>13</v>
+      </c>
+      <c r="AW2" s="186">
+        <v>16</v>
+      </c>
+      <c r="AX2" s="186">
+        <v>17</v>
+      </c>
+      <c r="AY2" s="186">
+        <v>18</v>
+      </c>
+      <c r="AZ2" s="186">
+        <v>19</v>
+      </c>
+      <c r="BA2" s="186">
+        <v>20</v>
+      </c>
+      <c r="BB2" s="186"/>
+      <c r="BC2" s="186"/>
+      <c r="BD2" s="187" t="s">
         <v>309</v>
       </c>
-      <c r="BI2" s="185" t="s">
+      <c r="BE2" s="187" t="s">
         <v>310</v>
       </c>
-      <c r="BJ2" s="185" t="s">
+      <c r="BF2" s="187" t="s">
         <v>311</v>
+      </c>
+      <c r="BG2" s="187" t="s">
+        <v>312</v>
+      </c>
+      <c r="BH2" s="188" t="s">
+        <v>313</v>
+      </c>
+      <c r="BI2" s="188" t="s">
+        <v>314</v>
+      </c>
+      <c r="BJ2" s="188" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9518,31 +9571,31 @@
       <c r="BA3" s="120"/>
       <c r="BB3" s="120"/>
       <c r="BC3" s="120"/>
-      <c r="BD3" s="186">
+      <c r="BD3" s="189">
         <f>SUM(B3:BC3)</f>
         <v>1</v>
       </c>
-      <c r="BE3" s="186" cm="1">
+      <c r="BE3" s="189" cm="1">
         <f t="array" ref="BE3">SUMPRODUCT(--(B3:BC3=INT(B3:BC3)),--(B3:BC3&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF3" s="186" cm="1">
+      <c r="BF3" s="189" cm="1">
         <f t="array" ref="BF3">MAX(FREQUENCY(IF((B3:BC3=INT(B3:BC3))*(B3:BC3&gt;0),COLUMN(B3:BC3)),IF((B3:BC3&lt;&gt;INT(B3:BC3))+(B3:BC3&lt;=0),COLUMN(B3:BC3))))</f>
         <v>1</v>
       </c>
-      <c r="BG3" s="187" cm="1">
+      <c r="BG3" s="190" cm="1">
         <f t="array" ref="BG3">SUMPRODUCT(--(B3:AI3=INT(B3:AI3)),--(B3:AI3&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH3" s="188">
+      <c r="BH3" s="191">
         <f>RANK(BD3,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI3" s="188">
+      <c r="BI3" s="191">
         <f>RANK(BE3,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ3" s="188">
+      <c r="BJ3" s="191">
         <f>RANK(BF3,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
@@ -9627,31 +9680,31 @@
       <c r="BA4" s="120"/>
       <c r="BB4" s="120"/>
       <c r="BC4" s="120"/>
-      <c r="BD4" s="186">
+      <c r="BD4" s="189">
         <f t="shared" ref="BD4:BD35" si="0">SUM(B4:BC4)</f>
         <v>12</v>
       </c>
-      <c r="BE4" s="186" cm="1">
+      <c r="BE4" s="189" cm="1">
         <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF4" s="186" cm="1">
+      <c r="BF4" s="189" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
         <v>3</v>
       </c>
-      <c r="BG4" s="187" cm="1">
+      <c r="BG4" s="190" cm="1">
         <f t="array" ref="BG4">SUMPRODUCT(--(B4:AI4=INT(B4:AI4)),--(B4:AI4&gt;0))/34*100%</f>
         <v>0.323529411764706</v>
       </c>
-      <c r="BH4" s="188">
+      <c r="BH4" s="191">
         <f t="shared" ref="BH4:BJ4" si="1">RANK(BD4,BD$3:BD$53,0)</f>
         <v>8</v>
       </c>
-      <c r="BI4" s="188">
+      <c r="BI4" s="191">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="BJ4" s="188">
+      <c r="BJ4" s="191">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -9718,31 +9771,31 @@
       <c r="BA5" s="120"/>
       <c r="BB5" s="120"/>
       <c r="BC5" s="120"/>
-      <c r="BD5" s="186">
+      <c r="BD5" s="189">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE5" s="186" cm="1">
+      <c r="BE5" s="189" cm="1">
         <f t="array" ref="BE5">SUMPRODUCT(--(B5:BC5=INT(B5:BC5)),--(B5:BC5&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF5" s="186" cm="1">
+      <c r="BF5" s="189" cm="1">
         <f t="array" ref="BF5">MAX(FREQUENCY(IF((B5:BC5=INT(B5:BC5))*(B5:BC5&gt;0),COLUMN(B5:BC5)),IF((B5:BC5&lt;&gt;INT(B5:BC5))+(B5:BC5&lt;=0),COLUMN(B5:BC5))))</f>
         <v>1</v>
       </c>
-      <c r="BG5" s="187" cm="1">
+      <c r="BG5" s="190" cm="1">
         <f t="array" ref="BG5">SUMPRODUCT(--(B5:AI5=INT(B5:AI5)),--(B5:AI5&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH5" s="188">
+      <c r="BH5" s="191">
         <f t="shared" ref="BH5:BJ5" si="2">RANK(BD5,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI5" s="188">
+      <c r="BI5" s="191">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="BJ5" s="188">
+      <c r="BJ5" s="191">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
@@ -9811,31 +9864,31 @@
       <c r="BA6" s="120"/>
       <c r="BB6" s="120"/>
       <c r="BC6" s="120"/>
-      <c r="BD6" s="186">
+      <c r="BD6" s="189">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="BE6" s="186" cm="1">
+      <c r="BE6" s="189" cm="1">
         <f t="array" ref="BE6">SUMPRODUCT(--(B6:BC6=INT(B6:BC6)),--(B6:BC6&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF6" s="186" cm="1">
+      <c r="BF6" s="189" cm="1">
         <f t="array" ref="BF6">MAX(FREQUENCY(IF((B6:BC6=INT(B6:BC6))*(B6:BC6&gt;0),COLUMN(B6:BC6)),IF((B6:BC6&lt;&gt;INT(B6:BC6))+(B6:BC6&lt;=0),COLUMN(B6:BC6))))</f>
         <v>1</v>
       </c>
-      <c r="BG6" s="187" cm="1">
+      <c r="BG6" s="190" cm="1">
         <f t="array" ref="BG6">SUMPRODUCT(--(B6:AI6=INT(B6:AI6)),--(B6:AI6&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH6" s="188">
+      <c r="BH6" s="191">
         <f t="shared" ref="BH6:BJ6" si="3">RANK(BD6,BD$3:BD$53,0)</f>
         <v>28</v>
       </c>
-      <c r="BI6" s="188">
+      <c r="BI6" s="191">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
-      <c r="BJ6" s="188">
+      <c r="BJ6" s="191">
         <f t="shared" si="3"/>
         <v>19</v>
       </c>
@@ -9904,31 +9957,31 @@
       <c r="BA7" s="120"/>
       <c r="BB7" s="120"/>
       <c r="BC7" s="120"/>
-      <c r="BD7" s="186">
+      <c r="BD7" s="189">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE7" s="186" cm="1">
+      <c r="BE7" s="189" cm="1">
         <f t="array" ref="BE7">SUMPRODUCT(--(B7:BC7=INT(B7:BC7)),--(B7:BC7&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF7" s="186" cm="1">
+      <c r="BF7" s="189" cm="1">
         <f t="array" ref="BF7">MAX(FREQUENCY(IF((B7:BC7=INT(B7:BC7))*(B7:BC7&gt;0),COLUMN(B7:BC7)),IF((B7:BC7&lt;&gt;INT(B7:BC7))+(B7:BC7&lt;=0),COLUMN(B7:BC7))))</f>
         <v>1</v>
       </c>
-      <c r="BG7" s="187" cm="1">
+      <c r="BG7" s="190" cm="1">
         <f t="array" ref="BG7">SUMPRODUCT(--(B7:AI7=INT(B7:AI7)),--(B7:AI7&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH7" s="188">
+      <c r="BH7" s="191">
         <f t="shared" ref="BH7:BJ7" si="4">RANK(BD7,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI7" s="188">
+      <c r="BI7" s="191">
         <f t="shared" si="4"/>
         <v>26</v>
       </c>
-      <c r="BJ7" s="188">
+      <c r="BJ7" s="191">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
@@ -10010,7 +10063,9 @@
         <v>1</v>
       </c>
       <c r="AL8" s="120"/>
-      <c r="AM8" s="120"/>
+      <c r="AM8" s="120">
+        <v>1</v>
+      </c>
       <c r="AN8" s="120"/>
       <c r="AO8" s="120"/>
       <c r="AP8" s="120"/>
@@ -10027,31 +10082,31 @@
       <c r="BA8" s="120"/>
       <c r="BB8" s="120"/>
       <c r="BC8" s="120"/>
-      <c r="BD8" s="186">
+      <c r="BD8" s="189">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="BE8" s="186" cm="1">
+        <v>19</v>
+      </c>
+      <c r="BE8" s="189" cm="1">
         <f t="array" ref="BE8">SUMPRODUCT(--(B8:BC8=INT(B8:BC8)),--(B8:BC8&gt;0))</f>
-        <v>18</v>
-      </c>
-      <c r="BF8" s="186" cm="1">
+        <v>19</v>
+      </c>
+      <c r="BF8" s="189" cm="1">
         <f t="array" ref="BF8">MAX(FREQUENCY(IF((B8:BC8=INT(B8:BC8))*(B8:BC8&gt;0),COLUMN(B8:BC8)),IF((B8:BC8&lt;&gt;INT(B8:BC8))+(B8:BC8&lt;=0),COLUMN(B8:BC8))))</f>
         <v>5</v>
       </c>
-      <c r="BG8" s="187" cm="1">
+      <c r="BG8" s="190" cm="1">
         <f t="array" ref="BG8">SUMPRODUCT(--(B8:AI8=INT(B8:AI8)),--(B8:AI8&gt;0))/34*100%</f>
         <v>0.470588235294118</v>
       </c>
-      <c r="BH8" s="188">
+      <c r="BH8" s="191">
         <f t="shared" ref="BH8:BJ8" si="5">RANK(BD8,BD$3:BD$53,0)</f>
         <v>3</v>
       </c>
-      <c r="BI8" s="188">
+      <c r="BI8" s="191">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="BJ8" s="188">
+      <c r="BJ8" s="191">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -10138,31 +10193,31 @@
       <c r="BA9" s="120"/>
       <c r="BB9" s="120"/>
       <c r="BC9" s="120"/>
-      <c r="BD9" s="186">
+      <c r="BD9" s="189">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="BE9" s="186" cm="1">
+      <c r="BE9" s="189" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
         <v>12</v>
       </c>
-      <c r="BF9" s="186" cm="1">
+      <c r="BF9" s="189" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
         <v>3</v>
       </c>
-      <c r="BG9" s="187" cm="1">
+      <c r="BG9" s="190" cm="1">
         <f t="array" ref="BG9">SUMPRODUCT(--(B9:AI9=INT(B9:AI9)),--(B9:AI9&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH9" s="188">
+      <c r="BH9" s="191">
         <f>RANK(BD9,BD$3:BD$53,0)</f>
         <v>8</v>
       </c>
-      <c r="BI9" s="188">
+      <c r="BI9" s="191">
         <f t="shared" ref="BH9:BJ9" si="6">RANK(BE9,BE$3:BE$53,0)</f>
         <v>6</v>
       </c>
-      <c r="BJ9" s="188">
+      <c r="BJ9" s="191">
         <f t="shared" si="6"/>
         <v>8</v>
       </c>
@@ -10227,31 +10282,31 @@
       <c r="BA10" s="120"/>
       <c r="BB10" s="120"/>
       <c r="BC10" s="120"/>
-      <c r="BD10" s="186">
+      <c r="BD10" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE10" s="186" cm="1">
+      <c r="BE10" s="189" cm="1">
         <f t="array" ref="BE10">SUMPRODUCT(--(B10:BC10=INT(B10:BC10)),--(B10:BC10&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF10" s="186" cm="1">
+      <c r="BF10" s="189" cm="1">
         <f t="array" ref="BF10">MAX(FREQUENCY(IF((B10:BC10=INT(B10:BC10))*(B10:BC10&gt;0),COLUMN(B10:BC10)),IF((B10:BC10&lt;&gt;INT(B10:BC10))+(B10:BC10&lt;=0),COLUMN(B10:BC10))))</f>
         <v>1</v>
       </c>
-      <c r="BG10" s="187" cm="1">
+      <c r="BG10" s="190" cm="1">
         <f t="array" ref="BG10">SUMPRODUCT(--(B10:AI10=INT(B10:AI10)),--(B10:AI10&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH10" s="188">
+      <c r="BH10" s="191">
         <f t="shared" ref="BH10:BJ10" si="7">RANK(BD10,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI10" s="188">
+      <c r="BI10" s="191">
         <f t="shared" si="7"/>
         <v>34</v>
       </c>
-      <c r="BJ10" s="188">
+      <c r="BJ10" s="191">
         <f t="shared" si="7"/>
         <v>19</v>
       </c>
@@ -10328,31 +10383,31 @@
       <c r="BA11" s="120"/>
       <c r="BB11" s="120"/>
       <c r="BC11" s="120"/>
-      <c r="BD11" s="186">
+      <c r="BD11" s="189">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="BE11" s="186" cm="1">
+      <c r="BE11" s="189" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(--(B11:BC11=INT(B11:BC11)),--(B11:BC11&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF11" s="186" cm="1">
+      <c r="BF11" s="189" cm="1">
         <f t="array" ref="BF11">MAX(FREQUENCY(IF((B11:BC11=INT(B11:BC11))*(B11:BC11&gt;0),COLUMN(B11:BC11)),IF((B11:BC11&lt;&gt;INT(B11:BC11))+(B11:BC11&lt;=0),COLUMN(B11:BC11))))</f>
         <v>1</v>
       </c>
-      <c r="BG11" s="187" cm="1">
+      <c r="BG11" s="190" cm="1">
         <f t="array" ref="BG11">SUMPRODUCT(--(B11:AI11=INT(B11:AI11)),--(B11:AI11&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH11" s="188">
+      <c r="BH11" s="191">
         <f t="shared" ref="BH11:BJ11" si="8">RANK(BD11,BD$3:BD$53,0)</f>
         <v>19</v>
       </c>
-      <c r="BI11" s="188">
+      <c r="BI11" s="191">
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="BJ11" s="188">
+      <c r="BJ11" s="191">
         <f t="shared" si="8"/>
         <v>19</v>
       </c>
@@ -10419,31 +10474,31 @@
       <c r="BA12" s="120"/>
       <c r="BB12" s="120"/>
       <c r="BC12" s="120"/>
-      <c r="BD12" s="186">
+      <c r="BD12" s="189">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE12" s="186" cm="1">
+      <c r="BE12" s="189" cm="1">
         <f t="array" ref="BE12">SUMPRODUCT(--(B12:BC12=INT(B12:BC12)),--(B12:BC12&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF12" s="186" cm="1">
+      <c r="BF12" s="189" cm="1">
         <f t="array" ref="BF12">MAX(FREQUENCY(IF((B12:BC12=INT(B12:BC12))*(B12:BC12&gt;0),COLUMN(B12:BC12)),IF((B12:BC12&lt;&gt;INT(B12:BC12))+(B12:BC12&lt;=0),COLUMN(B12:BC12))))</f>
         <v>1</v>
       </c>
-      <c r="BG12" s="187" cm="1">
+      <c r="BG12" s="190" cm="1">
         <f t="array" ref="BG12">SUMPRODUCT(--(B12:AI12=INT(B12:AI12)),--(B12:AI12&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH12" s="188">
+      <c r="BH12" s="191">
         <f t="shared" ref="BH12:BJ12" si="9">RANK(BD12,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI12" s="188">
+      <c r="BI12" s="191">
         <f t="shared" si="9"/>
         <v>29</v>
       </c>
-      <c r="BJ12" s="188">
+      <c r="BJ12" s="191">
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
@@ -10524,31 +10579,31 @@
       <c r="BA13" s="120"/>
       <c r="BB13" s="120"/>
       <c r="BC13" s="120"/>
-      <c r="BD13" s="186">
+      <c r="BD13" s="189">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="BE13" s="186" cm="1">
+      <c r="BE13" s="189" cm="1">
         <f t="array" ref="BE13">SUMPRODUCT(--(B13:BC13=INT(B13:BC13)),--(B13:BC13&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="BF13" s="186" cm="1">
+      <c r="BF13" s="189" cm="1">
         <f t="array" ref="BF13">MAX(FREQUENCY(IF((B13:BC13=INT(B13:BC13))*(B13:BC13&gt;0),COLUMN(B13:BC13)),IF((B13:BC13&lt;&gt;INT(B13:BC13))+(B13:BC13&lt;=0),COLUMN(B13:BC13))))</f>
         <v>1</v>
       </c>
-      <c r="BG13" s="187" cm="1">
+      <c r="BG13" s="190" cm="1">
         <f t="array" ref="BG13">SUMPRODUCT(--(B13:AI13=INT(B13:AI13)),--(B13:AI13&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH13" s="188">
+      <c r="BH13" s="191">
         <f t="shared" ref="BH13:BJ13" si="10">RANK(BD13,BD$3:BD$53,0)</f>
         <v>14</v>
       </c>
-      <c r="BI13" s="188">
+      <c r="BI13" s="191">
         <f t="shared" si="10"/>
-        <v>12</v>
-      </c>
-      <c r="BJ13" s="188">
+        <v>13</v>
+      </c>
+      <c r="BJ13" s="191">
         <f t="shared" si="10"/>
         <v>19</v>
       </c>
@@ -10615,31 +10670,31 @@
       <c r="BA14" s="120"/>
       <c r="BB14" s="120"/>
       <c r="BC14" s="120"/>
-      <c r="BD14" s="186">
+      <c r="BD14" s="189">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE14" s="186" cm="1">
+      <c r="BE14" s="189" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(--(B14:BC14=INT(B14:BC14)),--(B14:BC14&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF14" s="186" cm="1">
+      <c r="BF14" s="189" cm="1">
         <f t="array" ref="BF14">MAX(FREQUENCY(IF((B14:BC14=INT(B14:BC14))*(B14:BC14&gt;0),COLUMN(B14:BC14)),IF((B14:BC14&lt;&gt;INT(B14:BC14))+(B14:BC14&lt;=0),COLUMN(B14:BC14))))</f>
         <v>1</v>
       </c>
-      <c r="BG14" s="187" cm="1">
+      <c r="BG14" s="190" cm="1">
         <f t="array" ref="BG14">SUMPRODUCT(--(B14:AI14=INT(B14:AI14)),--(B14:AI14&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH14" s="188">
+      <c r="BH14" s="191">
         <f t="shared" ref="BH14:BJ14" si="11">RANK(BD14,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI14" s="188">
+      <c r="BI14" s="191">
         <f t="shared" si="11"/>
         <v>29</v>
       </c>
-      <c r="BJ14" s="188">
+      <c r="BJ14" s="191">
         <f t="shared" si="11"/>
         <v>19</v>
       </c>
@@ -10703,7 +10758,9 @@
       <c r="AJ15" s="120"/>
       <c r="AK15" s="120"/>
       <c r="AL15" s="120"/>
-      <c r="AM15" s="120"/>
+      <c r="AM15" s="120">
+        <v>1</v>
+      </c>
       <c r="AN15" s="120"/>
       <c r="AO15" s="120"/>
       <c r="AP15" s="120"/>
@@ -10720,31 +10777,31 @@
       <c r="BA15" s="120"/>
       <c r="BB15" s="120"/>
       <c r="BC15" s="120"/>
-      <c r="BD15" s="186">
+      <c r="BD15" s="189">
         <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="BE15" s="189" cm="1">
+        <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BE15" s="186" cm="1">
-        <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>9</v>
-      </c>
-      <c r="BF15" s="186" cm="1">
+      <c r="BF15" s="189" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
         <v>2</v>
       </c>
-      <c r="BG15" s="187" cm="1">
+      <c r="BG15" s="190" cm="1">
         <f t="array" ref="BG15">SUMPRODUCT(--(B15:AI15=INT(B15:AI15)),--(B15:AI15&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH15" s="188">
+      <c r="BH15" s="191">
         <f t="shared" ref="BH15:BJ15" si="12">RANK(BD15,BD$3:BD$53,0)</f>
-        <v>11</v>
-      </c>
-      <c r="BI15" s="188">
+        <v>10</v>
+      </c>
+      <c r="BI15" s="191">
         <f t="shared" si="12"/>
-        <v>12</v>
-      </c>
-      <c r="BJ15" s="188">
+        <v>9</v>
+      </c>
+      <c r="BJ15" s="191">
         <f t="shared" si="12"/>
         <v>13</v>
       </c>
@@ -10811,31 +10868,31 @@
       <c r="BA16" s="120"/>
       <c r="BB16" s="120"/>
       <c r="BC16" s="120"/>
-      <c r="BD16" s="186">
+      <c r="BD16" s="189">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE16" s="186" cm="1">
+      <c r="BE16" s="189" cm="1">
         <f t="array" ref="BE16">SUMPRODUCT(--(B16:BC16=INT(B16:BC16)),--(B16:BC16&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF16" s="186" cm="1">
+      <c r="BF16" s="189" cm="1">
         <f t="array" ref="BF16">MAX(FREQUENCY(IF((B16:BC16=INT(B16:BC16))*(B16:BC16&gt;0),COLUMN(B16:BC16)),IF((B16:BC16&lt;&gt;INT(B16:BC16))+(B16:BC16&lt;=0),COLUMN(B16:BC16))))</f>
         <v>1</v>
       </c>
-      <c r="BG16" s="187" cm="1">
+      <c r="BG16" s="190" cm="1">
         <f t="array" ref="BG16">SUMPRODUCT(--(B16:AI16=INT(B16:AI16)),--(B16:AI16&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH16" s="188">
+      <c r="BH16" s="191">
         <f t="shared" ref="BH16:BJ16" si="13">RANK(BD16,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI16" s="188">
+      <c r="BI16" s="191">
         <f t="shared" si="13"/>
         <v>29</v>
       </c>
-      <c r="BJ16" s="188">
+      <c r="BJ16" s="191">
         <f t="shared" si="13"/>
         <v>19</v>
       </c>
@@ -10906,31 +10963,31 @@
       <c r="BA17" s="120"/>
       <c r="BB17" s="120"/>
       <c r="BC17" s="120"/>
-      <c r="BD17" s="186">
+      <c r="BD17" s="189">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE17" s="186" cm="1">
+      <c r="BE17" s="189" cm="1">
         <f t="array" ref="BE17">SUMPRODUCT(--(B17:BC17=INT(B17:BC17)),--(B17:BC17&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF17" s="186" cm="1">
+      <c r="BF17" s="189" cm="1">
         <f t="array" ref="BF17">MAX(FREQUENCY(IF((B17:BC17=INT(B17:BC17))*(B17:BC17&gt;0),COLUMN(B17:BC17)),IF((B17:BC17&lt;&gt;INT(B17:BC17))+(B17:BC17&lt;=0),COLUMN(B17:BC17))))</f>
         <v>1</v>
       </c>
-      <c r="BG17" s="187" cm="1">
+      <c r="BG17" s="190" cm="1">
         <f t="array" ref="BG17">SUMPRODUCT(--(B17:AI17=INT(B17:AI17)),--(B17:AI17&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH17" s="188">
+      <c r="BH17" s="191">
         <f t="shared" ref="BH17:BJ17" si="14">RANK(BD17,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI17" s="188">
+      <c r="BI17" s="191">
         <f t="shared" si="14"/>
         <v>23</v>
       </c>
-      <c r="BJ17" s="188">
+      <c r="BJ17" s="191">
         <f t="shared" si="14"/>
         <v>19</v>
       </c>
@@ -10995,31 +11052,31 @@
       <c r="BA18" s="120"/>
       <c r="BB18" s="120"/>
       <c r="BC18" s="120"/>
-      <c r="BD18" s="186">
+      <c r="BD18" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE18" s="186" cm="1">
+      <c r="BE18" s="189" cm="1">
         <f t="array" ref="BE18">SUMPRODUCT(--(B18:BC18=INT(B18:BC18)),--(B18:BC18&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF18" s="186" cm="1">
+      <c r="BF18" s="189" cm="1">
         <f t="array" ref="BF18">MAX(FREQUENCY(IF((B18:BC18=INT(B18:BC18))*(B18:BC18&gt;0),COLUMN(B18:BC18)),IF((B18:BC18&lt;&gt;INT(B18:BC18))+(B18:BC18&lt;=0),COLUMN(B18:BC18))))</f>
         <v>1</v>
       </c>
-      <c r="BG18" s="187" cm="1">
+      <c r="BG18" s="190" cm="1">
         <f t="array" ref="BG18">SUMPRODUCT(--(B18:AI18=INT(B18:AI18)),--(B18:AI18&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH18" s="188">
+      <c r="BH18" s="191">
         <f t="shared" ref="BH18:BJ18" si="15">RANK(BD18,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI18" s="188">
+      <c r="BI18" s="191">
         <f t="shared" si="15"/>
         <v>34</v>
       </c>
-      <c r="BJ18" s="188">
+      <c r="BJ18" s="191">
         <f t="shared" si="15"/>
         <v>19</v>
       </c>
@@ -11092,31 +11149,31 @@
       <c r="BA19" s="120"/>
       <c r="BB19" s="120"/>
       <c r="BC19" s="120"/>
-      <c r="BD19" s="186">
+      <c r="BD19" s="189">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE19" s="186" cm="1">
+      <c r="BE19" s="189" cm="1">
         <f t="array" ref="BE19">SUMPRODUCT(--(B19:BC19=INT(B19:BC19)),--(B19:BC19&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF19" s="186" cm="1">
+      <c r="BF19" s="189" cm="1">
         <f t="array" ref="BF19">MAX(FREQUENCY(IF((B19:BC19=INT(B19:BC19))*(B19:BC19&gt;0),COLUMN(B19:BC19)),IF((B19:BC19&lt;&gt;INT(B19:BC19))+(B19:BC19&lt;=0),COLUMN(B19:BC19))))</f>
         <v>2</v>
       </c>
-      <c r="BG19" s="187" cm="1">
+      <c r="BG19" s="190" cm="1">
         <f t="array" ref="BG19">SUMPRODUCT(--(B19:AI19=INT(B19:AI19)),--(B19:AI19&gt;0))/34*100%</f>
         <v>0.147058823529412</v>
       </c>
-      <c r="BH19" s="188">
+      <c r="BH19" s="191">
         <f t="shared" ref="BH19:BJ19" si="16">RANK(BD19,BD$3:BD$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BI19" s="188">
+      <c r="BI19" s="191">
         <f t="shared" si="16"/>
         <v>20</v>
       </c>
-      <c r="BJ19" s="188">
+      <c r="BJ19" s="191">
         <f t="shared" si="16"/>
         <v>13</v>
       </c>
@@ -11181,31 +11238,31 @@
       <c r="BA20" s="120"/>
       <c r="BB20" s="120"/>
       <c r="BC20" s="120"/>
-      <c r="BD20" s="186">
+      <c r="BD20" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE20" s="186" cm="1">
+      <c r="BE20" s="189" cm="1">
         <f t="array" ref="BE20">SUMPRODUCT(--(B20:BC20=INT(B20:BC20)),--(B20:BC20&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF20" s="186" cm="1">
+      <c r="BF20" s="189" cm="1">
         <f t="array" ref="BF20">MAX(FREQUENCY(IF((B20:BC20=INT(B20:BC20))*(B20:BC20&gt;0),COLUMN(B20:BC20)),IF((B20:BC20&lt;&gt;INT(B20:BC20))+(B20:BC20&lt;=0),COLUMN(B20:BC20))))</f>
         <v>1</v>
       </c>
-      <c r="BG20" s="187" cm="1">
+      <c r="BG20" s="190" cm="1">
         <f t="array" ref="BG20">SUMPRODUCT(--(B20:AI20=INT(B20:AI20)),--(B20:AI20&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH20" s="188">
+      <c r="BH20" s="191">
         <f t="shared" ref="BH20:BJ20" si="17">RANK(BD20,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI20" s="188">
+      <c r="BI20" s="191">
         <f t="shared" si="17"/>
         <v>34</v>
       </c>
-      <c r="BJ20" s="188">
+      <c r="BJ20" s="191">
         <f t="shared" si="17"/>
         <v>19</v>
       </c>
@@ -11272,31 +11329,31 @@
       <c r="BA21" s="120"/>
       <c r="BB21" s="120"/>
       <c r="BC21" s="120"/>
-      <c r="BD21" s="186">
+      <c r="BD21" s="189">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE21" s="186" cm="1">
+      <c r="BE21" s="189" cm="1">
         <f t="array" ref="BE21">SUMPRODUCT(--(B21:BC21=INT(B21:BC21)),--(B21:BC21&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF21" s="186" cm="1">
+      <c r="BF21" s="189" cm="1">
         <f t="array" ref="BF21">MAX(FREQUENCY(IF((B21:BC21=INT(B21:BC21))*(B21:BC21&gt;0),COLUMN(B21:BC21)),IF((B21:BC21&lt;&gt;INT(B21:BC21))+(B21:BC21&lt;=0),COLUMN(B21:BC21))))</f>
         <v>1</v>
       </c>
-      <c r="BG21" s="187" cm="1">
+      <c r="BG21" s="190" cm="1">
         <f t="array" ref="BG21">SUMPRODUCT(--(B21:AI21=INT(B21:AI21)),--(B21:AI21&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH21" s="188">
+      <c r="BH21" s="191">
         <f t="shared" ref="BH21:BJ21" si="18">RANK(BD21,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI21" s="188">
+      <c r="BI21" s="191">
         <f t="shared" si="18"/>
         <v>29</v>
       </c>
-      <c r="BJ21" s="188">
+      <c r="BJ21" s="191">
         <f t="shared" si="18"/>
         <v>19</v>
       </c>
@@ -11381,37 +11438,37 @@
       <c r="BA22" s="120"/>
       <c r="BB22" s="120"/>
       <c r="BC22" s="120"/>
-      <c r="BD22" s="186">
+      <c r="BD22" s="189">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="BE22" s="186" cm="1">
+      <c r="BE22" s="189" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF22" s="186" cm="1">
+      <c r="BF22" s="189" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
         <v>4</v>
       </c>
-      <c r="BG22" s="187" cm="1">
+      <c r="BG22" s="190" cm="1">
         <f t="array" ref="BG22">SUMPRODUCT(--(B22:AI22=INT(B22:AI22)),--(B22:AI22&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH22" s="188">
+      <c r="BH22" s="191">
         <f t="shared" ref="BH22:BJ22" si="19">RANK(BD22,BD$3:BD$53,0)</f>
         <v>6</v>
       </c>
-      <c r="BI22" s="188">
+      <c r="BI22" s="191">
         <f t="shared" si="19"/>
         <v>7</v>
       </c>
-      <c r="BJ22" s="188">
+      <c r="BJ22" s="191">
         <f t="shared" si="19"/>
         <v>6</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:62">
-      <c r="A23" s="189">
+      <c r="A23" s="192">
         <v>21</v>
       </c>
       <c r="B23" s="120"/>
@@ -11468,31 +11525,31 @@
       <c r="BA23" s="120"/>
       <c r="BB23" s="120"/>
       <c r="BC23" s="120"/>
-      <c r="BD23" s="186">
+      <c r="BD23" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE23" s="186" cm="1">
+      <c r="BE23" s="189" cm="1">
         <f t="array" ref="BE23">SUMPRODUCT(--(B23:BC23=INT(B23:BC23)),--(B23:BC23&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF23" s="186" cm="1">
+      <c r="BF23" s="189" cm="1">
         <f t="array" ref="BF23">MAX(FREQUENCY(IF((B23:BC23=INT(B23:BC23))*(B23:BC23&gt;0),COLUMN(B23:BC23)),IF((B23:BC23&lt;&gt;INT(B23:BC23))+(B23:BC23&lt;=0),COLUMN(B23:BC23))))</f>
         <v>0</v>
       </c>
-      <c r="BG23" s="187" cm="1">
+      <c r="BG23" s="190" cm="1">
         <f t="array" ref="BG23">SUMPRODUCT(--(B23:AI23=INT(B23:AI23)),--(B23:AI23&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH23" s="188">
+      <c r="BH23" s="191">
         <f t="shared" ref="BH23:BJ23" si="20">RANK(BD23,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI23" s="188">
+      <c r="BI23" s="191">
         <f t="shared" si="20"/>
         <v>41</v>
       </c>
-      <c r="BJ23" s="188">
+      <c r="BJ23" s="191">
         <f t="shared" si="20"/>
         <v>41</v>
       </c>
@@ -11571,31 +11628,31 @@
       <c r="BA24" s="120"/>
       <c r="BB24" s="120"/>
       <c r="BC24" s="120"/>
-      <c r="BD24" s="186">
+      <c r="BD24" s="189">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="BE24" s="186" cm="1">
+      <c r="BE24" s="189" cm="1">
         <f t="array" ref="BE24">SUMPRODUCT(--(B24:BC24=INT(B24:BC24)),--(B24:BC24&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="BF24" s="186" cm="1">
+      <c r="BF24" s="189" cm="1">
         <f t="array" ref="BF24">MAX(FREQUENCY(IF((B24:BC24=INT(B24:BC24))*(B24:BC24&gt;0),COLUMN(B24:BC24)),IF((B24:BC24&lt;&gt;INT(B24:BC24))+(B24:BC24&lt;=0),COLUMN(B24:BC24))))</f>
         <v>3</v>
       </c>
-      <c r="BG24" s="187" cm="1">
+      <c r="BG24" s="190" cm="1">
         <f t="array" ref="BG24">SUMPRODUCT(--(B24:AI24=INT(B24:AI24)),--(B24:AI24&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH24" s="188">
+      <c r="BH24" s="191">
         <f t="shared" ref="BH24:BJ24" si="21">RANK(BD24,BD$3:BD$53,0)</f>
         <v>16</v>
       </c>
-      <c r="BI24" s="188">
+      <c r="BI24" s="191">
         <f t="shared" si="21"/>
         <v>16</v>
       </c>
-      <c r="BJ24" s="188">
+      <c r="BJ24" s="191">
         <f t="shared" si="21"/>
         <v>8</v>
       </c>
@@ -11660,37 +11717,37 @@
       <c r="BA25" s="120"/>
       <c r="BB25" s="120"/>
       <c r="BC25" s="120"/>
-      <c r="BD25" s="186">
+      <c r="BD25" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE25" s="186" cm="1">
+      <c r="BE25" s="189" cm="1">
         <f t="array" ref="BE25">SUMPRODUCT(--(B25:BC25=INT(B25:BC25)),--(B25:BC25&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF25" s="186" cm="1">
+      <c r="BF25" s="189" cm="1">
         <f t="array" ref="BF25">MAX(FREQUENCY(IF((B25:BC25=INT(B25:BC25))*(B25:BC25&gt;0),COLUMN(B25:BC25)),IF((B25:BC25&lt;&gt;INT(B25:BC25))+(B25:BC25&lt;=0),COLUMN(B25:BC25))))</f>
         <v>1</v>
       </c>
-      <c r="BG25" s="187" cm="1">
+      <c r="BG25" s="190" cm="1">
         <f t="array" ref="BG25">SUMPRODUCT(--(B25:AI25=INT(B25:AI25)),--(B25:AI25&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH25" s="188">
+      <c r="BH25" s="191">
         <f t="shared" ref="BH25:BJ25" si="22">RANK(BD25,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI25" s="188">
+      <c r="BI25" s="191">
         <f t="shared" si="22"/>
         <v>34</v>
       </c>
-      <c r="BJ25" s="188">
+      <c r="BJ25" s="191">
         <f t="shared" si="22"/>
         <v>19</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:62">
-      <c r="A26" s="189">
+      <c r="A26" s="192">
         <v>24</v>
       </c>
       <c r="B26" s="120"/>
@@ -11747,37 +11804,37 @@
       <c r="BA26" s="120"/>
       <c r="BB26" s="120"/>
       <c r="BC26" s="120"/>
-      <c r="BD26" s="186">
+      <c r="BD26" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="186" cm="1">
+      <c r="BE26" s="189" cm="1">
         <f t="array" ref="BE26">SUMPRODUCT(--(B26:BC26=INT(B26:BC26)),--(B26:BC26&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF26" s="186" cm="1">
+      <c r="BF26" s="189" cm="1">
         <f t="array" ref="BF26">MAX(FREQUENCY(IF((B26:BC26=INT(B26:BC26))*(B26:BC26&gt;0),COLUMN(B26:BC26)),IF((B26:BC26&lt;&gt;INT(B26:BC26))+(B26:BC26&lt;=0),COLUMN(B26:BC26))))</f>
         <v>0</v>
       </c>
-      <c r="BG26" s="187" cm="1">
+      <c r="BG26" s="190" cm="1">
         <f t="array" ref="BG26">SUMPRODUCT(--(B26:AI26=INT(B26:AI26)),--(B26:AI26&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH26" s="188">
+      <c r="BH26" s="191">
         <f t="shared" ref="BH26:BJ26" si="23">RANK(BD26,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI26" s="188">
+      <c r="BI26" s="191">
         <f t="shared" si="23"/>
         <v>41</v>
       </c>
-      <c r="BJ26" s="188">
+      <c r="BJ26" s="191">
         <f t="shared" si="23"/>
         <v>41</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:62">
-      <c r="A27" s="189">
+      <c r="A27" s="192">
         <v>25</v>
       </c>
       <c r="B27" s="120"/>
@@ -11834,31 +11891,31 @@
       <c r="BA27" s="120"/>
       <c r="BB27" s="120"/>
       <c r="BC27" s="120"/>
-      <c r="BD27" s="186">
+      <c r="BD27" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE27" s="186" cm="1">
+      <c r="BE27" s="189" cm="1">
         <f t="array" ref="BE27">SUMPRODUCT(--(B27:BC27=INT(B27:BC27)),--(B27:BC27&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF27" s="186" cm="1">
+      <c r="BF27" s="189" cm="1">
         <f t="array" ref="BF27">MAX(FREQUENCY(IF((B27:BC27=INT(B27:BC27))*(B27:BC27&gt;0),COLUMN(B27:BC27)),IF((B27:BC27&lt;&gt;INT(B27:BC27))+(B27:BC27&lt;=0),COLUMN(B27:BC27))))</f>
         <v>0</v>
       </c>
-      <c r="BG27" s="187" cm="1">
+      <c r="BG27" s="190" cm="1">
         <f t="array" ref="BG27">SUMPRODUCT(--(B27:AI27=INT(B27:AI27)),--(B27:AI27&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH27" s="188">
+      <c r="BH27" s="191">
         <f t="shared" ref="BH27:BJ27" si="24">RANK(BD27,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI27" s="188">
+      <c r="BI27" s="191">
         <f t="shared" si="24"/>
         <v>41</v>
       </c>
-      <c r="BJ27" s="188">
+      <c r="BJ27" s="191">
         <f t="shared" si="24"/>
         <v>41</v>
       </c>
@@ -11939,31 +11996,31 @@
       <c r="BA28" s="120"/>
       <c r="BB28" s="120"/>
       <c r="BC28" s="120"/>
-      <c r="BD28" s="186">
+      <c r="BD28" s="189">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="BE28" s="186" cm="1">
+      <c r="BE28" s="189" cm="1">
         <f t="array" ref="BE28">SUMPRODUCT(--(B28:BC28=INT(B28:BC28)),--(B28:BC28&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="BF28" s="186" cm="1">
+      <c r="BF28" s="189" cm="1">
         <f t="array" ref="BF28">MAX(FREQUENCY(IF((B28:BC28=INT(B28:BC28))*(B28:BC28&gt;0),COLUMN(B28:BC28)),IF((B28:BC28&lt;&gt;INT(B28:BC28))+(B28:BC28&lt;=0),COLUMN(B28:BC28))))</f>
         <v>2</v>
       </c>
-      <c r="BG28" s="187" cm="1">
+      <c r="BG28" s="190" cm="1">
         <f t="array" ref="BG28">SUMPRODUCT(--(B28:AI28=INT(B28:AI28)),--(B28:AI28&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH28" s="188">
+      <c r="BH28" s="191">
         <f t="shared" ref="BH28:BJ28" si="25">RANK(BD28,BD$3:BD$53,0)</f>
         <v>14</v>
       </c>
-      <c r="BI28" s="188">
+      <c r="BI28" s="191">
         <f t="shared" si="25"/>
-        <v>12</v>
-      </c>
-      <c r="BJ28" s="188">
+        <v>13</v>
+      </c>
+      <c r="BJ28" s="191">
         <f t="shared" si="25"/>
         <v>13</v>
       </c>
@@ -12036,31 +12093,31 @@
       <c r="BA29" s="120"/>
       <c r="BB29" s="120"/>
       <c r="BC29" s="120"/>
-      <c r="BD29" s="186">
+      <c r="BD29" s="189">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE29" s="186" cm="1">
+      <c r="BE29" s="189" cm="1">
         <f t="array" ref="BE29">SUMPRODUCT(--(B29:BC29=INT(B29:BC29)),--(B29:BC29&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF29" s="186" cm="1">
+      <c r="BF29" s="189" cm="1">
         <f t="array" ref="BF29">MAX(FREQUENCY(IF((B29:BC29=INT(B29:BC29))*(B29:BC29&gt;0),COLUMN(B29:BC29)),IF((B29:BC29&lt;&gt;INT(B29:BC29))+(B29:BC29&lt;=0),COLUMN(B29:BC29))))</f>
         <v>1</v>
       </c>
-      <c r="BG29" s="187" cm="1">
+      <c r="BG29" s="190" cm="1">
         <f t="array" ref="BG29">SUMPRODUCT(--(B29:AI29=INT(B29:AI29)),--(B29:AI29&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH29" s="188">
+      <c r="BH29" s="191">
         <f t="shared" ref="BH29:BJ29" si="26">RANK(BD29,BD$3:BD$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BI29" s="188">
+      <c r="BI29" s="191">
         <f t="shared" si="26"/>
         <v>20</v>
       </c>
-      <c r="BJ29" s="188">
+      <c r="BJ29" s="191">
         <f t="shared" si="26"/>
         <v>19</v>
       </c>
@@ -12137,31 +12194,31 @@
       <c r="BA30" s="120"/>
       <c r="BB30" s="120"/>
       <c r="BC30" s="120"/>
-      <c r="BD30" s="186">
+      <c r="BD30" s="189">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="BE30" s="186" cm="1">
+      <c r="BE30" s="189" cm="1">
         <f t="array" ref="BE30">SUMPRODUCT(--(B30:BC30=INT(B30:BC30)),--(B30:BC30&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF30" s="186" cm="1">
+      <c r="BF30" s="189" cm="1">
         <f t="array" ref="BF30">MAX(FREQUENCY(IF((B30:BC30=INT(B30:BC30))*(B30:BC30&gt;0),COLUMN(B30:BC30)),IF((B30:BC30&lt;&gt;INT(B30:BC30))+(B30:BC30&lt;=0),COLUMN(B30:BC30))))</f>
         <v>4</v>
       </c>
-      <c r="BG30" s="187" cm="1">
+      <c r="BG30" s="190" cm="1">
         <f t="array" ref="BG30">SUMPRODUCT(--(B30:AI30=INT(B30:AI30)),--(B30:AI30&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH30" s="188">
+      <c r="BH30" s="191">
         <f t="shared" ref="BH30:BJ30" si="27">RANK(BD30,BD$3:BD$53,0)</f>
         <v>16</v>
       </c>
-      <c r="BI30" s="188">
+      <c r="BI30" s="191">
         <f t="shared" si="27"/>
         <v>17</v>
       </c>
-      <c r="BJ30" s="188">
+      <c r="BJ30" s="191">
         <f t="shared" si="27"/>
         <v>6</v>
       </c>
@@ -12242,31 +12299,31 @@
       <c r="BA31" s="120"/>
       <c r="BB31" s="120"/>
       <c r="BC31" s="120"/>
-      <c r="BD31" s="186">
+      <c r="BD31" s="189">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="BE31" s="186" cm="1">
+      <c r="BE31" s="189" cm="1">
         <f t="array" ref="BE31">SUMPRODUCT(--(B31:BC31=INT(B31:BC31)),--(B31:BC31&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="BF31" s="186" cm="1">
+      <c r="BF31" s="189" cm="1">
         <f t="array" ref="BF31">MAX(FREQUENCY(IF((B31:BC31=INT(B31:BC31))*(B31:BC31&gt;0),COLUMN(B31:BC31)),IF((B31:BC31&lt;&gt;INT(B31:BC31))+(B31:BC31&lt;=0),COLUMN(B31:BC31))))</f>
         <v>2</v>
       </c>
-      <c r="BG31" s="187" cm="1">
+      <c r="BG31" s="190" cm="1">
         <f t="array" ref="BG31">SUMPRODUCT(--(B31:AI31=INT(B31:AI31)),--(B31:AI31&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH31" s="188">
+      <c r="BH31" s="191">
         <f t="shared" ref="BH31:BJ31" si="28">RANK(BD31,BD$3:BD$53,0)</f>
-        <v>11</v>
-      </c>
-      <c r="BI31" s="188">
+        <v>12</v>
+      </c>
+      <c r="BI31" s="191">
         <f t="shared" si="28"/>
-        <v>12</v>
-      </c>
-      <c r="BJ31" s="188">
+        <v>13</v>
+      </c>
+      <c r="BJ31" s="191">
         <f t="shared" si="28"/>
         <v>13</v>
       </c>
@@ -12349,31 +12406,31 @@
       <c r="BA32" s="120"/>
       <c r="BB32" s="120"/>
       <c r="BC32" s="120"/>
-      <c r="BD32" s="186">
+      <c r="BD32" s="189">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="BE32" s="186" cm="1">
+      <c r="BE32" s="189" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BF32" s="186" cm="1">
+      <c r="BF32" s="189" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
         <v>3</v>
       </c>
-      <c r="BG32" s="187" cm="1">
+      <c r="BG32" s="190" cm="1">
         <f t="array" ref="BG32">SUMPRODUCT(--(B32:AI32=INT(B32:AI32)),--(B32:AI32&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH32" s="188">
+      <c r="BH32" s="191">
         <f t="shared" ref="BH32:BJ32" si="29">RANK(BD32,BD$3:BD$53,0)</f>
         <v>10</v>
       </c>
-      <c r="BI32" s="188">
+      <c r="BI32" s="191">
         <f t="shared" si="29"/>
         <v>9</v>
       </c>
-      <c r="BJ32" s="188">
+      <c r="BJ32" s="191">
         <f t="shared" si="29"/>
         <v>8</v>
       </c>
@@ -12444,37 +12501,37 @@
       <c r="BA33" s="120"/>
       <c r="BB33" s="120"/>
       <c r="BC33" s="120"/>
-      <c r="BD33" s="186">
+      <c r="BD33" s="189">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE33" s="186" cm="1">
+      <c r="BE33" s="189" cm="1">
         <f t="array" ref="BE33">SUMPRODUCT(--(B33:BC33=INT(B33:BC33)),--(B33:BC33&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF33" s="186" cm="1">
+      <c r="BF33" s="189" cm="1">
         <f t="array" ref="BF33">MAX(FREQUENCY(IF((B33:BC33=INT(B33:BC33))*(B33:BC33&gt;0),COLUMN(B33:BC33)),IF((B33:BC33&lt;&gt;INT(B33:BC33))+(B33:BC33&lt;=0),COLUMN(B33:BC33))))</f>
         <v>1</v>
       </c>
-      <c r="BG33" s="187" cm="1">
+      <c r="BG33" s="190" cm="1">
         <f t="array" ref="BG33">SUMPRODUCT(--(B33:AI33=INT(B33:AI33)),--(B33:AI33&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH33" s="188">
+      <c r="BH33" s="191">
         <f t="shared" ref="BH33:BJ33" si="30">RANK(BD33,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI33" s="188">
+      <c r="BI33" s="191">
         <f t="shared" si="30"/>
         <v>23</v>
       </c>
-      <c r="BJ33" s="188">
+      <c r="BJ33" s="191">
         <f t="shared" si="30"/>
         <v>19</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:62">
-      <c r="A34" s="189">
+      <c r="A34" s="192">
         <v>32</v>
       </c>
       <c r="B34" s="120"/>
@@ -12531,37 +12588,37 @@
       <c r="BA34" s="120"/>
       <c r="BB34" s="120"/>
       <c r="BC34" s="120"/>
-      <c r="BD34" s="186">
+      <c r="BD34" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE34" s="186" cm="1">
+      <c r="BE34" s="189" cm="1">
         <f t="array" ref="BE34">SUMPRODUCT(--(B34:BC34=INT(B34:BC34)),--(B34:BC34&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF34" s="186" cm="1">
+      <c r="BF34" s="189" cm="1">
         <f t="array" ref="BF34">MAX(FREQUENCY(IF((B34:BC34=INT(B34:BC34))*(B34:BC34&gt;0),COLUMN(B34:BC34)),IF((B34:BC34&lt;&gt;INT(B34:BC34))+(B34:BC34&lt;=0),COLUMN(B34:BC34))))</f>
         <v>0</v>
       </c>
-      <c r="BG34" s="187" cm="1">
+      <c r="BG34" s="190" cm="1">
         <f t="array" ref="BG34">SUMPRODUCT(--(B34:AI34=INT(B34:AI34)),--(B34:AI34&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH34" s="188">
+      <c r="BH34" s="191">
         <f t="shared" ref="BH34:BJ34" si="31">RANK(BD34,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI34" s="188">
+      <c r="BI34" s="191">
         <f t="shared" si="31"/>
         <v>41</v>
       </c>
-      <c r="BJ34" s="188">
+      <c r="BJ34" s="191">
         <f t="shared" si="31"/>
         <v>41</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:62">
-      <c r="A35" s="189">
+      <c r="A35" s="192">
         <v>33</v>
       </c>
       <c r="B35" s="120"/>
@@ -12618,31 +12675,31 @@
       <c r="BA35" s="120"/>
       <c r="BB35" s="120"/>
       <c r="BC35" s="120"/>
-      <c r="BD35" s="186">
+      <c r="BD35" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="186" cm="1">
+      <c r="BE35" s="189" cm="1">
         <f t="array" ref="BE35">SUMPRODUCT(--(B35:BC35=INT(B35:BC35)),--(B35:BC35&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF35" s="186" cm="1">
+      <c r="BF35" s="189" cm="1">
         <f t="array" ref="BF35">MAX(FREQUENCY(IF((B35:BC35=INT(B35:BC35))*(B35:BC35&gt;0),COLUMN(B35:BC35)),IF((B35:BC35&lt;&gt;INT(B35:BC35))+(B35:BC35&lt;=0),COLUMN(B35:BC35))))</f>
         <v>0</v>
       </c>
-      <c r="BG35" s="187" cm="1">
+      <c r="BG35" s="190" cm="1">
         <f t="array" ref="BG35">SUMPRODUCT(--(B35:AI35=INT(B35:AI35)),--(B35:AI35&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH35" s="188">
+      <c r="BH35" s="191">
         <f t="shared" ref="BH35:BJ35" si="32">RANK(BD35,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI35" s="188">
+      <c r="BI35" s="191">
         <f t="shared" si="32"/>
         <v>41</v>
       </c>
-      <c r="BJ35" s="188">
+      <c r="BJ35" s="191">
         <f t="shared" si="32"/>
         <v>41</v>
       </c>
@@ -12707,31 +12764,31 @@
       <c r="BA36" s="120"/>
       <c r="BB36" s="120"/>
       <c r="BC36" s="120"/>
-      <c r="BD36" s="186">
+      <c r="BD36" s="189">
         <f t="shared" ref="BD36:BD53" si="33">SUM(B36:BC36)</f>
         <v>1</v>
       </c>
-      <c r="BE36" s="186" cm="1">
+      <c r="BE36" s="189" cm="1">
         <f t="array" ref="BE36">SUMPRODUCT(--(B36:BC36=INT(B36:BC36)),--(B36:BC36&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF36" s="186" cm="1">
+      <c r="BF36" s="189" cm="1">
         <f t="array" ref="BF36">MAX(FREQUENCY(IF((B36:BC36=INT(B36:BC36))*(B36:BC36&gt;0),COLUMN(B36:BC36)),IF((B36:BC36&lt;&gt;INT(B36:BC36))+(B36:BC36&lt;=0),COLUMN(B36:BC36))))</f>
         <v>1</v>
       </c>
-      <c r="BG36" s="187" cm="1">
+      <c r="BG36" s="190" cm="1">
         <f t="array" ref="BG36">SUMPRODUCT(--(B36:AI36=INT(B36:AI36)),--(B36:AI36&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH36" s="188">
+      <c r="BH36" s="191">
         <f t="shared" ref="BH36:BJ36" si="34">RANK(BD36,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI36" s="188">
+      <c r="BI36" s="191">
         <f t="shared" si="34"/>
         <v>34</v>
       </c>
-      <c r="BJ36" s="188">
+      <c r="BJ36" s="191">
         <f t="shared" si="34"/>
         <v>19</v>
       </c>
@@ -12808,31 +12865,31 @@
       <c r="BA37" s="120"/>
       <c r="BB37" s="120"/>
       <c r="BC37" s="120"/>
-      <c r="BD37" s="186">
+      <c r="BD37" s="189">
         <f t="shared" si="33"/>
         <v>8</v>
       </c>
-      <c r="BE37" s="186" cm="1">
+      <c r="BE37" s="189" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF37" s="186" cm="1">
+      <c r="BF37" s="189" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
         <v>3</v>
       </c>
-      <c r="BG37" s="187" cm="1">
+      <c r="BG37" s="190" cm="1">
         <f t="array" ref="BG37">SUMPRODUCT(--(B37:AI37=INT(B37:AI37)),--(B37:AI37&gt;0))/34*100%</f>
         <v>0.176470588235294</v>
       </c>
-      <c r="BH37" s="188">
+      <c r="BH37" s="191">
         <f t="shared" ref="BH37:BJ37" si="35">RANK(BD37,BD$3:BD$53,0)</f>
         <v>16</v>
       </c>
-      <c r="BI37" s="188">
+      <c r="BI37" s="191">
         <f t="shared" si="35"/>
         <v>17</v>
       </c>
-      <c r="BJ37" s="188">
+      <c r="BJ37" s="191">
         <f t="shared" si="35"/>
         <v>8</v>
       </c>
@@ -12901,31 +12958,31 @@
       <c r="BA38" s="120"/>
       <c r="BB38" s="120"/>
       <c r="BC38" s="120"/>
-      <c r="BD38" s="186">
+      <c r="BD38" s="189">
         <f t="shared" si="33"/>
         <v>4</v>
       </c>
-      <c r="BE38" s="186" cm="1">
+      <c r="BE38" s="189" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(--(B38:BC38=INT(B38:BC38)),--(B38:BC38&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF38" s="186" cm="1">
+      <c r="BF38" s="189" cm="1">
         <f t="array" ref="BF38">MAX(FREQUENCY(IF((B38:BC38=INT(B38:BC38))*(B38:BC38&gt;0),COLUMN(B38:BC38)),IF((B38:BC38&lt;&gt;INT(B38:BC38))+(B38:BC38&lt;=0),COLUMN(B38:BC38))))</f>
         <v>1</v>
       </c>
-      <c r="BG38" s="187" cm="1">
+      <c r="BG38" s="190" cm="1">
         <f t="array" ref="BG38">SUMPRODUCT(--(B38:AI38=INT(B38:AI38)),--(B38:AI38&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH38" s="188">
+      <c r="BH38" s="191">
         <f t="shared" ref="BH38:BJ38" si="36">RANK(BD38,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI38" s="188">
+      <c r="BI38" s="191">
         <f t="shared" si="36"/>
         <v>26</v>
       </c>
-      <c r="BJ38" s="188">
+      <c r="BJ38" s="191">
         <f t="shared" si="36"/>
         <v>19</v>
       </c>
@@ -12988,31 +13045,31 @@
       <c r="BA39" s="175"/>
       <c r="BB39" s="175"/>
       <c r="BC39" s="175"/>
-      <c r="BD39" s="186">
+      <c r="BD39" s="189">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BE39" s="186" cm="1">
+      <c r="BE39" s="189" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(--(B39:BC39=INT(B39:BC39)),--(B39:BC39&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF39" s="186" cm="1">
+      <c r="BF39" s="189" cm="1">
         <f t="array" ref="BF39">MAX(FREQUENCY(IF((B39:BC39=INT(B39:BC39))*(B39:BC39&gt;0),COLUMN(B39:BC39)),IF((B39:BC39&lt;&gt;INT(B39:BC39))+(B39:BC39&lt;=0),COLUMN(B39:BC39))))</f>
         <v>0</v>
       </c>
-      <c r="BG39" s="187" cm="1">
+      <c r="BG39" s="190" cm="1">
         <f t="array" ref="BG39">SUMPRODUCT(--(B39:AI39=INT(B39:AI39)),--(B39:AI39&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH39" s="190">
+      <c r="BH39" s="193">
         <f t="shared" ref="BH39:BJ39" si="37">RANK(BD39,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI39" s="190">
+      <c r="BI39" s="193">
         <f t="shared" si="37"/>
         <v>41</v>
       </c>
-      <c r="BJ39" s="190">
+      <c r="BJ39" s="193">
         <f t="shared" si="37"/>
         <v>41</v>
       </c>
@@ -13121,31 +13178,31 @@
       <c r="BA40" s="120"/>
       <c r="BB40" s="120"/>
       <c r="BC40" s="120"/>
-      <c r="BD40" s="186">
+      <c r="BD40" s="189">
         <f t="shared" si="33"/>
         <v>27</v>
       </c>
-      <c r="BE40" s="186" cm="1">
+      <c r="BE40" s="189" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
         <v>23</v>
       </c>
-      <c r="BF40" s="186" cm="1">
+      <c r="BF40" s="189" cm="1">
         <f t="array" ref="BF40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
         <v>12</v>
       </c>
-      <c r="BG40" s="187" cm="1">
+      <c r="BG40" s="190" cm="1">
         <f t="array" ref="BG40">SUMPRODUCT(--(B40:AI40=INT(B40:AI40)),--(B40:AI40&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH40" s="188">
+      <c r="BH40" s="191">
         <f t="shared" ref="BH40:BJ40" si="38">RANK(BD40,BD$3:BD$53,0)</f>
         <v>2</v>
       </c>
-      <c r="BI40" s="188">
+      <c r="BI40" s="191">
         <f t="shared" si="38"/>
         <v>1</v>
       </c>
-      <c r="BJ40" s="188">
+      <c r="BJ40" s="191">
         <f t="shared" si="38"/>
         <v>1</v>
       </c>
@@ -13228,31 +13285,31 @@
       <c r="BA41" s="120"/>
       <c r="BB41" s="120"/>
       <c r="BC41" s="120"/>
-      <c r="BD41" s="186">
+      <c r="BD41" s="189">
         <f t="shared" si="33"/>
         <v>13</v>
       </c>
-      <c r="BE41" s="186" cm="1">
+      <c r="BE41" s="189" cm="1">
         <f t="array" ref="BE41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BF41" s="186" cm="1">
+      <c r="BF41" s="189" cm="1">
         <f t="array" ref="BF41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
         <v>2</v>
       </c>
-      <c r="BG41" s="187" cm="1">
+      <c r="BG41" s="190" cm="1">
         <f t="array" ref="BG41">SUMPRODUCT(--(B41:AI41=INT(B41:AI41)),--(B41:AI41&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH41" s="188">
+      <c r="BH41" s="191">
         <f t="shared" ref="BH41:BJ41" si="39">RANK(BD41,BD$3:BD$53,0)</f>
         <v>7</v>
       </c>
-      <c r="BI41" s="188">
+      <c r="BI41" s="191">
         <f t="shared" si="39"/>
         <v>9</v>
       </c>
-      <c r="BJ41" s="188">
+      <c r="BJ41" s="191">
         <f t="shared" si="39"/>
         <v>13</v>
       </c>
@@ -13343,37 +13400,37 @@
       <c r="BA42" s="120"/>
       <c r="BB42" s="120"/>
       <c r="BC42" s="120"/>
-      <c r="BD42" s="186">
+      <c r="BD42" s="189">
         <f t="shared" si="33"/>
         <v>17</v>
       </c>
-      <c r="BE42" s="186" cm="1">
+      <c r="BE42" s="189" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
         <v>14</v>
       </c>
-      <c r="BF42" s="186" cm="1">
+      <c r="BF42" s="189" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
         <v>5</v>
       </c>
-      <c r="BG42" s="187" cm="1">
+      <c r="BG42" s="190" cm="1">
         <f t="array" ref="BG42">SUMPRODUCT(--(B42:AI42=INT(B42:AI42)),--(B42:AI42&gt;0))/34*100%</f>
         <v>0.352941176470588</v>
       </c>
-      <c r="BH42" s="188">
+      <c r="BH42" s="191">
         <f t="shared" ref="BH42:BJ42" si="40">RANK(BD42,BD$3:BD$53,0)</f>
         <v>4</v>
       </c>
-      <c r="BI42" s="188">
+      <c r="BI42" s="191">
         <f t="shared" si="40"/>
         <v>4</v>
       </c>
-      <c r="BJ42" s="188">
+      <c r="BJ42" s="191">
         <f t="shared" si="40"/>
         <v>3</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:62">
-      <c r="A43" s="189">
+      <c r="A43" s="192">
         <v>41</v>
       </c>
       <c r="B43" s="120"/>
@@ -13430,31 +13487,31 @@
       <c r="BA43" s="120"/>
       <c r="BB43" s="120"/>
       <c r="BC43" s="120"/>
-      <c r="BD43" s="186">
+      <c r="BD43" s="189">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BE43" s="186" cm="1">
+      <c r="BE43" s="189" cm="1">
         <f t="array" ref="BE43">SUMPRODUCT(--(B43:BC43=INT(B43:BC43)),--(B43:BC43&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF43" s="186" cm="1">
+      <c r="BF43" s="189" cm="1">
         <f t="array" ref="BF43">MAX(FREQUENCY(IF((B43:BC43=INT(B43:BC43))*(B43:BC43&gt;0),COLUMN(B43:BC43)),IF((B43:BC43&lt;&gt;INT(B43:BC43))+(B43:BC43&lt;=0),COLUMN(B43:BC43))))</f>
         <v>0</v>
       </c>
-      <c r="BG43" s="187" cm="1">
+      <c r="BG43" s="190" cm="1">
         <f t="array" ref="BG43">SUMPRODUCT(--(B43:AI43=INT(B43:AI43)),--(B43:AI43&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH43" s="188">
+      <c r="BH43" s="191">
         <f t="shared" ref="BH43:BJ43" si="41">RANK(BD43,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI43" s="188">
+      <c r="BI43" s="191">
         <f t="shared" si="41"/>
         <v>41</v>
       </c>
-      <c r="BJ43" s="188">
+      <c r="BJ43" s="191">
         <f t="shared" si="41"/>
         <v>41</v>
       </c>
@@ -13545,37 +13602,37 @@
       <c r="BA44" s="120"/>
       <c r="BB44" s="120"/>
       <c r="BC44" s="120"/>
-      <c r="BD44" s="186">
+      <c r="BD44" s="189">
         <f t="shared" si="33"/>
         <v>17</v>
       </c>
-      <c r="BE44" s="186" cm="1">
+      <c r="BE44" s="189" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
         <v>14</v>
       </c>
-      <c r="BF44" s="186" cm="1">
+      <c r="BF44" s="189" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
         <v>5</v>
       </c>
-      <c r="BG44" s="187" cm="1">
+      <c r="BG44" s="190" cm="1">
         <f t="array" ref="BG44">SUMPRODUCT(--(B44:AI44=INT(B44:AI44)),--(B44:AI44&gt;0))/34*100%</f>
         <v>0.411764705882353</v>
       </c>
-      <c r="BH44" s="188">
+      <c r="BH44" s="191">
         <f t="shared" ref="BH44:BJ44" si="42">RANK(BD44,BD$3:BD$53,0)</f>
         <v>4</v>
       </c>
-      <c r="BI44" s="188">
+      <c r="BI44" s="191">
         <f t="shared" si="42"/>
         <v>4</v>
       </c>
-      <c r="BJ44" s="188">
+      <c r="BJ44" s="191">
         <f t="shared" si="42"/>
         <v>3</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:62">
-      <c r="A45" s="189">
+      <c r="A45" s="192">
         <v>43</v>
       </c>
       <c r="B45" s="120"/>
@@ -13632,31 +13689,31 @@
       <c r="BA45" s="120"/>
       <c r="BB45" s="120"/>
       <c r="BC45" s="120"/>
-      <c r="BD45" s="186">
+      <c r="BD45" s="189">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BE45" s="186" cm="1">
+      <c r="BE45" s="189" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(--(B45:BC45=INT(B45:BC45)),--(B45:BC45&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF45" s="186" cm="1">
+      <c r="BF45" s="189" cm="1">
         <f t="array" ref="BF45">MAX(FREQUENCY(IF((B45:BC45=INT(B45:BC45))*(B45:BC45&gt;0),COLUMN(B45:BC45)),IF((B45:BC45&lt;&gt;INT(B45:BC45))+(B45:BC45&lt;=0),COLUMN(B45:BC45))))</f>
         <v>0</v>
       </c>
-      <c r="BG45" s="187" cm="1">
+      <c r="BG45" s="190" cm="1">
         <f t="array" ref="BG45">SUMPRODUCT(--(B45:AI45=INT(B45:AI45)),--(B45:AI45&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH45" s="188">
+      <c r="BH45" s="191">
         <f t="shared" ref="BH45:BJ45" si="43">RANK(BD45,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI45" s="188">
+      <c r="BI45" s="191">
         <f t="shared" si="43"/>
         <v>41</v>
       </c>
-      <c r="BJ45" s="188">
+      <c r="BJ45" s="191">
         <f t="shared" si="43"/>
         <v>41</v>
       </c>
@@ -13746,7 +13803,9 @@
       </c>
       <c r="AK46" s="120"/>
       <c r="AL46" s="120"/>
-      <c r="AM46" s="120"/>
+      <c r="AM46" s="120">
+        <v>1</v>
+      </c>
       <c r="AN46" s="120"/>
       <c r="AO46" s="120"/>
       <c r="AP46" s="120"/>
@@ -13763,37 +13822,37 @@
       <c r="BA46" s="120"/>
       <c r="BB46" s="120"/>
       <c r="BC46" s="120"/>
-      <c r="BD46" s="186">
+      <c r="BD46" s="189">
         <f t="shared" si="33"/>
-        <v>31</v>
-      </c>
-      <c r="BE46" s="186" cm="1">
+        <v>32</v>
+      </c>
+      <c r="BE46" s="189" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>22</v>
-      </c>
-      <c r="BF46" s="186" cm="1">
+        <v>23</v>
+      </c>
+      <c r="BF46" s="189" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
         <v>8</v>
       </c>
-      <c r="BG46" s="187" cm="1">
+      <c r="BG46" s="190" cm="1">
         <f t="array" ref="BG46">SUMPRODUCT(--(B46:AI46=INT(B46:AI46)),--(B46:AI46&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH46" s="188">
+      <c r="BH46" s="191">
         <f t="shared" ref="BH46:BJ46" si="44">RANK(BD46,BD$3:BD$53,0)</f>
         <v>1</v>
       </c>
-      <c r="BI46" s="188">
+      <c r="BI46" s="191">
+        <f t="shared" si="44"/>
+        <v>1</v>
+      </c>
+      <c r="BJ46" s="191">
         <f t="shared" si="44"/>
         <v>2</v>
       </c>
-      <c r="BJ46" s="188">
-        <f t="shared" si="44"/>
-        <v>2</v>
-      </c>
     </row>
     <row r="47" customHeight="1" spans="1:62">
-      <c r="A47" s="189">
+      <c r="A47" s="192">
         <v>45</v>
       </c>
       <c r="B47" s="120"/>
@@ -13850,31 +13909,31 @@
       <c r="BA47" s="120"/>
       <c r="BB47" s="120"/>
       <c r="BC47" s="120"/>
-      <c r="BD47" s="186">
+      <c r="BD47" s="189">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BE47" s="186" cm="1">
+      <c r="BE47" s="189" cm="1">
         <f t="array" ref="BE47">SUMPRODUCT(--(B47:BC47=INT(B47:BC47)),--(B47:BC47&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF47" s="186" cm="1">
+      <c r="BF47" s="189" cm="1">
         <f t="array" ref="BF47">MAX(FREQUENCY(IF((B47:BC47=INT(B47:BC47))*(B47:BC47&gt;0),COLUMN(B47:BC47)),IF((B47:BC47&lt;&gt;INT(B47:BC47))+(B47:BC47&lt;=0),COLUMN(B47:BC47))))</f>
         <v>0</v>
       </c>
-      <c r="BG47" s="187" cm="1">
+      <c r="BG47" s="190" cm="1">
         <f t="array" ref="BG47">SUMPRODUCT(--(B47:AI47=INT(B47:AI47)),--(B47:AI47&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH47" s="188">
+      <c r="BH47" s="191">
         <f t="shared" ref="BH47:BJ47" si="45">RANK(BD47,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI47" s="188">
+      <c r="BI47" s="191">
         <f t="shared" si="45"/>
         <v>41</v>
       </c>
-      <c r="BJ47" s="188">
+      <c r="BJ47" s="191">
         <f t="shared" si="45"/>
         <v>41</v>
       </c>
@@ -13957,31 +14016,31 @@
       <c r="BA48" s="120"/>
       <c r="BB48" s="120"/>
       <c r="BC48" s="120"/>
-      <c r="BD48" s="186">
+      <c r="BD48" s="189">
         <f t="shared" si="33"/>
         <v>10</v>
       </c>
-      <c r="BE48" s="186" cm="1">
+      <c r="BE48" s="189" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BF48" s="186" cm="1">
+      <c r="BF48" s="189" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
         <v>2</v>
       </c>
-      <c r="BG48" s="187" cm="1">
+      <c r="BG48" s="190" cm="1">
         <f t="array" ref="BG48">SUMPRODUCT(--(B48:AI48=INT(B48:AI48)),--(B48:AI48&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH48" s="188">
+      <c r="BH48" s="191">
         <f t="shared" ref="BH48:BJ48" si="46">RANK(BD48,BD$3:BD$53,0)</f>
-        <v>11</v>
-      </c>
-      <c r="BI48" s="188">
+        <v>12</v>
+      </c>
+      <c r="BI48" s="191">
         <f t="shared" si="46"/>
         <v>9</v>
       </c>
-      <c r="BJ48" s="188">
+      <c r="BJ48" s="191">
         <f t="shared" si="46"/>
         <v>13</v>
       </c>
@@ -14052,31 +14111,31 @@
       <c r="BA49" s="120"/>
       <c r="BB49" s="120"/>
       <c r="BC49" s="120"/>
-      <c r="BD49" s="186">
+      <c r="BD49" s="189">
         <f t="shared" si="33"/>
         <v>4</v>
       </c>
-      <c r="BE49" s="186" cm="1">
+      <c r="BE49" s="189" cm="1">
         <f t="array" ref="BE49">SUMPRODUCT(--(B49:BC49=INT(B49:BC49)),--(B49:BC49&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF49" s="186" cm="1">
+      <c r="BF49" s="189" cm="1">
         <f t="array" ref="BF49">MAX(FREQUENCY(IF((B49:BC49=INT(B49:BC49))*(B49:BC49&gt;0),COLUMN(B49:BC49)),IF((B49:BC49&lt;&gt;INT(B49:BC49))+(B49:BC49&lt;=0),COLUMN(B49:BC49))))</f>
         <v>1</v>
       </c>
-      <c r="BG49" s="187" cm="1">
+      <c r="BG49" s="190" cm="1">
         <f t="array" ref="BG49">SUMPRODUCT(--(B49:AI49=INT(B49:AI49)),--(B49:AI49&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH49" s="188">
+      <c r="BH49" s="191">
         <f t="shared" ref="BH49:BJ49" si="47">RANK(BD49,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI49" s="188">
+      <c r="BI49" s="191">
         <f t="shared" si="47"/>
         <v>23</v>
       </c>
-      <c r="BJ49" s="188">
+      <c r="BJ49" s="191">
         <f t="shared" si="47"/>
         <v>19</v>
       </c>
@@ -14149,37 +14208,37 @@
       <c r="BA50" s="120"/>
       <c r="BB50" s="120"/>
       <c r="BC50" s="120"/>
-      <c r="BD50" s="186">
+      <c r="BD50" s="189">
         <f t="shared" si="33"/>
         <v>5</v>
       </c>
-      <c r="BE50" s="186" cm="1">
+      <c r="BE50" s="189" cm="1">
         <f t="array" ref="BE50">SUMPRODUCT(--(B50:BC50=INT(B50:BC50)),--(B50:BC50&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF50" s="186" cm="1">
+      <c r="BF50" s="189" cm="1">
         <f t="array" ref="BF50">MAX(FREQUENCY(IF((B50:BC50=INT(B50:BC50))*(B50:BC50&gt;0),COLUMN(B50:BC50)),IF((B50:BC50&lt;&gt;INT(B50:BC50))+(B50:BC50&lt;=0),COLUMN(B50:BC50))))</f>
         <v>1</v>
       </c>
-      <c r="BG50" s="187" cm="1">
+      <c r="BG50" s="190" cm="1">
         <f t="array" ref="BG50">SUMPRODUCT(--(B50:AI50=INT(B50:AI50)),--(B50:AI50&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH50" s="188">
+      <c r="BH50" s="191">
         <f t="shared" ref="BH50:BJ50" si="48">RANK(BD50,BD$3:BD$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BI50" s="188">
+      <c r="BI50" s="191">
         <f t="shared" si="48"/>
         <v>20</v>
       </c>
-      <c r="BJ50" s="188">
+      <c r="BJ50" s="191">
         <f t="shared" si="48"/>
         <v>19</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:62">
-      <c r="A51" s="189">
+      <c r="A51" s="192">
         <v>49</v>
       </c>
       <c r="B51" s="120"/>
@@ -14236,37 +14295,37 @@
       <c r="BA51" s="120"/>
       <c r="BB51" s="120"/>
       <c r="BC51" s="120"/>
-      <c r="BD51" s="186">
+      <c r="BD51" s="189">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BE51" s="186" cm="1">
+      <c r="BE51" s="189" cm="1">
         <f t="array" ref="BE51">SUMPRODUCT(--(B51:BC51=INT(B51:BC51)),--(B51:BC51&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF51" s="186" cm="1">
+      <c r="BF51" s="189" cm="1">
         <f t="array" ref="BF51">MAX(FREQUENCY(IF((B51:BC51=INT(B51:BC51))*(B51:BC51&gt;0),COLUMN(B51:BC51)),IF((B51:BC51&lt;&gt;INT(B51:BC51))+(B51:BC51&lt;=0),COLUMN(B51:BC51))))</f>
         <v>0</v>
       </c>
-      <c r="BG51" s="187" cm="1">
+      <c r="BG51" s="190" cm="1">
         <f t="array" ref="BG51">SUMPRODUCT(--(B51:AI51=INT(B51:AI51)),--(B51:AI51&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH51" s="188">
+      <c r="BH51" s="191">
         <f t="shared" ref="BH51:BJ51" si="49">RANK(BD51,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI51" s="188">
+      <c r="BI51" s="191">
         <f t="shared" si="49"/>
         <v>41</v>
       </c>
-      <c r="BJ51" s="188">
+      <c r="BJ51" s="191">
         <f t="shared" si="49"/>
         <v>41</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:62">
-      <c r="A52" s="189">
+      <c r="A52" s="192">
         <v>50</v>
       </c>
       <c r="B52" s="120"/>
@@ -14323,31 +14382,31 @@
       <c r="BA52" s="120"/>
       <c r="BB52" s="120"/>
       <c r="BC52" s="120"/>
-      <c r="BD52" s="186">
+      <c r="BD52" s="189">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="BE52" s="186" cm="1">
+      <c r="BE52" s="189" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(--(B52:BC52=INT(B52:BC52)),--(B52:BC52&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF52" s="186" cm="1">
+      <c r="BF52" s="189" cm="1">
         <f t="array" ref="BF52">MAX(FREQUENCY(IF((B52:BC52=INT(B52:BC52))*(B52:BC52&gt;0),COLUMN(B52:BC52)),IF((B52:BC52&lt;&gt;INT(B52:BC52))+(B52:BC52&lt;=0),COLUMN(B52:BC52))))</f>
         <v>0</v>
       </c>
-      <c r="BG52" s="187" cm="1">
+      <c r="BG52" s="190" cm="1">
         <f t="array" ref="BG52">SUMPRODUCT(--(B52:AI52=INT(B52:AI52)),--(B52:AI52&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH52" s="188">
+      <c r="BH52" s="191">
         <f t="shared" ref="BH52:BJ52" si="50">RANK(BD52,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI52" s="188">
+      <c r="BI52" s="191">
         <f t="shared" si="50"/>
         <v>41</v>
       </c>
-      <c r="BJ52" s="188">
+      <c r="BJ52" s="191">
         <f t="shared" si="50"/>
         <v>41</v>
       </c>
@@ -14412,40 +14471,41 @@
       <c r="BA53" s="120"/>
       <c r="BB53" s="120"/>
       <c r="BC53" s="120"/>
-      <c r="BD53" s="186">
+      <c r="BD53" s="189">
         <f t="shared" si="33"/>
         <v>1</v>
       </c>
-      <c r="BE53" s="186" cm="1">
+      <c r="BE53" s="189" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(--(B53:BC53=INT(B53:BC53)),--(B53:BC53&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF53" s="186" cm="1">
+      <c r="BF53" s="189" cm="1">
         <f t="array" ref="BF53">MAX(FREQUENCY(IF((B53:BC53=INT(B53:BC53))*(B53:BC53&gt;0),COLUMN(B53:BC53)),IF((B53:BC53&lt;&gt;INT(B53:BC53))+(B53:BC53&lt;=0),COLUMN(B53:BC53))))</f>
         <v>1</v>
       </c>
-      <c r="BG53" s="187" cm="1">
+      <c r="BG53" s="190" cm="1">
         <f t="array" ref="BG53">SUMPRODUCT(--(B53:AI53=INT(B53:AI53)),--(B53:AI53&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH53" s="188">
+      <c r="BH53" s="191">
         <f t="shared" ref="BH53:BJ53" si="51">RANK(BD53,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI53" s="188">
+      <c r="BI53" s="191">
         <f t="shared" si="51"/>
         <v>34</v>
       </c>
-      <c r="BJ53" s="188">
+      <c r="BJ53" s="191">
         <f t="shared" si="51"/>
         <v>19</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="T1:AI1"/>
-    <mergeCell ref="AJ1:BC1"/>
+    <mergeCell ref="AJ1:AL1"/>
+    <mergeCell ref="AM1:BC1"/>
     <mergeCell ref="BD1:BJ1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
@@ -15563,9 +15623,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="Z9:AB9 AD9:AF9 X41 A9:X9" unlockedFormula="1"/>
-    <ignoredError sqref="A10:X10 Z3:AF3 A1:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH11:BJ39 Z10:AF10 BI9:BJ9 BH4:BJ8 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z28:AF33 A28:X33 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="AA15:AI15 BG41:BG53 AG12:AI14 AG28:AI39 AG5:AI8 AH41:AI41 AF42:AI42 AG49:AI53 AG43:AI47 AG1:AI3 AG16:AI21 Y12:Y15 BG11:BG39 BG4:BG8 AF4:AI4 W8:AF8 A50:AE50 A51:AF53 AF48:AI48 AC48:AD48 Y48:Y49 A45:AF45 A46:AE46 A44:AE44 Y42 W40:AD40 Y3:Y4 A38:AC38 A34:AF35 A36:Y36 A22:AI27 A28:Y33 A16:AF16 A17:Y18 AA13:AF13 Z14:AF14 AF11:AI11 A11:AA11 AD11" formulaRange="1"/>
+    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 A9:X9" unlockedFormula="1"/>
+    <ignoredError sqref="A1 C1:S1 U1:AF1 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z28:AF33 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 A3:X4 BD1:BJ2 BI3 AC40:AD40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 A48:X49 Z48:AB48 AE48 A51:AF53 A50:AD50 AF50 X8:AF8 A8:V8 A5:AF7 Z4:AE4 Z41:AE42 BH4:BJ8 BI9:BJ9 Z10:AF10 BH11:BJ39 Z49:AF49 A12:X15 A37:AF37 A39:AF39 A2:AF2 Z3:AF3 A10:X10" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="AG1:AI3 AD11:AI11 AC48:AI48 AG16:AI21 AG43:AI47 AG49:AI53 AF42:AI42 AH41:AI41 AG5:AI8 AG28:AI39 AG12:AI14 BG41:BG53 AA11 Z15:AA15 AF15:AI15 Z12:AF12 Z13:AA13 Y17:AF18 A19:AF21 Y22:AI22 A23:AI27 Y28:AF33 Y36:AF36 A37:AF37 Y38:AF38 A39:AF39 Y3:Y4 A40:AB40 Y42 A43:AF43 X44:AF44 Y46:AF46 A47:AF47 Y48:Y49 AE50:AF50 A5:AF7 A8:W8 AF4:AI4 BG4:BG8 BG11:BG39 Y12:Y15" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15612,21 +15672,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -15634,10 +15694,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -15650,7 +15710,7 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B4" s="158" t="s">
         <v>252</v>
@@ -15666,7 +15726,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -15686,7 +15746,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -15696,7 +15756,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -15704,10 +15764,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -15722,14 +15782,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -15740,10 +15800,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -15756,23 +15816,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -15780,7 +15840,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -15796,7 +15856,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -15814,17 +15874,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -15832,10 +15892,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -15910,7 +15970,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -15935,10 +15995,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -15950,7 +16010,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -15972,7 +16032,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -15984,7 +16044,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
@@ -16012,7 +16072,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16026,7 +16086,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -16038,7 +16098,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -16050,7 +16110,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>71</v>
@@ -16061,10 +16121,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>90</v>
@@ -16088,10 +16148,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -16102,7 +16162,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -16124,7 +16184,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -16136,7 +16196,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -16148,7 +16208,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>83</v>
@@ -16160,7 +16220,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>86</v>
@@ -16172,7 +16232,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -16184,7 +16244,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -16246,7 +16306,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -16277,7 +16337,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -16469,7 +16529,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -16661,7 +16721,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -16888,10 +16948,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>198</v>
@@ -16902,208 +16962,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -17111,118 +17171,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -17230,138 +17290,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="4"/>
+    <workbookView windowWidth="12410" windowHeight="10480" tabRatio="724" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="637">
   <si>
     <t>姓名</t>
   </si>
@@ -709,40 +709,10 @@
     <t>结束时女生已往棚子走约半圈，但偷懒直接掉头，被罚跑3圈。第一圈：提前掉头，导致混乱；第二圈：罚跑时唐家祺前面的学生越跑转弯越早；第三圈：罚跑时女生到棚子时走路。</t>
   </si>
   <si>
-    <t>郑永泽·阮贞铭</t>
-  </si>
-  <si>
-    <t>八上10.16</t>
-  </si>
-  <si>
-    <t>活动课下课，外面人讨论阮贞铭和江乐萱，郑永泽比“嘘”、盯着阮贞铭并嘴角上扬</t>
-  </si>
-  <si>
-    <t>八上12.17</t>
-  </si>
-  <si>
-    <t>数：十字相乘是不是还没讲？洪：数学书上都有写。生：哇……卓：被你装到我都受不了了。</t>
-  </si>
-  <si>
-    <t>八下1.8</t>
-  </si>
-  <si>
-    <t>语文课，师：“（写字丑）中考直接扣掉3分卷面分。”洪：“给他了。”（“给他了”经典）</t>
-  </si>
-  <si>
     <t>八上1.8</t>
   </si>
   <si>
-    <t>3、4、5能围成直角三角形我吃啊！（“吃”经典）</t>
-  </si>
-  <si>
     <t>（洪鑫洋在第三组前面，江允儿在二组中部）进班不往讲台走，往第二组过道绕并看江允儿一眼</t>
-  </si>
-  <si>
-    <t>八上1.11</t>
-  </si>
-  <si>
-    <t>物理难题，洪鑫洋：“题目出得不好”</t>
   </si>
   <si>
     <t>八上1.12</t>
@@ -790,169 +760,163 @@
     <t>语：我觉得他写的这些朋友圈都挺好的。</t>
   </si>
   <si>
+    <t>孔祥懿睡觉</t>
+  </si>
+  <si>
+    <t>八上12.16</t>
+  </si>
+  <si>
+    <t>物：头都快埋到地板上去了。</t>
+  </si>
+  <si>
+    <t>江允儿装</t>
+  </si>
+  <si>
+    <t>八上12.26</t>
+  </si>
+  <si>
+    <t>小测A-，“我都没背”</t>
+  </si>
+  <si>
+    <t>政治首个视频</t>
+  </si>
+  <si>
+    <t>八上12.18</t>
+  </si>
+  <si>
+    <t>八上12.29</t>
+  </si>
+  <si>
+    <t>和46号上台写英语句，多次探头看，刘老师让唐家祺改正后同步改正</t>
+  </si>
+  <si>
+    <t>八上12.30</t>
+  </si>
+  <si>
+    <t>迟到，多人提醒不站</t>
+  </si>
+  <si>
+    <t>七下3.4</t>
+  </si>
+  <si>
+    <t>体育课，黄恩亚和陈子岩聊天（Q=陈子岩，A=黄恩亚）。黄恩亚：“崔宇臣实在太萌了，心都快给他萌化了。”Q：为什么你现在不臭了？A：（把旧衣服拿去卖）……卖了十亿多，我家是卖劳斯莱斯的。Q：喜不喜欢崔宇臣、喜不喜欢讲黄话？A：半假半真。Q：你认为的自己的人生转折点？A：我从期中考后就尝到生物的滋味。Q：为什么爱玩抽象？A：为了刷在班里的存在感。</t>
+  </si>
+  <si>
+    <t>八下3.3</t>
+  </si>
+  <si>
+    <t>午餐吃麦当劳：饭盒里有薯条、麦乐鸡，最大的格子内直接放入带包装袋的板烧鸡腿堡</t>
+  </si>
+  <si>
+    <t>手机管理</t>
+  </si>
+  <si>
+    <t>崔母将崔玩手机事情告诉刘老师，手机被收，次日谈话</t>
+  </si>
+  <si>
+    <t>八上1.4</t>
+  </si>
+  <si>
+    <t>小测多人不过关，刘老师局部调查手机使用</t>
+  </si>
+  <si>
+    <t>刘必艳</t>
+  </si>
+  <si>
+    <t>八上12.31</t>
+  </si>
+  <si>
+    <t>文艺汇演，孔转头被调换位置。理由：转到后面讲话。孔：没讲话，只是转到后面看了一眼。刘：闭嘴。随后请张佳欣“作证”：是那个女生吗？-是。</t>
+  </si>
+  <si>
+    <t>（以小见大）林奕扬、崔宇臣升旗站位错——前几天也错——站最前面——谈话</t>
+  </si>
+  <si>
     <t>八上1.16</t>
   </si>
   <si>
-    <t>（数学）“180-α=β，这不一眼出答案吗？”</t>
+    <t>政治课前：“必艳来了！”生：奔回座位，瞬间安静</t>
+  </si>
+  <si>
+    <t>跑操喊口号</t>
+  </si>
+  <si>
+    <t>八上1.7</t>
+  </si>
+  <si>
+    <t>留下跑4圈</t>
+  </si>
+  <si>
+    <t>部分学生跑8小圈（约合4大圈），跑完逐个要求大声喊“一二三四”后回班</t>
+  </si>
+  <si>
+    <t>物理校本第三题关于足球守门员戴手套增大摩擦力。林奕扬：第三题不合实际，我就是守门员……手套上的乳胶是光滑的</t>
+  </si>
+  <si>
+    <t>八上1.13</t>
+  </si>
+  <si>
+    <t>吃切块甘蔗</t>
+  </si>
+  <si>
+    <t>踩桌子：从第四组出发，踩第三组第二桌2脚、第二组第二、一桌各1脚</t>
+  </si>
+  <si>
+    <t>数学课谈政策</t>
+  </si>
+  <si>
+    <t>讲评作业——上次作业只印了一半——家长会讲过，有家长疑惑，再讲——为何不“一刀切”（无作业必须打印）：考虑有人打印成本高——倡导自主学习——国家政策：不定教辅（上学期领导检查）——原因：培育人才（次）、人口减少（主）——当下情况：50人/班变为30~40人/班（仓实小现状）——内卷——大学录取率——国家政策——自主学习——买课外练习（五三、解析）——公立对比私立、学位与大学、公务员——985学生心高气傲——私企对比国企：导致公务员增加——学生：考公或保送——讲这些内容目的：给前景——好学生：学习；差生：送外卖？——本科挤压送外卖——素质：本科&gt;送外卖——努力学习——考高中前提：数学及格（浪费半节课）</t>
+  </si>
+  <si>
+    <t>八上1.14</t>
+  </si>
+  <si>
+    <t>试卷：解设没写单位-1——一分十几万——上周会考：50%老师外校——私立高中学费vs公立——总费用——一类校寄读费——很多人差1分——40中也有寄读（几万）——寄读条件（家境、走后门）——上次讲到“上高中的百分比变高”，原因：私立增加——每一分的价值——学生甘心、家长不甘心——借钱——兄弟姐妹（家长爱心）——好的儿女十几万都出——寄读一定好吗——（城门中学的学生觉得40中好，寄宿后越来越差）——学校没很照顾寄读——自己寄读其他学校感觉低人一等——学生内心——希望：努力——到时候后悔，3年多付10万</t>
+  </si>
+  <si>
+    <t>八上10.31</t>
+  </si>
+  <si>
+    <t>语文好段抄生物书“生态系统”章节导言</t>
+  </si>
+  <si>
+    <t>40中</t>
+  </si>
+  <si>
+    <t>数：油印室额度都用光了。</t>
+  </si>
+  <si>
+    <t>铃声错乱：①（周三）9：10响预备铃②响铃响到一半停止，几秒后重新响起</t>
+  </si>
+  <si>
+    <t>往棚子跑时不到一半脱离队伍走路，在白线前调头（套圈最厉害）</t>
+  </si>
+  <si>
+    <t>晴蔡</t>
+  </si>
+  <si>
+    <t>八上1.19</t>
+  </si>
+  <si>
+    <t>中午江雨晴整块鸡排（鸡块？）给蔡华楷（郑永泽说）</t>
+  </si>
+  <si>
+    <t>刘老师麦串台</t>
   </si>
   <si>
     <t>八上1.20</t>
   </si>
   <si>
-    <t>物：这也是前两年的二检题。洪：二检题？给他了！</t>
-  </si>
-  <si>
-    <t>孔祥懿睡觉</t>
-  </si>
-  <si>
-    <t>八上12.16</t>
-  </si>
-  <si>
-    <t>物：头都快埋到地板上去了。</t>
-  </si>
-  <si>
-    <t>江允儿装</t>
-  </si>
-  <si>
-    <t>八上12.26</t>
-  </si>
-  <si>
-    <t>小测A-，“我都没背”</t>
-  </si>
-  <si>
-    <t>政治首个视频</t>
-  </si>
-  <si>
-    <t>八上12.18</t>
-  </si>
-  <si>
-    <t>八上12.29</t>
-  </si>
-  <si>
-    <t>和46号上台写英语句，多次探头看，刘老师让唐家祺改正后同步改正</t>
-  </si>
-  <si>
-    <t>八上12.30</t>
-  </si>
-  <si>
-    <t>迟到，多人提醒不站</t>
+    <t>听到“然后，晚自习”</t>
+  </si>
+  <si>
+    <t>政治老师：你坐好嘛，女孩子……注意自己的形象。</t>
+  </si>
+  <si>
+    <t>吃东西</t>
   </si>
   <si>
     <t>八上1.21</t>
-  </si>
-  <si>
-    <t>英语课研究三角函数</t>
-  </si>
-  <si>
-    <t>七下3.4</t>
-  </si>
-  <si>
-    <t>体育课，黄恩亚和陈子岩聊天（Q=陈子岩，A=黄恩亚）。黄恩亚：“崔宇臣实在太萌了，心都快给他萌化了。”Q：为什么你现在不臭了？A：（把旧衣服拿去卖）……卖了十亿多，我家是卖劳斯莱斯的。Q：喜不喜欢崔宇臣、喜不喜欢讲黄话？A：半假半真。Q：你认为的自己的人生转折点？A：我从期中考后就尝到生物的滋味。Q：为什么爱玩抽象？A：为了刷在班里的存在感。</t>
-  </si>
-  <si>
-    <t>手机管理</t>
-  </si>
-  <si>
-    <t>崔母将崔玩手机事情告诉刘老师，手机被收，次日谈话</t>
-  </si>
-  <si>
-    <t>八上1.4</t>
-  </si>
-  <si>
-    <t>小测多人不过关，刘老师局部调查手机使用</t>
-  </si>
-  <si>
-    <t>刘必艳</t>
-  </si>
-  <si>
-    <t>八上12.31</t>
-  </si>
-  <si>
-    <t>文艺汇演，孔转头被调换位置。理由：转到后面讲话。孔：没讲话，只是转到后面看了一眼。刘：闭嘴。随后请张佳欣“作证”：是那个女生吗？-是。</t>
-  </si>
-  <si>
-    <t>（以小见大）林奕扬、崔宇臣升旗站位错——前几天也错——站最前面——谈话</t>
-  </si>
-  <si>
-    <t>政治课前：“必艳来了！”生：奔回座位，瞬间安静</t>
-  </si>
-  <si>
-    <t>跑操喊口号</t>
-  </si>
-  <si>
-    <t>八上1.7</t>
-  </si>
-  <si>
-    <t>留下跑4圈</t>
-  </si>
-  <si>
-    <t>部分学生跑8小圈（约合4大圈），跑完逐个要求大声喊“一二三四”后回班</t>
-  </si>
-  <si>
-    <t>物理校本第三题关于足球守门员戴手套增大摩擦力。林奕扬：第三题不合实际，我就是守门员……手套上的乳胶是光滑的</t>
-  </si>
-  <si>
-    <t>八上1.13</t>
-  </si>
-  <si>
-    <t>吃切块甘蔗</t>
-  </si>
-  <si>
-    <t>数学课谈政策</t>
-  </si>
-  <si>
-    <t>讲评作业——上次作业只印了一半——家长会讲过，有家长疑惑，再讲——为何不“一刀切”（无作业必须打印）：考虑有人打印成本高——倡导自主学习——国家政策：不定教辅（上学期领导检查）——原因：培育人才（次）、人口减少（主）——当下情况：50人/班变为30~40人/班（仓实小现状）——内卷——大学录取率——国家政策——自主学习——买课外练习（五三、解析）——公立对比私立、学位与大学、公务员——985学生心高气傲——私企对比国企：导致公务员增加——学生：考公或保送——讲这些内容目的：给前景——好学生：学习；差生：送外卖？——本科挤压送外卖——素质：本科&gt;送外卖——努力学习——考高中前提：数学及格（浪费半节课）</t>
-  </si>
-  <si>
-    <t>八上1.14</t>
-  </si>
-  <si>
-    <t>试卷：解设没写单位-1——一分十几万——上周会考：50%老师外校——私立高中学费vs公立——总费用——一类校寄读费——很多人差1分——40中也有寄读（几万）——寄读条件（家境、走后门）——上次讲到“上高中的百分比变高”，原因：私立增加——每一分的价值——学生甘心、家长不甘心——借钱——兄弟姐妹（家长爱心）——好的儿女十几万都出——寄读一定好吗——（城门中学的学生觉得40中好，寄宿后越来越差）——学校没很照顾寄读——自己寄读其他学校感觉低人一等——学生内心——希望：努力——到时候后悔，3年多付10万</t>
-  </si>
-  <si>
-    <t>八上10.31</t>
-  </si>
-  <si>
-    <t>语文好段抄生物书“生态系统”章节导言</t>
-  </si>
-  <si>
-    <t>信仰</t>
-  </si>
-  <si>
-    <t>叶弘毅：10班早读（或课前三分钟？）读书声小，冯越：你们要学习9班，他们读书特别有革命信念。举个例子，他们读中国共产党诞生，读到“信仰”两个字时特别大声。</t>
-  </si>
-  <si>
-    <t>40中</t>
-  </si>
-  <si>
-    <t>数：油印室额度都用光了。</t>
-  </si>
-  <si>
-    <t>铃声错乱：①（周三）9：10响预备铃②响铃响到一半停止，几秒后重新响起</t>
-  </si>
-  <si>
-    <t>往棚子跑时不到一半脱离队伍走路，在白线前调头（套圈最厉害）</t>
-  </si>
-  <si>
-    <t>晴蔡</t>
-  </si>
-  <si>
-    <t>八上1.19</t>
-  </si>
-  <si>
-    <t>中午江雨晴整块鸡排（鸡块？）给蔡华楷（郑永泽说）</t>
-  </si>
-  <si>
-    <t>刘老师麦串台</t>
-  </si>
-  <si>
-    <t>听到“然后，晚自习”</t>
-  </si>
-  <si>
-    <t>政治老师：你坐好嘛，女孩子……注意自己的形象。</t>
-  </si>
-  <si>
-    <t>吃东西</t>
   </si>
   <si>
     <t>崔宇臣：塔斯汀</t>
@@ -3299,6 +3263,17 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
       <scheme val="major"/>
     </font>
     <font>
@@ -3310,17 +3285,6 @@
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="华文仿宋"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4630,12 +4594,6 @@
     <xf numFmtId="57" fontId="24" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="57" fontId="24" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="57" fontId="24" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="57" fontId="24" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4732,17 +4690,23 @@
     <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="23" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5941,16 +5905,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5964,7 +5928,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5978,7 +5942,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5992,7 +5956,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6020,7 +5984,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6034,7 +5998,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6048,7 +6012,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6062,7 +6026,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6076,7 +6040,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6102,7 +6066,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6116,7 +6080,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6130,7 +6094,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6156,7 +6120,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6170,7 +6134,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6208,7 +6172,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6222,7 +6186,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6248,7 +6212,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6262,7 +6226,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6276,7 +6240,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6290,7 +6254,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6304,7 +6268,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6318,7 +6282,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6344,7 +6308,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6358,7 +6322,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6372,7 +6336,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6398,7 +6362,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6424,7 +6388,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6438,7 +6402,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6452,10 +6416,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="E38" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6469,7 +6433,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6483,7 +6447,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6497,10 +6461,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="E41" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6526,7 +6490,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6552,7 +6516,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6578,10 +6542,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="E47" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6595,7 +6559,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6621,7 +6585,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6647,7 +6611,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -6680,34 +6644,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6715,10 +6679,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6726,10 +6690,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6737,10 +6701,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6748,23 +6712,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6772,10 +6736,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6783,10 +6747,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6794,10 +6758,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6805,10 +6769,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6816,50 +6780,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6868,24 +6832,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6893,17 +6857,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6912,61 +6876,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>554</v>
+        <v>542</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6974,10 +6938,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>555</v>
+        <v>543</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>556</v>
+        <v>544</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6985,10 +6949,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -6996,27 +6960,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>561</v>
+        <v>549</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7024,10 +6988,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>562</v>
+        <v>550</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>563</v>
+        <v>551</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7035,10 +6999,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>564</v>
+        <v>552</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7046,53 +7010,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>565</v>
+        <v>553</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>570</v>
+        <v>558</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7103,42 +7067,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7146,64 +7110,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>579</v>
+        <v>567</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>581</v>
+        <v>569</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>585</v>
+        <v>573</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>587</v>
+        <v>575</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7213,16 +7177,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>589</v>
+        <v>577</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7231,7 +7195,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7240,42 +7204,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>591</v>
+        <v>579</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>592</v>
+        <v>580</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>593</v>
+        <v>581</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7285,10 +7249,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7296,10 +7260,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>594</v>
+        <v>582</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7311,18 +7275,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>595</v>
+        <v>583</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>596</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>
@@ -7430,7 +7394,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>597</v>
+        <v>585</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7444,7 +7408,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>598</v>
+        <v>586</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7468,7 +7432,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7481,7 +7445,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7494,7 +7458,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>601</v>
+        <v>589</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7528,7 +7492,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7574,7 +7538,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7610,7 +7574,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7644,10 +7608,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>605</v>
+        <v>593</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7659,10 +7623,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>607</v>
+        <v>595</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7685,7 +7649,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7698,10 +7662,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7735,10 +7699,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7750,10 +7714,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7777,7 +7741,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7844,7 +7808,7 @@
         <v>76</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7858,7 +7822,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7870,7 +7834,7 @@
         <v>81</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7884,7 +7848,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7896,10 +7860,10 @@
         <v>86</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7912,7 +7876,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7935,7 +7899,7 @@
         <v>97</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7959,7 +7923,7 @@
         <v>102</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -7995,7 +7959,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8019,7 +7983,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8042,10 +8006,10 @@
         <v>115</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8081,27 +8045,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8109,13 +8073,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8123,13 +8087,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8137,13 +8101,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8151,13 +8115,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>641</v>
+        <v>629</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8165,13 +8129,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8179,13 +8143,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8193,7 +8157,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8201,7 +8165,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8209,7 +8173,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8217,7 +8181,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8508,493 +8472,426 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="208" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="208" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="208" customWidth="1"/>
+    <col min="1" max="1" width="24" style="206" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="206" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="206" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="207" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="209" t="s">
+    <row r="1" s="205" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="207" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="209" t="s">
+      <c r="B1" s="207" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="209" t="s">
+      <c r="C1" s="207" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="208" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="210" t="s">
+      <c r="B2" s="208" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="208" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="210" t="s">
+      <c r="A3" s="208" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="210" t="s">
+      <c r="B3" s="208" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="208" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="210" t="s">
+      <c r="A4" s="208" t="s">
         <v>205</v>
       </c>
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="208" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="208" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="211" t="s">
+      <c r="A5" s="209" t="s">
         <v>207</v>
       </c>
-      <c r="B5" s="210" t="s">
+      <c r="B5" s="208" t="s">
         <v>208</v>
       </c>
-      <c r="C5" s="210" t="s">
+      <c r="C5" s="208" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="212"/>
-      <c r="B6" s="210" t="s">
+      <c r="A6" s="210"/>
+      <c r="B6" s="208" t="s">
         <v>210</v>
       </c>
-      <c r="C6" s="210" t="s">
+      <c r="C6" s="208" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="210" t="s">
+      <c r="A7" s="211" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="208" t="s">
         <v>212</v>
       </c>
-      <c r="B7" s="210" t="s">
+      <c r="C7" s="208" t="s">
         <v>213</v>
       </c>
-      <c r="C7" s="210" t="s">
+    </row>
+    <row r="8" ht="140" spans="1:3">
+      <c r="A8" s="211"/>
+      <c r="B8" s="208" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="213" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="210" t="s">
+      <c r="C8" s="208" t="s">
         <v>215</v>
       </c>
-      <c r="C8" s="210" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="211"/>
+      <c r="B9" s="208" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="214"/>
-      <c r="B9" s="210" t="s">
+      <c r="C9" s="208" t="s">
         <v>217</v>
       </c>
-      <c r="C9" s="210" t="s">
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="212"/>
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="208" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="214"/>
-      <c r="B10" s="210" t="s">
+      <c r="B11" s="208" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="210" t="s">
+      <c r="C11" s="208" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="214"/>
-      <c r="B11" s="210" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" s="210" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="208" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="214"/>
-      <c r="B12" s="210" t="s">
+      <c r="B12" s="208" t="s">
         <v>222</v>
       </c>
-      <c r="C12" s="210" t="s">
+      <c r="C12" s="208" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="13" ht="140" spans="1:3">
-      <c r="A13" s="214"/>
-      <c r="B13" s="210" t="s">
+    <row r="13" spans="1:3">
+      <c r="A13" s="208" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="210" t="s">
+      <c r="B13" s="208" t="s">
         <v>225</v>
       </c>
+      <c r="C13" s="213">
+        <v>0.440972222222222</v>
+      </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="214"/>
-      <c r="B14" s="210" t="s">
+      <c r="A14" s="214" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="208" t="s">
         <v>226</v>
       </c>
-      <c r="C14" s="210" t="s">
+      <c r="C14" s="208" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="214"/>
-      <c r="B15" s="210" t="s">
+      <c r="A15" s="215"/>
+      <c r="B15" s="208" t="s">
         <v>228</v>
       </c>
-      <c r="C15" s="210" t="s">
+      <c r="C15" s="208" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="214"/>
-      <c r="B16" s="210" t="s">
+    <row r="16" ht="56" spans="1:3">
+      <c r="A16" s="215"/>
+      <c r="B16" s="208" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="210" t="s">
+      <c r="C16" s="208" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="215"/>
-      <c r="B17" s="210"/>
-      <c r="C17" s="210"/>
+      <c r="B17" s="208" t="s">
+        <v>232</v>
+      </c>
+      <c r="C17" s="208" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="210" t="s">
+      <c r="A18" s="209" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" s="208" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" s="208" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="210"/>
+      <c r="B19" s="208" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="208" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:3">
+      <c r="A20" s="216" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="208" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="208" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="211"/>
+      <c r="B21" s="208" t="s">
+        <v>214</v>
+      </c>
+      <c r="C21" s="208" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="211"/>
+      <c r="B22" s="208" t="s">
+        <v>242</v>
+      </c>
+      <c r="C22" s="208" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="211"/>
+      <c r="B23" s="208"/>
+      <c r="C23" s="208"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="209" t="s">
+        <v>244</v>
+      </c>
+      <c r="B24" s="208" t="s">
+        <v>245</v>
+      </c>
+      <c r="C24" s="208" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="210"/>
+      <c r="B25" s="208" t="s">
+        <v>212</v>
+      </c>
+      <c r="C25" s="208" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="26" ht="28" spans="1:3">
+      <c r="A26" s="214" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="208" t="s">
+        <v>212</v>
+      </c>
+      <c r="C26" s="208" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="215"/>
+      <c r="B27" s="206" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="206" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="215"/>
+      <c r="B28" s="206" t="s">
         <v>232</v>
       </c>
-      <c r="B18" s="210" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="210" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="210" t="s">
-        <v>235</v>
-      </c>
-      <c r="B19" s="210" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="210" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="210" t="s">
-        <v>238</v>
-      </c>
-      <c r="B20" s="210" t="s">
-        <v>239</v>
-      </c>
-      <c r="C20" s="216">
-        <v>0.440972222222222</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="213" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="210" t="s">
-        <v>240</v>
-      </c>
-      <c r="C21" s="210" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="214"/>
-      <c r="B22" s="210" t="s">
-        <v>242</v>
-      </c>
-      <c r="C22" s="210" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="214"/>
-      <c r="B23" s="210" t="s">
-        <v>244</v>
-      </c>
-      <c r="C23" s="210" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="24" ht="56" spans="1:3">
-      <c r="A24" s="214"/>
-      <c r="B24" s="210" t="s">
-        <v>246</v>
-      </c>
-      <c r="C24" s="210" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="211" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="210" t="s">
-        <v>242</v>
-      </c>
-      <c r="C25" s="210" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="212"/>
-      <c r="B26" s="210" t="s">
-        <v>250</v>
-      </c>
-      <c r="C26" s="210" t="s">
+      <c r="C28" s="206" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="27" ht="28" spans="1:3">
-      <c r="A27" s="213" t="s">
+    <row r="29" ht="98" spans="1:3">
+      <c r="A29" s="216" t="s">
         <v>252</v>
       </c>
-      <c r="B27" s="210" t="s">
+      <c r="B29" s="206" t="s">
+        <v>212</v>
+      </c>
+      <c r="C29" s="206" t="s">
         <v>253</v>
       </c>
-      <c r="C27" s="210" t="s">
+    </row>
+    <row r="30" ht="84" spans="1:3">
+      <c r="A30" s="212"/>
+      <c r="B30" s="206" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="214"/>
-      <c r="B28" s="210" t="s">
-        <v>224</v>
-      </c>
-      <c r="C28" s="210" t="s">
+      <c r="C30" s="206" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="214"/>
-      <c r="B29" s="210" t="s">
-        <v>228</v>
-      </c>
-      <c r="C29" s="210" t="s">
+    <row r="31" spans="1:3">
+      <c r="A31" s="206" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="206" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="214"/>
-      <c r="B30" s="210"/>
-      <c r="C30" s="210"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="211" t="s">
+      <c r="C31" s="206" t="s">
         <v>257</v>
       </c>
-      <c r="B31" s="210" t="s">
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="216" t="s">
         <v>258</v>
       </c>
-      <c r="C31" s="210" t="s">
+      <c r="B32" s="206" t="s">
+        <v>214</v>
+      </c>
+      <c r="C32" s="206" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="212"/>
-      <c r="B32" s="210" t="s">
-        <v>219</v>
-      </c>
-      <c r="C32" s="210" t="s">
+    <row r="33" spans="1:3">
+      <c r="A33" s="212"/>
+      <c r="B33" s="206" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" s="206" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="33" ht="28" spans="1:3">
-      <c r="A33" s="213" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="210" t="s">
-        <v>219</v>
-      </c>
-      <c r="C33" s="210" t="s">
+    <row r="34" spans="1:3">
+      <c r="A34" s="206" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="206" t="s">
+        <v>216</v>
+      </c>
+      <c r="C34" s="206" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="215"/>
-      <c r="B34" s="208" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" s="206" t="s">
         <v>262</v>
       </c>
-      <c r="C34" s="208" t="s">
+      <c r="B35" s="206" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="35" ht="98" spans="1:3">
-      <c r="A35" s="213" t="s">
+      <c r="C35" s="206" t="s">
         <v>264</v>
       </c>
-      <c r="B35" s="208" t="s">
-        <v>219</v>
-      </c>
-      <c r="C35" s="208" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="206" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="36" ht="84" spans="1:3">
-      <c r="A36" s="215"/>
-      <c r="B36" s="208" t="s">
+      <c r="B36" s="206" t="s">
         <v>266</v>
       </c>
-      <c r="C36" s="208" t="s">
+      <c r="C36" s="206" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="208" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="208" t="s">
+      <c r="A37" s="206" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="206" t="s">
+        <v>254</v>
+      </c>
+      <c r="C37" s="206" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="208" t="s">
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="206" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="38" ht="28" spans="1:3">
-      <c r="A38" s="208" t="s">
+      <c r="B38" s="206" t="s">
         <v>270</v>
       </c>
-      <c r="B38" s="208" t="s">
-        <v>262</v>
-      </c>
-      <c r="C38" s="208" t="s">
+      <c r="C38" s="206" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="213" t="s">
+      <c r="A39" s="206" t="s">
         <v>272</v>
       </c>
-      <c r="B39" s="208" t="s">
-        <v>224</v>
-      </c>
-      <c r="C39" s="208" t="s">
+      <c r="B39" s="206" t="s">
         <v>273</v>
       </c>
+      <c r="C39" s="206" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="215"/>
-      <c r="B40" s="208" t="s">
-        <v>266</v>
-      </c>
-      <c r="C40" s="208" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="208" t="s">
-        <v>54</v>
-      </c>
-      <c r="B41" s="208" t="s">
-        <v>226</v>
-      </c>
-      <c r="C41" s="208" t="s">
+      <c r="A40" s="206" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="208" t="s">
+      <c r="B40" s="206" t="s">
+        <v>273</v>
+      </c>
+      <c r="C40" s="206" t="s">
         <v>276</v>
-      </c>
-      <c r="B42" s="208" t="s">
-        <v>277</v>
-      </c>
-      <c r="C42" s="208" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="208" t="s">
-        <v>279</v>
-      </c>
-      <c r="B43" s="208" t="s">
-        <v>230</v>
-      </c>
-      <c r="C43" s="208" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="208" t="s">
-        <v>10</v>
-      </c>
-      <c r="B44" s="208" t="s">
-        <v>266</v>
-      </c>
-      <c r="C44" s="208" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="208" t="s">
-        <v>282</v>
-      </c>
-      <c r="B45" s="208" t="s">
-        <v>244</v>
-      </c>
-      <c r="C45" s="208" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="208" t="s">
-        <v>284</v>
-      </c>
-      <c r="B46" s="208" t="s">
-        <v>285</v>
-      </c>
-      <c r="C46" s="208" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="208" t="s">
-        <v>287</v>
-      </c>
-      <c r="B47" s="208" t="s">
-        <v>285</v>
-      </c>
-      <c r="C47" s="208" t="s">
-        <v>288</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A8:A17"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A32:A33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -9013,45 +8910,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="196"/>
+    <col min="5" max="5" width="8.72727272727273" style="194"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="194" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="197" t="s">
-        <v>289</v>
-      </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="194" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="2" s="195" customFormat="1" spans="1:7">
-      <c r="A2" s="201" t="s">
+    <row r="1" s="192" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="195" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="196"/>
+      <c r="C1" s="196"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="192" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="2" s="193" customFormat="1" spans="1:7">
+      <c r="A2" s="199" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="202"/>
-      <c r="C2" s="195" t="s">
-        <v>291</v>
-      </c>
-      <c r="D2" s="195" t="s">
-        <v>292</v>
+      <c r="B2" s="200"/>
+      <c r="C2" s="193" t="s">
+        <v>279</v>
+      </c>
+      <c r="D2" s="193" t="s">
+        <v>280</v>
       </c>
       <c r="E2" s="141"/>
-      <c r="F2" s="195" t="s">
+      <c r="F2" s="193" t="s">
         <v>197</v>
       </c>
-      <c r="G2" s="195" t="s">
-        <v>293</v>
+      <c r="G2" s="193" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="203">
+      <c r="A3" s="201">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -9062,14 +8959,14 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="204"/>
+      <c r="A4" s="202"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -9078,14 +8975,14 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="204"/>
+      <c r="A5" s="202"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -9094,14 +8991,14 @@
       </c>
       <c r="D5" s="119"/>
       <c r="F5" s="119" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="G5" s="119" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="204"/>
+      <c r="A6" s="202"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9109,15 +9006,15 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="205" t="s">
-        <v>300</v>
+      <c r="F6" s="203" t="s">
+        <v>288</v>
       </c>
       <c r="G6" s="119" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="204"/>
+      <c r="A7" s="202"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9125,13 +9022,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="206"/>
+      <c r="F7" s="204"/>
       <c r="G7" s="119" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="204"/>
+      <c r="A8" s="202"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9143,7 +9040,7 @@
       <c r="G8" s="119"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="206"/>
+      <c r="A9" s="204"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9155,7 +9052,7 @@
       <c r="G9" s="119"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="205">
+      <c r="A10" s="203">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9169,7 +9066,7 @@
       <c r="G10" s="119"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="204"/>
+      <c r="A11" s="202"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9181,7 +9078,7 @@
       <c r="G11" s="119"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="206"/>
+      <c r="A12" s="204"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9193,7 +9090,7 @@
       <c r="G12" s="119"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="205">
+      <c r="A13" s="203">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9209,7 +9106,7 @@
       <c r="G13" s="119"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="206"/>
+      <c r="A14" s="204"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -9255,10 +9152,10 @@
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" s="175" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="C1" s="177"/>
       <c r="D1" s="177"/>
@@ -9278,7 +9175,7 @@
       <c r="R1" s="177"/>
       <c r="S1" s="177"/>
       <c r="T1" s="178" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="U1" s="179"/>
       <c r="V1" s="179"/>
@@ -9295,220 +9192,220 @@
       <c r="AG1" s="179"/>
       <c r="AH1" s="179"/>
       <c r="AI1" s="179"/>
-      <c r="AJ1" s="180" t="s">
-        <v>306</v>
-      </c>
-      <c r="AK1" s="181"/>
-      <c r="AL1" s="181"/>
-      <c r="AM1" s="180" t="s">
-        <v>307</v>
-      </c>
-      <c r="AN1" s="181"/>
-      <c r="AO1" s="181"/>
-      <c r="AP1" s="181"/>
-      <c r="AQ1" s="181"/>
-      <c r="AR1" s="181"/>
-      <c r="AS1" s="181"/>
-      <c r="AT1" s="181"/>
-      <c r="AU1" s="181"/>
-      <c r="AV1" s="181"/>
-      <c r="AW1" s="181"/>
-      <c r="AX1" s="181"/>
-      <c r="AY1" s="181"/>
-      <c r="AZ1" s="181"/>
-      <c r="BA1" s="181"/>
-      <c r="BB1" s="181"/>
-      <c r="BC1" s="182"/>
-      <c r="BD1" s="183" t="s">
-        <v>308</v>
-      </c>
-      <c r="BE1" s="184"/>
-      <c r="BF1" s="184"/>
-      <c r="BG1" s="184"/>
-      <c r="BH1" s="184"/>
-      <c r="BI1" s="184"/>
-      <c r="BJ1" s="185"/>
+      <c r="AJ1" s="178" t="s">
+        <v>294</v>
+      </c>
+      <c r="AK1" s="179"/>
+      <c r="AL1" s="179"/>
+      <c r="AM1" s="178" t="s">
+        <v>295</v>
+      </c>
+      <c r="AN1" s="179"/>
+      <c r="AO1" s="179"/>
+      <c r="AP1" s="179"/>
+      <c r="AQ1" s="179"/>
+      <c r="AR1" s="179"/>
+      <c r="AS1" s="179"/>
+      <c r="AT1" s="179"/>
+      <c r="AU1" s="179"/>
+      <c r="AV1" s="179"/>
+      <c r="AW1" s="179"/>
+      <c r="AX1" s="179"/>
+      <c r="AY1" s="179"/>
+      <c r="AZ1" s="179"/>
+      <c r="BA1" s="179"/>
+      <c r="BB1" s="179"/>
+      <c r="BC1" s="180"/>
+      <c r="BD1" s="181" t="s">
+        <v>296</v>
+      </c>
+      <c r="BE1" s="182"/>
+      <c r="BF1" s="182"/>
+      <c r="BG1" s="182"/>
+      <c r="BH1" s="182"/>
+      <c r="BI1" s="182"/>
+      <c r="BJ1" s="183"/>
     </row>
     <row r="2" s="173" customFormat="1" ht="28" spans="1:62">
       <c r="A2" s="175"/>
-      <c r="B2" s="186">
+      <c r="B2" s="184">
         <v>5</v>
       </c>
-      <c r="C2" s="186">
+      <c r="C2" s="184">
         <v>6</v>
       </c>
-      <c r="D2" s="186">
+      <c r="D2" s="184">
         <v>9</v>
       </c>
-      <c r="E2" s="186">
+      <c r="E2" s="184">
         <v>10</v>
       </c>
-      <c r="F2" s="186">
+      <c r="F2" s="184">
         <v>11</v>
       </c>
-      <c r="G2" s="186">
+      <c r="G2" s="184">
         <v>12</v>
       </c>
-      <c r="H2" s="186">
+      <c r="H2" s="184">
         <v>15</v>
       </c>
-      <c r="I2" s="186">
+      <c r="I2" s="184">
         <v>16</v>
       </c>
-      <c r="J2" s="186">
+      <c r="J2" s="184">
         <v>17</v>
       </c>
-      <c r="K2" s="186">
+      <c r="K2" s="184">
         <v>18</v>
       </c>
-      <c r="L2" s="186">
+      <c r="L2" s="184">
         <v>19</v>
       </c>
-      <c r="M2" s="186">
+      <c r="M2" s="184">
         <v>22</v>
       </c>
-      <c r="N2" s="186">
+      <c r="N2" s="184">
         <v>23</v>
       </c>
-      <c r="O2" s="186">
+      <c r="O2" s="184">
         <v>25</v>
       </c>
-      <c r="P2" s="186">
+      <c r="P2" s="184">
         <v>26</v>
       </c>
-      <c r="Q2" s="186">
+      <c r="Q2" s="184">
         <v>29</v>
       </c>
-      <c r="R2" s="186">
+      <c r="R2" s="184">
         <v>30</v>
       </c>
-      <c r="S2" s="186">
+      <c r="S2" s="184">
         <v>31</v>
       </c>
-      <c r="T2" s="186">
+      <c r="T2" s="184">
         <v>4</v>
       </c>
-      <c r="U2" s="186">
+      <c r="U2" s="184">
         <v>5</v>
       </c>
-      <c r="V2" s="186">
+      <c r="V2" s="184">
         <v>6</v>
       </c>
-      <c r="W2" s="186">
+      <c r="W2" s="184">
         <v>7</v>
       </c>
-      <c r="X2" s="186">
+      <c r="X2" s="184">
         <v>8</v>
       </c>
-      <c r="Y2" s="186">
+      <c r="Y2" s="184">
         <v>11</v>
       </c>
-      <c r="Z2" s="186">
+      <c r="Z2" s="184">
         <v>12</v>
       </c>
-      <c r="AA2" s="186">
+      <c r="AA2" s="184">
         <v>13</v>
       </c>
-      <c r="AB2" s="186">
+      <c r="AB2" s="184">
         <v>14</v>
       </c>
-      <c r="AC2" s="186">
+      <c r="AC2" s="184">
         <v>15</v>
       </c>
-      <c r="AD2" s="186">
+      <c r="AD2" s="184">
         <v>16</v>
       </c>
-      <c r="AE2" s="186">
+      <c r="AE2" s="184">
         <v>19</v>
       </c>
-      <c r="AF2" s="186">
+      <c r="AF2" s="184">
         <v>20</v>
       </c>
-      <c r="AG2" s="186">
+      <c r="AG2" s="184">
         <v>21</v>
       </c>
-      <c r="AH2" s="186">
+      <c r="AH2" s="184">
         <v>22</v>
       </c>
-      <c r="AI2" s="186">
+      <c r="AI2" s="184">
         <v>23</v>
       </c>
-      <c r="AJ2" s="186">
+      <c r="AJ2" s="184">
         <v>26</v>
       </c>
-      <c r="AK2" s="186">
+      <c r="AK2" s="184">
         <v>27</v>
       </c>
-      <c r="AL2" s="186">
+      <c r="AL2" s="184">
         <v>28</v>
       </c>
-      <c r="AM2" s="186">
+      <c r="AM2" s="184">
         <v>2</v>
       </c>
-      <c r="AN2" s="186">
+      <c r="AN2" s="184">
         <v>3</v>
       </c>
-      <c r="AO2" s="186">
+      <c r="AO2" s="184">
         <v>4</v>
       </c>
-      <c r="AP2" s="186">
+      <c r="AP2" s="184">
         <v>5</v>
       </c>
-      <c r="AQ2" s="186">
+      <c r="AQ2" s="184">
         <v>6</v>
       </c>
-      <c r="AR2" s="186">
+      <c r="AR2" s="184">
         <v>9</v>
       </c>
-      <c r="AS2" s="186">
+      <c r="AS2" s="184">
         <v>10</v>
       </c>
-      <c r="AT2" s="186">
+      <c r="AT2" s="184">
         <v>11</v>
       </c>
-      <c r="AU2" s="186">
+      <c r="AU2" s="184">
         <v>12</v>
       </c>
-      <c r="AV2" s="186">
+      <c r="AV2" s="184">
         <v>13</v>
       </c>
-      <c r="AW2" s="186">
+      <c r="AW2" s="184">
         <v>16</v>
       </c>
-      <c r="AX2" s="186">
+      <c r="AX2" s="184">
         <v>17</v>
       </c>
-      <c r="AY2" s="186">
+      <c r="AY2" s="184">
         <v>18</v>
       </c>
-      <c r="AZ2" s="186">
+      <c r="AZ2" s="184">
         <v>19</v>
       </c>
-      <c r="BA2" s="186">
+      <c r="BA2" s="184">
         <v>20</v>
       </c>
-      <c r="BB2" s="186"/>
-      <c r="BC2" s="186"/>
-      <c r="BD2" s="187" t="s">
-        <v>309</v>
-      </c>
-      <c r="BE2" s="187" t="s">
-        <v>310</v>
-      </c>
-      <c r="BF2" s="187" t="s">
-        <v>311</v>
-      </c>
-      <c r="BG2" s="187" t="s">
-        <v>312</v>
-      </c>
-      <c r="BH2" s="188" t="s">
-        <v>313</v>
-      </c>
-      <c r="BI2" s="188" t="s">
-        <v>314</v>
-      </c>
-      <c r="BJ2" s="188" t="s">
-        <v>315</v>
+      <c r="BB2" s="184"/>
+      <c r="BC2" s="184"/>
+      <c r="BD2" s="185" t="s">
+        <v>297</v>
+      </c>
+      <c r="BE2" s="185" t="s">
+        <v>298</v>
+      </c>
+      <c r="BF2" s="185" t="s">
+        <v>299</v>
+      </c>
+      <c r="BG2" s="185" t="s">
+        <v>300</v>
+      </c>
+      <c r="BH2" s="186" t="s">
+        <v>301</v>
+      </c>
+      <c r="BI2" s="186" t="s">
+        <v>302</v>
+      </c>
+      <c r="BJ2" s="186" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9571,31 +9468,31 @@
       <c r="BA3" s="120"/>
       <c r="BB3" s="120"/>
       <c r="BC3" s="120"/>
-      <c r="BD3" s="189">
+      <c r="BD3" s="187">
         <f>SUM(B3:BC3)</f>
         <v>1</v>
       </c>
-      <c r="BE3" s="189" cm="1">
+      <c r="BE3" s="187" cm="1">
         <f t="array" ref="BE3">SUMPRODUCT(--(B3:BC3=INT(B3:BC3)),--(B3:BC3&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF3" s="189" cm="1">
+      <c r="BF3" s="187" cm="1">
         <f t="array" ref="BF3">MAX(FREQUENCY(IF((B3:BC3=INT(B3:BC3))*(B3:BC3&gt;0),COLUMN(B3:BC3)),IF((B3:BC3&lt;&gt;INT(B3:BC3))+(B3:BC3&lt;=0),COLUMN(B3:BC3))))</f>
         <v>1</v>
       </c>
-      <c r="BG3" s="190" cm="1">
+      <c r="BG3" s="188" cm="1">
         <f t="array" ref="BG3">SUMPRODUCT(--(B3:AI3=INT(B3:AI3)),--(B3:AI3&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH3" s="191">
+      <c r="BH3" s="189">
         <f>RANK(BD3,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI3" s="191">
+      <c r="BI3" s="189">
         <f>RANK(BE3,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ3" s="191">
+      <c r="BJ3" s="189">
         <f>RANK(BF3,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
@@ -9664,7 +9561,9 @@
       <c r="AK4" s="120"/>
       <c r="AL4" s="120"/>
       <c r="AM4" s="120"/>
-      <c r="AN4" s="120"/>
+      <c r="AN4" s="120">
+        <v>1</v>
+      </c>
       <c r="AO4" s="120"/>
       <c r="AP4" s="120"/>
       <c r="AQ4" s="120"/>
@@ -9680,32 +9579,32 @@
       <c r="BA4" s="120"/>
       <c r="BB4" s="120"/>
       <c r="BC4" s="120"/>
-      <c r="BD4" s="189">
-        <f t="shared" ref="BD4:BD35" si="0">SUM(B4:BC4)</f>
+      <c r="BD4" s="187">
+        <f>SUM(B4:BC4)</f>
+        <v>13</v>
+      </c>
+      <c r="BE4" s="187" cm="1">
+        <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
         <v>12</v>
       </c>
-      <c r="BE4" s="189" cm="1">
-        <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>11</v>
-      </c>
-      <c r="BF4" s="189" cm="1">
+      <c r="BF4" s="187" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
         <v>3</v>
       </c>
-      <c r="BG4" s="190" cm="1">
+      <c r="BG4" s="188" cm="1">
         <f t="array" ref="BG4">SUMPRODUCT(--(B4:AI4=INT(B4:AI4)),--(B4:AI4&gt;0))/34*100%</f>
         <v>0.323529411764706</v>
       </c>
-      <c r="BH4" s="191">
-        <f t="shared" ref="BH4:BJ4" si="1">RANK(BD4,BD$3:BD$53,0)</f>
+      <c r="BH4" s="189">
+        <f>RANK(BD4,BD$3:BD$53,0)</f>
         <v>8</v>
       </c>
-      <c r="BI4" s="191">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="BJ4" s="191">
-        <f t="shared" si="1"/>
+      <c r="BI4" s="189">
+        <f>RANK(BE4,BE$3:BE$53,0)</f>
+        <v>6</v>
+      </c>
+      <c r="BJ4" s="189">
+        <f>RANK(BF4,BF$3:BF$53,0)</f>
         <v>8</v>
       </c>
     </row>
@@ -9771,32 +9670,32 @@
       <c r="BA5" s="120"/>
       <c r="BB5" s="120"/>
       <c r="BC5" s="120"/>
-      <c r="BD5" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD5" s="187">
+        <f>SUM(B5:BC5)</f>
         <v>2</v>
       </c>
-      <c r="BE5" s="189" cm="1">
+      <c r="BE5" s="187" cm="1">
         <f t="array" ref="BE5">SUMPRODUCT(--(B5:BC5=INT(B5:BC5)),--(B5:BC5&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF5" s="189" cm="1">
+      <c r="BF5" s="187" cm="1">
         <f t="array" ref="BF5">MAX(FREQUENCY(IF((B5:BC5=INT(B5:BC5))*(B5:BC5&gt;0),COLUMN(B5:BC5)),IF((B5:BC5&lt;&gt;INT(B5:BC5))+(B5:BC5&lt;=0),COLUMN(B5:BC5))))</f>
         <v>1</v>
       </c>
-      <c r="BG5" s="190" cm="1">
+      <c r="BG5" s="188" cm="1">
         <f t="array" ref="BG5">SUMPRODUCT(--(B5:AI5=INT(B5:AI5)),--(B5:AI5&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH5" s="191">
-        <f t="shared" ref="BH5:BJ5" si="2">RANK(BD5,BD$3:BD$53,0)</f>
+      <c r="BH5" s="189">
+        <f>RANK(BD5,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI5" s="191">
-        <f t="shared" si="2"/>
+      <c r="BI5" s="189">
+        <f>RANK(BE5,BE$3:BE$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BJ5" s="191">
-        <f t="shared" si="2"/>
+      <c r="BJ5" s="189">
+        <f>RANK(BF5,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -9864,32 +9763,32 @@
       <c r="BA6" s="120"/>
       <c r="BB6" s="120"/>
       <c r="BC6" s="120"/>
-      <c r="BD6" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD6" s="187">
+        <f>SUM(B6:BC6)</f>
         <v>3</v>
       </c>
-      <c r="BE6" s="189" cm="1">
+      <c r="BE6" s="187" cm="1">
         <f t="array" ref="BE6">SUMPRODUCT(--(B6:BC6=INT(B6:BC6)),--(B6:BC6&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF6" s="189" cm="1">
+      <c r="BF6" s="187" cm="1">
         <f t="array" ref="BF6">MAX(FREQUENCY(IF((B6:BC6=INT(B6:BC6))*(B6:BC6&gt;0),COLUMN(B6:BC6)),IF((B6:BC6&lt;&gt;INT(B6:BC6))+(B6:BC6&lt;=0),COLUMN(B6:BC6))))</f>
         <v>1</v>
       </c>
-      <c r="BG6" s="190" cm="1">
+      <c r="BG6" s="188" cm="1">
         <f t="array" ref="BG6">SUMPRODUCT(--(B6:AI6=INT(B6:AI6)),--(B6:AI6&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH6" s="191">
-        <f t="shared" ref="BH6:BJ6" si="3">RANK(BD6,BD$3:BD$53,0)</f>
+      <c r="BH6" s="189">
+        <f>RANK(BD6,BD$3:BD$53,0)</f>
         <v>28</v>
       </c>
-      <c r="BI6" s="191">
-        <f t="shared" si="3"/>
+      <c r="BI6" s="189">
+        <f>RANK(BE6,BE$3:BE$53,0)</f>
         <v>26</v>
       </c>
-      <c r="BJ6" s="191">
-        <f t="shared" si="3"/>
+      <c r="BJ6" s="189">
+        <f>RANK(BF6,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -9957,32 +9856,32 @@
       <c r="BA7" s="120"/>
       <c r="BB7" s="120"/>
       <c r="BC7" s="120"/>
-      <c r="BD7" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD7" s="187">
+        <f>SUM(B7:BC7)</f>
         <v>4</v>
       </c>
-      <c r="BE7" s="189" cm="1">
+      <c r="BE7" s="187" cm="1">
         <f t="array" ref="BE7">SUMPRODUCT(--(B7:BC7=INT(B7:BC7)),--(B7:BC7&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF7" s="189" cm="1">
+      <c r="BF7" s="187" cm="1">
         <f t="array" ref="BF7">MAX(FREQUENCY(IF((B7:BC7=INT(B7:BC7))*(B7:BC7&gt;0),COLUMN(B7:BC7)),IF((B7:BC7&lt;&gt;INT(B7:BC7))+(B7:BC7&lt;=0),COLUMN(B7:BC7))))</f>
         <v>1</v>
       </c>
-      <c r="BG7" s="190" cm="1">
+      <c r="BG7" s="188" cm="1">
         <f t="array" ref="BG7">SUMPRODUCT(--(B7:AI7=INT(B7:AI7)),--(B7:AI7&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH7" s="191">
-        <f t="shared" ref="BH7:BJ7" si="4">RANK(BD7,BD$3:BD$53,0)</f>
+      <c r="BH7" s="189">
+        <f>RANK(BD7,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI7" s="191">
-        <f t="shared" si="4"/>
+      <c r="BI7" s="189">
+        <f>RANK(BE7,BE$3:BE$53,0)</f>
         <v>26</v>
       </c>
-      <c r="BJ7" s="191">
-        <f t="shared" si="4"/>
+      <c r="BJ7" s="189">
+        <f>RANK(BF7,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -10066,7 +9965,9 @@
       <c r="AM8" s="120">
         <v>1</v>
       </c>
-      <c r="AN8" s="120"/>
+      <c r="AN8" s="120">
+        <v>1</v>
+      </c>
       <c r="AO8" s="120"/>
       <c r="AP8" s="120"/>
       <c r="AQ8" s="120"/>
@@ -10082,32 +9983,32 @@
       <c r="BA8" s="120"/>
       <c r="BB8" s="120"/>
       <c r="BC8" s="120"/>
-      <c r="BD8" s="189">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="BE8" s="189" cm="1">
+      <c r="BD8" s="187">
+        <f>SUM(B8:BC8)</f>
+        <v>20</v>
+      </c>
+      <c r="BE8" s="187" cm="1">
         <f t="array" ref="BE8">SUMPRODUCT(--(B8:BC8=INT(B8:BC8)),--(B8:BC8&gt;0))</f>
-        <v>19</v>
-      </c>
-      <c r="BF8" s="189" cm="1">
+        <v>20</v>
+      </c>
+      <c r="BF8" s="187" cm="1">
         <f t="array" ref="BF8">MAX(FREQUENCY(IF((B8:BC8=INT(B8:BC8))*(B8:BC8&gt;0),COLUMN(B8:BC8)),IF((B8:BC8&lt;&gt;INT(B8:BC8))+(B8:BC8&lt;=0),COLUMN(B8:BC8))))</f>
         <v>5</v>
       </c>
-      <c r="BG8" s="190" cm="1">
+      <c r="BG8" s="188" cm="1">
         <f t="array" ref="BG8">SUMPRODUCT(--(B8:AI8=INT(B8:AI8)),--(B8:AI8&gt;0))/34*100%</f>
         <v>0.470588235294118</v>
       </c>
-      <c r="BH8" s="191">
-        <f t="shared" ref="BH8:BJ8" si="5">RANK(BD8,BD$3:BD$53,0)</f>
+      <c r="BH8" s="189">
+        <f>RANK(BD8,BD$3:BD$53,0)</f>
         <v>3</v>
       </c>
-      <c r="BI8" s="191">
-        <f t="shared" si="5"/>
+      <c r="BI8" s="189">
+        <f>RANK(BE8,BE$3:BE$53,0)</f>
         <v>3</v>
       </c>
-      <c r="BJ8" s="191">
-        <f t="shared" si="5"/>
+      <c r="BJ8" s="189">
+        <f>RANK(BF8,BF$3:BF$53,0)</f>
         <v>3</v>
       </c>
     </row>
@@ -10193,32 +10094,32 @@
       <c r="BA9" s="120"/>
       <c r="BB9" s="120"/>
       <c r="BC9" s="120"/>
-      <c r="BD9" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD9" s="187">
+        <f>SUM(B9:BC9)</f>
         <v>12</v>
       </c>
-      <c r="BE9" s="189" cm="1">
+      <c r="BE9" s="187" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
         <v>12</v>
       </c>
-      <c r="BF9" s="189" cm="1">
+      <c r="BF9" s="187" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
         <v>3</v>
       </c>
-      <c r="BG9" s="190" cm="1">
+      <c r="BG9" s="188" cm="1">
         <f t="array" ref="BG9">SUMPRODUCT(--(B9:AI9=INT(B9:AI9)),--(B9:AI9&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH9" s="191">
+      <c r="BH9" s="189">
         <f>RANK(BD9,BD$3:BD$53,0)</f>
-        <v>8</v>
-      </c>
-      <c r="BI9" s="191">
-        <f t="shared" ref="BH9:BJ9" si="6">RANK(BE9,BE$3:BE$53,0)</f>
+        <v>10</v>
+      </c>
+      <c r="BI9" s="189">
+        <f>RANK(BE9,BE$3:BE$53,0)</f>
         <v>6</v>
       </c>
-      <c r="BJ9" s="191">
-        <f t="shared" si="6"/>
+      <c r="BJ9" s="189">
+        <f>RANK(BF9,BF$3:BF$53,0)</f>
         <v>8</v>
       </c>
     </row>
@@ -10282,32 +10183,32 @@
       <c r="BA10" s="120"/>
       <c r="BB10" s="120"/>
       <c r="BC10" s="120"/>
-      <c r="BD10" s="189">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="BE10" s="189" cm="1">
+      <c r="BD10" s="187">
+        <f>SUM(B10:BC10)</f>
+        <v>1</v>
+      </c>
+      <c r="BE10" s="187" cm="1">
         <f t="array" ref="BE10">SUMPRODUCT(--(B10:BC10=INT(B10:BC10)),--(B10:BC10&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF10" s="189" cm="1">
+      <c r="BF10" s="187" cm="1">
         <f t="array" ref="BF10">MAX(FREQUENCY(IF((B10:BC10=INT(B10:BC10))*(B10:BC10&gt;0),COLUMN(B10:BC10)),IF((B10:BC10&lt;&gt;INT(B10:BC10))+(B10:BC10&lt;=0),COLUMN(B10:BC10))))</f>
         <v>1</v>
       </c>
-      <c r="BG10" s="190" cm="1">
+      <c r="BG10" s="188" cm="1">
         <f t="array" ref="BG10">SUMPRODUCT(--(B10:AI10=INT(B10:AI10)),--(B10:AI10&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH10" s="191">
-        <f t="shared" ref="BH10:BJ10" si="7">RANK(BD10,BD$3:BD$53,0)</f>
+      <c r="BH10" s="189">
+        <f>RANK(BD10,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI10" s="191">
-        <f t="shared" si="7"/>
+      <c r="BI10" s="189">
+        <f>RANK(BE10,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ10" s="191">
-        <f t="shared" si="7"/>
+      <c r="BJ10" s="189">
+        <f>RANK(BF10,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -10383,32 +10284,32 @@
       <c r="BA11" s="120"/>
       <c r="BB11" s="120"/>
       <c r="BC11" s="120"/>
-      <c r="BD11" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD11" s="187">
+        <f>SUM(B11:BC11)</f>
         <v>7</v>
       </c>
-      <c r="BE11" s="189" cm="1">
+      <c r="BE11" s="187" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(--(B11:BC11=INT(B11:BC11)),--(B11:BC11&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF11" s="189" cm="1">
+      <c r="BF11" s="187" cm="1">
         <f t="array" ref="BF11">MAX(FREQUENCY(IF((B11:BC11=INT(B11:BC11))*(B11:BC11&gt;0),COLUMN(B11:BC11)),IF((B11:BC11&lt;&gt;INT(B11:BC11))+(B11:BC11&lt;=0),COLUMN(B11:BC11))))</f>
         <v>1</v>
       </c>
-      <c r="BG11" s="190" cm="1">
+      <c r="BG11" s="188" cm="1">
         <f t="array" ref="BG11">SUMPRODUCT(--(B11:AI11=INT(B11:AI11)),--(B11:AI11&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH11" s="191">
-        <f t="shared" ref="BH11:BJ11" si="8">RANK(BD11,BD$3:BD$53,0)</f>
+      <c r="BH11" s="189">
+        <f>RANK(BD11,BD$3:BD$53,0)</f>
         <v>19</v>
       </c>
-      <c r="BI11" s="191">
-        <f t="shared" si="8"/>
+      <c r="BI11" s="189">
+        <f>RANK(BE11,BE$3:BE$53,0)</f>
         <v>17</v>
       </c>
-      <c r="BJ11" s="191">
-        <f t="shared" si="8"/>
+      <c r="BJ11" s="189">
+        <f>RANK(BF11,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -10474,32 +10375,32 @@
       <c r="BA12" s="120"/>
       <c r="BB12" s="120"/>
       <c r="BC12" s="120"/>
-      <c r="BD12" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD12" s="187">
+        <f>SUM(B12:BC12)</f>
         <v>2</v>
       </c>
-      <c r="BE12" s="189" cm="1">
+      <c r="BE12" s="187" cm="1">
         <f t="array" ref="BE12">SUMPRODUCT(--(B12:BC12=INT(B12:BC12)),--(B12:BC12&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF12" s="189" cm="1">
+      <c r="BF12" s="187" cm="1">
         <f t="array" ref="BF12">MAX(FREQUENCY(IF((B12:BC12=INT(B12:BC12))*(B12:BC12&gt;0),COLUMN(B12:BC12)),IF((B12:BC12&lt;&gt;INT(B12:BC12))+(B12:BC12&lt;=0),COLUMN(B12:BC12))))</f>
         <v>1</v>
       </c>
-      <c r="BG12" s="190" cm="1">
+      <c r="BG12" s="188" cm="1">
         <f t="array" ref="BG12">SUMPRODUCT(--(B12:AI12=INT(B12:AI12)),--(B12:AI12&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH12" s="191">
-        <f t="shared" ref="BH12:BJ12" si="9">RANK(BD12,BD$3:BD$53,0)</f>
+      <c r="BH12" s="189">
+        <f>RANK(BD12,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI12" s="191">
-        <f t="shared" si="9"/>
+      <c r="BI12" s="189">
+        <f>RANK(BE12,BE$3:BE$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BJ12" s="191">
-        <f t="shared" si="9"/>
+      <c r="BJ12" s="189">
+        <f>RANK(BF12,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -10563,7 +10464,9 @@
       <c r="AK13" s="120"/>
       <c r="AL13" s="120"/>
       <c r="AM13" s="120"/>
-      <c r="AN13" s="120"/>
+      <c r="AN13" s="120">
+        <v>1</v>
+      </c>
       <c r="AO13" s="120"/>
       <c r="AP13" s="120"/>
       <c r="AQ13" s="120"/>
@@ -10579,32 +10482,32 @@
       <c r="BA13" s="120"/>
       <c r="BB13" s="120"/>
       <c r="BC13" s="120"/>
-      <c r="BD13" s="189">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="BE13" s="189" cm="1">
+      <c r="BD13" s="187">
+        <f>SUM(B13:BC13)</f>
+        <v>10</v>
+      </c>
+      <c r="BE13" s="187" cm="1">
         <f t="array" ref="BE13">SUMPRODUCT(--(B13:BC13=INT(B13:BC13)),--(B13:BC13&gt;0))</f>
-        <v>9</v>
-      </c>
-      <c r="BF13" s="189" cm="1">
+        <v>10</v>
+      </c>
+      <c r="BF13" s="187" cm="1">
         <f t="array" ref="BF13">MAX(FREQUENCY(IF((B13:BC13=INT(B13:BC13))*(B13:BC13&gt;0),COLUMN(B13:BC13)),IF((B13:BC13&lt;&gt;INT(B13:BC13))+(B13:BC13&lt;=0),COLUMN(B13:BC13))))</f>
         <v>1</v>
       </c>
-      <c r="BG13" s="190" cm="1">
+      <c r="BG13" s="188" cm="1">
         <f t="array" ref="BG13">SUMPRODUCT(--(B13:AI13=INT(B13:AI13)),--(B13:AI13&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH13" s="191">
-        <f t="shared" ref="BH13:BJ13" si="10">RANK(BD13,BD$3:BD$53,0)</f>
+      <c r="BH13" s="189">
+        <f>RANK(BD13,BD$3:BD$53,0)</f>
         <v>14</v>
       </c>
-      <c r="BI13" s="191">
-        <f t="shared" si="10"/>
-        <v>13</v>
-      </c>
-      <c r="BJ13" s="191">
-        <f t="shared" si="10"/>
+      <c r="BI13" s="189">
+        <f>RANK(BE13,BE$3:BE$53,0)</f>
+        <v>12</v>
+      </c>
+      <c r="BJ13" s="189">
+        <f>RANK(BF13,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -10670,32 +10573,32 @@
       <c r="BA14" s="120"/>
       <c r="BB14" s="120"/>
       <c r="BC14" s="120"/>
-      <c r="BD14" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD14" s="187">
+        <f>SUM(B14:BC14)</f>
         <v>2</v>
       </c>
-      <c r="BE14" s="189" cm="1">
+      <c r="BE14" s="187" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(--(B14:BC14=INT(B14:BC14)),--(B14:BC14&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF14" s="189" cm="1">
+      <c r="BF14" s="187" cm="1">
         <f t="array" ref="BF14">MAX(FREQUENCY(IF((B14:BC14=INT(B14:BC14))*(B14:BC14&gt;0),COLUMN(B14:BC14)),IF((B14:BC14&lt;&gt;INT(B14:BC14))+(B14:BC14&lt;=0),COLUMN(B14:BC14))))</f>
         <v>1</v>
       </c>
-      <c r="BG14" s="190" cm="1">
+      <c r="BG14" s="188" cm="1">
         <f t="array" ref="BG14">SUMPRODUCT(--(B14:AI14=INT(B14:AI14)),--(B14:AI14&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH14" s="191">
-        <f t="shared" ref="BH14:BJ14" si="11">RANK(BD14,BD$3:BD$53,0)</f>
+      <c r="BH14" s="189">
+        <f>RANK(BD14,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI14" s="191">
-        <f t="shared" si="11"/>
+      <c r="BI14" s="189">
+        <f>RANK(BE14,BE$3:BE$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BJ14" s="191">
-        <f t="shared" si="11"/>
+      <c r="BJ14" s="189">
+        <f>RANK(BF14,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -10761,7 +10664,9 @@
       <c r="AM15" s="120">
         <v>1</v>
       </c>
-      <c r="AN15" s="120"/>
+      <c r="AN15" s="120">
+        <v>2</v>
+      </c>
       <c r="AO15" s="120"/>
       <c r="AP15" s="120"/>
       <c r="AQ15" s="120"/>
@@ -10777,32 +10682,32 @@
       <c r="BA15" s="120"/>
       <c r="BB15" s="120"/>
       <c r="BC15" s="120"/>
-      <c r="BD15" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD15" s="187">
+        <f>SUM(B15:BC15)</f>
+        <v>13</v>
+      </c>
+      <c r="BE15" s="187" cm="1">
+        <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BE15" s="189" cm="1">
-        <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>10</v>
-      </c>
-      <c r="BF15" s="189" cm="1">
+      <c r="BF15" s="187" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
         <v>2</v>
       </c>
-      <c r="BG15" s="190" cm="1">
+      <c r="BG15" s="188" cm="1">
         <f t="array" ref="BG15">SUMPRODUCT(--(B15:AI15=INT(B15:AI15)),--(B15:AI15&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH15" s="191">
-        <f t="shared" ref="BH15:BJ15" si="12">RANK(BD15,BD$3:BD$53,0)</f>
-        <v>10</v>
-      </c>
-      <c r="BI15" s="191">
-        <f t="shared" si="12"/>
-        <v>9</v>
-      </c>
-      <c r="BJ15" s="191">
-        <f t="shared" si="12"/>
+      <c r="BH15" s="189">
+        <f>RANK(BD15,BD$3:BD$53,0)</f>
+        <v>8</v>
+      </c>
+      <c r="BI15" s="189">
+        <f>RANK(BE15,BE$3:BE$53,0)</f>
+        <v>8</v>
+      </c>
+      <c r="BJ15" s="189">
+        <f>RANK(BF15,BF$3:BF$53,0)</f>
         <v>13</v>
       </c>
     </row>
@@ -10868,32 +10773,32 @@
       <c r="BA16" s="120"/>
       <c r="BB16" s="120"/>
       <c r="BC16" s="120"/>
-      <c r="BD16" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD16" s="187">
+        <f>SUM(B16:BC16)</f>
         <v>2</v>
       </c>
-      <c r="BE16" s="189" cm="1">
+      <c r="BE16" s="187" cm="1">
         <f t="array" ref="BE16">SUMPRODUCT(--(B16:BC16=INT(B16:BC16)),--(B16:BC16&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF16" s="189" cm="1">
+      <c r="BF16" s="187" cm="1">
         <f t="array" ref="BF16">MAX(FREQUENCY(IF((B16:BC16=INT(B16:BC16))*(B16:BC16&gt;0),COLUMN(B16:BC16)),IF((B16:BC16&lt;&gt;INT(B16:BC16))+(B16:BC16&lt;=0),COLUMN(B16:BC16))))</f>
         <v>1</v>
       </c>
-      <c r="BG16" s="190" cm="1">
+      <c r="BG16" s="188" cm="1">
         <f t="array" ref="BG16">SUMPRODUCT(--(B16:AI16=INT(B16:AI16)),--(B16:AI16&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH16" s="191">
-        <f t="shared" ref="BH16:BJ16" si="13">RANK(BD16,BD$3:BD$53,0)</f>
+      <c r="BH16" s="189">
+        <f>RANK(BD16,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI16" s="191">
-        <f t="shared" si="13"/>
+      <c r="BI16" s="189">
+        <f>RANK(BE16,BE$3:BE$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BJ16" s="191">
-        <f t="shared" si="13"/>
+      <c r="BJ16" s="189">
+        <f>RANK(BF16,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -10963,32 +10868,32 @@
       <c r="BA17" s="120"/>
       <c r="BB17" s="120"/>
       <c r="BC17" s="120"/>
-      <c r="BD17" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD17" s="187">
+        <f>SUM(B17:BC17)</f>
         <v>4</v>
       </c>
-      <c r="BE17" s="189" cm="1">
+      <c r="BE17" s="187" cm="1">
         <f t="array" ref="BE17">SUMPRODUCT(--(B17:BC17=INT(B17:BC17)),--(B17:BC17&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF17" s="189" cm="1">
+      <c r="BF17" s="187" cm="1">
         <f t="array" ref="BF17">MAX(FREQUENCY(IF((B17:BC17=INT(B17:BC17))*(B17:BC17&gt;0),COLUMN(B17:BC17)),IF((B17:BC17&lt;&gt;INT(B17:BC17))+(B17:BC17&lt;=0),COLUMN(B17:BC17))))</f>
         <v>1</v>
       </c>
-      <c r="BG17" s="190" cm="1">
+      <c r="BG17" s="188" cm="1">
         <f t="array" ref="BG17">SUMPRODUCT(--(B17:AI17=INT(B17:AI17)),--(B17:AI17&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH17" s="191">
-        <f t="shared" ref="BH17:BJ17" si="14">RANK(BD17,BD$3:BD$53,0)</f>
+      <c r="BH17" s="189">
+        <f>RANK(BD17,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI17" s="191">
-        <f t="shared" si="14"/>
+      <c r="BI17" s="189">
+        <f>RANK(BE17,BE$3:BE$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BJ17" s="191">
-        <f t="shared" si="14"/>
+      <c r="BJ17" s="189">
+        <f>RANK(BF17,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -11052,32 +10957,32 @@
       <c r="BA18" s="120"/>
       <c r="BB18" s="120"/>
       <c r="BC18" s="120"/>
-      <c r="BD18" s="189">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="BE18" s="189" cm="1">
+      <c r="BD18" s="187">
+        <f>SUM(B18:BC18)</f>
+        <v>1</v>
+      </c>
+      <c r="BE18" s="187" cm="1">
         <f t="array" ref="BE18">SUMPRODUCT(--(B18:BC18=INT(B18:BC18)),--(B18:BC18&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF18" s="189" cm="1">
+      <c r="BF18" s="187" cm="1">
         <f t="array" ref="BF18">MAX(FREQUENCY(IF((B18:BC18=INT(B18:BC18))*(B18:BC18&gt;0),COLUMN(B18:BC18)),IF((B18:BC18&lt;&gt;INT(B18:BC18))+(B18:BC18&lt;=0),COLUMN(B18:BC18))))</f>
         <v>1</v>
       </c>
-      <c r="BG18" s="190" cm="1">
+      <c r="BG18" s="188" cm="1">
         <f t="array" ref="BG18">SUMPRODUCT(--(B18:AI18=INT(B18:AI18)),--(B18:AI18&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH18" s="191">
-        <f t="shared" ref="BH18:BJ18" si="15">RANK(BD18,BD$3:BD$53,0)</f>
+      <c r="BH18" s="189">
+        <f>RANK(BD18,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI18" s="191">
-        <f t="shared" si="15"/>
+      <c r="BI18" s="189">
+        <f>RANK(BE18,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ18" s="191">
-        <f t="shared" si="15"/>
+      <c r="BJ18" s="189">
+        <f>RANK(BF18,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -11149,32 +11054,32 @@
       <c r="BA19" s="120"/>
       <c r="BB19" s="120"/>
       <c r="BC19" s="120"/>
-      <c r="BD19" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD19" s="187">
+        <f>SUM(B19:BC19)</f>
         <v>5</v>
       </c>
-      <c r="BE19" s="189" cm="1">
+      <c r="BE19" s="187" cm="1">
         <f t="array" ref="BE19">SUMPRODUCT(--(B19:BC19=INT(B19:BC19)),--(B19:BC19&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF19" s="189" cm="1">
+      <c r="BF19" s="187" cm="1">
         <f t="array" ref="BF19">MAX(FREQUENCY(IF((B19:BC19=INT(B19:BC19))*(B19:BC19&gt;0),COLUMN(B19:BC19)),IF((B19:BC19&lt;&gt;INT(B19:BC19))+(B19:BC19&lt;=0),COLUMN(B19:BC19))))</f>
         <v>2</v>
       </c>
-      <c r="BG19" s="190" cm="1">
+      <c r="BG19" s="188" cm="1">
         <f t="array" ref="BG19">SUMPRODUCT(--(B19:AI19=INT(B19:AI19)),--(B19:AI19&gt;0))/34*100%</f>
         <v>0.147058823529412</v>
       </c>
-      <c r="BH19" s="191">
-        <f t="shared" ref="BH19:BJ19" si="16">RANK(BD19,BD$3:BD$53,0)</f>
+      <c r="BH19" s="189">
+        <f>RANK(BD19,BD$3:BD$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BI19" s="191">
-        <f t="shared" si="16"/>
+      <c r="BI19" s="189">
+        <f>RANK(BE19,BE$3:BE$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BJ19" s="191">
-        <f t="shared" si="16"/>
+      <c r="BJ19" s="189">
+        <f>RANK(BF19,BF$3:BF$53,0)</f>
         <v>13</v>
       </c>
     </row>
@@ -11238,32 +11143,32 @@
       <c r="BA20" s="120"/>
       <c r="BB20" s="120"/>
       <c r="BC20" s="120"/>
-      <c r="BD20" s="189">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="BE20" s="189" cm="1">
+      <c r="BD20" s="187">
+        <f>SUM(B20:BC20)</f>
+        <v>1</v>
+      </c>
+      <c r="BE20" s="187" cm="1">
         <f t="array" ref="BE20">SUMPRODUCT(--(B20:BC20=INT(B20:BC20)),--(B20:BC20&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF20" s="189" cm="1">
+      <c r="BF20" s="187" cm="1">
         <f t="array" ref="BF20">MAX(FREQUENCY(IF((B20:BC20=INT(B20:BC20))*(B20:BC20&gt;0),COLUMN(B20:BC20)),IF((B20:BC20&lt;&gt;INT(B20:BC20))+(B20:BC20&lt;=0),COLUMN(B20:BC20))))</f>
         <v>1</v>
       </c>
-      <c r="BG20" s="190" cm="1">
+      <c r="BG20" s="188" cm="1">
         <f t="array" ref="BG20">SUMPRODUCT(--(B20:AI20=INT(B20:AI20)),--(B20:AI20&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH20" s="191">
-        <f t="shared" ref="BH20:BJ20" si="17">RANK(BD20,BD$3:BD$53,0)</f>
+      <c r="BH20" s="189">
+        <f>RANK(BD20,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI20" s="191">
-        <f t="shared" si="17"/>
+      <c r="BI20" s="189">
+        <f>RANK(BE20,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ20" s="191">
-        <f t="shared" si="17"/>
+      <c r="BJ20" s="189">
+        <f>RANK(BF20,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -11329,32 +11234,32 @@
       <c r="BA21" s="120"/>
       <c r="BB21" s="120"/>
       <c r="BC21" s="120"/>
-      <c r="BD21" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD21" s="187">
+        <f>SUM(B21:BC21)</f>
         <v>2</v>
       </c>
-      <c r="BE21" s="189" cm="1">
+      <c r="BE21" s="187" cm="1">
         <f t="array" ref="BE21">SUMPRODUCT(--(B21:BC21=INT(B21:BC21)),--(B21:BC21&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF21" s="189" cm="1">
+      <c r="BF21" s="187" cm="1">
         <f t="array" ref="BF21">MAX(FREQUENCY(IF((B21:BC21=INT(B21:BC21))*(B21:BC21&gt;0),COLUMN(B21:BC21)),IF((B21:BC21&lt;&gt;INT(B21:BC21))+(B21:BC21&lt;=0),COLUMN(B21:BC21))))</f>
         <v>1</v>
       </c>
-      <c r="BG21" s="190" cm="1">
+      <c r="BG21" s="188" cm="1">
         <f t="array" ref="BG21">SUMPRODUCT(--(B21:AI21=INT(B21:AI21)),--(B21:AI21&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH21" s="191">
-        <f t="shared" ref="BH21:BJ21" si="18">RANK(BD21,BD$3:BD$53,0)</f>
+      <c r="BH21" s="189">
+        <f>RANK(BD21,BD$3:BD$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BI21" s="191">
-        <f t="shared" si="18"/>
+      <c r="BI21" s="189">
+        <f>RANK(BE21,BE$3:BE$53,0)</f>
         <v>29</v>
       </c>
-      <c r="BJ21" s="191">
-        <f t="shared" si="18"/>
+      <c r="BJ21" s="189">
+        <f>RANK(BF21,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -11438,37 +11343,37 @@
       <c r="BA22" s="120"/>
       <c r="BB22" s="120"/>
       <c r="BC22" s="120"/>
-      <c r="BD22" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD22" s="187">
+        <f>SUM(B22:BC22)</f>
         <v>14</v>
       </c>
-      <c r="BE22" s="189" cm="1">
+      <c r="BE22" s="187" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF22" s="189" cm="1">
+      <c r="BF22" s="187" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
         <v>4</v>
       </c>
-      <c r="BG22" s="190" cm="1">
+      <c r="BG22" s="188" cm="1">
         <f t="array" ref="BG22">SUMPRODUCT(--(B22:AI22=INT(B22:AI22)),--(B22:AI22&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH22" s="191">
-        <f t="shared" ref="BH22:BJ22" si="19">RANK(BD22,BD$3:BD$53,0)</f>
+      <c r="BH22" s="189">
+        <f>RANK(BD22,BD$3:BD$53,0)</f>
         <v>6</v>
       </c>
-      <c r="BI22" s="191">
-        <f t="shared" si="19"/>
-        <v>7</v>
-      </c>
-      <c r="BJ22" s="191">
-        <f t="shared" si="19"/>
+      <c r="BI22" s="189">
+        <f>RANK(BE22,BE$3:BE$53,0)</f>
+        <v>8</v>
+      </c>
+      <c r="BJ22" s="189">
+        <f>RANK(BF22,BF$3:BF$53,0)</f>
         <v>6</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:62">
-      <c r="A23" s="192">
+      <c r="A23" s="190">
         <v>21</v>
       </c>
       <c r="B23" s="120"/>
@@ -11525,32 +11430,32 @@
       <c r="BA23" s="120"/>
       <c r="BB23" s="120"/>
       <c r="BC23" s="120"/>
-      <c r="BD23" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD23" s="187">
+        <f>SUM(B23:BC23)</f>
         <v>0</v>
       </c>
-      <c r="BE23" s="189" cm="1">
+      <c r="BE23" s="187" cm="1">
         <f t="array" ref="BE23">SUMPRODUCT(--(B23:BC23=INT(B23:BC23)),--(B23:BC23&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF23" s="189" cm="1">
+      <c r="BF23" s="187" cm="1">
         <f t="array" ref="BF23">MAX(FREQUENCY(IF((B23:BC23=INT(B23:BC23))*(B23:BC23&gt;0),COLUMN(B23:BC23)),IF((B23:BC23&lt;&gt;INT(B23:BC23))+(B23:BC23&lt;=0),COLUMN(B23:BC23))))</f>
         <v>0</v>
       </c>
-      <c r="BG23" s="190" cm="1">
+      <c r="BG23" s="188" cm="1">
         <f t="array" ref="BG23">SUMPRODUCT(--(B23:AI23=INT(B23:AI23)),--(B23:AI23&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH23" s="191">
-        <f t="shared" ref="BH23:BJ23" si="20">RANK(BD23,BD$3:BD$53,0)</f>
+      <c r="BH23" s="189">
+        <f>RANK(BD23,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI23" s="191">
-        <f t="shared" si="20"/>
+      <c r="BI23" s="189">
+        <f>RANK(BE23,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ23" s="191">
-        <f t="shared" si="20"/>
+      <c r="BJ23" s="189">
+        <f>RANK(BF23,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
@@ -11628,32 +11533,32 @@
       <c r="BA24" s="120"/>
       <c r="BB24" s="120"/>
       <c r="BC24" s="120"/>
-      <c r="BD24" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD24" s="187">
+        <f>SUM(B24:BC24)</f>
         <v>8</v>
       </c>
-      <c r="BE24" s="189" cm="1">
+      <c r="BE24" s="187" cm="1">
         <f t="array" ref="BE24">SUMPRODUCT(--(B24:BC24=INT(B24:BC24)),--(B24:BC24&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="BF24" s="189" cm="1">
+      <c r="BF24" s="187" cm="1">
         <f t="array" ref="BF24">MAX(FREQUENCY(IF((B24:BC24=INT(B24:BC24))*(B24:BC24&gt;0),COLUMN(B24:BC24)),IF((B24:BC24&lt;&gt;INT(B24:BC24))+(B24:BC24&lt;=0),COLUMN(B24:BC24))))</f>
         <v>3</v>
       </c>
-      <c r="BG24" s="190" cm="1">
+      <c r="BG24" s="188" cm="1">
         <f t="array" ref="BG24">SUMPRODUCT(--(B24:AI24=INT(B24:AI24)),--(B24:AI24&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH24" s="191">
-        <f t="shared" ref="BH24:BJ24" si="21">RANK(BD24,BD$3:BD$53,0)</f>
+      <c r="BH24" s="189">
+        <f>RANK(BD24,BD$3:BD$53,0)</f>
         <v>16</v>
       </c>
-      <c r="BI24" s="191">
-        <f t="shared" si="21"/>
+      <c r="BI24" s="189">
+        <f>RANK(BE24,BE$3:BE$53,0)</f>
         <v>16</v>
       </c>
-      <c r="BJ24" s="191">
-        <f t="shared" si="21"/>
+      <c r="BJ24" s="189">
+        <f>RANK(BF24,BF$3:BF$53,0)</f>
         <v>8</v>
       </c>
     </row>
@@ -11717,37 +11622,37 @@
       <c r="BA25" s="120"/>
       <c r="BB25" s="120"/>
       <c r="BC25" s="120"/>
-      <c r="BD25" s="189">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="BE25" s="189" cm="1">
+      <c r="BD25" s="187">
+        <f>SUM(B25:BC25)</f>
+        <v>1</v>
+      </c>
+      <c r="BE25" s="187" cm="1">
         <f t="array" ref="BE25">SUMPRODUCT(--(B25:BC25=INT(B25:BC25)),--(B25:BC25&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF25" s="189" cm="1">
+      <c r="BF25" s="187" cm="1">
         <f t="array" ref="BF25">MAX(FREQUENCY(IF((B25:BC25=INT(B25:BC25))*(B25:BC25&gt;0),COLUMN(B25:BC25)),IF((B25:BC25&lt;&gt;INT(B25:BC25))+(B25:BC25&lt;=0),COLUMN(B25:BC25))))</f>
         <v>1</v>
       </c>
-      <c r="BG25" s="190" cm="1">
+      <c r="BG25" s="188" cm="1">
         <f t="array" ref="BG25">SUMPRODUCT(--(B25:AI25=INT(B25:AI25)),--(B25:AI25&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH25" s="191">
-        <f t="shared" ref="BH25:BJ25" si="22">RANK(BD25,BD$3:BD$53,0)</f>
+      <c r="BH25" s="189">
+        <f>RANK(BD25,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI25" s="191">
-        <f t="shared" si="22"/>
+      <c r="BI25" s="189">
+        <f>RANK(BE25,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ25" s="191">
-        <f t="shared" si="22"/>
+      <c r="BJ25" s="189">
+        <f>RANK(BF25,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:62">
-      <c r="A26" s="192">
+      <c r="A26" s="190">
         <v>24</v>
       </c>
       <c r="B26" s="120"/>
@@ -11804,37 +11709,37 @@
       <c r="BA26" s="120"/>
       <c r="BB26" s="120"/>
       <c r="BC26" s="120"/>
-      <c r="BD26" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD26" s="187">
+        <f>SUM(B26:BC26)</f>
         <v>0</v>
       </c>
-      <c r="BE26" s="189" cm="1">
+      <c r="BE26" s="187" cm="1">
         <f t="array" ref="BE26">SUMPRODUCT(--(B26:BC26=INT(B26:BC26)),--(B26:BC26&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF26" s="189" cm="1">
+      <c r="BF26" s="187" cm="1">
         <f t="array" ref="BF26">MAX(FREQUENCY(IF((B26:BC26=INT(B26:BC26))*(B26:BC26&gt;0),COLUMN(B26:BC26)),IF((B26:BC26&lt;&gt;INT(B26:BC26))+(B26:BC26&lt;=0),COLUMN(B26:BC26))))</f>
         <v>0</v>
       </c>
-      <c r="BG26" s="190" cm="1">
+      <c r="BG26" s="188" cm="1">
         <f t="array" ref="BG26">SUMPRODUCT(--(B26:AI26=INT(B26:AI26)),--(B26:AI26&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH26" s="191">
-        <f t="shared" ref="BH26:BJ26" si="23">RANK(BD26,BD$3:BD$53,0)</f>
+      <c r="BH26" s="189">
+        <f>RANK(BD26,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI26" s="191">
-        <f t="shared" si="23"/>
+      <c r="BI26" s="189">
+        <f>RANK(BE26,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ26" s="191">
-        <f t="shared" si="23"/>
+      <c r="BJ26" s="189">
+        <f>RANK(BF26,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:62">
-      <c r="A27" s="192">
+      <c r="A27" s="190">
         <v>25</v>
       </c>
       <c r="B27" s="120"/>
@@ -11891,32 +11796,32 @@
       <c r="BA27" s="120"/>
       <c r="BB27" s="120"/>
       <c r="BC27" s="120"/>
-      <c r="BD27" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD27" s="187">
+        <f>SUM(B27:BC27)</f>
         <v>0</v>
       </c>
-      <c r="BE27" s="189" cm="1">
+      <c r="BE27" s="187" cm="1">
         <f t="array" ref="BE27">SUMPRODUCT(--(B27:BC27=INT(B27:BC27)),--(B27:BC27&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF27" s="189" cm="1">
+      <c r="BF27" s="187" cm="1">
         <f t="array" ref="BF27">MAX(FREQUENCY(IF((B27:BC27=INT(B27:BC27))*(B27:BC27&gt;0),COLUMN(B27:BC27)),IF((B27:BC27&lt;&gt;INT(B27:BC27))+(B27:BC27&lt;=0),COLUMN(B27:BC27))))</f>
         <v>0</v>
       </c>
-      <c r="BG27" s="190" cm="1">
+      <c r="BG27" s="188" cm="1">
         <f t="array" ref="BG27">SUMPRODUCT(--(B27:AI27=INT(B27:AI27)),--(B27:AI27&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH27" s="191">
-        <f t="shared" ref="BH27:BJ27" si="24">RANK(BD27,BD$3:BD$53,0)</f>
+      <c r="BH27" s="189">
+        <f>RANK(BD27,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI27" s="191">
-        <f t="shared" si="24"/>
+      <c r="BI27" s="189">
+        <f>RANK(BE27,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ27" s="191">
-        <f t="shared" si="24"/>
+      <c r="BJ27" s="189">
+        <f>RANK(BF27,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
@@ -11996,32 +11901,32 @@
       <c r="BA28" s="120"/>
       <c r="BB28" s="120"/>
       <c r="BC28" s="120"/>
-      <c r="BD28" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD28" s="187">
+        <f>SUM(B28:BC28)</f>
         <v>9</v>
       </c>
-      <c r="BE28" s="189" cm="1">
+      <c r="BE28" s="187" cm="1">
         <f t="array" ref="BE28">SUMPRODUCT(--(B28:BC28=INT(B28:BC28)),--(B28:BC28&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="BF28" s="189" cm="1">
+      <c r="BF28" s="187" cm="1">
         <f t="array" ref="BF28">MAX(FREQUENCY(IF((B28:BC28=INT(B28:BC28))*(B28:BC28&gt;0),COLUMN(B28:BC28)),IF((B28:BC28&lt;&gt;INT(B28:BC28))+(B28:BC28&lt;=0),COLUMN(B28:BC28))))</f>
         <v>2</v>
       </c>
-      <c r="BG28" s="190" cm="1">
+      <c r="BG28" s="188" cm="1">
         <f t="array" ref="BG28">SUMPRODUCT(--(B28:AI28=INT(B28:AI28)),--(B28:AI28&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH28" s="191">
-        <f t="shared" ref="BH28:BJ28" si="25">RANK(BD28,BD$3:BD$53,0)</f>
-        <v>14</v>
-      </c>
-      <c r="BI28" s="191">
-        <f t="shared" si="25"/>
-        <v>13</v>
-      </c>
-      <c r="BJ28" s="191">
-        <f t="shared" si="25"/>
+      <c r="BH28" s="189">
+        <f>RANK(BD28,BD$3:BD$53,0)</f>
+        <v>15</v>
+      </c>
+      <c r="BI28" s="189">
+        <f>RANK(BE28,BE$3:BE$53,0)</f>
+        <v>15</v>
+      </c>
+      <c r="BJ28" s="189">
+        <f>RANK(BF28,BF$3:BF$53,0)</f>
         <v>13</v>
       </c>
     </row>
@@ -12093,32 +11998,32 @@
       <c r="BA29" s="120"/>
       <c r="BB29" s="120"/>
       <c r="BC29" s="120"/>
-      <c r="BD29" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD29" s="187">
+        <f>SUM(B29:BC29)</f>
         <v>5</v>
       </c>
-      <c r="BE29" s="189" cm="1">
+      <c r="BE29" s="187" cm="1">
         <f t="array" ref="BE29">SUMPRODUCT(--(B29:BC29=INT(B29:BC29)),--(B29:BC29&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF29" s="189" cm="1">
+      <c r="BF29" s="187" cm="1">
         <f t="array" ref="BF29">MAX(FREQUENCY(IF((B29:BC29=INT(B29:BC29))*(B29:BC29&gt;0),COLUMN(B29:BC29)),IF((B29:BC29&lt;&gt;INT(B29:BC29))+(B29:BC29&lt;=0),COLUMN(B29:BC29))))</f>
         <v>1</v>
       </c>
-      <c r="BG29" s="190" cm="1">
+      <c r="BG29" s="188" cm="1">
         <f t="array" ref="BG29">SUMPRODUCT(--(B29:AI29=INT(B29:AI29)),--(B29:AI29&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH29" s="191">
-        <f t="shared" ref="BH29:BJ29" si="26">RANK(BD29,BD$3:BD$53,0)</f>
+      <c r="BH29" s="189">
+        <f>RANK(BD29,BD$3:BD$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BI29" s="191">
-        <f t="shared" si="26"/>
+      <c r="BI29" s="189">
+        <f>RANK(BE29,BE$3:BE$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BJ29" s="191">
-        <f t="shared" si="26"/>
+      <c r="BJ29" s="189">
+        <f>RANK(BF29,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -12194,32 +12099,32 @@
       <c r="BA30" s="120"/>
       <c r="BB30" s="120"/>
       <c r="BC30" s="120"/>
-      <c r="BD30" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD30" s="187">
+        <f>SUM(B30:BC30)</f>
         <v>8</v>
       </c>
-      <c r="BE30" s="189" cm="1">
+      <c r="BE30" s="187" cm="1">
         <f t="array" ref="BE30">SUMPRODUCT(--(B30:BC30=INT(B30:BC30)),--(B30:BC30&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF30" s="189" cm="1">
+      <c r="BF30" s="187" cm="1">
         <f t="array" ref="BF30">MAX(FREQUENCY(IF((B30:BC30=INT(B30:BC30))*(B30:BC30&gt;0),COLUMN(B30:BC30)),IF((B30:BC30&lt;&gt;INT(B30:BC30))+(B30:BC30&lt;=0),COLUMN(B30:BC30))))</f>
         <v>4</v>
       </c>
-      <c r="BG30" s="190" cm="1">
+      <c r="BG30" s="188" cm="1">
         <f t="array" ref="BG30">SUMPRODUCT(--(B30:AI30=INT(B30:AI30)),--(B30:AI30&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH30" s="191">
-        <f t="shared" ref="BH30:BJ30" si="27">RANK(BD30,BD$3:BD$53,0)</f>
+      <c r="BH30" s="189">
+        <f>RANK(BD30,BD$3:BD$53,0)</f>
         <v>16</v>
       </c>
-      <c r="BI30" s="191">
-        <f t="shared" si="27"/>
+      <c r="BI30" s="189">
+        <f>RANK(BE30,BE$3:BE$53,0)</f>
         <v>17</v>
       </c>
-      <c r="BJ30" s="191">
-        <f t="shared" si="27"/>
+      <c r="BJ30" s="189">
+        <f>RANK(BF30,BF$3:BF$53,0)</f>
         <v>6</v>
       </c>
     </row>
@@ -12283,7 +12188,9 @@
       </c>
       <c r="AL31" s="120"/>
       <c r="AM31" s="120"/>
-      <c r="AN31" s="120"/>
+      <c r="AN31" s="120">
+        <v>1</v>
+      </c>
       <c r="AO31" s="120"/>
       <c r="AP31" s="120"/>
       <c r="AQ31" s="120"/>
@@ -12299,32 +12206,32 @@
       <c r="BA31" s="120"/>
       <c r="BB31" s="120"/>
       <c r="BC31" s="120"/>
-      <c r="BD31" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD31" s="187">
+        <f>SUM(B31:BC31)</f>
+        <v>11</v>
+      </c>
+      <c r="BE31" s="187" cm="1">
+        <f t="array" ref="BE31">SUMPRODUCT(--(B31:BC31=INT(B31:BC31)),--(B31:BC31&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BE31" s="189" cm="1">
-        <f t="array" ref="BE31">SUMPRODUCT(--(B31:BC31=INT(B31:BC31)),--(B31:BC31&gt;0))</f>
-        <v>9</v>
-      </c>
-      <c r="BF31" s="189" cm="1">
+      <c r="BF31" s="187" cm="1">
         <f t="array" ref="BF31">MAX(FREQUENCY(IF((B31:BC31=INT(B31:BC31))*(B31:BC31&gt;0),COLUMN(B31:BC31)),IF((B31:BC31&lt;&gt;INT(B31:BC31))+(B31:BC31&lt;=0),COLUMN(B31:BC31))))</f>
         <v>2</v>
       </c>
-      <c r="BG31" s="190" cm="1">
+      <c r="BG31" s="188" cm="1">
         <f t="array" ref="BG31">SUMPRODUCT(--(B31:AI31=INT(B31:AI31)),--(B31:AI31&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH31" s="191">
-        <f t="shared" ref="BH31:BJ31" si="28">RANK(BD31,BD$3:BD$53,0)</f>
+      <c r="BH31" s="189">
+        <f>RANK(BD31,BD$3:BD$53,0)</f>
         <v>12</v>
       </c>
-      <c r="BI31" s="191">
-        <f t="shared" si="28"/>
-        <v>13</v>
-      </c>
-      <c r="BJ31" s="191">
-        <f t="shared" si="28"/>
+      <c r="BI31" s="189">
+        <f>RANK(BE31,BE$3:BE$53,0)</f>
+        <v>12</v>
+      </c>
+      <c r="BJ31" s="189">
+        <f>RANK(BF31,BF$3:BF$53,0)</f>
         <v>13</v>
       </c>
     </row>
@@ -12406,32 +12313,32 @@
       <c r="BA32" s="120"/>
       <c r="BB32" s="120"/>
       <c r="BC32" s="120"/>
-      <c r="BD32" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD32" s="187">
+        <f>SUM(B32:BC32)</f>
         <v>11</v>
       </c>
-      <c r="BE32" s="189" cm="1">
+      <c r="BE32" s="187" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BF32" s="189" cm="1">
+      <c r="BF32" s="187" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
         <v>3</v>
       </c>
-      <c r="BG32" s="190" cm="1">
+      <c r="BG32" s="188" cm="1">
         <f t="array" ref="BG32">SUMPRODUCT(--(B32:AI32=INT(B32:AI32)),--(B32:AI32&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH32" s="191">
-        <f t="shared" ref="BH32:BJ32" si="29">RANK(BD32,BD$3:BD$53,0)</f>
-        <v>10</v>
-      </c>
-      <c r="BI32" s="191">
-        <f t="shared" si="29"/>
-        <v>9</v>
-      </c>
-      <c r="BJ32" s="191">
-        <f t="shared" si="29"/>
+      <c r="BH32" s="189">
+        <f>RANK(BD32,BD$3:BD$53,0)</f>
+        <v>12</v>
+      </c>
+      <c r="BI32" s="189">
+        <f>RANK(BE32,BE$3:BE$53,0)</f>
+        <v>12</v>
+      </c>
+      <c r="BJ32" s="189">
+        <f>RANK(BF32,BF$3:BF$53,0)</f>
         <v>8</v>
       </c>
     </row>
@@ -12501,37 +12408,37 @@
       <c r="BA33" s="120"/>
       <c r="BB33" s="120"/>
       <c r="BC33" s="120"/>
-      <c r="BD33" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD33" s="187">
+        <f>SUM(B33:BC33)</f>
         <v>4</v>
       </c>
-      <c r="BE33" s="189" cm="1">
+      <c r="BE33" s="187" cm="1">
         <f t="array" ref="BE33">SUMPRODUCT(--(B33:BC33=INT(B33:BC33)),--(B33:BC33&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF33" s="189" cm="1">
+      <c r="BF33" s="187" cm="1">
         <f t="array" ref="BF33">MAX(FREQUENCY(IF((B33:BC33=INT(B33:BC33))*(B33:BC33&gt;0),COLUMN(B33:BC33)),IF((B33:BC33&lt;&gt;INT(B33:BC33))+(B33:BC33&lt;=0),COLUMN(B33:BC33))))</f>
         <v>1</v>
       </c>
-      <c r="BG33" s="190" cm="1">
+      <c r="BG33" s="188" cm="1">
         <f t="array" ref="BG33">SUMPRODUCT(--(B33:AI33=INT(B33:AI33)),--(B33:AI33&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH33" s="191">
-        <f t="shared" ref="BH33:BJ33" si="30">RANK(BD33,BD$3:BD$53,0)</f>
+      <c r="BH33" s="189">
+        <f>RANK(BD33,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI33" s="191">
-        <f t="shared" si="30"/>
+      <c r="BI33" s="189">
+        <f>RANK(BE33,BE$3:BE$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BJ33" s="191">
-        <f t="shared" si="30"/>
+      <c r="BJ33" s="189">
+        <f>RANK(BF33,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:62">
-      <c r="A34" s="192">
+      <c r="A34" s="190">
         <v>32</v>
       </c>
       <c r="B34" s="120"/>
@@ -12588,37 +12495,37 @@
       <c r="BA34" s="120"/>
       <c r="BB34" s="120"/>
       <c r="BC34" s="120"/>
-      <c r="BD34" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD34" s="187">
+        <f>SUM(B34:BC34)</f>
         <v>0</v>
       </c>
-      <c r="BE34" s="189" cm="1">
+      <c r="BE34" s="187" cm="1">
         <f t="array" ref="BE34">SUMPRODUCT(--(B34:BC34=INT(B34:BC34)),--(B34:BC34&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF34" s="189" cm="1">
+      <c r="BF34" s="187" cm="1">
         <f t="array" ref="BF34">MAX(FREQUENCY(IF((B34:BC34=INT(B34:BC34))*(B34:BC34&gt;0),COLUMN(B34:BC34)),IF((B34:BC34&lt;&gt;INT(B34:BC34))+(B34:BC34&lt;=0),COLUMN(B34:BC34))))</f>
         <v>0</v>
       </c>
-      <c r="BG34" s="190" cm="1">
+      <c r="BG34" s="188" cm="1">
         <f t="array" ref="BG34">SUMPRODUCT(--(B34:AI34=INT(B34:AI34)),--(B34:AI34&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH34" s="191">
-        <f t="shared" ref="BH34:BJ34" si="31">RANK(BD34,BD$3:BD$53,0)</f>
+      <c r="BH34" s="189">
+        <f>RANK(BD34,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI34" s="191">
-        <f t="shared" si="31"/>
+      <c r="BI34" s="189">
+        <f>RANK(BE34,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ34" s="191">
-        <f t="shared" si="31"/>
+      <c r="BJ34" s="189">
+        <f>RANK(BF34,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:62">
-      <c r="A35" s="192">
+      <c r="A35" s="190">
         <v>33</v>
       </c>
       <c r="B35" s="120"/>
@@ -12675,32 +12582,32 @@
       <c r="BA35" s="120"/>
       <c r="BB35" s="120"/>
       <c r="BC35" s="120"/>
-      <c r="BD35" s="189">
-        <f t="shared" si="0"/>
+      <c r="BD35" s="187">
+        <f>SUM(B35:BC35)</f>
         <v>0</v>
       </c>
-      <c r="BE35" s="189" cm="1">
+      <c r="BE35" s="187" cm="1">
         <f t="array" ref="BE35">SUMPRODUCT(--(B35:BC35=INT(B35:BC35)),--(B35:BC35&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF35" s="189" cm="1">
+      <c r="BF35" s="187" cm="1">
         <f t="array" ref="BF35">MAX(FREQUENCY(IF((B35:BC35=INT(B35:BC35))*(B35:BC35&gt;0),COLUMN(B35:BC35)),IF((B35:BC35&lt;&gt;INT(B35:BC35))+(B35:BC35&lt;=0),COLUMN(B35:BC35))))</f>
         <v>0</v>
       </c>
-      <c r="BG35" s="190" cm="1">
+      <c r="BG35" s="188" cm="1">
         <f t="array" ref="BG35">SUMPRODUCT(--(B35:AI35=INT(B35:AI35)),--(B35:AI35&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH35" s="191">
-        <f t="shared" ref="BH35:BJ35" si="32">RANK(BD35,BD$3:BD$53,0)</f>
+      <c r="BH35" s="189">
+        <f>RANK(BD35,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI35" s="191">
-        <f t="shared" si="32"/>
+      <c r="BI35" s="189">
+        <f>RANK(BE35,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ35" s="191">
-        <f t="shared" si="32"/>
+      <c r="BJ35" s="189">
+        <f>RANK(BF35,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
@@ -12764,32 +12671,32 @@
       <c r="BA36" s="120"/>
       <c r="BB36" s="120"/>
       <c r="BC36" s="120"/>
-      <c r="BD36" s="189">
-        <f t="shared" ref="BD36:BD53" si="33">SUM(B36:BC36)</f>
-        <v>1</v>
-      </c>
-      <c r="BE36" s="189" cm="1">
+      <c r="BD36" s="187">
+        <f>SUM(B36:BC36)</f>
+        <v>1</v>
+      </c>
+      <c r="BE36" s="187" cm="1">
         <f t="array" ref="BE36">SUMPRODUCT(--(B36:BC36=INT(B36:BC36)),--(B36:BC36&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF36" s="189" cm="1">
+      <c r="BF36" s="187" cm="1">
         <f t="array" ref="BF36">MAX(FREQUENCY(IF((B36:BC36=INT(B36:BC36))*(B36:BC36&gt;0),COLUMN(B36:BC36)),IF((B36:BC36&lt;&gt;INT(B36:BC36))+(B36:BC36&lt;=0),COLUMN(B36:BC36))))</f>
         <v>1</v>
       </c>
-      <c r="BG36" s="190" cm="1">
+      <c r="BG36" s="188" cm="1">
         <f t="array" ref="BG36">SUMPRODUCT(--(B36:AI36=INT(B36:AI36)),--(B36:AI36&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH36" s="191">
-        <f t="shared" ref="BH36:BJ36" si="34">RANK(BD36,BD$3:BD$53,0)</f>
+      <c r="BH36" s="189">
+        <f>RANK(BD36,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI36" s="191">
-        <f t="shared" si="34"/>
+      <c r="BI36" s="189">
+        <f>RANK(BE36,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ36" s="191">
-        <f t="shared" si="34"/>
+      <c r="BJ36" s="189">
+        <f>RANK(BF36,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -12865,32 +12772,32 @@
       <c r="BA37" s="120"/>
       <c r="BB37" s="120"/>
       <c r="BC37" s="120"/>
-      <c r="BD37" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD37" s="187">
+        <f>SUM(B37:BC37)</f>
         <v>8</v>
       </c>
-      <c r="BE37" s="189" cm="1">
+      <c r="BE37" s="187" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF37" s="189" cm="1">
+      <c r="BF37" s="187" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
         <v>3</v>
       </c>
-      <c r="BG37" s="190" cm="1">
+      <c r="BG37" s="188" cm="1">
         <f t="array" ref="BG37">SUMPRODUCT(--(B37:AI37=INT(B37:AI37)),--(B37:AI37&gt;0))/34*100%</f>
         <v>0.176470588235294</v>
       </c>
-      <c r="BH37" s="191">
-        <f t="shared" ref="BH37:BJ37" si="35">RANK(BD37,BD$3:BD$53,0)</f>
+      <c r="BH37" s="189">
+        <f>RANK(BD37,BD$3:BD$53,0)</f>
         <v>16</v>
       </c>
-      <c r="BI37" s="191">
-        <f t="shared" si="35"/>
+      <c r="BI37" s="189">
+        <f>RANK(BE37,BE$3:BE$53,0)</f>
         <v>17</v>
       </c>
-      <c r="BJ37" s="191">
-        <f t="shared" si="35"/>
+      <c r="BJ37" s="189">
+        <f>RANK(BF37,BF$3:BF$53,0)</f>
         <v>8</v>
       </c>
     </row>
@@ -12958,32 +12865,32 @@
       <c r="BA38" s="120"/>
       <c r="BB38" s="120"/>
       <c r="BC38" s="120"/>
-      <c r="BD38" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD38" s="187">
+        <f>SUM(B38:BC38)</f>
         <v>4</v>
       </c>
-      <c r="BE38" s="189" cm="1">
+      <c r="BE38" s="187" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(--(B38:BC38=INT(B38:BC38)),--(B38:BC38&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF38" s="189" cm="1">
+      <c r="BF38" s="187" cm="1">
         <f t="array" ref="BF38">MAX(FREQUENCY(IF((B38:BC38=INT(B38:BC38))*(B38:BC38&gt;0),COLUMN(B38:BC38)),IF((B38:BC38&lt;&gt;INT(B38:BC38))+(B38:BC38&lt;=0),COLUMN(B38:BC38))))</f>
         <v>1</v>
       </c>
-      <c r="BG38" s="190" cm="1">
+      <c r="BG38" s="188" cm="1">
         <f t="array" ref="BG38">SUMPRODUCT(--(B38:AI38=INT(B38:AI38)),--(B38:AI38&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH38" s="191">
-        <f t="shared" ref="BH38:BJ38" si="36">RANK(BD38,BD$3:BD$53,0)</f>
+      <c r="BH38" s="189">
+        <f>RANK(BD38,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI38" s="191">
-        <f t="shared" si="36"/>
+      <c r="BI38" s="189">
+        <f>RANK(BE38,BE$3:BE$53,0)</f>
         <v>26</v>
       </c>
-      <c r="BJ38" s="191">
-        <f t="shared" si="36"/>
+      <c r="BJ38" s="189">
+        <f>RANK(BF38,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -13045,32 +12952,32 @@
       <c r="BA39" s="175"/>
       <c r="BB39" s="175"/>
       <c r="BC39" s="175"/>
-      <c r="BD39" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD39" s="187">
+        <f>SUM(B39:BC39)</f>
         <v>0</v>
       </c>
-      <c r="BE39" s="189" cm="1">
+      <c r="BE39" s="187" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(--(B39:BC39=INT(B39:BC39)),--(B39:BC39&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF39" s="189" cm="1">
+      <c r="BF39" s="187" cm="1">
         <f t="array" ref="BF39">MAX(FREQUENCY(IF((B39:BC39=INT(B39:BC39))*(B39:BC39&gt;0),COLUMN(B39:BC39)),IF((B39:BC39&lt;&gt;INT(B39:BC39))+(B39:BC39&lt;=0),COLUMN(B39:BC39))))</f>
         <v>0</v>
       </c>
-      <c r="BG39" s="190" cm="1">
+      <c r="BG39" s="188" cm="1">
         <f t="array" ref="BG39">SUMPRODUCT(--(B39:AI39=INT(B39:AI39)),--(B39:AI39&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH39" s="193">
-        <f t="shared" ref="BH39:BJ39" si="37">RANK(BD39,BD$3:BD$53,0)</f>
+      <c r="BH39" s="191">
+        <f>RANK(BD39,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI39" s="193">
-        <f t="shared" si="37"/>
+      <c r="BI39" s="191">
+        <f>RANK(BE39,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ39" s="193">
-        <f t="shared" si="37"/>
+      <c r="BJ39" s="191">
+        <f>RANK(BF39,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
@@ -13162,7 +13069,9 @@
       </c>
       <c r="AL40" s="120"/>
       <c r="AM40" s="120"/>
-      <c r="AN40" s="120"/>
+      <c r="AN40" s="120">
+        <v>1</v>
+      </c>
       <c r="AO40" s="120"/>
       <c r="AP40" s="120"/>
       <c r="AQ40" s="120"/>
@@ -13178,32 +13087,32 @@
       <c r="BA40" s="120"/>
       <c r="BB40" s="120"/>
       <c r="BC40" s="120"/>
-      <c r="BD40" s="189">
-        <f t="shared" si="33"/>
-        <v>27</v>
-      </c>
-      <c r="BE40" s="189" cm="1">
+      <c r="BD40" s="187">
+        <f>SUM(B40:BC40)</f>
+        <v>28</v>
+      </c>
+      <c r="BE40" s="187" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
-        <v>23</v>
-      </c>
-      <c r="BF40" s="189" cm="1">
+        <v>24</v>
+      </c>
+      <c r="BF40" s="187" cm="1">
         <f t="array" ref="BF40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
         <v>12</v>
       </c>
-      <c r="BG40" s="190" cm="1">
+      <c r="BG40" s="188" cm="1">
         <f t="array" ref="BG40">SUMPRODUCT(--(B40:AI40=INT(B40:AI40)),--(B40:AI40&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH40" s="191">
-        <f t="shared" ref="BH40:BJ40" si="38">RANK(BD40,BD$3:BD$53,0)</f>
+      <c r="BH40" s="189">
+        <f>RANK(BD40,BD$3:BD$53,0)</f>
         <v>2</v>
       </c>
-      <c r="BI40" s="191">
-        <f t="shared" si="38"/>
-        <v>1</v>
-      </c>
-      <c r="BJ40" s="191">
-        <f t="shared" si="38"/>
+      <c r="BI40" s="189">
+        <f>RANK(BE40,BE$3:BE$53,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ40" s="189">
+        <f>RANK(BF40,BF$3:BF$53,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -13269,7 +13178,9 @@
         <v>1</v>
       </c>
       <c r="AM41" s="120"/>
-      <c r="AN41" s="120"/>
+      <c r="AN41" s="120">
+        <v>1</v>
+      </c>
       <c r="AO41" s="120"/>
       <c r="AP41" s="120"/>
       <c r="AQ41" s="120"/>
@@ -13285,32 +13196,32 @@
       <c r="BA41" s="120"/>
       <c r="BB41" s="120"/>
       <c r="BC41" s="120"/>
-      <c r="BD41" s="189">
-        <f t="shared" si="33"/>
-        <v>13</v>
-      </c>
-      <c r="BE41" s="189" cm="1">
+      <c r="BD41" s="187">
+        <f>SUM(B41:BC41)</f>
+        <v>14</v>
+      </c>
+      <c r="BE41" s="187" cm="1">
         <f t="array" ref="BE41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
-        <v>10</v>
-      </c>
-      <c r="BF41" s="189" cm="1">
+        <v>11</v>
+      </c>
+      <c r="BF41" s="187" cm="1">
         <f t="array" ref="BF41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
         <v>2</v>
       </c>
-      <c r="BG41" s="190" cm="1">
+      <c r="BG41" s="188" cm="1">
         <f t="array" ref="BG41">SUMPRODUCT(--(B41:AI41=INT(B41:AI41)),--(B41:AI41&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH41" s="191">
-        <f t="shared" ref="BH41:BJ41" si="39">RANK(BD41,BD$3:BD$53,0)</f>
-        <v>7</v>
-      </c>
-      <c r="BI41" s="191">
-        <f t="shared" si="39"/>
-        <v>9</v>
-      </c>
-      <c r="BJ41" s="191">
-        <f t="shared" si="39"/>
+      <c r="BH41" s="189">
+        <f>RANK(BD41,BD$3:BD$53,0)</f>
+        <v>6</v>
+      </c>
+      <c r="BI41" s="189">
+        <f>RANK(BE41,BE$3:BE$53,0)</f>
+        <v>8</v>
+      </c>
+      <c r="BJ41" s="189">
+        <f>RANK(BF41,BF$3:BF$53,0)</f>
         <v>13</v>
       </c>
     </row>
@@ -13400,37 +13311,37 @@
       <c r="BA42" s="120"/>
       <c r="BB42" s="120"/>
       <c r="BC42" s="120"/>
-      <c r="BD42" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD42" s="187">
+        <f>SUM(B42:BC42)</f>
         <v>17</v>
       </c>
-      <c r="BE42" s="189" cm="1">
+      <c r="BE42" s="187" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
         <v>14</v>
       </c>
-      <c r="BF42" s="189" cm="1">
+      <c r="BF42" s="187" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
         <v>5</v>
       </c>
-      <c r="BG42" s="190" cm="1">
+      <c r="BG42" s="188" cm="1">
         <f t="array" ref="BG42">SUMPRODUCT(--(B42:AI42=INT(B42:AI42)),--(B42:AI42&gt;0))/34*100%</f>
         <v>0.352941176470588</v>
       </c>
-      <c r="BH42" s="191">
-        <f t="shared" ref="BH42:BJ42" si="40">RANK(BD42,BD$3:BD$53,0)</f>
+      <c r="BH42" s="189">
+        <f>RANK(BD42,BD$3:BD$53,0)</f>
         <v>4</v>
       </c>
-      <c r="BI42" s="191">
-        <f t="shared" si="40"/>
+      <c r="BI42" s="189">
+        <f>RANK(BE42,BE$3:BE$53,0)</f>
         <v>4</v>
       </c>
-      <c r="BJ42" s="191">
-        <f t="shared" si="40"/>
+      <c r="BJ42" s="189">
+        <f>RANK(BF42,BF$3:BF$53,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:62">
-      <c r="A43" s="192">
+      <c r="A43" s="190">
         <v>41</v>
       </c>
       <c r="B43" s="120"/>
@@ -13487,32 +13398,32 @@
       <c r="BA43" s="120"/>
       <c r="BB43" s="120"/>
       <c r="BC43" s="120"/>
-      <c r="BD43" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD43" s="187">
+        <f>SUM(B43:BC43)</f>
         <v>0</v>
       </c>
-      <c r="BE43" s="189" cm="1">
+      <c r="BE43" s="187" cm="1">
         <f t="array" ref="BE43">SUMPRODUCT(--(B43:BC43=INT(B43:BC43)),--(B43:BC43&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF43" s="189" cm="1">
+      <c r="BF43" s="187" cm="1">
         <f t="array" ref="BF43">MAX(FREQUENCY(IF((B43:BC43=INT(B43:BC43))*(B43:BC43&gt;0),COLUMN(B43:BC43)),IF((B43:BC43&lt;&gt;INT(B43:BC43))+(B43:BC43&lt;=0),COLUMN(B43:BC43))))</f>
         <v>0</v>
       </c>
-      <c r="BG43" s="190" cm="1">
+      <c r="BG43" s="188" cm="1">
         <f t="array" ref="BG43">SUMPRODUCT(--(B43:AI43=INT(B43:AI43)),--(B43:AI43&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH43" s="191">
-        <f t="shared" ref="BH43:BJ43" si="41">RANK(BD43,BD$3:BD$53,0)</f>
+      <c r="BH43" s="189">
+        <f>RANK(BD43,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI43" s="191">
-        <f t="shared" si="41"/>
+      <c r="BI43" s="189">
+        <f>RANK(BE43,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ43" s="191">
-        <f t="shared" si="41"/>
+      <c r="BJ43" s="189">
+        <f>RANK(BF43,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
@@ -13602,37 +13513,37 @@
       <c r="BA44" s="120"/>
       <c r="BB44" s="120"/>
       <c r="BC44" s="120"/>
-      <c r="BD44" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD44" s="187">
+        <f>SUM(B44:BC44)</f>
         <v>17</v>
       </c>
-      <c r="BE44" s="189" cm="1">
+      <c r="BE44" s="187" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
         <v>14</v>
       </c>
-      <c r="BF44" s="189" cm="1">
+      <c r="BF44" s="187" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
         <v>5</v>
       </c>
-      <c r="BG44" s="190" cm="1">
+      <c r="BG44" s="188" cm="1">
         <f t="array" ref="BG44">SUMPRODUCT(--(B44:AI44=INT(B44:AI44)),--(B44:AI44&gt;0))/34*100%</f>
         <v>0.411764705882353</v>
       </c>
-      <c r="BH44" s="191">
-        <f t="shared" ref="BH44:BJ44" si="42">RANK(BD44,BD$3:BD$53,0)</f>
+      <c r="BH44" s="189">
+        <f>RANK(BD44,BD$3:BD$53,0)</f>
         <v>4</v>
       </c>
-      <c r="BI44" s="191">
-        <f t="shared" si="42"/>
+      <c r="BI44" s="189">
+        <f>RANK(BE44,BE$3:BE$53,0)</f>
         <v>4</v>
       </c>
-      <c r="BJ44" s="191">
-        <f t="shared" si="42"/>
+      <c r="BJ44" s="189">
+        <f>RANK(BF44,BF$3:BF$53,0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:62">
-      <c r="A45" s="192">
+      <c r="A45" s="190">
         <v>43</v>
       </c>
       <c r="B45" s="120"/>
@@ -13689,32 +13600,32 @@
       <c r="BA45" s="120"/>
       <c r="BB45" s="120"/>
       <c r="BC45" s="120"/>
-      <c r="BD45" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD45" s="187">
+        <f>SUM(B45:BC45)</f>
         <v>0</v>
       </c>
-      <c r="BE45" s="189" cm="1">
+      <c r="BE45" s="187" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(--(B45:BC45=INT(B45:BC45)),--(B45:BC45&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF45" s="189" cm="1">
+      <c r="BF45" s="187" cm="1">
         <f t="array" ref="BF45">MAX(FREQUENCY(IF((B45:BC45=INT(B45:BC45))*(B45:BC45&gt;0),COLUMN(B45:BC45)),IF((B45:BC45&lt;&gt;INT(B45:BC45))+(B45:BC45&lt;=0),COLUMN(B45:BC45))))</f>
         <v>0</v>
       </c>
-      <c r="BG45" s="190" cm="1">
+      <c r="BG45" s="188" cm="1">
         <f t="array" ref="BG45">SUMPRODUCT(--(B45:AI45=INT(B45:AI45)),--(B45:AI45&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH45" s="191">
-        <f t="shared" ref="BH45:BJ45" si="43">RANK(BD45,BD$3:BD$53,0)</f>
+      <c r="BH45" s="189">
+        <f>RANK(BD45,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI45" s="191">
-        <f t="shared" si="43"/>
+      <c r="BI45" s="189">
+        <f>RANK(BE45,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ45" s="191">
-        <f t="shared" si="43"/>
+      <c r="BJ45" s="189">
+        <f>RANK(BF45,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
@@ -13806,7 +13717,9 @@
       <c r="AM46" s="120">
         <v>1</v>
       </c>
-      <c r="AN46" s="120"/>
+      <c r="AN46" s="120">
+        <v>1</v>
+      </c>
       <c r="AO46" s="120"/>
       <c r="AP46" s="120"/>
       <c r="AQ46" s="120"/>
@@ -13822,37 +13735,37 @@
       <c r="BA46" s="120"/>
       <c r="BB46" s="120"/>
       <c r="BC46" s="120"/>
-      <c r="BD46" s="189">
-        <f t="shared" si="33"/>
-        <v>32</v>
-      </c>
-      <c r="BE46" s="189" cm="1">
+      <c r="BD46" s="187">
+        <f>SUM(B46:BC46)</f>
+        <v>33</v>
+      </c>
+      <c r="BE46" s="187" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>23</v>
-      </c>
-      <c r="BF46" s="189" cm="1">
+        <v>24</v>
+      </c>
+      <c r="BF46" s="187" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
         <v>8</v>
       </c>
-      <c r="BG46" s="190" cm="1">
+      <c r="BG46" s="188" cm="1">
         <f t="array" ref="BG46">SUMPRODUCT(--(B46:AI46=INT(B46:AI46)),--(B46:AI46&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH46" s="191">
-        <f t="shared" ref="BH46:BJ46" si="44">RANK(BD46,BD$3:BD$53,0)</f>
-        <v>1</v>
-      </c>
-      <c r="BI46" s="191">
-        <f t="shared" si="44"/>
-        <v>1</v>
-      </c>
-      <c r="BJ46" s="191">
-        <f t="shared" si="44"/>
+      <c r="BH46" s="189">
+        <f>RANK(BD46,BD$3:BD$53,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BI46" s="189">
+        <f>RANK(BE46,BE$3:BE$53,0)</f>
+        <v>1</v>
+      </c>
+      <c r="BJ46" s="189">
+        <f>RANK(BF46,BF$3:BF$53,0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:62">
-      <c r="A47" s="192">
+      <c r="A47" s="190">
         <v>45</v>
       </c>
       <c r="B47" s="120"/>
@@ -13909,32 +13822,32 @@
       <c r="BA47" s="120"/>
       <c r="BB47" s="120"/>
       <c r="BC47" s="120"/>
-      <c r="BD47" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD47" s="187">
+        <f>SUM(B47:BC47)</f>
         <v>0</v>
       </c>
-      <c r="BE47" s="189" cm="1">
+      <c r="BE47" s="187" cm="1">
         <f t="array" ref="BE47">SUMPRODUCT(--(B47:BC47=INT(B47:BC47)),--(B47:BC47&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF47" s="189" cm="1">
+      <c r="BF47" s="187" cm="1">
         <f t="array" ref="BF47">MAX(FREQUENCY(IF((B47:BC47=INT(B47:BC47))*(B47:BC47&gt;0),COLUMN(B47:BC47)),IF((B47:BC47&lt;&gt;INT(B47:BC47))+(B47:BC47&lt;=0),COLUMN(B47:BC47))))</f>
         <v>0</v>
       </c>
-      <c r="BG47" s="190" cm="1">
+      <c r="BG47" s="188" cm="1">
         <f t="array" ref="BG47">SUMPRODUCT(--(B47:AI47=INT(B47:AI47)),--(B47:AI47&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH47" s="191">
-        <f t="shared" ref="BH47:BJ47" si="45">RANK(BD47,BD$3:BD$53,0)</f>
+      <c r="BH47" s="189">
+        <f>RANK(BD47,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI47" s="191">
-        <f t="shared" si="45"/>
+      <c r="BI47" s="189">
+        <f>RANK(BE47,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ47" s="191">
-        <f t="shared" si="45"/>
+      <c r="BJ47" s="189">
+        <f>RANK(BF47,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
@@ -14000,7 +13913,9 @@
       </c>
       <c r="AL48" s="120"/>
       <c r="AM48" s="120"/>
-      <c r="AN48" s="120"/>
+      <c r="AN48" s="120">
+        <v>2</v>
+      </c>
       <c r="AO48" s="120"/>
       <c r="AP48" s="120"/>
       <c r="AQ48" s="120"/>
@@ -14016,32 +13931,32 @@
       <c r="BA48" s="120"/>
       <c r="BB48" s="120"/>
       <c r="BC48" s="120"/>
-      <c r="BD48" s="189">
-        <f t="shared" si="33"/>
-        <v>10</v>
-      </c>
-      <c r="BE48" s="189" cm="1">
+      <c r="BD48" s="187">
+        <f>SUM(B48:BC48)</f>
+        <v>12</v>
+      </c>
+      <c r="BE48" s="187" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
-        <v>10</v>
-      </c>
-      <c r="BF48" s="189" cm="1">
+        <v>11</v>
+      </c>
+      <c r="BF48" s="187" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
         <v>2</v>
       </c>
-      <c r="BG48" s="190" cm="1">
+      <c r="BG48" s="188" cm="1">
         <f t="array" ref="BG48">SUMPRODUCT(--(B48:AI48=INT(B48:AI48)),--(B48:AI48&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH48" s="191">
-        <f t="shared" ref="BH48:BJ48" si="46">RANK(BD48,BD$3:BD$53,0)</f>
-        <v>12</v>
-      </c>
-      <c r="BI48" s="191">
-        <f t="shared" si="46"/>
-        <v>9</v>
-      </c>
-      <c r="BJ48" s="191">
-        <f t="shared" si="46"/>
+      <c r="BH48" s="189">
+        <f>RANK(BD48,BD$3:BD$53,0)</f>
+        <v>10</v>
+      </c>
+      <c r="BI48" s="189">
+        <f>RANK(BE48,BE$3:BE$53,0)</f>
+        <v>8</v>
+      </c>
+      <c r="BJ48" s="189">
+        <f>RANK(BF48,BF$3:BF$53,0)</f>
         <v>13</v>
       </c>
     </row>
@@ -14111,32 +14026,32 @@
       <c r="BA49" s="120"/>
       <c r="BB49" s="120"/>
       <c r="BC49" s="120"/>
-      <c r="BD49" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD49" s="187">
+        <f>SUM(B49:BC49)</f>
         <v>4</v>
       </c>
-      <c r="BE49" s="189" cm="1">
+      <c r="BE49" s="187" cm="1">
         <f t="array" ref="BE49">SUMPRODUCT(--(B49:BC49=INT(B49:BC49)),--(B49:BC49&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF49" s="189" cm="1">
+      <c r="BF49" s="187" cm="1">
         <f t="array" ref="BF49">MAX(FREQUENCY(IF((B49:BC49=INT(B49:BC49))*(B49:BC49&gt;0),COLUMN(B49:BC49)),IF((B49:BC49&lt;&gt;INT(B49:BC49))+(B49:BC49&lt;=0),COLUMN(B49:BC49))))</f>
         <v>1</v>
       </c>
-      <c r="BG49" s="190" cm="1">
+      <c r="BG49" s="188" cm="1">
         <f t="array" ref="BG49">SUMPRODUCT(--(B49:AI49=INT(B49:AI49)),--(B49:AI49&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH49" s="191">
-        <f t="shared" ref="BH49:BJ49" si="47">RANK(BD49,BD$3:BD$53,0)</f>
+      <c r="BH49" s="189">
+        <f>RANK(BD49,BD$3:BD$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BI49" s="191">
-        <f t="shared" si="47"/>
+      <c r="BI49" s="189">
+        <f>RANK(BE49,BE$3:BE$53,0)</f>
         <v>23</v>
       </c>
-      <c r="BJ49" s="191">
-        <f t="shared" si="47"/>
+      <c r="BJ49" s="189">
+        <f>RANK(BF49,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -14208,37 +14123,37 @@
       <c r="BA50" s="120"/>
       <c r="BB50" s="120"/>
       <c r="BC50" s="120"/>
-      <c r="BD50" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD50" s="187">
+        <f>SUM(B50:BC50)</f>
         <v>5</v>
       </c>
-      <c r="BE50" s="189" cm="1">
+      <c r="BE50" s="187" cm="1">
         <f t="array" ref="BE50">SUMPRODUCT(--(B50:BC50=INT(B50:BC50)),--(B50:BC50&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF50" s="189" cm="1">
+      <c r="BF50" s="187" cm="1">
         <f t="array" ref="BF50">MAX(FREQUENCY(IF((B50:BC50=INT(B50:BC50))*(B50:BC50&gt;0),COLUMN(B50:BC50)),IF((B50:BC50&lt;&gt;INT(B50:BC50))+(B50:BC50&lt;=0),COLUMN(B50:BC50))))</f>
         <v>1</v>
       </c>
-      <c r="BG50" s="190" cm="1">
+      <c r="BG50" s="188" cm="1">
         <f t="array" ref="BG50">SUMPRODUCT(--(B50:AI50=INT(B50:AI50)),--(B50:AI50&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH50" s="191">
-        <f t="shared" ref="BH50:BJ50" si="48">RANK(BD50,BD$3:BD$53,0)</f>
+      <c r="BH50" s="189">
+        <f>RANK(BD50,BD$3:BD$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BI50" s="191">
-        <f t="shared" si="48"/>
+      <c r="BI50" s="189">
+        <f>RANK(BE50,BE$3:BE$53,0)</f>
         <v>20</v>
       </c>
-      <c r="BJ50" s="191">
-        <f t="shared" si="48"/>
+      <c r="BJ50" s="189">
+        <f>RANK(BF50,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:62">
-      <c r="A51" s="192">
+      <c r="A51" s="190">
         <v>49</v>
       </c>
       <c r="B51" s="120"/>
@@ -14295,37 +14210,37 @@
       <c r="BA51" s="120"/>
       <c r="BB51" s="120"/>
       <c r="BC51" s="120"/>
-      <c r="BD51" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD51" s="187">
+        <f>SUM(B51:BC51)</f>
         <v>0</v>
       </c>
-      <c r="BE51" s="189" cm="1">
+      <c r="BE51" s="187" cm="1">
         <f t="array" ref="BE51">SUMPRODUCT(--(B51:BC51=INT(B51:BC51)),--(B51:BC51&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF51" s="189" cm="1">
+      <c r="BF51" s="187" cm="1">
         <f t="array" ref="BF51">MAX(FREQUENCY(IF((B51:BC51=INT(B51:BC51))*(B51:BC51&gt;0),COLUMN(B51:BC51)),IF((B51:BC51&lt;&gt;INT(B51:BC51))+(B51:BC51&lt;=0),COLUMN(B51:BC51))))</f>
         <v>0</v>
       </c>
-      <c r="BG51" s="190" cm="1">
+      <c r="BG51" s="188" cm="1">
         <f t="array" ref="BG51">SUMPRODUCT(--(B51:AI51=INT(B51:AI51)),--(B51:AI51&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH51" s="191">
-        <f t="shared" ref="BH51:BJ51" si="49">RANK(BD51,BD$3:BD$53,0)</f>
+      <c r="BH51" s="189">
+        <f>RANK(BD51,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI51" s="191">
-        <f t="shared" si="49"/>
+      <c r="BI51" s="189">
+        <f>RANK(BE51,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ51" s="191">
-        <f t="shared" si="49"/>
+      <c r="BJ51" s="189">
+        <f>RANK(BF51,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:62">
-      <c r="A52" s="192">
+      <c r="A52" s="190">
         <v>50</v>
       </c>
       <c r="B52" s="120"/>
@@ -14382,32 +14297,32 @@
       <c r="BA52" s="120"/>
       <c r="BB52" s="120"/>
       <c r="BC52" s="120"/>
-      <c r="BD52" s="189">
-        <f t="shared" si="33"/>
+      <c r="BD52" s="187">
+        <f>SUM(B52:BC52)</f>
         <v>0</v>
       </c>
-      <c r="BE52" s="189" cm="1">
+      <c r="BE52" s="187" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(--(B52:BC52=INT(B52:BC52)),--(B52:BC52&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF52" s="189" cm="1">
+      <c r="BF52" s="187" cm="1">
         <f t="array" ref="BF52">MAX(FREQUENCY(IF((B52:BC52=INT(B52:BC52))*(B52:BC52&gt;0),COLUMN(B52:BC52)),IF((B52:BC52&lt;&gt;INT(B52:BC52))+(B52:BC52&lt;=0),COLUMN(B52:BC52))))</f>
         <v>0</v>
       </c>
-      <c r="BG52" s="190" cm="1">
+      <c r="BG52" s="188" cm="1">
         <f t="array" ref="BG52">SUMPRODUCT(--(B52:AI52=INT(B52:AI52)),--(B52:AI52&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH52" s="191">
-        <f t="shared" ref="BH52:BJ52" si="50">RANK(BD52,BD$3:BD$53,0)</f>
+      <c r="BH52" s="189">
+        <f>RANK(BD52,BD$3:BD$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BI52" s="191">
-        <f t="shared" si="50"/>
+      <c r="BI52" s="189">
+        <f>RANK(BE52,BE$3:BE$53,0)</f>
         <v>41</v>
       </c>
-      <c r="BJ52" s="191">
-        <f t="shared" si="50"/>
+      <c r="BJ52" s="189">
+        <f>RANK(BF52,BF$3:BF$53,0)</f>
         <v>41</v>
       </c>
     </row>
@@ -14471,32 +14386,32 @@
       <c r="BA53" s="120"/>
       <c r="BB53" s="120"/>
       <c r="BC53" s="120"/>
-      <c r="BD53" s="189">
-        <f t="shared" si="33"/>
-        <v>1</v>
-      </c>
-      <c r="BE53" s="189" cm="1">
+      <c r="BD53" s="187">
+        <f>SUM(B53:BC53)</f>
+        <v>1</v>
+      </c>
+      <c r="BE53" s="187" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(--(B53:BC53=INT(B53:BC53)),--(B53:BC53&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF53" s="189" cm="1">
+      <c r="BF53" s="187" cm="1">
         <f t="array" ref="BF53">MAX(FREQUENCY(IF((B53:BC53=INT(B53:BC53))*(B53:BC53&gt;0),COLUMN(B53:BC53)),IF((B53:BC53&lt;&gt;INT(B53:BC53))+(B53:BC53&lt;=0),COLUMN(B53:BC53))))</f>
         <v>1</v>
       </c>
-      <c r="BG53" s="190" cm="1">
+      <c r="BG53" s="188" cm="1">
         <f t="array" ref="BG53">SUMPRODUCT(--(B53:AI53=INT(B53:AI53)),--(B53:AI53&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH53" s="191">
-        <f t="shared" ref="BH53:BJ53" si="51">RANK(BD53,BD$3:BD$53,0)</f>
+      <c r="BH53" s="189">
+        <f>RANK(BD53,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI53" s="191">
-        <f t="shared" si="51"/>
+      <c r="BI53" s="189">
+        <f>RANK(BE53,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ53" s="191">
-        <f t="shared" si="51"/>
+      <c r="BJ53" s="189">
+        <f>RANK(BF53,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -15623,9 +15538,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 A9:X9" unlockedFormula="1"/>
-    <ignoredError sqref="A1 C1:S1 U1:AF1 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z28:AF33 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 A3:X4 BD1:BJ2 BI3 AC40:AD40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 A48:X49 Z48:AB48 AE48 A51:AF53 A50:AD50 AF50 X8:AF8 A8:V8 A5:AF7 Z4:AE4 Z41:AE42 BH4:BJ8 BI9:BJ9 Z10:AF10 BH11:BJ39 Z49:AF49 A12:X15 A37:AF37 A39:AF39 A2:AF2 Z3:AF3 A10:X10" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="AG1:AI3 AD11:AI11 AC48:AI48 AG16:AI21 AG43:AI47 AG49:AI53 AF42:AI42 AH41:AI41 AG5:AI8 AG28:AI39 AG12:AI14 BG41:BG53 AA11 Z15:AA15 AF15:AI15 Z12:AF12 Z13:AA13 Y17:AF18 A19:AF21 Y22:AI22 A23:AI27 Y28:AF33 Y36:AF36 A37:AF37 Y38:AF38 A39:AF39 Y3:Y4 A40:AB40 Y42 A43:AF43 X44:AF44 Y46:AF46 A47:AF47 Y48:Y49 AE50:AF50 A5:AF7 A8:W8 AF4:AI4 BG4:BG8 BG11:BG39 Y12:Y15" formulaRange="1"/>
+    <ignoredError sqref="Z9:AB9 AD9:AF9 X41 A9:X9" unlockedFormula="1"/>
+    <ignoredError sqref="A10:X10 Z3:AF3 A2:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH11:BJ39 Z10:AF10 BI9:BJ9 BH4:BJ8 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z28:AF33 A28:X33 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11 U1:AF1 C1:S1 A1" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="BG41:BG53 AG12:AI14 AG26:AI39 AG5:AI8 AH41:AI41 AF42:AI42 AG49:AI53 AG43:AI47 AG16:AI22 AG1:AI3 Y12:Y15 BG11:BG39 BG4:BG8 AF4:AI4 W8:AF8 A50:AE50 A51:AF53 Z48:AD48 AF48:AI48 Y48:Y49 A45:AF45 A46:AE46 A44:AE44 Y42 W40:AD40 Y3:Y4 A38:AC38 A34:AF35 A36:Y36 A28:Y33 A23:AI25 A22:AE22 A16:AF16 A17:Y18 AA13:AF13 Z14:AF14 AA15 AF15:AI15 AD11 AF11:AI11 A11:AA11" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15672,21 +15587,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -15694,10 +15609,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -15710,10 +15625,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B4" s="158" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C4" s="158"/>
       <c r="D4" s="158"/>
@@ -15726,7 +15641,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -15746,7 +15661,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -15756,7 +15671,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -15764,10 +15679,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -15782,14 +15697,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -15800,10 +15715,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -15816,23 +15731,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -15840,7 +15755,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -15856,7 +15771,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -15874,17 +15789,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -15892,10 +15807,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -15970,7 +15885,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -15995,10 +15910,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -16010,7 +15925,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -16032,7 +15947,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -16044,7 +15959,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
@@ -16072,7 +15987,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16086,7 +16001,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -16098,7 +16013,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -16110,7 +16025,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>71</v>
@@ -16121,10 +16036,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>90</v>
@@ -16148,10 +16063,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -16162,7 +16077,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -16184,7 +16099,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -16196,7 +16111,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -16208,7 +16123,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>83</v>
@@ -16220,7 +16135,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>86</v>
@@ -16232,7 +16147,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -16244,7 +16159,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -16306,7 +16221,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -16337,7 +16252,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -16529,7 +16444,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -16721,7 +16636,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -16948,10 +16863,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>198</v>
@@ -16962,208 +16877,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -17171,118 +17086,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -17290,138 +17205,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="12410" windowHeight="10480" tabRatio="724" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="645">
   <si>
     <t>姓名</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>朋友圈（模糊图片、装）、马克笔写字、挠痒动作、起立时（借口、拖延、不情愿、偷坐）</t>
+  </si>
+  <si>
+    <t>麦当劳</t>
   </si>
   <si>
     <t>林承钰</t>
@@ -424,6 +427,9 @@
     <t>画画</t>
   </si>
   <si>
+    <t>发奋图强</t>
+  </si>
+  <si>
     <t>语1</t>
   </si>
   <si>
@@ -484,7 +490,7 @@
     <t>53面最后一段总结！53面最后一段总结！53面！53面！53面最后一段总结！53面最后一段总结！最后一段总结！最后一段！总结！53面！53面！53面最后一段总结！</t>
   </si>
   <si>
-    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛、欸欸欸、复读机、××什么？×——×。</t>
+    <t>啧+手势，对不对、重音、预习复习、透明水杯，拿学生水杯、嘛、欸欸欸、复读机、××什么？×——×。、理论性比较强</t>
   </si>
   <si>
     <t>史1</t>
@@ -496,7 +502,10 @@
     <t>史2</t>
   </si>
   <si>
-    <t>历史屌丝（论述题“中国只有变得更NB”、“中国要完蛋了”）我爱历史</t>
+    <t>历史屌丝（论述题“中国只有变得更NB”、“中国要完蛋了”）我爱历史、科代表放视频、小测翻书</t>
+  </si>
+  <si>
+    <t>屌丝集团</t>
   </si>
   <si>
     <t>地1</t>
@@ -656,6 +665,10 @@
   </si>
   <si>
     <t>26.1.23，林奕扬带蓝牙耳机</t>
+  </si>
+  <si>
+    <t>××住在澎湖湾，天天喝稀饭。
+没有筷子没有碗，只有破烂摊。</t>
   </si>
   <si>
     <t>日常</t>
@@ -808,6 +821,12 @@
     <t>午餐吃麦当劳：饭盒里有薯条、麦乐鸡，最大的格子内直接放入带包装袋的板烧鸡腿堡</t>
   </si>
   <si>
+    <t>八下3.4</t>
+  </si>
+  <si>
+    <t>午餐吃麦当劳（加苏打饼干）。进班时，生：恩亚我来了！落座后，围住，唱恩亚歌，刚打开缝隙就一哄而上，陆梓豪、林奕扬吃一口汉堡，光盘速度快。</t>
+  </si>
+  <si>
     <t>手机管理</t>
   </si>
   <si>
@@ -935,6 +954,12 @@
   </si>
   <si>
     <t>体育课二人独处在门口栏杆边聊天</t>
+  </si>
+  <si>
+    <t>电脑计时纪录</t>
+  </si>
+  <si>
+    <t>计时6:59:60，8点英语课开始，15点生物课结束</t>
   </si>
   <si>
     <t>政治课</t>
@@ -3260,14 +3285,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <strike/>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="华文仿宋"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3277,18 +3308,12 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
       <sz val="11"/>
-      <name val="黑体"/>
+      <name val="华文仿宋"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="57">
+  <fills count="59">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3430,6 +3455,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3924,7 +3961,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3948,16 +3985,16 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="29" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="30" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="28" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3966,92 +4003,92 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4628,6 +4665,12 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4677,7 +4720,7 @@
     <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4725,6 +4768,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5095,764 +5141,773 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="224" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="225" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="226" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="227"/>
+    <col min="1" max="1" width="7.59090909090909" style="227" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="228" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="229" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="230"/>
   </cols>
   <sheetData>
-    <row r="1" s="223" customFormat="1" spans="1:10">
-      <c r="A1" s="228" t="s">
+    <row r="1" s="226" customFormat="1" spans="1:10">
+      <c r="A1" s="231" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="229" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="229" t="s">
+      <c r="B1" s="232" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="232" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="229" t="s">
+      <c r="D1" s="232" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="229" t="s">
+      <c r="E1" s="232" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="229" t="s">
+      <c r="F1" s="232" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="229" t="s">
+      <c r="G1" s="232" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
-      <c r="J1" s="230"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="231" t="s">
+      <c r="A2" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="225" t="s">
+      <c r="B2" s="228" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="225" t="s">
+      <c r="C2" s="228" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="231" t="s">
+      <c r="A3" s="234" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="225" t="s">
+      <c r="C3" s="228" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="225" t="s">
+      <c r="D3" s="228" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="231" t="s">
+      <c r="A4" s="234" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="228" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="231" t="s">
+      <c r="A5" s="234" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="225" t="s">
+      <c r="C5" s="228" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="225" t="s">
+      <c r="D5" s="228" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="231" t="s">
+      <c r="A6" s="234" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="225" t="s">
+      <c r="C6" s="228" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="231" t="s">
+      <c r="A7" s="234" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="225" t="s">
+      <c r="B7" s="228" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="225" t="s">
+      <c r="C7" s="228" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="225" t="s">
+      <c r="D7" s="228" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="231" t="s">
+      <c r="A8" s="234" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="225" t="s">
+      <c r="D8" s="228" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="231" t="s">
+      <c r="A9" s="234" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="231" t="s">
+      <c r="A10" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="225" t="s">
+      <c r="B10" s="228" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="231" t="s">
+      <c r="A11" s="234" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="231" t="s">
+      <c r="A12" s="234" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="231" t="s">
+      <c r="A13" s="234" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="225" t="s">
+      <c r="D13" s="228" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="231" t="s">
+      <c r="A14" s="234" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="225" t="s">
+      <c r="B14" s="228" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="231" t="s">
+      <c r="A15" s="234" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="231" t="s">
+      <c r="A16" s="234" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="225" t="s">
+      <c r="C16" s="228" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="231" t="s">
+    <row r="17" ht="26" spans="1:5">
+      <c r="A17" s="234" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="225" t="s">
+      <c r="C17" s="228" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="231" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="234" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="225" t="s">
+      <c r="D18" s="228" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="19" ht="26" spans="1:4">
-      <c r="A19" s="231" t="s">
+    <row r="19" ht="26" spans="1:5">
+      <c r="A19" s="234" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="225" t="s">
+      <c r="D19" s="228" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" ht="26" spans="1:4">
-      <c r="A20" s="231" t="s">
+    <row r="20" ht="26" spans="1:5">
+      <c r="A20" s="234" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="225" t="s">
+      <c r="B20" s="228" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="225" t="s">
+      <c r="C20" s="228" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" ht="52" spans="1:4">
-      <c r="A21" s="231" t="s">
+    <row r="21" ht="52" spans="1:5">
+      <c r="A21" s="234" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="225" t="s">
+      <c r="B21" s="228" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="225" t="s">
+      <c r="C21" s="228" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="225" t="s">
+      <c r="D21" s="228" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="231" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="234" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="23" ht="26" spans="1:4">
-      <c r="A23" s="231" t="s">
+    <row r="23" ht="26" spans="1:5">
+      <c r="A23" s="234" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="225" t="s">
+      <c r="B23" s="228" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="24" ht="52" spans="1:4">
-      <c r="A24" s="231" t="s">
+    <row r="24" ht="52" spans="1:5">
+      <c r="A24" s="234" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="225" t="s">
+      <c r="B24" s="228" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="225" t="s">
+      <c r="C24" s="228" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="225" t="s">
+      <c r="D24" s="228" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="231" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="234" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="231" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" s="234" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="231" t="s">
+    <row r="27" spans="1:5">
+      <c r="A27" s="234" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="225" t="s">
+      <c r="B27" s="228" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="225" t="s">
+      <c r="C27" s="228" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="28" ht="91" spans="1:4">
-      <c r="A28" s="231" t="s">
+    <row r="28" ht="91" spans="1:5">
+      <c r="A28" s="234" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="225" t="s">
+      <c r="C28" s="228" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="225" t="s">
+      <c r="D28" s="228" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="231" t="s">
+      <c r="E28" s="228" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="231" t="s">
+    <row r="29" spans="1:5">
+      <c r="A29" s="234" t="s">
         <v>68</v>
       </c>
-      <c r="B30" s="225" t="s">
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="234" t="s">
         <v>69</v>
       </c>
-      <c r="C30" s="225" t="s">
+      <c r="B30" s="228" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="231" t="s">
+      <c r="C30" s="228" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="231" t="s">
+    <row r="31" spans="1:5">
+      <c r="A31" s="234" t="s">
         <v>72</v>
       </c>
     </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="234" t="s">
+        <v>73</v>
+      </c>
+    </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="231" t="s">
-        <v>73</v>
+      <c r="A33" s="234" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="231" t="s">
-        <v>74</v>
+      <c r="A34" s="234" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="231" t="s">
-        <v>75</v>
+      <c r="A35" s="234" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="231" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="225" t="s">
+      <c r="A36" s="234" t="s">
         <v>77</v>
       </c>
+      <c r="B36" s="228" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="231" t="s">
-        <v>78</v>
-      </c>
-      <c r="C37" s="225" t="s">
+      <c r="A37" s="234" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="225" t="s">
+      <c r="C37" s="228" t="s">
         <v>80</v>
       </c>
+      <c r="D37" s="228" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="231" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="225" t="s">
+      <c r="A38" s="234" t="s">
         <v>82</v>
       </c>
-      <c r="C38" s="232"/>
-      <c r="D38" s="232"/>
-      <c r="E38" s="232"/>
-      <c r="F38" s="232"/>
-      <c r="G38" s="232"/>
+      <c r="B38" s="228" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="235"/>
+      <c r="D38" s="235"/>
+      <c r="E38" s="235"/>
+      <c r="F38" s="235"/>
+      <c r="G38" s="235"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="231" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" s="225" t="s">
+      <c r="A39" s="234" t="s">
         <v>84</v>
       </c>
-      <c r="D39" s="225" t="s">
+      <c r="C39" s="228" t="s">
         <v>85</v>
       </c>
+      <c r="D39" s="228" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="231" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="225" t="s">
+      <c r="A40" s="234" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="225" t="s">
+      <c r="B40" s="228" t="s">
         <v>88</v>
       </c>
-      <c r="D40" s="225" t="s">
+      <c r="C40" s="228" t="s">
         <v>89</v>
       </c>
+      <c r="D40" s="228" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="231" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="225" t="s">
+      <c r="A41" s="234" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="225" t="s">
+      <c r="C41" s="228" t="s">
         <v>92</v>
       </c>
-      <c r="H41" s="226" t="s">
+      <c r="D41" s="228" t="s">
         <v>93</v>
       </c>
-      <c r="I41" s="226" t="s">
+      <c r="H41" s="229" t="s">
         <v>94</v>
       </c>
-      <c r="J41" s="226" t="s">
+      <c r="I41" s="229" t="s">
         <v>95</v>
       </c>
+      <c r="J41" s="229" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="231" t="s">
-        <v>96</v>
+      <c r="A42" s="234" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="231" t="s">
-        <v>97</v>
-      </c>
-      <c r="B43" s="225" t="s">
+      <c r="A43" s="234" t="s">
         <v>98</v>
       </c>
-      <c r="H43" s="226" t="s">
+      <c r="B43" s="228" t="s">
         <v>99</v>
       </c>
+      <c r="H43" s="229" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="231" t="s">
-        <v>100</v>
-      </c>
-      <c r="B44" s="225" t="s">
+      <c r="A44" s="234" t="s">
         <v>101</v>
       </c>
+      <c r="B44" s="228" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="231" t="s">
-        <v>102</v>
-      </c>
-      <c r="C45" s="225" t="s">
+      <c r="A45" s="234" t="s">
         <v>103</v>
       </c>
-      <c r="D45" s="225" t="s">
+      <c r="C45" s="228" t="s">
         <v>104</v>
       </c>
+      <c r="D45" s="228" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="231" t="s">
-        <v>105</v>
+      <c r="A46" s="234" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="231" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" s="225" t="s">
+      <c r="A47" s="234" t="s">
         <v>107</v>
       </c>
+      <c r="D47" s="228" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="231" t="s">
-        <v>108</v>
-      </c>
-      <c r="C48" s="225" t="s">
+      <c r="A48" s="234" t="s">
         <v>109</v>
       </c>
-      <c r="D48" s="225" t="s">
+      <c r="C48" s="228" t="s">
         <v>110</v>
       </c>
+      <c r="D48" s="228" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="231" t="s">
-        <v>111</v>
+      <c r="A49" s="234" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="231" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" s="225" t="s">
+      <c r="A50" s="234" t="s">
         <v>113</v>
       </c>
+      <c r="C50" s="228" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="231" t="s">
-        <v>114</v>
+      <c r="A51" s="234" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="231" t="s">
-        <v>115</v>
-      </c>
-      <c r="B52" s="225" t="s">
+      <c r="A52" s="234" t="s">
         <v>116</v>
       </c>
-      <c r="C52" s="225" t="s">
+      <c r="B52" s="228" t="s">
         <v>117</v>
       </c>
+      <c r="C52" s="228" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" s="228" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="224" t="s">
-        <v>118</v>
-      </c>
-      <c r="B53" s="225" t="s">
-        <v>119</v>
-      </c>
-      <c r="D53" s="232"/>
-      <c r="E53" s="232"/>
-      <c r="F53" s="232"/>
-      <c r="G53" s="232"/>
+      <c r="A53" s="227" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" s="228" t="s">
+        <v>121</v>
+      </c>
+      <c r="D53" s="235"/>
+      <c r="E53" s="235"/>
+      <c r="F53" s="235"/>
+      <c r="G53" s="235"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="224" t="s">
-        <v>120</v>
-      </c>
-      <c r="B54" s="225" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54" s="225" t="s">
+      <c r="A54" s="227" t="s">
         <v>122</v>
       </c>
-      <c r="D54" s="232"/>
-      <c r="E54" s="232"/>
-      <c r="F54" s="232"/>
-      <c r="G54" s="232"/>
+      <c r="B54" s="228" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="228" t="s">
+        <v>124</v>
+      </c>
+      <c r="D54" s="235"/>
+      <c r="E54" s="235"/>
+      <c r="F54" s="235"/>
+      <c r="G54" s="235"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="224" t="s">
-        <v>123</v>
-      </c>
-      <c r="B55" s="232"/>
-      <c r="C55" s="232"/>
-      <c r="D55" s="225" t="s">
-        <v>124</v>
+      <c r="A55" s="227" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" s="235"/>
+      <c r="C55" s="235"/>
+      <c r="D55" s="228" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="224" t="s">
-        <v>125</v>
+      <c r="A56" s="227" t="s">
+        <v>127</v>
       </c>
       <c r="B56" s="78" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="225" t="s">
-        <v>127</v>
+      <c r="D56" s="228" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="224" t="s">
-        <v>128</v>
+      <c r="A57" s="227" t="s">
+        <v>130</v>
       </c>
       <c r="B57" s="78" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C57" s="78" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57" s="225" t="s">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="D57" s="228" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="224" t="s">
-        <v>132</v>
-      </c>
-      <c r="B58" s="225" t="s">
-        <v>133</v>
-      </c>
-      <c r="C58" s="232"/>
-      <c r="D58" s="232"/>
-      <c r="E58" s="232"/>
-      <c r="F58" s="232"/>
-      <c r="G58" s="232"/>
+      <c r="A58" s="227" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" s="228" t="s">
+        <v>135</v>
+      </c>
+      <c r="C58" s="235"/>
+      <c r="D58" s="235"/>
+      <c r="E58" s="235"/>
+      <c r="F58" s="235"/>
+      <c r="G58" s="235"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="224" t="s">
-        <v>134</v>
-      </c>
-      <c r="B59" s="232"/>
-      <c r="C59" s="225" t="s">
-        <v>135</v>
-      </c>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
-    </row>
-    <row r="60" ht="52" spans="1:7">
-      <c r="A60" s="224" t="s">
+      <c r="A59" s="227" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="232" t="s">
+      <c r="B59" s="235"/>
+      <c r="C59" s="228" t="s">
         <v>137</v>
       </c>
-      <c r="C60" s="232"/>
-      <c r="D60" s="225" t="s">
+      <c r="D59" s="235"/>
+      <c r="E59" s="235"/>
+      <c r="F59" s="235"/>
+      <c r="G59" s="235"/>
+    </row>
+    <row r="60" ht="65" spans="1:7">
+      <c r="A60" s="227" t="s">
         <v>138</v>
       </c>
+      <c r="B60" s="235" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" s="235"/>
+      <c r="D60" s="228" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="224" t="s">
-        <v>139</v>
+      <c r="A61" s="227" t="s">
+        <v>141</v>
       </c>
       <c r="B61" s="78" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="232"/>
-      <c r="E61" s="232"/>
-      <c r="F61" s="232"/>
-      <c r="G61" s="232"/>
-    </row>
-    <row r="62" ht="39" spans="1:7">
-      <c r="A62" s="224" t="s">
-        <v>141</v>
-      </c>
-      <c r="B62" s="232"/>
-      <c r="C62" s="232"/>
-      <c r="D62" s="225" t="s">
-        <v>142</v>
+      <c r="D61" s="235"/>
+      <c r="E61" s="235"/>
+      <c r="F61" s="235"/>
+      <c r="G61" s="235"/>
+    </row>
+    <row r="62" ht="52" spans="1:7">
+      <c r="A62" s="227" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="235"/>
+      <c r="C62" s="235"/>
+      <c r="D62" s="228" t="s">
+        <v>144</v>
+      </c>
+      <c r="E62" s="228" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="224" t="s">
-        <v>143</v>
+      <c r="A63" s="227" t="s">
+        <v>146</v>
       </c>
       <c r="B63" s="78" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C63" s="78" t="s">
-        <v>145</v>
-      </c>
-      <c r="D63" s="232"/>
-      <c r="E63" s="232"/>
-      <c r="F63" s="232"/>
-      <c r="G63" s="232"/>
+        <v>148</v>
+      </c>
+      <c r="D63" s="235"/>
+      <c r="E63" s="235"/>
+      <c r="F63" s="235"/>
+      <c r="G63" s="235"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="224" t="s">
-        <v>146</v>
-      </c>
-      <c r="B64" s="232"/>
-      <c r="C64" s="232"/>
-      <c r="D64" s="225" t="s">
-        <v>147</v>
+      <c r="A64" s="227" t="s">
+        <v>149</v>
+      </c>
+      <c r="B64" s="235"/>
+      <c r="C64" s="235"/>
+      <c r="D64" s="228" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="224" t="s">
-        <v>148</v>
-      </c>
-      <c r="B65" s="233" t="s">
-        <v>149</v>
-      </c>
-      <c r="C65" s="232"/>
-      <c r="D65" s="232"/>
-      <c r="E65" s="232"/>
-      <c r="F65" s="232"/>
-      <c r="G65" s="232"/>
+      <c r="A65" s="227" t="s">
+        <v>151</v>
+      </c>
+      <c r="B65" s="236" t="s">
+        <v>152</v>
+      </c>
+      <c r="C65" s="235"/>
+      <c r="D65" s="235"/>
+      <c r="E65" s="235"/>
+      <c r="F65" s="235"/>
+      <c r="G65" s="235"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="224" t="s">
-        <v>150</v>
-      </c>
-      <c r="B66" s="232"/>
-      <c r="C66" s="225" t="s">
-        <v>151</v>
-      </c>
-      <c r="D66" s="232"/>
-      <c r="E66" s="232"/>
-      <c r="F66" s="232"/>
-      <c r="G66" s="232"/>
+      <c r="A66" s="227" t="s">
+        <v>153</v>
+      </c>
+      <c r="B66" s="235"/>
+      <c r="C66" s="228" t="s">
+        <v>154</v>
+      </c>
+      <c r="D66" s="235"/>
+      <c r="E66" s="235"/>
+      <c r="F66" s="235"/>
+      <c r="G66" s="235"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="224" t="s">
-        <v>152</v>
-      </c>
-      <c r="B67" s="232"/>
-      <c r="C67" s="232"/>
+      <c r="A67" s="227" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="235"/>
+      <c r="C67" s="235"/>
     </row>
     <row r="68" ht="65" spans="1:7">
-      <c r="A68" s="224" t="s">
-        <v>153</v>
-      </c>
-      <c r="B68" s="232"/>
-      <c r="C68" s="232"/>
-      <c r="D68" s="225" t="s">
-        <v>154</v>
+      <c r="A68" s="227" t="s">
+        <v>156</v>
+      </c>
+      <c r="B68" s="235"/>
+      <c r="C68" s="235"/>
+      <c r="D68" s="228" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="224" t="s">
-        <v>155</v>
+      <c r="A69" s="227" t="s">
+        <v>158</v>
       </c>
       <c r="B69" s="78" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="224" t="s">
-        <v>157</v>
+      <c r="A70" s="227" t="s">
+        <v>160</v>
       </c>
       <c r="B70" s="78" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="232"/>
-      <c r="E70" s="232"/>
-      <c r="F70" s="232"/>
-      <c r="G70" s="232"/>
+      <c r="D70" s="235"/>
+      <c r="E70" s="235"/>
+      <c r="F70" s="235"/>
+      <c r="G70" s="235"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="224" t="s">
-        <v>159</v>
-      </c>
-      <c r="B71" s="232"/>
-      <c r="C71" s="232"/>
+      <c r="A71" s="227" t="s">
+        <v>162</v>
+      </c>
+      <c r="B71" s="235"/>
+      <c r="C71" s="235"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="224" t="s">
-        <v>160</v>
-      </c>
-      <c r="B72" s="225" t="s">
-        <v>161</v>
-      </c>
-      <c r="C72" s="225" t="s">
-        <v>162</v>
-      </c>
-      <c r="D72" s="232"/>
-      <c r="E72" s="232"/>
-      <c r="F72" s="232"/>
-      <c r="G72" s="232"/>
+      <c r="A72" s="227" t="s">
+        <v>163</v>
+      </c>
+      <c r="B72" s="228" t="s">
+        <v>164</v>
+      </c>
+      <c r="C72" s="228" t="s">
+        <v>165</v>
+      </c>
+      <c r="D72" s="235"/>
+      <c r="E72" s="235"/>
+      <c r="F72" s="235"/>
+      <c r="G72" s="235"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="224" t="s">
-        <v>163</v>
-      </c>
-      <c r="B73" s="232"/>
-      <c r="C73" s="225" t="s">
-        <v>164</v>
-      </c>
-      <c r="D73" s="232"/>
-      <c r="E73" s="232"/>
-      <c r="F73" s="232"/>
-      <c r="G73" s="232"/>
+      <c r="A73" s="227" t="s">
+        <v>166</v>
+      </c>
+      <c r="B73" s="235"/>
+      <c r="C73" s="228" t="s">
+        <v>167</v>
+      </c>
+      <c r="D73" s="235"/>
+      <c r="E73" s="235"/>
+      <c r="F73" s="235"/>
+      <c r="G73" s="235"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="224" t="s">
-        <v>165</v>
+      <c r="A74" s="227" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="224" t="s">
-        <v>166</v>
-      </c>
-      <c r="D75" s="232"/>
-      <c r="E75" s="232"/>
-      <c r="F75" s="232"/>
-      <c r="G75" s="232"/>
+      <c r="A75" s="227" t="s">
+        <v>169</v>
+      </c>
+      <c r="D75" s="235"/>
+      <c r="E75" s="235"/>
+      <c r="F75" s="235"/>
+      <c r="G75" s="235"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="224" t="s">
-        <v>167</v>
-      </c>
-      <c r="B76" s="232"/>
-      <c r="C76" s="232"/>
-      <c r="D76" s="225" t="s">
-        <v>168</v>
+      <c r="A76" s="227" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="235"/>
+      <c r="C76" s="235"/>
+      <c r="D76" s="228" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="224" t="s">
-        <v>169</v>
+      <c r="A77" s="227" t="s">
+        <v>172</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="234" t="s">
-        <v>170</v>
-      </c>
-      <c r="B78" s="225" t="s">
-        <v>171</v>
+      <c r="A78" s="237" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" s="228" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -5905,16 +5960,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5928,7 +5983,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5942,7 +5997,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -5956,7 +6011,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -5984,7 +6039,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -5998,7 +6053,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6012,7 +6067,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6026,7 +6081,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6040,7 +6095,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6066,7 +6121,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6080,7 +6135,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6094,7 +6149,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6120,7 +6175,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6134,7 +6189,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6172,7 +6227,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6186,7 +6241,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6212,7 +6267,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6226,7 +6281,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6240,7 +6295,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6254,7 +6309,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6268,7 +6323,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6282,7 +6337,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6290,7 +6345,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C29" s="74">
         <v>20120110</v>
@@ -6302,13 +6357,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="72" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C30" s="74">
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6316,13 +6371,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="74">
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6330,13 +6385,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" s="74">
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6344,7 +6399,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33" s="74">
         <v>20120425</v>
@@ -6356,13 +6411,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="72" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C34" s="74">
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6370,7 +6425,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C35" s="74">
         <v>20120507</v>
@@ -6382,13 +6437,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="72" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C36" s="74">
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6396,13 +6451,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="72" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C37" s="73">
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6410,16 +6465,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="75" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C38" s="76">
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="E38" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6427,13 +6482,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="72" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C39" s="74">
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6441,13 +6496,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="72" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C40" s="74">
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6455,16 +6510,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="74">
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="E41" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6472,7 +6527,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="72" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="74">
         <v>20111027</v>
@@ -6484,13 +6539,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="74">
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6498,7 +6553,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="72" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C44" s="73">
         <v>20120508</v>
@@ -6510,13 +6565,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="72" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45" s="74">
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6524,7 +6579,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="72" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="74">
         <v>20111205</v>
@@ -6536,16 +6591,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="72" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C47" s="74">
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="E47" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6553,13 +6608,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="72" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C48" s="74">
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6567,7 +6622,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="72" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="74">
         <v>20110902</v>
@@ -6579,13 +6634,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="72" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C50" s="74">
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6593,7 +6648,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="72" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C51" s="74">
         <v>20120101</v>
@@ -6605,13 +6660,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="72" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C52" s="74">
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -6644,34 +6699,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6679,10 +6734,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6690,10 +6745,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6701,10 +6756,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6712,23 +6767,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6736,10 +6791,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6747,10 +6802,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6758,10 +6813,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6769,10 +6824,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6780,50 +6835,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6832,24 +6887,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6857,17 +6912,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6876,61 +6931,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6938,10 +6993,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6949,10 +7004,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -6960,27 +7015,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -6988,10 +7043,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -6999,10 +7054,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7010,99 +7065,99 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
       <c r="E36" s="52" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7110,83 +7165,83 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
       <c r="E45" s="33" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7195,7 +7250,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7204,55 +7259,55 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
       <c r="E51" s="33" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7260,10 +7315,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7275,18 +7330,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>
@@ -7394,7 +7449,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7408,7 +7463,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7432,7 +7487,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7445,7 +7500,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7458,7 +7513,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7492,7 +7547,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7538,7 +7593,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7574,7 +7629,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7608,10 +7663,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7623,10 +7678,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7649,7 +7704,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7662,10 +7717,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7699,10 +7754,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7714,10 +7769,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7726,7 +7781,7 @@
     </row>
     <row r="29" s="6" customFormat="1" spans="1:7">
       <c r="A29" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="9"/>
@@ -7737,11 +7792,11 @@
     </row>
     <row r="30" s="6" customFormat="1" ht="28" spans="1:7">
       <c r="A30" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7750,7 +7805,7 @@
     </row>
     <row r="31" s="6" customFormat="1" spans="1:7">
       <c r="A31" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="9"/>
@@ -7761,7 +7816,7 @@
     </row>
     <row r="32" s="6" customFormat="1" spans="1:7">
       <c r="A32" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="9"/>
@@ -7772,7 +7827,7 @@
     </row>
     <row r="33" s="6" customFormat="1" spans="1:7">
       <c r="A33" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="9"/>
@@ -7783,7 +7838,7 @@
     </row>
     <row r="34" s="6" customFormat="1" spans="1:7">
       <c r="A34" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="9"/>
@@ -7794,7 +7849,7 @@
     </row>
     <row r="35" s="6" customFormat="1" spans="1:7">
       <c r="A35" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
@@ -7805,10 +7860,10 @@
     </row>
     <row r="36" s="6" customFormat="1" ht="42" spans="1:7">
       <c r="A36" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7818,11 +7873,11 @@
     </row>
     <row r="37" s="6" customFormat="1" ht="126" spans="1:7">
       <c r="A37" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7831,10 +7886,10 @@
     </row>
     <row r="38" s="6" customFormat="1" ht="28" spans="1:7">
       <c r="A38" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7844,11 +7899,11 @@
     </row>
     <row r="39" s="6" customFormat="1" ht="42" spans="1:7">
       <c r="A39" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7857,13 +7912,13 @@
     </row>
     <row r="40" s="6" customFormat="1" spans="1:7">
       <c r="A40" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7872,11 +7927,11 @@
     </row>
     <row r="41" s="6" customFormat="1" ht="126" spans="1:7">
       <c r="A41" s="14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7885,7 +7940,7 @@
     </row>
     <row r="42" s="6" customFormat="1" spans="1:7">
       <c r="A42" s="14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
@@ -7896,10 +7951,10 @@
     </row>
     <row r="43" s="6" customFormat="1" spans="1:7">
       <c r="A43" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7909,7 +7964,7 @@
     </row>
     <row r="44" s="6" customFormat="1" spans="1:7">
       <c r="A44" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
@@ -7920,10 +7975,10 @@
     </row>
     <row r="45" s="6" customFormat="1" ht="387" spans="1:7">
       <c r="A45" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -7933,7 +7988,7 @@
     </row>
     <row r="46" s="6" customFormat="1" spans="1:7">
       <c r="A46" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
@@ -7944,7 +7999,7 @@
     </row>
     <row r="47" s="6" customFormat="1" spans="1:7">
       <c r="A47" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
@@ -7955,11 +8010,11 @@
     </row>
     <row r="48" s="6" customFormat="1" spans="1:7">
       <c r="A48" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -7968,7 +8023,7 @@
     </row>
     <row r="49" s="6" customFormat="1" spans="1:7">
       <c r="A49" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
@@ -7979,11 +8034,11 @@
     </row>
     <row r="50" s="6" customFormat="1" ht="322" spans="1:7">
       <c r="A50" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -7992,7 +8047,7 @@
     </row>
     <row r="51" s="6" customFormat="1" spans="1:7">
       <c r="A51" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
@@ -8003,13 +8058,13 @@
     </row>
     <row r="52" s="6" customFormat="1" ht="224" spans="1:7">
       <c r="A52" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8045,27 +8100,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8073,13 +8128,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8087,13 +8142,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8101,13 +8156,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8115,13 +8170,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8129,13 +8184,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8143,13 +8198,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8157,7 +8212,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8165,7 +8220,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8173,7 +8228,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8181,7 +8236,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8201,14 +8256,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="218" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="220" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="219"/>
+    <col min="8" max="16384" width="8.72727272727273" style="221"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="220"/>
+      <c r="A1" s="222"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8228,187 +8283,190 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="217" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="221" t="s">
-        <v>172</v>
+    <row r="2" s="219" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="223" t="s">
+        <v>175</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
       <c r="D2" s="78" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E2" s="78"/>
       <c r="F2" s="78"/>
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="222" t="s">
-        <v>174</v>
+      <c r="A3" s="224" t="s">
+        <v>177</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="222" t="s">
-        <v>176</v>
+      <c r="A4" s="224" t="s">
+        <v>179</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="222" t="s">
-        <v>179</v>
+      <c r="A5" s="224" t="s">
+        <v>182</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="222" t="s">
-        <v>182</v>
+      <c r="A6" s="224" t="s">
+        <v>185</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="222" t="s">
-        <v>185</v>
+      <c r="A7" s="224" t="s">
+        <v>188</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="222"/>
+      <c r="A8" s="224"/>
       <c r="D8" s="66" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="222"/>
+      <c r="A9" s="224"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="222"/>
+      <c r="A10" s="224"/>
       <c r="B10" s="66" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="222"/>
+      <c r="A11" s="224"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="222"/>
+      <c r="A12" s="224"/>
       <c r="B12" s="66" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="222"/>
+      <c r="A13" s="224"/>
       <c r="B13" s="66" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="222"/>
+      <c r="A14" s="224"/>
       <c r="B14" s="66" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="222"/>
+      <c r="A15" s="224"/>
       <c r="B15" s="66" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="222"/>
+      <c r="A16" s="224"/>
       <c r="B16" s="66" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="222"/>
+      <c r="A17" s="224"/>
       <c r="B17" s="66" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="222"/>
+      <c r="A18" s="224"/>
       <c r="B18" s="66" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="222"/>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" ht="26" spans="1:2">
+      <c r="A19" s="224"/>
+      <c r="B19" s="225" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="222"/>
+      <c r="A20" s="224"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="222"/>
+      <c r="A21" s="224"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="222"/>
+      <c r="A22" s="224"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="222"/>
+      <c r="A23" s="224"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="222"/>
+      <c r="A24" s="224"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="222"/>
+      <c r="A25" s="224"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="222"/>
+      <c r="A26" s="224"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="222"/>
+      <c r="A27" s="224"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="222"/>
+      <c r="A28" s="224"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="222"/>
+      <c r="A29" s="224"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="222"/>
+      <c r="A30" s="224"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="222"/>
+      <c r="A31" s="224"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="222"/>
+      <c r="A32" s="224"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="222"/>
+      <c r="A33" s="224"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="222"/>
+      <c r="A34" s="224"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="222"/>
+      <c r="A35" s="224"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="222"/>
+      <c r="A36" s="224"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="222"/>
+      <c r="A37" s="224"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="222"/>
+      <c r="A38" s="224"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8417,7 +8475,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="222"/>
+      <c r="A39" s="224"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8426,40 +8484,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="222"/>
+      <c r="A40" s="224"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="222"/>
+      <c r="A41" s="224"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="222"/>
+      <c r="A42" s="224"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="222"/>
+      <c r="A43" s="224"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="222"/>
+      <c r="A44" s="224"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="222"/>
+      <c r="A45" s="224"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="222"/>
+      <c r="A46" s="224"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="222"/>
+      <c r="A47" s="224"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="222"/>
+      <c r="A48" s="224"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="222"/>
+      <c r="A49" s="224"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="222"/>
+      <c r="A50" s="224"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="222"/>
+      <c r="A51" s="224"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8472,426 +8530,461 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="206" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="206" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="206" customWidth="1"/>
+    <col min="1" max="1" width="24" style="208" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="208" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="208" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="205" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="207" t="s">
-        <v>196</v>
-      </c>
-      <c r="B1" s="207" t="s">
-        <v>197</v>
-      </c>
-      <c r="C1" s="207" t="s">
-        <v>198</v>
+    <row r="1" s="207" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="209" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="209" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="209" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="208" t="s">
-        <v>199</v>
-      </c>
-      <c r="B2" s="208" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" s="208" t="s">
-        <v>201</v>
+      <c r="A2" s="210" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="210" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="210" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="208" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="208" t="s">
-        <v>203</v>
-      </c>
-      <c r="C3" s="208" t="s">
-        <v>204</v>
+      <c r="A3" s="210" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="210" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="210" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="208" t="s">
-        <v>205</v>
-      </c>
-      <c r="B4" s="208" t="s">
-        <v>203</v>
-      </c>
-      <c r="C4" s="208" t="s">
-        <v>206</v>
+      <c r="A4" s="210" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="210" t="s">
+        <v>207</v>
+      </c>
+      <c r="C4" s="210" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="209" t="s">
-        <v>207</v>
-      </c>
-      <c r="B5" s="208" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" s="208" t="s">
-        <v>209</v>
+      <c r="A5" s="211" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="210" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="210" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="210"/>
-      <c r="B6" s="208" t="s">
-        <v>210</v>
-      </c>
-      <c r="C6" s="208" t="s">
-        <v>211</v>
+      <c r="A6" s="212"/>
+      <c r="B6" s="210" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="210" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="211" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="208" t="s">
-        <v>212</v>
-      </c>
-      <c r="C7" s="208" t="s">
-        <v>213</v>
+      <c r="A7" s="213" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="210" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="210" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
-      <c r="A8" s="211"/>
-      <c r="B8" s="208" t="s">
-        <v>214</v>
-      </c>
-      <c r="C8" s="208" t="s">
-        <v>215</v>
+      <c r="A8" s="213"/>
+      <c r="B8" s="210" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="210" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="211"/>
-      <c r="B9" s="208" t="s">
+      <c r="A9" s="213"/>
+      <c r="B9" s="210" t="s">
+        <v>220</v>
+      </c>
+      <c r="C9" s="210" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="214"/>
+      <c r="B10" s="210"/>
+      <c r="C10" s="210"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="210" t="s">
+        <v>222</v>
+      </c>
+      <c r="B11" s="210" t="s">
+        <v>223</v>
+      </c>
+      <c r="C11" s="210" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="210" t="s">
+        <v>225</v>
+      </c>
+      <c r="B12" s="210" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="210" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="210" t="s">
+        <v>228</v>
+      </c>
+      <c r="B13" s="210" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" s="215">
+        <v>0.440972222222222</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="216" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="210" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="210" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="217"/>
+      <c r="B15" s="210" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="210" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" ht="56" spans="1:3">
+      <c r="A16" s="217"/>
+      <c r="B16" s="210" t="s">
+        <v>234</v>
+      </c>
+      <c r="C16" s="210" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="217"/>
+      <c r="B17" s="210" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="210" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" ht="28" spans="1:3">
+      <c r="A18" s="217"/>
+      <c r="B18" s="210" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" s="210" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="217"/>
+      <c r="B19" s="210"/>
+      <c r="C19" s="210"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="217"/>
+      <c r="B20" s="210"/>
+      <c r="C20" s="210"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="217"/>
+      <c r="B21" s="210"/>
+      <c r="C21" s="210"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="211" t="s">
+        <v>240</v>
+      </c>
+      <c r="B22" s="210" t="s">
+        <v>232</v>
+      </c>
+      <c r="C22" s="210" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="212"/>
+      <c r="B23" s="210" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" s="210" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" ht="28" spans="1:3">
+      <c r="A24" s="218" t="s">
+        <v>244</v>
+      </c>
+      <c r="B24" s="210" t="s">
+        <v>245</v>
+      </c>
+      <c r="C24" s="210" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="213"/>
+      <c r="B25" s="210" t="s">
+        <v>218</v>
+      </c>
+      <c r="C25" s="210" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="213"/>
+      <c r="B26" s="210" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" s="210" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="213"/>
+      <c r="B27" s="210"/>
+      <c r="C27" s="210"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="211" t="s">
+        <v>250</v>
+      </c>
+      <c r="B28" s="210" t="s">
+        <v>251</v>
+      </c>
+      <c r="C28" s="210" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="212"/>
+      <c r="B29" s="210" t="s">
         <v>216</v>
       </c>
-      <c r="C9" s="208" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="212"/>
-      <c r="B10" s="208"/>
-      <c r="C10" s="208"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="208" t="s">
+      <c r="C29" s="210" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="30" ht="28" spans="1:3">
+      <c r="A30" s="218" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="210" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="210" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="213"/>
+      <c r="B31" s="208" t="s">
+        <v>255</v>
+      </c>
+      <c r="C31" s="208" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="213"/>
+      <c r="B32" s="208" t="s">
+        <v>236</v>
+      </c>
+      <c r="C32" s="208" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="33" ht="98" spans="1:3">
+      <c r="A33" s="218" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="208" t="s">
+        <v>216</v>
+      </c>
+      <c r="C33" s="208" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="34" ht="84" spans="1:3">
+      <c r="A34" s="214"/>
+      <c r="B34" s="208" t="s">
+        <v>260</v>
+      </c>
+      <c r="C34" s="208" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="208" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="208" t="s">
+        <v>262</v>
+      </c>
+      <c r="C35" s="208" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="218" t="s">
+        <v>264</v>
+      </c>
+      <c r="B36" s="208" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="208" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" s="208" t="s">
+      <c r="C36" s="208" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="214"/>
+      <c r="B37" s="208" t="s">
+        <v>260</v>
+      </c>
+      <c r="C37" s="208" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="208" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="208" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="208" t="s">
-        <v>221</v>
-      </c>
-      <c r="B12" s="208" t="s">
-        <v>222</v>
-      </c>
-      <c r="C12" s="208" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="208" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" s="208" t="s">
-        <v>225</v>
-      </c>
-      <c r="C13" s="213">
-        <v>0.440972222222222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="214" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="208" t="s">
-        <v>226</v>
-      </c>
-      <c r="C14" s="208" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="215"/>
-      <c r="B15" s="208" t="s">
-        <v>228</v>
-      </c>
-      <c r="C15" s="208" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="16" ht="56" spans="1:3">
-      <c r="A16" s="215"/>
-      <c r="B16" s="208" t="s">
-        <v>230</v>
-      </c>
-      <c r="C16" s="208" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="215"/>
-      <c r="B17" s="208" t="s">
-        <v>232</v>
-      </c>
-      <c r="C17" s="208" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="209" t="s">
-        <v>234</v>
-      </c>
-      <c r="B18" s="208" t="s">
-        <v>228</v>
-      </c>
-      <c r="C18" s="208" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="210"/>
-      <c r="B19" s="208" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="208" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="20" ht="28" spans="1:3">
-      <c r="A20" s="216" t="s">
+      <c r="C38" s="208" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="208" t="s">
+        <v>268</v>
+      </c>
+      <c r="B39" s="208" t="s">
+        <v>269</v>
+      </c>
+      <c r="C39" s="208" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="208" t="s">
+        <v>271</v>
+      </c>
+      <c r="B40" s="208" t="s">
+        <v>272</v>
+      </c>
+      <c r="C40" s="208" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="208" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="208" t="s">
+        <v>260</v>
+      </c>
+      <c r="C41" s="208" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="208" t="s">
+        <v>275</v>
+      </c>
+      <c r="B42" s="208" t="s">
+        <v>276</v>
+      </c>
+      <c r="C42" s="208" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="208" t="s">
+        <v>278</v>
+      </c>
+      <c r="B43" s="208" t="s">
+        <v>279</v>
+      </c>
+      <c r="C43" s="208" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="208" t="s">
+        <v>281</v>
+      </c>
+      <c r="B44" s="208" t="s">
+        <v>279</v>
+      </c>
+      <c r="C44" s="208" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="208" t="s">
+        <v>283</v>
+      </c>
+      <c r="B45" s="208" t="s">
         <v>238</v>
       </c>
-      <c r="B20" s="208" t="s">
-        <v>239</v>
-      </c>
-      <c r="C20" s="208" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="211"/>
-      <c r="B21" s="208" t="s">
-        <v>214</v>
-      </c>
-      <c r="C21" s="208" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="211"/>
-      <c r="B22" s="208" t="s">
-        <v>242</v>
-      </c>
-      <c r="C22" s="208" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="211"/>
-      <c r="B23" s="208"/>
-      <c r="C23" s="208"/>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="209" t="s">
-        <v>244</v>
-      </c>
-      <c r="B24" s="208" t="s">
-        <v>245</v>
-      </c>
-      <c r="C24" s="208" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="210"/>
-      <c r="B25" s="208" t="s">
-        <v>212</v>
-      </c>
-      <c r="C25" s="208" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="26" ht="28" spans="1:3">
-      <c r="A26" s="214" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="208" t="s">
-        <v>212</v>
-      </c>
-      <c r="C26" s="208" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="215"/>
-      <c r="B27" s="206" t="s">
-        <v>249</v>
-      </c>
-      <c r="C27" s="206" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="215"/>
-      <c r="B28" s="206" t="s">
-        <v>232</v>
-      </c>
-      <c r="C28" s="206" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="29" ht="98" spans="1:3">
-      <c r="A29" s="216" t="s">
-        <v>252</v>
-      </c>
-      <c r="B29" s="206" t="s">
-        <v>212</v>
-      </c>
-      <c r="C29" s="206" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="30" ht="84" spans="1:3">
-      <c r="A30" s="212"/>
-      <c r="B30" s="206" t="s">
-        <v>254</v>
-      </c>
-      <c r="C30" s="206" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="206" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="206" t="s">
-        <v>256</v>
-      </c>
-      <c r="C31" s="206" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="216" t="s">
-        <v>258</v>
-      </c>
-      <c r="B32" s="206" t="s">
-        <v>214</v>
-      </c>
-      <c r="C32" s="206" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="212"/>
-      <c r="B33" s="206" t="s">
-        <v>254</v>
-      </c>
-      <c r="C33" s="206" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="206" t="s">
-        <v>54</v>
-      </c>
-      <c r="B34" s="206" t="s">
-        <v>216</v>
-      </c>
-      <c r="C34" s="206" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="206" t="s">
-        <v>262</v>
-      </c>
-      <c r="B35" s="206" t="s">
-        <v>263</v>
-      </c>
-      <c r="C35" s="206" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="206" t="s">
-        <v>265</v>
-      </c>
-      <c r="B36" s="206" t="s">
-        <v>266</v>
-      </c>
-      <c r="C36" s="206" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="206" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="206" t="s">
-        <v>254</v>
-      </c>
-      <c r="C37" s="206" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="206" t="s">
-        <v>269</v>
-      </c>
-      <c r="B38" s="206" t="s">
-        <v>270</v>
-      </c>
-      <c r="C38" s="206" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="206" t="s">
-        <v>272</v>
-      </c>
-      <c r="B39" s="206" t="s">
-        <v>273</v>
-      </c>
-      <c r="C39" s="206" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="206" t="s">
-        <v>275</v>
-      </c>
-      <c r="B40" s="206" t="s">
-        <v>273</v>
-      </c>
-      <c r="C40" s="206" t="s">
-        <v>276</v>
+      <c r="C45" s="208" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A36:A37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -8910,45 +9003,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="194"/>
+    <col min="5" max="5" width="8.72727272727273" style="196"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="192" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="195" t="s">
-        <v>277</v>
-      </c>
-      <c r="B1" s="196"/>
-      <c r="C1" s="196"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="198"/>
-      <c r="F1" s="192" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="2" s="193" customFormat="1" spans="1:7">
-      <c r="A2" s="199" t="s">
-        <v>197</v>
-      </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="193" t="s">
-        <v>279</v>
-      </c>
-      <c r="D2" s="193" t="s">
-        <v>280</v>
+    <row r="1" s="194" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="197" t="s">
+        <v>285</v>
+      </c>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="194" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" s="195" customFormat="1" spans="1:7">
+      <c r="A2" s="201" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="202"/>
+      <c r="C2" s="195" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" s="195" t="s">
+        <v>288</v>
       </c>
       <c r="E2" s="141"/>
-      <c r="F2" s="193" t="s">
-        <v>197</v>
-      </c>
-      <c r="G2" s="193" t="s">
-        <v>281</v>
+      <c r="F2" s="195" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="195" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="201">
+      <c r="A3" s="203">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -8959,14 +9052,14 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="202"/>
+      <c r="A4" s="204"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -8975,14 +9068,14 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="202"/>
+      <c r="A5" s="204"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -8991,14 +9084,14 @@
       </c>
       <c r="D5" s="119"/>
       <c r="F5" s="119" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="G5" s="119" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="202"/>
+      <c r="A6" s="204"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9006,15 +9099,15 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="203" t="s">
-        <v>288</v>
+      <c r="F6" s="205" t="s">
+        <v>296</v>
       </c>
       <c r="G6" s="119" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="202"/>
+      <c r="A7" s="204"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9022,13 +9115,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="204"/>
+      <c r="F7" s="206"/>
       <c r="G7" s="119" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="202"/>
+      <c r="A8" s="204"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9040,7 +9133,7 @@
       <c r="G8" s="119"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="204"/>
+      <c r="A9" s="206"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9052,7 +9145,7 @@
       <c r="G9" s="119"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="203">
+      <c r="A10" s="205">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9066,7 +9159,7 @@
       <c r="G10" s="119"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="202"/>
+      <c r="A11" s="204"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9078,7 +9171,7 @@
       <c r="G11" s="119"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="204"/>
+      <c r="A12" s="206"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9090,7 +9183,7 @@
       <c r="G12" s="119"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="203">
+      <c r="A13" s="205">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9106,7 +9199,7 @@
       <c r="G13" s="119"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="204"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -9152,10 +9245,10 @@
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" s="175" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C1" s="177"/>
       <c r="D1" s="177"/>
@@ -9175,7 +9268,7 @@
       <c r="R1" s="177"/>
       <c r="S1" s="177"/>
       <c r="T1" s="178" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="U1" s="179"/>
       <c r="V1" s="179"/>
@@ -9193,12 +9286,12 @@
       <c r="AH1" s="179"/>
       <c r="AI1" s="179"/>
       <c r="AJ1" s="178" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="AK1" s="179"/>
       <c r="AL1" s="179"/>
       <c r="AM1" s="178" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AN1" s="179"/>
       <c r="AO1" s="179"/>
@@ -9217,7 +9310,7 @@
       <c r="BB1" s="179"/>
       <c r="BC1" s="180"/>
       <c r="BD1" s="181" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="BE1" s="182"/>
       <c r="BF1" s="182"/>
@@ -9387,25 +9480,25 @@
       <c r="BB2" s="184"/>
       <c r="BC2" s="184"/>
       <c r="BD2" s="185" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="BE2" s="185" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="BF2" s="185" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="BG2" s="185" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="BH2" s="186" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="BI2" s="186" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="BJ2" s="186" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9469,7 +9562,7 @@
       <c r="BB3" s="120"/>
       <c r="BC3" s="120"/>
       <c r="BD3" s="187">
-        <f>SUM(B3:BC3)</f>
+        <f t="shared" ref="BD3:BD53" si="0">SUM(B3:BC3)</f>
         <v>1</v>
       </c>
       <c r="BE3" s="187" cm="1">
@@ -9485,15 +9578,15 @@
         <v>0.0294117647058824</v>
       </c>
       <c r="BH3" s="189">
-        <f>RANK(BD3,BD$3:BD$53,0)</f>
+        <f t="shared" ref="BH3:BH53" si="1">RANK(BD3,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
       <c r="BI3" s="189">
-        <f>RANK(BE3,BE$3:BE$53,0)</f>
+        <f t="shared" ref="BI3:BI53" si="2">RANK(BE3,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
       <c r="BJ3" s="189">
-        <f>RANK(BF3,BF$3:BF$53,0)</f>
+        <f t="shared" ref="BJ3:BJ53" si="3">RANK(BF3,BF$3:BF$53,0)</f>
         <v>19</v>
       </c>
     </row>
@@ -9580,7 +9673,7 @@
       <c r="BB4" s="120"/>
       <c r="BC4" s="120"/>
       <c r="BD4" s="187">
-        <f>SUM(B4:BC4)</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="BE4" s="187" cm="1">
@@ -9596,15 +9689,15 @@
         <v>0.323529411764706</v>
       </c>
       <c r="BH4" s="189">
-        <f>RANK(BD4,BD$3:BD$53,0)</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="BI4" s="189">
-        <f>RANK(BE4,BE$3:BE$53,0)</f>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="BJ4" s="189">
-        <f>RANK(BF4,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -9671,7 +9764,7 @@
       <c r="BB5" s="120"/>
       <c r="BC5" s="120"/>
       <c r="BD5" s="187">
-        <f>SUM(B5:BC5)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="BE5" s="187" cm="1">
@@ -9687,15 +9780,15 @@
         <v>0.0588235294117647</v>
       </c>
       <c r="BH5" s="189">
-        <f>RANK(BD5,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="BI5" s="189">
-        <f>RANK(BE5,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="BJ5" s="189">
-        <f>RANK(BF5,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -9748,7 +9841,9 @@
       <c r="AL6" s="120"/>
       <c r="AM6" s="120"/>
       <c r="AN6" s="120"/>
-      <c r="AO6" s="120"/>
+      <c r="AO6" s="120">
+        <v>1</v>
+      </c>
       <c r="AP6" s="120"/>
       <c r="AQ6" s="120"/>
       <c r="AR6" s="120"/>
@@ -9764,12 +9859,12 @@
       <c r="BB6" s="120"/>
       <c r="BC6" s="120"/>
       <c r="BD6" s="187">
-        <f>SUM(B6:BC6)</f>
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="BE6" s="187" cm="1">
         <f t="array" ref="BE6">SUMPRODUCT(--(B6:BC6=INT(B6:BC6)),--(B6:BC6&gt;0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BF6" s="187" cm="1">
         <f t="array" ref="BF6">MAX(FREQUENCY(IF((B6:BC6=INT(B6:BC6))*(B6:BC6&gt;0),COLUMN(B6:BC6)),IF((B6:BC6&lt;&gt;INT(B6:BC6))+(B6:BC6&lt;=0),COLUMN(B6:BC6))))</f>
@@ -9780,15 +9875,15 @@
         <v>0.0588235294117647</v>
       </c>
       <c r="BH6" s="189">
-        <f>RANK(BD6,BD$3:BD$53,0)</f>
-        <v>28</v>
+        <f t="shared" si="1"/>
+        <v>23</v>
       </c>
       <c r="BI6" s="189">
-        <f>RANK(BE6,BE$3:BE$53,0)</f>
-        <v>26</v>
+        <f t="shared" si="2"/>
+        <v>23</v>
       </c>
       <c r="BJ6" s="189">
-        <f>RANK(BF6,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -9857,7 +9952,7 @@
       <c r="BB7" s="120"/>
       <c r="BC7" s="120"/>
       <c r="BD7" s="187">
-        <f>SUM(B7:BC7)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="BE7" s="187" cm="1">
@@ -9873,15 +9968,15 @@
         <v>0.0882352941176471</v>
       </c>
       <c r="BH7" s="189">
-        <f>RANK(BD7,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="BI7" s="189">
-        <f>RANK(BE7,BE$3:BE$53,0)</f>
-        <v>26</v>
+        <f t="shared" si="2"/>
+        <v>27</v>
       </c>
       <c r="BJ7" s="189">
-        <f>RANK(BF7,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -9984,7 +10079,7 @@
       <c r="BB8" s="120"/>
       <c r="BC8" s="120"/>
       <c r="BD8" s="187">
-        <f>SUM(B8:BC8)</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="BE8" s="187" cm="1">
@@ -10000,15 +10095,15 @@
         <v>0.470588235294118</v>
       </c>
       <c r="BH8" s="189">
-        <f>RANK(BD8,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="BI8" s="189">
-        <f>RANK(BE8,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="BJ8" s="189">
-        <f>RANK(BF8,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -10079,7 +10174,9 @@
       <c r="AL9" s="120"/>
       <c r="AM9" s="120"/>
       <c r="AN9" s="120"/>
-      <c r="AO9" s="120"/>
+      <c r="AO9" s="120">
+        <v>1</v>
+      </c>
       <c r="AP9" s="120"/>
       <c r="AQ9" s="120"/>
       <c r="AR9" s="120"/>
@@ -10095,12 +10192,12 @@
       <c r="BB9" s="120"/>
       <c r="BC9" s="120"/>
       <c r="BD9" s="187">
-        <f>SUM(B9:BC9)</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="BE9" s="187" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF9" s="187" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
@@ -10111,15 +10208,15 @@
         <v>0.294117647058824</v>
       </c>
       <c r="BH9" s="189">
-        <f>RANK(BD9,BD$3:BD$53,0)</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="BI9" s="189">
-        <f>RANK(BE9,BE$3:BE$53,0)</f>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="BJ9" s="189">
-        <f>RANK(BF9,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -10184,7 +10281,7 @@
       <c r="BB10" s="120"/>
       <c r="BC10" s="120"/>
       <c r="BD10" s="187">
-        <f>SUM(B10:BC10)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="BE10" s="187" cm="1">
@@ -10200,15 +10297,15 @@
         <v>0.0294117647058824</v>
       </c>
       <c r="BH10" s="189">
-        <f>RANK(BD10,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="BI10" s="189">
-        <f>RANK(BE10,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="BJ10" s="189">
-        <f>RANK(BF10,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -10285,7 +10382,7 @@
       <c r="BB11" s="120"/>
       <c r="BC11" s="120"/>
       <c r="BD11" s="187">
-        <f>SUM(B11:BC11)</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="BE11" s="187" cm="1">
@@ -10301,15 +10398,15 @@
         <v>0.205882352941176</v>
       </c>
       <c r="BH11" s="189">
-        <f>RANK(BD11,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="BI11" s="189">
-        <f>RANK(BE11,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="BJ11" s="189">
-        <f>RANK(BF11,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -10376,7 +10473,7 @@
       <c r="BB12" s="120"/>
       <c r="BC12" s="120"/>
       <c r="BD12" s="187">
-        <f>SUM(B12:BC12)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="BE12" s="187" cm="1">
@@ -10392,15 +10489,15 @@
         <v>0.0588235294117647</v>
       </c>
       <c r="BH12" s="189">
-        <f>RANK(BD12,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="BI12" s="189">
-        <f>RANK(BE12,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="BJ12" s="189">
-        <f>RANK(BF12,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -10483,7 +10580,7 @@
       <c r="BB13" s="120"/>
       <c r="BC13" s="120"/>
       <c r="BD13" s="187">
-        <f>SUM(B13:BC13)</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="BE13" s="187" cm="1">
@@ -10499,15 +10596,15 @@
         <v>0.235294117647059</v>
       </c>
       <c r="BH13" s="189">
-        <f>RANK(BD13,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="BI13" s="189">
-        <f>RANK(BE13,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="BJ13" s="189">
-        <f>RANK(BF13,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -10574,7 +10671,7 @@
       <c r="BB14" s="120"/>
       <c r="BC14" s="120"/>
       <c r="BD14" s="187">
-        <f>SUM(B14:BC14)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="BE14" s="187" cm="1">
@@ -10590,15 +10687,15 @@
         <v>0.0588235294117647</v>
       </c>
       <c r="BH14" s="189">
-        <f>RANK(BD14,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="BI14" s="189">
-        <f>RANK(BE14,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="BJ14" s="189">
-        <f>RANK(BF14,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -10667,7 +10764,9 @@
       <c r="AN15" s="120">
         <v>2</v>
       </c>
-      <c r="AO15" s="120"/>
+      <c r="AO15" s="120">
+        <v>1</v>
+      </c>
       <c r="AP15" s="120"/>
       <c r="AQ15" s="120"/>
       <c r="AR15" s="120"/>
@@ -10683,32 +10782,32 @@
       <c r="BB15" s="120"/>
       <c r="BC15" s="120"/>
       <c r="BD15" s="187">
-        <f>SUM(B15:BC15)</f>
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="BE15" s="187" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF15" s="187" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG15" s="188" cm="1">
         <f t="array" ref="BG15">SUMPRODUCT(--(B15:AI15=INT(B15:AI15)),--(B15:AI15&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
       <c r="BH15" s="189">
-        <f>RANK(BD15,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="BI15" s="189">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="BJ15" s="189">
+        <f t="shared" si="3"/>
         <v>8</v>
-      </c>
-      <c r="BI15" s="189">
-        <f>RANK(BE15,BE$3:BE$53,0)</f>
-        <v>8</v>
-      </c>
-      <c r="BJ15" s="189">
-        <f>RANK(BF15,BF$3:BF$53,0)</f>
-        <v>13</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:62">
@@ -10774,7 +10873,7 @@
       <c r="BB16" s="120"/>
       <c r="BC16" s="120"/>
       <c r="BD16" s="187">
-        <f>SUM(B16:BC16)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="BE16" s="187" cm="1">
@@ -10790,15 +10889,15 @@
         <v>0.0588235294117647</v>
       </c>
       <c r="BH16" s="189">
-        <f>RANK(BD16,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="BI16" s="189">
-        <f>RANK(BE16,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="BJ16" s="189">
-        <f>RANK(BF16,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -10869,7 +10968,7 @@
       <c r="BB17" s="120"/>
       <c r="BC17" s="120"/>
       <c r="BD17" s="187">
-        <f>SUM(B17:BC17)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="BE17" s="187" cm="1">
@@ -10885,15 +10984,15 @@
         <v>0.0882352941176471</v>
       </c>
       <c r="BH17" s="189">
-        <f>RANK(BD17,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="BI17" s="189">
-        <f>RANK(BE17,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="BJ17" s="189">
-        <f>RANK(BF17,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -10958,7 +11057,7 @@
       <c r="BB18" s="120"/>
       <c r="BC18" s="120"/>
       <c r="BD18" s="187">
-        <f>SUM(B18:BC18)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="BE18" s="187" cm="1">
@@ -10974,15 +11073,15 @@
         <v>0.0294117647058824</v>
       </c>
       <c r="BH18" s="189">
-        <f>RANK(BD18,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="BI18" s="189">
-        <f>RANK(BE18,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="BJ18" s="189">
-        <f>RANK(BF18,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -11055,7 +11154,7 @@
       <c r="BB19" s="120"/>
       <c r="BC19" s="120"/>
       <c r="BD19" s="187">
-        <f>SUM(B19:BC19)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="BE19" s="187" cm="1">
@@ -11071,16 +11170,16 @@
         <v>0.147058823529412</v>
       </c>
       <c r="BH19" s="189">
-        <f>RANK(BD19,BD$3:BD$53,0)</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="BI19" s="189">
-        <f>RANK(BE19,BE$3:BE$53,0)</f>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>21</v>
       </c>
       <c r="BJ19" s="189">
-        <f>RANK(BF19,BF$3:BF$53,0)</f>
-        <v>13</v>
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:62">
@@ -11144,7 +11243,7 @@
       <c r="BB20" s="120"/>
       <c r="BC20" s="120"/>
       <c r="BD20" s="187">
-        <f>SUM(B20:BC20)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="BE20" s="187" cm="1">
@@ -11160,15 +11259,15 @@
         <v>0.0294117647058824</v>
       </c>
       <c r="BH20" s="189">
-        <f>RANK(BD20,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="BI20" s="189">
-        <f>RANK(BE20,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="BJ20" s="189">
-        <f>RANK(BF20,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -11235,7 +11334,7 @@
       <c r="BB21" s="120"/>
       <c r="BC21" s="120"/>
       <c r="BD21" s="187">
-        <f>SUM(B21:BC21)</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="BE21" s="187" cm="1">
@@ -11251,15 +11350,15 @@
         <v>0.0588235294117647</v>
       </c>
       <c r="BH21" s="189">
-        <f>RANK(BD21,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="BI21" s="189">
-        <f>RANK(BE21,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="BJ21" s="189">
-        <f>RANK(BF21,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -11344,7 +11443,7 @@
       <c r="BB22" s="120"/>
       <c r="BC22" s="120"/>
       <c r="BD22" s="187">
-        <f>SUM(B22:BC22)</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="BE22" s="187" cm="1">
@@ -11360,15 +11459,15 @@
         <v>0.294117647058824</v>
       </c>
       <c r="BH22" s="189">
-        <f>RANK(BD22,BD$3:BD$53,0)</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="BI22" s="189">
-        <f>RANK(BE22,BE$3:BE$53,0)</f>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>11</v>
       </c>
       <c r="BJ22" s="189">
-        <f>RANK(BF22,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -11431,7 +11530,7 @@
       <c r="BB23" s="120"/>
       <c r="BC23" s="120"/>
       <c r="BD23" s="187">
-        <f>SUM(B23:BC23)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE23" s="187" cm="1">
@@ -11447,15 +11546,15 @@
         <v>0</v>
       </c>
       <c r="BH23" s="189">
-        <f>RANK(BD23,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI23" s="189">
-        <f>RANK(BE23,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ23" s="189">
-        <f>RANK(BF23,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -11534,7 +11633,7 @@
       <c r="BB24" s="120"/>
       <c r="BC24" s="120"/>
       <c r="BD24" s="187">
-        <f>SUM(B24:BC24)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="BE24" s="187" cm="1">
@@ -11550,15 +11649,15 @@
         <v>0.235294117647059</v>
       </c>
       <c r="BH24" s="189">
-        <f>RANK(BD24,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="BI24" s="189">
-        <f>RANK(BE24,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="BJ24" s="189">
-        <f>RANK(BF24,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -11623,7 +11722,7 @@
       <c r="BB25" s="120"/>
       <c r="BC25" s="120"/>
       <c r="BD25" s="187">
-        <f>SUM(B25:BC25)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="BE25" s="187" cm="1">
@@ -11639,15 +11738,15 @@
         <v>0.0294117647058824</v>
       </c>
       <c r="BH25" s="189">
-        <f>RANK(BD25,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="BI25" s="189">
-        <f>RANK(BE25,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="BJ25" s="189">
-        <f>RANK(BF25,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -11710,7 +11809,7 @@
       <c r="BB26" s="120"/>
       <c r="BC26" s="120"/>
       <c r="BD26" s="187">
-        <f>SUM(B26:BC26)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE26" s="187" cm="1">
@@ -11726,15 +11825,15 @@
         <v>0</v>
       </c>
       <c r="BH26" s="189">
-        <f>RANK(BD26,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI26" s="189">
-        <f>RANK(BE26,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ26" s="189">
-        <f>RANK(BF26,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -11797,7 +11896,7 @@
       <c r="BB27" s="120"/>
       <c r="BC27" s="120"/>
       <c r="BD27" s="187">
-        <f>SUM(B27:BC27)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE27" s="187" cm="1">
@@ -11813,15 +11912,15 @@
         <v>0</v>
       </c>
       <c r="BH27" s="189">
-        <f>RANK(BD27,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI27" s="189">
-        <f>RANK(BE27,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ27" s="189">
-        <f>RANK(BF27,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -11902,7 +12001,7 @@
       <c r="BB28" s="120"/>
       <c r="BC28" s="120"/>
       <c r="BD28" s="187">
-        <f>SUM(B28:BC28)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="BE28" s="187" cm="1">
@@ -11918,16 +12017,16 @@
         <v>0.235294117647059</v>
       </c>
       <c r="BH28" s="189">
-        <f>RANK(BD28,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="BI28" s="189">
-        <f>RANK(BE28,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="BJ28" s="189">
-        <f>RANK(BF28,BF$3:BF$53,0)</f>
-        <v>13</v>
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:62">
@@ -11983,7 +12082,9 @@
       <c r="AL29" s="120"/>
       <c r="AM29" s="120"/>
       <c r="AN29" s="120"/>
-      <c r="AO29" s="120"/>
+      <c r="AO29" s="120">
+        <v>1</v>
+      </c>
       <c r="AP29" s="120"/>
       <c r="AQ29" s="120"/>
       <c r="AR29" s="120"/>
@@ -11999,12 +12100,12 @@
       <c r="BB29" s="120"/>
       <c r="BC29" s="120"/>
       <c r="BD29" s="187">
-        <f>SUM(B29:BC29)</f>
-        <v>5</v>
+        <f t="shared" si="0"/>
+        <v>6</v>
       </c>
       <c r="BE29" s="187" cm="1">
         <f t="array" ref="BE29">SUMPRODUCT(--(B29:BC29=INT(B29:BC29)),--(B29:BC29&gt;0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF29" s="187" cm="1">
         <f t="array" ref="BF29">MAX(FREQUENCY(IF((B29:BC29=INT(B29:BC29))*(B29:BC29&gt;0),COLUMN(B29:BC29)),IF((B29:BC29&lt;&gt;INT(B29:BC29))+(B29:BC29&lt;=0),COLUMN(B29:BC29))))</f>
@@ -12015,15 +12116,15 @@
         <v>0.117647058823529</v>
       </c>
       <c r="BH29" s="189">
-        <f>RANK(BD29,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="BI29" s="189">
-        <f>RANK(BE29,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="BJ29" s="189">
-        <f>RANK(BF29,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -12100,7 +12201,7 @@
       <c r="BB30" s="120"/>
       <c r="BC30" s="120"/>
       <c r="BD30" s="187">
-        <f>SUM(B30:BC30)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="BE30" s="187" cm="1">
@@ -12116,15 +12217,15 @@
         <v>0.205882352941176</v>
       </c>
       <c r="BH30" s="189">
-        <f>RANK(BD30,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="BI30" s="189">
-        <f>RANK(BE30,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="BJ30" s="189">
-        <f>RANK(BF30,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -12207,7 +12308,7 @@
       <c r="BB31" s="120"/>
       <c r="BC31" s="120"/>
       <c r="BD31" s="187">
-        <f>SUM(B31:BC31)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="BE31" s="187" cm="1">
@@ -12223,16 +12324,16 @@
         <v>0.205882352941176</v>
       </c>
       <c r="BH31" s="189">
-        <f>RANK(BD31,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="BI31" s="189">
-        <f>RANK(BE31,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="BJ31" s="189">
-        <f>RANK(BF31,BF$3:BF$53,0)</f>
-        <v>13</v>
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:62">
@@ -12314,7 +12415,7 @@
       <c r="BB32" s="120"/>
       <c r="BC32" s="120"/>
       <c r="BD32" s="187">
-        <f>SUM(B32:BC32)</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="BE32" s="187" cm="1">
@@ -12330,15 +12431,15 @@
         <v>0.264705882352941</v>
       </c>
       <c r="BH32" s="189">
-        <f>RANK(BD32,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="BI32" s="189">
-        <f>RANK(BE32,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="BJ32" s="189">
-        <f>RANK(BF32,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -12409,7 +12510,7 @@
       <c r="BB33" s="120"/>
       <c r="BC33" s="120"/>
       <c r="BD33" s="187">
-        <f>SUM(B33:BC33)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="BE33" s="187" cm="1">
@@ -12425,15 +12526,15 @@
         <v>0.0882352941176471</v>
       </c>
       <c r="BH33" s="189">
-        <f>RANK(BD33,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="BI33" s="189">
-        <f>RANK(BE33,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="BJ33" s="189">
-        <f>RANK(BF33,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -12496,7 +12597,7 @@
       <c r="BB34" s="120"/>
       <c r="BC34" s="120"/>
       <c r="BD34" s="187">
-        <f>SUM(B34:BC34)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE34" s="187" cm="1">
@@ -12512,78 +12613,78 @@
         <v>0</v>
       </c>
       <c r="BH34" s="189">
-        <f>RANK(BD34,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI34" s="189">
-        <f>RANK(BE34,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ34" s="189">
-        <f>RANK(BF34,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:62">
-      <c r="A35" s="190">
+      <c r="A35" s="191">
         <v>33</v>
       </c>
-      <c r="B35" s="120"/>
-      <c r="C35" s="120"/>
-      <c r="D35" s="120"/>
-      <c r="E35" s="120"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="120"/>
-      <c r="H35" s="120"/>
-      <c r="I35" s="120"/>
-      <c r="J35" s="120"/>
-      <c r="K35" s="120"/>
-      <c r="L35" s="120"/>
-      <c r="M35" s="120"/>
-      <c r="N35" s="120"/>
-      <c r="O35" s="120"/>
-      <c r="P35" s="120"/>
-      <c r="Q35" s="120"/>
-      <c r="R35" s="120"/>
-      <c r="S35" s="120"/>
-      <c r="T35" s="120"/>
-      <c r="U35" s="120"/>
-      <c r="V35" s="120"/>
-      <c r="W35" s="120"/>
-      <c r="X35" s="120"/>
-      <c r="Y35" s="120"/>
-      <c r="Z35" s="120"/>
-      <c r="AA35" s="120"/>
-      <c r="AB35" s="120"/>
-      <c r="AC35" s="120"/>
-      <c r="AD35" s="120"/>
-      <c r="AE35" s="120"/>
-      <c r="AF35" s="120"/>
-      <c r="AG35" s="120"/>
-      <c r="AH35" s="120"/>
-      <c r="AI35" s="120"/>
-      <c r="AJ35" s="120"/>
-      <c r="AK35" s="120"/>
-      <c r="AL35" s="120"/>
-      <c r="AM35" s="120"/>
-      <c r="AN35" s="120"/>
-      <c r="AO35" s="120"/>
-      <c r="AP35" s="120"/>
-      <c r="AQ35" s="120"/>
-      <c r="AR35" s="120"/>
-      <c r="AS35" s="120"/>
-      <c r="AT35" s="120"/>
-      <c r="AU35" s="120"/>
-      <c r="AV35" s="120"/>
-      <c r="AW35" s="120"/>
-      <c r="AX35" s="120"/>
-      <c r="AY35" s="120"/>
-      <c r="AZ35" s="120"/>
-      <c r="BA35" s="120"/>
-      <c r="BB35" s="120"/>
-      <c r="BC35" s="120"/>
+      <c r="B35" s="192"/>
+      <c r="C35" s="192"/>
+      <c r="D35" s="192"/>
+      <c r="E35" s="192"/>
+      <c r="F35" s="192"/>
+      <c r="G35" s="192"/>
+      <c r="H35" s="192"/>
+      <c r="I35" s="192"/>
+      <c r="J35" s="192"/>
+      <c r="K35" s="192"/>
+      <c r="L35" s="192"/>
+      <c r="M35" s="192"/>
+      <c r="N35" s="192"/>
+      <c r="O35" s="192"/>
+      <c r="P35" s="192"/>
+      <c r="Q35" s="192"/>
+      <c r="R35" s="192"/>
+      <c r="S35" s="192"/>
+      <c r="T35" s="192"/>
+      <c r="U35" s="192"/>
+      <c r="V35" s="192"/>
+      <c r="W35" s="192"/>
+      <c r="X35" s="192"/>
+      <c r="Y35" s="192"/>
+      <c r="Z35" s="192"/>
+      <c r="AA35" s="192"/>
+      <c r="AB35" s="192"/>
+      <c r="AC35" s="192"/>
+      <c r="AD35" s="192"/>
+      <c r="AE35" s="192"/>
+      <c r="AF35" s="192"/>
+      <c r="AG35" s="192"/>
+      <c r="AH35" s="192"/>
+      <c r="AI35" s="192"/>
+      <c r="AJ35" s="192"/>
+      <c r="AK35" s="192"/>
+      <c r="AL35" s="192"/>
+      <c r="AM35" s="192"/>
+      <c r="AN35" s="192"/>
+      <c r="AO35" s="192"/>
+      <c r="AP35" s="192"/>
+      <c r="AQ35" s="192"/>
+      <c r="AR35" s="192"/>
+      <c r="AS35" s="192"/>
+      <c r="AT35" s="192"/>
+      <c r="AU35" s="192"/>
+      <c r="AV35" s="192"/>
+      <c r="AW35" s="192"/>
+      <c r="AX35" s="192"/>
+      <c r="AY35" s="192"/>
+      <c r="AZ35" s="192"/>
+      <c r="BA35" s="192"/>
+      <c r="BB35" s="192"/>
+      <c r="BC35" s="192"/>
       <c r="BD35" s="187">
-        <f>SUM(B35:BC35)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE35" s="187" cm="1">
@@ -12599,15 +12700,15 @@
         <v>0</v>
       </c>
       <c r="BH35" s="189">
-        <f>RANK(BD35,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI35" s="189">
-        <f>RANK(BE35,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ35" s="189">
-        <f>RANK(BF35,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -12672,7 +12773,7 @@
       <c r="BB36" s="120"/>
       <c r="BC36" s="120"/>
       <c r="BD36" s="187">
-        <f>SUM(B36:BC36)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="BE36" s="187" cm="1">
@@ -12688,15 +12789,15 @@
         <v>0.0294117647058824</v>
       </c>
       <c r="BH36" s="189">
-        <f>RANK(BD36,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="BI36" s="189">
-        <f>RANK(BE36,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="BJ36" s="189">
-        <f>RANK(BF36,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -12773,7 +12874,7 @@
       <c r="BB37" s="120"/>
       <c r="BC37" s="120"/>
       <c r="BD37" s="187">
-        <f>SUM(B37:BC37)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="BE37" s="187" cm="1">
@@ -12789,15 +12890,15 @@
         <v>0.176470588235294</v>
       </c>
       <c r="BH37" s="189">
-        <f>RANK(BD37,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="BI37" s="189">
-        <f>RANK(BE37,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="BJ37" s="189">
-        <f>RANK(BF37,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
@@ -12866,7 +12967,7 @@
       <c r="BB38" s="120"/>
       <c r="BC38" s="120"/>
       <c r="BD38" s="187">
-        <f>SUM(B38:BC38)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="BE38" s="187" cm="1">
@@ -12882,78 +12983,78 @@
         <v>0.0882352941176471</v>
       </c>
       <c r="BH38" s="189">
-        <f>RANK(BD38,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="BI38" s="189">
-        <f>RANK(BE38,BE$3:BE$53,0)</f>
-        <v>26</v>
+        <f t="shared" si="2"/>
+        <v>27</v>
       </c>
       <c r="BJ38" s="189">
-        <f>RANK(BF38,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:62">
-      <c r="A39" s="175">
+      <c r="A39" s="191">
         <v>37</v>
       </c>
-      <c r="B39" s="175"/>
-      <c r="C39" s="175"/>
-      <c r="D39" s="175"/>
-      <c r="E39" s="175"/>
-      <c r="F39" s="175"/>
-      <c r="G39" s="175"/>
-      <c r="H39" s="175"/>
-      <c r="I39" s="175"/>
-      <c r="J39" s="175"/>
-      <c r="K39" s="175"/>
-      <c r="L39" s="175"/>
-      <c r="M39" s="175"/>
-      <c r="N39" s="175"/>
-      <c r="O39" s="175"/>
-      <c r="P39" s="175"/>
-      <c r="Q39" s="175"/>
-      <c r="R39" s="175"/>
-      <c r="S39" s="175"/>
-      <c r="T39" s="175"/>
-      <c r="U39" s="175"/>
-      <c r="V39" s="175"/>
-      <c r="W39" s="175"/>
-      <c r="X39" s="175"/>
-      <c r="Y39" s="175"/>
-      <c r="Z39" s="175"/>
-      <c r="AA39" s="175"/>
-      <c r="AB39" s="175"/>
-      <c r="AC39" s="175"/>
-      <c r="AD39" s="175"/>
-      <c r="AE39" s="175"/>
-      <c r="AF39" s="175"/>
-      <c r="AG39" s="175"/>
-      <c r="AH39" s="175"/>
-      <c r="AI39" s="175"/>
-      <c r="AJ39" s="175"/>
-      <c r="AK39" s="175"/>
-      <c r="AL39" s="175"/>
-      <c r="AM39" s="175"/>
-      <c r="AN39" s="175"/>
-      <c r="AO39" s="175"/>
-      <c r="AP39" s="175"/>
-      <c r="AQ39" s="175"/>
-      <c r="AR39" s="175"/>
-      <c r="AS39" s="175"/>
-      <c r="AT39" s="175"/>
-      <c r="AU39" s="175"/>
-      <c r="AV39" s="175"/>
-      <c r="AW39" s="175"/>
-      <c r="AX39" s="175"/>
-      <c r="AY39" s="175"/>
-      <c r="AZ39" s="175"/>
-      <c r="BA39" s="175"/>
-      <c r="BB39" s="175"/>
-      <c r="BC39" s="175"/>
+      <c r="B39" s="191"/>
+      <c r="C39" s="191"/>
+      <c r="D39" s="191"/>
+      <c r="E39" s="191"/>
+      <c r="F39" s="191"/>
+      <c r="G39" s="191"/>
+      <c r="H39" s="191"/>
+      <c r="I39" s="191"/>
+      <c r="J39" s="191"/>
+      <c r="K39" s="191"/>
+      <c r="L39" s="191"/>
+      <c r="M39" s="191"/>
+      <c r="N39" s="191"/>
+      <c r="O39" s="191"/>
+      <c r="P39" s="191"/>
+      <c r="Q39" s="191"/>
+      <c r="R39" s="191"/>
+      <c r="S39" s="191"/>
+      <c r="T39" s="191"/>
+      <c r="U39" s="191"/>
+      <c r="V39" s="191"/>
+      <c r="W39" s="191"/>
+      <c r="X39" s="191"/>
+      <c r="Y39" s="191"/>
+      <c r="Z39" s="191"/>
+      <c r="AA39" s="191"/>
+      <c r="AB39" s="191"/>
+      <c r="AC39" s="191"/>
+      <c r="AD39" s="191"/>
+      <c r="AE39" s="191"/>
+      <c r="AF39" s="191"/>
+      <c r="AG39" s="191"/>
+      <c r="AH39" s="191"/>
+      <c r="AI39" s="191"/>
+      <c r="AJ39" s="191"/>
+      <c r="AK39" s="191"/>
+      <c r="AL39" s="191"/>
+      <c r="AM39" s="191"/>
+      <c r="AN39" s="191"/>
+      <c r="AO39" s="191"/>
+      <c r="AP39" s="191"/>
+      <c r="AQ39" s="191"/>
+      <c r="AR39" s="191"/>
+      <c r="AS39" s="191"/>
+      <c r="AT39" s="191"/>
+      <c r="AU39" s="191"/>
+      <c r="AV39" s="191"/>
+      <c r="AW39" s="191"/>
+      <c r="AX39" s="191"/>
+      <c r="AY39" s="191"/>
+      <c r="AZ39" s="191"/>
+      <c r="BA39" s="191"/>
+      <c r="BB39" s="191"/>
+      <c r="BC39" s="191"/>
       <c r="BD39" s="187">
-        <f>SUM(B39:BC39)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE39" s="187" cm="1">
@@ -12968,16 +13069,16 @@
         <f t="array" ref="BG39">SUMPRODUCT(--(B39:AI39=INT(B39:AI39)),--(B39:AI39&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH39" s="191">
-        <f>RANK(BD39,BD$3:BD$53,0)</f>
+      <c r="BH39" s="193">
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="BI39" s="191">
-        <f>RANK(BE39,BE$3:BE$53,0)</f>
+      <c r="BI39" s="193">
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="BJ39" s="191">
-        <f>RANK(BF39,BF$3:BF$53,0)</f>
+      <c r="BJ39" s="193">
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -13088,7 +13189,7 @@
       <c r="BB40" s="120"/>
       <c r="BC40" s="120"/>
       <c r="BD40" s="187">
-        <f>SUM(B40:BC40)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="BE40" s="187" cm="1">
@@ -13104,15 +13205,15 @@
         <v>0.617647058823529</v>
       </c>
       <c r="BH40" s="189">
-        <f>RANK(BD40,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="BI40" s="189">
-        <f>RANK(BE40,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="BJ40" s="189">
-        <f>RANK(BF40,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -13181,7 +13282,9 @@
       <c r="AN41" s="120">
         <v>1</v>
       </c>
-      <c r="AO41" s="120"/>
+      <c r="AO41" s="120">
+        <v>2</v>
+      </c>
       <c r="AP41" s="120"/>
       <c r="AQ41" s="120"/>
       <c r="AR41" s="120"/>
@@ -13197,12 +13300,12 @@
       <c r="BB41" s="120"/>
       <c r="BC41" s="120"/>
       <c r="BD41" s="187">
-        <f>SUM(B41:BC41)</f>
-        <v>14</v>
+        <f t="shared" si="0"/>
+        <v>16</v>
       </c>
       <c r="BE41" s="187" cm="1">
         <f t="array" ref="BE41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF41" s="187" cm="1">
         <f t="array" ref="BF41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
@@ -13213,16 +13316,16 @@
         <v>0.235294117647059</v>
       </c>
       <c r="BH41" s="189">
-        <f>RANK(BD41,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="BI41" s="189">
-        <f>RANK(BE41,BE$3:BE$53,0)</f>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="BJ41" s="189">
-        <f>RANK(BF41,BF$3:BF$53,0)</f>
-        <v>13</v>
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:62">
@@ -13296,7 +13399,9 @@
       <c r="AL42" s="120"/>
       <c r="AM42" s="120"/>
       <c r="AN42" s="120"/>
-      <c r="AO42" s="120"/>
+      <c r="AO42" s="120">
+        <v>1</v>
+      </c>
       <c r="AP42" s="120"/>
       <c r="AQ42" s="120"/>
       <c r="AR42" s="120"/>
@@ -13312,12 +13417,12 @@
       <c r="BB42" s="120"/>
       <c r="BC42" s="120"/>
       <c r="BD42" s="187">
-        <f>SUM(B42:BC42)</f>
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="BE42" s="187" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF42" s="187" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
@@ -13328,15 +13433,15 @@
         <v>0.352941176470588</v>
       </c>
       <c r="BH42" s="189">
-        <f>RANK(BD42,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="BI42" s="189">
-        <f>RANK(BE42,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="BJ42" s="189">
-        <f>RANK(BF42,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -13399,7 +13504,7 @@
       <c r="BB43" s="120"/>
       <c r="BC43" s="120"/>
       <c r="BD43" s="187">
-        <f>SUM(B43:BC43)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE43" s="187" cm="1">
@@ -13415,15 +13520,15 @@
         <v>0</v>
       </c>
       <c r="BH43" s="189">
-        <f>RANK(BD43,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI43" s="189">
-        <f>RANK(BE43,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ43" s="189">
-        <f>RANK(BF43,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -13498,7 +13603,9 @@
       <c r="AL44" s="120"/>
       <c r="AM44" s="120"/>
       <c r="AN44" s="120"/>
-      <c r="AO44" s="120"/>
+      <c r="AO44" s="120">
+        <v>1</v>
+      </c>
       <c r="AP44" s="120"/>
       <c r="AQ44" s="120"/>
       <c r="AR44" s="120"/>
@@ -13514,12 +13621,12 @@
       <c r="BB44" s="120"/>
       <c r="BC44" s="120"/>
       <c r="BD44" s="187">
-        <f>SUM(B44:BC44)</f>
-        <v>17</v>
+        <f t="shared" si="0"/>
+        <v>18</v>
       </c>
       <c r="BE44" s="187" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF44" s="187" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
@@ -13530,15 +13637,15 @@
         <v>0.411764705882353</v>
       </c>
       <c r="BH44" s="189">
-        <f>RANK(BD44,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="BI44" s="189">
-        <f>RANK(BE44,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="BJ44" s="189">
-        <f>RANK(BF44,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -13601,7 +13708,7 @@
       <c r="BB45" s="120"/>
       <c r="BC45" s="120"/>
       <c r="BD45" s="187">
-        <f>SUM(B45:BC45)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE45" s="187" cm="1">
@@ -13617,15 +13724,15 @@
         <v>0</v>
       </c>
       <c r="BH45" s="189">
-        <f>RANK(BD45,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI45" s="189">
-        <f>RANK(BE45,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ45" s="189">
-        <f>RANK(BF45,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -13736,7 +13843,7 @@
       <c r="BB46" s="120"/>
       <c r="BC46" s="120"/>
       <c r="BD46" s="187">
-        <f>SUM(B46:BC46)</f>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="BE46" s="187" cm="1">
@@ -13752,15 +13859,15 @@
         <v>0.617647058823529</v>
       </c>
       <c r="BH46" s="189">
-        <f>RANK(BD46,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="BI46" s="189">
-        <f>RANK(BE46,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="BJ46" s="189">
-        <f>RANK(BF46,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
@@ -13823,7 +13930,7 @@
       <c r="BB47" s="120"/>
       <c r="BC47" s="120"/>
       <c r="BD47" s="187">
-        <f>SUM(B47:BC47)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE47" s="187" cm="1">
@@ -13839,15 +13946,15 @@
         <v>0</v>
       </c>
       <c r="BH47" s="189">
-        <f>RANK(BD47,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI47" s="189">
-        <f>RANK(BE47,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ47" s="189">
-        <f>RANK(BF47,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -13916,7 +14023,9 @@
       <c r="AN48" s="120">
         <v>2</v>
       </c>
-      <c r="AO48" s="120"/>
+      <c r="AO48" s="120">
+        <v>1</v>
+      </c>
       <c r="AP48" s="120"/>
       <c r="AQ48" s="120"/>
       <c r="AR48" s="120"/>
@@ -13932,12 +14041,12 @@
       <c r="BB48" s="120"/>
       <c r="BC48" s="120"/>
       <c r="BD48" s="187">
-        <f>SUM(B48:BC48)</f>
-        <v>12</v>
+        <f t="shared" si="0"/>
+        <v>13</v>
       </c>
       <c r="BE48" s="187" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF48" s="187" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
@@ -13948,16 +14057,16 @@
         <v>0.264705882352941</v>
       </c>
       <c r="BH48" s="189">
-        <f>RANK(BD48,BD$3:BD$53,0)</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="BI48" s="189">
-        <f>RANK(BE48,BE$3:BE$53,0)</f>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="BJ48" s="189">
-        <f>RANK(BF48,BF$3:BF$53,0)</f>
-        <v>13</v>
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:62">
@@ -14027,7 +14136,7 @@
       <c r="BB49" s="120"/>
       <c r="BC49" s="120"/>
       <c r="BD49" s="187">
-        <f>SUM(B49:BC49)</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="BE49" s="187" cm="1">
@@ -14043,15 +14152,15 @@
         <v>0.0882352941176471</v>
       </c>
       <c r="BH49" s="189">
-        <f>RANK(BD49,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="BI49" s="189">
-        <f>RANK(BE49,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="BJ49" s="189">
-        <f>RANK(BF49,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -14124,7 +14233,7 @@
       <c r="BB50" s="120"/>
       <c r="BC50" s="120"/>
       <c r="BD50" s="187">
-        <f>SUM(B50:BC50)</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="BE50" s="187" cm="1">
@@ -14140,15 +14249,15 @@
         <v>0.117647058823529</v>
       </c>
       <c r="BH50" s="189">
-        <f>RANK(BD50,BD$3:BD$53,0)</f>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
       <c r="BI50" s="189">
-        <f>RANK(BE50,BE$3:BE$53,0)</f>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>21</v>
       </c>
       <c r="BJ50" s="189">
-        <f>RANK(BF50,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -14211,7 +14320,7 @@
       <c r="BB51" s="120"/>
       <c r="BC51" s="120"/>
       <c r="BD51" s="187">
-        <f>SUM(B51:BC51)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE51" s="187" cm="1">
@@ -14227,15 +14336,15 @@
         <v>0</v>
       </c>
       <c r="BH51" s="189">
-        <f>RANK(BD51,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI51" s="189">
-        <f>RANK(BE51,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ51" s="189">
-        <f>RANK(BF51,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -14298,7 +14407,7 @@
       <c r="BB52" s="120"/>
       <c r="BC52" s="120"/>
       <c r="BD52" s="187">
-        <f>SUM(B52:BC52)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="BE52" s="187" cm="1">
@@ -14314,15 +14423,15 @@
         <v>0</v>
       </c>
       <c r="BH52" s="189">
-        <f>RANK(BD52,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="BI52" s="189">
-        <f>RANK(BE52,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>41</v>
       </c>
       <c r="BJ52" s="189">
-        <f>RANK(BF52,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>41</v>
       </c>
     </row>
@@ -14387,7 +14496,7 @@
       <c r="BB53" s="120"/>
       <c r="BC53" s="120"/>
       <c r="BD53" s="187">
-        <f>SUM(B53:BC53)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="BE53" s="187" cm="1">
@@ -14403,15 +14512,15 @@
         <v>0</v>
       </c>
       <c r="BH53" s="189">
-        <f>RANK(BD53,BD$3:BD$53,0)</f>
+        <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="BI53" s="189">
-        <f>RANK(BE53,BE$3:BE$53,0)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="BJ53" s="189">
-        <f>RANK(BF53,BF$3:BF$53,0)</f>
+        <f t="shared" si="3"/>
         <v>19</v>
       </c>
     </row>
@@ -15538,9 +15647,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="Z9:AB9 AD9:AF9 X41 A9:X9" unlockedFormula="1"/>
-    <ignoredError sqref="A10:X10 Z3:AF3 A2:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH11:BJ39 Z10:AF10 BI9:BJ9 BH4:BJ8 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z28:AF33 A28:X33 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11 U1:AF1 C1:S1 A1" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="BG41:BG53 AG12:AI14 AG26:AI39 AG5:AI8 AH41:AI41 AF42:AI42 AG49:AI53 AG43:AI47 AG16:AI22 AG1:AI3 Y12:Y15 BG11:BG39 BG4:BG8 AF4:AI4 W8:AF8 A50:AE50 A51:AF53 Z48:AD48 AF48:AI48 Y48:Y49 A45:AF45 A46:AE46 A44:AE44 Y42 W40:AD40 Y3:Y4 A38:AC38 A34:AF35 A36:Y36 A28:Y33 A23:AI25 A22:AE22 A16:AF16 A17:Y18 AA13:AF13 Z14:AF14 AA15 AF15:AI15 AD11 AF11:AI11 A11:AA11" formulaRange="1"/>
+    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 A9:X9" unlockedFormula="1"/>
+    <ignoredError sqref="A1 C1:S1 U1:AF1 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z28:AF33 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 A3:X4 BD1:BJ2 BI3 AC40:AD40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 A48:X49 Z48:AB48 AE48 A51:AF53 A50:AD50 AF50 X8:AF8 A8:V8 A5:AF7 Z4:AE4 Z41:AE42 BH4:BJ8 BI9:BJ9 Z10:AF10 BH11:BJ39 Z49:AF49 A12:X15 A37:AF37 A39:AF39 A2:AF2 Z3:AF3 A10:X10" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="AA11:AD11 AG1:AI3 AG16:AI23 AG43:AI47 AG49:AI53 AF42:AI42 AH41:AI41 AG5:AI8 AG26:AI39 AG12:AI14 BG41:BG53 AF11:AI11 AF15:AI15 AA15 Z12:AF12 Z13:AA13 Y17:AF18 A19:AF21 Y22:AF22 A24:AI25 Y28:AF33 Y36:AF36 A37:AF37 Y38:AF38 A39:AF39 Y3:Y4 A40:AB40 Y42 A43:AF43 X44:AF44 Y46:AF46 A47:AF47 Y48:Y49 AC48:AD48 AF48:AI48 AE50:AF50 A5:AF7 A8:W8 AF4:AI4 BG4:BG8 BG11:BG39 Y12:Y15" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15587,21 +15696,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -15609,10 +15718,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -15625,10 +15734,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B4" s="158" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="C4" s="158"/>
       <c r="D4" s="158"/>
@@ -15641,7 +15750,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -15661,7 +15770,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -15671,7 +15780,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -15679,10 +15788,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -15697,14 +15806,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -15715,10 +15824,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -15731,23 +15840,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -15755,7 +15864,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -15771,7 +15880,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -15789,17 +15898,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -15807,10 +15916,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -15885,7 +15994,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -15910,10 +16019,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -15925,7 +16034,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -15947,7 +16056,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -15959,13 +16068,13 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="131" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E6" s="132"/>
       <c r="F6" s="133"/>
@@ -15977,23 +16086,23 @@
         <v>52</v>
       </c>
       <c r="D7" s="118" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" s="131" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F7" s="133"/>
     </row>
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D8" s="131" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8" s="132"/>
       <c r="F8" s="133"/>
@@ -16001,7 +16110,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -16013,7 +16122,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -16025,10 +16134,10 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C11" s="127" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D11" s="128"/>
       <c r="E11" s="128"/>
@@ -16036,13 +16145,13 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C12" s="137" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" s="138"/>
       <c r="E12" s="139" t="s">
@@ -16063,10 +16172,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -16077,7 +16186,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -16099,7 +16208,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -16111,7 +16220,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -16123,10 +16232,10 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C19" s="137" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" s="142"/>
       <c r="E19" s="142"/>
@@ -16135,10 +16244,10 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C20" s="137" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D20" s="142"/>
       <c r="E20" s="142"/>
@@ -16147,7 +16256,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -16159,7 +16268,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -16221,7 +16330,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -16252,7 +16361,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -16260,7 +16369,7 @@
         <v>44</v>
       </c>
       <c r="E3" s="103" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3" s="104"/>
       <c r="G3" s="104"/>
@@ -16282,16 +16391,16 @@
         <v>7</v>
       </c>
       <c r="F4" s="104" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G4" s="104" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" s="105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I4" s="105" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" s="93" customFormat="1" customHeight="1" spans="1:16">
@@ -16303,10 +16412,10 @@
         <v>38</v>
       </c>
       <c r="D5" s="103" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E5" s="103" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F5" s="104" t="s">
         <v>20</v>
@@ -16324,7 +16433,7 @@
     <row r="6" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A6" s="106"/>
       <c r="B6" s="102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="102" t="s">
         <v>30</v>
@@ -16333,10 +16442,10 @@
         <v>42</v>
       </c>
       <c r="E6" s="103" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F6" s="104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="104" t="s">
         <v>27</v>
@@ -16345,7 +16454,7 @@
         <v>36</v>
       </c>
       <c r="I6" s="105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" s="93" customFormat="1" customHeight="1" spans="1:16">
@@ -16354,19 +16463,19 @@
         <v>24</v>
       </c>
       <c r="C7" s="102" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7" s="103" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="103" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F7" s="104" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G7" s="104" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H7" s="105" t="s">
         <v>63</v>
@@ -16378,7 +16487,7 @@
     <row r="8" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A8" s="106"/>
       <c r="B8" s="102" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="102" t="s">
         <v>33</v>
@@ -16390,43 +16499,43 @@
         <v>13</v>
       </c>
       <c r="F8" s="104" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8" s="104" t="s">
         <v>52</v>
       </c>
       <c r="H8" s="105" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I8" s="105" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A9" s="106"/>
       <c r="B9" s="102" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="102" t="s">
         <v>58</v>
       </c>
       <c r="D9" s="103" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" s="103" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F9" s="104" t="s">
         <v>47</v>
       </c>
       <c r="G9" s="104" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H9" s="105" t="s">
         <v>54</v>
       </c>
       <c r="I9" s="105" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" s="93" customFormat="1" customHeight="1" spans="1:16">
@@ -16434,7 +16543,7 @@
       <c r="B10" s="108"/>
       <c r="C10" s="109"/>
       <c r="D10" s="110" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E10" s="111"/>
       <c r="F10" s="112"/>
@@ -16444,7 +16553,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -16452,7 +16561,7 @@
         <v>44</v>
       </c>
       <c r="E11" s="103" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F11" s="104"/>
       <c r="G11" s="104"/>
@@ -16465,19 +16574,19 @@
         <v>51</v>
       </c>
       <c r="C12" s="102" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" s="103" t="s">
         <v>59</v>
       </c>
       <c r="E12" s="103" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F12" s="104" t="s">
         <v>15</v>
       </c>
       <c r="G12" s="104" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" s="105" t="s">
         <v>35</v>
@@ -16489,7 +16598,7 @@
     <row r="13" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A13" s="106"/>
       <c r="B13" s="102" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="102" t="s">
         <v>31</v>
@@ -16504,7 +16613,7 @@
         <v>20</v>
       </c>
       <c r="G13" s="104" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H13" s="105" t="s">
         <v>40</v>
@@ -16516,7 +16625,7 @@
     <row r="14" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A14" s="106"/>
       <c r="B14" s="102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="102" t="s">
         <v>42</v>
@@ -16525,16 +16634,16 @@
         <v>36</v>
       </c>
       <c r="E14" s="103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F14" s="104" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G14" s="104" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H14" s="105" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I14" s="105" t="s">
         <v>30</v>
@@ -16546,7 +16655,7 @@
         <v>24</v>
       </c>
       <c r="C15" s="102" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" s="103" t="s">
         <v>10</v>
@@ -16558,13 +16667,13 @@
         <v>27</v>
       </c>
       <c r="G15" s="104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="105" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="105" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" s="93" customFormat="1" customHeight="1" spans="1:16">
@@ -16573,13 +16682,13 @@
         <v>33</v>
       </c>
       <c r="C16" s="102" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D16" s="103" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="103" t="s">
         <v>97</v>
-      </c>
-      <c r="E16" s="103" t="s">
-        <v>96</v>
       </c>
       <c r="F16" s="104" t="s">
         <v>13</v>
@@ -16588,7 +16697,7 @@
         <v>52</v>
       </c>
       <c r="H16" s="105" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I16" s="105" t="s">
         <v>60</v>
@@ -16597,28 +16706,28 @@
     <row r="17" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A17" s="106"/>
       <c r="B17" s="102" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C17" s="102" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="103" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17" s="103" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F17" s="104" t="s">
         <v>47</v>
       </c>
       <c r="G17" s="104" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17" s="105" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I17" s="105" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" s="93" customFormat="1" customHeight="1" spans="1:9">
@@ -16636,7 +16745,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -16645,7 +16754,7 @@
       </c>
       <c r="E19" s="103"/>
       <c r="F19" s="104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G19" s="104"/>
       <c r="H19" s="105"/>
@@ -16660,16 +16769,16 @@
         <v>35</v>
       </c>
       <c r="D20" s="103" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E20" s="103" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="104" t="s">
         <v>51</v>
       </c>
       <c r="G20" s="104" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" s="105" t="s">
         <v>15</v>
@@ -16681,13 +16790,13 @@
     <row r="21" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A21" s="106"/>
       <c r="B21" s="102" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C21" s="102" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="103" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E21" s="103" t="s">
         <v>31</v>
@@ -16708,13 +16817,13 @@
     <row r="22" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A22" s="106"/>
       <c r="B22" s="102" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" s="102" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="103" t="s">
         <v>72</v>
-      </c>
-      <c r="D22" s="103" t="s">
-        <v>71</v>
       </c>
       <c r="E22" s="103" t="s">
         <v>36</v>
@@ -16726,7 +16835,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="105" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I22" s="105" t="s">
         <v>30</v>
@@ -16738,19 +16847,19 @@
         <v>24</v>
       </c>
       <c r="C23" s="102" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D23" s="103" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E23" s="103" t="s">
         <v>63</v>
       </c>
       <c r="F23" s="104" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G23" s="104" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H23" s="105" t="s">
         <v>18</v>
@@ -16765,16 +16874,16 @@
         <v>60</v>
       </c>
       <c r="C24" s="102" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D24" s="103" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E24" s="103" t="s">
         <v>33</v>
       </c>
       <c r="F24" s="104" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G24" s="104" t="s">
         <v>10</v>
@@ -16789,25 +16898,25 @@
     <row r="25" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A25" s="106"/>
       <c r="B25" s="102" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C25" s="102" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25" s="103" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E25" s="103" t="s">
         <v>58</v>
       </c>
       <c r="F25" s="104" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G25" s="104" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H25" s="105" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I25" s="105" t="s">
         <v>47</v>
@@ -16818,7 +16927,7 @@
       <c r="B26" s="115"/>
       <c r="C26" s="116"/>
       <c r="D26" s="110" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E26" s="111"/>
       <c r="F26" s="112"/>
@@ -16863,13 +16972,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C1" s="84" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -16877,208 +16986,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -17086,118 +17195,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -17205,138 +17314,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="652">
   <si>
     <t>姓名</t>
   </si>
@@ -773,6 +773,12 @@
     <t>语：我觉得他写的这些朋友圈都挺好的。</t>
   </si>
   <si>
+    <t>八上3.5</t>
+  </si>
+  <si>
+    <t>（洪鑫洋睡觉）物理：洪鑫洋来站起来。</t>
+  </si>
+  <si>
     <t>孔祥懿睡觉</t>
   </si>
   <si>
@@ -960,6 +966,21 @@
   </si>
   <si>
     <t>计时6:59:60，8点英语课开始，15点生物课结束</t>
+  </si>
+  <si>
+    <t>过小测</t>
+  </si>
+  <si>
+    <t>八下3.5</t>
+  </si>
+  <si>
+    <t>（物理午托）卓：卧槽有丧尸！（多人蹲在后排准备冲刺）；蒲林豪打开门；廖成羲：“上厕所”师：“憋着”</t>
+  </si>
+  <si>
+    <t>刘老师占课</t>
+  </si>
+  <si>
+    <t>音乐课长期变为做生物任务。当天无任务，改抄英语笔记，大课间时告知回班抄笔记，音乐课改背书（地理）</t>
   </si>
   <si>
     <t>政治课</t>
@@ -3292,14 +3313,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3308,12 +3329,12 @@
       <scheme val="major"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="华文仿宋"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="59">
+  <fills count="57">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3455,18 +3476,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3961,7 +3970,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3985,16 +3994,16 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="29" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="27" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="30" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="28" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="30" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="28" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="31" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -4003,92 +4012,92 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="238">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4665,10 +4674,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4720,7 +4726,7 @@
     <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4748,7 +4754,7 @@
     <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4768,9 +4774,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5141,535 +5144,535 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="227" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="228" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="229" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="230"/>
+    <col min="1" max="1" width="7.59090909090909" style="225" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="226" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="227" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="228"/>
   </cols>
   <sheetData>
-    <row r="1" s="226" customFormat="1" spans="1:10">
-      <c r="A1" s="231" t="s">
+    <row r="1" s="224" customFormat="1" spans="1:10">
+      <c r="A1" s="229" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="232" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="232" t="s">
+      <c r="B1" s="230" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="230" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="232" t="s">
+      <c r="D1" s="230" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="232" t="s">
+      <c r="E1" s="230" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="232" t="s">
+      <c r="F1" s="230" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="232" t="s">
+      <c r="G1" s="230" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
+      <c r="H1" s="231"/>
+      <c r="I1" s="231"/>
+      <c r="J1" s="231"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="234" t="s">
+      <c r="A2" s="232" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="228" t="s">
+      <c r="B2" s="226" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="228" t="s">
+      <c r="C2" s="226" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="234" t="s">
+      <c r="A3" s="232" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="228" t="s">
+      <c r="C3" s="226" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="228" t="s">
+      <c r="D3" s="226" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="234" t="s">
+      <c r="A4" s="232" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="228" t="s">
+      <c r="D4" s="226" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="234" t="s">
+      <c r="A5" s="232" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="228" t="s">
+      <c r="C5" s="226" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="228" t="s">
+      <c r="D5" s="226" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="234" t="s">
+      <c r="A6" s="232" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="228" t="s">
+      <c r="C6" s="226" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="234" t="s">
+      <c r="A7" s="232" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="228" t="s">
+      <c r="B7" s="226" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="228" t="s">
+      <c r="C7" s="226" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="228" t="s">
+      <c r="D7" s="226" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="234" t="s">
+      <c r="A8" s="232" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="228" t="s">
+      <c r="D8" s="226" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="234" t="s">
+      <c r="A9" s="232" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="234" t="s">
+      <c r="A10" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="228" t="s">
+      <c r="B10" s="226" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="234" t="s">
+      <c r="A11" s="232" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="234" t="s">
+      <c r="A12" s="232" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="234" t="s">
+      <c r="A13" s="232" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="228" t="s">
+      <c r="D13" s="226" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="234" t="s">
+      <c r="A14" s="232" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="228" t="s">
+      <c r="B14" s="226" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="234" t="s">
+      <c r="A15" s="232" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="234" t="s">
+      <c r="A16" s="232" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="228" t="s">
+      <c r="C16" s="226" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:5">
-      <c r="A17" s="234" t="s">
+      <c r="A17" s="232" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="228" t="s">
+      <c r="C17" s="226" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="234" t="s">
+      <c r="A18" s="232" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="228" t="s">
+      <c r="D18" s="226" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:5">
-      <c r="A19" s="234" t="s">
+      <c r="A19" s="232" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="228" t="s">
+      <c r="D19" s="226" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:5">
-      <c r="A20" s="234" t="s">
+      <c r="A20" s="232" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="228" t="s">
+      <c r="B20" s="226" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="228" t="s">
+      <c r="C20" s="226" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:5">
-      <c r="A21" s="234" t="s">
+      <c r="A21" s="232" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="228" t="s">
+      <c r="B21" s="226" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="228" t="s">
+      <c r="C21" s="226" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="228" t="s">
+      <c r="D21" s="226" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="234" t="s">
+      <c r="A22" s="232" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:5">
-      <c r="A23" s="234" t="s">
+      <c r="A23" s="232" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="228" t="s">
+      <c r="B23" s="226" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:5">
-      <c r="A24" s="234" t="s">
+      <c r="A24" s="232" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="228" t="s">
+      <c r="B24" s="226" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="228" t="s">
+      <c r="C24" s="226" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="228" t="s">
+      <c r="D24" s="226" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="234" t="s">
+      <c r="A25" s="232" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="234" t="s">
+      <c r="A26" s="232" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="234" t="s">
+      <c r="A27" s="232" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="228" t="s">
+      <c r="B27" s="226" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="228" t="s">
+      <c r="C27" s="226" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:5">
-      <c r="A28" s="234" t="s">
+      <c r="A28" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="228" t="s">
+      <c r="B28" s="226" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="228" t="s">
+      <c r="C28" s="226" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="228" t="s">
+      <c r="D28" s="226" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="228" t="s">
+      <c r="E28" s="226" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="234" t="s">
+      <c r="A29" s="232" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="234" t="s">
+      <c r="A30" s="232" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="228" t="s">
+      <c r="B30" s="226" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="228" t="s">
+      <c r="C30" s="226" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="234" t="s">
+      <c r="A31" s="232" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="234" t="s">
+      <c r="A32" s="232" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="234" t="s">
+      <c r="A33" s="232" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="234" t="s">
+      <c r="A34" s="232" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="234" t="s">
+      <c r="A35" s="232" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="234" t="s">
+      <c r="A36" s="232" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="228" t="s">
+      <c r="B36" s="226" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="234" t="s">
+      <c r="A37" s="232" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="228" t="s">
+      <c r="C37" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="228" t="s">
+      <c r="D37" s="226" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="234" t="s">
+      <c r="A38" s="232" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="228" t="s">
+      <c r="B38" s="226" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="235"/>
-      <c r="D38" s="235"/>
-      <c r="E38" s="235"/>
-      <c r="F38" s="235"/>
-      <c r="G38" s="235"/>
+      <c r="C38" s="233"/>
+      <c r="D38" s="233"/>
+      <c r="E38" s="233"/>
+      <c r="F38" s="233"/>
+      <c r="G38" s="233"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="234" t="s">
+      <c r="A39" s="232" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="228" t="s">
+      <c r="C39" s="226" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="228" t="s">
+      <c r="D39" s="226" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="234" t="s">
+      <c r="A40" s="232" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="228" t="s">
+      <c r="B40" s="226" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="228" t="s">
+      <c r="C40" s="226" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="228" t="s">
+      <c r="D40" s="226" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="234" t="s">
+      <c r="A41" s="232" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="228" t="s">
+      <c r="C41" s="226" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="228" t="s">
+      <c r="D41" s="226" t="s">
         <v>93</v>
       </c>
-      <c r="H41" s="229" t="s">
+      <c r="H41" s="227" t="s">
         <v>94</v>
       </c>
-      <c r="I41" s="229" t="s">
+      <c r="I41" s="227" t="s">
         <v>95</v>
       </c>
-      <c r="J41" s="229" t="s">
+      <c r="J41" s="227" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="234" t="s">
+      <c r="A42" s="232" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="234" t="s">
+      <c r="A43" s="232" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="228" t="s">
+      <c r="B43" s="226" t="s">
         <v>99</v>
       </c>
-      <c r="H43" s="229" t="s">
+      <c r="H43" s="227" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="234" t="s">
+      <c r="A44" s="232" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="228" t="s">
+      <c r="B44" s="226" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="234" t="s">
+      <c r="A45" s="232" t="s">
         <v>103</v>
       </c>
-      <c r="C45" s="228" t="s">
+      <c r="C45" s="226" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="228" t="s">
+      <c r="D45" s="226" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="234" t="s">
+      <c r="A46" s="232" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="234" t="s">
+      <c r="A47" s="232" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="228" t="s">
+      <c r="D47" s="226" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="234" t="s">
+      <c r="A48" s="232" t="s">
         <v>109</v>
       </c>
-      <c r="C48" s="228" t="s">
+      <c r="C48" s="226" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="228" t="s">
+      <c r="D48" s="226" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="234" t="s">
+      <c r="A49" s="232" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="234" t="s">
+      <c r="A50" s="232" t="s">
         <v>113</v>
       </c>
-      <c r="C50" s="228" t="s">
+      <c r="C50" s="226" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="234" t="s">
+      <c r="A51" s="232" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="234" t="s">
+      <c r="A52" s="232" t="s">
         <v>116</v>
       </c>
-      <c r="B52" s="228" t="s">
+      <c r="B52" s="226" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="228" t="s">
+      <c r="C52" s="226" t="s">
         <v>118</v>
       </c>
-      <c r="E52" s="228" t="s">
+      <c r="E52" s="226" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="227" t="s">
+      <c r="A53" s="225" t="s">
         <v>120</v>
       </c>
-      <c r="B53" s="228" t="s">
+      <c r="B53" s="226" t="s">
         <v>121</v>
       </c>
-      <c r="D53" s="235"/>
-      <c r="E53" s="235"/>
-      <c r="F53" s="235"/>
-      <c r="G53" s="235"/>
+      <c r="D53" s="233"/>
+      <c r="E53" s="233"/>
+      <c r="F53" s="233"/>
+      <c r="G53" s="233"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="227" t="s">
+      <c r="A54" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="B54" s="228" t="s">
+      <c r="B54" s="226" t="s">
         <v>123</v>
       </c>
-      <c r="C54" s="228" t="s">
+      <c r="C54" s="226" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="235"/>
-      <c r="E54" s="235"/>
-      <c r="F54" s="235"/>
-      <c r="G54" s="235"/>
+      <c r="D54" s="233"/>
+      <c r="E54" s="233"/>
+      <c r="F54" s="233"/>
+      <c r="G54" s="233"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="227" t="s">
+      <c r="A55" s="225" t="s">
         <v>125</v>
       </c>
-      <c r="B55" s="235"/>
-      <c r="C55" s="235"/>
-      <c r="D55" s="228" t="s">
+      <c r="B55" s="233"/>
+      <c r="C55" s="233"/>
+      <c r="D55" s="226" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="227" t="s">
+      <c r="A56" s="225" t="s">
         <v>127</v>
       </c>
       <c r="B56" s="78" t="s">
         <v>128</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="228" t="s">
+      <c r="D56" s="226" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="227" t="s">
+      <c r="A57" s="225" t="s">
         <v>130</v>
       </c>
       <c r="B57" s="78" t="s">
@@ -5678,76 +5681,76 @@
       <c r="C57" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="D57" s="228" t="s">
+      <c r="D57" s="226" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="227" t="s">
+      <c r="A58" s="225" t="s">
         <v>134</v>
       </c>
-      <c r="B58" s="228" t="s">
+      <c r="B58" s="226" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="235"/>
-      <c r="D58" s="235"/>
-      <c r="E58" s="235"/>
-      <c r="F58" s="235"/>
-      <c r="G58" s="235"/>
+      <c r="C58" s="233"/>
+      <c r="D58" s="233"/>
+      <c r="E58" s="233"/>
+      <c r="F58" s="233"/>
+      <c r="G58" s="233"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="227" t="s">
+      <c r="A59" s="225" t="s">
         <v>136</v>
       </c>
-      <c r="B59" s="235"/>
-      <c r="C59" s="228" t="s">
+      <c r="B59" s="233"/>
+      <c r="C59" s="226" t="s">
         <v>137</v>
       </c>
-      <c r="D59" s="235"/>
-      <c r="E59" s="235"/>
-      <c r="F59" s="235"/>
-      <c r="G59" s="235"/>
+      <c r="D59" s="233"/>
+      <c r="E59" s="233"/>
+      <c r="F59" s="233"/>
+      <c r="G59" s="233"/>
     </row>
     <row r="60" ht="65" spans="1:7">
-      <c r="A60" s="227" t="s">
+      <c r="A60" s="225" t="s">
         <v>138</v>
       </c>
-      <c r="B60" s="235" t="s">
+      <c r="B60" s="233" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="235"/>
-      <c r="D60" s="228" t="s">
+      <c r="C60" s="233"/>
+      <c r="D60" s="226" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="227" t="s">
+      <c r="A61" s="225" t="s">
         <v>141</v>
       </c>
       <c r="B61" s="78" t="s">
         <v>142</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="235"/>
-      <c r="E61" s="235"/>
-      <c r="F61" s="235"/>
-      <c r="G61" s="235"/>
+      <c r="D61" s="233"/>
+      <c r="E61" s="233"/>
+      <c r="F61" s="233"/>
+      <c r="G61" s="233"/>
     </row>
     <row r="62" ht="52" spans="1:7">
-      <c r="A62" s="227" t="s">
+      <c r="A62" s="225" t="s">
         <v>143</v>
       </c>
-      <c r="B62" s="235"/>
-      <c r="C62" s="235"/>
-      <c r="D62" s="228" t="s">
+      <c r="B62" s="233"/>
+      <c r="C62" s="233"/>
+      <c r="D62" s="226" t="s">
         <v>144</v>
       </c>
-      <c r="E62" s="228" t="s">
+      <c r="E62" s="226" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="227" t="s">
+      <c r="A63" s="225" t="s">
         <v>146</v>
       </c>
       <c r="B63" s="78" t="s">
@@ -5756,66 +5759,66 @@
       <c r="C63" s="78" t="s">
         <v>148</v>
       </c>
-      <c r="D63" s="235"/>
-      <c r="E63" s="235"/>
-      <c r="F63" s="235"/>
-      <c r="G63" s="235"/>
+      <c r="D63" s="233"/>
+      <c r="E63" s="233"/>
+      <c r="F63" s="233"/>
+      <c r="G63" s="233"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="227" t="s">
+      <c r="A64" s="225" t="s">
         <v>149</v>
       </c>
-      <c r="B64" s="235"/>
-      <c r="C64" s="235"/>
-      <c r="D64" s="228" t="s">
+      <c r="B64" s="233"/>
+      <c r="C64" s="233"/>
+      <c r="D64" s="226" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="227" t="s">
+      <c r="A65" s="225" t="s">
         <v>151</v>
       </c>
-      <c r="B65" s="236" t="s">
+      <c r="B65" s="234" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="235"/>
-      <c r="D65" s="235"/>
-      <c r="E65" s="235"/>
-      <c r="F65" s="235"/>
-      <c r="G65" s="235"/>
+      <c r="C65" s="233"/>
+      <c r="D65" s="233"/>
+      <c r="E65" s="233"/>
+      <c r="F65" s="233"/>
+      <c r="G65" s="233"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="227" t="s">
+      <c r="A66" s="225" t="s">
         <v>153</v>
       </c>
-      <c r="B66" s="235"/>
-      <c r="C66" s="228" t="s">
+      <c r="B66" s="233"/>
+      <c r="C66" s="226" t="s">
         <v>154</v>
       </c>
-      <c r="D66" s="235"/>
-      <c r="E66" s="235"/>
-      <c r="F66" s="235"/>
-      <c r="G66" s="235"/>
+      <c r="D66" s="233"/>
+      <c r="E66" s="233"/>
+      <c r="F66" s="233"/>
+      <c r="G66" s="233"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="227" t="s">
+      <c r="A67" s="225" t="s">
         <v>155</v>
       </c>
-      <c r="B67" s="235"/>
-      <c r="C67" s="235"/>
+      <c r="B67" s="233"/>
+      <c r="C67" s="233"/>
     </row>
     <row r="68" ht="65" spans="1:7">
-      <c r="A68" s="227" t="s">
+      <c r="A68" s="225" t="s">
         <v>156</v>
       </c>
-      <c r="B68" s="235"/>
-      <c r="C68" s="235"/>
-      <c r="D68" s="228" t="s">
+      <c r="B68" s="233"/>
+      <c r="C68" s="233"/>
+      <c r="D68" s="226" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="227" t="s">
+      <c r="A69" s="225" t="s">
         <v>158</v>
       </c>
       <c r="B69" s="78" t="s">
@@ -5824,89 +5827,89 @@
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="227" t="s">
+      <c r="A70" s="225" t="s">
         <v>160</v>
       </c>
       <c r="B70" s="78" t="s">
         <v>161</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="235"/>
-      <c r="E70" s="235"/>
-      <c r="F70" s="235"/>
-      <c r="G70" s="235"/>
+      <c r="D70" s="233"/>
+      <c r="E70" s="233"/>
+      <c r="F70" s="233"/>
+      <c r="G70" s="233"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="227" t="s">
+      <c r="A71" s="225" t="s">
         <v>162</v>
       </c>
-      <c r="B71" s="235"/>
-      <c r="C71" s="235"/>
+      <c r="B71" s="233"/>
+      <c r="C71" s="233"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="227" t="s">
+      <c r="A72" s="225" t="s">
         <v>163</v>
       </c>
-      <c r="B72" s="228" t="s">
+      <c r="B72" s="226" t="s">
         <v>164</v>
       </c>
-      <c r="C72" s="228" t="s">
+      <c r="C72" s="226" t="s">
         <v>165</v>
       </c>
-      <c r="D72" s="235"/>
-      <c r="E72" s="235"/>
-      <c r="F72" s="235"/>
-      <c r="G72" s="235"/>
+      <c r="D72" s="233"/>
+      <c r="E72" s="233"/>
+      <c r="F72" s="233"/>
+      <c r="G72" s="233"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="227" t="s">
+      <c r="A73" s="225" t="s">
         <v>166</v>
       </c>
-      <c r="B73" s="235"/>
-      <c r="C73" s="228" t="s">
+      <c r="B73" s="233"/>
+      <c r="C73" s="226" t="s">
         <v>167</v>
       </c>
-      <c r="D73" s="235"/>
-      <c r="E73" s="235"/>
-      <c r="F73" s="235"/>
-      <c r="G73" s="235"/>
+      <c r="D73" s="233"/>
+      <c r="E73" s="233"/>
+      <c r="F73" s="233"/>
+      <c r="G73" s="233"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="227" t="s">
+      <c r="A74" s="225" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="227" t="s">
+      <c r="A75" s="225" t="s">
         <v>169</v>
       </c>
-      <c r="D75" s="235"/>
-      <c r="E75" s="235"/>
-      <c r="F75" s="235"/>
-      <c r="G75" s="235"/>
+      <c r="D75" s="233"/>
+      <c r="E75" s="233"/>
+      <c r="F75" s="233"/>
+      <c r="G75" s="233"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="227" t="s">
+      <c r="A76" s="225" t="s">
         <v>170</v>
       </c>
-      <c r="B76" s="235"/>
-      <c r="C76" s="235"/>
-      <c r="D76" s="228" t="s">
+      <c r="B76" s="233"/>
+      <c r="C76" s="233"/>
+      <c r="D76" s="226" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="227" t="s">
+      <c r="A77" s="225" t="s">
         <v>172</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="237" t="s">
+      <c r="A78" s="235" t="s">
         <v>173</v>
       </c>
-      <c r="B78" s="228" t="s">
+      <c r="B78" s="226" t="s">
         <v>174</v>
       </c>
     </row>
@@ -5960,16 +5963,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5983,7 +5986,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -5997,7 +6000,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6011,7 +6014,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6039,7 +6042,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6053,7 +6056,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6067,7 +6070,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6081,7 +6084,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6095,7 +6098,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6121,7 +6124,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6135,7 +6138,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6149,7 +6152,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6175,7 +6178,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6189,7 +6192,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6227,7 +6230,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6241,7 +6244,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6267,7 +6270,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6281,7 +6284,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6295,7 +6298,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6309,7 +6312,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6323,7 +6326,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6337,7 +6340,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6363,7 +6366,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6377,7 +6380,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6391,7 +6394,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6417,7 +6420,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6443,7 +6446,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6457,7 +6460,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6471,10 +6474,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="E38" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6488,7 +6491,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6502,7 +6505,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6516,10 +6519,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="E41" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6545,7 +6548,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6571,7 +6574,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6597,10 +6600,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="E47" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6614,7 +6617,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6640,7 +6643,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6666,7 +6669,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -6699,34 +6702,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6734,10 +6737,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6745,10 +6748,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6756,10 +6759,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6767,23 +6770,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6791,10 +6794,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6802,10 +6805,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6813,10 +6816,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6824,10 +6827,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6835,50 +6838,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6887,24 +6890,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6912,17 +6915,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6931,61 +6934,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>542</v>
+        <v>549</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6993,10 +6996,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7004,10 +7007,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7015,27 +7018,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7043,10 +7046,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7054,10 +7057,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7065,53 +7068,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7122,42 +7125,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7165,64 +7168,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7232,16 +7235,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7250,7 +7253,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7259,42 +7262,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7304,10 +7307,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7315,10 +7318,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7330,18 +7333,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -7449,7 +7452,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7463,7 +7466,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7487,7 +7490,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7500,7 +7503,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7513,7 +7516,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7547,7 +7550,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7593,7 +7596,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7629,7 +7632,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7663,10 +7666,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7678,10 +7681,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7704,7 +7707,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7717,10 +7720,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7754,10 +7757,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7769,10 +7772,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7796,7 +7799,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7863,7 +7866,7 @@
         <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7877,7 +7880,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7889,7 +7892,7 @@
         <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7903,7 +7906,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7915,10 +7918,10 @@
         <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7931,7 +7934,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7954,7 +7957,7 @@
         <v>98</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7978,7 +7981,7 @@
         <v>103</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -8014,7 +8017,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8038,7 +8041,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8061,10 +8064,10 @@
         <v>116</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8100,27 +8103,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8128,13 +8131,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8142,13 +8145,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8156,13 +8159,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8170,13 +8173,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8184,13 +8187,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8198,13 +8201,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8212,7 +8215,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8220,7 +8223,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8228,7 +8231,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8236,7 +8239,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8256,14 +8259,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="220" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="219" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="221"/>
+    <col min="8" max="16384" width="8.72727272727273" style="220"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="222"/>
+      <c r="A1" s="221"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8283,8 +8286,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="219" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="223" t="s">
+    <row r="2" s="218" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="222" t="s">
         <v>175</v>
       </c>
       <c r="B2" s="78"/>
@@ -8297,7 +8300,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="224" t="s">
+      <c r="A3" s="223" t="s">
         <v>177</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8305,7 +8308,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="224" t="s">
+      <c r="A4" s="223" t="s">
         <v>179</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8316,7 +8319,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="224" t="s">
+      <c r="A5" s="223" t="s">
         <v>182</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8327,7 +8330,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="224" t="s">
+      <c r="A6" s="223" t="s">
         <v>185</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8338,7 +8341,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="224" t="s">
+      <c r="A7" s="223" t="s">
         <v>188</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8346,127 +8349,127 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="224"/>
+      <c r="A8" s="223"/>
       <c r="D8" s="66" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="224"/>
+      <c r="A9" s="223"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="224"/>
+      <c r="A10" s="223"/>
       <c r="B10" s="66" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="224"/>
+      <c r="A11" s="223"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="224"/>
+      <c r="A12" s="223"/>
       <c r="B12" s="66" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="224"/>
+      <c r="A13" s="223"/>
       <c r="B13" s="66" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="224"/>
+      <c r="A14" s="223"/>
       <c r="B14" s="66" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="224"/>
+      <c r="A15" s="223"/>
       <c r="B15" s="66" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="224"/>
+      <c r="A16" s="223"/>
       <c r="B16" s="66" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="224"/>
+      <c r="A17" s="223"/>
       <c r="B17" s="66" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="224"/>
+      <c r="A18" s="223"/>
       <c r="B18" s="66" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:2">
-      <c r="A19" s="224"/>
-      <c r="B19" s="225" t="s">
+      <c r="A19" s="223"/>
+      <c r="B19" s="78" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="224"/>
+      <c r="A20" s="223"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="224"/>
+      <c r="A21" s="223"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="224"/>
+      <c r="A22" s="223"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="224"/>
+      <c r="A23" s="223"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="224"/>
+      <c r="A24" s="223"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="224"/>
+      <c r="A25" s="223"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="224"/>
+      <c r="A26" s="223"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="224"/>
+      <c r="A27" s="223"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="224"/>
+      <c r="A28" s="223"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="224"/>
+      <c r="A29" s="223"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="224"/>
+      <c r="A30" s="223"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="224"/>
+      <c r="A31" s="223"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="224"/>
+      <c r="A32" s="223"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="224"/>
+      <c r="A33" s="223"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="224"/>
+      <c r="A34" s="223"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="224"/>
+      <c r="A35" s="223"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="224"/>
+      <c r="A36" s="223"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="224"/>
+      <c r="A37" s="223"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="224"/>
+      <c r="A38" s="223"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8475,7 +8478,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="224"/>
+      <c r="A39" s="223"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8484,40 +8487,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="224"/>
+      <c r="A40" s="223"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="224"/>
+      <c r="A41" s="223"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="224"/>
+      <c r="A42" s="223"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="224"/>
+      <c r="A43" s="223"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="224"/>
+      <c r="A44" s="223"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="224"/>
+      <c r="A45" s="223"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="224"/>
+      <c r="A46" s="223"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="224"/>
+      <c r="A47" s="223"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="224"/>
+      <c r="A48" s="223"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="224"/>
+      <c r="A49" s="223"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="224"/>
+      <c r="A50" s="223"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="224"/>
+      <c r="A51" s="223"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8530,461 +8533,507 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="208" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="208" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="208" customWidth="1"/>
+    <col min="1" max="1" width="24" style="207" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="207" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="207" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="207" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="209" t="s">
+    <row r="1" s="206" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="208" t="s">
         <v>200</v>
       </c>
-      <c r="B1" s="209" t="s">
+      <c r="B1" s="208" t="s">
         <v>201</v>
       </c>
-      <c r="C1" s="209" t="s">
+      <c r="C1" s="208" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="209" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="210" t="s">
+      <c r="B2" s="209" t="s">
         <v>204</v>
       </c>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="209" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="210" t="s">
+      <c r="A3" s="209" t="s">
         <v>206</v>
       </c>
-      <c r="B3" s="210" t="s">
+      <c r="B3" s="209" t="s">
         <v>207</v>
       </c>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="209" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="210" t="s">
+      <c r="A4" s="209" t="s">
         <v>209</v>
       </c>
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="209" t="s">
         <v>207</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="209" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="211" t="s">
+      <c r="A5" s="210" t="s">
         <v>211</v>
       </c>
-      <c r="B5" s="210" t="s">
+      <c r="B5" s="209" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="210" t="s">
+      <c r="C5" s="209" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="212"/>
-      <c r="B6" s="210" t="s">
+      <c r="A6" s="211"/>
+      <c r="B6" s="209" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="210" t="s">
+      <c r="C6" s="209" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="213" t="s">
+      <c r="A7" s="212" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="210" t="s">
+      <c r="B7" s="209" t="s">
         <v>216</v>
       </c>
-      <c r="C7" s="210" t="s">
+      <c r="C7" s="209" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
-      <c r="A8" s="213"/>
-      <c r="B8" s="210" t="s">
+      <c r="A8" s="212"/>
+      <c r="B8" s="209" t="s">
         <v>218</v>
       </c>
-      <c r="C8" s="210" t="s">
+      <c r="C8" s="209" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="213"/>
-      <c r="B9" s="210" t="s">
+      <c r="A9" s="212"/>
+      <c r="B9" s="209" t="s">
         <v>220</v>
       </c>
-      <c r="C9" s="210" t="s">
+      <c r="C9" s="209" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="214"/>
-      <c r="B10" s="210"/>
-      <c r="C10" s="210"/>
+      <c r="A10" s="212"/>
+      <c r="B10" s="209" t="s">
+        <v>222</v>
+      </c>
+      <c r="C10" s="209" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="210" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" s="210" t="s">
-        <v>223</v>
-      </c>
-      <c r="C11" s="210" t="s">
+      <c r="A11" s="212"/>
+      <c r="B11" s="209"/>
+      <c r="C11" s="209"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="212"/>
+      <c r="B12" s="209"/>
+      <c r="C12" s="209"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="212"/>
+      <c r="B13" s="209"/>
+      <c r="C13" s="209"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="213"/>
+      <c r="B14" s="209"/>
+      <c r="C14" s="209"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="209" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="210" t="s">
+      <c r="B15" s="209" t="s">
         <v>225</v>
       </c>
-      <c r="B12" s="210" t="s">
+      <c r="C15" s="209" t="s">
         <v>226</v>
       </c>
-      <c r="C12" s="210" t="s">
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="209" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="210" t="s">
+      <c r="B16" s="209" t="s">
         <v>228</v>
       </c>
-      <c r="B13" s="210" t="s">
+      <c r="C16" s="209" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="215">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="209" t="s">
+        <v>230</v>
+      </c>
+      <c r="B17" s="209" t="s">
+        <v>231</v>
+      </c>
+      <c r="C17" s="214">
         <v>0.440972222222222</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="216" t="s">
+    <row r="18" spans="1:3">
+      <c r="A18" s="215" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="210" t="s">
-        <v>230</v>
-      </c>
-      <c r="C14" s="210" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="217"/>
-      <c r="B15" s="210" t="s">
+      <c r="B18" s="209" t="s">
         <v>232</v>
       </c>
-      <c r="C15" s="210" t="s">
+      <c r="C18" s="209" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="16" ht="56" spans="1:3">
-      <c r="A16" s="217"/>
-      <c r="B16" s="210" t="s">
+    <row r="19" spans="1:3">
+      <c r="A19" s="216"/>
+      <c r="B19" s="209" t="s">
         <v>234</v>
       </c>
-      <c r="C16" s="210" t="s">
+      <c r="C19" s="209" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="217"/>
-      <c r="B17" s="210" t="s">
+    <row r="20" ht="56" spans="1:3">
+      <c r="A20" s="216"/>
+      <c r="B20" s="209" t="s">
         <v>236</v>
       </c>
-      <c r="C17" s="210" t="s">
+      <c r="C20" s="209" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="18" ht="28" spans="1:3">
-      <c r="A18" s="217"/>
-      <c r="B18" s="210" t="s">
+    <row r="21" spans="1:3">
+      <c r="A21" s="216"/>
+      <c r="B21" s="209" t="s">
         <v>238</v>
       </c>
-      <c r="C18" s="210" t="s">
+      <c r="C21" s="209" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="217"/>
-      <c r="B19" s="210"/>
-      <c r="C19" s="210"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="217"/>
-      <c r="B20" s="210"/>
-      <c r="C20" s="210"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="217"/>
-      <c r="B21" s="210"/>
-      <c r="C21" s="210"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="211" t="s">
+    <row r="22" ht="28" spans="1:3">
+      <c r="A22" s="216"/>
+      <c r="B22" s="209" t="s">
         <v>240</v>
       </c>
-      <c r="B22" s="210" t="s">
-        <v>232</v>
-      </c>
-      <c r="C22" s="210" t="s">
+      <c r="C22" s="209" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="212"/>
-      <c r="B23" s="210" t="s">
+      <c r="A23" s="216"/>
+      <c r="B23" s="209"/>
+      <c r="C23" s="209"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="216"/>
+      <c r="B24" s="209"/>
+      <c r="C24" s="209"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="216"/>
+      <c r="B25" s="209"/>
+      <c r="C25" s="209"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="210" t="s">
         <v>242</v>
       </c>
-      <c r="C23" s="210" t="s">
+      <c r="B26" s="209" t="s">
+        <v>234</v>
+      </c>
+      <c r="C26" s="209" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="24" ht="28" spans="1:3">
-      <c r="A24" s="218" t="s">
+    <row r="27" spans="1:3">
+      <c r="A27" s="211"/>
+      <c r="B27" s="209" t="s">
         <v>244</v>
       </c>
-      <c r="B24" s="210" t="s">
+      <c r="C27" s="209" t="s">
         <v>245</v>
       </c>
-      <c r="C24" s="210" t="s">
+    </row>
+    <row r="28" ht="28" spans="1:3">
+      <c r="A28" s="215" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="213"/>
-      <c r="B25" s="210" t="s">
+      <c r="B28" s="209" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="209" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="216"/>
+      <c r="B29" s="209" t="s">
         <v>218</v>
       </c>
-      <c r="C25" s="210" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="213"/>
-      <c r="B26" s="210" t="s">
-        <v>248</v>
-      </c>
-      <c r="C26" s="210" t="s">
+      <c r="C29" s="209" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="213"/>
-      <c r="B27" s="210"/>
-      <c r="C27" s="210"/>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="211" t="s">
+    <row r="30" spans="1:3">
+      <c r="A30" s="216"/>
+      <c r="B30" s="209" t="s">
         <v>250</v>
       </c>
-      <c r="B28" s="210" t="s">
+      <c r="C30" s="209" t="s">
         <v>251</v>
       </c>
-      <c r="C28" s="210" t="s">
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="216"/>
+      <c r="B31" s="209"/>
+      <c r="C31" s="209"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="210" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="212"/>
-      <c r="B29" s="210" t="s">
+      <c r="B32" s="209" t="s">
+        <v>253</v>
+      </c>
+      <c r="C32" s="209" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="211"/>
+      <c r="B33" s="209" t="s">
         <v>216</v>
       </c>
-      <c r="C29" s="210" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="30" ht="28" spans="1:3">
-      <c r="A30" s="218" t="s">
+      <c r="C33" s="209" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="34" ht="28" spans="1:3">
+      <c r="A34" s="215" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="210" t="s">
+      <c r="B34" s="209" t="s">
         <v>216</v>
       </c>
-      <c r="C30" s="210" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="213"/>
-      <c r="B31" s="208" t="s">
-        <v>255</v>
-      </c>
-      <c r="C31" s="208" t="s">
+      <c r="C34" s="209" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="213"/>
-      <c r="B32" s="208" t="s">
-        <v>236</v>
-      </c>
-      <c r="C32" s="208" t="s">
+    <row r="35" spans="1:3">
+      <c r="A35" s="216"/>
+      <c r="B35" s="207" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="33" ht="98" spans="1:3">
-      <c r="A33" s="218" t="s">
+      <c r="C35" s="207" t="s">
         <v>258</v>
       </c>
-      <c r="B33" s="208" t="s">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="216"/>
+      <c r="B36" s="207" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="207" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="37" ht="98" spans="1:3">
+      <c r="A37" s="215" t="s">
+        <v>260</v>
+      </c>
+      <c r="B37" s="207" t="s">
         <v>216</v>
       </c>
-      <c r="C33" s="208" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="34" ht="84" spans="1:3">
-      <c r="A34" s="214"/>
-      <c r="B34" s="208" t="s">
-        <v>260</v>
-      </c>
-      <c r="C34" s="208" t="s">
+      <c r="C37" s="207" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="208" t="s">
+    <row r="38" ht="84" spans="1:3">
+      <c r="A38" s="217"/>
+      <c r="B38" s="207" t="s">
+        <v>262</v>
+      </c>
+      <c r="C38" s="207" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="208" t="s">
+      <c r="B39" s="207" t="s">
+        <v>264</v>
+      </c>
+      <c r="C39" s="207" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="215" t="s">
+        <v>266</v>
+      </c>
+      <c r="B40" s="207" t="s">
+        <v>218</v>
+      </c>
+      <c r="C40" s="207" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="217"/>
+      <c r="B41" s="207" t="s">
         <v>262</v>
       </c>
-      <c r="C35" s="208" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="218" t="s">
-        <v>264</v>
-      </c>
-      <c r="B36" s="208" t="s">
-        <v>218</v>
-      </c>
-      <c r="C36" s="208" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="214"/>
-      <c r="B37" s="208" t="s">
-        <v>260</v>
-      </c>
-      <c r="C37" s="208" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="208" t="s">
+      <c r="C41" s="207" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="207" t="s">
         <v>54</v>
       </c>
-      <c r="B38" s="208" t="s">
+      <c r="B42" s="207" t="s">
         <v>220</v>
       </c>
-      <c r="C38" s="208" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="208" t="s">
-        <v>268</v>
-      </c>
-      <c r="B39" s="208" t="s">
+      <c r="C42" s="207" t="s">
         <v>269</v>
       </c>
-      <c r="C39" s="208" t="s">
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="207" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="208" t="s">
+      <c r="B43" s="207" t="s">
         <v>271</v>
       </c>
-      <c r="B40" s="208" t="s">
+      <c r="C43" s="207" t="s">
         <v>272</v>
       </c>
-      <c r="C40" s="208" t="s">
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="207" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="208" t="s">
+      <c r="B44" s="207" t="s">
+        <v>274</v>
+      </c>
+      <c r="C44" s="207" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="207" t="s">
         <v>10</v>
       </c>
-      <c r="B41" s="208" t="s">
-        <v>260</v>
-      </c>
-      <c r="C41" s="208" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="208" t="s">
-        <v>275</v>
-      </c>
-      <c r="B42" s="208" t="s">
+      <c r="B45" s="207" t="s">
+        <v>262</v>
+      </c>
+      <c r="C45" s="207" t="s">
         <v>276</v>
       </c>
-      <c r="C42" s="208" t="s">
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="207" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="208" t="s">
+      <c r="B46" s="207" t="s">
         <v>278</v>
       </c>
-      <c r="B43" s="208" t="s">
+      <c r="C46" s="207" t="s">
         <v>279</v>
       </c>
-      <c r="C43" s="208" t="s">
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="207" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="208" t="s">
+      <c r="B47" s="207" t="s">
         <v>281</v>
       </c>
-      <c r="B44" s="208" t="s">
-        <v>279</v>
-      </c>
-      <c r="C44" s="208" t="s">
+      <c r="C47" s="207" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="208" t="s">
+    <row r="48" spans="1:3">
+      <c r="A48" s="207" t="s">
         <v>283</v>
       </c>
-      <c r="B45" s="208" t="s">
-        <v>238</v>
-      </c>
-      <c r="C45" s="208" t="s">
+      <c r="B48" s="207" t="s">
+        <v>281</v>
+      </c>
+      <c r="C48" s="207" t="s">
         <v>284</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="207" t="s">
+        <v>285</v>
+      </c>
+      <c r="B49" s="207" t="s">
+        <v>240</v>
+      </c>
+      <c r="C49" s="207" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" ht="28" spans="1:3">
+      <c r="A50" s="207" t="s">
+        <v>287</v>
+      </c>
+      <c r="B50" s="207" t="s">
+        <v>288</v>
+      </c>
+      <c r="C50" s="207" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="51" ht="28" spans="1:3">
+      <c r="A51" s="207" t="s">
+        <v>290</v>
+      </c>
+      <c r="B51" s="207" t="s">
+        <v>288</v>
+      </c>
+      <c r="C51" s="207" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A14:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A7:A14"/>
+    <mergeCell ref="A18:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A40:A41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -9003,45 +9052,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="196"/>
+    <col min="5" max="5" width="8.72727272727273" style="195"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="194" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="197" t="s">
-        <v>285</v>
-      </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="194" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="2" s="195" customFormat="1" spans="1:7">
-      <c r="A2" s="201" t="s">
+    <row r="1" s="193" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="196" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="197"/>
+      <c r="C1" s="197"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="199"/>
+      <c r="F1" s="193" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="2" s="194" customFormat="1" spans="1:7">
+      <c r="A2" s="200" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="202"/>
-      <c r="C2" s="195" t="s">
-        <v>287</v>
-      </c>
-      <c r="D2" s="195" t="s">
-        <v>288</v>
+      <c r="B2" s="201"/>
+      <c r="C2" s="194" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="194" t="s">
+        <v>295</v>
       </c>
       <c r="E2" s="141"/>
-      <c r="F2" s="195" t="s">
+      <c r="F2" s="194" t="s">
         <v>201</v>
       </c>
-      <c r="G2" s="195" t="s">
-        <v>289</v>
+      <c r="G2" s="194" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="203">
+      <c r="A3" s="202">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -9052,14 +9101,14 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="204"/>
+      <c r="A4" s="203"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -9068,14 +9117,14 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="204"/>
+      <c r="A5" s="203"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -9084,14 +9133,14 @@
       </c>
       <c r="D5" s="119"/>
       <c r="F5" s="119" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="G5" s="119" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="204"/>
+      <c r="A6" s="203"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9099,15 +9148,15 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="205" t="s">
-        <v>296</v>
+      <c r="F6" s="204" t="s">
+        <v>303</v>
       </c>
       <c r="G6" s="119" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="204"/>
+      <c r="A7" s="203"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9115,13 +9164,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="206"/>
+      <c r="F7" s="205"/>
       <c r="G7" s="119" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="204"/>
+      <c r="A8" s="203"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9133,7 +9182,7 @@
       <c r="G8" s="119"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="206"/>
+      <c r="A9" s="205"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9145,7 +9194,7 @@
       <c r="G9" s="119"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="205">
+      <c r="A10" s="204">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9159,7 +9208,7 @@
       <c r="G10" s="119"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="204"/>
+      <c r="A11" s="203"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9171,7 +9220,7 @@
       <c r="G11" s="119"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="206"/>
+      <c r="A12" s="205"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9183,7 +9232,7 @@
       <c r="G12" s="119"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="205">
+      <c r="A13" s="204">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9199,7 +9248,7 @@
       <c r="G13" s="119"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="206"/>
+      <c r="A14" s="205"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -9245,10 +9294,10 @@
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" s="175" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C1" s="177"/>
       <c r="D1" s="177"/>
@@ -9268,7 +9317,7 @@
       <c r="R1" s="177"/>
       <c r="S1" s="177"/>
       <c r="T1" s="178" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="U1" s="179"/>
       <c r="V1" s="179"/>
@@ -9286,12 +9335,12 @@
       <c r="AH1" s="179"/>
       <c r="AI1" s="179"/>
       <c r="AJ1" s="178" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="AK1" s="179"/>
       <c r="AL1" s="179"/>
       <c r="AM1" s="178" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="AN1" s="179"/>
       <c r="AO1" s="179"/>
@@ -9310,7 +9359,7 @@
       <c r="BB1" s="179"/>
       <c r="BC1" s="180"/>
       <c r="BD1" s="181" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="BE1" s="182"/>
       <c r="BF1" s="182"/>
@@ -9480,25 +9529,25 @@
       <c r="BB2" s="184"/>
       <c r="BC2" s="184"/>
       <c r="BD2" s="185" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="BE2" s="185" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="BF2" s="185" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="BG2" s="185" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="BH2" s="186" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="BI2" s="186" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="BJ2" s="186" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9781,11 +9830,11 @@
       </c>
       <c r="BH5" s="189">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BI5" s="189">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BJ5" s="189">
         <f t="shared" si="3"/>
@@ -10213,7 +10262,7 @@
       </c>
       <c r="BI9" s="189">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BJ9" s="189">
         <f t="shared" si="3"/>
@@ -10490,11 +10539,11 @@
       </c>
       <c r="BH12" s="189">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BI12" s="189">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BJ12" s="189">
         <f t="shared" si="3"/>
@@ -10601,7 +10650,7 @@
       </c>
       <c r="BI13" s="189">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BJ13" s="189">
         <f t="shared" si="3"/>
@@ -10688,11 +10737,11 @@
       </c>
       <c r="BH14" s="189">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BI14" s="189">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BJ14" s="189">
         <f t="shared" si="3"/>
@@ -10890,11 +10939,11 @@
       </c>
       <c r="BH16" s="189">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BI16" s="189">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BJ16" s="189">
         <f t="shared" si="3"/>
@@ -11319,7 +11368,9 @@
       <c r="AM21" s="120"/>
       <c r="AN21" s="120"/>
       <c r="AO21" s="120"/>
-      <c r="AP21" s="120"/>
+      <c r="AP21" s="120">
+        <v>1</v>
+      </c>
       <c r="AQ21" s="120"/>
       <c r="AR21" s="120"/>
       <c r="AS21" s="120"/>
@@ -11335,11 +11386,11 @@
       <c r="BC21" s="120"/>
       <c r="BD21" s="187">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE21" s="187" cm="1">
         <f t="array" ref="BE21">SUMPRODUCT(--(B21:BC21=INT(B21:BC21)),--(B21:BC21&gt;0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BF21" s="187" cm="1">
         <f t="array" ref="BF21">MAX(FREQUENCY(IF((B21:BC21=INT(B21:BC21))*(B21:BC21&gt;0),COLUMN(B21:BC21)),IF((B21:BC21&lt;&gt;INT(B21:BC21))+(B21:BC21&lt;=0),COLUMN(B21:BC21))))</f>
@@ -11355,7 +11406,7 @@
       </c>
       <c r="BI21" s="189">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BJ21" s="189">
         <f t="shared" si="3"/>
@@ -12293,7 +12344,9 @@
         <v>1</v>
       </c>
       <c r="AO31" s="120"/>
-      <c r="AP31" s="120"/>
+      <c r="AP31" s="120">
+        <v>1</v>
+      </c>
       <c r="AQ31" s="120"/>
       <c r="AR31" s="120"/>
       <c r="AS31" s="120"/>
@@ -12309,11 +12362,11 @@
       <c r="BC31" s="120"/>
       <c r="BD31" s="187">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE31" s="187" cm="1">
         <f t="array" ref="BE31">SUMPRODUCT(--(B31:BC31=INT(B31:BC31)),--(B31:BC31&gt;0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF31" s="187" cm="1">
         <f t="array" ref="BF31">MAX(FREQUENCY(IF((B31:BC31=INT(B31:BC31))*(B31:BC31&gt;0),COLUMN(B31:BC31)),IF((B31:BC31&lt;&gt;INT(B31:BC31))+(B31:BC31&lt;=0),COLUMN(B31:BC31))))</f>
@@ -12329,7 +12382,7 @@
       </c>
       <c r="BI31" s="189">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BJ31" s="189">
         <f t="shared" si="3"/>
@@ -12432,11 +12485,11 @@
       </c>
       <c r="BH32" s="189">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BI32" s="189">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BJ32" s="189">
         <f t="shared" si="3"/>
@@ -12629,60 +12682,60 @@
       <c r="A35" s="191">
         <v>33</v>
       </c>
-      <c r="B35" s="192"/>
-      <c r="C35" s="192"/>
-      <c r="D35" s="192"/>
-      <c r="E35" s="192"/>
-      <c r="F35" s="192"/>
-      <c r="G35" s="192"/>
-      <c r="H35" s="192"/>
-      <c r="I35" s="192"/>
-      <c r="J35" s="192"/>
-      <c r="K35" s="192"/>
-      <c r="L35" s="192"/>
-      <c r="M35" s="192"/>
-      <c r="N35" s="192"/>
-      <c r="O35" s="192"/>
-      <c r="P35" s="192"/>
-      <c r="Q35" s="192"/>
-      <c r="R35" s="192"/>
-      <c r="S35" s="192"/>
-      <c r="T35" s="192"/>
-      <c r="U35" s="192"/>
-      <c r="V35" s="192"/>
-      <c r="W35" s="192"/>
-      <c r="X35" s="192"/>
-      <c r="Y35" s="192"/>
-      <c r="Z35" s="192"/>
-      <c r="AA35" s="192"/>
-      <c r="AB35" s="192"/>
-      <c r="AC35" s="192"/>
-      <c r="AD35" s="192"/>
-      <c r="AE35" s="192"/>
-      <c r="AF35" s="192"/>
-      <c r="AG35" s="192"/>
-      <c r="AH35" s="192"/>
-      <c r="AI35" s="192"/>
-      <c r="AJ35" s="192"/>
-      <c r="AK35" s="192"/>
-      <c r="AL35" s="192"/>
-      <c r="AM35" s="192"/>
-      <c r="AN35" s="192"/>
-      <c r="AO35" s="192"/>
-      <c r="AP35" s="192"/>
-      <c r="AQ35" s="192"/>
-      <c r="AR35" s="192"/>
-      <c r="AS35" s="192"/>
-      <c r="AT35" s="192"/>
-      <c r="AU35" s="192"/>
-      <c r="AV35" s="192"/>
-      <c r="AW35" s="192"/>
-      <c r="AX35" s="192"/>
-      <c r="AY35" s="192"/>
-      <c r="AZ35" s="192"/>
-      <c r="BA35" s="192"/>
-      <c r="BB35" s="192"/>
-      <c r="BC35" s="192"/>
+      <c r="B35" s="191"/>
+      <c r="C35" s="191"/>
+      <c r="D35" s="191"/>
+      <c r="E35" s="191"/>
+      <c r="F35" s="191"/>
+      <c r="G35" s="191"/>
+      <c r="H35" s="191"/>
+      <c r="I35" s="191"/>
+      <c r="J35" s="191"/>
+      <c r="K35" s="191"/>
+      <c r="L35" s="191"/>
+      <c r="M35" s="191"/>
+      <c r="N35" s="191"/>
+      <c r="O35" s="191"/>
+      <c r="P35" s="191"/>
+      <c r="Q35" s="191"/>
+      <c r="R35" s="191"/>
+      <c r="S35" s="191"/>
+      <c r="T35" s="191"/>
+      <c r="U35" s="191"/>
+      <c r="V35" s="191"/>
+      <c r="W35" s="191"/>
+      <c r="X35" s="191"/>
+      <c r="Y35" s="191"/>
+      <c r="Z35" s="191"/>
+      <c r="AA35" s="191"/>
+      <c r="AB35" s="191"/>
+      <c r="AC35" s="191"/>
+      <c r="AD35" s="191"/>
+      <c r="AE35" s="191"/>
+      <c r="AF35" s="191"/>
+      <c r="AG35" s="191"/>
+      <c r="AH35" s="191"/>
+      <c r="AI35" s="191"/>
+      <c r="AJ35" s="191"/>
+      <c r="AK35" s="191"/>
+      <c r="AL35" s="191"/>
+      <c r="AM35" s="191"/>
+      <c r="AN35" s="191"/>
+      <c r="AO35" s="191"/>
+      <c r="AP35" s="191"/>
+      <c r="AQ35" s="191"/>
+      <c r="AR35" s="191"/>
+      <c r="AS35" s="191"/>
+      <c r="AT35" s="191"/>
+      <c r="AU35" s="191"/>
+      <c r="AV35" s="191"/>
+      <c r="AW35" s="191"/>
+      <c r="AX35" s="191"/>
+      <c r="AY35" s="191"/>
+      <c r="AZ35" s="191"/>
+      <c r="BA35" s="191"/>
+      <c r="BB35" s="191"/>
+      <c r="BC35" s="191"/>
       <c r="BD35" s="187">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -13069,15 +13122,15 @@
         <f t="array" ref="BG39">SUMPRODUCT(--(B39:AI39=INT(B39:AI39)),--(B39:AI39&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH39" s="193">
+      <c r="BH39" s="192">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="BI39" s="193">
+      <c r="BI39" s="192">
         <f t="shared" si="2"/>
         <v>41</v>
       </c>
-      <c r="BJ39" s="193">
+      <c r="BJ39" s="192">
         <f t="shared" si="3"/>
         <v>41</v>
       </c>
@@ -15647,9 +15700,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 A9:X9" unlockedFormula="1"/>
-    <ignoredError sqref="A1 C1:S1 U1:AF1 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z28:AF33 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 A3:X4 BD1:BJ2 BI3 AC40:AD40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 A48:X49 Z48:AB48 AE48 A51:AF53 A50:AD50 AF50 X8:AF8 A8:V8 A5:AF7 Z4:AE4 Z41:AE42 BH4:BJ8 BI9:BJ9 Z10:AF10 BH11:BJ39 Z49:AF49 A12:X15 A37:AF37 A39:AF39 A2:AF2 Z3:AF3 A10:X10" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="AA11:AD11 AG1:AI3 AG16:AI23 AG43:AI47 AG49:AI53 AF42:AI42 AH41:AI41 AG5:AI8 AG26:AI39 AG12:AI14 BG41:BG53 AF11:AI11 AF15:AI15 AA15 Z12:AF12 Z13:AA13 Y17:AF18 A19:AF21 Y22:AF22 A24:AI25 Y28:AF33 Y36:AF36 A37:AF37 Y38:AF38 A39:AF39 Y3:Y4 A40:AB40 Y42 A43:AF43 X44:AF44 Y46:AF46 A47:AF47 Y48:Y49 AC48:AD48 AF48:AI48 AE50:AF50 A5:AF7 A8:W8 AF4:AI4 BG4:BG8 BG11:BG39 Y12:Y15" formulaRange="1"/>
+    <ignoredError sqref="Z9:AB9 AD9:AF9 X41 A9:X9" unlockedFormula="1"/>
+    <ignoredError sqref="A10:X10 Z3:AF3 A2:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH11:BJ39 Z10:AF10 BI9:BJ9 BH4:BJ8 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z28:AF33 A28:X33 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11 U1:AF1 C1:S1 A1" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="AA15:AI15 BG41:BG53 AG12:AI14 AG24:AI39 AG5:AI8 AH41:AI41 AF42:AI42 AG49:AI53 AG43:AI47 AG16:AI23 AG1:AI3 Y12:Y15 BG11:BG39 BG4:BG8 AF4:AI4 W8:AF8 A50:AE50 A51:AF53 AF48:AI48 AC48:AD48 Y48:Y49 A45:AF45 A46:AE46 A44:AE44 Y42 W40:AD40 Y3:Y4 A38:AC38 A34:AF35 A36:Y36 A26:AF27 A28:Y33 A24:Y25 A22:AE22 A16:AF16 A17:Y18 AA13:AF13 Z14:AF14 AF11:AI11 A11:AA11 AD11" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15696,21 +15749,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -15718,10 +15771,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -15734,10 +15787,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B4" s="158" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C4" s="158"/>
       <c r="D4" s="158"/>
@@ -15750,7 +15803,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -15770,7 +15823,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -15780,7 +15833,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -15788,10 +15841,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -15806,14 +15859,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -15824,10 +15877,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -15840,23 +15893,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -15864,7 +15917,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -15880,7 +15933,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -15898,17 +15951,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -15916,10 +15969,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -15994,7 +16047,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -16019,10 +16072,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -16034,7 +16087,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -16056,7 +16109,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -16068,7 +16121,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
@@ -16096,7 +16149,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16110,7 +16163,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -16122,7 +16175,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -16134,7 +16187,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>72</v>
@@ -16145,10 +16198,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>91</v>
@@ -16172,10 +16225,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -16186,7 +16239,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -16208,7 +16261,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -16220,7 +16273,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -16232,7 +16285,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>84</v>
@@ -16244,7 +16297,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>87</v>
@@ -16256,7 +16309,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -16268,7 +16321,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -16330,7 +16383,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -16361,7 +16414,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -16553,7 +16606,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -16745,7 +16798,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -16972,10 +17025,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>202</v>
@@ -16986,208 +17039,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -17195,118 +17248,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -17314,138 +17367,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="1"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="653">
   <si>
     <t>姓名</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>孺子、反思（我也老了、相见时难别亦难，东风无力百花残、未来是你们，但现在未必、革命尚未成功）（一旬老人）、哲学（旁观者：学地理要以旁观者视角、水循环：逆水行舟，退到极点就是进）、装（问第几题有问题，体现自己做得快、费马点）、考进班级前10、种地（初二第三次月考、打赌八上期末物理自己和郑永泽考的低者种地）、因错题争论、三江口（小宝）（江怡佳、江允儿、江雨晴）、问问题（秦岭山顶的人）、摘眼镜：睡觉</t>
+  </si>
+  <si>
+    <t>下课和语文老师聊天（自己的事）</t>
   </si>
   <si>
     <t>洪鑫洋名言：
@@ -541,7 +544,7 @@
     <t>物1</t>
   </si>
   <si>
-    <t>读“m”“l”“等于”、写“解”、M来了、给课代表买奶茶、自印卷子、提前进班、写其他课作业、物理课本拿出来、上句话是什么、作业课上完成</t>
+    <t>读“m”“l”“等于”、写“解”、M来了、给课代表买奶茶、自印卷子、提前进班、写其他课作业、物理课本拿出来、上句话是什么、作业课上完成、电话铃“lemon tree”</t>
   </si>
   <si>
     <t>体1</t>
@@ -3306,6 +3309,23 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
@@ -3314,23 +3334,6 @@
     <font>
       <sz val="11"/>
       <name val="华文仿宋"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4097,7 +4100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="234">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4749,12 +4752,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5144,773 +5141,776 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="225" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="226" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="227" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="228"/>
+    <col min="1" max="1" width="7.59090909090909" style="223" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="224" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="225" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="226"/>
   </cols>
   <sheetData>
-    <row r="1" s="224" customFormat="1" spans="1:10">
-      <c r="A1" s="229" t="s">
+    <row r="1" s="222" customFormat="1" spans="1:10">
+      <c r="A1" s="227" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="230" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="230" t="s">
+      <c r="B1" s="228" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="228" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="230" t="s">
+      <c r="D1" s="228" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="230" t="s">
+      <c r="E1" s="228" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="230" t="s">
+      <c r="F1" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="230" t="s">
+      <c r="G1" s="228" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="231"/>
-      <c r="I1" s="231"/>
-      <c r="J1" s="231"/>
+      <c r="H1" s="229"/>
+      <c r="I1" s="229"/>
+      <c r="J1" s="229"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="232" t="s">
+      <c r="A2" s="230" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="226" t="s">
+      <c r="B2" s="224" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="226" t="s">
+      <c r="C2" s="224" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="232" t="s">
+      <c r="A3" s="230" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="226" t="s">
+      <c r="C3" s="224" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="226" t="s">
+      <c r="D3" s="224" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="232" t="s">
+      <c r="A4" s="230" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="226" t="s">
+      <c r="D4" s="224" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="232" t="s">
+      <c r="A5" s="230" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="226" t="s">
+      <c r="C5" s="224" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="226" t="s">
+      <c r="D5" s="224" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="232" t="s">
+      <c r="A6" s="230" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="226" t="s">
+      <c r="C6" s="224" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="232" t="s">
+      <c r="A7" s="230" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="226" t="s">
+      <c r="B7" s="224" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="226" t="s">
+      <c r="C7" s="224" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="226" t="s">
+      <c r="D7" s="224" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="232" t="s">
+      <c r="A8" s="230" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="226" t="s">
+      <c r="D8" s="224" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="232" t="s">
+      <c r="A9" s="230" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="232" t="s">
+      <c r="A10" s="230" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="226" t="s">
+      <c r="B10" s="224" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="232" t="s">
+      <c r="A11" s="230" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="232" t="s">
+      <c r="A12" s="230" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="232" t="s">
+      <c r="A13" s="230" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="226" t="s">
+      <c r="D13" s="224" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="232" t="s">
+      <c r="A14" s="230" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="226" t="s">
+      <c r="B14" s="224" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="232" t="s">
+      <c r="A15" s="230" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="232" t="s">
+      <c r="A16" s="230" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="226" t="s">
+      <c r="C16" s="224" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:5">
-      <c r="A17" s="232" t="s">
+      <c r="A17" s="230" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="226" t="s">
+      <c r="C17" s="224" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="232" t="s">
+      <c r="A18" s="230" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="226" t="s">
+      <c r="D18" s="224" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:5">
-      <c r="A19" s="232" t="s">
+      <c r="A19" s="230" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="226" t="s">
+      <c r="D19" s="224" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:5">
-      <c r="A20" s="232" t="s">
+      <c r="A20" s="230" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="226" t="s">
+      <c r="B20" s="224" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="226" t="s">
+      <c r="C20" s="224" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:5">
-      <c r="A21" s="232" t="s">
+      <c r="A21" s="230" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="226" t="s">
+      <c r="B21" s="224" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="226" t="s">
+      <c r="C21" s="224" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="226" t="s">
+      <c r="D21" s="224" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="232" t="s">
+      <c r="A22" s="230" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:5">
-      <c r="A23" s="232" t="s">
+      <c r="A23" s="230" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="226" t="s">
+      <c r="B23" s="224" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:5">
-      <c r="A24" s="232" t="s">
+      <c r="A24" s="230" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="226" t="s">
+      <c r="B24" s="224" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="226" t="s">
+      <c r="C24" s="224" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="226" t="s">
+      <c r="D24" s="224" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="232" t="s">
+      <c r="A25" s="230" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="232" t="s">
+      <c r="A26" s="230" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="232" t="s">
+      <c r="A27" s="230" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="226" t="s">
+      <c r="B27" s="224" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="226" t="s">
+      <c r="C27" s="224" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:5">
-      <c r="A28" s="232" t="s">
+      <c r="A28" s="230" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="226" t="s">
+      <c r="B28" s="224" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="226" t="s">
+      <c r="C28" s="224" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="226" t="s">
+      <c r="D28" s="224" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="226" t="s">
+      <c r="E28" s="224" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="232" t="s">
+      <c r="A29" s="230" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="232" t="s">
+      <c r="A30" s="230" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="226" t="s">
+      <c r="B30" s="224" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="226" t="s">
+      <c r="C30" s="224" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="232" t="s">
+      <c r="A31" s="230" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="232" t="s">
+      <c r="A32" s="230" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="232" t="s">
+      <c r="A33" s="230" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="232" t="s">
+      <c r="A34" s="230" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="232" t="s">
+      <c r="A35" s="230" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="232" t="s">
+      <c r="A36" s="230" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="226" t="s">
+      <c r="B36" s="224" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="232" t="s">
+      <c r="A37" s="230" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="226" t="s">
+      <c r="C37" s="224" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="226" t="s">
+      <c r="D37" s="224" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="232" t="s">
+      <c r="A38" s="230" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="226" t="s">
+      <c r="B38" s="224" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="233"/>
-      <c r="D38" s="233"/>
-      <c r="E38" s="233"/>
-      <c r="F38" s="233"/>
-      <c r="G38" s="233"/>
+      <c r="C38" s="231"/>
+      <c r="D38" s="231"/>
+      <c r="E38" s="231"/>
+      <c r="F38" s="231"/>
+      <c r="G38" s="231"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="232" t="s">
+      <c r="A39" s="230" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="226" t="s">
+      <c r="C39" s="224" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="226" t="s">
+      <c r="D39" s="224" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="232" t="s">
+      <c r="A40" s="230" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="226" t="s">
+      <c r="B40" s="224" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="226" t="s">
+      <c r="C40" s="224" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="226" t="s">
+      <c r="D40" s="224" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="232" t="s">
+      <c r="A41" s="230" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="226" t="s">
+      <c r="C41" s="224" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="226" t="s">
+      <c r="D41" s="224" t="s">
         <v>93</v>
       </c>
-      <c r="H41" s="227" t="s">
+      <c r="E41" s="224" t="s">
         <v>94</v>
       </c>
-      <c r="I41" s="227" t="s">
+      <c r="H41" s="225" t="s">
         <v>95</v>
       </c>
-      <c r="J41" s="227" t="s">
+      <c r="I41" s="225" t="s">
         <v>96</v>
       </c>
+      <c r="J41" s="225" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="232" t="s">
-        <v>97</v>
+      <c r="A42" s="230" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="232" t="s">
-        <v>98</v>
-      </c>
-      <c r="B43" s="226" t="s">
+      <c r="A43" s="230" t="s">
         <v>99</v>
       </c>
-      <c r="H43" s="227" t="s">
+      <c r="B43" s="224" t="s">
         <v>100</v>
       </c>
+      <c r="H43" s="225" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="232" t="s">
-        <v>101</v>
-      </c>
-      <c r="B44" s="226" t="s">
+      <c r="A44" s="230" t="s">
         <v>102</v>
       </c>
+      <c r="B44" s="224" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="232" t="s">
-        <v>103</v>
-      </c>
-      <c r="C45" s="226" t="s">
+      <c r="A45" s="230" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="226" t="s">
+      <c r="C45" s="224" t="s">
         <v>105</v>
       </c>
+      <c r="D45" s="224" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="232" t="s">
-        <v>106</v>
+      <c r="A46" s="230" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="232" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" s="226" t="s">
+      <c r="A47" s="230" t="s">
         <v>108</v>
       </c>
+      <c r="D47" s="224" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="232" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="226" t="s">
+      <c r="A48" s="230" t="s">
         <v>110</v>
       </c>
-      <c r="D48" s="226" t="s">
+      <c r="C48" s="224" t="s">
         <v>111</v>
       </c>
+      <c r="D48" s="224" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="232" t="s">
-        <v>112</v>
+      <c r="A49" s="230" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="232" t="s">
-        <v>113</v>
-      </c>
-      <c r="C50" s="226" t="s">
+      <c r="A50" s="230" t="s">
         <v>114</v>
       </c>
+      <c r="C50" s="224" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="232" t="s">
-        <v>115</v>
+      <c r="A51" s="230" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="232" t="s">
-        <v>116</v>
-      </c>
-      <c r="B52" s="226" t="s">
+      <c r="A52" s="230" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="226" t="s">
+      <c r="B52" s="224" t="s">
         <v>118</v>
       </c>
-      <c r="E52" s="226" t="s">
+      <c r="C52" s="224" t="s">
         <v>119</v>
       </c>
+      <c r="E52" s="224" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="225" t="s">
-        <v>120</v>
-      </c>
-      <c r="B53" s="226" t="s">
+      <c r="A53" s="223" t="s">
         <v>121</v>
       </c>
-      <c r="D53" s="233"/>
-      <c r="E53" s="233"/>
-      <c r="F53" s="233"/>
-      <c r="G53" s="233"/>
+      <c r="B53" s="224" t="s">
+        <v>122</v>
+      </c>
+      <c r="D53" s="231"/>
+      <c r="E53" s="231"/>
+      <c r="F53" s="231"/>
+      <c r="G53" s="231"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="225" t="s">
-        <v>122</v>
-      </c>
-      <c r="B54" s="226" t="s">
+      <c r="A54" s="223" t="s">
         <v>123</v>
       </c>
-      <c r="C54" s="226" t="s">
+      <c r="B54" s="224" t="s">
         <v>124</v>
       </c>
-      <c r="D54" s="233"/>
-      <c r="E54" s="233"/>
-      <c r="F54" s="233"/>
-      <c r="G54" s="233"/>
+      <c r="C54" s="224" t="s">
+        <v>125</v>
+      </c>
+      <c r="D54" s="231"/>
+      <c r="E54" s="231"/>
+      <c r="F54" s="231"/>
+      <c r="G54" s="231"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="225" t="s">
-        <v>125</v>
-      </c>
-      <c r="B55" s="233"/>
-      <c r="C55" s="233"/>
-      <c r="D55" s="226" t="s">
+      <c r="A55" s="223" t="s">
         <v>126</v>
       </c>
+      <c r="B55" s="231"/>
+      <c r="C55" s="231"/>
+      <c r="D55" s="224" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="225" t="s">
-        <v>127</v>
+      <c r="A56" s="223" t="s">
+        <v>128</v>
       </c>
       <c r="B56" s="78" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="226" t="s">
-        <v>129</v>
+      <c r="D56" s="224" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="225" t="s">
-        <v>130</v>
+      <c r="A57" s="223" t="s">
+        <v>131</v>
       </c>
       <c r="B57" s="78" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C57" s="78" t="s">
-        <v>132</v>
-      </c>
-      <c r="D57" s="226" t="s">
         <v>133</v>
       </c>
+      <c r="D57" s="224" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="225" t="s">
-        <v>134</v>
-      </c>
-      <c r="B58" s="226" t="s">
+      <c r="A58" s="223" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="233"/>
-      <c r="D58" s="233"/>
-      <c r="E58" s="233"/>
-      <c r="F58" s="233"/>
-      <c r="G58" s="233"/>
+      <c r="B58" s="224" t="s">
+        <v>136</v>
+      </c>
+      <c r="C58" s="231"/>
+      <c r="D58" s="231"/>
+      <c r="E58" s="231"/>
+      <c r="F58" s="231"/>
+      <c r="G58" s="231"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="225" t="s">
-        <v>136</v>
-      </c>
-      <c r="B59" s="233"/>
-      <c r="C59" s="226" t="s">
+      <c r="A59" s="223" t="s">
         <v>137</v>
       </c>
-      <c r="D59" s="233"/>
-      <c r="E59" s="233"/>
-      <c r="F59" s="233"/>
-      <c r="G59" s="233"/>
+      <c r="B59" s="231"/>
+      <c r="C59" s="224" t="s">
+        <v>138</v>
+      </c>
+      <c r="D59" s="231"/>
+      <c r="E59" s="231"/>
+      <c r="F59" s="231"/>
+      <c r="G59" s="231"/>
     </row>
     <row r="60" ht="65" spans="1:7">
-      <c r="A60" s="225" t="s">
-        <v>138</v>
-      </c>
-      <c r="B60" s="233" t="s">
+      <c r="A60" s="223" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="233"/>
-      <c r="D60" s="226" t="s">
+      <c r="B60" s="231" t="s">
         <v>140</v>
       </c>
+      <c r="C60" s="231"/>
+      <c r="D60" s="224" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="225" t="s">
-        <v>141</v>
+      <c r="A61" s="223" t="s">
+        <v>142</v>
       </c>
       <c r="B61" s="78" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="233"/>
-      <c r="E61" s="233"/>
-      <c r="F61" s="233"/>
-      <c r="G61" s="233"/>
+      <c r="D61" s="231"/>
+      <c r="E61" s="231"/>
+      <c r="F61" s="231"/>
+      <c r="G61" s="231"/>
     </row>
     <row r="62" ht="52" spans="1:7">
-      <c r="A62" s="225" t="s">
-        <v>143</v>
-      </c>
-      <c r="B62" s="233"/>
-      <c r="C62" s="233"/>
-      <c r="D62" s="226" t="s">
+      <c r="A62" s="223" t="s">
         <v>144</v>
       </c>
-      <c r="E62" s="226" t="s">
+      <c r="B62" s="231"/>
+      <c r="C62" s="231"/>
+      <c r="D62" s="224" t="s">
         <v>145</v>
       </c>
+      <c r="E62" s="224" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="225" t="s">
-        <v>146</v>
+      <c r="A63" s="223" t="s">
+        <v>147</v>
       </c>
       <c r="B63" s="78" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C63" s="78" t="s">
-        <v>148</v>
-      </c>
-      <c r="D63" s="233"/>
-      <c r="E63" s="233"/>
-      <c r="F63" s="233"/>
-      <c r="G63" s="233"/>
+        <v>149</v>
+      </c>
+      <c r="D63" s="231"/>
+      <c r="E63" s="231"/>
+      <c r="F63" s="231"/>
+      <c r="G63" s="231"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="225" t="s">
-        <v>149</v>
-      </c>
-      <c r="B64" s="233"/>
-      <c r="C64" s="233"/>
-      <c r="D64" s="226" t="s">
+      <c r="A64" s="223" t="s">
         <v>150</v>
       </c>
+      <c r="B64" s="231"/>
+      <c r="C64" s="231"/>
+      <c r="D64" s="224" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="225" t="s">
-        <v>151</v>
-      </c>
-      <c r="B65" s="234" t="s">
+      <c r="A65" s="223" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="233"/>
-      <c r="D65" s="233"/>
-      <c r="E65" s="233"/>
-      <c r="F65" s="233"/>
-      <c r="G65" s="233"/>
+      <c r="B65" s="232" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" s="231"/>
+      <c r="D65" s="231"/>
+      <c r="E65" s="231"/>
+      <c r="F65" s="231"/>
+      <c r="G65" s="231"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="225" t="s">
-        <v>153</v>
-      </c>
-      <c r="B66" s="233"/>
-      <c r="C66" s="226" t="s">
+      <c r="A66" s="223" t="s">
         <v>154</v>
       </c>
-      <c r="D66" s="233"/>
-      <c r="E66" s="233"/>
-      <c r="F66" s="233"/>
-      <c r="G66" s="233"/>
+      <c r="B66" s="231"/>
+      <c r="C66" s="224" t="s">
+        <v>155</v>
+      </c>
+      <c r="D66" s="231"/>
+      <c r="E66" s="231"/>
+      <c r="F66" s="231"/>
+      <c r="G66" s="231"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="225" t="s">
-        <v>155</v>
-      </c>
-      <c r="B67" s="233"/>
-      <c r="C67" s="233"/>
-    </row>
-    <row r="68" ht="65" spans="1:7">
-      <c r="A68" s="225" t="s">
+      <c r="A67" s="223" t="s">
         <v>156</v>
       </c>
-      <c r="B68" s="233"/>
-      <c r="C68" s="233"/>
-      <c r="D68" s="226" t="s">
+      <c r="B67" s="231"/>
+      <c r="C67" s="231"/>
+    </row>
+    <row r="68" ht="78" spans="1:7">
+      <c r="A68" s="223" t="s">
         <v>157</v>
       </c>
+      <c r="B68" s="231"/>
+      <c r="C68" s="231"/>
+      <c r="D68" s="224" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="225" t="s">
-        <v>158</v>
+      <c r="A69" s="223" t="s">
+        <v>159</v>
       </c>
       <c r="B69" s="78" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="225" t="s">
-        <v>160</v>
+      <c r="A70" s="223" t="s">
+        <v>161</v>
       </c>
       <c r="B70" s="78" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="233"/>
-      <c r="E70" s="233"/>
-      <c r="F70" s="233"/>
-      <c r="G70" s="233"/>
+      <c r="D70" s="231"/>
+      <c r="E70" s="231"/>
+      <c r="F70" s="231"/>
+      <c r="G70" s="231"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="225" t="s">
-        <v>162</v>
-      </c>
-      <c r="B71" s="233"/>
-      <c r="C71" s="233"/>
+      <c r="A71" s="223" t="s">
+        <v>163</v>
+      </c>
+      <c r="B71" s="231"/>
+      <c r="C71" s="231"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="225" t="s">
-        <v>163</v>
-      </c>
-      <c r="B72" s="226" t="s">
+      <c r="A72" s="223" t="s">
         <v>164</v>
       </c>
-      <c r="C72" s="226" t="s">
+      <c r="B72" s="224" t="s">
         <v>165</v>
       </c>
-      <c r="D72" s="233"/>
-      <c r="E72" s="233"/>
-      <c r="F72" s="233"/>
-      <c r="G72" s="233"/>
+      <c r="C72" s="224" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72" s="231"/>
+      <c r="E72" s="231"/>
+      <c r="F72" s="231"/>
+      <c r="G72" s="231"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="225" t="s">
-        <v>166</v>
-      </c>
-      <c r="B73" s="233"/>
-      <c r="C73" s="226" t="s">
+      <c r="A73" s="223" t="s">
         <v>167</v>
       </c>
-      <c r="D73" s="233"/>
-      <c r="E73" s="233"/>
-      <c r="F73" s="233"/>
-      <c r="G73" s="233"/>
+      <c r="B73" s="231"/>
+      <c r="C73" s="224" t="s">
+        <v>168</v>
+      </c>
+      <c r="D73" s="231"/>
+      <c r="E73" s="231"/>
+      <c r="F73" s="231"/>
+      <c r="G73" s="231"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="225" t="s">
-        <v>168</v>
+      <c r="A74" s="223" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="225" t="s">
-        <v>169</v>
-      </c>
-      <c r="D75" s="233"/>
-      <c r="E75" s="233"/>
-      <c r="F75" s="233"/>
-      <c r="G75" s="233"/>
+      <c r="A75" s="223" t="s">
+        <v>170</v>
+      </c>
+      <c r="D75" s="231"/>
+      <c r="E75" s="231"/>
+      <c r="F75" s="231"/>
+      <c r="G75" s="231"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="225" t="s">
-        <v>170</v>
-      </c>
-      <c r="B76" s="233"/>
-      <c r="C76" s="233"/>
-      <c r="D76" s="226" t="s">
+      <c r="A76" s="223" t="s">
         <v>171</v>
       </c>
+      <c r="B76" s="231"/>
+      <c r="C76" s="231"/>
+      <c r="D76" s="224" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="225" t="s">
-        <v>172</v>
+      <c r="A77" s="223" t="s">
+        <v>173</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="235" t="s">
-        <v>173</v>
-      </c>
-      <c r="B78" s="226" t="s">
+      <c r="A78" s="233" t="s">
         <v>174</v>
+      </c>
+      <c r="B78" s="224" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -5963,16 +5963,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5986,7 +5986,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6000,7 +6000,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6014,7 +6014,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6042,7 +6042,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6056,7 +6056,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6070,7 +6070,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6084,7 +6084,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6098,7 +6098,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6124,7 +6124,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6138,7 +6138,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6152,7 +6152,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6178,7 +6178,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6192,7 +6192,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6230,7 +6230,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6244,7 +6244,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6270,7 +6270,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6284,7 +6284,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6298,7 +6298,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6312,7 +6312,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6326,7 +6326,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6340,7 +6340,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6366,7 +6366,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6380,7 +6380,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6394,7 +6394,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6420,7 +6420,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6446,7 +6446,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6460,7 +6460,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6474,10 +6474,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E38" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6491,7 +6491,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6505,7 +6505,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6519,10 +6519,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E41" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6530,7 +6530,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="72" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C42" s="74">
         <v>20111027</v>
@@ -6542,13 +6542,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C43" s="74">
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6556,7 +6556,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="72" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C44" s="73">
         <v>20120508</v>
@@ -6568,13 +6568,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="72" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="74">
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6582,7 +6582,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="72" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C46" s="74">
         <v>20111205</v>
@@ -6594,16 +6594,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="72" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" s="74">
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E47" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6611,13 +6611,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="72" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="74">
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6625,7 +6625,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="72" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C49" s="74">
         <v>20110902</v>
@@ -6637,13 +6637,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="72" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="74">
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6651,7 +6651,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="72" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51" s="74">
         <v>20120101</v>
@@ -6663,13 +6663,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="72" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C52" s="74">
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -6702,34 +6702,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6737,10 +6737,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6748,10 +6748,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6759,10 +6759,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6770,23 +6770,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6794,10 +6794,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6805,10 +6805,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6816,10 +6816,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6827,10 +6827,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6838,50 +6838,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6890,24 +6890,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6915,17 +6915,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6934,61 +6934,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6996,10 +6996,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7007,10 +7007,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7018,27 +7018,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7046,10 +7046,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7057,10 +7057,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7068,99 +7068,99 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
       <c r="E36" s="52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7168,83 +7168,83 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
       <c r="E45" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7253,7 +7253,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7262,55 +7262,55 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
       <c r="E51" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7318,10 +7318,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7333,18 +7333,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -7452,7 +7452,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7550,7 +7550,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7596,7 +7596,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7666,10 +7666,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7681,10 +7681,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7707,7 +7707,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7720,10 +7720,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7757,10 +7757,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7772,10 +7772,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7866,7 +7866,7 @@
         <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7892,7 +7892,7 @@
         <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7918,10 +7918,10 @@
         <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7934,7 +7934,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7943,7 +7943,7 @@
     </row>
     <row r="42" s="6" customFormat="1" spans="1:7">
       <c r="A42" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="43" s="6" customFormat="1" spans="1:7">
       <c r="A43" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7967,7 +7967,7 @@
     </row>
     <row r="44" s="6" customFormat="1" spans="1:7">
       <c r="A44" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
@@ -7978,10 +7978,10 @@
     </row>
     <row r="45" s="6" customFormat="1" ht="387" spans="1:7">
       <c r="A45" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -7991,7 +7991,7 @@
     </row>
     <row r="46" s="6" customFormat="1" spans="1:7">
       <c r="A46" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
@@ -8002,7 +8002,7 @@
     </row>
     <row r="47" s="6" customFormat="1" spans="1:7">
       <c r="A47" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
@@ -8013,11 +8013,11 @@
     </row>
     <row r="48" s="6" customFormat="1" spans="1:7">
       <c r="A48" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8026,7 +8026,7 @@
     </row>
     <row r="49" s="6" customFormat="1" spans="1:7">
       <c r="A49" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
@@ -8037,11 +8037,11 @@
     </row>
     <row r="50" s="6" customFormat="1" ht="322" spans="1:7">
       <c r="A50" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="51" s="6" customFormat="1" spans="1:7">
       <c r="A51" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
@@ -8061,13 +8061,13 @@
     </row>
     <row r="52" s="6" customFormat="1" ht="224" spans="1:7">
       <c r="A52" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8103,27 +8103,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8131,13 +8131,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8145,13 +8145,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8159,13 +8159,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8173,13 +8173,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8187,13 +8187,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8201,13 +8201,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8223,7 +8223,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8231,7 +8231,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8239,7 +8239,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8259,14 +8259,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="219" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="217" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="220"/>
+    <col min="8" max="16384" width="8.72727272727273" style="218"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="221"/>
+      <c r="A1" s="219"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8286,190 +8286,190 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="218" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="222" t="s">
-        <v>175</v>
+    <row r="2" s="216" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="220" t="s">
+        <v>176</v>
       </c>
       <c r="B2" s="78"/>
       <c r="C2" s="78"/>
       <c r="D2" s="78" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E2" s="78"/>
       <c r="F2" s="78"/>
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="223" t="s">
-        <v>177</v>
+      <c r="A3" s="221" t="s">
+        <v>178</v>
       </c>
       <c r="C3" s="66" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="223" t="s">
-        <v>179</v>
+      <c r="A4" s="221" t="s">
+        <v>180</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="223" t="s">
-        <v>182</v>
+      <c r="A5" s="221" t="s">
+        <v>183</v>
       </c>
       <c r="C5" s="66" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D5" s="66" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="223" t="s">
-        <v>185</v>
+      <c r="A6" s="221" t="s">
+        <v>186</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="223" t="s">
-        <v>188</v>
+      <c r="A7" s="221" t="s">
+        <v>189</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="223"/>
+      <c r="A8" s="221"/>
       <c r="D8" s="66" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="223"/>
+      <c r="A9" s="221"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="223"/>
+      <c r="A10" s="221"/>
       <c r="B10" s="66" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="223"/>
+      <c r="A11" s="221"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="223"/>
+      <c r="A12" s="221"/>
       <c r="B12" s="66" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="223"/>
+      <c r="A13" s="221"/>
       <c r="B13" s="66" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="223"/>
+      <c r="A14" s="221"/>
       <c r="B14" s="66" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="223"/>
+      <c r="A15" s="221"/>
       <c r="B15" s="66" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="223"/>
+      <c r="A16" s="221"/>
       <c r="B16" s="66" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="223"/>
+      <c r="A17" s="221"/>
       <c r="B17" s="66" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="223"/>
+      <c r="A18" s="221"/>
       <c r="B18" s="66" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:2">
-      <c r="A19" s="223"/>
+      <c r="A19" s="221"/>
       <c r="B19" s="78" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="223"/>
+      <c r="A20" s="221"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="223"/>
+      <c r="A21" s="221"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="223"/>
+      <c r="A22" s="221"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="223"/>
+      <c r="A23" s="221"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="223"/>
+      <c r="A24" s="221"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="223"/>
+      <c r="A25" s="221"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="223"/>
+      <c r="A26" s="221"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="223"/>
+      <c r="A27" s="221"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="223"/>
+      <c r="A28" s="221"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="223"/>
+      <c r="A29" s="221"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="223"/>
+      <c r="A30" s="221"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="223"/>
+      <c r="A31" s="221"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="223"/>
+      <c r="A32" s="221"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="223"/>
+      <c r="A33" s="221"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="223"/>
+      <c r="A34" s="221"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="223"/>
+      <c r="A35" s="221"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="223"/>
+      <c r="A36" s="221"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="223"/>
+      <c r="A37" s="221"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="223"/>
+      <c r="A38" s="221"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8478,7 +8478,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="223"/>
+      <c r="A39" s="221"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8487,40 +8487,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="223"/>
+      <c r="A40" s="221"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="223"/>
+      <c r="A41" s="221"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="223"/>
+      <c r="A42" s="221"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="223"/>
+      <c r="A43" s="221"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="223"/>
+      <c r="A44" s="221"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="223"/>
+      <c r="A45" s="221"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="223"/>
+      <c r="A46" s="221"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="223"/>
+      <c r="A47" s="221"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="223"/>
+      <c r="A48" s="221"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="223"/>
+      <c r="A49" s="221"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="223"/>
+      <c r="A50" s="221"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="223"/>
+      <c r="A51" s="221"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8544,66 +8544,66 @@
   <sheetData>
     <row r="1" s="206" customFormat="1" ht="15" spans="1:3">
       <c r="A1" s="208" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B1" s="208" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C1" s="208" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="209" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B2" s="209" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C2" s="209" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="209" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B3" s="209" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C3" s="209" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="209" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B4" s="209" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C4" s="209" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
       <c r="A5" s="210" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B5" s="209" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C5" s="209" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
       <c r="A6" s="211"/>
       <c r="B6" s="209" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C6" s="209" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8611,37 +8611,37 @@
         <v>91</v>
       </c>
       <c r="B7" s="209" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C7" s="209" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
       <c r="A8" s="212"/>
       <c r="B8" s="209" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C8" s="209" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="212"/>
       <c r="B9" s="209" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C9" s="209" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="212"/>
       <c r="B10" s="209" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C10" s="209" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8666,32 +8666,32 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="209" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B15" s="209" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C15" s="209" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="209" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B16" s="209" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C16" s="209" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="209" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B17" s="209" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C17" s="214">
         <v>0.440972222222222</v>
@@ -8702,135 +8702,135 @@
         <v>63</v>
       </c>
       <c r="B18" s="209" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C18" s="209" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="216"/>
+      <c r="A19" s="212"/>
       <c r="B19" s="209" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C19" s="209" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" ht="56" spans="1:3">
-      <c r="A20" s="216"/>
+      <c r="A20" s="212"/>
       <c r="B20" s="209" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" s="209" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="216"/>
+      <c r="A21" s="212"/>
       <c r="B21" s="209" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C21" s="209" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:3">
-      <c r="A22" s="216"/>
+      <c r="A22" s="212"/>
       <c r="B22" s="209" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C22" s="209" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="216"/>
+      <c r="A23" s="212"/>
       <c r="B23" s="209"/>
       <c r="C23" s="209"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="216"/>
+      <c r="A24" s="212"/>
       <c r="B24" s="209"/>
       <c r="C24" s="209"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="216"/>
+      <c r="A25" s="212"/>
       <c r="B25" s="209"/>
       <c r="C25" s="209"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="210" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B26" s="209" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C26" s="209" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="211"/>
       <c r="B27" s="209" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C27" s="209" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:3">
       <c r="A28" s="215" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B28" s="209" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="209" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="216"/>
+      <c r="A29" s="212"/>
       <c r="B29" s="209" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C29" s="209" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="216"/>
+      <c r="A30" s="212"/>
       <c r="B30" s="209" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C30" s="209" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="216"/>
+      <c r="A31" s="212"/>
       <c r="B31" s="209"/>
       <c r="C31" s="209"/>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="210" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B32" s="209" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C32" s="209" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="211"/>
       <c r="B33" s="209" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C33" s="209" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:3">
@@ -8838,48 +8838,48 @@
         <v>47</v>
       </c>
       <c r="B34" s="209" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C34" s="209" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="216"/>
+      <c r="A35" s="212"/>
       <c r="B35" s="207" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C35" s="207" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="216"/>
+      <c r="A36" s="212"/>
       <c r="B36" s="207" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C36" s="207" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" ht="98" spans="1:3">
       <c r="A37" s="215" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B37" s="207" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C37" s="207" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="38" ht="84" spans="1:3">
-      <c r="A38" s="217"/>
+      <c r="A38" s="213"/>
       <c r="B38" s="207" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C38" s="207" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -8887,30 +8887,30 @@
         <v>38</v>
       </c>
       <c r="B39" s="207" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C39" s="207" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="215" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B40" s="207" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C40" s="207" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="217"/>
+      <c r="A41" s="213"/>
       <c r="B41" s="207" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C41" s="207" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -8918,32 +8918,32 @@
         <v>54</v>
       </c>
       <c r="B42" s="207" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C42" s="207" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="207" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B43" s="207" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C43" s="207" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="207" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B44" s="207" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C44" s="207" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -8951,76 +8951,76 @@
         <v>10</v>
       </c>
       <c r="B45" s="207" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C45" s="207" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="207" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B46" s="207" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C46" s="207" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="207" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B47" s="207" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C47" s="207" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="207" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B48" s="207" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C48" s="207" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="207" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B49" s="207" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C49" s="207" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" ht="28" spans="1:3">
       <c r="A50" s="207" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B50" s="207" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C50" s="207" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" ht="28" spans="1:3">
       <c r="A51" s="207" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B51" s="207" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C51" s="207" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -9060,33 +9060,33 @@
   <sheetData>
     <row r="1" s="193" customFormat="1" ht="15" spans="1:7">
       <c r="A1" s="196" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B1" s="197"/>
       <c r="C1" s="197"/>
       <c r="D1" s="198"/>
       <c r="E1" s="199"/>
       <c r="F1" s="193" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" s="194" customFormat="1" spans="1:7">
       <c r="A2" s="200" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B2" s="201"/>
       <c r="C2" s="194" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D2" s="194" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E2" s="141"/>
       <c r="F2" s="194" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G2" s="194" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9101,10 +9101,10 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9117,10 +9117,10 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9133,10 +9133,10 @@
       </c>
       <c r="D5" s="119"/>
       <c r="F5" s="119" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G5" s="119" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9149,10 +9149,10 @@
       </c>
       <c r="D6" s="119"/>
       <c r="F6" s="204" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G6" s="119" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -9166,7 +9166,7 @@
       <c r="D7" s="119"/>
       <c r="F7" s="205"/>
       <c r="G7" s="119" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -9294,10 +9294,10 @@
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" s="175" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C1" s="177"/>
       <c r="D1" s="177"/>
@@ -9317,7 +9317,7 @@
       <c r="R1" s="177"/>
       <c r="S1" s="177"/>
       <c r="T1" s="178" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="U1" s="179"/>
       <c r="V1" s="179"/>
@@ -9335,12 +9335,12 @@
       <c r="AH1" s="179"/>
       <c r="AI1" s="179"/>
       <c r="AJ1" s="178" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AK1" s="179"/>
       <c r="AL1" s="179"/>
       <c r="AM1" s="178" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN1" s="179"/>
       <c r="AO1" s="179"/>
@@ -9359,7 +9359,7 @@
       <c r="BB1" s="179"/>
       <c r="BC1" s="180"/>
       <c r="BD1" s="181" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="BE1" s="182"/>
       <c r="BF1" s="182"/>
@@ -9529,25 +9529,25 @@
       <c r="BB2" s="184"/>
       <c r="BC2" s="184"/>
       <c r="BD2" s="185" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BE2" s="185" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="BF2" s="185" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="BG2" s="185" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="BH2" s="186" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="BI2" s="186" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="BJ2" s="186" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="BI4" s="189">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BJ4" s="189">
         <f t="shared" si="3"/>
@@ -9830,11 +9830,11 @@
       </c>
       <c r="BH5" s="189">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BI5" s="189">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BJ5" s="189">
         <f t="shared" si="3"/>
@@ -10417,7 +10417,9 @@
       <c r="AN11" s="120"/>
       <c r="AO11" s="120"/>
       <c r="AP11" s="120"/>
-      <c r="AQ11" s="120"/>
+      <c r="AQ11" s="120">
+        <v>1</v>
+      </c>
       <c r="AR11" s="120"/>
       <c r="AS11" s="120"/>
       <c r="AT11" s="120"/>
@@ -10432,11 +10434,11 @@
       <c r="BC11" s="120"/>
       <c r="BD11" s="187">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE11" s="187" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(--(B11:BC11=INT(B11:BC11)),--(B11:BC11&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF11" s="187" cm="1">
         <f t="array" ref="BF11">MAX(FREQUENCY(IF((B11:BC11=INT(B11:BC11))*(B11:BC11&gt;0),COLUMN(B11:BC11)),IF((B11:BC11&lt;&gt;INT(B11:BC11))+(B11:BC11&lt;=0),COLUMN(B11:BC11))))</f>
@@ -10448,11 +10450,11 @@
       </c>
       <c r="BH11" s="189">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BI11" s="189">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BJ11" s="189">
         <f t="shared" si="3"/>
@@ -10539,11 +10541,11 @@
       </c>
       <c r="BH12" s="189">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BI12" s="189">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BJ12" s="189">
         <f t="shared" si="3"/>
@@ -10615,7 +10617,9 @@
       </c>
       <c r="AO13" s="120"/>
       <c r="AP13" s="120"/>
-      <c r="AQ13" s="120"/>
+      <c r="AQ13" s="120">
+        <v>1</v>
+      </c>
       <c r="AR13" s="120"/>
       <c r="AS13" s="120"/>
       <c r="AT13" s="120"/>
@@ -10630,11 +10634,11 @@
       <c r="BC13" s="120"/>
       <c r="BD13" s="187">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE13" s="187" cm="1">
         <f t="array" ref="BE13">SUMPRODUCT(--(B13:BC13=INT(B13:BC13)),--(B13:BC13&gt;0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF13" s="187" cm="1">
         <f t="array" ref="BF13">MAX(FREQUENCY(IF((B13:BC13=INT(B13:BC13))*(B13:BC13&gt;0),COLUMN(B13:BC13)),IF((B13:BC13&lt;&gt;INT(B13:BC13))+(B13:BC13&lt;=0),COLUMN(B13:BC13))))</f>
@@ -10646,11 +10650,11 @@
       </c>
       <c r="BH13" s="189">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BI13" s="189">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BJ13" s="189">
         <f t="shared" si="3"/>
@@ -10706,7 +10710,9 @@
       <c r="AN14" s="120"/>
       <c r="AO14" s="120"/>
       <c r="AP14" s="120"/>
-      <c r="AQ14" s="120"/>
+      <c r="AQ14" s="120">
+        <v>1</v>
+      </c>
       <c r="AR14" s="120"/>
       <c r="AS14" s="120"/>
       <c r="AT14" s="120"/>
@@ -10721,11 +10727,11 @@
       <c r="BC14" s="120"/>
       <c r="BD14" s="187">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BE14" s="187" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(--(B14:BC14=INT(B14:BC14)),--(B14:BC14&gt;0))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BF14" s="187" cm="1">
         <f t="array" ref="BF14">MAX(FREQUENCY(IF((B14:BC14=INT(B14:BC14))*(B14:BC14&gt;0),COLUMN(B14:BC14)),IF((B14:BC14&lt;&gt;INT(B14:BC14))+(B14:BC14&lt;=0),COLUMN(B14:BC14))))</f>
@@ -10737,11 +10743,11 @@
       </c>
       <c r="BH14" s="189">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BI14" s="189">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BJ14" s="189">
         <f t="shared" si="3"/>
@@ -10817,7 +10823,9 @@
         <v>1</v>
       </c>
       <c r="AP15" s="120"/>
-      <c r="AQ15" s="120"/>
+      <c r="AQ15" s="120">
+        <v>1</v>
+      </c>
       <c r="AR15" s="120"/>
       <c r="AS15" s="120"/>
       <c r="AT15" s="120"/>
@@ -10832,11 +10840,11 @@
       <c r="BC15" s="120"/>
       <c r="BD15" s="187">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE15" s="187" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF15" s="187" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
@@ -10852,7 +10860,7 @@
       </c>
       <c r="BI15" s="189">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BJ15" s="189">
         <f t="shared" si="3"/>
@@ -10939,11 +10947,11 @@
       </c>
       <c r="BH16" s="189">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BI16" s="189">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BJ16" s="189">
         <f t="shared" si="3"/>
@@ -11511,7 +11519,7 @@
       </c>
       <c r="BH22" s="189">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BI22" s="189">
         <f t="shared" si="2"/>
@@ -12137,7 +12145,9 @@
         <v>1</v>
       </c>
       <c r="AP29" s="120"/>
-      <c r="AQ29" s="120"/>
+      <c r="AQ29" s="120">
+        <v>1</v>
+      </c>
       <c r="AR29" s="120"/>
       <c r="AS29" s="120"/>
       <c r="AT29" s="120"/>
@@ -12152,11 +12162,11 @@
       <c r="BC29" s="120"/>
       <c r="BD29" s="187">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE29" s="187" cm="1">
         <f t="array" ref="BE29">SUMPRODUCT(--(B29:BC29=INT(B29:BC29)),--(B29:BC29&gt;0))</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF29" s="187" cm="1">
         <f t="array" ref="BF29">MAX(FREQUENCY(IF((B29:BC29=INT(B29:BC29))*(B29:BC29&gt;0),COLUMN(B29:BC29)),IF((B29:BC29&lt;&gt;INT(B29:BC29))+(B29:BC29&lt;=0),COLUMN(B29:BC29))))</f>
@@ -12172,7 +12182,7 @@
       </c>
       <c r="BI29" s="189">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BJ29" s="189">
         <f t="shared" si="3"/>
@@ -12273,7 +12283,7 @@
       </c>
       <c r="BI30" s="189">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BJ30" s="189">
         <f t="shared" si="3"/>
@@ -12489,7 +12499,7 @@
       </c>
       <c r="BI32" s="189">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BJ32" s="189">
         <f t="shared" si="3"/>
@@ -12948,7 +12958,7 @@
       </c>
       <c r="BI37" s="189">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BJ37" s="189">
         <f t="shared" si="3"/>
@@ -13263,7 +13273,7 @@
       </c>
       <c r="BI40" s="189">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ40" s="189">
         <f t="shared" si="3"/>
@@ -13374,7 +13384,7 @@
       </c>
       <c r="BI41" s="189">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BJ41" s="189">
         <f t="shared" si="3"/>
@@ -13882,7 +13892,9 @@
       </c>
       <c r="AO46" s="120"/>
       <c r="AP46" s="120"/>
-      <c r="AQ46" s="120"/>
+      <c r="AQ46" s="120">
+        <v>1</v>
+      </c>
       <c r="AR46" s="120"/>
       <c r="AS46" s="120"/>
       <c r="AT46" s="120"/>
@@ -13897,11 +13909,11 @@
       <c r="BC46" s="120"/>
       <c r="BD46" s="187">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BE46" s="187" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BF46" s="187" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
@@ -14115,7 +14127,7 @@
       </c>
       <c r="BI48" s="189">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BJ48" s="189">
         <f t="shared" si="3"/>
@@ -15700,9 +15712,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="Z9:AB9 AD9:AF9 X41 A9:X9" unlockedFormula="1"/>
-    <ignoredError sqref="A10:X10 Z3:AF3 A2:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH11:BJ39 Z10:AF10 BI9:BJ9 BH4:BJ8 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z28:AF33 A28:X33 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11 U1:AF1 C1:S1 A1" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="AA15:AI15 BG41:BG53 AG12:AI14 AG24:AI39 AG5:AI8 AH41:AI41 AF42:AI42 AG49:AI53 AG43:AI47 AG16:AI23 AG1:AI3 Y12:Y15 BG11:BG39 BG4:BG8 AF4:AI4 W8:AF8 A50:AE50 A51:AF53 AF48:AI48 AC48:AD48 Y48:Y49 A45:AF45 A46:AE46 A44:AE44 Y42 W40:AD40 Y3:Y4 A38:AC38 A34:AF35 A36:Y36 A26:AF27 A28:Y33 A24:Y25 A22:AE22 A16:AF16 A17:Y18 AA13:AF13 Z14:AF14 AF11:AI11 A11:AA11 AD11" formulaRange="1"/>
+    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 A9:X9" unlockedFormula="1"/>
+    <ignoredError sqref="A1 C1:S1 U1:AF1 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z28:AF33 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 A3:X4 BD1:BJ2 BI3 AC40:AD40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 A48:X49 Z48:AB48 AE48 A51:AF53 A50:AD50 AF50 X8:AF8 A8:V8 A5:AF7 Z4:AE4 Z41:AE42 BH4:BJ8 BI9:BJ9 Z10:AF10 BH11:BJ39 Z49:AF49 A12:X15 A37:AF37 A39:AF39 A2:AF2 Z3:AF3 A10:X10" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="AD11:AI11 AC48:AI48 AG1:AI3 AG43:AI47 AG49:AI53 AF42:AI42 AH41:AI41 AG5:AI8 AG16:AI39 AG12:AI14 BG41:BG53 AA11 Z15:AA15 AF15:AI15 Z12:AF12 Z13:AA13 Y17:AF18 A19:AF21 Y22:AF22 A23:AF23 Y24:AF25 Y28:AF33 Y36:AF36 A37:AF37 Y38:AF38 A39:AF39 Y3:Y4 A40:AB40 Y42 A43:AF43 X44:AF44 Y46:AF46 A47:AF47 Y48:Y49 AE50:AF50 A5:AF7 A8:W8 AF4:AI4 BG4:BG8 BG11:BG39 Y12:Y15" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15749,21 +15761,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="148" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B2" s="152" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C2" s="153" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D2" s="154"/>
       <c r="E2" s="152" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F2" s="152"/>
       <c r="G2" s="155" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H2" s="147"/>
       <c r="I2" s="147"/>
@@ -15771,10 +15783,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="148" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B3" s="157" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C3" s="157"/>
       <c r="D3" s="157"/>
@@ -15787,10 +15799,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="148" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B4" s="158" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C4" s="158"/>
       <c r="D4" s="158"/>
@@ -15803,7 +15815,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="148" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B5" s="159">
         <v>1</v>
@@ -15823,7 +15835,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="148" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B6" s="161">
         <v>1</v>
@@ -15833,7 +15845,7 @@
       <c r="E6" s="161"/>
       <c r="F6" s="161"/>
       <c r="G6" s="162" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H6" s="147"/>
       <c r="I6" s="147"/>
@@ -15841,10 +15853,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="148" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B7" s="163" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C7" s="163"/>
       <c r="D7" s="163"/>
@@ -15859,14 +15871,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="148" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B8" s="165">
         <v>1</v>
       </c>
       <c r="C8" s="165"/>
       <c r="D8" s="166" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E8" s="166"/>
       <c r="F8" s="166"/>
@@ -15877,10 +15889,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="148" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B9" s="152" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C9" s="152"/>
       <c r="D9" s="152"/>
@@ -15893,23 +15905,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="148" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B10" s="157">
         <v>1</v>
       </c>
       <c r="C10" s="157"/>
       <c r="D10" s="167" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E10" s="157">
         <v>1</v>
       </c>
       <c r="F10" s="167" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G10" s="147" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H10" s="147"/>
       <c r="I10" s="147"/>
@@ -15917,7 +15929,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="148" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B11" s="158">
         <v>1</v>
@@ -15933,7 +15945,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="148" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B12" s="159">
         <v>1</v>
@@ -15951,17 +15963,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="148" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="168" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -15969,10 +15981,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="148" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B14" s="170" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C14" s="170"/>
       <c r="D14" s="170"/>
@@ -16047,7 +16059,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -16072,10 +16084,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -16087,7 +16099,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -16109,7 +16121,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -16121,13 +16133,13 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="131" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E6" s="132"/>
       <c r="F6" s="133"/>
@@ -16149,7 +16161,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16163,7 +16175,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -16175,7 +16187,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -16187,7 +16199,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>72</v>
@@ -16198,10 +16210,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>91</v>
@@ -16225,10 +16237,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="141"/>
       <c r="B14" s="136" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D14" s="142"/>
       <c r="E14" s="138"/>
@@ -16239,7 +16251,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="141"/>
       <c r="B15" s="136" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -16261,7 +16273,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="141"/>
       <c r="B17" s="136" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -16273,7 +16285,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="141"/>
       <c r="B18" s="136" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -16285,7 +16297,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="141"/>
       <c r="B19" s="136" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>84</v>
@@ -16297,7 +16309,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="141"/>
       <c r="B20" s="136" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>87</v>
@@ -16309,7 +16321,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="141"/>
       <c r="B21" s="136" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C21" s="143"/>
       <c r="D21" s="144"/>
@@ -16321,7 +16333,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="145"/>
       <c r="B22" s="136" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C22" s="143"/>
       <c r="D22" s="146"/>
@@ -16383,7 +16395,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -16414,7 +16426,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -16422,7 +16434,7 @@
         <v>44</v>
       </c>
       <c r="E3" s="103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F3" s="104"/>
       <c r="G3" s="104"/>
@@ -16450,7 +16462,7 @@
         <v>79</v>
       </c>
       <c r="H4" s="105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I4" s="105" t="s">
         <v>91</v>
@@ -16465,7 +16477,7 @@
         <v>38</v>
       </c>
       <c r="D5" s="103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E5" s="103" t="s">
         <v>82</v>
@@ -16507,7 +16519,7 @@
         <v>36</v>
       </c>
       <c r="I6" s="105" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" s="93" customFormat="1" customHeight="1" spans="1:16">
@@ -16528,7 +16540,7 @@
         <v>87</v>
       </c>
       <c r="G7" s="104" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H7" s="105" t="s">
         <v>63</v>
@@ -16540,7 +16552,7 @@
     <row r="8" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A8" s="106"/>
       <c r="B8" s="102" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="102" t="s">
         <v>33</v>
@@ -16552,7 +16564,7 @@
         <v>13</v>
       </c>
       <c r="F8" s="104" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G8" s="104" t="s">
         <v>52</v>
@@ -16561,13 +16573,13 @@
         <v>77</v>
       </c>
       <c r="I8" s="105" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A9" s="106"/>
       <c r="B9" s="102" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="102" t="s">
         <v>58</v>
@@ -16576,13 +16588,13 @@
         <v>69</v>
       </c>
       <c r="E9" s="103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F9" s="104" t="s">
         <v>47</v>
       </c>
       <c r="G9" s="104" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H9" s="105" t="s">
         <v>54</v>
@@ -16596,7 +16608,7 @@
       <c r="B10" s="108"/>
       <c r="C10" s="109"/>
       <c r="D10" s="110" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E10" s="111"/>
       <c r="F10" s="112"/>
@@ -16606,7 +16618,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -16614,7 +16626,7 @@
         <v>44</v>
       </c>
       <c r="E11" s="103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F11" s="104"/>
       <c r="G11" s="104"/>
@@ -16633,7 +16645,7 @@
         <v>59</v>
       </c>
       <c r="E12" s="103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F12" s="104" t="s">
         <v>15</v>
@@ -16687,10 +16699,10 @@
         <v>36</v>
       </c>
       <c r="E14" s="103" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F14" s="104" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G14" s="104" t="s">
         <v>74</v>
@@ -16735,13 +16747,13 @@
         <v>33</v>
       </c>
       <c r="C16" s="102" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D16" s="103" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="103" t="s">
         <v>98</v>
-      </c>
-      <c r="E16" s="103" t="s">
-        <v>97</v>
       </c>
       <c r="F16" s="104" t="s">
         <v>13</v>
@@ -16759,16 +16771,16 @@
     <row r="17" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A17" s="106"/>
       <c r="B17" s="102" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C17" s="102" t="s">
         <v>58</v>
       </c>
       <c r="D17" s="103" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E17" s="103" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F17" s="104" t="s">
         <v>47</v>
@@ -16777,7 +16789,7 @@
         <v>69</v>
       </c>
       <c r="H17" s="105" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I17" s="105" t="s">
         <v>84</v>
@@ -16798,7 +16810,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -16807,7 +16819,7 @@
       </c>
       <c r="E19" s="103"/>
       <c r="F19" s="104" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G19" s="104"/>
       <c r="H19" s="105"/>
@@ -16822,7 +16834,7 @@
         <v>35</v>
       </c>
       <c r="D20" s="103" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E20" s="103" t="s">
         <v>79</v>
@@ -16909,10 +16921,10 @@
         <v>63</v>
       </c>
       <c r="F23" s="104" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G23" s="104" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H23" s="105" t="s">
         <v>18</v>
@@ -16927,7 +16939,7 @@
         <v>60</v>
       </c>
       <c r="C24" s="102" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" s="103" t="s">
         <v>75</v>
@@ -16936,7 +16948,7 @@
         <v>33</v>
       </c>
       <c r="F24" s="104" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G24" s="104" t="s">
         <v>10</v>
@@ -16951,7 +16963,7 @@
     <row r="25" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A25" s="106"/>
       <c r="B25" s="102" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C25" s="102" t="s">
         <v>84</v>
@@ -16966,10 +16978,10 @@
         <v>75</v>
       </c>
       <c r="G25" s="104" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H25" s="105" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I25" s="105" t="s">
         <v>47</v>
@@ -16980,7 +16992,7 @@
       <c r="B26" s="115"/>
       <c r="C26" s="116"/>
       <c r="D26" s="110" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E26" s="111"/>
       <c r="F26" s="112"/>
@@ -17025,13 +17037,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1" s="84" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -17039,208 +17051,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -17248,118 +17260,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -17367,138 +17379,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -3321,11 +3321,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
@@ -3334,6 +3329,11 @@
     <font>
       <sz val="11"/>
       <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="BJ3" s="189">
         <f t="shared" ref="BJ3:BJ53" si="3">RANK(BF3,BF$3:BF$53,0)</f>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:62">
@@ -9709,8 +9709,12 @@
       <c r="AO4" s="120"/>
       <c r="AP4" s="120"/>
       <c r="AQ4" s="120"/>
-      <c r="AR4" s="120"/>
-      <c r="AS4" s="120"/>
+      <c r="AR4" s="120">
+        <v>1</v>
+      </c>
+      <c r="AS4" s="120">
+        <v>1</v>
+      </c>
       <c r="AT4" s="120"/>
       <c r="AU4" s="120"/>
       <c r="AV4" s="120"/>
@@ -9723,11 +9727,11 @@
       <c r="BC4" s="120"/>
       <c r="BD4" s="187">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE4" s="187" cm="1">
         <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF4" s="187" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
@@ -9739,7 +9743,7 @@
       </c>
       <c r="BH4" s="189">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI4" s="189">
         <f t="shared" si="2"/>
@@ -9838,7 +9842,7 @@
       </c>
       <c r="BJ5" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:62">
@@ -9895,8 +9899,12 @@
       </c>
       <c r="AP6" s="120"/>
       <c r="AQ6" s="120"/>
-      <c r="AR6" s="120"/>
-      <c r="AS6" s="120"/>
+      <c r="AR6" s="120">
+        <v>1</v>
+      </c>
+      <c r="AS6" s="120">
+        <v>1</v>
+      </c>
       <c r="AT6" s="120"/>
       <c r="AU6" s="120"/>
       <c r="AV6" s="120"/>
@@ -9909,15 +9917,15 @@
       <c r="BC6" s="120"/>
       <c r="BD6" s="187">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BE6" s="187" cm="1">
         <f t="array" ref="BE6">SUMPRODUCT(--(B6:BC6=INT(B6:BC6)),--(B6:BC6&gt;0))</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BF6" s="187" cm="1">
         <f t="array" ref="BF6">MAX(FREQUENCY(IF((B6:BC6=INT(B6:BC6))*(B6:BC6&gt;0),COLUMN(B6:BC6)),IF((B6:BC6&lt;&gt;INT(B6:BC6))+(B6:BC6&lt;=0),COLUMN(B6:BC6))))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG6" s="188" cm="1">
         <f t="array" ref="BG6">SUMPRODUCT(--(B6:AI6=INT(B6:AI6)),--(B6:AI6&gt;0))/34*100%</f>
@@ -9925,15 +9933,15 @@
       </c>
       <c r="BH6" s="189">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BI6" s="189">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BJ6" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:62">
@@ -10018,7 +10026,7 @@
       </c>
       <c r="BH7" s="189">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BI7" s="189">
         <f t="shared" si="2"/>
@@ -10026,7 +10034,7 @@
       </c>
       <c r="BJ7" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:62">
@@ -10115,8 +10123,12 @@
       <c r="AO8" s="120"/>
       <c r="AP8" s="120"/>
       <c r="AQ8" s="120"/>
-      <c r="AR8" s="120"/>
-      <c r="AS8" s="120"/>
+      <c r="AR8" s="120">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="120">
+        <v>1</v>
+      </c>
       <c r="AT8" s="120"/>
       <c r="AU8" s="120"/>
       <c r="AV8" s="120"/>
@@ -10129,11 +10141,11 @@
       <c r="BC8" s="120"/>
       <c r="BD8" s="187">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE8" s="187" cm="1">
         <f t="array" ref="BE8">SUMPRODUCT(--(B8:BC8=INT(B8:BC8)),--(B8:BC8&gt;0))</f>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BF8" s="187" cm="1">
         <f t="array" ref="BF8">MAX(FREQUENCY(IF((B8:BC8=INT(B8:BC8))*(B8:BC8&gt;0),COLUMN(B8:BC8)),IF((B8:BC8&lt;&gt;INT(B8:BC8))+(B8:BC8&lt;=0),COLUMN(B8:BC8))))</f>
@@ -10228,8 +10240,12 @@
       </c>
       <c r="AP9" s="120"/>
       <c r="AQ9" s="120"/>
-      <c r="AR9" s="120"/>
-      <c r="AS9" s="120"/>
+      <c r="AR9" s="120">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="120">
+        <v>1</v>
+      </c>
       <c r="AT9" s="120"/>
       <c r="AU9" s="120"/>
       <c r="AV9" s="120"/>
@@ -10242,11 +10258,11 @@
       <c r="BC9" s="120"/>
       <c r="BD9" s="187">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE9" s="187" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BF9" s="187" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
@@ -10258,7 +10274,7 @@
       </c>
       <c r="BH9" s="189">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI9" s="189">
         <f t="shared" si="2"/>
@@ -10355,7 +10371,7 @@
       </c>
       <c r="BJ10" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:62">
@@ -10421,7 +10437,9 @@
         <v>1</v>
       </c>
       <c r="AR11" s="120"/>
-      <c r="AS11" s="120"/>
+      <c r="AS11" s="120">
+        <v>1</v>
+      </c>
       <c r="AT11" s="120"/>
       <c r="AU11" s="120"/>
       <c r="AV11" s="120"/>
@@ -10434,11 +10452,11 @@
       <c r="BC11" s="120"/>
       <c r="BD11" s="187">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE11" s="187" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(--(B11:BC11=INT(B11:BC11)),--(B11:BC11&gt;0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF11" s="187" cm="1">
         <f t="array" ref="BF11">MAX(FREQUENCY(IF((B11:BC11=INT(B11:BC11))*(B11:BC11&gt;0),COLUMN(B11:BC11)),IF((B11:BC11&lt;&gt;INT(B11:BC11))+(B11:BC11&lt;=0),COLUMN(B11:BC11))))</f>
@@ -10458,7 +10476,7 @@
       </c>
       <c r="BJ11" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:62">
@@ -10549,7 +10567,7 @@
       </c>
       <c r="BJ12" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:62">
@@ -10650,15 +10668,15 @@
       </c>
       <c r="BH13" s="189">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BI13" s="189">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BJ13" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:62">
@@ -10751,7 +10769,7 @@
       </c>
       <c r="BJ14" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:62">
@@ -10826,8 +10844,12 @@
       <c r="AQ15" s="120">
         <v>1</v>
       </c>
-      <c r="AR15" s="120"/>
-      <c r="AS15" s="120"/>
+      <c r="AR15" s="120">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="120">
+        <v>1</v>
+      </c>
       <c r="AT15" s="120"/>
       <c r="AU15" s="120"/>
       <c r="AV15" s="120"/>
@@ -10840,11 +10862,11 @@
       <c r="BC15" s="120"/>
       <c r="BD15" s="187">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BE15" s="187" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BF15" s="187" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
@@ -10955,7 +10977,7 @@
       </c>
       <c r="BJ16" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:62">
@@ -11042,15 +11064,15 @@
       </c>
       <c r="BH17" s="189">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BI17" s="189">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BJ17" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:62">
@@ -11139,7 +11161,7 @@
       </c>
       <c r="BJ18" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:62">
@@ -11228,15 +11250,15 @@
       </c>
       <c r="BH19" s="189">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BI19" s="189">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BJ19" s="189">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:62">
@@ -11325,7 +11347,7 @@
       </c>
       <c r="BJ20" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:62">
@@ -11418,7 +11440,7 @@
       </c>
       <c r="BJ21" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:62">
@@ -11489,7 +11511,9 @@
       <c r="AO22" s="120"/>
       <c r="AP22" s="120"/>
       <c r="AQ22" s="120"/>
-      <c r="AR22" s="120"/>
+      <c r="AR22" s="120">
+        <v>1</v>
+      </c>
       <c r="AS22" s="120"/>
       <c r="AT22" s="120"/>
       <c r="AU22" s="120"/>
@@ -11503,11 +11527,11 @@
       <c r="BC22" s="120"/>
       <c r="BD22" s="187">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE22" s="187" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF22" s="187" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
@@ -11709,11 +11733,11 @@
       </c>
       <c r="BH24" s="189">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BI24" s="189">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BJ24" s="189">
         <f t="shared" si="3"/>
@@ -11806,7 +11830,7 @@
       </c>
       <c r="BJ25" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:62">
@@ -12047,7 +12071,9 @@
       <c r="AO28" s="120"/>
       <c r="AP28" s="120"/>
       <c r="AQ28" s="120"/>
-      <c r="AR28" s="120"/>
+      <c r="AR28" s="120">
+        <v>1</v>
+      </c>
       <c r="AS28" s="120"/>
       <c r="AT28" s="120"/>
       <c r="AU28" s="120"/>
@@ -12061,11 +12087,11 @@
       <c r="BC28" s="120"/>
       <c r="BD28" s="187">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE28" s="187" cm="1">
         <f t="array" ref="BE28">SUMPRODUCT(--(B28:BC28=INT(B28:BC28)),--(B28:BC28&gt;0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF28" s="187" cm="1">
         <f t="array" ref="BF28">MAX(FREQUENCY(IF((B28:BC28=INT(B28:BC28))*(B28:BC28&gt;0),COLUMN(B28:BC28)),IF((B28:BC28&lt;&gt;INT(B28:BC28))+(B28:BC28&lt;=0),COLUMN(B28:BC28))))</f>
@@ -12085,7 +12111,7 @@
       </c>
       <c r="BJ28" s="189">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:62">
@@ -12148,8 +12174,12 @@
       <c r="AQ29" s="120">
         <v>1</v>
       </c>
-      <c r="AR29" s="120"/>
-      <c r="AS29" s="120"/>
+      <c r="AR29" s="120">
+        <v>1</v>
+      </c>
+      <c r="AS29" s="120">
+        <v>1</v>
+      </c>
       <c r="AT29" s="120"/>
       <c r="AU29" s="120"/>
       <c r="AV29" s="120"/>
@@ -12162,15 +12192,15 @@
       <c r="BC29" s="120"/>
       <c r="BD29" s="187">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BE29" s="187" cm="1">
         <f t="array" ref="BE29">SUMPRODUCT(--(B29:BC29=INT(B29:BC29)),--(B29:BC29&gt;0))</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF29" s="187" cm="1">
         <f t="array" ref="BF29">MAX(FREQUENCY(IF((B29:BC29=INT(B29:BC29))*(B29:BC29&gt;0),COLUMN(B29:BC29)),IF((B29:BC29&lt;&gt;INT(B29:BC29))+(B29:BC29&lt;=0),COLUMN(B29:BC29))))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG29" s="188" cm="1">
         <f t="array" ref="BG29">SUMPRODUCT(--(B29:AI29=INT(B29:AI29)),--(B29:AI29&gt;0))/34*100%</f>
@@ -12178,15 +12208,15 @@
       </c>
       <c r="BH29" s="189">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BI29" s="189">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BJ29" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:62">
@@ -12279,11 +12309,11 @@
       </c>
       <c r="BH30" s="189">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BI30" s="189">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BJ30" s="189">
         <f t="shared" si="3"/>
@@ -12392,11 +12422,11 @@
       </c>
       <c r="BI31" s="189">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BJ31" s="189">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:62">
@@ -12465,7 +12495,9 @@
       <c r="AO32" s="120"/>
       <c r="AP32" s="120"/>
       <c r="AQ32" s="120"/>
-      <c r="AR32" s="120"/>
+      <c r="AR32" s="120">
+        <v>1</v>
+      </c>
       <c r="AS32" s="120"/>
       <c r="AT32" s="120"/>
       <c r="AU32" s="120"/>
@@ -12479,11 +12511,11 @@
       <c r="BC32" s="120"/>
       <c r="BD32" s="187">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE32" s="187" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF32" s="187" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
@@ -12495,11 +12527,11 @@
       </c>
       <c r="BH32" s="189">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BI32" s="189">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BJ32" s="189">
         <f t="shared" si="3"/>
@@ -12561,7 +12593,9 @@
       <c r="AP33" s="120"/>
       <c r="AQ33" s="120"/>
       <c r="AR33" s="120"/>
-      <c r="AS33" s="120"/>
+      <c r="AS33" s="120">
+        <v>1</v>
+      </c>
       <c r="AT33" s="120"/>
       <c r="AU33" s="120"/>
       <c r="AV33" s="120"/>
@@ -12574,11 +12608,11 @@
       <c r="BC33" s="120"/>
       <c r="BD33" s="187">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE33" s="187" cm="1">
         <f t="array" ref="BE33">SUMPRODUCT(--(B33:BC33=INT(B33:BC33)),--(B33:BC33&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BF33" s="187" cm="1">
         <f t="array" ref="BF33">MAX(FREQUENCY(IF((B33:BC33=INT(B33:BC33))*(B33:BC33&gt;0),COLUMN(B33:BC33)),IF((B33:BC33&lt;&gt;INT(B33:BC33))+(B33:BC33&lt;=0),COLUMN(B33:BC33))))</f>
@@ -12590,15 +12624,15 @@
       </c>
       <c r="BH33" s="189">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BI33" s="189">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BJ33" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:62">
@@ -12861,7 +12895,7 @@
       </c>
       <c r="BJ36" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:62">
@@ -12924,7 +12958,9 @@
       <c r="AO37" s="120"/>
       <c r="AP37" s="120"/>
       <c r="AQ37" s="120"/>
-      <c r="AR37" s="120"/>
+      <c r="AR37" s="120">
+        <v>1</v>
+      </c>
       <c r="AS37" s="120"/>
       <c r="AT37" s="120"/>
       <c r="AU37" s="120"/>
@@ -12938,11 +12974,11 @@
       <c r="BC37" s="120"/>
       <c r="BD37" s="187">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE37" s="187" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF37" s="187" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
@@ -13047,7 +13083,7 @@
       </c>
       <c r="BH38" s="189">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BI38" s="189">
         <f t="shared" si="2"/>
@@ -13055,7 +13091,7 @@
       </c>
       <c r="BJ38" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:62">
@@ -13350,8 +13386,12 @@
       </c>
       <c r="AP41" s="120"/>
       <c r="AQ41" s="120"/>
-      <c r="AR41" s="120"/>
-      <c r="AS41" s="120"/>
+      <c r="AR41" s="120">
+        <v>1</v>
+      </c>
+      <c r="AS41" s="120">
+        <v>1</v>
+      </c>
       <c r="AT41" s="120"/>
       <c r="AU41" s="120"/>
       <c r="AV41" s="120"/>
@@ -13364,11 +13404,11 @@
       <c r="BC41" s="120"/>
       <c r="BD41" s="187">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BE41" s="187" cm="1">
         <f t="array" ref="BE41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF41" s="187" cm="1">
         <f t="array" ref="BF41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
@@ -13388,7 +13428,7 @@
       </c>
       <c r="BJ41" s="189">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:62">
@@ -13467,7 +13507,9 @@
       </c>
       <c r="AP42" s="120"/>
       <c r="AQ42" s="120"/>
-      <c r="AR42" s="120"/>
+      <c r="AR42" s="120">
+        <v>2</v>
+      </c>
       <c r="AS42" s="120"/>
       <c r="AT42" s="120"/>
       <c r="AU42" s="120"/>
@@ -13481,11 +13523,11 @@
       <c r="BC42" s="120"/>
       <c r="BD42" s="187">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BE42" s="187" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BF42" s="187" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
@@ -13671,7 +13713,9 @@
       </c>
       <c r="AP44" s="120"/>
       <c r="AQ44" s="120"/>
-      <c r="AR44" s="120"/>
+      <c r="AR44" s="120">
+        <v>1</v>
+      </c>
       <c r="AS44" s="120"/>
       <c r="AT44" s="120"/>
       <c r="AU44" s="120"/>
@@ -13685,11 +13729,11 @@
       <c r="BC44" s="120"/>
       <c r="BD44" s="187">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE44" s="187" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BF44" s="187" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
@@ -13701,7 +13745,7 @@
       </c>
       <c r="BH44" s="189">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BI44" s="189">
         <f t="shared" si="2"/>
@@ -13895,8 +13939,12 @@
       <c r="AQ46" s="120">
         <v>1</v>
       </c>
-      <c r="AR46" s="120"/>
-      <c r="AS46" s="120"/>
+      <c r="AR46" s="120">
+        <v>2</v>
+      </c>
+      <c r="AS46" s="120">
+        <v>1</v>
+      </c>
       <c r="AT46" s="120"/>
       <c r="AU46" s="120"/>
       <c r="AV46" s="120"/>
@@ -13909,11 +13957,11 @@
       <c r="BC46" s="120"/>
       <c r="BD46" s="187">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="BE46" s="187" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BF46" s="187" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
@@ -14093,7 +14141,9 @@
       </c>
       <c r="AP48" s="120"/>
       <c r="AQ48" s="120"/>
-      <c r="AR48" s="120"/>
+      <c r="AR48" s="120">
+        <v>2</v>
+      </c>
       <c r="AS48" s="120"/>
       <c r="AT48" s="120"/>
       <c r="AU48" s="120"/>
@@ -14107,11 +14157,11 @@
       <c r="BC48" s="120"/>
       <c r="BD48" s="187">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BE48" s="187" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF48" s="187" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
@@ -14123,15 +14173,15 @@
       </c>
       <c r="BH48" s="189">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI48" s="189">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BJ48" s="189">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:62">
@@ -14218,15 +14268,15 @@
       </c>
       <c r="BH49" s="189">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BI49" s="189">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BJ49" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:62">
@@ -14315,15 +14365,15 @@
       </c>
       <c r="BH50" s="189">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BI50" s="189">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BJ50" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:62">
@@ -14586,7 +14636,7 @@
       </c>
       <c r="BJ53" s="189">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -15712,9 +15762,8 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 A9:X9" unlockedFormula="1"/>
-    <ignoredError sqref="A1 C1:S1 U1:AF1 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z28:AF33 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 A3:X4 BD1:BJ2 BI3 AC40:AD40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 A48:X49 Z48:AB48 AE48 A51:AF53 A50:AD50 AF50 X8:AF8 A8:V8 A5:AF7 Z4:AE4 Z41:AE42 BH4:BJ8 BI9:BJ9 Z10:AF10 BH11:BJ39 Z49:AF49 A12:X15 A37:AF37 A39:AF39 A2:AF2 Z3:AF3 A10:X10" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="AD11:AI11 AC48:AI48 AG1:AI3 AG43:AI47 AG49:AI53 AF42:AI42 AH41:AI41 AG5:AI8 AG16:AI39 AG12:AI14 BG41:BG53 AA11 Z15:AA15 AF15:AI15 Z12:AF12 Z13:AA13 Y17:AF18 A19:AF21 Y22:AF22 A23:AF23 Y24:AF25 Y28:AF33 Y36:AF36 A37:AF37 Y38:AF38 A39:AF39 Y3:Y4 A40:AB40 Y42 A43:AF43 X44:AF44 Y46:AF46 A47:AF47 Y48:Y49 AE50:AF50 A5:AF7 A8:W8 AF4:AI4 BG4:BG8 BG11:BG39 Y12:Y15" formulaRange="1"/>
+    <ignoredError sqref="A1:BJ8 Y9:BJ10 A11:BJ53" formulaRange="1"/>
+    <ignoredError sqref="A9:X10 Z3:AF3 A2:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH11:BJ39 Z10:AF10 BI9:BJ9 BH4:BJ8 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z28:AF33 A28:X33 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11 U1:AF1 C1:S1 A1 Z9:AB9 AD9:AF9 X41" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="654">
   <si>
     <t>姓名</t>
   </si>
@@ -902,6 +902,12 @@
     <t>试卷：解设没写单位-1——一分十几万——上周会考：50%老师外校——私立高中学费vs公立——总费用——一类校寄读费——很多人差1分——40中也有寄读（几万）——寄读条件（家境、走后门）——上次讲到“上高中的百分比变高”，原因：私立增加——每一分的价值——学生甘心、家长不甘心——借钱——兄弟姐妹（家长爱心）——好的儿女十几万都出——寄读一定好吗——（城门中学的学生觉得40中好，寄宿后越来越差）——学校没很照顾寄读——自己寄读其他学校感觉低人一等——学生内心——希望：努力——到时候后悔，3年多付10万</t>
   </si>
   <si>
+    <t>八下3.5</t>
+  </si>
+  <si>
+    <t>好高中无人管——一三附无第四节/第四节无老师看管——有人退步，一本考不上（6%）——原因：初中逼着念——自觉——刘老师逼着（优缺点）</t>
+  </si>
+  <si>
     <t>八上10.31</t>
   </si>
   <si>
@@ -972,9 +978,6 @@
   </si>
   <si>
     <t>过小测</t>
-  </si>
-  <si>
-    <t>八下3.5</t>
   </si>
   <si>
     <t>（物理午托）卓：卧槽有丧尸！（多人蹲在后排准备冲刺）；蒲林豪打开门；廖成羲：“上厕所”师：“憋着”</t>
@@ -3309,16 +3312,20 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="黑体"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
     </font>
     <font>
       <strike/>
@@ -3328,13 +3335,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="华文仿宋"/>
+      <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="57">
@@ -4100,7 +4103,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4522,11 +4525,23 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4674,6 +4689,9 @@
     <xf numFmtId="0" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4752,6 +4770,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5141,538 +5168,538 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="223" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="224" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="225" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="226"/>
+    <col min="1" max="1" width="7.59090909090909" style="231" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="232" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="233" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="234"/>
   </cols>
   <sheetData>
-    <row r="1" s="222" customFormat="1" spans="1:10">
-      <c r="A1" s="227" t="s">
+    <row r="1" s="230" customFormat="1" spans="1:10">
+      <c r="A1" s="235" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="228" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="228" t="s">
+      <c r="B1" s="236" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="236" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="228" t="s">
+      <c r="D1" s="236" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="228" t="s">
+      <c r="E1" s="236" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="228" t="s">
+      <c r="F1" s="236" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="228" t="s">
+      <c r="G1" s="236" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="229"/>
-      <c r="I1" s="229"/>
-      <c r="J1" s="229"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="237"/>
+      <c r="J1" s="237"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="230" t="s">
+      <c r="A2" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="224" t="s">
+      <c r="B2" s="232" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="224" t="s">
+      <c r="C2" s="232" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="230" t="s">
+      <c r="A3" s="238" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="224" t="s">
+      <c r="C3" s="232" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="224" t="s">
+      <c r="D3" s="232" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="230" t="s">
+      <c r="A4" s="238" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="224" t="s">
+      <c r="D4" s="232" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="230" t="s">
+      <c r="A5" s="238" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="224" t="s">
+      <c r="C5" s="232" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="224" t="s">
+      <c r="D5" s="232" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="230" t="s">
+      <c r="A6" s="238" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="224" t="s">
+      <c r="C6" s="232" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="230" t="s">
+      <c r="A7" s="238" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="224" t="s">
+      <c r="B7" s="232" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="224" t="s">
+      <c r="C7" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="224" t="s">
+      <c r="D7" s="232" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="230" t="s">
+      <c r="A8" s="238" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="224" t="s">
+      <c r="D8" s="232" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="230" t="s">
+      <c r="A9" s="238" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="230" t="s">
+      <c r="A10" s="238" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="224" t="s">
+      <c r="B10" s="232" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="230" t="s">
+      <c r="A11" s="238" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="230" t="s">
+      <c r="A12" s="238" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="230" t="s">
+      <c r="A13" s="238" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="224" t="s">
+      <c r="D13" s="232" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="230" t="s">
+      <c r="A14" s="238" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="224" t="s">
+      <c r="B14" s="232" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="230" t="s">
+      <c r="A15" s="238" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="230" t="s">
+      <c r="A16" s="238" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="224" t="s">
+      <c r="C16" s="232" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:5">
-      <c r="A17" s="230" t="s">
+      <c r="A17" s="238" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="224" t="s">
+      <c r="C17" s="232" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="230" t="s">
+      <c r="A18" s="238" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="224" t="s">
+      <c r="D18" s="232" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:5">
-      <c r="A19" s="230" t="s">
+      <c r="A19" s="238" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="224" t="s">
+      <c r="D19" s="232" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:5">
-      <c r="A20" s="230" t="s">
+      <c r="A20" s="238" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="224" t="s">
+      <c r="B20" s="232" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="224" t="s">
+      <c r="C20" s="232" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:5">
-      <c r="A21" s="230" t="s">
+      <c r="A21" s="238" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="224" t="s">
+      <c r="B21" s="232" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="224" t="s">
+      <c r="C21" s="232" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="224" t="s">
+      <c r="D21" s="232" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="230" t="s">
+      <c r="A22" s="238" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:5">
-      <c r="A23" s="230" t="s">
+      <c r="A23" s="238" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="224" t="s">
+      <c r="B23" s="232" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:5">
-      <c r="A24" s="230" t="s">
+      <c r="A24" s="238" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="224" t="s">
+      <c r="B24" s="232" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="224" t="s">
+      <c r="C24" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="224" t="s">
+      <c r="D24" s="232" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="230" t="s">
+      <c r="A25" s="238" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="230" t="s">
+      <c r="A26" s="238" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="230" t="s">
+      <c r="A27" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="224" t="s">
+      <c r="B27" s="232" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="224" t="s">
+      <c r="C27" s="232" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:5">
-      <c r="A28" s="230" t="s">
+      <c r="A28" s="238" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="224" t="s">
+      <c r="B28" s="232" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="224" t="s">
+      <c r="C28" s="232" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="224" t="s">
+      <c r="D28" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="224" t="s">
+      <c r="E28" s="232" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="230" t="s">
+      <c r="A29" s="238" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="230" t="s">
+      <c r="A30" s="238" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="224" t="s">
+      <c r="B30" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="224" t="s">
+      <c r="C30" s="232" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="230" t="s">
+      <c r="A31" s="238" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="230" t="s">
+      <c r="A32" s="238" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="230" t="s">
+      <c r="A33" s="238" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="230" t="s">
+      <c r="A34" s="238" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="230" t="s">
+      <c r="A35" s="238" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="230" t="s">
+      <c r="A36" s="238" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="224" t="s">
+      <c r="B36" s="232" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="230" t="s">
+      <c r="A37" s="238" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="224" t="s">
+      <c r="C37" s="232" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="224" t="s">
+      <c r="D37" s="232" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="230" t="s">
+      <c r="A38" s="238" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="224" t="s">
+      <c r="B38" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="231"/>
-      <c r="D38" s="231"/>
-      <c r="E38" s="231"/>
-      <c r="F38" s="231"/>
-      <c r="G38" s="231"/>
+      <c r="C38" s="239"/>
+      <c r="D38" s="239"/>
+      <c r="E38" s="239"/>
+      <c r="F38" s="239"/>
+      <c r="G38" s="239"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="230" t="s">
+      <c r="A39" s="238" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="224" t="s">
+      <c r="C39" s="232" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="224" t="s">
+      <c r="D39" s="232" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="230" t="s">
+      <c r="A40" s="238" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="224" t="s">
+      <c r="B40" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="224" t="s">
+      <c r="C40" s="232" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="224" t="s">
+      <c r="D40" s="232" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="230" t="s">
+      <c r="A41" s="238" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="224" t="s">
+      <c r="C41" s="232" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="224" t="s">
+      <c r="D41" s="232" t="s">
         <v>93</v>
       </c>
-      <c r="E41" s="224" t="s">
+      <c r="E41" s="232" t="s">
         <v>94</v>
       </c>
-      <c r="H41" s="225" t="s">
+      <c r="H41" s="233" t="s">
         <v>95</v>
       </c>
-      <c r="I41" s="225" t="s">
+      <c r="I41" s="233" t="s">
         <v>96</v>
       </c>
-      <c r="J41" s="225" t="s">
+      <c r="J41" s="233" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="230" t="s">
+      <c r="A42" s="238" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="230" t="s">
+      <c r="A43" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="224" t="s">
+      <c r="B43" s="232" t="s">
         <v>100</v>
       </c>
-      <c r="H43" s="225" t="s">
+      <c r="H43" s="233" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="230" t="s">
+      <c r="A44" s="238" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="224" t="s">
+      <c r="B44" s="232" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="230" t="s">
+      <c r="A45" s="238" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="224" t="s">
+      <c r="C45" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="224" t="s">
+      <c r="D45" s="232" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="230" t="s">
+      <c r="A46" s="238" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="230" t="s">
+      <c r="A47" s="238" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="224" t="s">
+      <c r="D47" s="232" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="230" t="s">
+      <c r="A48" s="238" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="224" t="s">
+      <c r="C48" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="D48" s="224" t="s">
+      <c r="D48" s="232" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="230" t="s">
+      <c r="A49" s="238" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="230" t="s">
+      <c r="A50" s="238" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="224" t="s">
+      <c r="C50" s="232" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="230" t="s">
+      <c r="A51" s="238" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="230" t="s">
+      <c r="A52" s="238" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="224" t="s">
+      <c r="B52" s="232" t="s">
         <v>118</v>
       </c>
-      <c r="C52" s="224" t="s">
+      <c r="C52" s="232" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="224" t="s">
+      <c r="E52" s="232" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="223" t="s">
+      <c r="A53" s="231" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="224" t="s">
+      <c r="B53" s="232" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="231"/>
-      <c r="E53" s="231"/>
-      <c r="F53" s="231"/>
-      <c r="G53" s="231"/>
+      <c r="D53" s="239"/>
+      <c r="E53" s="239"/>
+      <c r="F53" s="239"/>
+      <c r="G53" s="239"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="223" t="s">
+      <c r="A54" s="231" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="224" t="s">
+      <c r="B54" s="232" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="224" t="s">
+      <c r="C54" s="232" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="231"/>
-      <c r="E54" s="231"/>
-      <c r="F54" s="231"/>
-      <c r="G54" s="231"/>
+      <c r="D54" s="239"/>
+      <c r="E54" s="239"/>
+      <c r="F54" s="239"/>
+      <c r="G54" s="239"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="223" t="s">
+      <c r="A55" s="231" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="231"/>
-      <c r="C55" s="231"/>
-      <c r="D55" s="224" t="s">
+      <c r="B55" s="239"/>
+      <c r="C55" s="239"/>
+      <c r="D55" s="232" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="223" t="s">
+      <c r="A56" s="231" t="s">
         <v>128</v>
       </c>
       <c r="B56" s="78" t="s">
         <v>129</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="224" t="s">
+      <c r="D56" s="232" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="223" t="s">
+      <c r="A57" s="231" t="s">
         <v>131</v>
       </c>
       <c r="B57" s="78" t="s">
@@ -5681,76 +5708,76 @@
       <c r="C57" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="224" t="s">
+      <c r="D57" s="232" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="223" t="s">
+      <c r="A58" s="231" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="224" t="s">
+      <c r="B58" s="232" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="231"/>
-      <c r="D58" s="231"/>
-      <c r="E58" s="231"/>
-      <c r="F58" s="231"/>
-      <c r="G58" s="231"/>
+      <c r="C58" s="239"/>
+      <c r="D58" s="239"/>
+      <c r="E58" s="239"/>
+      <c r="F58" s="239"/>
+      <c r="G58" s="239"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="223" t="s">
+      <c r="A59" s="231" t="s">
         <v>137</v>
       </c>
-      <c r="B59" s="231"/>
-      <c r="C59" s="224" t="s">
+      <c r="B59" s="239"/>
+      <c r="C59" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="D59" s="231"/>
-      <c r="E59" s="231"/>
-      <c r="F59" s="231"/>
-      <c r="G59" s="231"/>
+      <c r="D59" s="239"/>
+      <c r="E59" s="239"/>
+      <c r="F59" s="239"/>
+      <c r="G59" s="239"/>
     </row>
     <row r="60" ht="65" spans="1:7">
-      <c r="A60" s="223" t="s">
+      <c r="A60" s="231" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="231" t="s">
+      <c r="B60" s="239" t="s">
         <v>140</v>
       </c>
-      <c r="C60" s="231"/>
-      <c r="D60" s="224" t="s">
+      <c r="C60" s="239"/>
+      <c r="D60" s="232" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="223" t="s">
+      <c r="A61" s="231" t="s">
         <v>142</v>
       </c>
       <c r="B61" s="78" t="s">
         <v>143</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="231"/>
-      <c r="E61" s="231"/>
-      <c r="F61" s="231"/>
-      <c r="G61" s="231"/>
+      <c r="D61" s="239"/>
+      <c r="E61" s="239"/>
+      <c r="F61" s="239"/>
+      <c r="G61" s="239"/>
     </row>
     <row r="62" ht="52" spans="1:7">
-      <c r="A62" s="223" t="s">
+      <c r="A62" s="231" t="s">
         <v>144</v>
       </c>
-      <c r="B62" s="231"/>
-      <c r="C62" s="231"/>
-      <c r="D62" s="224" t="s">
+      <c r="B62" s="239"/>
+      <c r="C62" s="239"/>
+      <c r="D62" s="232" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="224" t="s">
+      <c r="E62" s="232" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="223" t="s">
+      <c r="A63" s="231" t="s">
         <v>147</v>
       </c>
       <c r="B63" s="78" t="s">
@@ -5759,66 +5786,66 @@
       <c r="C63" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="231"/>
-      <c r="E63" s="231"/>
-      <c r="F63" s="231"/>
-      <c r="G63" s="231"/>
+      <c r="D63" s="239"/>
+      <c r="E63" s="239"/>
+      <c r="F63" s="239"/>
+      <c r="G63" s="239"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="223" t="s">
+      <c r="A64" s="231" t="s">
         <v>150</v>
       </c>
-      <c r="B64" s="231"/>
-      <c r="C64" s="231"/>
-      <c r="D64" s="224" t="s">
+      <c r="B64" s="239"/>
+      <c r="C64" s="239"/>
+      <c r="D64" s="232" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="223" t="s">
+      <c r="A65" s="231" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="232" t="s">
+      <c r="B65" s="240" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="231"/>
-      <c r="D65" s="231"/>
-      <c r="E65" s="231"/>
-      <c r="F65" s="231"/>
-      <c r="G65" s="231"/>
+      <c r="C65" s="239"/>
+      <c r="D65" s="239"/>
+      <c r="E65" s="239"/>
+      <c r="F65" s="239"/>
+      <c r="G65" s="239"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="223" t="s">
+      <c r="A66" s="231" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="231"/>
-      <c r="C66" s="224" t="s">
+      <c r="B66" s="239"/>
+      <c r="C66" s="232" t="s">
         <v>155</v>
       </c>
-      <c r="D66" s="231"/>
-      <c r="E66" s="231"/>
-      <c r="F66" s="231"/>
-      <c r="G66" s="231"/>
+      <c r="D66" s="239"/>
+      <c r="E66" s="239"/>
+      <c r="F66" s="239"/>
+      <c r="G66" s="239"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="223" t="s">
+      <c r="A67" s="231" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="231"/>
-      <c r="C67" s="231"/>
+      <c r="B67" s="239"/>
+      <c r="C67" s="239"/>
     </row>
     <row r="68" ht="78" spans="1:7">
-      <c r="A68" s="223" t="s">
+      <c r="A68" s="231" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="231"/>
-      <c r="C68" s="231"/>
-      <c r="D68" s="224" t="s">
+      <c r="B68" s="239"/>
+      <c r="C68" s="239"/>
+      <c r="D68" s="232" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="223" t="s">
+      <c r="A69" s="231" t="s">
         <v>159</v>
       </c>
       <c r="B69" s="78" t="s">
@@ -5827,89 +5854,89 @@
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="223" t="s">
+      <c r="A70" s="231" t="s">
         <v>161</v>
       </c>
       <c r="B70" s="78" t="s">
         <v>162</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="231"/>
-      <c r="E70" s="231"/>
-      <c r="F70" s="231"/>
-      <c r="G70" s="231"/>
+      <c r="D70" s="239"/>
+      <c r="E70" s="239"/>
+      <c r="F70" s="239"/>
+      <c r="G70" s="239"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="223" t="s">
+      <c r="A71" s="231" t="s">
         <v>163</v>
       </c>
-      <c r="B71" s="231"/>
-      <c r="C71" s="231"/>
+      <c r="B71" s="239"/>
+      <c r="C71" s="239"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="223" t="s">
+      <c r="A72" s="231" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="224" t="s">
+      <c r="B72" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="C72" s="224" t="s">
+      <c r="C72" s="232" t="s">
         <v>166</v>
       </c>
-      <c r="D72" s="231"/>
-      <c r="E72" s="231"/>
-      <c r="F72" s="231"/>
-      <c r="G72" s="231"/>
+      <c r="D72" s="239"/>
+      <c r="E72" s="239"/>
+      <c r="F72" s="239"/>
+      <c r="G72" s="239"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="223" t="s">
+      <c r="A73" s="231" t="s">
         <v>167</v>
       </c>
-      <c r="B73" s="231"/>
-      <c r="C73" s="224" t="s">
+      <c r="B73" s="239"/>
+      <c r="C73" s="232" t="s">
         <v>168</v>
       </c>
-      <c r="D73" s="231"/>
-      <c r="E73" s="231"/>
-      <c r="F73" s="231"/>
-      <c r="G73" s="231"/>
+      <c r="D73" s="239"/>
+      <c r="E73" s="239"/>
+      <c r="F73" s="239"/>
+      <c r="G73" s="239"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="223" t="s">
+      <c r="A74" s="231" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="223" t="s">
+      <c r="A75" s="231" t="s">
         <v>170</v>
       </c>
-      <c r="D75" s="231"/>
-      <c r="E75" s="231"/>
-      <c r="F75" s="231"/>
-      <c r="G75" s="231"/>
+      <c r="D75" s="239"/>
+      <c r="E75" s="239"/>
+      <c r="F75" s="239"/>
+      <c r="G75" s="239"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="223" t="s">
+      <c r="A76" s="231" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="231"/>
-      <c r="C76" s="231"/>
-      <c r="D76" s="224" t="s">
+      <c r="B76" s="239"/>
+      <c r="C76" s="239"/>
+      <c r="D76" s="232" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="223" t="s">
+      <c r="A77" s="231" t="s">
         <v>173</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="233" t="s">
+      <c r="A78" s="241" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="224" t="s">
+      <c r="B78" s="232" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5963,16 +5990,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5986,7 +6013,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6000,7 +6027,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6014,7 +6041,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6042,7 +6069,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6056,7 +6083,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6070,7 +6097,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6084,7 +6111,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6098,7 +6125,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6124,7 +6151,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6138,7 +6165,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6152,7 +6179,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6178,7 +6205,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6192,7 +6219,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6230,7 +6257,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6244,7 +6271,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6270,7 +6297,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6284,7 +6311,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6298,7 +6325,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6312,7 +6339,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6326,7 +6353,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6340,7 +6367,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6366,7 +6393,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6380,7 +6407,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6394,7 +6421,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6420,7 +6447,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6446,7 +6473,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6460,7 +6487,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6474,10 +6501,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E38" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6491,7 +6518,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6505,7 +6532,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6519,10 +6546,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E41" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6548,7 +6575,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6574,7 +6601,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6600,10 +6627,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E47" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6617,7 +6644,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6643,7 +6670,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6669,7 +6696,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -6702,34 +6729,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>247</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6737,10 +6764,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6748,10 +6775,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6759,10 +6786,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6770,23 +6797,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6794,10 +6821,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6805,10 +6832,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6816,10 +6843,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6827,10 +6854,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6838,50 +6865,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6890,24 +6917,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6915,17 +6942,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6934,61 +6961,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -6996,10 +7023,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7007,10 +7034,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7018,27 +7045,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7046,10 +7073,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7057,10 +7084,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7068,53 +7095,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7125,42 +7152,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7168,64 +7195,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7235,16 +7262,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7253,7 +7280,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7262,42 +7289,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7307,10 +7334,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7318,10 +7345,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7333,18 +7360,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -7452,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7466,7 +7493,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7490,7 +7517,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7503,7 +7530,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7516,7 +7543,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7550,7 +7577,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7596,7 +7623,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7632,7 +7659,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7666,10 +7693,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7681,10 +7708,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7707,7 +7734,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7720,10 +7747,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7757,10 +7784,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7772,10 +7799,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7799,7 +7826,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7866,7 +7893,7 @@
         <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7880,7 +7907,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7892,7 +7919,7 @@
         <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7906,7 +7933,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7918,10 +7945,10 @@
         <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7934,7 +7961,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7957,7 +7984,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7981,7 +8008,7 @@
         <v>104</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -8017,7 +8044,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8041,7 +8068,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8064,10 +8091,10 @@
         <v>117</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8103,27 +8130,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8131,13 +8158,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8145,13 +8172,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8159,13 +8186,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8173,13 +8200,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8187,13 +8214,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8201,13 +8228,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8215,7 +8242,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8223,7 +8250,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8231,7 +8258,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8239,7 +8266,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8259,14 +8286,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="217" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="225" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="218"/>
+    <col min="8" max="16384" width="8.72727272727273" style="226"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="219"/>
+      <c r="A1" s="227"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8286,8 +8313,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="216" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="220" t="s">
+    <row r="2" s="224" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="228" t="s">
         <v>176</v>
       </c>
       <c r="B2" s="78"/>
@@ -8300,7 +8327,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="221" t="s">
+      <c r="A3" s="229" t="s">
         <v>178</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8308,7 +8335,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="221" t="s">
+      <c r="A4" s="229" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8319,7 +8346,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="221" t="s">
+      <c r="A5" s="229" t="s">
         <v>183</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8330,7 +8357,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="221" t="s">
+      <c r="A6" s="229" t="s">
         <v>186</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8341,7 +8368,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="221" t="s">
+      <c r="A7" s="229" t="s">
         <v>189</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8349,127 +8376,127 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="221"/>
+      <c r="A8" s="229"/>
       <c r="D8" s="66" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="221"/>
+      <c r="A9" s="229"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="221"/>
+      <c r="A10" s="229"/>
       <c r="B10" s="66" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="221"/>
+      <c r="A11" s="229"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="221"/>
+      <c r="A12" s="229"/>
       <c r="B12" s="66" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="221"/>
+      <c r="A13" s="229"/>
       <c r="B13" s="66" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="221"/>
+      <c r="A14" s="229"/>
       <c r="B14" s="66" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="221"/>
+      <c r="A15" s="229"/>
       <c r="B15" s="66" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="221"/>
+      <c r="A16" s="229"/>
       <c r="B16" s="66" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="221"/>
+      <c r="A17" s="229"/>
       <c r="B17" s="66" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="221"/>
+      <c r="A18" s="229"/>
       <c r="B18" s="66" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:2">
-      <c r="A19" s="221"/>
+      <c r="A19" s="229"/>
       <c r="B19" s="78" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="221"/>
+      <c r="A20" s="229"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="221"/>
+      <c r="A21" s="229"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="221"/>
+      <c r="A22" s="229"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="221"/>
+      <c r="A23" s="229"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="221"/>
+      <c r="A24" s="229"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="221"/>
+      <c r="A25" s="229"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="221"/>
+      <c r="A26" s="229"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="221"/>
+      <c r="A27" s="229"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="221"/>
+      <c r="A28" s="229"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="221"/>
+      <c r="A29" s="229"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="221"/>
+      <c r="A30" s="229"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="221"/>
+      <c r="A31" s="229"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="221"/>
+      <c r="A32" s="229"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="221"/>
+      <c r="A33" s="229"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="221"/>
+      <c r="A34" s="229"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="221"/>
+      <c r="A35" s="229"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="221"/>
+      <c r="A36" s="229"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="221"/>
+      <c r="A37" s="229"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="221"/>
+      <c r="A38" s="229"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8478,7 +8505,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="221"/>
+      <c r="A39" s="229"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8487,40 +8514,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="221"/>
+      <c r="A40" s="229"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="221"/>
+      <c r="A41" s="229"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="221"/>
+      <c r="A42" s="229"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="221"/>
+      <c r="A43" s="229"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="221"/>
+      <c r="A44" s="229"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="221"/>
+      <c r="A45" s="229"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="221"/>
+      <c r="A46" s="229"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="221"/>
+      <c r="A47" s="229"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="221"/>
+      <c r="A48" s="229"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="221"/>
+      <c r="A49" s="229"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="221"/>
+      <c r="A50" s="229"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="221"/>
+      <c r="A51" s="229"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8533,494 +8560,503 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="207" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="207" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="207" customWidth="1"/>
+    <col min="1" max="1" width="24" style="212" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="212" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="212" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="206" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="208" t="s">
+    <row r="1" s="211" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="213" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="208" t="s">
+      <c r="B1" s="213" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="208" t="s">
+      <c r="C1" s="213" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="209" t="s">
+      <c r="A2" s="214" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="209" t="s">
+      <c r="B2" s="214" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="209" t="s">
+      <c r="C2" s="214" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="209" t="s">
+      <c r="A3" s="214" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="209" t="s">
+      <c r="B3" s="214" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="209" t="s">
+      <c r="C3" s="214" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="209" t="s">
+      <c r="A4" s="214" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="209" t="s">
+      <c r="B4" s="214" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="209" t="s">
+      <c r="C4" s="214" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="210" t="s">
+      <c r="A5" s="215" t="s">
         <v>212</v>
       </c>
-      <c r="B5" s="209" t="s">
+      <c r="B5" s="214" t="s">
         <v>213</v>
       </c>
-      <c r="C5" s="209" t="s">
+      <c r="C5" s="214" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="211"/>
-      <c r="B6" s="209" t="s">
+      <c r="A6" s="216"/>
+      <c r="B6" s="214" t="s">
         <v>215</v>
       </c>
-      <c r="C6" s="209" t="s">
+      <c r="C6" s="214" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="212" t="s">
+      <c r="A7" s="217" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="209" t="s">
+      <c r="B7" s="214" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="209" t="s">
+      <c r="C7" s="214" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
-      <c r="A8" s="212"/>
-      <c r="B8" s="209" t="s">
+      <c r="A8" s="217"/>
+      <c r="B8" s="214" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="209" t="s">
+      <c r="C8" s="214" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="212"/>
-      <c r="B9" s="209" t="s">
+      <c r="A9" s="217"/>
+      <c r="B9" s="214" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="209" t="s">
+      <c r="C9" s="214" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="212"/>
-      <c r="B10" s="209" t="s">
+      <c r="A10" s="217"/>
+      <c r="B10" s="214" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="209" t="s">
+      <c r="C10" s="214" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="212"/>
-      <c r="B11" s="209"/>
-      <c r="C11" s="209"/>
+      <c r="A11" s="217"/>
+      <c r="B11" s="214"/>
+      <c r="C11" s="214"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="212"/>
-      <c r="B12" s="209"/>
-      <c r="C12" s="209"/>
+      <c r="A12" s="217"/>
+      <c r="B12" s="214"/>
+      <c r="C12" s="214"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="212"/>
-      <c r="B13" s="209"/>
-      <c r="C13" s="209"/>
+      <c r="A13" s="217"/>
+      <c r="B13" s="214"/>
+      <c r="C13" s="214"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="213"/>
-      <c r="B14" s="209"/>
-      <c r="C14" s="209"/>
+      <c r="A14" s="218"/>
+      <c r="B14" s="214"/>
+      <c r="C14" s="214"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="209" t="s">
+      <c r="A15" s="214" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="209" t="s">
+      <c r="B15" s="214" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="209" t="s">
+      <c r="C15" s="214" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="209" t="s">
+      <c r="A16" s="214" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="209" t="s">
+      <c r="B16" s="214" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="209" t="s">
+      <c r="C16" s="214" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="209" t="s">
+      <c r="A17" s="214" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="209" t="s">
+      <c r="B17" s="214" t="s">
         <v>232</v>
       </c>
-      <c r="C17" s="214">
+      <c r="C17" s="219">
         <v>0.440972222222222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="215" t="s">
+      <c r="A18" s="220" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="209" t="s">
+      <c r="B18" s="214" t="s">
         <v>233</v>
       </c>
-      <c r="C18" s="209" t="s">
+      <c r="C18" s="214" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="212"/>
-      <c r="B19" s="209" t="s">
+      <c r="A19" s="217"/>
+      <c r="B19" s="214" t="s">
         <v>235</v>
       </c>
-      <c r="C19" s="209" t="s">
+      <c r="C19" s="214" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="20" ht="56" spans="1:3">
-      <c r="A20" s="212"/>
-      <c r="B20" s="209" t="s">
+      <c r="A20" s="217"/>
+      <c r="B20" s="214" t="s">
         <v>237</v>
       </c>
-      <c r="C20" s="209" t="s">
+      <c r="C20" s="214" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="212"/>
-      <c r="B21" s="209" t="s">
+      <c r="A21" s="217"/>
+      <c r="B21" s="214" t="s">
         <v>239</v>
       </c>
-      <c r="C21" s="209" t="s">
+      <c r="C21" s="214" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:3">
-      <c r="A22" s="212"/>
-      <c r="B22" s="209" t="s">
+      <c r="A22" s="217"/>
+      <c r="B22" s="214" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="209" t="s">
+      <c r="C22" s="214" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="212"/>
-      <c r="B23" s="209"/>
-      <c r="C23" s="209"/>
+      <c r="A23" s="217"/>
+      <c r="B23" s="214"/>
+      <c r="C23" s="214"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="212"/>
-      <c r="B24" s="209"/>
-      <c r="C24" s="209"/>
+      <c r="A24" s="217"/>
+      <c r="B24" s="214"/>
+      <c r="C24" s="214"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="212"/>
-      <c r="B25" s="209"/>
-      <c r="C25" s="209"/>
+      <c r="A25" s="217"/>
+      <c r="B25" s="214"/>
+      <c r="C25" s="214"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="210" t="s">
+      <c r="A26" s="215" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="209" t="s">
+      <c r="B26" s="214" t="s">
         <v>235</v>
       </c>
-      <c r="C26" s="209" t="s">
+      <c r="C26" s="214" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="211"/>
-      <c r="B27" s="209" t="s">
+      <c r="A27" s="216"/>
+      <c r="B27" s="214" t="s">
         <v>245</v>
       </c>
-      <c r="C27" s="209" t="s">
+      <c r="C27" s="214" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:3">
-      <c r="A28" s="215" t="s">
+      <c r="A28" s="220" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="209" t="s">
+      <c r="B28" s="214" t="s">
         <v>248</v>
       </c>
-      <c r="C28" s="209" t="s">
+      <c r="C28" s="214" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="212"/>
-      <c r="B29" s="209" t="s">
+      <c r="A29" s="217"/>
+      <c r="B29" s="214" t="s">
         <v>219</v>
       </c>
-      <c r="C29" s="209" t="s">
+      <c r="C29" s="214" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="212"/>
-      <c r="B30" s="209" t="s">
+      <c r="A30" s="217"/>
+      <c r="B30" s="214" t="s">
         <v>251</v>
       </c>
-      <c r="C30" s="209" t="s">
+      <c r="C30" s="214" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="212"/>
-      <c r="B31" s="209"/>
-      <c r="C31" s="209"/>
+      <c r="A31" s="217"/>
+      <c r="B31" s="214"/>
+      <c r="C31" s="214"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="210" t="s">
+      <c r="A32" s="215" t="s">
         <v>253</v>
       </c>
-      <c r="B32" s="209" t="s">
+      <c r="B32" s="214" t="s">
         <v>254</v>
       </c>
-      <c r="C32" s="209" t="s">
+      <c r="C32" s="214" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="211"/>
-      <c r="B33" s="209" t="s">
+      <c r="A33" s="216"/>
+      <c r="B33" s="214" t="s">
         <v>217</v>
       </c>
-      <c r="C33" s="209" t="s">
+      <c r="C33" s="214" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:3">
-      <c r="A34" s="215" t="s">
+      <c r="A34" s="220" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="209" t="s">
+      <c r="B34" s="214" t="s">
         <v>217</v>
       </c>
-      <c r="C34" s="209" t="s">
+      <c r="C34" s="214" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="212"/>
-      <c r="B35" s="207" t="s">
+      <c r="A35" s="217"/>
+      <c r="B35" s="212" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="207" t="s">
+      <c r="C35" s="212" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="212"/>
-      <c r="B36" s="207" t="s">
+      <c r="A36" s="217"/>
+      <c r="B36" s="212" t="s">
         <v>239</v>
       </c>
-      <c r="C36" s="207" t="s">
+      <c r="C36" s="212" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="37" ht="98" spans="1:3">
-      <c r="A37" s="215" t="s">
+      <c r="A37" s="221" t="s">
         <v>261</v>
       </c>
-      <c r="B37" s="207" t="s">
+      <c r="B37" s="212" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="207" t="s">
+      <c r="C37" s="212" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="38" ht="84" spans="1:3">
-      <c r="A38" s="213"/>
-      <c r="B38" s="207" t="s">
+      <c r="A38" s="222"/>
+      <c r="B38" s="212" t="s">
         <v>263</v>
       </c>
-      <c r="C38" s="207" t="s">
+      <c r="C38" s="212" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="207" t="s">
+    <row r="39" ht="28" spans="1:3">
+      <c r="A39" s="223"/>
+      <c r="B39" s="212" t="s">
+        <v>265</v>
+      </c>
+      <c r="C39" s="212" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="212" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="207" t="s">
+      <c r="B40" s="212" t="s">
+        <v>267</v>
+      </c>
+      <c r="C40" s="212" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="220" t="s">
+        <v>269</v>
+      </c>
+      <c r="B41" s="212" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="212" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="218"/>
+      <c r="B42" s="212" t="s">
+        <v>263</v>
+      </c>
+      <c r="C42" s="212" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="212" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="212" t="s">
+        <v>221</v>
+      </c>
+      <c r="C43" s="212" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="212" t="s">
+        <v>273</v>
+      </c>
+      <c r="B44" s="212" t="s">
+        <v>274</v>
+      </c>
+      <c r="C44" s="212" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="212" t="s">
+        <v>276</v>
+      </c>
+      <c r="B45" s="212" t="s">
+        <v>277</v>
+      </c>
+      <c r="C45" s="212" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="212" t="s">
+        <v>10</v>
+      </c>
+      <c r="B46" s="212" t="s">
+        <v>263</v>
+      </c>
+      <c r="C46" s="212" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" s="212" t="s">
+        <v>280</v>
+      </c>
+      <c r="B47" s="212" t="s">
+        <v>281</v>
+      </c>
+      <c r="C47" s="212" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" s="212" t="s">
+        <v>283</v>
+      </c>
+      <c r="B48" s="212" t="s">
+        <v>284</v>
+      </c>
+      <c r="C48" s="212" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="212" t="s">
+        <v>286</v>
+      </c>
+      <c r="B49" s="212" t="s">
+        <v>284</v>
+      </c>
+      <c r="C49" s="212" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="212" t="s">
+        <v>288</v>
+      </c>
+      <c r="B50" s="212" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="212" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="51" ht="28" spans="1:3">
+      <c r="A51" s="212" t="s">
+        <v>290</v>
+      </c>
+      <c r="B51" s="212" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="207" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="215" t="s">
-        <v>267</v>
-      </c>
-      <c r="B40" s="207" t="s">
-        <v>219</v>
-      </c>
-      <c r="C40" s="207" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="213"/>
-      <c r="B41" s="207" t="s">
-        <v>263</v>
-      </c>
-      <c r="C41" s="207" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="207" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" s="207" t="s">
-        <v>221</v>
-      </c>
-      <c r="C42" s="207" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="207" t="s">
-        <v>271</v>
-      </c>
-      <c r="B43" s="207" t="s">
-        <v>272</v>
-      </c>
-      <c r="C43" s="207" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="207" t="s">
-        <v>274</v>
-      </c>
-      <c r="B44" s="207" t="s">
-        <v>275</v>
-      </c>
-      <c r="C44" s="207" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="207" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="207" t="s">
-        <v>263</v>
-      </c>
-      <c r="C45" s="207" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="207" t="s">
-        <v>278</v>
-      </c>
-      <c r="B46" s="207" t="s">
-        <v>279</v>
-      </c>
-      <c r="C46" s="207" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="207" t="s">
-        <v>281</v>
-      </c>
-      <c r="B47" s="207" t="s">
-        <v>282</v>
-      </c>
-      <c r="C47" s="207" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="207" t="s">
-        <v>284</v>
-      </c>
-      <c r="B48" s="207" t="s">
-        <v>282</v>
-      </c>
-      <c r="C48" s="207" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="207" t="s">
-        <v>286</v>
-      </c>
-      <c r="B49" s="207" t="s">
-        <v>241</v>
-      </c>
-      <c r="C49" s="207" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="50" ht="28" spans="1:3">
-      <c r="A50" s="207" t="s">
-        <v>288</v>
-      </c>
-      <c r="B50" s="207" t="s">
-        <v>289</v>
-      </c>
-      <c r="C50" s="207" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="51" ht="28" spans="1:3">
-      <c r="A51" s="207" t="s">
+      <c r="C51" s="212" t="s">
         <v>291</v>
       </c>
-      <c r="B51" s="207" t="s">
-        <v>289</v>
-      </c>
-      <c r="C51" s="207" t="s">
+    </row>
+    <row r="52" ht="28" spans="1:3">
+      <c r="A52" s="212" t="s">
         <v>292</v>
+      </c>
+      <c r="B52" s="212" t="s">
+        <v>265</v>
+      </c>
+      <c r="C52" s="212" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -9032,8 +9068,8 @@
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A34:A36"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A37:A39"/>
+    <mergeCell ref="A41:A42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -9052,45 +9088,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="195"/>
+    <col min="5" max="5" width="8.72727272727273" style="200"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="193" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="196" t="s">
-        <v>293</v>
-      </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="198"/>
-      <c r="E1" s="199"/>
-      <c r="F1" s="193" t="s">
+    <row r="1" s="198" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="201" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="2" s="194" customFormat="1" spans="1:7">
-      <c r="A2" s="200" t="s">
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="198" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2" s="199" customFormat="1" spans="1:7">
+      <c r="A2" s="205" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="201"/>
-      <c r="C2" s="194" t="s">
-        <v>295</v>
-      </c>
-      <c r="D2" s="194" t="s">
+      <c r="B2" s="206"/>
+      <c r="C2" s="199" t="s">
         <v>296</v>
       </c>
-      <c r="E2" s="141"/>
-      <c r="F2" s="194" t="s">
+      <c r="D2" s="199" t="s">
+        <v>297</v>
+      </c>
+      <c r="E2" s="142"/>
+      <c r="F2" s="199" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="194" t="s">
-        <v>297</v>
+      <c r="G2" s="199" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="202">
+      <c r="A3" s="207">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -9101,14 +9137,14 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="203"/>
+      <c r="A4" s="208"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -9117,14 +9153,14 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="203"/>
+      <c r="A5" s="208"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -9133,14 +9169,14 @@
       </c>
       <c r="D5" s="119"/>
       <c r="F5" s="119" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G5" s="119" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="203"/>
+      <c r="A6" s="208"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9148,15 +9184,15 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="204" t="s">
-        <v>304</v>
+      <c r="F6" s="209" t="s">
+        <v>305</v>
       </c>
       <c r="G6" s="119" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="203"/>
+      <c r="A7" s="208"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9164,13 +9200,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="205"/>
+      <c r="F7" s="210"/>
       <c r="G7" s="119" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="203"/>
+      <c r="A8" s="208"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9182,7 +9218,7 @@
       <c r="G8" s="119"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="205"/>
+      <c r="A9" s="210"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9194,7 +9230,7 @@
       <c r="G9" s="119"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="204">
+      <c r="A10" s="209">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9208,7 +9244,7 @@
       <c r="G10" s="119"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="203"/>
+      <c r="A11" s="208"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9220,7 +9256,7 @@
       <c r="G11" s="119"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="205"/>
+      <c r="A12" s="210"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9232,7 +9268,7 @@
       <c r="G12" s="119"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="204">
+      <c r="A13" s="209">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9248,7 +9284,7 @@
       <c r="G13" s="119"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="205"/>
+      <c r="A14" s="210"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -9287,267 +9323,267 @@
   <cols>
     <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
     <col min="2" max="55" width="3.23636363636364" customWidth="1"/>
-    <col min="56" max="58" width="4.81818181818182" style="174" customWidth="1"/>
-    <col min="59" max="59" width="7.18181818181818" style="174" customWidth="1"/>
-    <col min="60" max="62" width="4.81818181818182" style="174" customWidth="1"/>
+    <col min="56" max="58" width="4.81818181818182" style="178" customWidth="1"/>
+    <col min="59" max="59" width="7.18181818181818" style="178" customWidth="1"/>
+    <col min="60" max="62" width="4.81818181818182" style="178" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62">
-      <c r="A1" s="175" t="s">
-        <v>307</v>
-      </c>
-      <c r="B1" s="176" t="s">
+      <c r="A1" s="179" t="s">
         <v>308</v>
       </c>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
-      <c r="H1" s="177"/>
-      <c r="I1" s="177"/>
-      <c r="J1" s="177"/>
-      <c r="K1" s="177"/>
-      <c r="L1" s="177"/>
-      <c r="M1" s="177"/>
-      <c r="N1" s="177"/>
-      <c r="O1" s="177"/>
-      <c r="P1" s="177"/>
-      <c r="Q1" s="177"/>
-      <c r="R1" s="177"/>
-      <c r="S1" s="177"/>
-      <c r="T1" s="178" t="s">
+      <c r="B1" s="180" t="s">
         <v>309</v>
       </c>
-      <c r="U1" s="179"/>
-      <c r="V1" s="179"/>
-      <c r="W1" s="179"/>
-      <c r="X1" s="179"/>
-      <c r="Y1" s="179"/>
-      <c r="Z1" s="179"/>
-      <c r="AA1" s="179"/>
-      <c r="AB1" s="179"/>
-      <c r="AC1" s="179"/>
-      <c r="AD1" s="179"/>
-      <c r="AE1" s="179"/>
-      <c r="AF1" s="179"/>
-      <c r="AG1" s="179"/>
-      <c r="AH1" s="179"/>
-      <c r="AI1" s="179"/>
-      <c r="AJ1" s="178" t="s">
+      <c r="C1" s="181"/>
+      <c r="D1" s="181"/>
+      <c r="E1" s="181"/>
+      <c r="F1" s="181"/>
+      <c r="G1" s="181"/>
+      <c r="H1" s="181"/>
+      <c r="I1" s="181"/>
+      <c r="J1" s="181"/>
+      <c r="K1" s="181"/>
+      <c r="L1" s="181"/>
+      <c r="M1" s="181"/>
+      <c r="N1" s="181"/>
+      <c r="O1" s="181"/>
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="181"/>
+      <c r="T1" s="182" t="s">
         <v>310</v>
       </c>
-      <c r="AK1" s="179"/>
-      <c r="AL1" s="179"/>
-      <c r="AM1" s="178" t="s">
+      <c r="U1" s="183"/>
+      <c r="V1" s="183"/>
+      <c r="W1" s="183"/>
+      <c r="X1" s="183"/>
+      <c r="Y1" s="183"/>
+      <c r="Z1" s="183"/>
+      <c r="AA1" s="183"/>
+      <c r="AB1" s="183"/>
+      <c r="AC1" s="183"/>
+      <c r="AD1" s="183"/>
+      <c r="AE1" s="183"/>
+      <c r="AF1" s="183"/>
+      <c r="AG1" s="183"/>
+      <c r="AH1" s="183"/>
+      <c r="AI1" s="183"/>
+      <c r="AJ1" s="182" t="s">
         <v>311</v>
       </c>
-      <c r="AN1" s="179"/>
-      <c r="AO1" s="179"/>
-      <c r="AP1" s="179"/>
-      <c r="AQ1" s="179"/>
-      <c r="AR1" s="179"/>
-      <c r="AS1" s="179"/>
-      <c r="AT1" s="179"/>
-      <c r="AU1" s="179"/>
-      <c r="AV1" s="179"/>
-      <c r="AW1" s="179"/>
-      <c r="AX1" s="179"/>
-      <c r="AY1" s="179"/>
-      <c r="AZ1" s="179"/>
-      <c r="BA1" s="179"/>
-      <c r="BB1" s="179"/>
-      <c r="BC1" s="180"/>
-      <c r="BD1" s="181" t="s">
+      <c r="AK1" s="183"/>
+      <c r="AL1" s="183"/>
+      <c r="AM1" s="182" t="s">
         <v>312</v>
       </c>
-      <c r="BE1" s="182"/>
-      <c r="BF1" s="182"/>
-      <c r="BG1" s="182"/>
-      <c r="BH1" s="182"/>
-      <c r="BI1" s="182"/>
-      <c r="BJ1" s="183"/>
-    </row>
-    <row r="2" s="173" customFormat="1" ht="28" spans="1:62">
-      <c r="A2" s="175"/>
-      <c r="B2" s="184">
+      <c r="AN1" s="183"/>
+      <c r="AO1" s="183"/>
+      <c r="AP1" s="183"/>
+      <c r="AQ1" s="183"/>
+      <c r="AR1" s="183"/>
+      <c r="AS1" s="183"/>
+      <c r="AT1" s="183"/>
+      <c r="AU1" s="183"/>
+      <c r="AV1" s="183"/>
+      <c r="AW1" s="183"/>
+      <c r="AX1" s="183"/>
+      <c r="AY1" s="183"/>
+      <c r="AZ1" s="183"/>
+      <c r="BA1" s="183"/>
+      <c r="BB1" s="183"/>
+      <c r="BC1" s="184"/>
+      <c r="BD1" s="185" t="s">
+        <v>313</v>
+      </c>
+      <c r="BE1" s="186"/>
+      <c r="BF1" s="186"/>
+      <c r="BG1" s="186"/>
+      <c r="BH1" s="186"/>
+      <c r="BI1" s="186"/>
+      <c r="BJ1" s="187"/>
+    </row>
+    <row r="2" s="177" customFormat="1" ht="28" spans="1:62">
+      <c r="A2" s="179"/>
+      <c r="B2" s="188">
         <v>5</v>
       </c>
-      <c r="C2" s="184">
+      <c r="C2" s="188">
         <v>6</v>
       </c>
-      <c r="D2" s="184">
+      <c r="D2" s="188">
         <v>9</v>
       </c>
-      <c r="E2" s="184">
+      <c r="E2" s="188">
         <v>10</v>
       </c>
-      <c r="F2" s="184">
+      <c r="F2" s="188">
         <v>11</v>
       </c>
-      <c r="G2" s="184">
+      <c r="G2" s="188">
         <v>12</v>
       </c>
-      <c r="H2" s="184">
+      <c r="H2" s="188">
         <v>15</v>
       </c>
-      <c r="I2" s="184">
+      <c r="I2" s="188">
         <v>16</v>
       </c>
-      <c r="J2" s="184">
+      <c r="J2" s="188">
         <v>17</v>
       </c>
-      <c r="K2" s="184">
+      <c r="K2" s="188">
         <v>18</v>
       </c>
-      <c r="L2" s="184">
+      <c r="L2" s="188">
         <v>19</v>
       </c>
-      <c r="M2" s="184">
+      <c r="M2" s="188">
         <v>22</v>
       </c>
-      <c r="N2" s="184">
+      <c r="N2" s="188">
         <v>23</v>
       </c>
-      <c r="O2" s="184">
+      <c r="O2" s="188">
         <v>25</v>
       </c>
-      <c r="P2" s="184">
+      <c r="P2" s="188">
         <v>26</v>
       </c>
-      <c r="Q2" s="184">
+      <c r="Q2" s="188">
         <v>29</v>
       </c>
-      <c r="R2" s="184">
+      <c r="R2" s="188">
         <v>30</v>
       </c>
-      <c r="S2" s="184">
+      <c r="S2" s="188">
         <v>31</v>
       </c>
-      <c r="T2" s="184">
+      <c r="T2" s="188">
         <v>4</v>
       </c>
-      <c r="U2" s="184">
+      <c r="U2" s="188">
         <v>5</v>
       </c>
-      <c r="V2" s="184">
+      <c r="V2" s="188">
         <v>6</v>
       </c>
-      <c r="W2" s="184">
+      <c r="W2" s="188">
         <v>7</v>
       </c>
-      <c r="X2" s="184">
+      <c r="X2" s="188">
         <v>8</v>
       </c>
-      <c r="Y2" s="184">
+      <c r="Y2" s="188">
         <v>11</v>
       </c>
-      <c r="Z2" s="184">
+      <c r="Z2" s="188">
         <v>12</v>
       </c>
-      <c r="AA2" s="184">
+      <c r="AA2" s="188">
         <v>13</v>
       </c>
-      <c r="AB2" s="184">
+      <c r="AB2" s="188">
         <v>14</v>
       </c>
-      <c r="AC2" s="184">
+      <c r="AC2" s="188">
         <v>15</v>
       </c>
-      <c r="AD2" s="184">
+      <c r="AD2" s="188">
         <v>16</v>
       </c>
-      <c r="AE2" s="184">
+      <c r="AE2" s="188">
         <v>19</v>
       </c>
-      <c r="AF2" s="184">
+      <c r="AF2" s="188">
         <v>20</v>
       </c>
-      <c r="AG2" s="184">
+      <c r="AG2" s="188">
         <v>21</v>
       </c>
-      <c r="AH2" s="184">
+      <c r="AH2" s="188">
         <v>22</v>
       </c>
-      <c r="AI2" s="184">
+      <c r="AI2" s="188">
         <v>23</v>
       </c>
-      <c r="AJ2" s="184">
+      <c r="AJ2" s="188">
         <v>26</v>
       </c>
-      <c r="AK2" s="184">
+      <c r="AK2" s="188">
         <v>27</v>
       </c>
-      <c r="AL2" s="184">
+      <c r="AL2" s="188">
         <v>28</v>
       </c>
-      <c r="AM2" s="184">
+      <c r="AM2" s="188">
         <v>2</v>
       </c>
-      <c r="AN2" s="184">
+      <c r="AN2" s="188">
         <v>3</v>
       </c>
-      <c r="AO2" s="184">
+      <c r="AO2" s="188">
         <v>4</v>
       </c>
-      <c r="AP2" s="184">
+      <c r="AP2" s="188">
         <v>5</v>
       </c>
-      <c r="AQ2" s="184">
+      <c r="AQ2" s="188">
         <v>6</v>
       </c>
-      <c r="AR2" s="184">
+      <c r="AR2" s="188">
         <v>9</v>
       </c>
-      <c r="AS2" s="184">
+      <c r="AS2" s="188">
         <v>10</v>
       </c>
-      <c r="AT2" s="184">
+      <c r="AT2" s="188">
         <v>11</v>
       </c>
-      <c r="AU2" s="184">
+      <c r="AU2" s="188">
         <v>12</v>
       </c>
-      <c r="AV2" s="184">
+      <c r="AV2" s="188">
         <v>13</v>
       </c>
-      <c r="AW2" s="184">
+      <c r="AW2" s="188">
         <v>16</v>
       </c>
-      <c r="AX2" s="184">
+      <c r="AX2" s="188">
         <v>17</v>
       </c>
-      <c r="AY2" s="184">
+      <c r="AY2" s="188">
         <v>18</v>
       </c>
-      <c r="AZ2" s="184">
+      <c r="AZ2" s="188">
         <v>19</v>
       </c>
-      <c r="BA2" s="184">
+      <c r="BA2" s="188">
         <v>20</v>
       </c>
-      <c r="BB2" s="184"/>
-      <c r="BC2" s="184"/>
-      <c r="BD2" s="185" t="s">
-        <v>313</v>
-      </c>
-      <c r="BE2" s="185" t="s">
+      <c r="BB2" s="188"/>
+      <c r="BC2" s="188"/>
+      <c r="BD2" s="189" t="s">
         <v>314</v>
       </c>
-      <c r="BF2" s="185" t="s">
+      <c r="BE2" s="189" t="s">
         <v>315</v>
       </c>
-      <c r="BG2" s="185" t="s">
+      <c r="BF2" s="189" t="s">
         <v>316</v>
       </c>
-      <c r="BH2" s="186" t="s">
+      <c r="BG2" s="189" t="s">
         <v>317</v>
       </c>
-      <c r="BI2" s="186" t="s">
+      <c r="BH2" s="190" t="s">
         <v>318</v>
       </c>
-      <c r="BJ2" s="186" t="s">
+      <c r="BI2" s="190" t="s">
         <v>319</v>
+      </c>
+      <c r="BJ2" s="190" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9610,33 +9646,33 @@
       <c r="BA3" s="120"/>
       <c r="BB3" s="120"/>
       <c r="BC3" s="120"/>
-      <c r="BD3" s="187">
+      <c r="BD3" s="191">
         <f t="shared" ref="BD3:BD53" si="0">SUM(B3:BC3)</f>
         <v>1</v>
       </c>
-      <c r="BE3" s="187" cm="1">
+      <c r="BE3" s="191" cm="1">
         <f t="array" ref="BE3">SUMPRODUCT(--(B3:BC3=INT(B3:BC3)),--(B3:BC3&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF3" s="187" cm="1">
+      <c r="BF3" s="191" cm="1">
         <f t="array" ref="BF3">MAX(FREQUENCY(IF((B3:BC3=INT(B3:BC3))*(B3:BC3&gt;0),COLUMN(B3:BC3)),IF((B3:BC3&lt;&gt;INT(B3:BC3))+(B3:BC3&lt;=0),COLUMN(B3:BC3))))</f>
         <v>1</v>
       </c>
-      <c r="BG3" s="188" cm="1">
+      <c r="BG3" s="192" cm="1">
         <f t="array" ref="BG3">SUMPRODUCT(--(B3:AI3=INT(B3:AI3)),--(B3:AI3&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH3" s="189">
+      <c r="BH3" s="193">
         <f t="shared" ref="BH3:BH53" si="1">RANK(BD3,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI3" s="189">
+      <c r="BI3" s="193">
         <f t="shared" ref="BI3:BI53" si="2">RANK(BE3,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ3" s="189">
+      <c r="BJ3" s="193">
         <f t="shared" ref="BJ3:BJ53" si="3">RANK(BF3,BF$3:BF$53,0)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:62">
@@ -9715,7 +9751,9 @@
       <c r="AS4" s="120">
         <v>1</v>
       </c>
-      <c r="AT4" s="120"/>
+      <c r="AT4" s="120">
+        <v>1</v>
+      </c>
       <c r="AU4" s="120"/>
       <c r="AV4" s="120"/>
       <c r="AW4" s="120"/>
@@ -9725,33 +9763,33 @@
       <c r="BA4" s="120"/>
       <c r="BB4" s="120"/>
       <c r="BC4" s="120"/>
-      <c r="BD4" s="187">
+      <c r="BD4" s="191">
         <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="BE4" s="191" cm="1">
+        <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
         <v>15</v>
       </c>
-      <c r="BE4" s="187" cm="1">
-        <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>14</v>
-      </c>
-      <c r="BF4" s="187" cm="1">
+      <c r="BF4" s="191" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
         <v>3</v>
       </c>
-      <c r="BG4" s="188" cm="1">
+      <c r="BG4" s="192" cm="1">
         <f t="array" ref="BG4">SUMPRODUCT(--(B4:AI4=INT(B4:AI4)),--(B4:AI4&gt;0))/34*100%</f>
         <v>0.323529411764706</v>
       </c>
-      <c r="BH4" s="189">
+      <c r="BH4" s="193">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="BI4" s="189">
+      <c r="BI4" s="193">
         <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="BJ4" s="189">
+        <v>6</v>
+      </c>
+      <c r="BJ4" s="193">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:62">
@@ -9816,33 +9854,33 @@
       <c r="BA5" s="120"/>
       <c r="BB5" s="120"/>
       <c r="BC5" s="120"/>
-      <c r="BD5" s="187">
+      <c r="BD5" s="191">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE5" s="187" cm="1">
+      <c r="BE5" s="191" cm="1">
         <f t="array" ref="BE5">SUMPRODUCT(--(B5:BC5=INT(B5:BC5)),--(B5:BC5&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF5" s="187" cm="1">
+      <c r="BF5" s="191" cm="1">
         <f t="array" ref="BF5">MAX(FREQUENCY(IF((B5:BC5=INT(B5:BC5))*(B5:BC5&gt;0),COLUMN(B5:BC5)),IF((B5:BC5&lt;&gt;INT(B5:BC5))+(B5:BC5&lt;=0),COLUMN(B5:BC5))))</f>
         <v>1</v>
       </c>
-      <c r="BG5" s="188" cm="1">
+      <c r="BG5" s="192" cm="1">
         <f t="array" ref="BG5">SUMPRODUCT(--(B5:AI5=INT(B5:AI5)),--(B5:AI5&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH5" s="189">
+      <c r="BH5" s="193">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI5" s="189">
+      <c r="BI5" s="193">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ5" s="189">
+      <c r="BJ5" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:62">
@@ -9905,7 +9943,9 @@
       <c r="AS6" s="120">
         <v>1</v>
       </c>
-      <c r="AT6" s="120"/>
+      <c r="AT6" s="120">
+        <v>1</v>
+      </c>
       <c r="AU6" s="120"/>
       <c r="AV6" s="120"/>
       <c r="AW6" s="120"/>
@@ -9915,33 +9955,33 @@
       <c r="BA6" s="120"/>
       <c r="BB6" s="120"/>
       <c r="BC6" s="120"/>
-      <c r="BD6" s="187">
+      <c r="BD6" s="191">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="BE6" s="187" cm="1">
+        <v>7</v>
+      </c>
+      <c r="BE6" s="191" cm="1">
         <f t="array" ref="BE6">SUMPRODUCT(--(B6:BC6=INT(B6:BC6)),--(B6:BC6&gt;0))</f>
-        <v>6</v>
-      </c>
-      <c r="BF6" s="187" cm="1">
+        <v>7</v>
+      </c>
+      <c r="BF6" s="191" cm="1">
         <f t="array" ref="BF6">MAX(FREQUENCY(IF((B6:BC6=INT(B6:BC6))*(B6:BC6&gt;0),COLUMN(B6:BC6)),IF((B6:BC6&lt;&gt;INT(B6:BC6))+(B6:BC6&lt;=0),COLUMN(B6:BC6))))</f>
-        <v>2</v>
-      </c>
-      <c r="BG6" s="188" cm="1">
+        <v>3</v>
+      </c>
+      <c r="BG6" s="192" cm="1">
         <f t="array" ref="BG6">SUMPRODUCT(--(B6:AI6=INT(B6:AI6)),--(B6:AI6&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH6" s="189">
+      <c r="BH6" s="193">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="BI6" s="189">
+      <c r="BI6" s="193">
         <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-      <c r="BJ6" s="189">
+        <v>20</v>
+      </c>
+      <c r="BJ6" s="193">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:62">
@@ -10008,33 +10048,33 @@
       <c r="BA7" s="120"/>
       <c r="BB7" s="120"/>
       <c r="BC7" s="120"/>
-      <c r="BD7" s="187">
+      <c r="BD7" s="191">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE7" s="187" cm="1">
+      <c r="BE7" s="191" cm="1">
         <f t="array" ref="BE7">SUMPRODUCT(--(B7:BC7=INT(B7:BC7)),--(B7:BC7&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF7" s="187" cm="1">
+      <c r="BF7" s="191" cm="1">
         <f t="array" ref="BF7">MAX(FREQUENCY(IF((B7:BC7=INT(B7:BC7))*(B7:BC7&gt;0),COLUMN(B7:BC7)),IF((B7:BC7&lt;&gt;INT(B7:BC7))+(B7:BC7&lt;=0),COLUMN(B7:BC7))))</f>
         <v>1</v>
       </c>
-      <c r="BG7" s="188" cm="1">
+      <c r="BG7" s="192" cm="1">
         <f t="array" ref="BG7">SUMPRODUCT(--(B7:AI7=INT(B7:AI7)),--(B7:AI7&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH7" s="189">
+      <c r="BH7" s="193">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="BI7" s="189">
+        <v>0</v>
+      </c>
+      <c r="BI7" s="193">
         <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="BJ7" s="189">
+        <v>28</v>
+      </c>
+      <c r="BJ7" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:62">
@@ -10129,7 +10169,9 @@
       <c r="AS8" s="120">
         <v>1</v>
       </c>
-      <c r="AT8" s="120"/>
+      <c r="AT8" s="120">
+        <v>1</v>
+      </c>
       <c r="AU8" s="120"/>
       <c r="AV8" s="120"/>
       <c r="AW8" s="120"/>
@@ -10139,31 +10181,31 @@
       <c r="BA8" s="120"/>
       <c r="BB8" s="120"/>
       <c r="BC8" s="120"/>
-      <c r="BD8" s="187">
+      <c r="BD8" s="191">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="BE8" s="187" cm="1">
+        <v>23</v>
+      </c>
+      <c r="BE8" s="191" cm="1">
         <f t="array" ref="BE8">SUMPRODUCT(--(B8:BC8=INT(B8:BC8)),--(B8:BC8&gt;0))</f>
-        <v>22</v>
-      </c>
-      <c r="BF8" s="187" cm="1">
+        <v>23</v>
+      </c>
+      <c r="BF8" s="191" cm="1">
         <f t="array" ref="BF8">MAX(FREQUENCY(IF((B8:BC8=INT(B8:BC8))*(B8:BC8&gt;0),COLUMN(B8:BC8)),IF((B8:BC8&lt;&gt;INT(B8:BC8))+(B8:BC8&lt;=0),COLUMN(B8:BC8))))</f>
         <v>5</v>
       </c>
-      <c r="BG8" s="188" cm="1">
+      <c r="BG8" s="192" cm="1">
         <f t="array" ref="BG8">SUMPRODUCT(--(B8:AI8=INT(B8:AI8)),--(B8:AI8&gt;0))/34*100%</f>
         <v>0.470588235294118</v>
       </c>
-      <c r="BH8" s="189">
+      <c r="BH8" s="193">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="BI8" s="189">
+      <c r="BI8" s="193">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="BJ8" s="189">
+      <c r="BJ8" s="193">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -10256,33 +10298,33 @@
       <c r="BA9" s="120"/>
       <c r="BB9" s="120"/>
       <c r="BC9" s="120"/>
-      <c r="BD9" s="187">
+      <c r="BD9" s="191">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="BE9" s="187" cm="1">
+      <c r="BE9" s="191" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
         <v>15</v>
       </c>
-      <c r="BF9" s="187" cm="1">
+      <c r="BF9" s="191" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
         <v>3</v>
       </c>
-      <c r="BG9" s="188" cm="1">
+      <c r="BG9" s="192" cm="1">
         <f t="array" ref="BG9">SUMPRODUCT(--(B9:AI9=INT(B9:AI9)),--(B9:AI9&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH9" s="189">
+      <c r="BH9" s="193">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="BI9" s="189">
+        <v>9</v>
+      </c>
+      <c r="BI9" s="193">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="BJ9" s="189">
+      <c r="BJ9" s="193">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:62">
@@ -10345,33 +10387,33 @@
       <c r="BA10" s="120"/>
       <c r="BB10" s="120"/>
       <c r="BC10" s="120"/>
-      <c r="BD10" s="187">
+      <c r="BD10" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE10" s="187" cm="1">
+      <c r="BE10" s="191" cm="1">
         <f t="array" ref="BE10">SUMPRODUCT(--(B10:BC10=INT(B10:BC10)),--(B10:BC10&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF10" s="187" cm="1">
+      <c r="BF10" s="191" cm="1">
         <f t="array" ref="BF10">MAX(FREQUENCY(IF((B10:BC10=INT(B10:BC10))*(B10:BC10&gt;0),COLUMN(B10:BC10)),IF((B10:BC10&lt;&gt;INT(B10:BC10))+(B10:BC10&lt;=0),COLUMN(B10:BC10))))</f>
         <v>1</v>
       </c>
-      <c r="BG10" s="188" cm="1">
+      <c r="BG10" s="192" cm="1">
         <f t="array" ref="BG10">SUMPRODUCT(--(B10:AI10=INT(B10:AI10)),--(B10:AI10&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH10" s="189">
+      <c r="BH10" s="193">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI10" s="189">
+      <c r="BI10" s="193">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ10" s="189">
+      <c r="BJ10" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:62">
@@ -10440,7 +10482,9 @@
       <c r="AS11" s="120">
         <v>1</v>
       </c>
-      <c r="AT11" s="120"/>
+      <c r="AT11" s="120">
+        <v>1</v>
+      </c>
       <c r="AU11" s="120"/>
       <c r="AV11" s="120"/>
       <c r="AW11" s="120"/>
@@ -10450,33 +10494,33 @@
       <c r="BA11" s="120"/>
       <c r="BB11" s="120"/>
       <c r="BC11" s="120"/>
-      <c r="BD11" s="187">
+      <c r="BD11" s="191">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="BE11" s="187" cm="1">
+        <v>10</v>
+      </c>
+      <c r="BE11" s="191" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(--(B11:BC11=INT(B11:BC11)),--(B11:BC11&gt;0))</f>
-        <v>9</v>
-      </c>
-      <c r="BF11" s="187" cm="1">
+        <v>10</v>
+      </c>
+      <c r="BF11" s="191" cm="1">
         <f t="array" ref="BF11">MAX(FREQUENCY(IF((B11:BC11=INT(B11:BC11))*(B11:BC11&gt;0),COLUMN(B11:BC11)),IF((B11:BC11&lt;&gt;INT(B11:BC11))+(B11:BC11&lt;=0),COLUMN(B11:BC11))))</f>
-        <v>1</v>
-      </c>
-      <c r="BG11" s="188" cm="1">
+        <v>2</v>
+      </c>
+      <c r="BG11" s="192" cm="1">
         <f t="array" ref="BG11">SUMPRODUCT(--(B11:AI11=INT(B11:AI11)),--(B11:AI11&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH11" s="189">
+      <c r="BH11" s="193">
         <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="BI11" s="193">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="BJ11" s="193">
+        <f t="shared" si="3"/>
         <v>16</v>
-      </c>
-      <c r="BI11" s="189">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="BJ11" s="189">
-        <f t="shared" si="3"/>
-        <v>21</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:62">
@@ -10541,33 +10585,33 @@
       <c r="BA12" s="120"/>
       <c r="BB12" s="120"/>
       <c r="BC12" s="120"/>
-      <c r="BD12" s="187">
+      <c r="BD12" s="191">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE12" s="187" cm="1">
+      <c r="BE12" s="191" cm="1">
         <f t="array" ref="BE12">SUMPRODUCT(--(B12:BC12=INT(B12:BC12)),--(B12:BC12&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF12" s="187" cm="1">
+      <c r="BF12" s="191" cm="1">
         <f t="array" ref="BF12">MAX(FREQUENCY(IF((B12:BC12=INT(B12:BC12))*(B12:BC12&gt;0),COLUMN(B12:BC12)),IF((B12:BC12&lt;&gt;INT(B12:BC12))+(B12:BC12&lt;=0),COLUMN(B12:BC12))))</f>
         <v>1</v>
       </c>
-      <c r="BG12" s="188" cm="1">
+      <c r="BG12" s="192" cm="1">
         <f t="array" ref="BG12">SUMPRODUCT(--(B12:AI12=INT(B12:AI12)),--(B12:AI12&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH12" s="189">
+      <c r="BH12" s="193">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI12" s="189">
+      <c r="BI12" s="193">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ12" s="189">
+      <c r="BJ12" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:62">
@@ -10650,33 +10694,33 @@
       <c r="BA13" s="120"/>
       <c r="BB13" s="120"/>
       <c r="BC13" s="120"/>
-      <c r="BD13" s="187">
+      <c r="BD13" s="191">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="BE13" s="187" cm="1">
+      <c r="BE13" s="191" cm="1">
         <f t="array" ref="BE13">SUMPRODUCT(--(B13:BC13=INT(B13:BC13)),--(B13:BC13&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF13" s="187" cm="1">
+      <c r="BF13" s="191" cm="1">
         <f t="array" ref="BF13">MAX(FREQUENCY(IF((B13:BC13=INT(B13:BC13))*(B13:BC13&gt;0),COLUMN(B13:BC13)),IF((B13:BC13&lt;&gt;INT(B13:BC13))+(B13:BC13&lt;=0),COLUMN(B13:BC13))))</f>
         <v>1</v>
       </c>
-      <c r="BG13" s="188" cm="1">
+      <c r="BG13" s="192" cm="1">
         <f t="array" ref="BG13">SUMPRODUCT(--(B13:AI13=INT(B13:AI13)),--(B13:AI13&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH13" s="189">
+      <c r="BH13" s="193">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="BI13" s="189">
+      <c r="BI13" s="193">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ13" s="189">
+      <c r="BJ13" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:62">
@@ -10733,7 +10777,9 @@
       </c>
       <c r="AR14" s="120"/>
       <c r="AS14" s="120"/>
-      <c r="AT14" s="120"/>
+      <c r="AT14" s="120">
+        <v>1</v>
+      </c>
       <c r="AU14" s="120"/>
       <c r="AV14" s="120"/>
       <c r="AW14" s="120"/>
@@ -10743,33 +10789,33 @@
       <c r="BA14" s="120"/>
       <c r="BB14" s="120"/>
       <c r="BC14" s="120"/>
-      <c r="BD14" s="187">
+      <c r="BD14" s="191">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="BE14" s="187" cm="1">
+        <v>4</v>
+      </c>
+      <c r="BE14" s="191" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(--(B14:BC14=INT(B14:BC14)),--(B14:BC14&gt;0))</f>
-        <v>3</v>
-      </c>
-      <c r="BF14" s="187" cm="1">
+        <v>4</v>
+      </c>
+      <c r="BF14" s="191" cm="1">
         <f t="array" ref="BF14">MAX(FREQUENCY(IF((B14:BC14=INT(B14:BC14))*(B14:BC14&gt;0),COLUMN(B14:BC14)),IF((B14:BC14&lt;&gt;INT(B14:BC14))+(B14:BC14&lt;=0),COLUMN(B14:BC14))))</f>
         <v>1</v>
       </c>
-      <c r="BG14" s="188" cm="1">
+      <c r="BG14" s="192" cm="1">
         <f t="array" ref="BG14">SUMPRODUCT(--(B14:AI14=INT(B14:AI14)),--(B14:AI14&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH14" s="189">
+      <c r="BH14" s="193">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="BI14" s="189">
+        <v>25</v>
+      </c>
+      <c r="BI14" s="193">
         <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="BJ14" s="189">
+        <v>25</v>
+      </c>
+      <c r="BJ14" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:62">
@@ -10860,33 +10906,33 @@
       <c r="BA15" s="120"/>
       <c r="BB15" s="120"/>
       <c r="BC15" s="120"/>
-      <c r="BD15" s="187">
+      <c r="BD15" s="191">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="BE15" s="187" cm="1">
+      <c r="BE15" s="191" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
         <v>15</v>
       </c>
-      <c r="BF15" s="187" cm="1">
+      <c r="BF15" s="191" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
         <v>3</v>
       </c>
-      <c r="BG15" s="188" cm="1">
+      <c r="BG15" s="192" cm="1">
         <f t="array" ref="BG15">SUMPRODUCT(--(B15:AI15=INT(B15:AI15)),--(B15:AI15&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH15" s="189">
+      <c r="BH15" s="193">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="BI15" s="189">
+      <c r="BI15" s="193">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="BJ15" s="189">
+      <c r="BJ15" s="193">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:62">
@@ -10951,33 +10997,33 @@
       <c r="BA16" s="120"/>
       <c r="BB16" s="120"/>
       <c r="BC16" s="120"/>
-      <c r="BD16" s="187">
+      <c r="BD16" s="191">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE16" s="187" cm="1">
+      <c r="BE16" s="191" cm="1">
         <f t="array" ref="BE16">SUMPRODUCT(--(B16:BC16=INT(B16:BC16)),--(B16:BC16&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF16" s="187" cm="1">
+      <c r="BF16" s="191" cm="1">
         <f t="array" ref="BF16">MAX(FREQUENCY(IF((B16:BC16=INT(B16:BC16))*(B16:BC16&gt;0),COLUMN(B16:BC16)),IF((B16:BC16&lt;&gt;INT(B16:BC16))+(B16:BC16&lt;=0),COLUMN(B16:BC16))))</f>
         <v>1</v>
       </c>
-      <c r="BG16" s="188" cm="1">
+      <c r="BG16" s="192" cm="1">
         <f t="array" ref="BG16">SUMPRODUCT(--(B16:AI16=INT(B16:AI16)),--(B16:AI16&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH16" s="189">
+      <c r="BH16" s="193">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI16" s="189">
+      <c r="BI16" s="193">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ16" s="189">
+      <c r="BJ16" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:62">
@@ -11046,33 +11092,33 @@
       <c r="BA17" s="120"/>
       <c r="BB17" s="120"/>
       <c r="BC17" s="120"/>
-      <c r="BD17" s="187">
+      <c r="BD17" s="191">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE17" s="187" cm="1">
+      <c r="BE17" s="191" cm="1">
         <f t="array" ref="BE17">SUMPRODUCT(--(B17:BC17=INT(B17:BC17)),--(B17:BC17&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF17" s="187" cm="1">
+      <c r="BF17" s="191" cm="1">
         <f t="array" ref="BF17">MAX(FREQUENCY(IF((B17:BC17=INT(B17:BC17))*(B17:BC17&gt;0),COLUMN(B17:BC17)),IF((B17:BC17&lt;&gt;INT(B17:BC17))+(B17:BC17&lt;=0),COLUMN(B17:BC17))))</f>
         <v>1</v>
       </c>
-      <c r="BG17" s="188" cm="1">
+      <c r="BG17" s="192" cm="1">
         <f t="array" ref="BG17">SUMPRODUCT(--(B17:AI17=INT(B17:AI17)),--(B17:AI17&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH17" s="189">
+      <c r="BH17" s="193">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="BI17" s="189">
+      <c r="BI17" s="193">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ17" s="189">
+      <c r="BJ17" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:62">
@@ -11135,33 +11181,33 @@
       <c r="BA18" s="120"/>
       <c r="BB18" s="120"/>
       <c r="BC18" s="120"/>
-      <c r="BD18" s="187">
+      <c r="BD18" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE18" s="187" cm="1">
+      <c r="BE18" s="191" cm="1">
         <f t="array" ref="BE18">SUMPRODUCT(--(B18:BC18=INT(B18:BC18)),--(B18:BC18&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF18" s="187" cm="1">
+      <c r="BF18" s="191" cm="1">
         <f t="array" ref="BF18">MAX(FREQUENCY(IF((B18:BC18=INT(B18:BC18))*(B18:BC18&gt;0),COLUMN(B18:BC18)),IF((B18:BC18&lt;&gt;INT(B18:BC18))+(B18:BC18&lt;=0),COLUMN(B18:BC18))))</f>
         <v>1</v>
       </c>
-      <c r="BG18" s="188" cm="1">
+      <c r="BG18" s="192" cm="1">
         <f t="array" ref="BG18">SUMPRODUCT(--(B18:AI18=INT(B18:AI18)),--(B18:AI18&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH18" s="189">
+      <c r="BH18" s="193">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI18" s="189">
+      <c r="BI18" s="193">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ18" s="189">
+      <c r="BJ18" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:62">
@@ -11232,33 +11278,33 @@
       <c r="BA19" s="120"/>
       <c r="BB19" s="120"/>
       <c r="BC19" s="120"/>
-      <c r="BD19" s="187">
+      <c r="BD19" s="191">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE19" s="187" cm="1">
+      <c r="BE19" s="191" cm="1">
         <f t="array" ref="BE19">SUMPRODUCT(--(B19:BC19=INT(B19:BC19)),--(B19:BC19&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF19" s="187" cm="1">
+      <c r="BF19" s="191" cm="1">
         <f t="array" ref="BF19">MAX(FREQUENCY(IF((B19:BC19=INT(B19:BC19))*(B19:BC19&gt;0),COLUMN(B19:BC19)),IF((B19:BC19&lt;&gt;INT(B19:BC19))+(B19:BC19&lt;=0),COLUMN(B19:BC19))))</f>
         <v>2</v>
       </c>
-      <c r="BG19" s="188" cm="1">
+      <c r="BG19" s="192" cm="1">
         <f t="array" ref="BG19">SUMPRODUCT(--(B19:AI19=INT(B19:AI19)),--(B19:AI19&gt;0))/34*100%</f>
         <v>0.147058823529412</v>
       </c>
-      <c r="BH19" s="189">
+      <c r="BH19" s="193">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="BI19" s="189">
+      <c r="BI19" s="193">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="BJ19" s="189">
+      <c r="BJ19" s="193">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:62">
@@ -11321,33 +11367,33 @@
       <c r="BA20" s="120"/>
       <c r="BB20" s="120"/>
       <c r="BC20" s="120"/>
-      <c r="BD20" s="187">
+      <c r="BD20" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE20" s="187" cm="1">
+      <c r="BE20" s="191" cm="1">
         <f t="array" ref="BE20">SUMPRODUCT(--(B20:BC20=INT(B20:BC20)),--(B20:BC20&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF20" s="187" cm="1">
+      <c r="BF20" s="191" cm="1">
         <f t="array" ref="BF20">MAX(FREQUENCY(IF((B20:BC20=INT(B20:BC20))*(B20:BC20&gt;0),COLUMN(B20:BC20)),IF((B20:BC20&lt;&gt;INT(B20:BC20))+(B20:BC20&lt;=0),COLUMN(B20:BC20))))</f>
         <v>1</v>
       </c>
-      <c r="BG20" s="188" cm="1">
+      <c r="BG20" s="192" cm="1">
         <f t="array" ref="BG20">SUMPRODUCT(--(B20:AI20=INT(B20:AI20)),--(B20:AI20&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH20" s="189">
+      <c r="BH20" s="193">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI20" s="189">
+      <c r="BI20" s="193">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ20" s="189">
+      <c r="BJ20" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="1:62">
@@ -11414,33 +11460,33 @@
       <c r="BA21" s="120"/>
       <c r="BB21" s="120"/>
       <c r="BC21" s="120"/>
-      <c r="BD21" s="187">
+      <c r="BD21" s="191">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="BE21" s="187" cm="1">
+      <c r="BE21" s="191" cm="1">
         <f t="array" ref="BE21">SUMPRODUCT(--(B21:BC21=INT(B21:BC21)),--(B21:BC21&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF21" s="187" cm="1">
+      <c r="BF21" s="191" cm="1">
         <f t="array" ref="BF21">MAX(FREQUENCY(IF((B21:BC21=INT(B21:BC21))*(B21:BC21&gt;0),COLUMN(B21:BC21)),IF((B21:BC21&lt;&gt;INT(B21:BC21))+(B21:BC21&lt;=0),COLUMN(B21:BC21))))</f>
         <v>1</v>
       </c>
-      <c r="BG21" s="188" cm="1">
+      <c r="BG21" s="192" cm="1">
         <f t="array" ref="BG21">SUMPRODUCT(--(B21:AI21=INT(B21:AI21)),--(B21:AI21&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH21" s="189">
+      <c r="BH21" s="193">
         <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="BI21" s="189">
+        <v>30</v>
+      </c>
+      <c r="BI21" s="193">
         <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="BJ21" s="189">
+        <v>28</v>
+      </c>
+      <c r="BJ21" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="1:62">
@@ -11525,37 +11571,37 @@
       <c r="BA22" s="120"/>
       <c r="BB22" s="120"/>
       <c r="BC22" s="120"/>
-      <c r="BD22" s="187">
+      <c r="BD22" s="191">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="BE22" s="187" cm="1">
+      <c r="BE22" s="191" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
         <v>12</v>
       </c>
-      <c r="BF22" s="187" cm="1">
+      <c r="BF22" s="191" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
         <v>4</v>
       </c>
-      <c r="BG22" s="188" cm="1">
+      <c r="BG22" s="192" cm="1">
         <f t="array" ref="BG22">SUMPRODUCT(--(B22:AI22=INT(B22:AI22)),--(B22:AI22&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH22" s="189">
+      <c r="BH22" s="193">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="BI22" s="189">
+        <v>9</v>
+      </c>
+      <c r="BI22" s="193">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="BJ22" s="189">
+      <c r="BJ22" s="193">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:62">
-      <c r="A23" s="190">
+      <c r="A23" s="194">
         <v>21</v>
       </c>
       <c r="B23" s="120"/>
@@ -11602,7 +11648,9 @@
       <c r="AQ23" s="120"/>
       <c r="AR23" s="120"/>
       <c r="AS23" s="120"/>
-      <c r="AT23" s="120"/>
+      <c r="AT23" s="120">
+        <v>1</v>
+      </c>
       <c r="AU23" s="120"/>
       <c r="AV23" s="120"/>
       <c r="AW23" s="120"/>
@@ -11612,33 +11660,33 @@
       <c r="BA23" s="120"/>
       <c r="BB23" s="120"/>
       <c r="BC23" s="120"/>
-      <c r="BD23" s="187">
+      <c r="BD23" s="191">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="BE23" s="187" cm="1">
+        <v>1</v>
+      </c>
+      <c r="BE23" s="191" cm="1">
         <f t="array" ref="BE23">SUMPRODUCT(--(B23:BC23=INT(B23:BC23)),--(B23:BC23&gt;0))</f>
-        <v>0</v>
-      </c>
-      <c r="BF23" s="187" cm="1">
+        <v>1</v>
+      </c>
+      <c r="BF23" s="191" cm="1">
         <f t="array" ref="BF23">MAX(FREQUENCY(IF((B23:BC23=INT(B23:BC23))*(B23:BC23&gt;0),COLUMN(B23:BC23)),IF((B23:BC23&lt;&gt;INT(B23:BC23))+(B23:BC23&lt;=0),COLUMN(B23:BC23))))</f>
-        <v>0</v>
-      </c>
-      <c r="BG23" s="188" cm="1">
+        <v>1</v>
+      </c>
+      <c r="BG23" s="192" cm="1">
         <f t="array" ref="BG23">SUMPRODUCT(--(B23:AI23=INT(B23:AI23)),--(B23:AI23&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH23" s="189">
+      <c r="BH23" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI23" s="189">
+        <v>34</v>
+      </c>
+      <c r="BI23" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ23" s="189">
+        <v>34</v>
+      </c>
+      <c r="BJ23" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" customHeight="1" spans="1:62">
@@ -11715,33 +11763,33 @@
       <c r="BA24" s="120"/>
       <c r="BB24" s="120"/>
       <c r="BC24" s="120"/>
-      <c r="BD24" s="187">
+      <c r="BD24" s="191">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="BE24" s="187" cm="1">
+      <c r="BE24" s="191" cm="1">
         <f t="array" ref="BE24">SUMPRODUCT(--(B24:BC24=INT(B24:BC24)),--(B24:BC24&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="BF24" s="187" cm="1">
+      <c r="BF24" s="191" cm="1">
         <f t="array" ref="BF24">MAX(FREQUENCY(IF((B24:BC24=INT(B24:BC24))*(B24:BC24&gt;0),COLUMN(B24:BC24)),IF((B24:BC24&lt;&gt;INT(B24:BC24))+(B24:BC24&lt;=0),COLUMN(B24:BC24))))</f>
         <v>3</v>
       </c>
-      <c r="BG24" s="188" cm="1">
+      <c r="BG24" s="192" cm="1">
         <f t="array" ref="BG24">SUMPRODUCT(--(B24:AI24=INT(B24:AI24)),--(B24:AI24&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH24" s="189">
+      <c r="BH24" s="193">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="BI24" s="189">
+      <c r="BI24" s="193">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="BJ24" s="189">
+      <c r="BJ24" s="193">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:62">
@@ -11804,37 +11852,37 @@
       <c r="BA25" s="120"/>
       <c r="BB25" s="120"/>
       <c r="BC25" s="120"/>
-      <c r="BD25" s="187">
+      <c r="BD25" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE25" s="187" cm="1">
+      <c r="BE25" s="191" cm="1">
         <f t="array" ref="BE25">SUMPRODUCT(--(B25:BC25=INT(B25:BC25)),--(B25:BC25&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF25" s="187" cm="1">
+      <c r="BF25" s="191" cm="1">
         <f t="array" ref="BF25">MAX(FREQUENCY(IF((B25:BC25=INT(B25:BC25))*(B25:BC25&gt;0),COLUMN(B25:BC25)),IF((B25:BC25&lt;&gt;INT(B25:BC25))+(B25:BC25&lt;=0),COLUMN(B25:BC25))))</f>
         <v>1</v>
       </c>
-      <c r="BG25" s="188" cm="1">
+      <c r="BG25" s="192" cm="1">
         <f t="array" ref="BG25">SUMPRODUCT(--(B25:AI25=INT(B25:AI25)),--(B25:AI25&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH25" s="189">
+      <c r="BH25" s="193">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI25" s="189">
+      <c r="BI25" s="193">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ25" s="189">
+      <c r="BJ25" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:62">
-      <c r="A26" s="190">
+      <c r="A26" s="195">
         <v>24</v>
       </c>
       <c r="B26" s="120"/>
@@ -11891,37 +11939,37 @@
       <c r="BA26" s="120"/>
       <c r="BB26" s="120"/>
       <c r="BC26" s="120"/>
-      <c r="BD26" s="187">
+      <c r="BD26" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="187" cm="1">
+      <c r="BE26" s="191" cm="1">
         <f t="array" ref="BE26">SUMPRODUCT(--(B26:BC26=INT(B26:BC26)),--(B26:BC26&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF26" s="187" cm="1">
+      <c r="BF26" s="191" cm="1">
         <f t="array" ref="BF26">MAX(FREQUENCY(IF((B26:BC26=INT(B26:BC26))*(B26:BC26&gt;0),COLUMN(B26:BC26)),IF((B26:BC26&lt;&gt;INT(B26:BC26))+(B26:BC26&lt;=0),COLUMN(B26:BC26))))</f>
         <v>0</v>
       </c>
-      <c r="BG26" s="188" cm="1">
+      <c r="BG26" s="192" cm="1">
         <f t="array" ref="BG26">SUMPRODUCT(--(B26:AI26=INT(B26:AI26)),--(B26:AI26&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH26" s="189">
+      <c r="BH26" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI26" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI26" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ26" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ26" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:62">
-      <c r="A27" s="190">
+      <c r="A27" s="195">
         <v>25</v>
       </c>
       <c r="B27" s="120"/>
@@ -11978,33 +12026,33 @@
       <c r="BA27" s="120"/>
       <c r="BB27" s="120"/>
       <c r="BC27" s="120"/>
-      <c r="BD27" s="187">
+      <c r="BD27" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE27" s="187" cm="1">
+      <c r="BE27" s="191" cm="1">
         <f t="array" ref="BE27">SUMPRODUCT(--(B27:BC27=INT(B27:BC27)),--(B27:BC27&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF27" s="187" cm="1">
+      <c r="BF27" s="191" cm="1">
         <f t="array" ref="BF27">MAX(FREQUENCY(IF((B27:BC27=INT(B27:BC27))*(B27:BC27&gt;0),COLUMN(B27:BC27)),IF((B27:BC27&lt;&gt;INT(B27:BC27))+(B27:BC27&lt;=0),COLUMN(B27:BC27))))</f>
         <v>0</v>
       </c>
-      <c r="BG27" s="188" cm="1">
+      <c r="BG27" s="192" cm="1">
         <f t="array" ref="BG27">SUMPRODUCT(--(B27:AI27=INT(B27:AI27)),--(B27:AI27&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH27" s="189">
+      <c r="BH27" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI27" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI27" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ27" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ27" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:62">
@@ -12085,33 +12133,33 @@
       <c r="BA28" s="120"/>
       <c r="BB28" s="120"/>
       <c r="BC28" s="120"/>
-      <c r="BD28" s="187">
+      <c r="BD28" s="191">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="BE28" s="187" cm="1">
+      <c r="BE28" s="191" cm="1">
         <f t="array" ref="BE28">SUMPRODUCT(--(B28:BC28=INT(B28:BC28)),--(B28:BC28&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BF28" s="187" cm="1">
+      <c r="BF28" s="191" cm="1">
         <f t="array" ref="BF28">MAX(FREQUENCY(IF((B28:BC28=INT(B28:BC28))*(B28:BC28&gt;0),COLUMN(B28:BC28)),IF((B28:BC28&lt;&gt;INT(B28:BC28))+(B28:BC28&lt;=0),COLUMN(B28:BC28))))</f>
         <v>2</v>
       </c>
-      <c r="BG28" s="188" cm="1">
+      <c r="BG28" s="192" cm="1">
         <f t="array" ref="BG28">SUMPRODUCT(--(B28:AI28=INT(B28:AI28)),--(B28:AI28&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH28" s="189">
+      <c r="BH28" s="193">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="BI28" s="189">
+      <c r="BI28" s="193">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="BJ28" s="189">
+      <c r="BJ28" s="193">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:62">
@@ -12180,7 +12228,9 @@
       <c r="AS29" s="120">
         <v>1</v>
       </c>
-      <c r="AT29" s="120"/>
+      <c r="AT29" s="120">
+        <v>1</v>
+      </c>
       <c r="AU29" s="120"/>
       <c r="AV29" s="120"/>
       <c r="AW29" s="120"/>
@@ -12190,33 +12240,33 @@
       <c r="BA29" s="120"/>
       <c r="BB29" s="120"/>
       <c r="BC29" s="120"/>
-      <c r="BD29" s="187">
+      <c r="BD29" s="191">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="BE29" s="187" cm="1">
+        <v>10</v>
+      </c>
+      <c r="BE29" s="191" cm="1">
         <f t="array" ref="BE29">SUMPRODUCT(--(B29:BC29=INT(B29:BC29)),--(B29:BC29&gt;0))</f>
-        <v>9</v>
-      </c>
-      <c r="BF29" s="187" cm="1">
+        <v>10</v>
+      </c>
+      <c r="BF29" s="191" cm="1">
         <f t="array" ref="BF29">MAX(FREQUENCY(IF((B29:BC29=INT(B29:BC29))*(B29:BC29&gt;0),COLUMN(B29:BC29)),IF((B29:BC29&lt;&gt;INT(B29:BC29))+(B29:BC29&lt;=0),COLUMN(B29:BC29))))</f>
-        <v>3</v>
-      </c>
-      <c r="BG29" s="188" cm="1">
+        <v>4</v>
+      </c>
+      <c r="BG29" s="192" cm="1">
         <f t="array" ref="BG29">SUMPRODUCT(--(B29:AI29=INT(B29:AI29)),--(B29:AI29&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH29" s="189">
+      <c r="BH29" s="193">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="BI29" s="189">
+        <v>15</v>
+      </c>
+      <c r="BI29" s="193">
         <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="BJ29" s="189">
+        <v>15</v>
+      </c>
+      <c r="BJ29" s="193">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:62">
@@ -12291,31 +12341,31 @@
       <c r="BA30" s="120"/>
       <c r="BB30" s="120"/>
       <c r="BC30" s="120"/>
-      <c r="BD30" s="187">
+      <c r="BD30" s="191">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="BE30" s="187" cm="1">
+      <c r="BE30" s="191" cm="1">
         <f t="array" ref="BE30">SUMPRODUCT(--(B30:BC30=INT(B30:BC30)),--(B30:BC30&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF30" s="187" cm="1">
+      <c r="BF30" s="191" cm="1">
         <f t="array" ref="BF30">MAX(FREQUENCY(IF((B30:BC30=INT(B30:BC30))*(B30:BC30&gt;0),COLUMN(B30:BC30)),IF((B30:BC30&lt;&gt;INT(B30:BC30))+(B30:BC30&lt;=0),COLUMN(B30:BC30))))</f>
         <v>4</v>
       </c>
-      <c r="BG30" s="188" cm="1">
+      <c r="BG30" s="192" cm="1">
         <f t="array" ref="BG30">SUMPRODUCT(--(B30:AI30=INT(B30:AI30)),--(B30:AI30&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH30" s="189">
+      <c r="BH30" s="193">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="BI30" s="189">
+      <c r="BI30" s="193">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="BJ30" s="189">
+      <c r="BJ30" s="193">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
@@ -12400,33 +12450,33 @@
       <c r="BA31" s="120"/>
       <c r="BB31" s="120"/>
       <c r="BC31" s="120"/>
-      <c r="BD31" s="187">
+      <c r="BD31" s="191">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="BE31" s="187" cm="1">
+      <c r="BE31" s="191" cm="1">
         <f t="array" ref="BE31">SUMPRODUCT(--(B31:BC31=INT(B31:BC31)),--(B31:BC31&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF31" s="187" cm="1">
+      <c r="BF31" s="191" cm="1">
         <f t="array" ref="BF31">MAX(FREQUENCY(IF((B31:BC31=INT(B31:BC31))*(B31:BC31&gt;0),COLUMN(B31:BC31)),IF((B31:BC31&lt;&gt;INT(B31:BC31))+(B31:BC31&lt;=0),COLUMN(B31:BC31))))</f>
         <v>2</v>
       </c>
-      <c r="BG31" s="188" cm="1">
+      <c r="BG31" s="192" cm="1">
         <f t="array" ref="BG31">SUMPRODUCT(--(B31:AI31=INT(B31:AI31)),--(B31:AI31&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH31" s="189">
+      <c r="BH31" s="193">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="BI31" s="189">
+      <c r="BI31" s="193">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ31" s="189">
+      <c r="BJ31" s="193">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:62">
@@ -12509,33 +12559,33 @@
       <c r="BA32" s="120"/>
       <c r="BB32" s="120"/>
       <c r="BC32" s="120"/>
-      <c r="BD32" s="187">
+      <c r="BD32" s="191">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="BE32" s="187" cm="1">
+      <c r="BE32" s="191" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF32" s="187" cm="1">
+      <c r="BF32" s="191" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
         <v>3</v>
       </c>
-      <c r="BG32" s="188" cm="1">
+      <c r="BG32" s="192" cm="1">
         <f t="array" ref="BG32">SUMPRODUCT(--(B32:AI32=INT(B32:AI32)),--(B32:AI32&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH32" s="189">
+      <c r="BH32" s="193">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="BI32" s="189">
+      <c r="BI32" s="193">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ32" s="189">
+      <c r="BJ32" s="193">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:62">
@@ -12606,37 +12656,37 @@
       <c r="BA33" s="120"/>
       <c r="BB33" s="120"/>
       <c r="BC33" s="120"/>
-      <c r="BD33" s="187">
+      <c r="BD33" s="191">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE33" s="187" cm="1">
+      <c r="BE33" s="191" cm="1">
         <f t="array" ref="BE33">SUMPRODUCT(--(B33:BC33=INT(B33:BC33)),--(B33:BC33&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF33" s="187" cm="1">
+      <c r="BF33" s="191" cm="1">
         <f t="array" ref="BF33">MAX(FREQUENCY(IF((B33:BC33=INT(B33:BC33))*(B33:BC33&gt;0),COLUMN(B33:BC33)),IF((B33:BC33&lt;&gt;INT(B33:BC33))+(B33:BC33&lt;=0),COLUMN(B33:BC33))))</f>
         <v>1</v>
       </c>
-      <c r="BG33" s="188" cm="1">
+      <c r="BG33" s="192" cm="1">
         <f t="array" ref="BG33">SUMPRODUCT(--(B33:AI33=INT(B33:AI33)),--(B33:AI33&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH33" s="189">
+      <c r="BH33" s="193">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="BI33" s="189">
+      <c r="BI33" s="193">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="BJ33" s="189">
+      <c r="BJ33" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:62">
-      <c r="A34" s="190">
+      <c r="A34" s="195">
         <v>32</v>
       </c>
       <c r="B34" s="120"/>
@@ -12693,120 +12743,120 @@
       <c r="BA34" s="120"/>
       <c r="BB34" s="120"/>
       <c r="BC34" s="120"/>
-      <c r="BD34" s="187">
+      <c r="BD34" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE34" s="187" cm="1">
+      <c r="BE34" s="191" cm="1">
         <f t="array" ref="BE34">SUMPRODUCT(--(B34:BC34=INT(B34:BC34)),--(B34:BC34&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF34" s="187" cm="1">
+      <c r="BF34" s="191" cm="1">
         <f t="array" ref="BF34">MAX(FREQUENCY(IF((B34:BC34=INT(B34:BC34))*(B34:BC34&gt;0),COLUMN(B34:BC34)),IF((B34:BC34&lt;&gt;INT(B34:BC34))+(B34:BC34&lt;=0),COLUMN(B34:BC34))))</f>
         <v>0</v>
       </c>
-      <c r="BG34" s="188" cm="1">
+      <c r="BG34" s="192" cm="1">
         <f t="array" ref="BG34">SUMPRODUCT(--(B34:AI34=INT(B34:AI34)),--(B34:AI34&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH34" s="189">
+      <c r="BH34" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI34" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI34" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ34" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ34" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:62">
-      <c r="A35" s="191">
+      <c r="A35" s="196">
         <v>33</v>
       </c>
-      <c r="B35" s="191"/>
-      <c r="C35" s="191"/>
-      <c r="D35" s="191"/>
-      <c r="E35" s="191"/>
-      <c r="F35" s="191"/>
-      <c r="G35" s="191"/>
-      <c r="H35" s="191"/>
-      <c r="I35" s="191"/>
-      <c r="J35" s="191"/>
-      <c r="K35" s="191"/>
-      <c r="L35" s="191"/>
-      <c r="M35" s="191"/>
-      <c r="N35" s="191"/>
-      <c r="O35" s="191"/>
-      <c r="P35" s="191"/>
-      <c r="Q35" s="191"/>
-      <c r="R35" s="191"/>
-      <c r="S35" s="191"/>
-      <c r="T35" s="191"/>
-      <c r="U35" s="191"/>
-      <c r="V35" s="191"/>
-      <c r="W35" s="191"/>
-      <c r="X35" s="191"/>
-      <c r="Y35" s="191"/>
-      <c r="Z35" s="191"/>
-      <c r="AA35" s="191"/>
-      <c r="AB35" s="191"/>
-      <c r="AC35" s="191"/>
-      <c r="AD35" s="191"/>
-      <c r="AE35" s="191"/>
-      <c r="AF35" s="191"/>
-      <c r="AG35" s="191"/>
-      <c r="AH35" s="191"/>
-      <c r="AI35" s="191"/>
-      <c r="AJ35" s="191"/>
-      <c r="AK35" s="191"/>
-      <c r="AL35" s="191"/>
-      <c r="AM35" s="191"/>
-      <c r="AN35" s="191"/>
-      <c r="AO35" s="191"/>
-      <c r="AP35" s="191"/>
-      <c r="AQ35" s="191"/>
-      <c r="AR35" s="191"/>
-      <c r="AS35" s="191"/>
-      <c r="AT35" s="191"/>
-      <c r="AU35" s="191"/>
-      <c r="AV35" s="191"/>
-      <c r="AW35" s="191"/>
-      <c r="AX35" s="191"/>
-      <c r="AY35" s="191"/>
-      <c r="AZ35" s="191"/>
-      <c r="BA35" s="191"/>
-      <c r="BB35" s="191"/>
-      <c r="BC35" s="191"/>
-      <c r="BD35" s="187">
+      <c r="B35" s="196"/>
+      <c r="C35" s="196"/>
+      <c r="D35" s="196"/>
+      <c r="E35" s="196"/>
+      <c r="F35" s="196"/>
+      <c r="G35" s="196"/>
+      <c r="H35" s="196"/>
+      <c r="I35" s="196"/>
+      <c r="J35" s="196"/>
+      <c r="K35" s="196"/>
+      <c r="L35" s="196"/>
+      <c r="M35" s="196"/>
+      <c r="N35" s="196"/>
+      <c r="O35" s="196"/>
+      <c r="P35" s="196"/>
+      <c r="Q35" s="196"/>
+      <c r="R35" s="196"/>
+      <c r="S35" s="196"/>
+      <c r="T35" s="196"/>
+      <c r="U35" s="196"/>
+      <c r="V35" s="196"/>
+      <c r="W35" s="196"/>
+      <c r="X35" s="196"/>
+      <c r="Y35" s="196"/>
+      <c r="Z35" s="196"/>
+      <c r="AA35" s="196"/>
+      <c r="AB35" s="196"/>
+      <c r="AC35" s="196"/>
+      <c r="AD35" s="196"/>
+      <c r="AE35" s="196"/>
+      <c r="AF35" s="196"/>
+      <c r="AG35" s="196"/>
+      <c r="AH35" s="196"/>
+      <c r="AI35" s="196"/>
+      <c r="AJ35" s="196"/>
+      <c r="AK35" s="196"/>
+      <c r="AL35" s="196"/>
+      <c r="AM35" s="196"/>
+      <c r="AN35" s="196"/>
+      <c r="AO35" s="196"/>
+      <c r="AP35" s="196"/>
+      <c r="AQ35" s="196"/>
+      <c r="AR35" s="196"/>
+      <c r="AS35" s="196"/>
+      <c r="AT35" s="196"/>
+      <c r="AU35" s="196"/>
+      <c r="AV35" s="196"/>
+      <c r="AW35" s="196"/>
+      <c r="AX35" s="196"/>
+      <c r="AY35" s="196"/>
+      <c r="AZ35" s="196"/>
+      <c r="BA35" s="196"/>
+      <c r="BB35" s="196"/>
+      <c r="BC35" s="196"/>
+      <c r="BD35" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="187" cm="1">
+      <c r="BE35" s="191" cm="1">
         <f t="array" ref="BE35">SUMPRODUCT(--(B35:BC35=INT(B35:BC35)),--(B35:BC35&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF35" s="187" cm="1">
+      <c r="BF35" s="191" cm="1">
         <f t="array" ref="BF35">MAX(FREQUENCY(IF((B35:BC35=INT(B35:BC35))*(B35:BC35&gt;0),COLUMN(B35:BC35)),IF((B35:BC35&lt;&gt;INT(B35:BC35))+(B35:BC35&lt;=0),COLUMN(B35:BC35))))</f>
         <v>0</v>
       </c>
-      <c r="BG35" s="188" cm="1">
+      <c r="BG35" s="192" cm="1">
         <f t="array" ref="BG35">SUMPRODUCT(--(B35:AI35=INT(B35:AI35)),--(B35:AI35&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH35" s="189">
+      <c r="BH35" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI35" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI35" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ35" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ35" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:62">
@@ -12869,33 +12919,33 @@
       <c r="BA36" s="120"/>
       <c r="BB36" s="120"/>
       <c r="BC36" s="120"/>
-      <c r="BD36" s="187">
+      <c r="BD36" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE36" s="187" cm="1">
+      <c r="BE36" s="191" cm="1">
         <f t="array" ref="BE36">SUMPRODUCT(--(B36:BC36=INT(B36:BC36)),--(B36:BC36&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF36" s="187" cm="1">
+      <c r="BF36" s="191" cm="1">
         <f t="array" ref="BF36">MAX(FREQUENCY(IF((B36:BC36=INT(B36:BC36))*(B36:BC36&gt;0),COLUMN(B36:BC36)),IF((B36:BC36&lt;&gt;INT(B36:BC36))+(B36:BC36&lt;=0),COLUMN(B36:BC36))))</f>
         <v>1</v>
       </c>
-      <c r="BG36" s="188" cm="1">
+      <c r="BG36" s="192" cm="1">
         <f t="array" ref="BG36">SUMPRODUCT(--(B36:AI36=INT(B36:AI36)),--(B36:AI36&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH36" s="189">
+      <c r="BH36" s="193">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI36" s="189">
+      <c r="BI36" s="193">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ36" s="189">
+      <c r="BJ36" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:62">
@@ -12972,33 +13022,33 @@
       <c r="BA37" s="120"/>
       <c r="BB37" s="120"/>
       <c r="BC37" s="120"/>
-      <c r="BD37" s="187">
+      <c r="BD37" s="191">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="BE37" s="187" cm="1">
+      <c r="BE37" s="191" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="BF37" s="187" cm="1">
+      <c r="BF37" s="191" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
         <v>3</v>
       </c>
-      <c r="BG37" s="188" cm="1">
+      <c r="BG37" s="192" cm="1">
         <f t="array" ref="BG37">SUMPRODUCT(--(B37:AI37=INT(B37:AI37)),--(B37:AI37&gt;0))/34*100%</f>
         <v>0.176470588235294</v>
       </c>
-      <c r="BH37" s="189">
+      <c r="BH37" s="193">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="BI37" s="189">
+        <v>18</v>
+      </c>
+      <c r="BI37" s="193">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="BJ37" s="189">
+      <c r="BJ37" s="193">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:62">
@@ -13065,120 +13115,120 @@
       <c r="BA38" s="120"/>
       <c r="BB38" s="120"/>
       <c r="BC38" s="120"/>
-      <c r="BD38" s="187">
+      <c r="BD38" s="191">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE38" s="187" cm="1">
+      <c r="BE38" s="191" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(--(B38:BC38=INT(B38:BC38)),--(B38:BC38&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF38" s="187" cm="1">
+      <c r="BF38" s="191" cm="1">
         <f t="array" ref="BF38">MAX(FREQUENCY(IF((B38:BC38=INT(B38:BC38))*(B38:BC38&gt;0),COLUMN(B38:BC38)),IF((B38:BC38&lt;&gt;INT(B38:BC38))+(B38:BC38&lt;=0),COLUMN(B38:BC38))))</f>
         <v>1</v>
       </c>
-      <c r="BG38" s="188" cm="1">
+      <c r="BG38" s="192" cm="1">
         <f t="array" ref="BG38">SUMPRODUCT(--(B38:AI38=INT(B38:AI38)),--(B38:AI38&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH38" s="189">
+      <c r="BH38" s="193">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="BI38" s="189">
+      <c r="BI38" s="193">
         <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="BJ38" s="189">
+        <v>28</v>
+      </c>
+      <c r="BJ38" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:62">
-      <c r="A39" s="191">
+      <c r="A39" s="196">
         <v>37</v>
       </c>
-      <c r="B39" s="191"/>
-      <c r="C39" s="191"/>
-      <c r="D39" s="191"/>
-      <c r="E39" s="191"/>
-      <c r="F39" s="191"/>
-      <c r="G39" s="191"/>
-      <c r="H39" s="191"/>
-      <c r="I39" s="191"/>
-      <c r="J39" s="191"/>
-      <c r="K39" s="191"/>
-      <c r="L39" s="191"/>
-      <c r="M39" s="191"/>
-      <c r="N39" s="191"/>
-      <c r="O39" s="191"/>
-      <c r="P39" s="191"/>
-      <c r="Q39" s="191"/>
-      <c r="R39" s="191"/>
-      <c r="S39" s="191"/>
-      <c r="T39" s="191"/>
-      <c r="U39" s="191"/>
-      <c r="V39" s="191"/>
-      <c r="W39" s="191"/>
-      <c r="X39" s="191"/>
-      <c r="Y39" s="191"/>
-      <c r="Z39" s="191"/>
-      <c r="AA39" s="191"/>
-      <c r="AB39" s="191"/>
-      <c r="AC39" s="191"/>
-      <c r="AD39" s="191"/>
-      <c r="AE39" s="191"/>
-      <c r="AF39" s="191"/>
-      <c r="AG39" s="191"/>
-      <c r="AH39" s="191"/>
-      <c r="AI39" s="191"/>
-      <c r="AJ39" s="191"/>
-      <c r="AK39" s="191"/>
-      <c r="AL39" s="191"/>
-      <c r="AM39" s="191"/>
-      <c r="AN39" s="191"/>
-      <c r="AO39" s="191"/>
-      <c r="AP39" s="191"/>
-      <c r="AQ39" s="191"/>
-      <c r="AR39" s="191"/>
-      <c r="AS39" s="191"/>
-      <c r="AT39" s="191"/>
-      <c r="AU39" s="191"/>
-      <c r="AV39" s="191"/>
-      <c r="AW39" s="191"/>
-      <c r="AX39" s="191"/>
-      <c r="AY39" s="191"/>
-      <c r="AZ39" s="191"/>
-      <c r="BA39" s="191"/>
-      <c r="BB39" s="191"/>
-      <c r="BC39" s="191"/>
-      <c r="BD39" s="187">
+      <c r="B39" s="196"/>
+      <c r="C39" s="196"/>
+      <c r="D39" s="196"/>
+      <c r="E39" s="196"/>
+      <c r="F39" s="196"/>
+      <c r="G39" s="196"/>
+      <c r="H39" s="196"/>
+      <c r="I39" s="196"/>
+      <c r="J39" s="196"/>
+      <c r="K39" s="196"/>
+      <c r="L39" s="196"/>
+      <c r="M39" s="196"/>
+      <c r="N39" s="196"/>
+      <c r="O39" s="196"/>
+      <c r="P39" s="196"/>
+      <c r="Q39" s="196"/>
+      <c r="R39" s="196"/>
+      <c r="S39" s="196"/>
+      <c r="T39" s="196"/>
+      <c r="U39" s="196"/>
+      <c r="V39" s="196"/>
+      <c r="W39" s="196"/>
+      <c r="X39" s="196"/>
+      <c r="Y39" s="196"/>
+      <c r="Z39" s="196"/>
+      <c r="AA39" s="196"/>
+      <c r="AB39" s="196"/>
+      <c r="AC39" s="196"/>
+      <c r="AD39" s="196"/>
+      <c r="AE39" s="196"/>
+      <c r="AF39" s="196"/>
+      <c r="AG39" s="196"/>
+      <c r="AH39" s="196"/>
+      <c r="AI39" s="196"/>
+      <c r="AJ39" s="196"/>
+      <c r="AK39" s="196"/>
+      <c r="AL39" s="196"/>
+      <c r="AM39" s="196"/>
+      <c r="AN39" s="196"/>
+      <c r="AO39" s="196"/>
+      <c r="AP39" s="196"/>
+      <c r="AQ39" s="196"/>
+      <c r="AR39" s="196"/>
+      <c r="AS39" s="196"/>
+      <c r="AT39" s="196"/>
+      <c r="AU39" s="196"/>
+      <c r="AV39" s="196"/>
+      <c r="AW39" s="196"/>
+      <c r="AX39" s="196"/>
+      <c r="AY39" s="196"/>
+      <c r="AZ39" s="196"/>
+      <c r="BA39" s="196"/>
+      <c r="BB39" s="196"/>
+      <c r="BC39" s="196"/>
+      <c r="BD39" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE39" s="187" cm="1">
+      <c r="BE39" s="191" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(--(B39:BC39=INT(B39:BC39)),--(B39:BC39&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF39" s="187" cm="1">
+      <c r="BF39" s="191" cm="1">
         <f t="array" ref="BF39">MAX(FREQUENCY(IF((B39:BC39=INT(B39:BC39))*(B39:BC39&gt;0),COLUMN(B39:BC39)),IF((B39:BC39&lt;&gt;INT(B39:BC39))+(B39:BC39&lt;=0),COLUMN(B39:BC39))))</f>
         <v>0</v>
       </c>
-      <c r="BG39" s="188" cm="1">
+      <c r="BG39" s="192" cm="1">
         <f t="array" ref="BG39">SUMPRODUCT(--(B39:AI39=INT(B39:AI39)),--(B39:AI39&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH39" s="192">
+      <c r="BH39" s="197">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI39" s="192">
+        <v>42</v>
+      </c>
+      <c r="BI39" s="197">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ39" s="192">
+        <v>42</v>
+      </c>
+      <c r="BJ39" s="197">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:62">
@@ -13287,31 +13337,31 @@
       <c r="BA40" s="120"/>
       <c r="BB40" s="120"/>
       <c r="BC40" s="120"/>
-      <c r="BD40" s="187">
+      <c r="BD40" s="191">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="BE40" s="187" cm="1">
+      <c r="BE40" s="191" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
         <v>24</v>
       </c>
-      <c r="BF40" s="187" cm="1">
+      <c r="BF40" s="191" cm="1">
         <f t="array" ref="BF40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
         <v>12</v>
       </c>
-      <c r="BG40" s="188" cm="1">
+      <c r="BG40" s="192" cm="1">
         <f t="array" ref="BG40">SUMPRODUCT(--(B40:AI40=INT(B40:AI40)),--(B40:AI40&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH40" s="189">
+      <c r="BH40" s="193">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="BI40" s="189">
+      <c r="BI40" s="193">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="BJ40" s="189">
+      <c r="BJ40" s="193">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -13402,33 +13452,33 @@
       <c r="BA41" s="120"/>
       <c r="BB41" s="120"/>
       <c r="BC41" s="120"/>
-      <c r="BD41" s="187">
+      <c r="BD41" s="191">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="BE41" s="187" cm="1">
+      <c r="BE41" s="191" cm="1">
         <f t="array" ref="BE41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
         <v>14</v>
       </c>
-      <c r="BF41" s="187" cm="1">
+      <c r="BF41" s="191" cm="1">
         <f t="array" ref="BF41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
         <v>2</v>
       </c>
-      <c r="BG41" s="188" cm="1">
+      <c r="BG41" s="192" cm="1">
         <f t="array" ref="BG41">SUMPRODUCT(--(B41:AI41=INT(B41:AI41)),--(B41:AI41&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH41" s="189">
+      <c r="BH41" s="193">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="BI41" s="189">
+      <c r="BI41" s="193">
         <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="BJ41" s="189">
+        <v>9</v>
+      </c>
+      <c r="BJ41" s="193">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:62">
@@ -13511,7 +13561,9 @@
         <v>2</v>
       </c>
       <c r="AS42" s="120"/>
-      <c r="AT42" s="120"/>
+      <c r="AT42" s="120">
+        <v>1</v>
+      </c>
       <c r="AU42" s="120"/>
       <c r="AV42" s="120"/>
       <c r="AW42" s="120"/>
@@ -13521,37 +13573,37 @@
       <c r="BA42" s="120"/>
       <c r="BB42" s="120"/>
       <c r="BC42" s="120"/>
-      <c r="BD42" s="187">
+      <c r="BD42" s="191">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="BE42" s="187" cm="1">
+        <v>21</v>
+      </c>
+      <c r="BE42" s="191" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
-        <v>16</v>
-      </c>
-      <c r="BF42" s="187" cm="1">
+        <v>17</v>
+      </c>
+      <c r="BF42" s="191" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
         <v>5</v>
       </c>
-      <c r="BG42" s="188" cm="1">
+      <c r="BG42" s="192" cm="1">
         <f t="array" ref="BG42">SUMPRODUCT(--(B42:AI42=INT(B42:AI42)),--(B42:AI42&gt;0))/34*100%</f>
         <v>0.352941176470588</v>
       </c>
-      <c r="BH42" s="189">
+      <c r="BH42" s="193">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="BI42" s="189">
+      <c r="BI42" s="193">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="BJ42" s="189">
+      <c r="BJ42" s="193">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:62">
-      <c r="A43" s="190">
+      <c r="A43" s="195">
         <v>41</v>
       </c>
       <c r="B43" s="120"/>
@@ -13608,33 +13660,33 @@
       <c r="BA43" s="120"/>
       <c r="BB43" s="120"/>
       <c r="BC43" s="120"/>
-      <c r="BD43" s="187">
+      <c r="BD43" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE43" s="187" cm="1">
+      <c r="BE43" s="191" cm="1">
         <f t="array" ref="BE43">SUMPRODUCT(--(B43:BC43=INT(B43:BC43)),--(B43:BC43&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF43" s="187" cm="1">
+      <c r="BF43" s="191" cm="1">
         <f t="array" ref="BF43">MAX(FREQUENCY(IF((B43:BC43=INT(B43:BC43))*(B43:BC43&gt;0),COLUMN(B43:BC43)),IF((B43:BC43&lt;&gt;INT(B43:BC43))+(B43:BC43&lt;=0),COLUMN(B43:BC43))))</f>
         <v>0</v>
       </c>
-      <c r="BG43" s="188" cm="1">
+      <c r="BG43" s="192" cm="1">
         <f t="array" ref="BG43">SUMPRODUCT(--(B43:AI43=INT(B43:AI43)),--(B43:AI43&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH43" s="189">
+      <c r="BH43" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI43" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI43" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ43" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ43" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:62">
@@ -13727,37 +13779,37 @@
       <c r="BA44" s="120"/>
       <c r="BB44" s="120"/>
       <c r="BC44" s="120"/>
-      <c r="BD44" s="187">
+      <c r="BD44" s="191">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="BE44" s="187" cm="1">
+      <c r="BE44" s="191" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
         <v>16</v>
       </c>
-      <c r="BF44" s="187" cm="1">
+      <c r="BF44" s="191" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
         <v>5</v>
       </c>
-      <c r="BG44" s="188" cm="1">
+      <c r="BG44" s="192" cm="1">
         <f t="array" ref="BG44">SUMPRODUCT(--(B44:AI44=INT(B44:AI44)),--(B44:AI44&gt;0))/34*100%</f>
         <v>0.411764705882353</v>
       </c>
-      <c r="BH44" s="189">
+      <c r="BH44" s="193">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="BI44" s="189">
+      <c r="BI44" s="193">
         <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="BJ44" s="189">
+        <v>5</v>
+      </c>
+      <c r="BJ44" s="193">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:62">
-      <c r="A45" s="190">
+      <c r="A45" s="195">
         <v>43</v>
       </c>
       <c r="B45" s="120"/>
@@ -13814,33 +13866,33 @@
       <c r="BA45" s="120"/>
       <c r="BB45" s="120"/>
       <c r="BC45" s="120"/>
-      <c r="BD45" s="187">
+      <c r="BD45" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE45" s="187" cm="1">
+      <c r="BE45" s="191" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(--(B45:BC45=INT(B45:BC45)),--(B45:BC45&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF45" s="187" cm="1">
+      <c r="BF45" s="191" cm="1">
         <f t="array" ref="BF45">MAX(FREQUENCY(IF((B45:BC45=INT(B45:BC45))*(B45:BC45&gt;0),COLUMN(B45:BC45)),IF((B45:BC45&lt;&gt;INT(B45:BC45))+(B45:BC45&lt;=0),COLUMN(B45:BC45))))</f>
         <v>0</v>
       </c>
-      <c r="BG45" s="188" cm="1">
+      <c r="BG45" s="192" cm="1">
         <f t="array" ref="BG45">SUMPRODUCT(--(B45:AI45=INT(B45:AI45)),--(B45:AI45&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH45" s="189">
+      <c r="BH45" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI45" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI45" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ45" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ45" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:62">
@@ -13945,7 +13997,9 @@
       <c r="AS46" s="120">
         <v>1</v>
       </c>
-      <c r="AT46" s="120"/>
+      <c r="AT46" s="120">
+        <v>1</v>
+      </c>
       <c r="AU46" s="120"/>
       <c r="AV46" s="120"/>
       <c r="AW46" s="120"/>
@@ -13955,37 +14009,37 @@
       <c r="BA46" s="120"/>
       <c r="BB46" s="120"/>
       <c r="BC46" s="120"/>
-      <c r="BD46" s="187">
+      <c r="BD46" s="191">
         <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="BE46" s="187" cm="1">
+        <v>38</v>
+      </c>
+      <c r="BE46" s="191" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>27</v>
-      </c>
-      <c r="BF46" s="187" cm="1">
+        <v>28</v>
+      </c>
+      <c r="BF46" s="191" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
         <v>8</v>
       </c>
-      <c r="BG46" s="188" cm="1">
+      <c r="BG46" s="192" cm="1">
         <f t="array" ref="BG46">SUMPRODUCT(--(B46:AI46=INT(B46:AI46)),--(B46:AI46&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH46" s="189">
+      <c r="BH46" s="193">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="BI46" s="189">
+      <c r="BI46" s="193">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="BJ46" s="189">
+      <c r="BJ46" s="193">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:62">
-      <c r="A47" s="190">
+      <c r="A47" s="195">
         <v>45</v>
       </c>
       <c r="B47" s="120"/>
@@ -14042,33 +14096,33 @@
       <c r="BA47" s="120"/>
       <c r="BB47" s="120"/>
       <c r="BC47" s="120"/>
-      <c r="BD47" s="187">
+      <c r="BD47" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE47" s="187" cm="1">
+      <c r="BE47" s="191" cm="1">
         <f t="array" ref="BE47">SUMPRODUCT(--(B47:BC47=INT(B47:BC47)),--(B47:BC47&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF47" s="187" cm="1">
+      <c r="BF47" s="191" cm="1">
         <f t="array" ref="BF47">MAX(FREQUENCY(IF((B47:BC47=INT(B47:BC47))*(B47:BC47&gt;0),COLUMN(B47:BC47)),IF((B47:BC47&lt;&gt;INT(B47:BC47))+(B47:BC47&lt;=0),COLUMN(B47:BC47))))</f>
         <v>0</v>
       </c>
-      <c r="BG47" s="188" cm="1">
+      <c r="BG47" s="192" cm="1">
         <f t="array" ref="BG47">SUMPRODUCT(--(B47:AI47=INT(B47:AI47)),--(B47:AI47&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH47" s="189">
+      <c r="BH47" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI47" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI47" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ47" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ47" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:62">
@@ -14155,33 +14209,33 @@
       <c r="BA48" s="120"/>
       <c r="BB48" s="120"/>
       <c r="BC48" s="120"/>
-      <c r="BD48" s="187">
+      <c r="BD48" s="191">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="BE48" s="187" cm="1">
+      <c r="BE48" s="191" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
         <v>13</v>
       </c>
-      <c r="BF48" s="187" cm="1">
+      <c r="BF48" s="191" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
         <v>2</v>
       </c>
-      <c r="BG48" s="188" cm="1">
+      <c r="BG48" s="192" cm="1">
         <f t="array" ref="BG48">SUMPRODUCT(--(B48:AI48=INT(B48:AI48)),--(B48:AI48&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH48" s="189">
+      <c r="BH48" s="193">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="BI48" s="189">
+        <v>9</v>
+      </c>
+      <c r="BI48" s="193">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="BJ48" s="189">
+      <c r="BJ48" s="193">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:62">
@@ -14250,33 +14304,33 @@
       <c r="BA49" s="120"/>
       <c r="BB49" s="120"/>
       <c r="BC49" s="120"/>
-      <c r="BD49" s="187">
+      <c r="BD49" s="191">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE49" s="187" cm="1">
+      <c r="BE49" s="191" cm="1">
         <f t="array" ref="BE49">SUMPRODUCT(--(B49:BC49=INT(B49:BC49)),--(B49:BC49&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF49" s="187" cm="1">
+      <c r="BF49" s="191" cm="1">
         <f t="array" ref="BF49">MAX(FREQUENCY(IF((B49:BC49=INT(B49:BC49))*(B49:BC49&gt;0),COLUMN(B49:BC49)),IF((B49:BC49&lt;&gt;INT(B49:BC49))+(B49:BC49&lt;=0),COLUMN(B49:BC49))))</f>
         <v>1</v>
       </c>
-      <c r="BG49" s="188" cm="1">
+      <c r="BG49" s="192" cm="1">
         <f t="array" ref="BG49">SUMPRODUCT(--(B49:AI49=INT(B49:AI49)),--(B49:AI49&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH49" s="189">
+      <c r="BH49" s="193">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="BI49" s="189">
+      <c r="BI49" s="193">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ49" s="189">
+      <c r="BJ49" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:62">
@@ -14347,37 +14401,37 @@
       <c r="BA50" s="120"/>
       <c r="BB50" s="120"/>
       <c r="BC50" s="120"/>
-      <c r="BD50" s="187">
+      <c r="BD50" s="191">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE50" s="187" cm="1">
+      <c r="BE50" s="191" cm="1">
         <f t="array" ref="BE50">SUMPRODUCT(--(B50:BC50=INT(B50:BC50)),--(B50:BC50&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF50" s="187" cm="1">
+      <c r="BF50" s="191" cm="1">
         <f t="array" ref="BF50">MAX(FREQUENCY(IF((B50:BC50=INT(B50:BC50))*(B50:BC50&gt;0),COLUMN(B50:BC50)),IF((B50:BC50&lt;&gt;INT(B50:BC50))+(B50:BC50&lt;=0),COLUMN(B50:BC50))))</f>
         <v>1</v>
       </c>
-      <c r="BG50" s="188" cm="1">
+      <c r="BG50" s="192" cm="1">
         <f t="array" ref="BG50">SUMPRODUCT(--(B50:AI50=INT(B50:AI50)),--(B50:AI50&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH50" s="189">
+      <c r="BH50" s="193">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="BI50" s="189">
+      <c r="BI50" s="193">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="BJ50" s="189">
+      <c r="BJ50" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:62">
-      <c r="A51" s="190">
+      <c r="A51" s="195">
         <v>49</v>
       </c>
       <c r="B51" s="120"/>
@@ -14434,37 +14488,37 @@
       <c r="BA51" s="120"/>
       <c r="BB51" s="120"/>
       <c r="BC51" s="120"/>
-      <c r="BD51" s="187">
+      <c r="BD51" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE51" s="187" cm="1">
+      <c r="BE51" s="191" cm="1">
         <f t="array" ref="BE51">SUMPRODUCT(--(B51:BC51=INT(B51:BC51)),--(B51:BC51&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF51" s="187" cm="1">
+      <c r="BF51" s="191" cm="1">
         <f t="array" ref="BF51">MAX(FREQUENCY(IF((B51:BC51=INT(B51:BC51))*(B51:BC51&gt;0),COLUMN(B51:BC51)),IF((B51:BC51&lt;&gt;INT(B51:BC51))+(B51:BC51&lt;=0),COLUMN(B51:BC51))))</f>
         <v>0</v>
       </c>
-      <c r="BG51" s="188" cm="1">
+      <c r="BG51" s="192" cm="1">
         <f t="array" ref="BG51">SUMPRODUCT(--(B51:AI51=INT(B51:AI51)),--(B51:AI51&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH51" s="189">
+      <c r="BH51" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI51" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI51" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ51" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ51" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:62">
-      <c r="A52" s="190">
+      <c r="A52" s="195">
         <v>50</v>
       </c>
       <c r="B52" s="120"/>
@@ -14521,33 +14575,33 @@
       <c r="BA52" s="120"/>
       <c r="BB52" s="120"/>
       <c r="BC52" s="120"/>
-      <c r="BD52" s="187">
+      <c r="BD52" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE52" s="187" cm="1">
+      <c r="BE52" s="191" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(--(B52:BC52=INT(B52:BC52)),--(B52:BC52&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF52" s="187" cm="1">
+      <c r="BF52" s="191" cm="1">
         <f t="array" ref="BF52">MAX(FREQUENCY(IF((B52:BC52=INT(B52:BC52))*(B52:BC52&gt;0),COLUMN(B52:BC52)),IF((B52:BC52&lt;&gt;INT(B52:BC52))+(B52:BC52&lt;=0),COLUMN(B52:BC52))))</f>
         <v>0</v>
       </c>
-      <c r="BG52" s="188" cm="1">
+      <c r="BG52" s="192" cm="1">
         <f t="array" ref="BG52">SUMPRODUCT(--(B52:AI52=INT(B52:AI52)),--(B52:AI52&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH52" s="189">
+      <c r="BH52" s="193">
         <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="BI52" s="189">
+        <v>42</v>
+      </c>
+      <c r="BI52" s="193">
         <f t="shared" si="2"/>
-        <v>41</v>
-      </c>
-      <c r="BJ52" s="189">
+        <v>42</v>
+      </c>
+      <c r="BJ52" s="193">
         <f t="shared" si="3"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:62">
@@ -14610,33 +14664,33 @@
       <c r="BA53" s="120"/>
       <c r="BB53" s="120"/>
       <c r="BC53" s="120"/>
-      <c r="BD53" s="187">
+      <c r="BD53" s="191">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE53" s="187" cm="1">
+      <c r="BE53" s="191" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(--(B53:BC53=INT(B53:BC53)),--(B53:BC53&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF53" s="187" cm="1">
+      <c r="BF53" s="191" cm="1">
         <f t="array" ref="BF53">MAX(FREQUENCY(IF((B53:BC53=INT(B53:BC53))*(B53:BC53&gt;0),COLUMN(B53:BC53)),IF((B53:BC53&lt;&gt;INT(B53:BC53))+(B53:BC53&lt;=0),COLUMN(B53:BC53))))</f>
         <v>1</v>
       </c>
-      <c r="BG53" s="188" cm="1">
+      <c r="BG53" s="192" cm="1">
         <f t="array" ref="BG53">SUMPRODUCT(--(B53:AI53=INT(B53:AI53)),--(B53:AI53&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH53" s="189">
+      <c r="BH53" s="193">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI53" s="189">
+      <c r="BI53" s="193">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ53" s="189">
+      <c r="BJ53" s="193">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -15762,8 +15816,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BJ8 Y9:BJ10 A11:BJ53" formulaRange="1"/>
-    <ignoredError sqref="A9:X10 Z3:AF3 A2:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH11:BJ39 Z10:AF10 BI9:BJ9 BH4:BJ8 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z28:AF33 A28:X33 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11 U1:AF1 C1:S1 A1 Z9:AB9 AD9:AF9 X41" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A29:X33 Z29:AF33 A4:X4 Z42:AE42 BH4:BJ4 BH6:BJ8 BH11:BJ14 BH23:BJ39 A12:X14" unlockedFormula="1"/>
+    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 Z9:AB9 A1 C1:S1 C1:S1 U1:AF1 U1:AF1 A11:Z11 AB11:AC11 AB11:AC11 AE11 AE11 AB15:AE15 Z15 Z15 Z14:AF14 AB13:AF13 Z13 Z13 Z12:AF12 A16:AF16 A16:AF16 A17:X18 A17:X18 Z17:AF18 Z17:AF18 A19:AF21 A19:AF21 A22:X22 A22:X22 AA22:AD22 AA22:AD22 AF22 AF22 A23:AF23 A24:X25 Z24:AF25 Z24:AF25 A26:AF27 A26:AF27 A28:X28 A30:X33 Z28:AF28 Z30:AF33 Z29:AF29 A34:AF35 A34:AF35 A36:X36 A36:X36 Z36:AF36 Z36:AF36 A38:X38 A38:X38 Z38:AB38 Z38:AB38 AD38:AF38 AD38:AF38 A3:X3 A3:X4 BD1:BJ2 BD1:BJ2 BI3 BI3 AC40:AD40 AC40:AD40 A40:V40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 Z44:AD44 AF44 AF44 A43:AF43 A43:AF43 A46:X46 AA46 AA46 AC46:AD46 AC46:AD46 AF46 AF46 A47:AF47 A48:X49 A48:X49 Z48:AB48 Z48:AB48 AE48 AE48 A51:AF53 A51:AF53 A50:AD50 A50:AD50 AF50 AF50 X8:AF8 A8:V8 A8:V8 A5:AF7 Z4:AE4 Z41:AE41 Z42:AE42 Z41:AE42 BH5:BJ5 BH7:BJ7 BI9:BJ9 BI9:BJ9 Z10:AF10 Z10:AF10 BH15:BJ22 BH13:BJ13 BH12:BJ12 BH24:BJ28 BH30:BJ39 BH11:BJ39 Z49:AF49 Z49:AF49 A15:X15 A14:X14 A13:X13 A12:X12 A12:X15 A37:AF37 A37:AF37 A39:AF39 A39:AF39 A2:AF2 A2:AF2 Z3:AF3 Z3:AF3 A9:X10" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="AU11:BG11 AU14:BG14 AU23:BG23 AU29:BG29 AU42:BJ42 AU46:BJ46 AU4:BG4 AG6:AS6 AU6:BG6 AU8:BG8 A41:W41 Y41:BJ41 Y9:AC9 AG9:BJ9 Y10:BJ10 B1:BJ1 A2:BJ3 AA11:AS11 A15:AA15 AF15:BJ15 A16:BJ22 A12:X14 AG14:AS14 A13:AA13 BH11:BJ14 A12:Y12 AG23:AS23 BH23:BJ39 A26:BJ28 Y30:BJ33 A34:BJ40 Y29 AG29:AS29 A4:Y4 Z42:AE42 AG45:BJ45 A43:BJ43 X44:BJ44 Y46:AS46 AG47:BJ47 A48:BJ53 A8:W8 AG8:AS8 AF4:AS4 AG5:BG5 AG7:BG7" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15785,264 +15840,264 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="147"/>
-      <c r="B1" s="148" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="148"/>
-      <c r="D1" s="149" t="s">
+      <c r="A1" s="151"/>
+      <c r="B1" s="152" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="152"/>
+      <c r="D1" s="153" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="148" t="s">
+      <c r="E1" s="154"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="152" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="148" t="s">
+      <c r="H1" s="152" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="148" t="s">
+      <c r="I1" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="148" t="s">
+      <c r="J1" s="152" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="148" t="s">
-        <v>320</v>
-      </c>
-      <c r="B2" s="152" t="s">
+      <c r="A2" s="152" t="s">
         <v>321</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="B2" s="156" t="s">
         <v>322</v>
       </c>
-      <c r="D2" s="154"/>
-      <c r="E2" s="152" t="s">
-        <v>321</v>
-      </c>
-      <c r="F2" s="152"/>
-      <c r="G2" s="155" t="s">
+      <c r="C2" s="157" t="s">
         <v>323</v>
       </c>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="156"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="156" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" s="156"/>
+      <c r="G2" s="159" t="s">
+        <v>324</v>
+      </c>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="160"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="148" t="s">
-        <v>324</v>
-      </c>
-      <c r="B3" s="157" t="s">
+      <c r="A3" s="152" t="s">
         <v>325</v>
       </c>
-      <c r="C3" s="157"/>
-      <c r="D3" s="157"/>
-      <c r="E3" s="157"/>
-      <c r="F3" s="157"/>
-      <c r="G3" s="157"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="147"/>
-      <c r="J3" s="156"/>
+      <c r="B3" s="161" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="160"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="148" t="s">
-        <v>326</v>
-      </c>
-      <c r="B4" s="158" t="s">
+      <c r="A4" s="152" t="s">
+        <v>327</v>
+      </c>
+      <c r="B4" s="162" t="s">
         <v>247</v>
       </c>
-      <c r="C4" s="158"/>
-      <c r="D4" s="158"/>
-      <c r="E4" s="158"/>
-      <c r="F4" s="158"/>
-      <c r="G4" s="158"/>
-      <c r="H4" s="147"/>
-      <c r="I4" s="147"/>
-      <c r="J4" s="156"/>
+      <c r="C4" s="162"/>
+      <c r="D4" s="162"/>
+      <c r="E4" s="162"/>
+      <c r="F4" s="162"/>
+      <c r="G4" s="162"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="160"/>
     </row>
     <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="148" t="s">
-        <v>327</v>
-      </c>
-      <c r="B5" s="159">
-        <v>1</v>
-      </c>
-      <c r="C5" s="159"/>
-      <c r="D5" s="160">
+      <c r="A5" s="152" t="s">
+        <v>328</v>
+      </c>
+      <c r="B5" s="163">
+        <v>1</v>
+      </c>
+      <c r="C5" s="163"/>
+      <c r="D5" s="164">
         <v>2</v>
       </c>
-      <c r="E5" s="160"/>
-      <c r="F5" s="160"/>
-      <c r="G5" s="159">
+      <c r="E5" s="164"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="163">
         <v>3</v>
       </c>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-      <c r="J5" s="156"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="160"/>
     </row>
     <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="148" t="s">
-        <v>328</v>
-      </c>
-      <c r="B6" s="161">
-        <v>1</v>
-      </c>
-      <c r="C6" s="161"/>
-      <c r="D6" s="161"/>
-      <c r="E6" s="161"/>
-      <c r="F6" s="161"/>
-      <c r="G6" s="162" t="s">
+      <c r="A6" s="152" t="s">
         <v>329</v>
       </c>
-      <c r="H6" s="147"/>
-      <c r="I6" s="147"/>
-      <c r="J6" s="156"/>
+      <c r="B6" s="165">
+        <v>1</v>
+      </c>
+      <c r="C6" s="165"/>
+      <c r="D6" s="165"/>
+      <c r="E6" s="165"/>
+      <c r="F6" s="165"/>
+      <c r="G6" s="166" t="s">
+        <v>330</v>
+      </c>
+      <c r="H6" s="151"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="160"/>
     </row>
     <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="148" t="s">
-        <v>330</v>
-      </c>
-      <c r="B7" s="163" t="s">
+      <c r="A7" s="152" t="s">
         <v>331</v>
       </c>
-      <c r="C7" s="163"/>
-      <c r="D7" s="163"/>
-      <c r="E7" s="163"/>
-      <c r="F7" s="163"/>
-      <c r="G7" s="164">
+      <c r="B7" s="167" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="167"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="167"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="168">
         <v>2</v>
       </c>
-      <c r="H7" s="147"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="156"/>
+      <c r="H7" s="151"/>
+      <c r="I7" s="151"/>
+      <c r="J7" s="160"/>
     </row>
     <row r="8" ht="16.5" spans="1:10">
-      <c r="A8" s="148" t="s">
-        <v>332</v>
-      </c>
-      <c r="B8" s="165">
-        <v>1</v>
-      </c>
-      <c r="C8" s="165"/>
-      <c r="D8" s="166" t="s">
+      <c r="A8" s="152" t="s">
         <v>333</v>
       </c>
-      <c r="E8" s="166"/>
-      <c r="F8" s="166"/>
-      <c r="G8" s="165"/>
-      <c r="H8" s="147"/>
-      <c r="I8" s="147"/>
-      <c r="J8" s="156"/>
+      <c r="B8" s="169">
+        <v>1</v>
+      </c>
+      <c r="C8" s="169"/>
+      <c r="D8" s="170" t="s">
+        <v>334</v>
+      </c>
+      <c r="E8" s="170"/>
+      <c r="F8" s="170"/>
+      <c r="G8" s="169"/>
+      <c r="H8" s="151"/>
+      <c r="I8" s="151"/>
+      <c r="J8" s="160"/>
     </row>
     <row r="9" ht="16.5" spans="1:10">
-      <c r="A9" s="148" t="s">
-        <v>334</v>
-      </c>
-      <c r="B9" s="152" t="s">
+      <c r="A9" s="152" t="s">
         <v>335</v>
       </c>
-      <c r="C9" s="152"/>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
-      <c r="G9" s="152"/>
-      <c r="H9" s="147"/>
-      <c r="I9" s="147"/>
-      <c r="J9" s="156"/>
+      <c r="B9" s="156" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" s="156"/>
+      <c r="D9" s="156"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="156"/>
+      <c r="G9" s="156"/>
+      <c r="H9" s="151"/>
+      <c r="I9" s="151"/>
+      <c r="J9" s="160"/>
     </row>
     <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="148" t="s">
-        <v>336</v>
-      </c>
-      <c r="B10" s="157">
-        <v>1</v>
-      </c>
-      <c r="C10" s="157"/>
-      <c r="D10" s="167" t="s">
+      <c r="A10" s="152" t="s">
         <v>337</v>
       </c>
-      <c r="E10" s="157">
-        <v>1</v>
-      </c>
-      <c r="F10" s="167" t="s">
-        <v>337</v>
-      </c>
-      <c r="G10" s="147" t="s">
+      <c r="B10" s="161">
+        <v>1</v>
+      </c>
+      <c r="C10" s="161"/>
+      <c r="D10" s="171" t="s">
         <v>338</v>
       </c>
-      <c r="H10" s="147"/>
-      <c r="I10" s="147"/>
-      <c r="J10" s="156"/>
+      <c r="E10" s="161">
+        <v>1</v>
+      </c>
+      <c r="F10" s="171" t="s">
+        <v>338</v>
+      </c>
+      <c r="G10" s="151" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" s="151"/>
+      <c r="I10" s="151"/>
+      <c r="J10" s="160"/>
     </row>
     <row r="11" ht="16.5" spans="1:10">
-      <c r="A11" s="148" t="s">
+      <c r="A11" s="152" t="s">
+        <v>340</v>
+      </c>
+      <c r="B11" s="162">
+        <v>1</v>
+      </c>
+      <c r="C11" s="162"/>
+      <c r="D11" s="162"/>
+      <c r="E11" s="162"/>
+      <c r="F11" s="162"/>
+      <c r="G11" s="162"/>
+      <c r="H11" s="151"/>
+      <c r="I11" s="151"/>
+      <c r="J11" s="160"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:10">
+      <c r="A12" s="152" t="s">
+        <v>341</v>
+      </c>
+      <c r="B12" s="163">
+        <v>1</v>
+      </c>
+      <c r="C12" s="163"/>
+      <c r="D12" s="163"/>
+      <c r="E12" s="163"/>
+      <c r="F12" s="163"/>
+      <c r="G12" s="164">
+        <v>2</v>
+      </c>
+      <c r="H12" s="151"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="160"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
+      <c r="A13" s="152" t="s">
+        <v>342</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="B11" s="158">
-        <v>1</v>
-      </c>
-      <c r="C11" s="158"/>
-      <c r="D11" s="158"/>
-      <c r="E11" s="158"/>
-      <c r="F11" s="158"/>
-      <c r="G11" s="158"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="156"/>
-    </row>
-    <row r="12" ht="16.5" spans="1:10">
-      <c r="A12" s="148" t="s">
-        <v>340</v>
-      </c>
-      <c r="B12" s="159">
-        <v>1</v>
-      </c>
-      <c r="C12" s="159"/>
-      <c r="D12" s="159"/>
-      <c r="E12" s="159"/>
-      <c r="F12" s="159"/>
-      <c r="G12" s="160">
-        <v>2</v>
-      </c>
-      <c r="H12" s="147"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="156"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A13" s="148" t="s">
-        <v>341</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>338</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="168" t="s">
-        <v>342</v>
+      <c r="G13" s="172" t="s">
+        <v>343</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="169"/>
+      <c r="J13" s="173"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A14" s="148" t="s">
-        <v>343</v>
-      </c>
-      <c r="B14" s="170" t="s">
-        <v>338</v>
-      </c>
-      <c r="C14" s="170"/>
-      <c r="D14" s="170"/>
-      <c r="E14" s="170"/>
-      <c r="F14" s="170"/>
-      <c r="G14" s="170"/>
-      <c r="H14" s="170"/>
-      <c r="I14" s="171"/>
-      <c r="J14" s="172"/>
+      <c r="A14" s="152" t="s">
+        <v>344</v>
+      </c>
+      <c r="B14" s="174" t="s">
+        <v>339</v>
+      </c>
+      <c r="C14" s="174"/>
+      <c r="D14" s="174"/>
+      <c r="E14" s="174"/>
+      <c r="F14" s="174"/>
+      <c r="G14" s="174"/>
+      <c r="H14" s="174"/>
+      <c r="I14" s="175"/>
+      <c r="J14" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -16108,7 +16163,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -16133,29 +16188,31 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="128"/>
       <c r="E2" s="128"/>
-      <c r="F2" s="129"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="129"/>
     </row>
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="128"/>
       <c r="E3" s="128"/>
-      <c r="F3" s="129"/>
+      <c r="F3" s="128"/>
+      <c r="G3" s="129"/>
     </row>
     <row r="4" s="118" customFormat="1" spans="1:9">
       <c r="A4" s="130"/>
@@ -16165,24 +16222,26 @@
       </c>
       <c r="D4" s="128"/>
       <c r="E4" s="128"/>
-      <c r="F4" s="129"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="129"/>
     </row>
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="128"/>
       <c r="E5" s="128"/>
-      <c r="F5" s="129"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="129"/>
     </row>
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
@@ -16191,7 +16250,8 @@
         <v>104</v>
       </c>
       <c r="E6" s="132"/>
-      <c r="F6" s="133"/>
+      <c r="F6" s="132"/>
+      <c r="G6" s="133"/>
     </row>
     <row r="7" s="118" customFormat="1" spans="1:9">
       <c r="A7" s="130"/>
@@ -16205,12 +16265,13 @@
       <c r="E7" s="131" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="133"/>
+      <c r="F7" s="132"/>
+      <c r="G7" s="133"/>
     </row>
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16219,50 +16280,54 @@
         <v>84</v>
       </c>
       <c r="E8" s="132"/>
-      <c r="F8" s="133"/>
+      <c r="F8" s="132"/>
+      <c r="G8" s="133"/>
     </row>
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
       </c>
       <c r="D9" s="128"/>
       <c r="E9" s="128"/>
-      <c r="F9" s="129"/>
+      <c r="F9" s="128"/>
+      <c r="G9" s="129"/>
     </row>
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="128"/>
       <c r="E10" s="128"/>
-      <c r="F10" s="129"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="129"/>
     </row>
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>72</v>
       </c>
       <c r="D11" s="128"/>
       <c r="E11" s="128"/>
-      <c r="F11" s="129"/>
+      <c r="F11" s="128"/>
+      <c r="G11" s="129"/>
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>91</v>
@@ -16272,150 +16337,161 @@
         <v>20</v>
       </c>
       <c r="F12" s="140"/>
+      <c r="G12" s="141"/>
     </row>
     <row r="13" s="119" customFormat="1" spans="1:9">
-      <c r="A13" s="141"/>
+      <c r="A13" s="142"/>
       <c r="B13" s="136"/>
-      <c r="C13" s="137" t="s">
+      <c r="C13" s="143" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="142"/>
-      <c r="E13" s="142"/>
-      <c r="F13" s="138"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="145"/>
     </row>
     <row r="14" s="119" customFormat="1" spans="1:9">
-      <c r="A14" s="141"/>
+      <c r="A14" s="142"/>
       <c r="B14" s="136" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>357</v>
-      </c>
-      <c r="D14" s="142"/>
+        <v>358</v>
+      </c>
+      <c r="D14" s="146"/>
       <c r="E14" s="138"/>
       <c r="F14" s="140" t="s">
         <v>36</v>
       </c>
+      <c r="G14" s="141"/>
     </row>
     <row r="15" s="119" customFormat="1" spans="1:9">
-      <c r="A15" s="141"/>
+      <c r="A15" s="142"/>
       <c r="B15" s="136" t="s">
-        <v>358</v>
-      </c>
-      <c r="C15" s="137" t="s">
+        <v>359</v>
+      </c>
+      <c r="C15" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="142"/>
-      <c r="E15" s="142"/>
-      <c r="F15" s="138"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="145"/>
     </row>
     <row r="16" s="119" customFormat="1" spans="1:9">
-      <c r="A16" s="141"/>
+      <c r="A16" s="142"/>
       <c r="B16" s="136"/>
-      <c r="C16" s="137" t="s">
+      <c r="C16" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
-      <c r="F16" s="138"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="145"/>
     </row>
     <row r="17" s="119" customFormat="1" spans="1:7">
-      <c r="A17" s="141"/>
+      <c r="A17" s="142"/>
       <c r="B17" s="136" t="s">
-        <v>359</v>
-      </c>
-      <c r="C17" s="137" t="s">
+        <v>360</v>
+      </c>
+      <c r="C17" s="143" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="138"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="145"/>
     </row>
     <row r="18" s="119" customFormat="1" spans="1:7">
-      <c r="A18" s="141"/>
+      <c r="A18" s="142"/>
       <c r="B18" s="136" t="s">
-        <v>360</v>
-      </c>
-      <c r="C18" s="137" t="s">
+        <v>361</v>
+      </c>
+      <c r="C18" s="143" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="138"/>
+      <c r="D18" s="144"/>
+      <c r="E18" s="144"/>
+      <c r="F18" s="144"/>
+      <c r="G18" s="145"/>
     </row>
     <row r="19" s="119" customFormat="1" spans="1:7">
-      <c r="A19" s="141"/>
+      <c r="A19" s="142"/>
       <c r="B19" s="136" t="s">
-        <v>361</v>
-      </c>
-      <c r="C19" s="137" t="s">
+        <v>362</v>
+      </c>
+      <c r="C19" s="143" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="138"/>
+      <c r="D19" s="144"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="144"/>
+      <c r="G19" s="145"/>
     </row>
     <row r="20" s="119" customFormat="1" spans="1:7">
-      <c r="A20" s="141"/>
+      <c r="A20" s="142"/>
       <c r="B20" s="136" t="s">
-        <v>362</v>
-      </c>
-      <c r="C20" s="137" t="s">
+        <v>363</v>
+      </c>
+      <c r="C20" s="143" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="142"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="138"/>
+      <c r="D20" s="144"/>
+      <c r="E20" s="144"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="145"/>
     </row>
     <row r="21" s="119" customFormat="1" spans="1:7">
-      <c r="A21" s="141"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="136" t="s">
-        <v>363</v>
-      </c>
-      <c r="C21" s="143"/>
-      <c r="D21" s="144"/>
+        <v>364</v>
+      </c>
+      <c r="C21" s="147"/>
+      <c r="D21" s="148"/>
       <c r="E21" s="139" t="s">
         <v>27</v>
       </c>
       <c r="F21" s="140"/>
+      <c r="G21" s="141"/>
     </row>
     <row r="22" s="119" customFormat="1" spans="1:7">
-      <c r="A22" s="145"/>
+      <c r="A22" s="149"/>
       <c r="B22" s="136" t="s">
-        <v>364</v>
-      </c>
-      <c r="C22" s="143"/>
-      <c r="D22" s="146"/>
-      <c r="E22" s="146"/>
-      <c r="F22" s="146"/>
-      <c r="G22" s="144"/>
+        <v>365</v>
+      </c>
+      <c r="C22" s="147"/>
+      <c r="D22" s="150"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="150"/>
+      <c r="G22" s="148"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="C13:G13"/>
     <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="A2:A11"/>
     <mergeCell ref="A12:A22"/>
@@ -16444,7 +16520,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -16475,7 +16551,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -16667,7 +16743,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -16859,7 +16935,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -17086,10 +17162,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>203</v>
@@ -17100,208 +17176,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -17309,118 +17385,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -17428,138 +17504,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -3312,8 +3312,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="华文仿宋"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3323,21 +3329,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="华文仿宋"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="黑体"/>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="57">
@@ -4103,7 +4103,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="235">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4534,15 +4534,6 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4689,9 +4680,6 @@
     <xf numFmtId="0" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4770,15 +4758,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5168,538 +5147,538 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="231" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="232" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="233" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="234"/>
+    <col min="1" max="1" width="7.59090909090909" style="224" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="225" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="226" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="227"/>
   </cols>
   <sheetData>
-    <row r="1" s="230" customFormat="1" spans="1:10">
-      <c r="A1" s="235" t="s">
+    <row r="1" s="223" customFormat="1" spans="1:10">
+      <c r="A1" s="228" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="236" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="236" t="s">
+      <c r="B1" s="229" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="229" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="236" t="s">
+      <c r="D1" s="229" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="236" t="s">
+      <c r="E1" s="229" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="236" t="s">
+      <c r="F1" s="229" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="236" t="s">
+      <c r="G1" s="229" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="237"/>
-      <c r="I1" s="237"/>
-      <c r="J1" s="237"/>
+      <c r="H1" s="230"/>
+      <c r="I1" s="230"/>
+      <c r="J1" s="230"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="238" t="s">
+      <c r="A2" s="231" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="232" t="s">
+      <c r="B2" s="225" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="225" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="238" t="s">
+      <c r="A3" s="231" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="225" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="232" t="s">
+      <c r="D3" s="225" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="238" t="s">
+      <c r="A4" s="231" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="232" t="s">
+      <c r="D4" s="225" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="238" t="s">
+      <c r="A5" s="231" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="232" t="s">
+      <c r="C5" s="225" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="232" t="s">
+      <c r="D5" s="225" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="238" t="s">
+      <c r="A6" s="231" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="232" t="s">
+      <c r="C6" s="225" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="238" t="s">
+      <c r="A7" s="231" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="232" t="s">
+      <c r="B7" s="225" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="232" t="s">
+      <c r="C7" s="225" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="232" t="s">
+      <c r="D7" s="225" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="238" t="s">
+      <c r="A8" s="231" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="232" t="s">
+      <c r="D8" s="225" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="238" t="s">
+      <c r="A9" s="231" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="238" t="s">
+      <c r="A10" s="231" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="232" t="s">
+      <c r="B10" s="225" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="238" t="s">
+      <c r="A11" s="231" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="238" t="s">
+      <c r="A12" s="231" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="238" t="s">
+      <c r="A13" s="231" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="232" t="s">
+      <c r="D13" s="225" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="238" t="s">
+      <c r="A14" s="231" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="232" t="s">
+      <c r="B14" s="225" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="238" t="s">
+      <c r="A15" s="231" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="238" t="s">
+      <c r="A16" s="231" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="232" t="s">
+      <c r="C16" s="225" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:5">
-      <c r="A17" s="238" t="s">
+      <c r="A17" s="231" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="232" t="s">
+      <c r="C17" s="225" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="238" t="s">
+      <c r="A18" s="231" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="232" t="s">
+      <c r="D18" s="225" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:5">
-      <c r="A19" s="238" t="s">
+      <c r="A19" s="231" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="232" t="s">
+      <c r="D19" s="225" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:5">
-      <c r="A20" s="238" t="s">
+      <c r="A20" s="231" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="232" t="s">
+      <c r="B20" s="225" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="232" t="s">
+      <c r="C20" s="225" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:5">
-      <c r="A21" s="238" t="s">
+      <c r="A21" s="231" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="225" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="232" t="s">
+      <c r="C21" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="232" t="s">
+      <c r="D21" s="225" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="238" t="s">
+      <c r="A22" s="231" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:5">
-      <c r="A23" s="238" t="s">
+      <c r="A23" s="231" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="232" t="s">
+      <c r="B23" s="225" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:5">
-      <c r="A24" s="238" t="s">
+      <c r="A24" s="231" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="232" t="s">
+      <c r="B24" s="225" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="232" t="s">
+      <c r="C24" s="225" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="232" t="s">
+      <c r="D24" s="225" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="238" t="s">
+      <c r="A25" s="231" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="238" t="s">
+      <c r="A26" s="231" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="238" t="s">
+      <c r="A27" s="231" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="232" t="s">
+      <c r="B27" s="225" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="232" t="s">
+      <c r="C27" s="225" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:5">
-      <c r="A28" s="238" t="s">
+      <c r="A28" s="231" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="232" t="s">
+      <c r="B28" s="225" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="232" t="s">
+      <c r="C28" s="225" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="232" t="s">
+      <c r="D28" s="225" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="232" t="s">
+      <c r="E28" s="225" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="238" t="s">
+      <c r="A29" s="231" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="238" t="s">
+      <c r="A30" s="231" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="232" t="s">
+      <c r="B30" s="225" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="232" t="s">
+      <c r="C30" s="225" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="238" t="s">
+      <c r="A31" s="231" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="238" t="s">
+      <c r="A32" s="231" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="238" t="s">
+      <c r="A33" s="231" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="238" t="s">
+      <c r="A34" s="231" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="238" t="s">
+      <c r="A35" s="231" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="238" t="s">
+      <c r="A36" s="231" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="232" t="s">
+      <c r="B36" s="225" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="238" t="s">
+      <c r="A37" s="231" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="232" t="s">
+      <c r="C37" s="225" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="232" t="s">
+      <c r="D37" s="225" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="238" t="s">
+      <c r="A38" s="231" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="232" t="s">
+      <c r="B38" s="225" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="239"/>
-      <c r="D38" s="239"/>
-      <c r="E38" s="239"/>
-      <c r="F38" s="239"/>
-      <c r="G38" s="239"/>
+      <c r="C38" s="232"/>
+      <c r="D38" s="232"/>
+      <c r="E38" s="232"/>
+      <c r="F38" s="232"/>
+      <c r="G38" s="232"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="238" t="s">
+      <c r="A39" s="231" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="232" t="s">
+      <c r="C39" s="225" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="232" t="s">
+      <c r="D39" s="225" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="238" t="s">
+      <c r="A40" s="231" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="232" t="s">
+      <c r="B40" s="225" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="232" t="s">
+      <c r="C40" s="225" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="232" t="s">
+      <c r="D40" s="225" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="238" t="s">
+      <c r="A41" s="231" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="232" t="s">
+      <c r="C41" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="232" t="s">
+      <c r="D41" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="E41" s="232" t="s">
+      <c r="E41" s="225" t="s">
         <v>94</v>
       </c>
-      <c r="H41" s="233" t="s">
+      <c r="H41" s="226" t="s">
         <v>95</v>
       </c>
-      <c r="I41" s="233" t="s">
+      <c r="I41" s="226" t="s">
         <v>96</v>
       </c>
-      <c r="J41" s="233" t="s">
+      <c r="J41" s="226" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="238" t="s">
+      <c r="A42" s="231" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="238" t="s">
+      <c r="A43" s="231" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="232" t="s">
+      <c r="B43" s="225" t="s">
         <v>100</v>
       </c>
-      <c r="H43" s="233" t="s">
+      <c r="H43" s="226" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="238" t="s">
+      <c r="A44" s="231" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="232" t="s">
+      <c r="B44" s="225" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="238" t="s">
+      <c r="A45" s="231" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="232" t="s">
+      <c r="C45" s="225" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="232" t="s">
+      <c r="D45" s="225" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="238" t="s">
+      <c r="A46" s="231" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="238" t="s">
+      <c r="A47" s="231" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="232" t="s">
+      <c r="D47" s="225" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="238" t="s">
+      <c r="A48" s="231" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="232" t="s">
+      <c r="C48" s="225" t="s">
         <v>111</v>
       </c>
-      <c r="D48" s="232" t="s">
+      <c r="D48" s="225" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="238" t="s">
+      <c r="A49" s="231" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="238" t="s">
+      <c r="A50" s="231" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="232" t="s">
+      <c r="C50" s="225" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="238" t="s">
+      <c r="A51" s="231" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="238" t="s">
+      <c r="A52" s="231" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="225" t="s">
         <v>118</v>
       </c>
-      <c r="C52" s="232" t="s">
+      <c r="C52" s="225" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="232" t="s">
+      <c r="E52" s="225" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="231" t="s">
+      <c r="A53" s="224" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="232" t="s">
+      <c r="B53" s="225" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="239"/>
-      <c r="E53" s="239"/>
-      <c r="F53" s="239"/>
-      <c r="G53" s="239"/>
+      <c r="D53" s="232"/>
+      <c r="E53" s="232"/>
+      <c r="F53" s="232"/>
+      <c r="G53" s="232"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="231" t="s">
+      <c r="A54" s="224" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="232" t="s">
+      <c r="B54" s="225" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="232" t="s">
+      <c r="C54" s="225" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="239"/>
-      <c r="E54" s="239"/>
-      <c r="F54" s="239"/>
-      <c r="G54" s="239"/>
+      <c r="D54" s="232"/>
+      <c r="E54" s="232"/>
+      <c r="F54" s="232"/>
+      <c r="G54" s="232"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="231" t="s">
+      <c r="A55" s="224" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="239"/>
-      <c r="C55" s="239"/>
-      <c r="D55" s="232" t="s">
+      <c r="B55" s="232"/>
+      <c r="C55" s="232"/>
+      <c r="D55" s="225" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="231" t="s">
+      <c r="A56" s="224" t="s">
         <v>128</v>
       </c>
       <c r="B56" s="78" t="s">
         <v>129</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="232" t="s">
+      <c r="D56" s="225" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="231" t="s">
+      <c r="A57" s="224" t="s">
         <v>131</v>
       </c>
       <c r="B57" s="78" t="s">
@@ -5708,76 +5687,76 @@
       <c r="C57" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="232" t="s">
+      <c r="D57" s="225" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="231" t="s">
+      <c r="A58" s="224" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="232" t="s">
+      <c r="B58" s="225" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="239"/>
-      <c r="D58" s="239"/>
-      <c r="E58" s="239"/>
-      <c r="F58" s="239"/>
-      <c r="G58" s="239"/>
+      <c r="C58" s="232"/>
+      <c r="D58" s="232"/>
+      <c r="E58" s="232"/>
+      <c r="F58" s="232"/>
+      <c r="G58" s="232"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="231" t="s">
+      <c r="A59" s="224" t="s">
         <v>137</v>
       </c>
-      <c r="B59" s="239"/>
-      <c r="C59" s="232" t="s">
+      <c r="B59" s="232"/>
+      <c r="C59" s="225" t="s">
         <v>138</v>
       </c>
-      <c r="D59" s="239"/>
-      <c r="E59" s="239"/>
-      <c r="F59" s="239"/>
-      <c r="G59" s="239"/>
+      <c r="D59" s="232"/>
+      <c r="E59" s="232"/>
+      <c r="F59" s="232"/>
+      <c r="G59" s="232"/>
     </row>
     <row r="60" ht="65" spans="1:7">
-      <c r="A60" s="231" t="s">
+      <c r="A60" s="224" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="239" t="s">
+      <c r="B60" s="232" t="s">
         <v>140</v>
       </c>
-      <c r="C60" s="239"/>
-      <c r="D60" s="232" t="s">
+      <c r="C60" s="232"/>
+      <c r="D60" s="225" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="231" t="s">
+      <c r="A61" s="224" t="s">
         <v>142</v>
       </c>
       <c r="B61" s="78" t="s">
         <v>143</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="239"/>
-      <c r="E61" s="239"/>
-      <c r="F61" s="239"/>
-      <c r="G61" s="239"/>
+      <c r="D61" s="232"/>
+      <c r="E61" s="232"/>
+      <c r="F61" s="232"/>
+      <c r="G61" s="232"/>
     </row>
     <row r="62" ht="52" spans="1:7">
-      <c r="A62" s="231" t="s">
+      <c r="A62" s="224" t="s">
         <v>144</v>
       </c>
-      <c r="B62" s="239"/>
-      <c r="C62" s="239"/>
-      <c r="D62" s="232" t="s">
+      <c r="B62" s="232"/>
+      <c r="C62" s="232"/>
+      <c r="D62" s="225" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="232" t="s">
+      <c r="E62" s="225" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="231" t="s">
+      <c r="A63" s="224" t="s">
         <v>147</v>
       </c>
       <c r="B63" s="78" t="s">
@@ -5786,66 +5765,66 @@
       <c r="C63" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="239"/>
-      <c r="E63" s="239"/>
-      <c r="F63" s="239"/>
-      <c r="G63" s="239"/>
+      <c r="D63" s="232"/>
+      <c r="E63" s="232"/>
+      <c r="F63" s="232"/>
+      <c r="G63" s="232"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="231" t="s">
+      <c r="A64" s="224" t="s">
         <v>150</v>
       </c>
-      <c r="B64" s="239"/>
-      <c r="C64" s="239"/>
-      <c r="D64" s="232" t="s">
+      <c r="B64" s="232"/>
+      <c r="C64" s="232"/>
+      <c r="D64" s="225" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="231" t="s">
+      <c r="A65" s="224" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="240" t="s">
+      <c r="B65" s="233" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="239"/>
-      <c r="D65" s="239"/>
-      <c r="E65" s="239"/>
-      <c r="F65" s="239"/>
-      <c r="G65" s="239"/>
+      <c r="C65" s="232"/>
+      <c r="D65" s="232"/>
+      <c r="E65" s="232"/>
+      <c r="F65" s="232"/>
+      <c r="G65" s="232"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="231" t="s">
+      <c r="A66" s="224" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="239"/>
-      <c r="C66" s="232" t="s">
+      <c r="B66" s="232"/>
+      <c r="C66" s="225" t="s">
         <v>155</v>
       </c>
-      <c r="D66" s="239"/>
-      <c r="E66" s="239"/>
-      <c r="F66" s="239"/>
-      <c r="G66" s="239"/>
+      <c r="D66" s="232"/>
+      <c r="E66" s="232"/>
+      <c r="F66" s="232"/>
+      <c r="G66" s="232"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="231" t="s">
+      <c r="A67" s="224" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="239"/>
-      <c r="C67" s="239"/>
+      <c r="B67" s="232"/>
+      <c r="C67" s="232"/>
     </row>
     <row r="68" ht="78" spans="1:7">
-      <c r="A68" s="231" t="s">
+      <c r="A68" s="224" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="239"/>
-      <c r="C68" s="239"/>
-      <c r="D68" s="232" t="s">
+      <c r="B68" s="232"/>
+      <c r="C68" s="232"/>
+      <c r="D68" s="225" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="231" t="s">
+      <c r="A69" s="224" t="s">
         <v>159</v>
       </c>
       <c r="B69" s="78" t="s">
@@ -5854,89 +5833,89 @@
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="231" t="s">
+      <c r="A70" s="224" t="s">
         <v>161</v>
       </c>
       <c r="B70" s="78" t="s">
         <v>162</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="239"/>
-      <c r="E70" s="239"/>
-      <c r="F70" s="239"/>
-      <c r="G70" s="239"/>
+      <c r="D70" s="232"/>
+      <c r="E70" s="232"/>
+      <c r="F70" s="232"/>
+      <c r="G70" s="232"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="231" t="s">
+      <c r="A71" s="224" t="s">
         <v>163</v>
       </c>
-      <c r="B71" s="239"/>
-      <c r="C71" s="239"/>
+      <c r="B71" s="232"/>
+      <c r="C71" s="232"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="231" t="s">
+      <c r="A72" s="224" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="232" t="s">
+      <c r="B72" s="225" t="s">
         <v>165</v>
       </c>
-      <c r="C72" s="232" t="s">
+      <c r="C72" s="225" t="s">
         <v>166</v>
       </c>
-      <c r="D72" s="239"/>
-      <c r="E72" s="239"/>
-      <c r="F72" s="239"/>
-      <c r="G72" s="239"/>
+      <c r="D72" s="232"/>
+      <c r="E72" s="232"/>
+      <c r="F72" s="232"/>
+      <c r="G72" s="232"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="231" t="s">
+      <c r="A73" s="224" t="s">
         <v>167</v>
       </c>
-      <c r="B73" s="239"/>
-      <c r="C73" s="232" t="s">
+      <c r="B73" s="232"/>
+      <c r="C73" s="225" t="s">
         <v>168</v>
       </c>
-      <c r="D73" s="239"/>
-      <c r="E73" s="239"/>
-      <c r="F73" s="239"/>
-      <c r="G73" s="239"/>
+      <c r="D73" s="232"/>
+      <c r="E73" s="232"/>
+      <c r="F73" s="232"/>
+      <c r="G73" s="232"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="231" t="s">
+      <c r="A74" s="224" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="231" t="s">
+      <c r="A75" s="224" t="s">
         <v>170</v>
       </c>
-      <c r="D75" s="239"/>
-      <c r="E75" s="239"/>
-      <c r="F75" s="239"/>
-      <c r="G75" s="239"/>
+      <c r="D75" s="232"/>
+      <c r="E75" s="232"/>
+      <c r="F75" s="232"/>
+      <c r="G75" s="232"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="231" t="s">
+      <c r="A76" s="224" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="239"/>
-      <c r="C76" s="239"/>
-      <c r="D76" s="232" t="s">
+      <c r="B76" s="232"/>
+      <c r="C76" s="232"/>
+      <c r="D76" s="225" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="231" t="s">
+      <c r="A77" s="224" t="s">
         <v>173</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="241" t="s">
+      <c r="A78" s="234" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="232" t="s">
+      <c r="B78" s="225" t="s">
         <v>175</v>
       </c>
     </row>
@@ -8286,14 +8265,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="225" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="218" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="226"/>
+    <col min="8" max="16384" width="8.72727272727273" style="219"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="227"/>
+      <c r="A1" s="220"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8313,8 +8292,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="224" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="228" t="s">
+    <row r="2" s="217" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="221" t="s">
         <v>176</v>
       </c>
       <c r="B2" s="78"/>
@@ -8327,7 +8306,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="229" t="s">
+      <c r="A3" s="222" t="s">
         <v>178</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8335,7 +8314,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="229" t="s">
+      <c r="A4" s="222" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8346,7 +8325,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="229" t="s">
+      <c r="A5" s="222" t="s">
         <v>183</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8357,7 +8336,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="229" t="s">
+      <c r="A6" s="222" t="s">
         <v>186</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8368,7 +8347,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="229" t="s">
+      <c r="A7" s="222" t="s">
         <v>189</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8376,127 +8355,127 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="229"/>
+      <c r="A8" s="222"/>
       <c r="D8" s="66" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="229"/>
+      <c r="A9" s="222"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="229"/>
+      <c r="A10" s="222"/>
       <c r="B10" s="66" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="229"/>
+      <c r="A11" s="222"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="229"/>
+      <c r="A12" s="222"/>
       <c r="B12" s="66" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="229"/>
+      <c r="A13" s="222"/>
       <c r="B13" s="66" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="229"/>
+      <c r="A14" s="222"/>
       <c r="B14" s="66" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="229"/>
+      <c r="A15" s="222"/>
       <c r="B15" s="66" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="229"/>
+      <c r="A16" s="222"/>
       <c r="B16" s="66" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="229"/>
+      <c r="A17" s="222"/>
       <c r="B17" s="66" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="229"/>
+      <c r="A18" s="222"/>
       <c r="B18" s="66" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:2">
-      <c r="A19" s="229"/>
+      <c r="A19" s="222"/>
       <c r="B19" s="78" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="229"/>
+      <c r="A20" s="222"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="229"/>
+      <c r="A21" s="222"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="229"/>
+      <c r="A22" s="222"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="229"/>
+      <c r="A23" s="222"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="229"/>
+      <c r="A24" s="222"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="229"/>
+      <c r="A25" s="222"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="229"/>
+      <c r="A26" s="222"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="229"/>
+      <c r="A27" s="222"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="229"/>
+      <c r="A28" s="222"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="229"/>
+      <c r="A29" s="222"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="229"/>
+      <c r="A30" s="222"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="229"/>
+      <c r="A31" s="222"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="229"/>
+      <c r="A32" s="222"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="229"/>
+      <c r="A33" s="222"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="229"/>
+      <c r="A34" s="222"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="229"/>
+      <c r="A35" s="222"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="229"/>
+      <c r="A36" s="222"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="229"/>
+      <c r="A37" s="222"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="229"/>
+      <c r="A38" s="222"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8505,7 +8484,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="229"/>
+      <c r="A39" s="222"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8514,40 +8493,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="229"/>
+      <c r="A40" s="222"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="229"/>
+      <c r="A41" s="222"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="229"/>
+      <c r="A42" s="222"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="229"/>
+      <c r="A43" s="222"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="229"/>
+      <c r="A44" s="222"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="229"/>
+      <c r="A45" s="222"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="229"/>
+      <c r="A46" s="222"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="229"/>
+      <c r="A47" s="222"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="229"/>
+      <c r="A48" s="222"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="229"/>
+      <c r="A49" s="222"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="229"/>
+      <c r="A50" s="222"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="229"/>
+      <c r="A51" s="222"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8563,499 +8542,499 @@
   <dimension ref="A1:C52"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="212" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="212" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="212" customWidth="1"/>
+    <col min="1" max="1" width="24" style="208" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="208" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="208" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="211" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="213" t="s">
+    <row r="1" s="207" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="209" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="213" t="s">
+      <c r="B1" s="209" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="213" t="s">
+      <c r="C1" s="209" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="214" t="s">
+      <c r="A2" s="210" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="210" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="214" t="s">
+      <c r="C2" s="210" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="214" t="s">
+      <c r="A3" s="210" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="214" t="s">
+      <c r="B3" s="210" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="214" t="s">
+      <c r="C3" s="210" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="214" t="s">
+      <c r="A4" s="210" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="214" t="s">
+      <c r="B4" s="210" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="214" t="s">
+      <c r="C4" s="210" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="215" t="s">
+      <c r="A5" s="211" t="s">
         <v>212</v>
       </c>
-      <c r="B5" s="214" t="s">
+      <c r="B5" s="210" t="s">
         <v>213</v>
       </c>
-      <c r="C5" s="214" t="s">
+      <c r="C5" s="210" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="216"/>
-      <c r="B6" s="214" t="s">
+      <c r="A6" s="212"/>
+      <c r="B6" s="210" t="s">
         <v>215</v>
       </c>
-      <c r="C6" s="214" t="s">
+      <c r="C6" s="210" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="217" t="s">
+      <c r="A7" s="213" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="214" t="s">
+      <c r="B7" s="210" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="214" t="s">
+      <c r="C7" s="210" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
-      <c r="A8" s="217"/>
-      <c r="B8" s="214" t="s">
+      <c r="A8" s="213"/>
+      <c r="B8" s="210" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="214" t="s">
+      <c r="C8" s="210" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="217"/>
-      <c r="B9" s="214" t="s">
+      <c r="A9" s="213"/>
+      <c r="B9" s="210" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="214" t="s">
+      <c r="C9" s="210" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="217"/>
-      <c r="B10" s="214" t="s">
+      <c r="A10" s="213"/>
+      <c r="B10" s="210" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="214" t="s">
+      <c r="C10" s="210" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="217"/>
-      <c r="B11" s="214"/>
-      <c r="C11" s="214"/>
+      <c r="A11" s="213"/>
+      <c r="B11" s="210"/>
+      <c r="C11" s="210"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="217"/>
-      <c r="B12" s="214"/>
-      <c r="C12" s="214"/>
+      <c r="A12" s="213"/>
+      <c r="B12" s="210"/>
+      <c r="C12" s="210"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="217"/>
-      <c r="B13" s="214"/>
-      <c r="C13" s="214"/>
+      <c r="A13" s="213"/>
+      <c r="B13" s="210"/>
+      <c r="C13" s="210"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="218"/>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
+      <c r="A14" s="214"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="214" t="s">
+      <c r="A15" s="210" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="214" t="s">
+      <c r="B15" s="210" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="214" t="s">
+      <c r="C15" s="210" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="214" t="s">
+      <c r="A16" s="210" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="214" t="s">
+      <c r="B16" s="210" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="214" t="s">
+      <c r="C16" s="210" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="214" t="s">
+      <c r="A17" s="210" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="214" t="s">
+      <c r="B17" s="210" t="s">
         <v>232</v>
       </c>
-      <c r="C17" s="219">
+      <c r="C17" s="215">
         <v>0.440972222222222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="220" t="s">
+      <c r="A18" s="216" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="214" t="s">
+      <c r="B18" s="210" t="s">
         <v>233</v>
       </c>
-      <c r="C18" s="214" t="s">
+      <c r="C18" s="210" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="217"/>
-      <c r="B19" s="214" t="s">
+      <c r="A19" s="213"/>
+      <c r="B19" s="210" t="s">
         <v>235</v>
       </c>
-      <c r="C19" s="214" t="s">
+      <c r="C19" s="210" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="20" ht="56" spans="1:3">
-      <c r="A20" s="217"/>
-      <c r="B20" s="214" t="s">
+      <c r="A20" s="213"/>
+      <c r="B20" s="210" t="s">
         <v>237</v>
       </c>
-      <c r="C20" s="214" t="s">
+      <c r="C20" s="210" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="217"/>
-      <c r="B21" s="214" t="s">
+      <c r="A21" s="213"/>
+      <c r="B21" s="210" t="s">
         <v>239</v>
       </c>
-      <c r="C21" s="214" t="s">
+      <c r="C21" s="210" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:3">
-      <c r="A22" s="217"/>
-      <c r="B22" s="214" t="s">
+      <c r="A22" s="213"/>
+      <c r="B22" s="210" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="214" t="s">
+      <c r="C22" s="210" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="217"/>
-      <c r="B23" s="214"/>
-      <c r="C23" s="214"/>
+      <c r="A23" s="213"/>
+      <c r="B23" s="210"/>
+      <c r="C23" s="210"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="217"/>
-      <c r="B24" s="214"/>
-      <c r="C24" s="214"/>
+      <c r="A24" s="213"/>
+      <c r="B24" s="210"/>
+      <c r="C24" s="210"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="217"/>
-      <c r="B25" s="214"/>
-      <c r="C25" s="214"/>
+      <c r="A25" s="213"/>
+      <c r="B25" s="210"/>
+      <c r="C25" s="210"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="215" t="s">
+      <c r="A26" s="211" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="214" t="s">
+      <c r="B26" s="210" t="s">
         <v>235</v>
       </c>
-      <c r="C26" s="214" t="s">
+      <c r="C26" s="210" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="216"/>
-      <c r="B27" s="214" t="s">
+      <c r="A27" s="212"/>
+      <c r="B27" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="C27" s="214" t="s">
+      <c r="C27" s="210" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:3">
-      <c r="A28" s="220" t="s">
+      <c r="A28" s="216" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="214" t="s">
+      <c r="B28" s="210" t="s">
         <v>248</v>
       </c>
-      <c r="C28" s="214" t="s">
+      <c r="C28" s="210" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="217"/>
-      <c r="B29" s="214" t="s">
+      <c r="A29" s="213"/>
+      <c r="B29" s="210" t="s">
         <v>219</v>
       </c>
-      <c r="C29" s="214" t="s">
+      <c r="C29" s="210" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="217"/>
-      <c r="B30" s="214" t="s">
+      <c r="A30" s="213"/>
+      <c r="B30" s="210" t="s">
         <v>251</v>
       </c>
-      <c r="C30" s="214" t="s">
+      <c r="C30" s="210" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="217"/>
-      <c r="B31" s="214"/>
-      <c r="C31" s="214"/>
+      <c r="A31" s="213"/>
+      <c r="B31" s="210"/>
+      <c r="C31" s="210"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="215" t="s">
+      <c r="A32" s="211" t="s">
         <v>253</v>
       </c>
-      <c r="B32" s="214" t="s">
+      <c r="B32" s="210" t="s">
         <v>254</v>
       </c>
-      <c r="C32" s="214" t="s">
+      <c r="C32" s="210" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="216"/>
-      <c r="B33" s="214" t="s">
+      <c r="A33" s="212"/>
+      <c r="B33" s="210" t="s">
         <v>217</v>
       </c>
-      <c r="C33" s="214" t="s">
+      <c r="C33" s="210" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:3">
-      <c r="A34" s="220" t="s">
+      <c r="A34" s="216" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="214" t="s">
+      <c r="B34" s="210" t="s">
         <v>217</v>
       </c>
-      <c r="C34" s="214" t="s">
+      <c r="C34" s="210" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="217"/>
-      <c r="B35" s="212" t="s">
+      <c r="A35" s="213"/>
+      <c r="B35" s="208" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="212" t="s">
+      <c r="C35" s="208" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="217"/>
-      <c r="B36" s="212" t="s">
+      <c r="A36" s="213"/>
+      <c r="B36" s="208" t="s">
         <v>239</v>
       </c>
-      <c r="C36" s="212" t="s">
+      <c r="C36" s="208" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="37" ht="98" spans="1:3">
-      <c r="A37" s="221" t="s">
+      <c r="A37" s="216" t="s">
         <v>261</v>
       </c>
-      <c r="B37" s="212" t="s">
+      <c r="B37" s="208" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="212" t="s">
+      <c r="C37" s="208" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="38" ht="84" spans="1:3">
-      <c r="A38" s="222"/>
-      <c r="B38" s="212" t="s">
+      <c r="A38" s="213"/>
+      <c r="B38" s="208" t="s">
         <v>263</v>
       </c>
-      <c r="C38" s="212" t="s">
+      <c r="C38" s="208" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="39" ht="28" spans="1:3">
-      <c r="A39" s="223"/>
-      <c r="B39" s="212" t="s">
+      <c r="A39" s="214"/>
+      <c r="B39" s="208" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="212" t="s">
+      <c r="C39" s="208" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="212" t="s">
+      <c r="A40" s="208" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="212" t="s">
+      <c r="B40" s="208" t="s">
         <v>267</v>
       </c>
-      <c r="C40" s="212" t="s">
+      <c r="C40" s="208" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="220" t="s">
+      <c r="A41" s="216" t="s">
         <v>269</v>
       </c>
-      <c r="B41" s="212" t="s">
+      <c r="B41" s="208" t="s">
         <v>219</v>
       </c>
-      <c r="C41" s="212" t="s">
+      <c r="C41" s="208" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="218"/>
-      <c r="B42" s="212" t="s">
+      <c r="A42" s="214"/>
+      <c r="B42" s="208" t="s">
         <v>263</v>
       </c>
-      <c r="C42" s="212" t="s">
+      <c r="C42" s="208" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="212" t="s">
+      <c r="A43" s="208" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="212" t="s">
+      <c r="B43" s="208" t="s">
         <v>221</v>
       </c>
-      <c r="C43" s="212" t="s">
+      <c r="C43" s="208" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="212" t="s">
+      <c r="A44" s="208" t="s">
         <v>273</v>
       </c>
-      <c r="B44" s="212" t="s">
+      <c r="B44" s="208" t="s">
         <v>274</v>
       </c>
-      <c r="C44" s="212" t="s">
+      <c r="C44" s="208" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="212" t="s">
+      <c r="A45" s="208" t="s">
         <v>276</v>
       </c>
-      <c r="B45" s="212" t="s">
+      <c r="B45" s="208" t="s">
         <v>277</v>
       </c>
-      <c r="C45" s="212" t="s">
+      <c r="C45" s="208" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="212" t="s">
+      <c r="A46" s="208" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="212" t="s">
+      <c r="B46" s="208" t="s">
         <v>263</v>
       </c>
-      <c r="C46" s="212" t="s">
+      <c r="C46" s="208" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="212" t="s">
+      <c r="A47" s="208" t="s">
         <v>280</v>
       </c>
-      <c r="B47" s="212" t="s">
+      <c r="B47" s="208" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="212" t="s">
+      <c r="C47" s="208" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="212" t="s">
+      <c r="A48" s="208" t="s">
         <v>283</v>
       </c>
-      <c r="B48" s="212" t="s">
+      <c r="B48" s="208" t="s">
         <v>284</v>
       </c>
-      <c r="C48" s="212" t="s">
+      <c r="C48" s="208" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="212" t="s">
+      <c r="A49" s="208" t="s">
         <v>286</v>
       </c>
-      <c r="B49" s="212" t="s">
+      <c r="B49" s="208" t="s">
         <v>284</v>
       </c>
-      <c r="C49" s="212" t="s">
+      <c r="C49" s="208" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="212" t="s">
+      <c r="A50" s="208" t="s">
         <v>288</v>
       </c>
-      <c r="B50" s="212" t="s">
+      <c r="B50" s="208" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="212" t="s">
+      <c r="C50" s="208" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="51" ht="28" spans="1:3">
-      <c r="A51" s="212" t="s">
+      <c r="A51" s="208" t="s">
         <v>290</v>
       </c>
-      <c r="B51" s="212" t="s">
+      <c r="B51" s="208" t="s">
         <v>265</v>
       </c>
-      <c r="C51" s="212" t="s">
+      <c r="C51" s="208" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:3">
-      <c r="A52" s="212" t="s">
+      <c r="A52" s="208" t="s">
         <v>292</v>
       </c>
-      <c r="B52" s="212" t="s">
+      <c r="B52" s="208" t="s">
         <v>265</v>
       </c>
-      <c r="C52" s="212" t="s">
+      <c r="C52" s="208" t="s">
         <v>293</v>
       </c>
     </row>
@@ -9088,45 +9067,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="200"/>
+    <col min="5" max="5" width="8.72727272727273" style="196"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="198" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="201" t="s">
+    <row r="1" s="194" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="197" t="s">
         <v>294</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="198" t="s">
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="199"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="194" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="2" s="199" customFormat="1" spans="1:7">
-      <c r="A2" s="205" t="s">
+    <row r="2" s="195" customFormat="1" spans="1:7">
+      <c r="A2" s="201" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="206"/>
-      <c r="C2" s="199" t="s">
+      <c r="B2" s="202"/>
+      <c r="C2" s="195" t="s">
         <v>296</v>
       </c>
-      <c r="D2" s="199" t="s">
+      <c r="D2" s="195" t="s">
         <v>297</v>
       </c>
       <c r="E2" s="142"/>
-      <c r="F2" s="199" t="s">
+      <c r="F2" s="195" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="199" t="s">
+      <c r="G2" s="195" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="207">
+      <c r="A3" s="203">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -9144,7 +9123,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="208"/>
+      <c r="A4" s="204"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -9160,7 +9139,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="208"/>
+      <c r="A5" s="204"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -9176,7 +9155,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="208"/>
+      <c r="A6" s="204"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9184,7 +9163,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="209" t="s">
+      <c r="F6" s="205" t="s">
         <v>305</v>
       </c>
       <c r="G6" s="119" t="s">
@@ -9192,7 +9171,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="208"/>
+      <c r="A7" s="204"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9200,13 +9179,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="210"/>
+      <c r="F7" s="206"/>
       <c r="G7" s="119" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="208"/>
+      <c r="A8" s="204"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9218,7 +9197,7 @@
       <c r="G8" s="119"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="210"/>
+      <c r="A9" s="206"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9230,7 +9209,7 @@
       <c r="G9" s="119"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="209">
+      <c r="A10" s="205">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9244,7 +9223,7 @@
       <c r="G10" s="119"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="208"/>
+      <c r="A11" s="204"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9256,7 +9235,7 @@
       <c r="G11" s="119"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="210"/>
+      <c r="A12" s="206"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9268,7 +9247,7 @@
       <c r="G12" s="119"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="209">
+      <c r="A13" s="205">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9284,7 +9263,7 @@
       <c r="G13" s="119"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="210"/>
+      <c r="A14" s="206"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -9323,266 +9302,266 @@
   <cols>
     <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
     <col min="2" max="55" width="3.23636363636364" customWidth="1"/>
-    <col min="56" max="58" width="4.81818181818182" style="178" customWidth="1"/>
-    <col min="59" max="59" width="7.18181818181818" style="178" customWidth="1"/>
-    <col min="60" max="62" width="4.81818181818182" style="178" customWidth="1"/>
+    <col min="56" max="58" width="4.81818181818182" style="175" customWidth="1"/>
+    <col min="59" max="59" width="7.18181818181818" style="175" customWidth="1"/>
+    <col min="60" max="62" width="4.81818181818182" style="175" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="176" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="180" t="s">
+      <c r="B1" s="177" t="s">
         <v>309</v>
       </c>
-      <c r="C1" s="181"/>
-      <c r="D1" s="181"/>
-      <c r="E1" s="181"/>
-      <c r="F1" s="181"/>
-      <c r="G1" s="181"/>
-      <c r="H1" s="181"/>
-      <c r="I1" s="181"/>
-      <c r="J1" s="181"/>
-      <c r="K1" s="181"/>
-      <c r="L1" s="181"/>
-      <c r="M1" s="181"/>
-      <c r="N1" s="181"/>
-      <c r="O1" s="181"/>
-      <c r="P1" s="181"/>
-      <c r="Q1" s="181"/>
-      <c r="R1" s="181"/>
-      <c r="S1" s="181"/>
-      <c r="T1" s="182" t="s">
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
+      <c r="M1" s="178"/>
+      <c r="N1" s="178"/>
+      <c r="O1" s="178"/>
+      <c r="P1" s="178"/>
+      <c r="Q1" s="178"/>
+      <c r="R1" s="178"/>
+      <c r="S1" s="178"/>
+      <c r="T1" s="179" t="s">
         <v>310</v>
       </c>
-      <c r="U1" s="183"/>
-      <c r="V1" s="183"/>
-      <c r="W1" s="183"/>
-      <c r="X1" s="183"/>
-      <c r="Y1" s="183"/>
-      <c r="Z1" s="183"/>
-      <c r="AA1" s="183"/>
-      <c r="AB1" s="183"/>
-      <c r="AC1" s="183"/>
-      <c r="AD1" s="183"/>
-      <c r="AE1" s="183"/>
-      <c r="AF1" s="183"/>
-      <c r="AG1" s="183"/>
-      <c r="AH1" s="183"/>
-      <c r="AI1" s="183"/>
-      <c r="AJ1" s="182" t="s">
+      <c r="U1" s="180"/>
+      <c r="V1" s="180"/>
+      <c r="W1" s="180"/>
+      <c r="X1" s="180"/>
+      <c r="Y1" s="180"/>
+      <c r="Z1" s="180"/>
+      <c r="AA1" s="180"/>
+      <c r="AB1" s="180"/>
+      <c r="AC1" s="180"/>
+      <c r="AD1" s="180"/>
+      <c r="AE1" s="180"/>
+      <c r="AF1" s="180"/>
+      <c r="AG1" s="180"/>
+      <c r="AH1" s="180"/>
+      <c r="AI1" s="180"/>
+      <c r="AJ1" s="179" t="s">
         <v>311</v>
       </c>
-      <c r="AK1" s="183"/>
-      <c r="AL1" s="183"/>
-      <c r="AM1" s="182" t="s">
+      <c r="AK1" s="180"/>
+      <c r="AL1" s="180"/>
+      <c r="AM1" s="179" t="s">
         <v>312</v>
       </c>
-      <c r="AN1" s="183"/>
-      <c r="AO1" s="183"/>
-      <c r="AP1" s="183"/>
-      <c r="AQ1" s="183"/>
-      <c r="AR1" s="183"/>
-      <c r="AS1" s="183"/>
-      <c r="AT1" s="183"/>
-      <c r="AU1" s="183"/>
-      <c r="AV1" s="183"/>
-      <c r="AW1" s="183"/>
-      <c r="AX1" s="183"/>
-      <c r="AY1" s="183"/>
-      <c r="AZ1" s="183"/>
-      <c r="BA1" s="183"/>
-      <c r="BB1" s="183"/>
-      <c r="BC1" s="184"/>
-      <c r="BD1" s="185" t="s">
+      <c r="AN1" s="180"/>
+      <c r="AO1" s="180"/>
+      <c r="AP1" s="180"/>
+      <c r="AQ1" s="180"/>
+      <c r="AR1" s="180"/>
+      <c r="AS1" s="180"/>
+      <c r="AT1" s="180"/>
+      <c r="AU1" s="180"/>
+      <c r="AV1" s="180"/>
+      <c r="AW1" s="180"/>
+      <c r="AX1" s="180"/>
+      <c r="AY1" s="180"/>
+      <c r="AZ1" s="180"/>
+      <c r="BA1" s="180"/>
+      <c r="BB1" s="180"/>
+      <c r="BC1" s="181"/>
+      <c r="BD1" s="182" t="s">
         <v>313</v>
       </c>
-      <c r="BE1" s="186"/>
-      <c r="BF1" s="186"/>
-      <c r="BG1" s="186"/>
-      <c r="BH1" s="186"/>
-      <c r="BI1" s="186"/>
-      <c r="BJ1" s="187"/>
-    </row>
-    <row r="2" s="177" customFormat="1" ht="28" spans="1:62">
-      <c r="A2" s="179"/>
-      <c r="B2" s="188">
+      <c r="BE1" s="183"/>
+      <c r="BF1" s="183"/>
+      <c r="BG1" s="183"/>
+      <c r="BH1" s="183"/>
+      <c r="BI1" s="183"/>
+      <c r="BJ1" s="184"/>
+    </row>
+    <row r="2" s="174" customFormat="1" ht="28" spans="1:62">
+      <c r="A2" s="176"/>
+      <c r="B2" s="185">
         <v>5</v>
       </c>
-      <c r="C2" s="188">
+      <c r="C2" s="185">
         <v>6</v>
       </c>
-      <c r="D2" s="188">
+      <c r="D2" s="185">
         <v>9</v>
       </c>
-      <c r="E2" s="188">
+      <c r="E2" s="185">
         <v>10</v>
       </c>
-      <c r="F2" s="188">
+      <c r="F2" s="185">
         <v>11</v>
       </c>
-      <c r="G2" s="188">
+      <c r="G2" s="185">
         <v>12</v>
       </c>
-      <c r="H2" s="188">
+      <c r="H2" s="185">
         <v>15</v>
       </c>
-      <c r="I2" s="188">
+      <c r="I2" s="185">
         <v>16</v>
       </c>
-      <c r="J2" s="188">
+      <c r="J2" s="185">
         <v>17</v>
       </c>
-      <c r="K2" s="188">
+      <c r="K2" s="185">
         <v>18</v>
       </c>
-      <c r="L2" s="188">
+      <c r="L2" s="185">
         <v>19</v>
       </c>
-      <c r="M2" s="188">
+      <c r="M2" s="185">
         <v>22</v>
       </c>
-      <c r="N2" s="188">
+      <c r="N2" s="185">
         <v>23</v>
       </c>
-      <c r="O2" s="188">
+      <c r="O2" s="185">
         <v>25</v>
       </c>
-      <c r="P2" s="188">
+      <c r="P2" s="185">
         <v>26</v>
       </c>
-      <c r="Q2" s="188">
+      <c r="Q2" s="185">
         <v>29</v>
       </c>
-      <c r="R2" s="188">
+      <c r="R2" s="185">
         <v>30</v>
       </c>
-      <c r="S2" s="188">
+      <c r="S2" s="185">
         <v>31</v>
       </c>
-      <c r="T2" s="188">
+      <c r="T2" s="185">
         <v>4</v>
       </c>
-      <c r="U2" s="188">
+      <c r="U2" s="185">
         <v>5</v>
       </c>
-      <c r="V2" s="188">
+      <c r="V2" s="185">
         <v>6</v>
       </c>
-      <c r="W2" s="188">
+      <c r="W2" s="185">
         <v>7</v>
       </c>
-      <c r="X2" s="188">
+      <c r="X2" s="185">
         <v>8</v>
       </c>
-      <c r="Y2" s="188">
+      <c r="Y2" s="185">
         <v>11</v>
       </c>
-      <c r="Z2" s="188">
+      <c r="Z2" s="185">
         <v>12</v>
       </c>
-      <c r="AA2" s="188">
+      <c r="AA2" s="185">
         <v>13</v>
       </c>
-      <c r="AB2" s="188">
+      <c r="AB2" s="185">
         <v>14</v>
       </c>
-      <c r="AC2" s="188">
+      <c r="AC2" s="185">
         <v>15</v>
       </c>
-      <c r="AD2" s="188">
+      <c r="AD2" s="185">
         <v>16</v>
       </c>
-      <c r="AE2" s="188">
+      <c r="AE2" s="185">
         <v>19</v>
       </c>
-      <c r="AF2" s="188">
+      <c r="AF2" s="185">
         <v>20</v>
       </c>
-      <c r="AG2" s="188">
+      <c r="AG2" s="185">
         <v>21</v>
       </c>
-      <c r="AH2" s="188">
+      <c r="AH2" s="185">
         <v>22</v>
       </c>
-      <c r="AI2" s="188">
+      <c r="AI2" s="185">
         <v>23</v>
       </c>
-      <c r="AJ2" s="188">
+      <c r="AJ2" s="185">
         <v>26</v>
       </c>
-      <c r="AK2" s="188">
+      <c r="AK2" s="185">
         <v>27</v>
       </c>
-      <c r="AL2" s="188">
+      <c r="AL2" s="185">
         <v>28</v>
       </c>
-      <c r="AM2" s="188">
+      <c r="AM2" s="185">
         <v>2</v>
       </c>
-      <c r="AN2" s="188">
+      <c r="AN2" s="185">
         <v>3</v>
       </c>
-      <c r="AO2" s="188">
+      <c r="AO2" s="185">
         <v>4</v>
       </c>
-      <c r="AP2" s="188">
+      <c r="AP2" s="185">
         <v>5</v>
       </c>
-      <c r="AQ2" s="188">
+      <c r="AQ2" s="185">
         <v>6</v>
       </c>
-      <c r="AR2" s="188">
+      <c r="AR2" s="185">
         <v>9</v>
       </c>
-      <c r="AS2" s="188">
+      <c r="AS2" s="185">
         <v>10</v>
       </c>
-      <c r="AT2" s="188">
+      <c r="AT2" s="185">
         <v>11</v>
       </c>
-      <c r="AU2" s="188">
+      <c r="AU2" s="185">
         <v>12</v>
       </c>
-      <c r="AV2" s="188">
+      <c r="AV2" s="185">
         <v>13</v>
       </c>
-      <c r="AW2" s="188">
+      <c r="AW2" s="185">
         <v>16</v>
       </c>
-      <c r="AX2" s="188">
+      <c r="AX2" s="185">
         <v>17</v>
       </c>
-      <c r="AY2" s="188">
+      <c r="AY2" s="185">
         <v>18</v>
       </c>
-      <c r="AZ2" s="188">
+      <c r="AZ2" s="185">
         <v>19</v>
       </c>
-      <c r="BA2" s="188">
+      <c r="BA2" s="185">
         <v>20</v>
       </c>
-      <c r="BB2" s="188"/>
-      <c r="BC2" s="188"/>
-      <c r="BD2" s="189" t="s">
+      <c r="BB2" s="185"/>
+      <c r="BC2" s="185"/>
+      <c r="BD2" s="186" t="s">
         <v>314</v>
       </c>
-      <c r="BE2" s="189" t="s">
+      <c r="BE2" s="186" t="s">
         <v>315</v>
       </c>
-      <c r="BF2" s="189" t="s">
+      <c r="BF2" s="186" t="s">
         <v>316</v>
       </c>
-      <c r="BG2" s="189" t="s">
+      <c r="BG2" s="186" t="s">
         <v>317</v>
       </c>
-      <c r="BH2" s="190" t="s">
+      <c r="BH2" s="187" t="s">
         <v>318</v>
       </c>
-      <c r="BI2" s="190" t="s">
+      <c r="BI2" s="187" t="s">
         <v>319</v>
       </c>
-      <c r="BJ2" s="190" t="s">
+      <c r="BJ2" s="187" t="s">
         <v>320</v>
       </c>
     </row>
@@ -9646,31 +9625,31 @@
       <c r="BA3" s="120"/>
       <c r="BB3" s="120"/>
       <c r="BC3" s="120"/>
-      <c r="BD3" s="191">
+      <c r="BD3" s="188">
         <f t="shared" ref="BD3:BD53" si="0">SUM(B3:BC3)</f>
         <v>1</v>
       </c>
-      <c r="BE3" s="191" cm="1">
+      <c r="BE3" s="188" cm="1">
         <f t="array" ref="BE3">SUMPRODUCT(--(B3:BC3=INT(B3:BC3)),--(B3:BC3&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF3" s="191" cm="1">
+      <c r="BF3" s="188" cm="1">
         <f t="array" ref="BF3">MAX(FREQUENCY(IF((B3:BC3=INT(B3:BC3))*(B3:BC3&gt;0),COLUMN(B3:BC3)),IF((B3:BC3&lt;&gt;INT(B3:BC3))+(B3:BC3&lt;=0),COLUMN(B3:BC3))))</f>
         <v>1</v>
       </c>
-      <c r="BG3" s="192" cm="1">
+      <c r="BG3" s="189" cm="1">
         <f t="array" ref="BG3">SUMPRODUCT(--(B3:AI3=INT(B3:AI3)),--(B3:AI3&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH3" s="193">
+      <c r="BH3" s="190">
         <f t="shared" ref="BH3:BH53" si="1">RANK(BD3,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI3" s="193">
+      <c r="BI3" s="190">
         <f t="shared" ref="BI3:BI53" si="2">RANK(BE3,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ3" s="193">
+      <c r="BJ3" s="190">
         <f t="shared" ref="BJ3:BJ53" si="3">RANK(BF3,BF$3:BF$53,0)</f>
         <v>22</v>
       </c>
@@ -9754,7 +9733,9 @@
       <c r="AT4" s="120">
         <v>1</v>
       </c>
-      <c r="AU4" s="120"/>
+      <c r="AU4" s="120">
+        <v>2</v>
+      </c>
       <c r="AV4" s="120"/>
       <c r="AW4" s="120"/>
       <c r="AX4" s="120"/>
@@ -9763,33 +9744,33 @@
       <c r="BA4" s="120"/>
       <c r="BB4" s="120"/>
       <c r="BC4" s="120"/>
-      <c r="BD4" s="191">
+      <c r="BD4" s="188">
         <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="BE4" s="188" cm="1">
+        <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
         <v>16</v>
       </c>
-      <c r="BE4" s="191" cm="1">
-        <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>15</v>
-      </c>
-      <c r="BF4" s="191" cm="1">
+      <c r="BF4" s="188" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
-        <v>3</v>
-      </c>
-      <c r="BG4" s="192" cm="1">
+        <v>4</v>
+      </c>
+      <c r="BG4" s="189" cm="1">
         <f t="array" ref="BG4">SUMPRODUCT(--(B4:AI4=INT(B4:AI4)),--(B4:AI4&gt;0))/34*100%</f>
         <v>0.323529411764706</v>
       </c>
-      <c r="BH4" s="193">
+      <c r="BH4" s="190">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="BI4" s="193">
+        <v>7</v>
+      </c>
+      <c r="BI4" s="190">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="BJ4" s="193">
+      <c r="BJ4" s="190">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:62">
@@ -9854,31 +9835,31 @@
       <c r="BA5" s="120"/>
       <c r="BB5" s="120"/>
       <c r="BC5" s="120"/>
-      <c r="BD5" s="191">
+      <c r="BD5" s="188">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE5" s="191" cm="1">
+      <c r="BE5" s="188" cm="1">
         <f t="array" ref="BE5">SUMPRODUCT(--(B5:BC5=INT(B5:BC5)),--(B5:BC5&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF5" s="191" cm="1">
+      <c r="BF5" s="188" cm="1">
         <f t="array" ref="BF5">MAX(FREQUENCY(IF((B5:BC5=INT(B5:BC5))*(B5:BC5&gt;0),COLUMN(B5:BC5)),IF((B5:BC5&lt;&gt;INT(B5:BC5))+(B5:BC5&lt;=0),COLUMN(B5:BC5))))</f>
         <v>1</v>
       </c>
-      <c r="BG5" s="192" cm="1">
+      <c r="BG5" s="189" cm="1">
         <f t="array" ref="BG5">SUMPRODUCT(--(B5:AI5=INT(B5:AI5)),--(B5:AI5&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH5" s="193">
+      <c r="BH5" s="190">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI5" s="193">
+      <c r="BI5" s="190">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ5" s="193">
+      <c r="BJ5" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -9955,33 +9936,33 @@
       <c r="BA6" s="120"/>
       <c r="BB6" s="120"/>
       <c r="BC6" s="120"/>
-      <c r="BD6" s="191">
+      <c r="BD6" s="188">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="BE6" s="191" cm="1">
+      <c r="BE6" s="188" cm="1">
         <f t="array" ref="BE6">SUMPRODUCT(--(B6:BC6=INT(B6:BC6)),--(B6:BC6&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF6" s="191" cm="1">
+      <c r="BF6" s="188" cm="1">
         <f t="array" ref="BF6">MAX(FREQUENCY(IF((B6:BC6=INT(B6:BC6))*(B6:BC6&gt;0),COLUMN(B6:BC6)),IF((B6:BC6&lt;&gt;INT(B6:BC6))+(B6:BC6&lt;=0),COLUMN(B6:BC6))))</f>
         <v>3</v>
       </c>
-      <c r="BG6" s="192" cm="1">
+      <c r="BG6" s="189" cm="1">
         <f t="array" ref="BG6">SUMPRODUCT(--(B6:AI6=INT(B6:AI6)),--(B6:AI6&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH6" s="193">
+      <c r="BH6" s="190">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="BI6" s="193">
+      <c r="BI6" s="190">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="BJ6" s="193">
+      <c r="BJ6" s="190">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:62">
@@ -10048,31 +10029,31 @@
       <c r="BA7" s="120"/>
       <c r="BB7" s="120"/>
       <c r="BC7" s="120"/>
-      <c r="BD7" s="191">
+      <c r="BD7" s="188">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE7" s="191" cm="1">
+      <c r="BE7" s="188" cm="1">
         <f t="array" ref="BE7">SUMPRODUCT(--(B7:BC7=INT(B7:BC7)),--(B7:BC7&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF7" s="191" cm="1">
+      <c r="BF7" s="188" cm="1">
         <f t="array" ref="BF7">MAX(FREQUENCY(IF((B7:BC7=INT(B7:BC7))*(B7:BC7&gt;0),COLUMN(B7:BC7)),IF((B7:BC7&lt;&gt;INT(B7:BC7))+(B7:BC7&lt;=0),COLUMN(B7:BC7))))</f>
         <v>1</v>
       </c>
-      <c r="BG7" s="192" cm="1">
+      <c r="BG7" s="189" cm="1">
         <f t="array" ref="BG7">SUMPRODUCT(--(B7:AI7=INT(B7:AI7)),--(B7:AI7&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH7" s="193">
+      <c r="BH7" s="190">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="BI7" s="193">
+        <v>26</v>
+      </c>
+      <c r="BI7" s="190">
         <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="BJ7" s="193">
+        <v>29</v>
+      </c>
+      <c r="BJ7" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10172,7 +10153,9 @@
       <c r="AT8" s="120">
         <v>1</v>
       </c>
-      <c r="AU8" s="120"/>
+      <c r="AU8" s="120">
+        <v>1</v>
+      </c>
       <c r="AV8" s="120"/>
       <c r="AW8" s="120"/>
       <c r="AX8" s="120"/>
@@ -10181,31 +10164,31 @@
       <c r="BA8" s="120"/>
       <c r="BB8" s="120"/>
       <c r="BC8" s="120"/>
-      <c r="BD8" s="191">
+      <c r="BD8" s="188">
         <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="BE8" s="191" cm="1">
+        <v>24</v>
+      </c>
+      <c r="BE8" s="188" cm="1">
         <f t="array" ref="BE8">SUMPRODUCT(--(B8:BC8=INT(B8:BC8)),--(B8:BC8&gt;0))</f>
-        <v>23</v>
-      </c>
-      <c r="BF8" s="191" cm="1">
+        <v>24</v>
+      </c>
+      <c r="BF8" s="188" cm="1">
         <f t="array" ref="BF8">MAX(FREQUENCY(IF((B8:BC8=INT(B8:BC8))*(B8:BC8&gt;0),COLUMN(B8:BC8)),IF((B8:BC8&lt;&gt;INT(B8:BC8))+(B8:BC8&lt;=0),COLUMN(B8:BC8))))</f>
         <v>5</v>
       </c>
-      <c r="BG8" s="192" cm="1">
+      <c r="BG8" s="189" cm="1">
         <f t="array" ref="BG8">SUMPRODUCT(--(B8:AI8=INT(B8:AI8)),--(B8:AI8&gt;0))/34*100%</f>
         <v>0.470588235294118</v>
       </c>
-      <c r="BH8" s="193">
+      <c r="BH8" s="190">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="BI8" s="193">
+      <c r="BI8" s="190">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="BJ8" s="193">
+      <c r="BJ8" s="190">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -10289,7 +10272,9 @@
         <v>1</v>
       </c>
       <c r="AT9" s="120"/>
-      <c r="AU9" s="120"/>
+      <c r="AU9" s="120">
+        <v>1</v>
+      </c>
       <c r="AV9" s="120"/>
       <c r="AW9" s="120"/>
       <c r="AX9" s="120"/>
@@ -10298,33 +10283,33 @@
       <c r="BA9" s="120"/>
       <c r="BB9" s="120"/>
       <c r="BC9" s="120"/>
-      <c r="BD9" s="191">
+      <c r="BD9" s="188">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="BE9" s="191" cm="1">
+        <v>16</v>
+      </c>
+      <c r="BE9" s="188" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
-        <v>15</v>
-      </c>
-      <c r="BF9" s="191" cm="1">
+        <v>16</v>
+      </c>
+      <c r="BF9" s="188" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
         <v>3</v>
       </c>
-      <c r="BG9" s="192" cm="1">
+      <c r="BG9" s="189" cm="1">
         <f t="array" ref="BG9">SUMPRODUCT(--(B9:AI9=INT(B9:AI9)),--(B9:AI9&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH9" s="193">
+      <c r="BH9" s="190">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="BI9" s="193">
+        <v>10</v>
+      </c>
+      <c r="BI9" s="190">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="BJ9" s="193">
+      <c r="BJ9" s="190">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:62">
@@ -10387,31 +10372,31 @@
       <c r="BA10" s="120"/>
       <c r="BB10" s="120"/>
       <c r="BC10" s="120"/>
-      <c r="BD10" s="191">
+      <c r="BD10" s="188">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE10" s="191" cm="1">
+      <c r="BE10" s="188" cm="1">
         <f t="array" ref="BE10">SUMPRODUCT(--(B10:BC10=INT(B10:BC10)),--(B10:BC10&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF10" s="191" cm="1">
+      <c r="BF10" s="188" cm="1">
         <f t="array" ref="BF10">MAX(FREQUENCY(IF((B10:BC10=INT(B10:BC10))*(B10:BC10&gt;0),COLUMN(B10:BC10)),IF((B10:BC10&lt;&gt;INT(B10:BC10))+(B10:BC10&lt;=0),COLUMN(B10:BC10))))</f>
         <v>1</v>
       </c>
-      <c r="BG10" s="192" cm="1">
+      <c r="BG10" s="189" cm="1">
         <f t="array" ref="BG10">SUMPRODUCT(--(B10:AI10=INT(B10:AI10)),--(B10:AI10&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH10" s="193">
+      <c r="BH10" s="190">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI10" s="193">
+      <c r="BI10" s="190">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ10" s="193">
+      <c r="BJ10" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10494,31 +10479,31 @@
       <c r="BA11" s="120"/>
       <c r="BB11" s="120"/>
       <c r="BC11" s="120"/>
-      <c r="BD11" s="191">
+      <c r="BD11" s="188">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="BE11" s="191" cm="1">
+      <c r="BE11" s="188" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(--(B11:BC11=INT(B11:BC11)),--(B11:BC11&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BF11" s="191" cm="1">
+      <c r="BF11" s="188" cm="1">
         <f t="array" ref="BF11">MAX(FREQUENCY(IF((B11:BC11=INT(B11:BC11))*(B11:BC11&gt;0),COLUMN(B11:BC11)),IF((B11:BC11&lt;&gt;INT(B11:BC11))+(B11:BC11&lt;=0),COLUMN(B11:BC11))))</f>
         <v>2</v>
       </c>
-      <c r="BG11" s="192" cm="1">
+      <c r="BG11" s="189" cm="1">
         <f t="array" ref="BG11">SUMPRODUCT(--(B11:AI11=INT(B11:AI11)),--(B11:AI11&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH11" s="193">
+      <c r="BH11" s="190">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="BI11" s="193">
+        <v>17</v>
+      </c>
+      <c r="BI11" s="190">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="BJ11" s="193">
+        <v>17</v>
+      </c>
+      <c r="BJ11" s="190">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -10585,31 +10570,31 @@
       <c r="BA12" s="120"/>
       <c r="BB12" s="120"/>
       <c r="BC12" s="120"/>
-      <c r="BD12" s="191">
+      <c r="BD12" s="188">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE12" s="191" cm="1">
+      <c r="BE12" s="188" cm="1">
         <f t="array" ref="BE12">SUMPRODUCT(--(B12:BC12=INT(B12:BC12)),--(B12:BC12&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF12" s="191" cm="1">
+      <c r="BF12" s="188" cm="1">
         <f t="array" ref="BF12">MAX(FREQUENCY(IF((B12:BC12=INT(B12:BC12))*(B12:BC12&gt;0),COLUMN(B12:BC12)),IF((B12:BC12&lt;&gt;INT(B12:BC12))+(B12:BC12&lt;=0),COLUMN(B12:BC12))))</f>
         <v>1</v>
       </c>
-      <c r="BG12" s="192" cm="1">
+      <c r="BG12" s="189" cm="1">
         <f t="array" ref="BG12">SUMPRODUCT(--(B12:AI12=INT(B12:AI12)),--(B12:AI12&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH12" s="193">
+      <c r="BH12" s="190">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI12" s="193">
+      <c r="BI12" s="190">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ12" s="193">
+      <c r="BJ12" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10694,31 +10679,31 @@
       <c r="BA13" s="120"/>
       <c r="BB13" s="120"/>
       <c r="BC13" s="120"/>
-      <c r="BD13" s="191">
+      <c r="BD13" s="188">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="BE13" s="191" cm="1">
+      <c r="BE13" s="188" cm="1">
         <f t="array" ref="BE13">SUMPRODUCT(--(B13:BC13=INT(B13:BC13)),--(B13:BC13&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF13" s="191" cm="1">
+      <c r="BF13" s="188" cm="1">
         <f t="array" ref="BF13">MAX(FREQUENCY(IF((B13:BC13=INT(B13:BC13))*(B13:BC13&gt;0),COLUMN(B13:BC13)),IF((B13:BC13&lt;&gt;INT(B13:BC13))+(B13:BC13&lt;=0),COLUMN(B13:BC13))))</f>
         <v>1</v>
       </c>
-      <c r="BG13" s="192" cm="1">
+      <c r="BG13" s="189" cm="1">
         <f t="array" ref="BG13">SUMPRODUCT(--(B13:AI13=INT(B13:AI13)),--(B13:AI13&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH13" s="193">
+      <c r="BH13" s="190">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="BI13" s="193">
+      <c r="BI13" s="190">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ13" s="193">
+      <c r="BJ13" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10789,31 +10774,31 @@
       <c r="BA14" s="120"/>
       <c r="BB14" s="120"/>
       <c r="BC14" s="120"/>
-      <c r="BD14" s="191">
+      <c r="BD14" s="188">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE14" s="191" cm="1">
+      <c r="BE14" s="188" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(--(B14:BC14=INT(B14:BC14)),--(B14:BC14&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF14" s="191" cm="1">
+      <c r="BF14" s="188" cm="1">
         <f t="array" ref="BF14">MAX(FREQUENCY(IF((B14:BC14=INT(B14:BC14))*(B14:BC14&gt;0),COLUMN(B14:BC14)),IF((B14:BC14&lt;&gt;INT(B14:BC14))+(B14:BC14&lt;=0),COLUMN(B14:BC14))))</f>
         <v>1</v>
       </c>
-      <c r="BG14" s="192" cm="1">
+      <c r="BG14" s="189" cm="1">
         <f t="array" ref="BG14">SUMPRODUCT(--(B14:AI14=INT(B14:AI14)),--(B14:AI14&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH14" s="193">
+      <c r="BH14" s="190">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="BI14" s="193">
+        <v>26</v>
+      </c>
+      <c r="BI14" s="190">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ14" s="193">
+      <c r="BJ14" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10897,7 +10882,9 @@
         <v>1</v>
       </c>
       <c r="AT15" s="120"/>
-      <c r="AU15" s="120"/>
+      <c r="AU15" s="120">
+        <v>1</v>
+      </c>
       <c r="AV15" s="120"/>
       <c r="AW15" s="120"/>
       <c r="AX15" s="120"/>
@@ -10906,33 +10893,33 @@
       <c r="BA15" s="120"/>
       <c r="BB15" s="120"/>
       <c r="BC15" s="120"/>
-      <c r="BD15" s="191">
+      <c r="BD15" s="188">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="BE15" s="191" cm="1">
+        <v>18</v>
+      </c>
+      <c r="BE15" s="188" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>15</v>
-      </c>
-      <c r="BF15" s="191" cm="1">
+        <v>16</v>
+      </c>
+      <c r="BF15" s="188" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
         <v>3</v>
       </c>
-      <c r="BG15" s="192" cm="1">
+      <c r="BG15" s="189" cm="1">
         <f t="array" ref="BG15">SUMPRODUCT(--(B15:AI15=INT(B15:AI15)),--(B15:AI15&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH15" s="193">
+      <c r="BH15" s="190">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="BI15" s="193">
+      <c r="BI15" s="190">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="BJ15" s="193">
+      <c r="BJ15" s="190">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:62">
@@ -10997,31 +10984,31 @@
       <c r="BA16" s="120"/>
       <c r="BB16" s="120"/>
       <c r="BC16" s="120"/>
-      <c r="BD16" s="191">
+      <c r="BD16" s="188">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE16" s="191" cm="1">
+      <c r="BE16" s="188" cm="1">
         <f t="array" ref="BE16">SUMPRODUCT(--(B16:BC16=INT(B16:BC16)),--(B16:BC16&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF16" s="191" cm="1">
+      <c r="BF16" s="188" cm="1">
         <f t="array" ref="BF16">MAX(FREQUENCY(IF((B16:BC16=INT(B16:BC16))*(B16:BC16&gt;0),COLUMN(B16:BC16)),IF((B16:BC16&lt;&gt;INT(B16:BC16))+(B16:BC16&lt;=0),COLUMN(B16:BC16))))</f>
         <v>1</v>
       </c>
-      <c r="BG16" s="192" cm="1">
+      <c r="BG16" s="189" cm="1">
         <f t="array" ref="BG16">SUMPRODUCT(--(B16:AI16=INT(B16:AI16)),--(B16:AI16&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH16" s="193">
+      <c r="BH16" s="190">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI16" s="193">
+      <c r="BI16" s="190">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ16" s="193">
+      <c r="BJ16" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11092,31 +11079,31 @@
       <c r="BA17" s="120"/>
       <c r="BB17" s="120"/>
       <c r="BC17" s="120"/>
-      <c r="BD17" s="191">
+      <c r="BD17" s="188">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE17" s="191" cm="1">
+      <c r="BE17" s="188" cm="1">
         <f t="array" ref="BE17">SUMPRODUCT(--(B17:BC17=INT(B17:BC17)),--(B17:BC17&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF17" s="191" cm="1">
+      <c r="BF17" s="188" cm="1">
         <f t="array" ref="BF17">MAX(FREQUENCY(IF((B17:BC17=INT(B17:BC17))*(B17:BC17&gt;0),COLUMN(B17:BC17)),IF((B17:BC17&lt;&gt;INT(B17:BC17))+(B17:BC17&lt;=0),COLUMN(B17:BC17))))</f>
         <v>1</v>
       </c>
-      <c r="BG17" s="192" cm="1">
+      <c r="BG17" s="189" cm="1">
         <f t="array" ref="BG17">SUMPRODUCT(--(B17:AI17=INT(B17:AI17)),--(B17:AI17&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH17" s="193">
+      <c r="BH17" s="190">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="BI17" s="193">
+        <v>26</v>
+      </c>
+      <c r="BI17" s="190">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ17" s="193">
+      <c r="BJ17" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11181,31 +11168,31 @@
       <c r="BA18" s="120"/>
       <c r="BB18" s="120"/>
       <c r="BC18" s="120"/>
-      <c r="BD18" s="191">
+      <c r="BD18" s="188">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE18" s="191" cm="1">
+      <c r="BE18" s="188" cm="1">
         <f t="array" ref="BE18">SUMPRODUCT(--(B18:BC18=INT(B18:BC18)),--(B18:BC18&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF18" s="191" cm="1">
+      <c r="BF18" s="188" cm="1">
         <f t="array" ref="BF18">MAX(FREQUENCY(IF((B18:BC18=INT(B18:BC18))*(B18:BC18&gt;0),COLUMN(B18:BC18)),IF((B18:BC18&lt;&gt;INT(B18:BC18))+(B18:BC18&lt;=0),COLUMN(B18:BC18))))</f>
         <v>1</v>
       </c>
-      <c r="BG18" s="192" cm="1">
+      <c r="BG18" s="189" cm="1">
         <f t="array" ref="BG18">SUMPRODUCT(--(B18:AI18=INT(B18:AI18)),--(B18:AI18&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH18" s="193">
+      <c r="BH18" s="190">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI18" s="193">
+      <c r="BI18" s="190">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ18" s="193">
+      <c r="BJ18" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11269,7 +11256,9 @@
       <c r="AR19" s="120"/>
       <c r="AS19" s="120"/>
       <c r="AT19" s="120"/>
-      <c r="AU19" s="120"/>
+      <c r="AU19" s="120">
+        <v>2</v>
+      </c>
       <c r="AV19" s="120"/>
       <c r="AW19" s="120"/>
       <c r="AX19" s="120"/>
@@ -11278,31 +11267,31 @@
       <c r="BA19" s="120"/>
       <c r="BB19" s="120"/>
       <c r="BC19" s="120"/>
-      <c r="BD19" s="191">
+      <c r="BD19" s="188">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="BE19" s="191" cm="1">
+        <v>7</v>
+      </c>
+      <c r="BE19" s="188" cm="1">
         <f t="array" ref="BE19">SUMPRODUCT(--(B19:BC19=INT(B19:BC19)),--(B19:BC19&gt;0))</f>
-        <v>5</v>
-      </c>
-      <c r="BF19" s="191" cm="1">
+        <v>6</v>
+      </c>
+      <c r="BF19" s="188" cm="1">
         <f t="array" ref="BF19">MAX(FREQUENCY(IF((B19:BC19=INT(B19:BC19))*(B19:BC19&gt;0),COLUMN(B19:BC19)),IF((B19:BC19&lt;&gt;INT(B19:BC19))+(B19:BC19&lt;=0),COLUMN(B19:BC19))))</f>
         <v>2</v>
       </c>
-      <c r="BG19" s="192" cm="1">
+      <c r="BG19" s="189" cm="1">
         <f t="array" ref="BG19">SUMPRODUCT(--(B19:AI19=INT(B19:AI19)),--(B19:AI19&gt;0))/34*100%</f>
         <v>0.147058823529412</v>
       </c>
-      <c r="BH19" s="193">
+      <c r="BH19" s="190">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="BI19" s="193">
+        <v>21</v>
+      </c>
+      <c r="BI19" s="190">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="BJ19" s="193">
+      <c r="BJ19" s="190">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -11367,31 +11356,31 @@
       <c r="BA20" s="120"/>
       <c r="BB20" s="120"/>
       <c r="BC20" s="120"/>
-      <c r="BD20" s="191">
+      <c r="BD20" s="188">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE20" s="191" cm="1">
+      <c r="BE20" s="188" cm="1">
         <f t="array" ref="BE20">SUMPRODUCT(--(B20:BC20=INT(B20:BC20)),--(B20:BC20&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF20" s="191" cm="1">
+      <c r="BF20" s="188" cm="1">
         <f t="array" ref="BF20">MAX(FREQUENCY(IF((B20:BC20=INT(B20:BC20))*(B20:BC20&gt;0),COLUMN(B20:BC20)),IF((B20:BC20&lt;&gt;INT(B20:BC20))+(B20:BC20&lt;=0),COLUMN(B20:BC20))))</f>
         <v>1</v>
       </c>
-      <c r="BG20" s="192" cm="1">
+      <c r="BG20" s="189" cm="1">
         <f t="array" ref="BG20">SUMPRODUCT(--(B20:AI20=INT(B20:AI20)),--(B20:AI20&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH20" s="193">
+      <c r="BH20" s="190">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI20" s="193">
+      <c r="BI20" s="190">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ20" s="193">
+      <c r="BJ20" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11451,7 +11440,9 @@
       <c r="AR21" s="120"/>
       <c r="AS21" s="120"/>
       <c r="AT21" s="120"/>
-      <c r="AU21" s="120"/>
+      <c r="AU21" s="120">
+        <v>2</v>
+      </c>
       <c r="AV21" s="120"/>
       <c r="AW21" s="120"/>
       <c r="AX21" s="120"/>
@@ -11460,31 +11451,31 @@
       <c r="BA21" s="120"/>
       <c r="BB21" s="120"/>
       <c r="BC21" s="120"/>
-      <c r="BD21" s="191">
+      <c r="BD21" s="188">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="BE21" s="191" cm="1">
+        <v>5</v>
+      </c>
+      <c r="BE21" s="188" cm="1">
         <f t="array" ref="BE21">SUMPRODUCT(--(B21:BC21=INT(B21:BC21)),--(B21:BC21&gt;0))</f>
-        <v>3</v>
-      </c>
-      <c r="BF21" s="191" cm="1">
+        <v>4</v>
+      </c>
+      <c r="BF21" s="188" cm="1">
         <f t="array" ref="BF21">MAX(FREQUENCY(IF((B21:BC21=INT(B21:BC21))*(B21:BC21&gt;0),COLUMN(B21:BC21)),IF((B21:BC21&lt;&gt;INT(B21:BC21))+(B21:BC21&lt;=0),COLUMN(B21:BC21))))</f>
         <v>1</v>
       </c>
-      <c r="BG21" s="192" cm="1">
+      <c r="BG21" s="189" cm="1">
         <f t="array" ref="BG21">SUMPRODUCT(--(B21:AI21=INT(B21:AI21)),--(B21:AI21&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH21" s="193">
+      <c r="BH21" s="190">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="BI21" s="193">
+        <v>23</v>
+      </c>
+      <c r="BI21" s="190">
         <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="BJ21" s="193">
+        <v>25</v>
+      </c>
+      <c r="BJ21" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11562,7 +11553,9 @@
       </c>
       <c r="AS22" s="120"/>
       <c r="AT22" s="120"/>
-      <c r="AU22" s="120"/>
+      <c r="AU22" s="120">
+        <v>1</v>
+      </c>
       <c r="AV22" s="120"/>
       <c r="AW22" s="120"/>
       <c r="AX22" s="120"/>
@@ -11571,37 +11564,37 @@
       <c r="BA22" s="120"/>
       <c r="BB22" s="120"/>
       <c r="BC22" s="120"/>
-      <c r="BD22" s="191">
+      <c r="BD22" s="188">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="BE22" s="191" cm="1">
+        <v>16</v>
+      </c>
+      <c r="BE22" s="188" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
-        <v>12</v>
-      </c>
-      <c r="BF22" s="191" cm="1">
+        <v>13</v>
+      </c>
+      <c r="BF22" s="188" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
         <v>4</v>
       </c>
-      <c r="BG22" s="192" cm="1">
+      <c r="BG22" s="189" cm="1">
         <f t="array" ref="BG22">SUMPRODUCT(--(B22:AI22=INT(B22:AI22)),--(B22:AI22&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH22" s="193">
+      <c r="BH22" s="190">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-      <c r="BI22" s="193">
+        <v>10</v>
+      </c>
+      <c r="BI22" s="190">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="BJ22" s="193">
+      <c r="BJ22" s="190">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:62">
-      <c r="A23" s="194">
+      <c r="A23" s="120">
         <v>21</v>
       </c>
       <c r="B23" s="120"/>
@@ -11660,31 +11653,31 @@
       <c r="BA23" s="120"/>
       <c r="BB23" s="120"/>
       <c r="BC23" s="120"/>
-      <c r="BD23" s="191">
+      <c r="BD23" s="188">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE23" s="191" cm="1">
+      <c r="BE23" s="188" cm="1">
         <f t="array" ref="BE23">SUMPRODUCT(--(B23:BC23=INT(B23:BC23)),--(B23:BC23&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF23" s="191" cm="1">
+      <c r="BF23" s="188" cm="1">
         <f t="array" ref="BF23">MAX(FREQUENCY(IF((B23:BC23=INT(B23:BC23))*(B23:BC23&gt;0),COLUMN(B23:BC23)),IF((B23:BC23&lt;&gt;INT(B23:BC23))+(B23:BC23&lt;=0),COLUMN(B23:BC23))))</f>
         <v>1</v>
       </c>
-      <c r="BG23" s="192" cm="1">
+      <c r="BG23" s="189" cm="1">
         <f t="array" ref="BG23">SUMPRODUCT(--(B23:AI23=INT(B23:AI23)),--(B23:AI23&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH23" s="193">
+      <c r="BH23" s="190">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI23" s="193">
+      <c r="BI23" s="190">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ23" s="193">
+      <c r="BJ23" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11763,33 +11756,33 @@
       <c r="BA24" s="120"/>
       <c r="BB24" s="120"/>
       <c r="BC24" s="120"/>
-      <c r="BD24" s="191">
+      <c r="BD24" s="188">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="BE24" s="191" cm="1">
+      <c r="BE24" s="188" cm="1">
         <f t="array" ref="BE24">SUMPRODUCT(--(B24:BC24=INT(B24:BC24)),--(B24:BC24&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="BF24" s="191" cm="1">
+      <c r="BF24" s="188" cm="1">
         <f t="array" ref="BF24">MAX(FREQUENCY(IF((B24:BC24=INT(B24:BC24))*(B24:BC24&gt;0),COLUMN(B24:BC24)),IF((B24:BC24&lt;&gt;INT(B24:BC24))+(B24:BC24&lt;=0),COLUMN(B24:BC24))))</f>
         <v>3</v>
       </c>
-      <c r="BG24" s="192" cm="1">
+      <c r="BG24" s="189" cm="1">
         <f t="array" ref="BG24">SUMPRODUCT(--(B24:AI24=INT(B24:AI24)),--(B24:AI24&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH24" s="193">
+      <c r="BH24" s="190">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="BI24" s="193">
+      <c r="BI24" s="190">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="BJ24" s="193">
+      <c r="BJ24" s="190">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:62">
@@ -11852,37 +11845,37 @@
       <c r="BA25" s="120"/>
       <c r="BB25" s="120"/>
       <c r="BC25" s="120"/>
-      <c r="BD25" s="191">
+      <c r="BD25" s="188">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE25" s="191" cm="1">
+      <c r="BE25" s="188" cm="1">
         <f t="array" ref="BE25">SUMPRODUCT(--(B25:BC25=INT(B25:BC25)),--(B25:BC25&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF25" s="191" cm="1">
+      <c r="BF25" s="188" cm="1">
         <f t="array" ref="BF25">MAX(FREQUENCY(IF((B25:BC25=INT(B25:BC25))*(B25:BC25&gt;0),COLUMN(B25:BC25)),IF((B25:BC25&lt;&gt;INT(B25:BC25))+(B25:BC25&lt;=0),COLUMN(B25:BC25))))</f>
         <v>1</v>
       </c>
-      <c r="BG25" s="192" cm="1">
+      <c r="BG25" s="189" cm="1">
         <f t="array" ref="BG25">SUMPRODUCT(--(B25:AI25=INT(B25:AI25)),--(B25:AI25&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH25" s="193">
+      <c r="BH25" s="190">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI25" s="193">
+      <c r="BI25" s="190">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ25" s="193">
+      <c r="BJ25" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:62">
-      <c r="A26" s="195">
+      <c r="A26" s="191">
         <v>24</v>
       </c>
       <c r="B26" s="120"/>
@@ -11939,37 +11932,37 @@
       <c r="BA26" s="120"/>
       <c r="BB26" s="120"/>
       <c r="BC26" s="120"/>
-      <c r="BD26" s="191">
+      <c r="BD26" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="191" cm="1">
+      <c r="BE26" s="188" cm="1">
         <f t="array" ref="BE26">SUMPRODUCT(--(B26:BC26=INT(B26:BC26)),--(B26:BC26&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF26" s="191" cm="1">
+      <c r="BF26" s="188" cm="1">
         <f t="array" ref="BF26">MAX(FREQUENCY(IF((B26:BC26=INT(B26:BC26))*(B26:BC26&gt;0),COLUMN(B26:BC26)),IF((B26:BC26&lt;&gt;INT(B26:BC26))+(B26:BC26&lt;=0),COLUMN(B26:BC26))))</f>
         <v>0</v>
       </c>
-      <c r="BG26" s="192" cm="1">
+      <c r="BG26" s="189" cm="1">
         <f t="array" ref="BG26">SUMPRODUCT(--(B26:AI26=INT(B26:AI26)),--(B26:AI26&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH26" s="193">
+      <c r="BH26" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI26" s="193">
+      <c r="BI26" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ26" s="193">
+      <c r="BJ26" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:62">
-      <c r="A27" s="195">
+      <c r="A27" s="191">
         <v>25</v>
       </c>
       <c r="B27" s="120"/>
@@ -12026,31 +12019,31 @@
       <c r="BA27" s="120"/>
       <c r="BB27" s="120"/>
       <c r="BC27" s="120"/>
-      <c r="BD27" s="191">
+      <c r="BD27" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE27" s="191" cm="1">
+      <c r="BE27" s="188" cm="1">
         <f t="array" ref="BE27">SUMPRODUCT(--(B27:BC27=INT(B27:BC27)),--(B27:BC27&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF27" s="191" cm="1">
+      <c r="BF27" s="188" cm="1">
         <f t="array" ref="BF27">MAX(FREQUENCY(IF((B27:BC27=INT(B27:BC27))*(B27:BC27&gt;0),COLUMN(B27:BC27)),IF((B27:BC27&lt;&gt;INT(B27:BC27))+(B27:BC27&lt;=0),COLUMN(B27:BC27))))</f>
         <v>0</v>
       </c>
-      <c r="BG27" s="192" cm="1">
+      <c r="BG27" s="189" cm="1">
         <f t="array" ref="BG27">SUMPRODUCT(--(B27:AI27=INT(B27:AI27)),--(B27:AI27&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH27" s="193">
+      <c r="BH27" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI27" s="193">
+      <c r="BI27" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ27" s="193">
+      <c r="BJ27" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -12124,7 +12117,9 @@
       </c>
       <c r="AS28" s="120"/>
       <c r="AT28" s="120"/>
-      <c r="AU28" s="120"/>
+      <c r="AU28" s="120">
+        <v>1</v>
+      </c>
       <c r="AV28" s="120"/>
       <c r="AW28" s="120"/>
       <c r="AX28" s="120"/>
@@ -12133,31 +12128,31 @@
       <c r="BA28" s="120"/>
       <c r="BB28" s="120"/>
       <c r="BC28" s="120"/>
-      <c r="BD28" s="191">
+      <c r="BD28" s="188">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="BE28" s="191" cm="1">
+        <v>11</v>
+      </c>
+      <c r="BE28" s="188" cm="1">
         <f t="array" ref="BE28">SUMPRODUCT(--(B28:BC28=INT(B28:BC28)),--(B28:BC28&gt;0))</f>
-        <v>10</v>
-      </c>
-      <c r="BF28" s="191" cm="1">
+        <v>11</v>
+      </c>
+      <c r="BF28" s="188" cm="1">
         <f t="array" ref="BF28">MAX(FREQUENCY(IF((B28:BC28=INT(B28:BC28))*(B28:BC28&gt;0),COLUMN(B28:BC28)),IF((B28:BC28&lt;&gt;INT(B28:BC28))+(B28:BC28&lt;=0),COLUMN(B28:BC28))))</f>
         <v>2</v>
       </c>
-      <c r="BG28" s="192" cm="1">
+      <c r="BG28" s="189" cm="1">
         <f t="array" ref="BG28">SUMPRODUCT(--(B28:AI28=INT(B28:AI28)),--(B28:AI28&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH28" s="193">
+      <c r="BH28" s="190">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="BI28" s="193">
+        <v>14</v>
+      </c>
+      <c r="BI28" s="190">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="BJ28" s="193">
+        <v>12</v>
+      </c>
+      <c r="BJ28" s="190">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -12231,7 +12226,9 @@
       <c r="AT29" s="120">
         <v>1</v>
       </c>
-      <c r="AU29" s="120"/>
+      <c r="AU29" s="120">
+        <v>1</v>
+      </c>
       <c r="AV29" s="120"/>
       <c r="AW29" s="120"/>
       <c r="AX29" s="120"/>
@@ -12240,33 +12237,33 @@
       <c r="BA29" s="120"/>
       <c r="BB29" s="120"/>
       <c r="BC29" s="120"/>
-      <c r="BD29" s="191">
+      <c r="BD29" s="188">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="BE29" s="191" cm="1">
+        <v>11</v>
+      </c>
+      <c r="BE29" s="188" cm="1">
         <f t="array" ref="BE29">SUMPRODUCT(--(B29:BC29=INT(B29:BC29)),--(B29:BC29&gt;0))</f>
-        <v>10</v>
-      </c>
-      <c r="BF29" s="191" cm="1">
+        <v>11</v>
+      </c>
+      <c r="BF29" s="188" cm="1">
         <f t="array" ref="BF29">MAX(FREQUENCY(IF((B29:BC29=INT(B29:BC29))*(B29:BC29&gt;0),COLUMN(B29:BC29)),IF((B29:BC29&lt;&gt;INT(B29:BC29))+(B29:BC29&lt;=0),COLUMN(B29:BC29))))</f>
-        <v>4</v>
-      </c>
-      <c r="BG29" s="192" cm="1">
+        <v>5</v>
+      </c>
+      <c r="BG29" s="189" cm="1">
         <f t="array" ref="BG29">SUMPRODUCT(--(B29:AI29=INT(B29:AI29)),--(B29:AI29&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH29" s="193">
+      <c r="BH29" s="190">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="BI29" s="193">
+        <v>14</v>
+      </c>
+      <c r="BI29" s="190">
         <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="BJ29" s="193">
+        <v>12</v>
+      </c>
+      <c r="BJ29" s="190">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:62">
@@ -12341,33 +12338,33 @@
       <c r="BA30" s="120"/>
       <c r="BB30" s="120"/>
       <c r="BC30" s="120"/>
-      <c r="BD30" s="191">
+      <c r="BD30" s="188">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="BE30" s="191" cm="1">
+      <c r="BE30" s="188" cm="1">
         <f t="array" ref="BE30">SUMPRODUCT(--(B30:BC30=INT(B30:BC30)),--(B30:BC30&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF30" s="191" cm="1">
+      <c r="BF30" s="188" cm="1">
         <f t="array" ref="BF30">MAX(FREQUENCY(IF((B30:BC30=INT(B30:BC30))*(B30:BC30&gt;0),COLUMN(B30:BC30)),IF((B30:BC30&lt;&gt;INT(B30:BC30))+(B30:BC30&lt;=0),COLUMN(B30:BC30))))</f>
         <v>4</v>
       </c>
-      <c r="BG30" s="192" cm="1">
+      <c r="BG30" s="189" cm="1">
         <f t="array" ref="BG30">SUMPRODUCT(--(B30:AI30=INT(B30:AI30)),--(B30:AI30&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH30" s="193">
+      <c r="BH30" s="190">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="BI30" s="193">
+      <c r="BI30" s="190">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="BJ30" s="193">
+      <c r="BJ30" s="190">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:62">
@@ -12450,31 +12447,31 @@
       <c r="BA31" s="120"/>
       <c r="BB31" s="120"/>
       <c r="BC31" s="120"/>
-      <c r="BD31" s="191">
+      <c r="BD31" s="188">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="BE31" s="191" cm="1">
+      <c r="BE31" s="188" cm="1">
         <f t="array" ref="BE31">SUMPRODUCT(--(B31:BC31=INT(B31:BC31)),--(B31:BC31&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF31" s="191" cm="1">
+      <c r="BF31" s="188" cm="1">
         <f t="array" ref="BF31">MAX(FREQUENCY(IF((B31:BC31=INT(B31:BC31))*(B31:BC31&gt;0),COLUMN(B31:BC31)),IF((B31:BC31&lt;&gt;INT(B31:BC31))+(B31:BC31&lt;=0),COLUMN(B31:BC31))))</f>
         <v>2</v>
       </c>
-      <c r="BG31" s="192" cm="1">
+      <c r="BG31" s="189" cm="1">
         <f t="array" ref="BG31">SUMPRODUCT(--(B31:AI31=INT(B31:AI31)),--(B31:AI31&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH31" s="193">
+      <c r="BH31" s="190">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="BI31" s="193">
+      <c r="BI31" s="190">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ31" s="193">
+      <c r="BJ31" s="190">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -12559,33 +12556,33 @@
       <c r="BA32" s="120"/>
       <c r="BB32" s="120"/>
       <c r="BC32" s="120"/>
-      <c r="BD32" s="191">
+      <c r="BD32" s="188">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="BE32" s="191" cm="1">
+      <c r="BE32" s="188" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF32" s="191" cm="1">
+      <c r="BF32" s="188" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
         <v>3</v>
       </c>
-      <c r="BG32" s="192" cm="1">
+      <c r="BG32" s="189" cm="1">
         <f t="array" ref="BG32">SUMPRODUCT(--(B32:AI32=INT(B32:AI32)),--(B32:AI32&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH32" s="193">
+      <c r="BH32" s="190">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="BI32" s="193">
+      <c r="BI32" s="190">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ32" s="193">
+      <c r="BJ32" s="190">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:62">
@@ -12656,37 +12653,37 @@
       <c r="BA33" s="120"/>
       <c r="BB33" s="120"/>
       <c r="BC33" s="120"/>
-      <c r="BD33" s="191">
+      <c r="BD33" s="188">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE33" s="191" cm="1">
+      <c r="BE33" s="188" cm="1">
         <f t="array" ref="BE33">SUMPRODUCT(--(B33:BC33=INT(B33:BC33)),--(B33:BC33&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF33" s="191" cm="1">
+      <c r="BF33" s="188" cm="1">
         <f t="array" ref="BF33">MAX(FREQUENCY(IF((B33:BC33=INT(B33:BC33))*(B33:BC33&gt;0),COLUMN(B33:BC33)),IF((B33:BC33&lt;&gt;INT(B33:BC33))+(B33:BC33&lt;=0),COLUMN(B33:BC33))))</f>
         <v>1</v>
       </c>
-      <c r="BG33" s="192" cm="1">
+      <c r="BG33" s="189" cm="1">
         <f t="array" ref="BG33">SUMPRODUCT(--(B33:AI33=INT(B33:AI33)),--(B33:AI33&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH33" s="193">
+      <c r="BH33" s="190">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="BI33" s="193">
+        <v>23</v>
+      </c>
+      <c r="BI33" s="190">
         <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="BJ33" s="193">
+        <v>23</v>
+      </c>
+      <c r="BJ33" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:62">
-      <c r="A34" s="195">
+      <c r="A34" s="191">
         <v>32</v>
       </c>
       <c r="B34" s="120"/>
@@ -12743,118 +12740,118 @@
       <c r="BA34" s="120"/>
       <c r="BB34" s="120"/>
       <c r="BC34" s="120"/>
-      <c r="BD34" s="191">
+      <c r="BD34" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE34" s="191" cm="1">
+      <c r="BE34" s="188" cm="1">
         <f t="array" ref="BE34">SUMPRODUCT(--(B34:BC34=INT(B34:BC34)),--(B34:BC34&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF34" s="191" cm="1">
+      <c r="BF34" s="188" cm="1">
         <f t="array" ref="BF34">MAX(FREQUENCY(IF((B34:BC34=INT(B34:BC34))*(B34:BC34&gt;0),COLUMN(B34:BC34)),IF((B34:BC34&lt;&gt;INT(B34:BC34))+(B34:BC34&lt;=0),COLUMN(B34:BC34))))</f>
         <v>0</v>
       </c>
-      <c r="BG34" s="192" cm="1">
+      <c r="BG34" s="189" cm="1">
         <f t="array" ref="BG34">SUMPRODUCT(--(B34:AI34=INT(B34:AI34)),--(B34:AI34&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH34" s="193">
+      <c r="BH34" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI34" s="193">
+      <c r="BI34" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ34" s="193">
+      <c r="BJ34" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:62">
-      <c r="A35" s="196">
+      <c r="A35" s="192">
         <v>33</v>
       </c>
-      <c r="B35" s="196"/>
-      <c r="C35" s="196"/>
-      <c r="D35" s="196"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="196"/>
-      <c r="I35" s="196"/>
-      <c r="J35" s="196"/>
-      <c r="K35" s="196"/>
-      <c r="L35" s="196"/>
-      <c r="M35" s="196"/>
-      <c r="N35" s="196"/>
-      <c r="O35" s="196"/>
-      <c r="P35" s="196"/>
-      <c r="Q35" s="196"/>
-      <c r="R35" s="196"/>
-      <c r="S35" s="196"/>
-      <c r="T35" s="196"/>
-      <c r="U35" s="196"/>
-      <c r="V35" s="196"/>
-      <c r="W35" s="196"/>
-      <c r="X35" s="196"/>
-      <c r="Y35" s="196"/>
-      <c r="Z35" s="196"/>
-      <c r="AA35" s="196"/>
-      <c r="AB35" s="196"/>
-      <c r="AC35" s="196"/>
-      <c r="AD35" s="196"/>
-      <c r="AE35" s="196"/>
-      <c r="AF35" s="196"/>
-      <c r="AG35" s="196"/>
-      <c r="AH35" s="196"/>
-      <c r="AI35" s="196"/>
-      <c r="AJ35" s="196"/>
-      <c r="AK35" s="196"/>
-      <c r="AL35" s="196"/>
-      <c r="AM35" s="196"/>
-      <c r="AN35" s="196"/>
-      <c r="AO35" s="196"/>
-      <c r="AP35" s="196"/>
-      <c r="AQ35" s="196"/>
-      <c r="AR35" s="196"/>
-      <c r="AS35" s="196"/>
-      <c r="AT35" s="196"/>
-      <c r="AU35" s="196"/>
-      <c r="AV35" s="196"/>
-      <c r="AW35" s="196"/>
-      <c r="AX35" s="196"/>
-      <c r="AY35" s="196"/>
-      <c r="AZ35" s="196"/>
-      <c r="BA35" s="196"/>
-      <c r="BB35" s="196"/>
-      <c r="BC35" s="196"/>
-      <c r="BD35" s="191">
+      <c r="B35" s="192"/>
+      <c r="C35" s="192"/>
+      <c r="D35" s="192"/>
+      <c r="E35" s="192"/>
+      <c r="F35" s="192"/>
+      <c r="G35" s="192"/>
+      <c r="H35" s="192"/>
+      <c r="I35" s="192"/>
+      <c r="J35" s="192"/>
+      <c r="K35" s="192"/>
+      <c r="L35" s="192"/>
+      <c r="M35" s="192"/>
+      <c r="N35" s="192"/>
+      <c r="O35" s="192"/>
+      <c r="P35" s="192"/>
+      <c r="Q35" s="192"/>
+      <c r="R35" s="192"/>
+      <c r="S35" s="192"/>
+      <c r="T35" s="192"/>
+      <c r="U35" s="192"/>
+      <c r="V35" s="192"/>
+      <c r="W35" s="192"/>
+      <c r="X35" s="192"/>
+      <c r="Y35" s="192"/>
+      <c r="Z35" s="192"/>
+      <c r="AA35" s="192"/>
+      <c r="AB35" s="192"/>
+      <c r="AC35" s="192"/>
+      <c r="AD35" s="192"/>
+      <c r="AE35" s="192"/>
+      <c r="AF35" s="192"/>
+      <c r="AG35" s="192"/>
+      <c r="AH35" s="192"/>
+      <c r="AI35" s="192"/>
+      <c r="AJ35" s="192"/>
+      <c r="AK35" s="192"/>
+      <c r="AL35" s="192"/>
+      <c r="AM35" s="192"/>
+      <c r="AN35" s="192"/>
+      <c r="AO35" s="192"/>
+      <c r="AP35" s="192"/>
+      <c r="AQ35" s="192"/>
+      <c r="AR35" s="192"/>
+      <c r="AS35" s="192"/>
+      <c r="AT35" s="192"/>
+      <c r="AU35" s="192"/>
+      <c r="AV35" s="192"/>
+      <c r="AW35" s="192"/>
+      <c r="AX35" s="192"/>
+      <c r="AY35" s="192"/>
+      <c r="AZ35" s="192"/>
+      <c r="BA35" s="192"/>
+      <c r="BB35" s="192"/>
+      <c r="BC35" s="192"/>
+      <c r="BD35" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="191" cm="1">
+      <c r="BE35" s="188" cm="1">
         <f t="array" ref="BE35">SUMPRODUCT(--(B35:BC35=INT(B35:BC35)),--(B35:BC35&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF35" s="191" cm="1">
+      <c r="BF35" s="188" cm="1">
         <f t="array" ref="BF35">MAX(FREQUENCY(IF((B35:BC35=INT(B35:BC35))*(B35:BC35&gt;0),COLUMN(B35:BC35)),IF((B35:BC35&lt;&gt;INT(B35:BC35))+(B35:BC35&lt;=0),COLUMN(B35:BC35))))</f>
         <v>0</v>
       </c>
-      <c r="BG35" s="192" cm="1">
+      <c r="BG35" s="189" cm="1">
         <f t="array" ref="BG35">SUMPRODUCT(--(B35:AI35=INT(B35:AI35)),--(B35:AI35&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH35" s="193">
+      <c r="BH35" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI35" s="193">
+      <c r="BI35" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ35" s="193">
+      <c r="BJ35" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -12919,31 +12916,31 @@
       <c r="BA36" s="120"/>
       <c r="BB36" s="120"/>
       <c r="BC36" s="120"/>
-      <c r="BD36" s="191">
+      <c r="BD36" s="188">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE36" s="191" cm="1">
+      <c r="BE36" s="188" cm="1">
         <f t="array" ref="BE36">SUMPRODUCT(--(B36:BC36=INT(B36:BC36)),--(B36:BC36&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF36" s="191" cm="1">
+      <c r="BF36" s="188" cm="1">
         <f t="array" ref="BF36">MAX(FREQUENCY(IF((B36:BC36=INT(B36:BC36))*(B36:BC36&gt;0),COLUMN(B36:BC36)),IF((B36:BC36&lt;&gt;INT(B36:BC36))+(B36:BC36&lt;=0),COLUMN(B36:BC36))))</f>
         <v>1</v>
       </c>
-      <c r="BG36" s="192" cm="1">
+      <c r="BG36" s="189" cm="1">
         <f t="array" ref="BG36">SUMPRODUCT(--(B36:AI36=INT(B36:AI36)),--(B36:AI36&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH36" s="193">
+      <c r="BH36" s="190">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI36" s="193">
+      <c r="BI36" s="190">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ36" s="193">
+      <c r="BJ36" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -13022,33 +13019,33 @@
       <c r="BA37" s="120"/>
       <c r="BB37" s="120"/>
       <c r="BC37" s="120"/>
-      <c r="BD37" s="191">
+      <c r="BD37" s="188">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="BE37" s="191" cm="1">
+      <c r="BE37" s="188" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="BF37" s="191" cm="1">
+      <c r="BF37" s="188" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
         <v>3</v>
       </c>
-      <c r="BG37" s="192" cm="1">
+      <c r="BG37" s="189" cm="1">
         <f t="array" ref="BG37">SUMPRODUCT(--(B37:AI37=INT(B37:AI37)),--(B37:AI37&gt;0))/34*100%</f>
         <v>0.176470588235294</v>
       </c>
-      <c r="BH37" s="193">
+      <c r="BH37" s="190">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="BI37" s="193">
+      <c r="BI37" s="190">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="BJ37" s="193">
+      <c r="BJ37" s="190">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:62">
@@ -13115,118 +13112,118 @@
       <c r="BA38" s="120"/>
       <c r="BB38" s="120"/>
       <c r="BC38" s="120"/>
-      <c r="BD38" s="191">
+      <c r="BD38" s="188">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE38" s="191" cm="1">
+      <c r="BE38" s="188" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(--(B38:BC38=INT(B38:BC38)),--(B38:BC38&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF38" s="191" cm="1">
+      <c r="BF38" s="188" cm="1">
         <f t="array" ref="BF38">MAX(FREQUENCY(IF((B38:BC38=INT(B38:BC38))*(B38:BC38&gt;0),COLUMN(B38:BC38)),IF((B38:BC38&lt;&gt;INT(B38:BC38))+(B38:BC38&lt;=0),COLUMN(B38:BC38))))</f>
         <v>1</v>
       </c>
-      <c r="BG38" s="192" cm="1">
+      <c r="BG38" s="189" cm="1">
         <f t="array" ref="BG38">SUMPRODUCT(--(B38:AI38=INT(B38:AI38)),--(B38:AI38&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH38" s="193">
+      <c r="BH38" s="190">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="BI38" s="193">
+        <v>26</v>
+      </c>
+      <c r="BI38" s="190">
         <f t="shared" si="2"/>
-        <v>28</v>
-      </c>
-      <c r="BJ38" s="193">
+        <v>29</v>
+      </c>
+      <c r="BJ38" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:62">
-      <c r="A39" s="196">
+      <c r="A39" s="192">
         <v>37</v>
       </c>
-      <c r="B39" s="196"/>
-      <c r="C39" s="196"/>
-      <c r="D39" s="196"/>
-      <c r="E39" s="196"/>
-      <c r="F39" s="196"/>
-      <c r="G39" s="196"/>
-      <c r="H39" s="196"/>
-      <c r="I39" s="196"/>
-      <c r="J39" s="196"/>
-      <c r="K39" s="196"/>
-      <c r="L39" s="196"/>
-      <c r="M39" s="196"/>
-      <c r="N39" s="196"/>
-      <c r="O39" s="196"/>
-      <c r="P39" s="196"/>
-      <c r="Q39" s="196"/>
-      <c r="R39" s="196"/>
-      <c r="S39" s="196"/>
-      <c r="T39" s="196"/>
-      <c r="U39" s="196"/>
-      <c r="V39" s="196"/>
-      <c r="W39" s="196"/>
-      <c r="X39" s="196"/>
-      <c r="Y39" s="196"/>
-      <c r="Z39" s="196"/>
-      <c r="AA39" s="196"/>
-      <c r="AB39" s="196"/>
-      <c r="AC39" s="196"/>
-      <c r="AD39" s="196"/>
-      <c r="AE39" s="196"/>
-      <c r="AF39" s="196"/>
-      <c r="AG39" s="196"/>
-      <c r="AH39" s="196"/>
-      <c r="AI39" s="196"/>
-      <c r="AJ39" s="196"/>
-      <c r="AK39" s="196"/>
-      <c r="AL39" s="196"/>
-      <c r="AM39" s="196"/>
-      <c r="AN39" s="196"/>
-      <c r="AO39" s="196"/>
-      <c r="AP39" s="196"/>
-      <c r="AQ39" s="196"/>
-      <c r="AR39" s="196"/>
-      <c r="AS39" s="196"/>
-      <c r="AT39" s="196"/>
-      <c r="AU39" s="196"/>
-      <c r="AV39" s="196"/>
-      <c r="AW39" s="196"/>
-      <c r="AX39" s="196"/>
-      <c r="AY39" s="196"/>
-      <c r="AZ39" s="196"/>
-      <c r="BA39" s="196"/>
-      <c r="BB39" s="196"/>
-      <c r="BC39" s="196"/>
-      <c r="BD39" s="191">
+      <c r="B39" s="192"/>
+      <c r="C39" s="192"/>
+      <c r="D39" s="192"/>
+      <c r="E39" s="192"/>
+      <c r="F39" s="192"/>
+      <c r="G39" s="192"/>
+      <c r="H39" s="192"/>
+      <c r="I39" s="192"/>
+      <c r="J39" s="192"/>
+      <c r="K39" s="192"/>
+      <c r="L39" s="192"/>
+      <c r="M39" s="192"/>
+      <c r="N39" s="192"/>
+      <c r="O39" s="192"/>
+      <c r="P39" s="192"/>
+      <c r="Q39" s="192"/>
+      <c r="R39" s="192"/>
+      <c r="S39" s="192"/>
+      <c r="T39" s="192"/>
+      <c r="U39" s="192"/>
+      <c r="V39" s="192"/>
+      <c r="W39" s="192"/>
+      <c r="X39" s="192"/>
+      <c r="Y39" s="192"/>
+      <c r="Z39" s="192"/>
+      <c r="AA39" s="192"/>
+      <c r="AB39" s="192"/>
+      <c r="AC39" s="192"/>
+      <c r="AD39" s="192"/>
+      <c r="AE39" s="192"/>
+      <c r="AF39" s="192"/>
+      <c r="AG39" s="192"/>
+      <c r="AH39" s="192"/>
+      <c r="AI39" s="192"/>
+      <c r="AJ39" s="192"/>
+      <c r="AK39" s="192"/>
+      <c r="AL39" s="192"/>
+      <c r="AM39" s="192"/>
+      <c r="AN39" s="192"/>
+      <c r="AO39" s="192"/>
+      <c r="AP39" s="192"/>
+      <c r="AQ39" s="192"/>
+      <c r="AR39" s="192"/>
+      <c r="AS39" s="192"/>
+      <c r="AT39" s="192"/>
+      <c r="AU39" s="192"/>
+      <c r="AV39" s="192"/>
+      <c r="AW39" s="192"/>
+      <c r="AX39" s="192"/>
+      <c r="AY39" s="192"/>
+      <c r="AZ39" s="192"/>
+      <c r="BA39" s="192"/>
+      <c r="BB39" s="192"/>
+      <c r="BC39" s="192"/>
+      <c r="BD39" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE39" s="191" cm="1">
+      <c r="BE39" s="188" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(--(B39:BC39=INT(B39:BC39)),--(B39:BC39&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF39" s="191" cm="1">
+      <c r="BF39" s="188" cm="1">
         <f t="array" ref="BF39">MAX(FREQUENCY(IF((B39:BC39=INT(B39:BC39))*(B39:BC39&gt;0),COLUMN(B39:BC39)),IF((B39:BC39&lt;&gt;INT(B39:BC39))+(B39:BC39&lt;=0),COLUMN(B39:BC39))))</f>
         <v>0</v>
       </c>
-      <c r="BG39" s="192" cm="1">
+      <c r="BG39" s="189" cm="1">
         <f t="array" ref="BG39">SUMPRODUCT(--(B39:AI39=INT(B39:AI39)),--(B39:AI39&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH39" s="197">
+      <c r="BH39" s="193">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI39" s="197">
+      <c r="BI39" s="193">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ39" s="197">
+      <c r="BJ39" s="193">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -13328,7 +13325,9 @@
       <c r="AR40" s="120"/>
       <c r="AS40" s="120"/>
       <c r="AT40" s="120"/>
-      <c r="AU40" s="120"/>
+      <c r="AU40" s="120">
+        <v>1</v>
+      </c>
       <c r="AV40" s="120"/>
       <c r="AW40" s="120"/>
       <c r="AX40" s="120"/>
@@ -13337,31 +13336,31 @@
       <c r="BA40" s="120"/>
       <c r="BB40" s="120"/>
       <c r="BC40" s="120"/>
-      <c r="BD40" s="191">
+      <c r="BD40" s="188">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="BE40" s="191" cm="1">
+        <v>29</v>
+      </c>
+      <c r="BE40" s="188" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
-        <v>24</v>
-      </c>
-      <c r="BF40" s="191" cm="1">
+        <v>25</v>
+      </c>
+      <c r="BF40" s="188" cm="1">
         <f t="array" ref="BF40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
         <v>12</v>
       </c>
-      <c r="BG40" s="192" cm="1">
+      <c r="BG40" s="189" cm="1">
         <f t="array" ref="BG40">SUMPRODUCT(--(B40:AI40=INT(B40:AI40)),--(B40:AI40&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH40" s="193">
+      <c r="BH40" s="190">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="BI40" s="193">
+      <c r="BI40" s="190">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="BJ40" s="193">
+      <c r="BJ40" s="190">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -13443,7 +13442,9 @@
         <v>1</v>
       </c>
       <c r="AT41" s="120"/>
-      <c r="AU41" s="120"/>
+      <c r="AU41" s="120">
+        <v>1</v>
+      </c>
       <c r="AV41" s="120"/>
       <c r="AW41" s="120"/>
       <c r="AX41" s="120"/>
@@ -13452,31 +13453,31 @@
       <c r="BA41" s="120"/>
       <c r="BB41" s="120"/>
       <c r="BC41" s="120"/>
-      <c r="BD41" s="191">
+      <c r="BD41" s="188">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="BE41" s="191" cm="1">
+        <v>19</v>
+      </c>
+      <c r="BE41" s="188" cm="1">
         <f t="array" ref="BE41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
-        <v>14</v>
-      </c>
-      <c r="BF41" s="191" cm="1">
+        <v>15</v>
+      </c>
+      <c r="BF41" s="188" cm="1">
         <f t="array" ref="BF41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
         <v>2</v>
       </c>
-      <c r="BG41" s="192" cm="1">
+      <c r="BG41" s="189" cm="1">
         <f t="array" ref="BG41">SUMPRODUCT(--(B41:AI41=INT(B41:AI41)),--(B41:AI41&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH41" s="193">
+      <c r="BH41" s="190">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="BI41" s="193">
+      <c r="BI41" s="190">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="BJ41" s="193">
+      <c r="BJ41" s="190">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -13564,7 +13565,9 @@
       <c r="AT42" s="120">
         <v>1</v>
       </c>
-      <c r="AU42" s="120"/>
+      <c r="AU42" s="120">
+        <v>3</v>
+      </c>
       <c r="AV42" s="120"/>
       <c r="AW42" s="120"/>
       <c r="AX42" s="120"/>
@@ -13573,37 +13576,37 @@
       <c r="BA42" s="120"/>
       <c r="BB42" s="120"/>
       <c r="BC42" s="120"/>
-      <c r="BD42" s="191">
+      <c r="BD42" s="188">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="BE42" s="191" cm="1">
+        <v>24</v>
+      </c>
+      <c r="BE42" s="188" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
-        <v>17</v>
-      </c>
-      <c r="BF42" s="191" cm="1">
+        <v>18</v>
+      </c>
+      <c r="BF42" s="188" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
         <v>5</v>
       </c>
-      <c r="BG42" s="192" cm="1">
+      <c r="BG42" s="189" cm="1">
         <f t="array" ref="BG42">SUMPRODUCT(--(B42:AI42=INT(B42:AI42)),--(B42:AI42&gt;0))/34*100%</f>
         <v>0.352941176470588</v>
       </c>
-      <c r="BH42" s="193">
+      <c r="BH42" s="190">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="BI42" s="193">
+        <v>3</v>
+      </c>
+      <c r="BI42" s="190">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="BJ42" s="193">
+      <c r="BJ42" s="190">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:62">
-      <c r="A43" s="195">
+      <c r="A43" s="191">
         <v>41</v>
       </c>
       <c r="B43" s="120"/>
@@ -13660,31 +13663,31 @@
       <c r="BA43" s="120"/>
       <c r="BB43" s="120"/>
       <c r="BC43" s="120"/>
-      <c r="BD43" s="191">
+      <c r="BD43" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE43" s="191" cm="1">
+      <c r="BE43" s="188" cm="1">
         <f t="array" ref="BE43">SUMPRODUCT(--(B43:BC43=INT(B43:BC43)),--(B43:BC43&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF43" s="191" cm="1">
+      <c r="BF43" s="188" cm="1">
         <f t="array" ref="BF43">MAX(FREQUENCY(IF((B43:BC43=INT(B43:BC43))*(B43:BC43&gt;0),COLUMN(B43:BC43)),IF((B43:BC43&lt;&gt;INT(B43:BC43))+(B43:BC43&lt;=0),COLUMN(B43:BC43))))</f>
         <v>0</v>
       </c>
-      <c r="BG43" s="192" cm="1">
+      <c r="BG43" s="189" cm="1">
         <f t="array" ref="BG43">SUMPRODUCT(--(B43:AI43=INT(B43:AI43)),--(B43:AI43&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH43" s="193">
+      <c r="BH43" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI43" s="193">
+      <c r="BI43" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ43" s="193">
+      <c r="BJ43" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -13770,7 +13773,9 @@
       </c>
       <c r="AS44" s="120"/>
       <c r="AT44" s="120"/>
-      <c r="AU44" s="120"/>
+      <c r="AU44" s="120">
+        <v>2</v>
+      </c>
       <c r="AV44" s="120"/>
       <c r="AW44" s="120"/>
       <c r="AX44" s="120"/>
@@ -13779,37 +13784,37 @@
       <c r="BA44" s="120"/>
       <c r="BB44" s="120"/>
       <c r="BC44" s="120"/>
-      <c r="BD44" s="191">
+      <c r="BD44" s="188">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="BE44" s="191" cm="1">
+        <v>21</v>
+      </c>
+      <c r="BE44" s="188" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
-        <v>16</v>
-      </c>
-      <c r="BF44" s="191" cm="1">
+        <v>17</v>
+      </c>
+      <c r="BF44" s="188" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
         <v>5</v>
       </c>
-      <c r="BG44" s="192" cm="1">
+      <c r="BG44" s="189" cm="1">
         <f t="array" ref="BG44">SUMPRODUCT(--(B44:AI44=INT(B44:AI44)),--(B44:AI44&gt;0))/34*100%</f>
         <v>0.411764705882353</v>
       </c>
-      <c r="BH44" s="193">
+      <c r="BH44" s="190">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="BI44" s="193">
+      <c r="BI44" s="190">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="BJ44" s="193">
+      <c r="BJ44" s="190">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:62">
-      <c r="A45" s="195">
+      <c r="A45" s="191">
         <v>43</v>
       </c>
       <c r="B45" s="120"/>
@@ -13866,31 +13871,31 @@
       <c r="BA45" s="120"/>
       <c r="BB45" s="120"/>
       <c r="BC45" s="120"/>
-      <c r="BD45" s="191">
+      <c r="BD45" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE45" s="191" cm="1">
+      <c r="BE45" s="188" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(--(B45:BC45=INT(B45:BC45)),--(B45:BC45&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF45" s="191" cm="1">
+      <c r="BF45" s="188" cm="1">
         <f t="array" ref="BF45">MAX(FREQUENCY(IF((B45:BC45=INT(B45:BC45))*(B45:BC45&gt;0),COLUMN(B45:BC45)),IF((B45:BC45&lt;&gt;INT(B45:BC45))+(B45:BC45&lt;=0),COLUMN(B45:BC45))))</f>
         <v>0</v>
       </c>
-      <c r="BG45" s="192" cm="1">
+      <c r="BG45" s="189" cm="1">
         <f t="array" ref="BG45">SUMPRODUCT(--(B45:AI45=INT(B45:AI45)),--(B45:AI45&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH45" s="193">
+      <c r="BH45" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI45" s="193">
+      <c r="BI45" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ45" s="193">
+      <c r="BJ45" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -14000,7 +14005,9 @@
       <c r="AT46" s="120">
         <v>1</v>
       </c>
-      <c r="AU46" s="120"/>
+      <c r="AU46" s="120">
+        <v>2</v>
+      </c>
       <c r="AV46" s="120"/>
       <c r="AW46" s="120"/>
       <c r="AX46" s="120"/>
@@ -14009,37 +14016,37 @@
       <c r="BA46" s="120"/>
       <c r="BB46" s="120"/>
       <c r="BC46" s="120"/>
-      <c r="BD46" s="191">
+      <c r="BD46" s="188">
         <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="BE46" s="191" cm="1">
+        <v>40</v>
+      </c>
+      <c r="BE46" s="188" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>28</v>
-      </c>
-      <c r="BF46" s="191" cm="1">
+        <v>29</v>
+      </c>
+      <c r="BF46" s="188" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
         <v>8</v>
       </c>
-      <c r="BG46" s="192" cm="1">
+      <c r="BG46" s="189" cm="1">
         <f t="array" ref="BG46">SUMPRODUCT(--(B46:AI46=INT(B46:AI46)),--(B46:AI46&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH46" s="193">
+      <c r="BH46" s="190">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="BI46" s="193">
+      <c r="BI46" s="190">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="BJ46" s="193">
+      <c r="BJ46" s="190">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:62">
-      <c r="A47" s="195">
+      <c r="A47" s="191">
         <v>45</v>
       </c>
       <c r="B47" s="120"/>
@@ -14096,31 +14103,31 @@
       <c r="BA47" s="120"/>
       <c r="BB47" s="120"/>
       <c r="BC47" s="120"/>
-      <c r="BD47" s="191">
+      <c r="BD47" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE47" s="191" cm="1">
+      <c r="BE47" s="188" cm="1">
         <f t="array" ref="BE47">SUMPRODUCT(--(B47:BC47=INT(B47:BC47)),--(B47:BC47&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF47" s="191" cm="1">
+      <c r="BF47" s="188" cm="1">
         <f t="array" ref="BF47">MAX(FREQUENCY(IF((B47:BC47=INT(B47:BC47))*(B47:BC47&gt;0),COLUMN(B47:BC47)),IF((B47:BC47&lt;&gt;INT(B47:BC47))+(B47:BC47&lt;=0),COLUMN(B47:BC47))))</f>
         <v>0</v>
       </c>
-      <c r="BG47" s="192" cm="1">
+      <c r="BG47" s="189" cm="1">
         <f t="array" ref="BG47">SUMPRODUCT(--(B47:AI47=INT(B47:AI47)),--(B47:AI47&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH47" s="193">
+      <c r="BH47" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI47" s="193">
+      <c r="BI47" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ47" s="193">
+      <c r="BJ47" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -14200,7 +14207,9 @@
       </c>
       <c r="AS48" s="120"/>
       <c r="AT48" s="120"/>
-      <c r="AU48" s="120"/>
+      <c r="AU48" s="120">
+        <v>2</v>
+      </c>
       <c r="AV48" s="120"/>
       <c r="AW48" s="120"/>
       <c r="AX48" s="120"/>
@@ -14209,31 +14218,31 @@
       <c r="BA48" s="120"/>
       <c r="BB48" s="120"/>
       <c r="BC48" s="120"/>
-      <c r="BD48" s="191">
+      <c r="BD48" s="188">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="BE48" s="191" cm="1">
+        <v>17</v>
+      </c>
+      <c r="BE48" s="188" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
-        <v>13</v>
-      </c>
-      <c r="BF48" s="191" cm="1">
+        <v>14</v>
+      </c>
+      <c r="BF48" s="188" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
         <v>2</v>
       </c>
-      <c r="BG48" s="192" cm="1">
+      <c r="BG48" s="189" cm="1">
         <f t="array" ref="BG48">SUMPRODUCT(--(B48:AI48=INT(B48:AI48)),--(B48:AI48&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH48" s="193">
+      <c r="BH48" s="190">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="BI48" s="193">
+      <c r="BI48" s="190">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="BJ48" s="193">
+      <c r="BJ48" s="190">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -14304,31 +14313,31 @@
       <c r="BA49" s="120"/>
       <c r="BB49" s="120"/>
       <c r="BC49" s="120"/>
-      <c r="BD49" s="191">
+      <c r="BD49" s="188">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE49" s="191" cm="1">
+      <c r="BE49" s="188" cm="1">
         <f t="array" ref="BE49">SUMPRODUCT(--(B49:BC49=INT(B49:BC49)),--(B49:BC49&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF49" s="191" cm="1">
+      <c r="BF49" s="188" cm="1">
         <f t="array" ref="BF49">MAX(FREQUENCY(IF((B49:BC49=INT(B49:BC49))*(B49:BC49&gt;0),COLUMN(B49:BC49)),IF((B49:BC49&lt;&gt;INT(B49:BC49))+(B49:BC49&lt;=0),COLUMN(B49:BC49))))</f>
         <v>1</v>
       </c>
-      <c r="BG49" s="192" cm="1">
+      <c r="BG49" s="189" cm="1">
         <f t="array" ref="BG49">SUMPRODUCT(--(B49:AI49=INT(B49:AI49)),--(B49:AI49&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH49" s="193">
+      <c r="BH49" s="190">
         <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="BI49" s="193">
+        <v>26</v>
+      </c>
+      <c r="BI49" s="190">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ49" s="193">
+      <c r="BJ49" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -14401,37 +14410,37 @@
       <c r="BA50" s="120"/>
       <c r="BB50" s="120"/>
       <c r="BC50" s="120"/>
-      <c r="BD50" s="191">
+      <c r="BD50" s="188">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE50" s="191" cm="1">
+      <c r="BE50" s="188" cm="1">
         <f t="array" ref="BE50">SUMPRODUCT(--(B50:BC50=INT(B50:BC50)),--(B50:BC50&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF50" s="191" cm="1">
+      <c r="BF50" s="188" cm="1">
         <f t="array" ref="BF50">MAX(FREQUENCY(IF((B50:BC50=INT(B50:BC50))*(B50:BC50&gt;0),COLUMN(B50:BC50)),IF((B50:BC50&lt;&gt;INT(B50:BC50))+(B50:BC50&lt;=0),COLUMN(B50:BC50))))</f>
         <v>1</v>
       </c>
-      <c r="BG50" s="192" cm="1">
+      <c r="BG50" s="189" cm="1">
         <f t="array" ref="BG50">SUMPRODUCT(--(B50:AI50=INT(B50:AI50)),--(B50:AI50&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH50" s="193">
+      <c r="BH50" s="190">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="BI50" s="193">
+        <v>23</v>
+      </c>
+      <c r="BI50" s="190">
         <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="BJ50" s="193">
+        <v>23</v>
+      </c>
+      <c r="BJ50" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:62">
-      <c r="A51" s="195">
+      <c r="A51" s="191">
         <v>49</v>
       </c>
       <c r="B51" s="120"/>
@@ -14488,37 +14497,37 @@
       <c r="BA51" s="120"/>
       <c r="BB51" s="120"/>
       <c r="BC51" s="120"/>
-      <c r="BD51" s="191">
+      <c r="BD51" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE51" s="191" cm="1">
+      <c r="BE51" s="188" cm="1">
         <f t="array" ref="BE51">SUMPRODUCT(--(B51:BC51=INT(B51:BC51)),--(B51:BC51&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF51" s="191" cm="1">
+      <c r="BF51" s="188" cm="1">
         <f t="array" ref="BF51">MAX(FREQUENCY(IF((B51:BC51=INT(B51:BC51))*(B51:BC51&gt;0),COLUMN(B51:BC51)),IF((B51:BC51&lt;&gt;INT(B51:BC51))+(B51:BC51&lt;=0),COLUMN(B51:BC51))))</f>
         <v>0</v>
       </c>
-      <c r="BG51" s="192" cm="1">
+      <c r="BG51" s="189" cm="1">
         <f t="array" ref="BG51">SUMPRODUCT(--(B51:AI51=INT(B51:AI51)),--(B51:AI51&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH51" s="193">
+      <c r="BH51" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI51" s="193">
+      <c r="BI51" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ51" s="193">
+      <c r="BJ51" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:62">
-      <c r="A52" s="195">
+      <c r="A52" s="191">
         <v>50</v>
       </c>
       <c r="B52" s="120"/>
@@ -14575,31 +14584,31 @@
       <c r="BA52" s="120"/>
       <c r="BB52" s="120"/>
       <c r="BC52" s="120"/>
-      <c r="BD52" s="191">
+      <c r="BD52" s="188">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE52" s="191" cm="1">
+      <c r="BE52" s="188" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(--(B52:BC52=INT(B52:BC52)),--(B52:BC52&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF52" s="191" cm="1">
+      <c r="BF52" s="188" cm="1">
         <f t="array" ref="BF52">MAX(FREQUENCY(IF((B52:BC52=INT(B52:BC52))*(B52:BC52&gt;0),COLUMN(B52:BC52)),IF((B52:BC52&lt;&gt;INT(B52:BC52))+(B52:BC52&lt;=0),COLUMN(B52:BC52))))</f>
         <v>0</v>
       </c>
-      <c r="BG52" s="192" cm="1">
+      <c r="BG52" s="189" cm="1">
         <f t="array" ref="BG52">SUMPRODUCT(--(B52:AI52=INT(B52:AI52)),--(B52:AI52&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH52" s="193">
+      <c r="BH52" s="190">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI52" s="193">
+      <c r="BI52" s="190">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ52" s="193">
+      <c r="BJ52" s="190">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -14664,31 +14673,31 @@
       <c r="BA53" s="120"/>
       <c r="BB53" s="120"/>
       <c r="BC53" s="120"/>
-      <c r="BD53" s="191">
+      <c r="BD53" s="188">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE53" s="191" cm="1">
+      <c r="BE53" s="188" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(--(B53:BC53=INT(B53:BC53)),--(B53:BC53&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF53" s="191" cm="1">
+      <c r="BF53" s="188" cm="1">
         <f t="array" ref="BF53">MAX(FREQUENCY(IF((B53:BC53=INT(B53:BC53))*(B53:BC53&gt;0),COLUMN(B53:BC53)),IF((B53:BC53&lt;&gt;INT(B53:BC53))+(B53:BC53&lt;=0),COLUMN(B53:BC53))))</f>
         <v>1</v>
       </c>
-      <c r="BG53" s="192" cm="1">
+      <c r="BG53" s="189" cm="1">
         <f t="array" ref="BG53">SUMPRODUCT(--(B53:AI53=INT(B53:AI53)),--(B53:AI53&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH53" s="193">
+      <c r="BH53" s="190">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI53" s="193">
+      <c r="BI53" s="190">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ53" s="193">
+      <c r="BJ53" s="190">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -15816,9 +15825,8 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A29:X33 Z29:AF33 A4:X4 Z42:AE42 BH4:BJ4 BH6:BJ8 BH11:BJ14 BH23:BJ39 A12:X14" unlockedFormula="1"/>
-    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 Z9:AB9 A1 C1:S1 C1:S1 U1:AF1 U1:AF1 A11:Z11 AB11:AC11 AB11:AC11 AE11 AE11 AB15:AE15 Z15 Z15 Z14:AF14 AB13:AF13 Z13 Z13 Z12:AF12 A16:AF16 A16:AF16 A17:X18 A17:X18 Z17:AF18 Z17:AF18 A19:AF21 A19:AF21 A22:X22 A22:X22 AA22:AD22 AA22:AD22 AF22 AF22 A23:AF23 A24:X25 Z24:AF25 Z24:AF25 A26:AF27 A26:AF27 A28:X28 A30:X33 Z28:AF28 Z30:AF33 Z29:AF29 A34:AF35 A34:AF35 A36:X36 A36:X36 Z36:AF36 Z36:AF36 A38:X38 A38:X38 Z38:AB38 Z38:AB38 AD38:AF38 AD38:AF38 A3:X3 A3:X4 BD1:BJ2 BD1:BJ2 BI3 BI3 AC40:AD40 AC40:AD40 A40:V40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 Z44:AD44 AF44 AF44 A43:AF43 A43:AF43 A46:X46 AA46 AA46 AC46:AD46 AC46:AD46 AF46 AF46 A47:AF47 A48:X49 A48:X49 Z48:AB48 Z48:AB48 AE48 AE48 A51:AF53 A51:AF53 A50:AD50 A50:AD50 AF50 AF50 X8:AF8 A8:V8 A8:V8 A5:AF7 Z4:AE4 Z41:AE41 Z42:AE42 Z41:AE42 BH5:BJ5 BH7:BJ7 BI9:BJ9 BI9:BJ9 Z10:AF10 Z10:AF10 BH15:BJ22 BH13:BJ13 BH12:BJ12 BH24:BJ28 BH30:BJ39 BH11:BJ39 Z49:AF49 Z49:AF49 A15:X15 A14:X14 A13:X13 A12:X12 A12:X15 A37:AF37 A37:AF37 A39:AF39 A39:AF39 A2:AF2 A2:AF2 Z3:AF3 Z3:AF3 A9:X10" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="AU11:BG11 AU14:BG14 AU23:BG23 AU29:BG29 AU42:BJ42 AU46:BJ46 AU4:BG4 AG6:AS6 AU6:BG6 AU8:BG8 A41:W41 Y41:BJ41 Y9:AC9 AG9:BJ9 Y10:BJ10 B1:BJ1 A2:BJ3 AA11:AS11 A15:AA15 AF15:BJ15 A16:BJ22 A12:X14 AG14:AS14 A13:AA13 BH11:BJ14 A12:Y12 AG23:AS23 BH23:BJ39 A26:BJ28 Y30:BJ33 A34:BJ40 Y29 AG29:AS29 A4:Y4 Z42:AE42 AG45:BJ45 A43:BJ43 X44:BJ44 Y46:AS46 AG47:BJ47 A48:BJ53 A8:W8 AG8:AS8 AF4:AS4 AG5:BG5 AG7:BG7" formulaRange="1"/>
+    <ignoredError sqref="A1:BJ8 Y9:BJ10 A11:BJ53" formulaRange="1"/>
+    <ignoredError sqref="A9:X10 Z3:AF3 A2:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH23:BJ29 BI35:BJ35 BH36:BJ39 BH24:BJ28 BH11:BJ14 Z10:AF10 BI9:BJ9 BH6:BJ8 BH4:BJ5 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z29:AF29 A29:X33 A28:X28 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11 U1:AF1 C1:S1 A1 Z9:AB9 AD9:AF9 X41" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15840,233 +15848,233 @@
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:10">
-      <c r="A1" s="151"/>
-      <c r="B1" s="152" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="152"/>
-      <c r="D1" s="153" t="s">
+      <c r="A1" s="148"/>
+      <c r="B1" s="149" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="149"/>
+      <c r="D1" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="154"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="152" t="s">
+      <c r="E1" s="151"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="149" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="152" t="s">
+      <c r="H1" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="152" t="s">
+      <c r="I1" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="152" t="s">
+      <c r="J1" s="149" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="16.5" spans="1:10">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="149" t="s">
         <v>321</v>
       </c>
-      <c r="B2" s="156" t="s">
+      <c r="B2" s="153" t="s">
         <v>322</v>
       </c>
-      <c r="C2" s="157" t="s">
+      <c r="C2" s="154" t="s">
         <v>323</v>
       </c>
-      <c r="D2" s="158"/>
-      <c r="E2" s="156" t="s">
+      <c r="D2" s="155"/>
+      <c r="E2" s="153" t="s">
         <v>322</v>
       </c>
-      <c r="F2" s="156"/>
-      <c r="G2" s="159" t="s">
+      <c r="F2" s="153"/>
+      <c r="G2" s="156" t="s">
         <v>324</v>
       </c>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="160"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="157"/>
     </row>
     <row r="3" ht="16.5" spans="1:10">
-      <c r="A3" s="152" t="s">
+      <c r="A3" s="149" t="s">
         <v>325</v>
       </c>
-      <c r="B3" s="161" t="s">
+      <c r="B3" s="158" t="s">
         <v>326</v>
       </c>
-      <c r="C3" s="161"/>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="151"/>
-      <c r="I3" s="151"/>
-      <c r="J3" s="160"/>
+      <c r="C3" s="158"/>
+      <c r="D3" s="158"/>
+      <c r="E3" s="158"/>
+      <c r="F3" s="158"/>
+      <c r="G3" s="158"/>
+      <c r="H3" s="148"/>
+      <c r="I3" s="148"/>
+      <c r="J3" s="157"/>
     </row>
     <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="149" t="s">
         <v>327</v>
       </c>
-      <c r="B4" s="162" t="s">
+      <c r="B4" s="159" t="s">
         <v>247</v>
       </c>
-      <c r="C4" s="162"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="162"/>
-      <c r="F4" s="162"/>
-      <c r="G4" s="162"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="151"/>
-      <c r="J4" s="160"/>
+      <c r="C4" s="159"/>
+      <c r="D4" s="159"/>
+      <c r="E4" s="159"/>
+      <c r="F4" s="159"/>
+      <c r="G4" s="159"/>
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="157"/>
     </row>
     <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="149" t="s">
         <v>328</v>
       </c>
-      <c r="B5" s="163">
-        <v>1</v>
-      </c>
-      <c r="C5" s="163"/>
-      <c r="D5" s="164">
+      <c r="B5" s="160">
+        <v>1</v>
+      </c>
+      <c r="C5" s="160"/>
+      <c r="D5" s="161">
         <v>2</v>
       </c>
-      <c r="E5" s="164"/>
-      <c r="F5" s="164"/>
-      <c r="G5" s="163">
+      <c r="E5" s="161"/>
+      <c r="F5" s="161"/>
+      <c r="G5" s="160">
         <v>3</v>
       </c>
-      <c r="H5" s="151"/>
-      <c r="I5" s="151"/>
-      <c r="J5" s="160"/>
+      <c r="H5" s="148"/>
+      <c r="I5" s="148"/>
+      <c r="J5" s="157"/>
     </row>
     <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="152" t="s">
+      <c r="A6" s="149" t="s">
         <v>329</v>
       </c>
-      <c r="B6" s="165">
-        <v>1</v>
-      </c>
-      <c r="C6" s="165"/>
-      <c r="D6" s="165"/>
-      <c r="E6" s="165"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="166" t="s">
+      <c r="B6" s="162">
+        <v>1</v>
+      </c>
+      <c r="C6" s="162"/>
+      <c r="D6" s="162"/>
+      <c r="E6" s="162"/>
+      <c r="F6" s="162"/>
+      <c r="G6" s="163" t="s">
         <v>330</v>
       </c>
-      <c r="H6" s="151"/>
-      <c r="I6" s="151"/>
-      <c r="J6" s="160"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="157"/>
     </row>
     <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="152" t="s">
+      <c r="A7" s="149" t="s">
         <v>331</v>
       </c>
-      <c r="B7" s="167" t="s">
+      <c r="B7" s="164" t="s">
         <v>332</v>
       </c>
-      <c r="C7" s="167"/>
-      <c r="D7" s="167"/>
-      <c r="E7" s="167"/>
-      <c r="F7" s="167"/>
-      <c r="G7" s="168">
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="165">
         <v>2</v>
       </c>
-      <c r="H7" s="151"/>
-      <c r="I7" s="151"/>
-      <c r="J7" s="160"/>
+      <c r="H7" s="148"/>
+      <c r="I7" s="148"/>
+      <c r="J7" s="157"/>
     </row>
     <row r="8" ht="16.5" spans="1:10">
-      <c r="A8" s="152" t="s">
+      <c r="A8" s="149" t="s">
         <v>333</v>
       </c>
-      <c r="B8" s="169">
-        <v>1</v>
-      </c>
-      <c r="C8" s="169"/>
-      <c r="D8" s="170" t="s">
+      <c r="B8" s="166">
+        <v>1</v>
+      </c>
+      <c r="C8" s="166"/>
+      <c r="D8" s="167" t="s">
         <v>334</v>
       </c>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="169"/>
-      <c r="H8" s="151"/>
-      <c r="I8" s="151"/>
-      <c r="J8" s="160"/>
+      <c r="E8" s="167"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="166"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="157"/>
     </row>
     <row r="9" ht="16.5" spans="1:10">
-      <c r="A9" s="152" t="s">
+      <c r="A9" s="149" t="s">
         <v>335</v>
       </c>
-      <c r="B9" s="156" t="s">
+      <c r="B9" s="153" t="s">
         <v>336</v>
       </c>
-      <c r="C9" s="156"/>
-      <c r="D9" s="156"/>
-      <c r="E9" s="156"/>
-      <c r="F9" s="156"/>
-      <c r="G9" s="156"/>
-      <c r="H9" s="151"/>
-      <c r="I9" s="151"/>
-      <c r="J9" s="160"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="148"/>
+      <c r="I9" s="148"/>
+      <c r="J9" s="157"/>
     </row>
     <row r="10" ht="16.5" spans="1:10">
-      <c r="A10" s="152" t="s">
+      <c r="A10" s="149" t="s">
         <v>337</v>
       </c>
-      <c r="B10" s="161">
-        <v>1</v>
-      </c>
-      <c r="C10" s="161"/>
-      <c r="D10" s="171" t="s">
+      <c r="B10" s="158">
+        <v>1</v>
+      </c>
+      <c r="C10" s="158"/>
+      <c r="D10" s="168" t="s">
         <v>338</v>
       </c>
-      <c r="E10" s="161">
-        <v>1</v>
-      </c>
-      <c r="F10" s="171" t="s">
+      <c r="E10" s="158">
+        <v>1</v>
+      </c>
+      <c r="F10" s="168" t="s">
         <v>338</v>
       </c>
-      <c r="G10" s="151" t="s">
+      <c r="G10" s="148" t="s">
         <v>339</v>
       </c>
-      <c r="H10" s="151"/>
-      <c r="I10" s="151"/>
-      <c r="J10" s="160"/>
+      <c r="H10" s="148"/>
+      <c r="I10" s="148"/>
+      <c r="J10" s="157"/>
     </row>
     <row r="11" ht="16.5" spans="1:10">
-      <c r="A11" s="152" t="s">
+      <c r="A11" s="149" t="s">
         <v>340</v>
       </c>
-      <c r="B11" s="162">
-        <v>1</v>
-      </c>
-      <c r="C11" s="162"/>
-      <c r="D11" s="162"/>
-      <c r="E11" s="162"/>
-      <c r="F11" s="162"/>
-      <c r="G11" s="162"/>
-      <c r="H11" s="151"/>
-      <c r="I11" s="151"/>
-      <c r="J11" s="160"/>
+      <c r="B11" s="159">
+        <v>1</v>
+      </c>
+      <c r="C11" s="159"/>
+      <c r="D11" s="159"/>
+      <c r="E11" s="159"/>
+      <c r="F11" s="159"/>
+      <c r="G11" s="159"/>
+      <c r="H11" s="148"/>
+      <c r="I11" s="148"/>
+      <c r="J11" s="157"/>
     </row>
     <row r="12" ht="16.5" spans="1:10">
-      <c r="A12" s="152" t="s">
+      <c r="A12" s="149" t="s">
         <v>341</v>
       </c>
-      <c r="B12" s="163">
-        <v>1</v>
-      </c>
-      <c r="C12" s="163"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="163"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="164">
+      <c r="B12" s="160">
+        <v>1</v>
+      </c>
+      <c r="C12" s="160"/>
+      <c r="D12" s="160"/>
+      <c r="E12" s="160"/>
+      <c r="F12" s="160"/>
+      <c r="G12" s="161">
         <v>2</v>
       </c>
-      <c r="H12" s="151"/>
-      <c r="I12" s="151"/>
-      <c r="J12" s="160"/>
+      <c r="H12" s="148"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="157"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A13" s="152" t="s">
+      <c r="A13" s="149" t="s">
         <v>342</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -16076,28 +16084,28 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="172" t="s">
+      <c r="G13" s="169" t="s">
         <v>343</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="173"/>
+      <c r="J13" s="170"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
-      <c r="A14" s="152" t="s">
+      <c r="A14" s="149" t="s">
         <v>344</v>
       </c>
-      <c r="B14" s="174" t="s">
+      <c r="B14" s="171" t="s">
         <v>339</v>
       </c>
-      <c r="C14" s="174"/>
-      <c r="D14" s="174"/>
-      <c r="E14" s="174"/>
-      <c r="F14" s="174"/>
-      <c r="G14" s="174"/>
-      <c r="H14" s="174"/>
-      <c r="I14" s="175"/>
-      <c r="J14" s="176"/>
+      <c r="C14" s="171"/>
+      <c r="D14" s="171"/>
+      <c r="E14" s="171"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="171"/>
+      <c r="H14" s="171"/>
+      <c r="I14" s="172"/>
+      <c r="J14" s="173"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -16342,13 +16350,13 @@
     <row r="13" s="119" customFormat="1" spans="1:9">
       <c r="A13" s="142"/>
       <c r="B13" s="136"/>
-      <c r="C13" s="143" t="s">
+      <c r="C13" s="137" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="145"/>
+      <c r="D13" s="143"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="143"/>
+      <c r="G13" s="138"/>
     </row>
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="142"/>
@@ -16358,7 +16366,7 @@
       <c r="C14" s="137" t="s">
         <v>358</v>
       </c>
-      <c r="D14" s="146"/>
+      <c r="D14" s="143"/>
       <c r="E14" s="138"/>
       <c r="F14" s="140" t="s">
         <v>36</v>
@@ -16370,84 +16378,84 @@
       <c r="B15" s="136" t="s">
         <v>359</v>
       </c>
-      <c r="C15" s="143" t="s">
+      <c r="C15" s="137" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="144"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="145"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="143"/>
+      <c r="G15" s="138"/>
     </row>
     <row r="16" s="119" customFormat="1" spans="1:9">
       <c r="A16" s="142"/>
       <c r="B16" s="136"/>
-      <c r="C16" s="143" t="s">
+      <c r="C16" s="137" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="144"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="145"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="138"/>
     </row>
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="142"/>
       <c r="B17" s="136" t="s">
         <v>360</v>
       </c>
-      <c r="C17" s="143" t="s">
+      <c r="C17" s="137" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="144"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="145"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="143"/>
+      <c r="G17" s="138"/>
     </row>
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="142"/>
       <c r="B18" s="136" t="s">
         <v>361</v>
       </c>
-      <c r="C18" s="143" t="s">
+      <c r="C18" s="137" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="144"/>
-      <c r="E18" s="144"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="145"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="143"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="138"/>
     </row>
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="142"/>
       <c r="B19" s="136" t="s">
         <v>362</v>
       </c>
-      <c r="C19" s="143" t="s">
+      <c r="C19" s="137" t="s">
         <v>84</v>
       </c>
-      <c r="D19" s="144"/>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
-      <c r="G19" s="145"/>
+      <c r="D19" s="143"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="143"/>
+      <c r="G19" s="138"/>
     </row>
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="142"/>
       <c r="B20" s="136" t="s">
         <v>363</v>
       </c>
-      <c r="C20" s="143" t="s">
+      <c r="C20" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="144"/>
-      <c r="E20" s="144"/>
-      <c r="F20" s="144"/>
-      <c r="G20" s="145"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="143"/>
+      <c r="F20" s="143"/>
+      <c r="G20" s="138"/>
     </row>
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="142"/>
       <c r="B21" s="136" t="s">
         <v>364</v>
       </c>
-      <c r="C21" s="147"/>
-      <c r="D21" s="148"/>
+      <c r="C21" s="144"/>
+      <c r="D21" s="145"/>
       <c r="E21" s="139" t="s">
         <v>27</v>
       </c>
@@ -16455,15 +16463,15 @@
       <c r="G21" s="141"/>
     </row>
     <row r="22" s="119" customFormat="1" spans="1:7">
-      <c r="A22" s="149"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="136" t="s">
         <v>365</v>
       </c>
-      <c r="C22" s="147"/>
-      <c r="D22" s="150"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="150"/>
-      <c r="G22" s="148"/>
+      <c r="C22" s="144"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="147"/>
+      <c r="G22" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="32">

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="4"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="662">
   <si>
     <t>姓名</t>
   </si>
@@ -989,6 +989,18 @@
     <t>音乐课长期变为做生物任务。当天无任务，改抄英语笔记，大课间时告知回班抄笔记，音乐课改背书（地理）</t>
   </si>
   <si>
+    <t>刘老师“以小见大”</t>
+  </si>
+  <si>
+    <t>八下3.13</t>
+  </si>
+  <si>
+    <t>课件：“Emm,then you will have to take some ()”任务：listen and repeat。
+听完本句录音，学生大声朗读“emm”，空格处说不出来。刘老师：注意力不在重点、刚才崔宇臣/林芷琪笑、不止“emm”，其他也一样、态度
+重来，学生顺利读出“foreign money”。刘老师：都能说出来
+接下来顺利读完。刘老师：集中注意力就不会拖拉停顿、命令执行效率（circle/underline/repeat）、80%学生认识circle（认识的举手），但执行时（第一遍：10个左右成绩好学生完成；第二遍：要去催的人完成；第三遍：提醒蔡华楷、薛阅晨、崔宇臣等人，王淮等人可进行下一步骤）、刚才段长公开课无拖拉，说明是能专心的、课程紧迫，但这样导致无法完成课时、吸收效率（有人90%吸收，有人10%但晚上努力背诵，却无效果）、笔记本不要合上/笔拿手上：频繁拿笔效率低，细节问题不容忽视、注意力集中的方法（take notes/answer the questions aloud）</t>
+  </si>
+  <si>
     <t>政治课</t>
   </si>
   <si>
@@ -1029,6 +1041,12 @@
   </si>
   <si>
     <t>下午第一节语文</t>
+  </si>
+  <si>
+    <t>2026.3.13</t>
+  </si>
+  <si>
+    <t>下午第二节语文</t>
   </si>
   <si>
     <t>座号</t>
@@ -1075,6 +1093,28 @@
   <si>
     <t>连击
 排名</t>
+  </si>
+  <si>
+    <t>请人
+个数</t>
+  </si>
+  <si>
+    <r>
+      <t>数学课情人记录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+起立回答问题、主动起立回答问题、上台写题目均为有效数据。</t>
+    </r>
+  </si>
+  <si>
+    <t>请人
+次数</t>
   </si>
   <si>
     <t>语文</t>
@@ -2985,7 +3025,7 @@
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="55">
+  <fonts count="56">
     <font>
       <sz val="11"/>
       <name val="宋体"/>
@@ -3134,6 +3174,12 @@
     <font>
       <sz val="11"/>
       <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3315,7 +3361,12 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3326,17 +3377,12 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
     <font>
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3678,7 +3724,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -3853,6 +3899,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -3955,155 +4021,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="15" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="27" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="28" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="28" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="29" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="28" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="48" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="235">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4631,6 +4697,9 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -4680,16 +4749,37 @@
     <xf numFmtId="0" fontId="25" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4698,16 +4788,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4728,14 +4818,14 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -4787,7 +4877,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4799,7 +4889,7 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5147,538 +5237,538 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="224" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="225" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="226" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="227"/>
+    <col min="1" max="1" width="7.59090909090909" style="232" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="233" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="234" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="235"/>
   </cols>
   <sheetData>
-    <row r="1" s="223" customFormat="1" spans="1:10">
-      <c r="A1" s="228" t="s">
+    <row r="1" s="231" customFormat="1" spans="1:10">
+      <c r="A1" s="236" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="229" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="229" t="s">
+      <c r="B1" s="237" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="237" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="229" t="s">
+      <c r="D1" s="237" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="229" t="s">
+      <c r="E1" s="237" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="229" t="s">
+      <c r="F1" s="237" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="229" t="s">
+      <c r="G1" s="237" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="230"/>
-      <c r="I1" s="230"/>
-      <c r="J1" s="230"/>
+      <c r="H1" s="238"/>
+      <c r="I1" s="238"/>
+      <c r="J1" s="238"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="231" t="s">
+      <c r="A2" s="239" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="225" t="s">
+      <c r="B2" s="233" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="225" t="s">
+      <c r="C2" s="233" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="231" t="s">
+      <c r="A3" s="239" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="225" t="s">
+      <c r="C3" s="233" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="225" t="s">
+      <c r="D3" s="233" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="231" t="s">
+      <c r="A4" s="239" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="225" t="s">
+      <c r="D4" s="233" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="231" t="s">
+      <c r="A5" s="239" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="225" t="s">
+      <c r="C5" s="233" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="225" t="s">
+      <c r="D5" s="233" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="231" t="s">
+      <c r="A6" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="225" t="s">
+      <c r="C6" s="233" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="231" t="s">
+      <c r="A7" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="225" t="s">
+      <c r="B7" s="233" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="225" t="s">
+      <c r="C7" s="233" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="225" t="s">
+      <c r="D7" s="233" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="231" t="s">
+      <c r="A8" s="239" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="225" t="s">
+      <c r="D8" s="233" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="231" t="s">
+      <c r="A9" s="239" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="231" t="s">
+      <c r="A10" s="239" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="225" t="s">
+      <c r="B10" s="233" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="231" t="s">
+      <c r="A11" s="239" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="231" t="s">
+      <c r="A12" s="239" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="231" t="s">
+      <c r="A13" s="239" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="225" t="s">
+      <c r="D13" s="233" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="231" t="s">
+      <c r="A14" s="239" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="225" t="s">
+      <c r="B14" s="233" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="231" t="s">
+      <c r="A15" s="239" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="231" t="s">
+      <c r="A16" s="239" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="225" t="s">
+      <c r="C16" s="233" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:5">
-      <c r="A17" s="231" t="s">
+      <c r="A17" s="239" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="225" t="s">
+      <c r="C17" s="233" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="231" t="s">
+      <c r="A18" s="239" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="225" t="s">
+      <c r="D18" s="233" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:5">
-      <c r="A19" s="231" t="s">
+      <c r="A19" s="239" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="225" t="s">
+      <c r="D19" s="233" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:5">
-      <c r="A20" s="231" t="s">
+      <c r="A20" s="239" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="225" t="s">
+      <c r="B20" s="233" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="225" t="s">
+      <c r="C20" s="233" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:5">
-      <c r="A21" s="231" t="s">
+      <c r="A21" s="239" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="225" t="s">
+      <c r="B21" s="233" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="225" t="s">
+      <c r="C21" s="233" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="225" t="s">
+      <c r="D21" s="233" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="231" t="s">
+      <c r="A22" s="239" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:5">
-      <c r="A23" s="231" t="s">
+      <c r="A23" s="239" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="225" t="s">
+      <c r="B23" s="233" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:5">
-      <c r="A24" s="231" t="s">
+      <c r="A24" s="239" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="225" t="s">
+      <c r="B24" s="233" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="225" t="s">
+      <c r="C24" s="233" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="225" t="s">
+      <c r="D24" s="233" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="231" t="s">
+      <c r="A25" s="239" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="231" t="s">
+      <c r="A26" s="239" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="231" t="s">
+      <c r="A27" s="239" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="225" t="s">
+      <c r="B27" s="233" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="225" t="s">
+      <c r="C27" s="233" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:5">
-      <c r="A28" s="231" t="s">
+      <c r="A28" s="239" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="225" t="s">
+      <c r="B28" s="233" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="225" t="s">
+      <c r="C28" s="233" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="225" t="s">
+      <c r="D28" s="233" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="225" t="s">
+      <c r="E28" s="233" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="231" t="s">
+      <c r="A29" s="239" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="231" t="s">
+      <c r="A30" s="239" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="225" t="s">
+      <c r="B30" s="233" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="225" t="s">
+      <c r="C30" s="233" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="231" t="s">
+      <c r="A31" s="239" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="231" t="s">
+      <c r="A32" s="239" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="231" t="s">
+      <c r="A33" s="239" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="231" t="s">
+      <c r="A34" s="239" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="231" t="s">
+      <c r="A35" s="239" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="231" t="s">
+      <c r="A36" s="239" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="225" t="s">
+      <c r="B36" s="233" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="231" t="s">
+      <c r="A37" s="239" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="225" t="s">
+      <c r="C37" s="233" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="225" t="s">
+      <c r="D37" s="233" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="231" t="s">
+      <c r="A38" s="239" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="225" t="s">
+      <c r="B38" s="233" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="232"/>
-      <c r="D38" s="232"/>
-      <c r="E38" s="232"/>
-      <c r="F38" s="232"/>
-      <c r="G38" s="232"/>
+      <c r="C38" s="240"/>
+      <c r="D38" s="240"/>
+      <c r="E38" s="240"/>
+      <c r="F38" s="240"/>
+      <c r="G38" s="240"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="231" t="s">
+      <c r="A39" s="239" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="225" t="s">
+      <c r="C39" s="233" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="225" t="s">
+      <c r="D39" s="233" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="231" t="s">
+      <c r="A40" s="239" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="225" t="s">
+      <c r="B40" s="233" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="225" t="s">
+      <c r="C40" s="233" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="225" t="s">
+      <c r="D40" s="233" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="231" t="s">
+      <c r="A41" s="239" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="225" t="s">
+      <c r="C41" s="233" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="225" t="s">
+      <c r="D41" s="233" t="s">
         <v>93</v>
       </c>
-      <c r="E41" s="225" t="s">
+      <c r="E41" s="233" t="s">
         <v>94</v>
       </c>
-      <c r="H41" s="226" t="s">
+      <c r="H41" s="234" t="s">
         <v>95</v>
       </c>
-      <c r="I41" s="226" t="s">
+      <c r="I41" s="234" t="s">
         <v>96</v>
       </c>
-      <c r="J41" s="226" t="s">
+      <c r="J41" s="234" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="231" t="s">
+      <c r="A42" s="239" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="231" t="s">
+      <c r="A43" s="239" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="225" t="s">
+      <c r="B43" s="233" t="s">
         <v>100</v>
       </c>
-      <c r="H43" s="226" t="s">
+      <c r="H43" s="234" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="231" t="s">
+      <c r="A44" s="239" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="225" t="s">
+      <c r="B44" s="233" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="231" t="s">
+      <c r="A45" s="239" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="225" t="s">
+      <c r="C45" s="233" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="225" t="s">
+      <c r="D45" s="233" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="231" t="s">
+      <c r="A46" s="239" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="231" t="s">
+      <c r="A47" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="225" t="s">
+      <c r="D47" s="233" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="231" t="s">
+      <c r="A48" s="239" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="225" t="s">
+      <c r="C48" s="233" t="s">
         <v>111</v>
       </c>
-      <c r="D48" s="225" t="s">
+      <c r="D48" s="233" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="231" t="s">
+      <c r="A49" s="239" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="231" t="s">
+      <c r="A50" s="239" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="225" t="s">
+      <c r="C50" s="233" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="231" t="s">
+      <c r="A51" s="239" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="231" t="s">
+      <c r="A52" s="239" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="225" t="s">
+      <c r="B52" s="233" t="s">
         <v>118</v>
       </c>
-      <c r="C52" s="225" t="s">
+      <c r="C52" s="233" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="225" t="s">
+      <c r="E52" s="233" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="224" t="s">
+      <c r="A53" s="232" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="225" t="s">
+      <c r="B53" s="233" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="232"/>
-      <c r="E53" s="232"/>
-      <c r="F53" s="232"/>
-      <c r="G53" s="232"/>
+      <c r="D53" s="240"/>
+      <c r="E53" s="240"/>
+      <c r="F53" s="240"/>
+      <c r="G53" s="240"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="224" t="s">
+      <c r="A54" s="232" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="225" t="s">
+      <c r="B54" s="233" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="225" t="s">
+      <c r="C54" s="233" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="232"/>
-      <c r="E54" s="232"/>
-      <c r="F54" s="232"/>
-      <c r="G54" s="232"/>
+      <c r="D54" s="240"/>
+      <c r="E54" s="240"/>
+      <c r="F54" s="240"/>
+      <c r="G54" s="240"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="224" t="s">
+      <c r="A55" s="232" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="232"/>
-      <c r="C55" s="232"/>
-      <c r="D55" s="225" t="s">
+      <c r="B55" s="240"/>
+      <c r="C55" s="240"/>
+      <c r="D55" s="233" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="224" t="s">
+      <c r="A56" s="232" t="s">
         <v>128</v>
       </c>
       <c r="B56" s="78" t="s">
         <v>129</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="225" t="s">
+      <c r="D56" s="233" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="224" t="s">
+      <c r="A57" s="232" t="s">
         <v>131</v>
       </c>
       <c r="B57" s="78" t="s">
@@ -5687,76 +5777,76 @@
       <c r="C57" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="225" t="s">
+      <c r="D57" s="233" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="224" t="s">
+      <c r="A58" s="232" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="225" t="s">
+      <c r="B58" s="233" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="232"/>
-      <c r="D58" s="232"/>
-      <c r="E58" s="232"/>
-      <c r="F58" s="232"/>
-      <c r="G58" s="232"/>
+      <c r="C58" s="240"/>
+      <c r="D58" s="240"/>
+      <c r="E58" s="240"/>
+      <c r="F58" s="240"/>
+      <c r="G58" s="240"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="224" t="s">
+      <c r="A59" s="232" t="s">
         <v>137</v>
       </c>
-      <c r="B59" s="232"/>
-      <c r="C59" s="225" t="s">
+      <c r="B59" s="240"/>
+      <c r="C59" s="233" t="s">
         <v>138</v>
       </c>
-      <c r="D59" s="232"/>
-      <c r="E59" s="232"/>
-      <c r="F59" s="232"/>
-      <c r="G59" s="232"/>
+      <c r="D59" s="240"/>
+      <c r="E59" s="240"/>
+      <c r="F59" s="240"/>
+      <c r="G59" s="240"/>
     </row>
     <row r="60" ht="65" spans="1:7">
-      <c r="A60" s="224" t="s">
+      <c r="A60" s="232" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="232" t="s">
+      <c r="B60" s="240" t="s">
         <v>140</v>
       </c>
-      <c r="C60" s="232"/>
-      <c r="D60" s="225" t="s">
+      <c r="C60" s="240"/>
+      <c r="D60" s="233" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="224" t="s">
+      <c r="A61" s="232" t="s">
         <v>142</v>
       </c>
       <c r="B61" s="78" t="s">
         <v>143</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="232"/>
-      <c r="E61" s="232"/>
-      <c r="F61" s="232"/>
-      <c r="G61" s="232"/>
+      <c r="D61" s="240"/>
+      <c r="E61" s="240"/>
+      <c r="F61" s="240"/>
+      <c r="G61" s="240"/>
     </row>
     <row r="62" ht="52" spans="1:7">
-      <c r="A62" s="224" t="s">
+      <c r="A62" s="232" t="s">
         <v>144</v>
       </c>
-      <c r="B62" s="232"/>
-      <c r="C62" s="232"/>
-      <c r="D62" s="225" t="s">
+      <c r="B62" s="240"/>
+      <c r="C62" s="240"/>
+      <c r="D62" s="233" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="225" t="s">
+      <c r="E62" s="233" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="224" t="s">
+      <c r="A63" s="232" t="s">
         <v>147</v>
       </c>
       <c r="B63" s="78" t="s">
@@ -5765,66 +5855,66 @@
       <c r="C63" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="232"/>
-      <c r="E63" s="232"/>
-      <c r="F63" s="232"/>
-      <c r="G63" s="232"/>
+      <c r="D63" s="240"/>
+      <c r="E63" s="240"/>
+      <c r="F63" s="240"/>
+      <c r="G63" s="240"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="224" t="s">
+      <c r="A64" s="232" t="s">
         <v>150</v>
       </c>
-      <c r="B64" s="232"/>
-      <c r="C64" s="232"/>
-      <c r="D64" s="225" t="s">
+      <c r="B64" s="240"/>
+      <c r="C64" s="240"/>
+      <c r="D64" s="233" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="224" t="s">
+      <c r="A65" s="232" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="233" t="s">
+      <c r="B65" s="241" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="232"/>
-      <c r="D65" s="232"/>
-      <c r="E65" s="232"/>
-      <c r="F65" s="232"/>
-      <c r="G65" s="232"/>
+      <c r="C65" s="240"/>
+      <c r="D65" s="240"/>
+      <c r="E65" s="240"/>
+      <c r="F65" s="240"/>
+      <c r="G65" s="240"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="224" t="s">
+      <c r="A66" s="232" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="232"/>
-      <c r="C66" s="225" t="s">
+      <c r="B66" s="240"/>
+      <c r="C66" s="233" t="s">
         <v>155</v>
       </c>
-      <c r="D66" s="232"/>
-      <c r="E66" s="232"/>
-      <c r="F66" s="232"/>
-      <c r="G66" s="232"/>
+      <c r="D66" s="240"/>
+      <c r="E66" s="240"/>
+      <c r="F66" s="240"/>
+      <c r="G66" s="240"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="224" t="s">
+      <c r="A67" s="232" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="232"/>
-      <c r="C67" s="232"/>
+      <c r="B67" s="240"/>
+      <c r="C67" s="240"/>
     </row>
     <row r="68" ht="78" spans="1:7">
-      <c r="A68" s="224" t="s">
+      <c r="A68" s="232" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="232"/>
-      <c r="C68" s="232"/>
-      <c r="D68" s="225" t="s">
+      <c r="B68" s="240"/>
+      <c r="C68" s="240"/>
+      <c r="D68" s="233" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="224" t="s">
+      <c r="A69" s="232" t="s">
         <v>159</v>
       </c>
       <c r="B69" s="78" t="s">
@@ -5833,89 +5923,89 @@
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="224" t="s">
+      <c r="A70" s="232" t="s">
         <v>161</v>
       </c>
       <c r="B70" s="78" t="s">
         <v>162</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="232"/>
-      <c r="E70" s="232"/>
-      <c r="F70" s="232"/>
-      <c r="G70" s="232"/>
+      <c r="D70" s="240"/>
+      <c r="E70" s="240"/>
+      <c r="F70" s="240"/>
+      <c r="G70" s="240"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="224" t="s">
+      <c r="A71" s="232" t="s">
         <v>163</v>
       </c>
-      <c r="B71" s="232"/>
-      <c r="C71" s="232"/>
+      <c r="B71" s="240"/>
+      <c r="C71" s="240"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="224" t="s">
+      <c r="A72" s="232" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="225" t="s">
+      <c r="B72" s="233" t="s">
         <v>165</v>
       </c>
-      <c r="C72" s="225" t="s">
+      <c r="C72" s="233" t="s">
         <v>166</v>
       </c>
-      <c r="D72" s="232"/>
-      <c r="E72" s="232"/>
-      <c r="F72" s="232"/>
-      <c r="G72" s="232"/>
+      <c r="D72" s="240"/>
+      <c r="E72" s="240"/>
+      <c r="F72" s="240"/>
+      <c r="G72" s="240"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="224" t="s">
+      <c r="A73" s="232" t="s">
         <v>167</v>
       </c>
-      <c r="B73" s="232"/>
-      <c r="C73" s="225" t="s">
+      <c r="B73" s="240"/>
+      <c r="C73" s="233" t="s">
         <v>168</v>
       </c>
-      <c r="D73" s="232"/>
-      <c r="E73" s="232"/>
-      <c r="F73" s="232"/>
-      <c r="G73" s="232"/>
+      <c r="D73" s="240"/>
+      <c r="E73" s="240"/>
+      <c r="F73" s="240"/>
+      <c r="G73" s="240"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="224" t="s">
+      <c r="A74" s="232" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="224" t="s">
+      <c r="A75" s="232" t="s">
         <v>170</v>
       </c>
-      <c r="D75" s="232"/>
-      <c r="E75" s="232"/>
-      <c r="F75" s="232"/>
-      <c r="G75" s="232"/>
+      <c r="D75" s="240"/>
+      <c r="E75" s="240"/>
+      <c r="F75" s="240"/>
+      <c r="G75" s="240"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="224" t="s">
+      <c r="A76" s="232" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="232"/>
-      <c r="C76" s="232"/>
-      <c r="D76" s="225" t="s">
+      <c r="B76" s="240"/>
+      <c r="C76" s="240"/>
+      <c r="D76" s="233" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="224" t="s">
+      <c r="A77" s="232" t="s">
         <v>173</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="234" t="s">
+      <c r="A78" s="242" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="225" t="s">
+      <c r="B78" s="233" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5969,16 +6059,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5992,7 +6082,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6006,7 +6096,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6020,7 +6110,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6048,7 +6138,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6062,7 +6152,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6076,7 +6166,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6090,7 +6180,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6104,7 +6194,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6130,7 +6220,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6144,7 +6234,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6158,7 +6248,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6184,7 +6274,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6198,7 +6288,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6236,7 +6326,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6250,7 +6340,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6276,7 +6366,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6290,7 +6380,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6304,7 +6394,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6318,7 +6408,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6332,7 +6422,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6346,7 +6436,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6372,7 +6462,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6386,7 +6476,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6400,7 +6490,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6426,7 +6516,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6452,7 +6542,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6466,7 +6556,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6480,10 +6570,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="E38" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6497,7 +6587,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6511,7 +6601,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6525,10 +6615,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="E41" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6554,7 +6644,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6580,7 +6670,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6606,10 +6696,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="E47" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6623,7 +6713,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6649,7 +6739,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6675,7 +6765,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -6708,34 +6798,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>247</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6743,10 +6833,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6754,10 +6844,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6765,10 +6855,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6776,23 +6866,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6800,10 +6890,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>527</v>
+        <v>535</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6811,10 +6901,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6822,10 +6912,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>530</v>
+        <v>538</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6833,10 +6923,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>533</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6844,50 +6934,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>539</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>541</v>
+        <v>549</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6896,24 +6986,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>544</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>545</v>
+        <v>553</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>546</v>
+        <v>554</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>547</v>
+        <v>555</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -6921,17 +7011,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -6940,61 +7030,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>552</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>554</v>
+        <v>562</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -7002,10 +7092,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>561</v>
+        <v>569</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7013,10 +7103,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7024,27 +7114,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>565</v>
+        <v>573</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7052,10 +7142,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7063,10 +7153,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7074,53 +7164,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7131,42 +7221,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7174,64 +7264,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>591</v>
+        <v>599</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>592</v>
+        <v>600</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7241,16 +7331,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>593</v>
+        <v>601</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>594</v>
+        <v>602</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7259,7 +7349,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>595</v>
+        <v>603</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7268,42 +7358,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7313,10 +7403,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7324,10 +7414,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7339,18 +7429,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>601</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -7458,7 +7548,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7472,7 +7562,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>603</v>
+        <v>611</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7496,7 +7586,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>604</v>
+        <v>612</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7509,7 +7599,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7522,7 +7612,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>606</v>
+        <v>614</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7556,7 +7646,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7602,7 +7692,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7638,7 +7728,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7672,10 +7762,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7687,10 +7777,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7713,7 +7803,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7726,10 +7816,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7763,10 +7853,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7778,10 +7868,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7805,7 +7895,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7872,7 +7962,7 @@
         <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7886,7 +7976,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7898,7 +7988,7 @@
         <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -7912,7 +8002,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -7924,10 +8014,10 @@
         <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -7940,7 +8030,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -7963,7 +8053,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -7987,7 +8077,7 @@
         <v>104</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -8023,7 +8113,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8047,7 +8137,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8070,10 +8160,10 @@
         <v>117</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8109,27 +8199,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8137,13 +8227,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8151,13 +8241,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8165,13 +8255,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8179,13 +8269,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8193,13 +8283,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8207,13 +8297,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8221,7 +8311,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8229,7 +8319,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8237,7 +8327,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8245,7 +8335,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8265,14 +8355,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="218" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="226" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="219"/>
+    <col min="8" max="16384" width="8.72727272727273" style="227"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="220"/>
+      <c r="A1" s="228"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8292,8 +8382,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="217" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="221" t="s">
+    <row r="2" s="225" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="229" t="s">
         <v>176</v>
       </c>
       <c r="B2" s="78"/>
@@ -8306,7 +8396,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="222" t="s">
+      <c r="A3" s="230" t="s">
         <v>178</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8314,7 +8404,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="222" t="s">
+      <c r="A4" s="230" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8325,7 +8415,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="222" t="s">
+      <c r="A5" s="230" t="s">
         <v>183</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8336,7 +8426,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="222" t="s">
+      <c r="A6" s="230" t="s">
         <v>186</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8347,7 +8437,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="222" t="s">
+      <c r="A7" s="230" t="s">
         <v>189</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8355,127 +8445,127 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="222"/>
+      <c r="A8" s="230"/>
       <c r="D8" s="66" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="222"/>
+      <c r="A9" s="230"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="222"/>
+      <c r="A10" s="230"/>
       <c r="B10" s="66" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="222"/>
+      <c r="A11" s="230"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="222"/>
+      <c r="A12" s="230"/>
       <c r="B12" s="66" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="222"/>
+      <c r="A13" s="230"/>
       <c r="B13" s="66" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="222"/>
+      <c r="A14" s="230"/>
       <c r="B14" s="66" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="222"/>
+      <c r="A15" s="230"/>
       <c r="B15" s="66" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="222"/>
+      <c r="A16" s="230"/>
       <c r="B16" s="66" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="222"/>
+      <c r="A17" s="230"/>
       <c r="B17" s="66" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="222"/>
+      <c r="A18" s="230"/>
       <c r="B18" s="66" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:2">
-      <c r="A19" s="222"/>
+      <c r="A19" s="230"/>
       <c r="B19" s="78" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="222"/>
+      <c r="A20" s="230"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="222"/>
+      <c r="A21" s="230"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="222"/>
+      <c r="A22" s="230"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="222"/>
+      <c r="A23" s="230"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="222"/>
+      <c r="A24" s="230"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="222"/>
+      <c r="A25" s="230"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="222"/>
+      <c r="A26" s="230"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="222"/>
+      <c r="A27" s="230"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="222"/>
+      <c r="A28" s="230"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="222"/>
+      <c r="A29" s="230"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="222"/>
+      <c r="A30" s="230"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="222"/>
+      <c r="A31" s="230"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="222"/>
+      <c r="A32" s="230"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="222"/>
+      <c r="A33" s="230"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="222"/>
+      <c r="A34" s="230"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="222"/>
+      <c r="A35" s="230"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="222"/>
+      <c r="A36" s="230"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="222"/>
+      <c r="A37" s="230"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="222"/>
+      <c r="A38" s="230"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8484,7 +8574,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="222"/>
+      <c r="A39" s="230"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8493,40 +8583,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="222"/>
+      <c r="A40" s="230"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="222"/>
+      <c r="A41" s="230"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="222"/>
+      <c r="A42" s="230"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="222"/>
+      <c r="A43" s="230"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="222"/>
+      <c r="A44" s="230"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="222"/>
+      <c r="A45" s="230"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="222"/>
+      <c r="A46" s="230"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="222"/>
+      <c r="A47" s="230"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="222"/>
+      <c r="A48" s="230"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="222"/>
+      <c r="A49" s="230"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="222"/>
+      <c r="A50" s="230"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="222"/>
+      <c r="A51" s="230"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8539,503 +8629,514 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="208" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="208" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="208" customWidth="1"/>
+    <col min="1" max="1" width="24" style="216" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="216" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="216" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="207" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="209" t="s">
+    <row r="1" s="215" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="217" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="209" t="s">
+      <c r="B1" s="217" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="209" t="s">
+      <c r="C1" s="217" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="218" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="210" t="s">
+      <c r="B2" s="218" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="218" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="210" t="s">
+      <c r="A3" s="218" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="210" t="s">
+      <c r="B3" s="218" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="210" t="s">
+      <c r="C3" s="218" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="210" t="s">
+      <c r="A4" s="218" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="210" t="s">
+      <c r="B4" s="218" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="210" t="s">
+      <c r="C4" s="218" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="211" t="s">
+      <c r="A5" s="219" t="s">
         <v>212</v>
       </c>
-      <c r="B5" s="210" t="s">
+      <c r="B5" s="218" t="s">
         <v>213</v>
       </c>
-      <c r="C5" s="210" t="s">
+      <c r="C5" s="218" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="212"/>
-      <c r="B6" s="210" t="s">
+      <c r="A6" s="220"/>
+      <c r="B6" s="218" t="s">
         <v>215</v>
       </c>
-      <c r="C6" s="210" t="s">
+      <c r="C6" s="218" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="213" t="s">
+      <c r="A7" s="221" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="210" t="s">
+      <c r="B7" s="218" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="210" t="s">
+      <c r="C7" s="218" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
-      <c r="A8" s="213"/>
-      <c r="B8" s="210" t="s">
+      <c r="A8" s="221"/>
+      <c r="B8" s="218" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="210" t="s">
+      <c r="C8" s="218" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="213"/>
-      <c r="B9" s="210" t="s">
+      <c r="A9" s="221"/>
+      <c r="B9" s="218" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="210" t="s">
+      <c r="C9" s="218" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="213"/>
-      <c r="B10" s="210" t="s">
+      <c r="A10" s="221"/>
+      <c r="B10" s="218" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="210" t="s">
+      <c r="C10" s="218" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="213"/>
-      <c r="B11" s="210"/>
-      <c r="C11" s="210"/>
+      <c r="A11" s="221"/>
+      <c r="B11" s="218"/>
+      <c r="C11" s="218"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="213"/>
-      <c r="B12" s="210"/>
-      <c r="C12" s="210"/>
+      <c r="A12" s="221"/>
+      <c r="B12" s="218"/>
+      <c r="C12" s="218"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="213"/>
-      <c r="B13" s="210"/>
-      <c r="C13" s="210"/>
+      <c r="A13" s="221"/>
+      <c r="B13" s="218"/>
+      <c r="C13" s="218"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="214"/>
-      <c r="B14" s="210"/>
-      <c r="C14" s="210"/>
+      <c r="A14" s="222"/>
+      <c r="B14" s="218"/>
+      <c r="C14" s="218"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="210" t="s">
+      <c r="A15" s="218" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="210" t="s">
+      <c r="B15" s="218" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="210" t="s">
+      <c r="C15" s="218" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="210" t="s">
+      <c r="A16" s="218" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="210" t="s">
+      <c r="B16" s="218" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="210" t="s">
+      <c r="C16" s="218" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="210" t="s">
+      <c r="A17" s="218" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="210" t="s">
+      <c r="B17" s="218" t="s">
         <v>232</v>
       </c>
-      <c r="C17" s="215">
+      <c r="C17" s="223">
         <v>0.440972222222222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="216" t="s">
+      <c r="A18" s="224" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="210" t="s">
+      <c r="B18" s="218" t="s">
         <v>233</v>
       </c>
-      <c r="C18" s="210" t="s">
+      <c r="C18" s="218" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="213"/>
-      <c r="B19" s="210" t="s">
+      <c r="A19" s="221"/>
+      <c r="B19" s="218" t="s">
         <v>235</v>
       </c>
-      <c r="C19" s="210" t="s">
+      <c r="C19" s="218" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="20" ht="56" spans="1:3">
-      <c r="A20" s="213"/>
-      <c r="B20" s="210" t="s">
+      <c r="A20" s="221"/>
+      <c r="B20" s="218" t="s">
         <v>237</v>
       </c>
-      <c r="C20" s="210" t="s">
+      <c r="C20" s="218" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="213"/>
-      <c r="B21" s="210" t="s">
+      <c r="A21" s="221"/>
+      <c r="B21" s="218" t="s">
         <v>239</v>
       </c>
-      <c r="C21" s="210" t="s">
+      <c r="C21" s="218" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:3">
-      <c r="A22" s="213"/>
-      <c r="B22" s="210" t="s">
+      <c r="A22" s="221"/>
+      <c r="B22" s="218" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="210" t="s">
+      <c r="C22" s="218" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="213"/>
-      <c r="B23" s="210"/>
-      <c r="C23" s="210"/>
+      <c r="A23" s="221"/>
+      <c r="B23" s="218"/>
+      <c r="C23" s="218"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="213"/>
-      <c r="B24" s="210"/>
-      <c r="C24" s="210"/>
+      <c r="A24" s="221"/>
+      <c r="B24" s="218"/>
+      <c r="C24" s="218"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="213"/>
-      <c r="B25" s="210"/>
-      <c r="C25" s="210"/>
+      <c r="A25" s="221"/>
+      <c r="B25" s="218"/>
+      <c r="C25" s="218"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="211" t="s">
+      <c r="A26" s="219" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="210" t="s">
+      <c r="B26" s="218" t="s">
         <v>235</v>
       </c>
-      <c r="C26" s="210" t="s">
+      <c r="C26" s="218" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="212"/>
-      <c r="B27" s="210" t="s">
+      <c r="A27" s="220"/>
+      <c r="B27" s="218" t="s">
         <v>245</v>
       </c>
-      <c r="C27" s="210" t="s">
+      <c r="C27" s="218" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:3">
-      <c r="A28" s="216" t="s">
+      <c r="A28" s="224" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="210" t="s">
+      <c r="B28" s="218" t="s">
         <v>248</v>
       </c>
-      <c r="C28" s="210" t="s">
+      <c r="C28" s="218" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="213"/>
-      <c r="B29" s="210" t="s">
+      <c r="A29" s="221"/>
+      <c r="B29" s="218" t="s">
         <v>219</v>
       </c>
-      <c r="C29" s="210" t="s">
+      <c r="C29" s="218" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="213"/>
-      <c r="B30" s="210" t="s">
+      <c r="A30" s="221"/>
+      <c r="B30" s="218" t="s">
         <v>251</v>
       </c>
-      <c r="C30" s="210" t="s">
+      <c r="C30" s="218" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="213"/>
-      <c r="B31" s="210"/>
-      <c r="C31" s="210"/>
+      <c r="A31" s="221"/>
+      <c r="B31" s="218"/>
+      <c r="C31" s="218"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="211" t="s">
+      <c r="A32" s="219" t="s">
         <v>253</v>
       </c>
-      <c r="B32" s="210" t="s">
+      <c r="B32" s="218" t="s">
         <v>254</v>
       </c>
-      <c r="C32" s="210" t="s">
+      <c r="C32" s="218" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="212"/>
-      <c r="B33" s="210" t="s">
+      <c r="A33" s="220"/>
+      <c r="B33" s="218" t="s">
         <v>217</v>
       </c>
-      <c r="C33" s="210" t="s">
+      <c r="C33" s="218" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:3">
-      <c r="A34" s="216" t="s">
+      <c r="A34" s="224" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="210" t="s">
+      <c r="B34" s="218" t="s">
         <v>217</v>
       </c>
-      <c r="C34" s="210" t="s">
+      <c r="C34" s="218" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="213"/>
-      <c r="B35" s="208" t="s">
+      <c r="A35" s="221"/>
+      <c r="B35" s="216" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="208" t="s">
+      <c r="C35" s="216" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="213"/>
-      <c r="B36" s="208" t="s">
+      <c r="A36" s="221"/>
+      <c r="B36" s="216" t="s">
         <v>239</v>
       </c>
-      <c r="C36" s="208" t="s">
+      <c r="C36" s="216" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="37" ht="98" spans="1:3">
-      <c r="A37" s="216" t="s">
+      <c r="A37" s="224" t="s">
         <v>261</v>
       </c>
-      <c r="B37" s="208" t="s">
+      <c r="B37" s="216" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="208" t="s">
+      <c r="C37" s="216" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="38" ht="84" spans="1:3">
-      <c r="A38" s="213"/>
-      <c r="B38" s="208" t="s">
+      <c r="A38" s="221"/>
+      <c r="B38" s="216" t="s">
         <v>263</v>
       </c>
-      <c r="C38" s="208" t="s">
+      <c r="C38" s="216" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="39" ht="28" spans="1:3">
-      <c r="A39" s="214"/>
-      <c r="B39" s="208" t="s">
+      <c r="A39" s="222"/>
+      <c r="B39" s="216" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="208" t="s">
+      <c r="C39" s="216" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="208" t="s">
+      <c r="A40" s="216" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="208" t="s">
+      <c r="B40" s="216" t="s">
         <v>267</v>
       </c>
-      <c r="C40" s="208" t="s">
+      <c r="C40" s="216" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="216" t="s">
+      <c r="A41" s="224" t="s">
         <v>269</v>
       </c>
-      <c r="B41" s="208" t="s">
+      <c r="B41" s="216" t="s">
         <v>219</v>
       </c>
-      <c r="C41" s="208" t="s">
+      <c r="C41" s="216" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="214"/>
-      <c r="B42" s="208" t="s">
+      <c r="A42" s="222"/>
+      <c r="B42" s="216" t="s">
         <v>263</v>
       </c>
-      <c r="C42" s="208" t="s">
+      <c r="C42" s="216" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="208" t="s">
+      <c r="A43" s="216" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="208" t="s">
+      <c r="B43" s="216" t="s">
         <v>221</v>
       </c>
-      <c r="C43" s="208" t="s">
+      <c r="C43" s="216" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="208" t="s">
+      <c r="A44" s="216" t="s">
         <v>273</v>
       </c>
-      <c r="B44" s="208" t="s">
+      <c r="B44" s="216" t="s">
         <v>274</v>
       </c>
-      <c r="C44" s="208" t="s">
+      <c r="C44" s="216" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="208" t="s">
+      <c r="A45" s="216" t="s">
         <v>276</v>
       </c>
-      <c r="B45" s="208" t="s">
+      <c r="B45" s="216" t="s">
         <v>277</v>
       </c>
-      <c r="C45" s="208" t="s">
+      <c r="C45" s="216" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="208" t="s">
+      <c r="A46" s="216" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="208" t="s">
+      <c r="B46" s="216" t="s">
         <v>263</v>
       </c>
-      <c r="C46" s="208" t="s">
+      <c r="C46" s="216" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="208" t="s">
+      <c r="A47" s="216" t="s">
         <v>280</v>
       </c>
-      <c r="B47" s="208" t="s">
+      <c r="B47" s="216" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="208" t="s">
+      <c r="C47" s="216" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="208" t="s">
+      <c r="A48" s="216" t="s">
         <v>283</v>
       </c>
-      <c r="B48" s="208" t="s">
+      <c r="B48" s="216" t="s">
         <v>284</v>
       </c>
-      <c r="C48" s="208" t="s">
+      <c r="C48" s="216" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="208" t="s">
+      <c r="A49" s="216" t="s">
         <v>286</v>
       </c>
-      <c r="B49" s="208" t="s">
+      <c r="B49" s="216" t="s">
         <v>284</v>
       </c>
-      <c r="C49" s="208" t="s">
+      <c r="C49" s="216" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="208" t="s">
+      <c r="A50" s="216" t="s">
         <v>288</v>
       </c>
-      <c r="B50" s="208" t="s">
+      <c r="B50" s="216" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="208" t="s">
+      <c r="C50" s="216" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="51" ht="28" spans="1:3">
-      <c r="A51" s="208" t="s">
+      <c r="A51" s="216" t="s">
         <v>290</v>
       </c>
-      <c r="B51" s="208" t="s">
+      <c r="B51" s="216" t="s">
         <v>265</v>
       </c>
-      <c r="C51" s="208" t="s">
+      <c r="C51" s="216" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:3">
-      <c r="A52" s="208" t="s">
+      <c r="A52" s="216" t="s">
         <v>292</v>
       </c>
-      <c r="B52" s="208" t="s">
+      <c r="B52" s="216" t="s">
         <v>265</v>
       </c>
-      <c r="C52" s="208" t="s">
+      <c r="C52" s="216" t="s">
         <v>293</v>
+      </c>
+    </row>
+    <row r="53" ht="140" spans="1:3">
+      <c r="A53" s="216" t="s">
+        <v>294</v>
+      </c>
+      <c r="B53" s="216" t="s">
+        <v>295</v>
+      </c>
+      <c r="C53" s="216" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -9067,45 +9168,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="196"/>
+    <col min="5" max="5" width="8.72727272727273" style="204"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="194" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="197" t="s">
-        <v>294</v>
-      </c>
-      <c r="B1" s="198"/>
-      <c r="C1" s="198"/>
-      <c r="D1" s="199"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="194" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="2" s="195" customFormat="1" spans="1:7">
-      <c r="A2" s="201" t="s">
+    <row r="1" s="202" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="205" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="202" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" s="203" customFormat="1" spans="1:7">
+      <c r="A2" s="209" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="202"/>
-      <c r="C2" s="195" t="s">
-        <v>296</v>
-      </c>
-      <c r="D2" s="195" t="s">
-        <v>297</v>
+      <c r="B2" s="210"/>
+      <c r="C2" s="203" t="s">
+        <v>299</v>
+      </c>
+      <c r="D2" s="203" t="s">
+        <v>300</v>
       </c>
       <c r="E2" s="142"/>
-      <c r="F2" s="195" t="s">
+      <c r="F2" s="203" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="195" t="s">
-        <v>298</v>
+      <c r="G2" s="203" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="203">
+      <c r="A3" s="211">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -9116,14 +9217,14 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="204"/>
+      <c r="A4" s="212"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -9132,14 +9233,14 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="204"/>
+      <c r="A5" s="212"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -9148,14 +9249,14 @@
       </c>
       <c r="D5" s="119"/>
       <c r="F5" s="119" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G5" s="119" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="204"/>
+      <c r="A6" s="212"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9163,15 +9264,15 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="205" t="s">
-        <v>305</v>
+      <c r="F6" s="213" t="s">
+        <v>308</v>
       </c>
       <c r="G6" s="119" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="204"/>
+      <c r="A7" s="212"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9179,13 +9280,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="206"/>
+      <c r="F7" s="214"/>
       <c r="G7" s="119" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="204"/>
+      <c r="A8" s="212"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9193,11 +9294,15 @@
         <v>135</v>
       </c>
       <c r="D8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
+      <c r="F8" s="119" t="s">
+        <v>311</v>
+      </c>
+      <c r="G8" s="119" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="206"/>
+      <c r="A9" s="214"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9209,7 +9314,7 @@
       <c r="G9" s="119"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="205">
+      <c r="A10" s="213">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9223,7 +9328,7 @@
       <c r="G10" s="119"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="204"/>
+      <c r="A11" s="212"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9235,7 +9340,7 @@
       <c r="G11" s="119"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="206"/>
+      <c r="A12" s="214"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9247,7 +9352,7 @@
       <c r="G12" s="119"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="205">
+      <c r="A13" s="213">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9263,7 +9368,7 @@
       <c r="G13" s="119"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="206"/>
+      <c r="A14" s="214"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -9297,272 +9402,272 @@
     <tabColor theme="5" tint="0.8"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BJ53"/>
+  <dimension ref="A1:BJ55"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="4.07272727272727" customWidth="1"/>
+    <col min="1" max="1" width="4.96363636363636" customWidth="1"/>
     <col min="2" max="55" width="3.23636363636364" customWidth="1"/>
-    <col min="56" max="58" width="4.81818181818182" style="175" customWidth="1"/>
-    <col min="59" max="59" width="7.18181818181818" style="175" customWidth="1"/>
-    <col min="60" max="62" width="4.81818181818182" style="175" customWidth="1"/>
+    <col min="56" max="58" width="5.44545454545455" style="176" customWidth="1"/>
+    <col min="59" max="59" width="7.18181818181818" style="176" customWidth="1"/>
+    <col min="60" max="62" width="5.44545454545455" style="176" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:62">
-      <c r="A1" s="176" t="s">
-        <v>308</v>
-      </c>
-      <c r="B1" s="177" t="s">
-        <v>309</v>
-      </c>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
-      <c r="H1" s="178"/>
-      <c r="I1" s="178"/>
-      <c r="J1" s="178"/>
-      <c r="K1" s="178"/>
-      <c r="L1" s="178"/>
-      <c r="M1" s="178"/>
-      <c r="N1" s="178"/>
-      <c r="O1" s="178"/>
-      <c r="P1" s="178"/>
-      <c r="Q1" s="178"/>
-      <c r="R1" s="178"/>
-      <c r="S1" s="178"/>
-      <c r="T1" s="179" t="s">
-        <v>310</v>
-      </c>
-      <c r="U1" s="180"/>
-      <c r="V1" s="180"/>
-      <c r="W1" s="180"/>
-      <c r="X1" s="180"/>
-      <c r="Y1" s="180"/>
-      <c r="Z1" s="180"/>
-      <c r="AA1" s="180"/>
-      <c r="AB1" s="180"/>
-      <c r="AC1" s="180"/>
-      <c r="AD1" s="180"/>
-      <c r="AE1" s="180"/>
-      <c r="AF1" s="180"/>
-      <c r="AG1" s="180"/>
-      <c r="AH1" s="180"/>
-      <c r="AI1" s="180"/>
-      <c r="AJ1" s="179" t="s">
-        <v>311</v>
-      </c>
-      <c r="AK1" s="180"/>
-      <c r="AL1" s="180"/>
-      <c r="AM1" s="179" t="s">
-        <v>312</v>
-      </c>
-      <c r="AN1" s="180"/>
-      <c r="AO1" s="180"/>
-      <c r="AP1" s="180"/>
-      <c r="AQ1" s="180"/>
-      <c r="AR1" s="180"/>
-      <c r="AS1" s="180"/>
-      <c r="AT1" s="180"/>
-      <c r="AU1" s="180"/>
-      <c r="AV1" s="180"/>
-      <c r="AW1" s="180"/>
-      <c r="AX1" s="180"/>
-      <c r="AY1" s="180"/>
-      <c r="AZ1" s="180"/>
-      <c r="BA1" s="180"/>
-      <c r="BB1" s="180"/>
-      <c r="BC1" s="181"/>
-      <c r="BD1" s="182" t="s">
+      <c r="A1" s="177" t="s">
         <v>313</v>
       </c>
-      <c r="BE1" s="183"/>
-      <c r="BF1" s="183"/>
-      <c r="BG1" s="183"/>
-      <c r="BH1" s="183"/>
-      <c r="BI1" s="183"/>
-      <c r="BJ1" s="184"/>
+      <c r="B1" s="178" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="179"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="179"/>
+      <c r="I1" s="179"/>
+      <c r="J1" s="179"/>
+      <c r="K1" s="179"/>
+      <c r="L1" s="179"/>
+      <c r="M1" s="179"/>
+      <c r="N1" s="179"/>
+      <c r="O1" s="179"/>
+      <c r="P1" s="179"/>
+      <c r="Q1" s="179"/>
+      <c r="R1" s="179"/>
+      <c r="S1" s="179"/>
+      <c r="T1" s="180" t="s">
+        <v>315</v>
+      </c>
+      <c r="U1" s="181"/>
+      <c r="V1" s="181"/>
+      <c r="W1" s="181"/>
+      <c r="X1" s="181"/>
+      <c r="Y1" s="181"/>
+      <c r="Z1" s="181"/>
+      <c r="AA1" s="181"/>
+      <c r="AB1" s="181"/>
+      <c r="AC1" s="181"/>
+      <c r="AD1" s="181"/>
+      <c r="AE1" s="181"/>
+      <c r="AF1" s="181"/>
+      <c r="AG1" s="181"/>
+      <c r="AH1" s="181"/>
+      <c r="AI1" s="181"/>
+      <c r="AJ1" s="180" t="s">
+        <v>316</v>
+      </c>
+      <c r="AK1" s="181"/>
+      <c r="AL1" s="181"/>
+      <c r="AM1" s="180" t="s">
+        <v>317</v>
+      </c>
+      <c r="AN1" s="181"/>
+      <c r="AO1" s="181"/>
+      <c r="AP1" s="181"/>
+      <c r="AQ1" s="181"/>
+      <c r="AR1" s="181"/>
+      <c r="AS1" s="181"/>
+      <c r="AT1" s="181"/>
+      <c r="AU1" s="181"/>
+      <c r="AV1" s="181"/>
+      <c r="AW1" s="181"/>
+      <c r="AX1" s="181"/>
+      <c r="AY1" s="181"/>
+      <c r="AZ1" s="181"/>
+      <c r="BA1" s="181"/>
+      <c r="BB1" s="181"/>
+      <c r="BC1" s="182"/>
+      <c r="BD1" s="183" t="s">
+        <v>318</v>
+      </c>
+      <c r="BE1" s="184"/>
+      <c r="BF1" s="184"/>
+      <c r="BG1" s="184"/>
+      <c r="BH1" s="184"/>
+      <c r="BI1" s="184"/>
+      <c r="BJ1" s="185"/>
     </row>
     <row r="2" s="174" customFormat="1" ht="28" spans="1:62">
-      <c r="A2" s="176"/>
-      <c r="B2" s="185">
+      <c r="A2" s="177"/>
+      <c r="B2" s="186">
         <v>5</v>
       </c>
-      <c r="C2" s="185">
+      <c r="C2" s="186">
         <v>6</v>
       </c>
-      <c r="D2" s="185">
+      <c r="D2" s="186">
         <v>9</v>
       </c>
-      <c r="E2" s="185">
+      <c r="E2" s="186">
         <v>10</v>
       </c>
-      <c r="F2" s="185">
+      <c r="F2" s="186">
         <v>11</v>
       </c>
-      <c r="G2" s="185">
+      <c r="G2" s="186">
         <v>12</v>
       </c>
-      <c r="H2" s="185">
+      <c r="H2" s="186">
         <v>15</v>
       </c>
-      <c r="I2" s="185">
+      <c r="I2" s="186">
         <v>16</v>
       </c>
-      <c r="J2" s="185">
+      <c r="J2" s="186">
         <v>17</v>
       </c>
-      <c r="K2" s="185">
+      <c r="K2" s="186">
         <v>18</v>
       </c>
-      <c r="L2" s="185">
+      <c r="L2" s="186">
         <v>19</v>
       </c>
-      <c r="M2" s="185">
+      <c r="M2" s="186">
         <v>22</v>
       </c>
-      <c r="N2" s="185">
+      <c r="N2" s="186">
         <v>23</v>
       </c>
-      <c r="O2" s="185">
+      <c r="O2" s="186">
         <v>25</v>
       </c>
-      <c r="P2" s="185">
+      <c r="P2" s="186">
         <v>26</v>
       </c>
-      <c r="Q2" s="185">
+      <c r="Q2" s="186">
         <v>29</v>
       </c>
-      <c r="R2" s="185">
+      <c r="R2" s="186">
         <v>30</v>
       </c>
-      <c r="S2" s="185">
+      <c r="S2" s="186">
         <v>31</v>
       </c>
-      <c r="T2" s="185">
+      <c r="T2" s="186">
         <v>4</v>
       </c>
-      <c r="U2" s="185">
+      <c r="U2" s="186">
         <v>5</v>
       </c>
-      <c r="V2" s="185">
+      <c r="V2" s="186">
         <v>6</v>
       </c>
-      <c r="W2" s="185">
+      <c r="W2" s="186">
         <v>7</v>
       </c>
-      <c r="X2" s="185">
+      <c r="X2" s="186">
         <v>8</v>
       </c>
-      <c r="Y2" s="185">
+      <c r="Y2" s="186">
         <v>11</v>
       </c>
-      <c r="Z2" s="185">
+      <c r="Z2" s="186">
         <v>12</v>
       </c>
-      <c r="AA2" s="185">
+      <c r="AA2" s="186">
         <v>13</v>
       </c>
-      <c r="AB2" s="185">
+      <c r="AB2" s="186">
         <v>14</v>
       </c>
-      <c r="AC2" s="185">
+      <c r="AC2" s="186">
         <v>15</v>
       </c>
-      <c r="AD2" s="185">
+      <c r="AD2" s="186">
         <v>16</v>
       </c>
-      <c r="AE2" s="185">
+      <c r="AE2" s="186">
         <v>19</v>
       </c>
-      <c r="AF2" s="185">
+      <c r="AF2" s="186">
         <v>20</v>
       </c>
-      <c r="AG2" s="185">
+      <c r="AG2" s="186">
         <v>21</v>
       </c>
-      <c r="AH2" s="185">
+      <c r="AH2" s="186">
         <v>22</v>
       </c>
-      <c r="AI2" s="185">
+      <c r="AI2" s="186">
         <v>23</v>
       </c>
-      <c r="AJ2" s="185">
+      <c r="AJ2" s="186">
         <v>26</v>
       </c>
-      <c r="AK2" s="185">
+      <c r="AK2" s="186">
         <v>27</v>
       </c>
-      <c r="AL2" s="185">
+      <c r="AL2" s="186">
         <v>28</v>
       </c>
-      <c r="AM2" s="185">
+      <c r="AM2" s="186">
         <v>2</v>
       </c>
-      <c r="AN2" s="185">
+      <c r="AN2" s="186">
         <v>3</v>
       </c>
-      <c r="AO2" s="185">
+      <c r="AO2" s="186">
         <v>4</v>
       </c>
-      <c r="AP2" s="185">
+      <c r="AP2" s="186">
         <v>5</v>
       </c>
-      <c r="AQ2" s="185">
+      <c r="AQ2" s="186">
         <v>6</v>
       </c>
-      <c r="AR2" s="185">
+      <c r="AR2" s="186">
         <v>9</v>
       </c>
-      <c r="AS2" s="185">
+      <c r="AS2" s="186">
         <v>10</v>
       </c>
-      <c r="AT2" s="185">
+      <c r="AT2" s="186">
         <v>11</v>
       </c>
-      <c r="AU2" s="185">
+      <c r="AU2" s="186">
         <v>12</v>
       </c>
-      <c r="AV2" s="185">
+      <c r="AV2" s="186">
         <v>13</v>
       </c>
-      <c r="AW2" s="185">
+      <c r="AW2" s="186">
         <v>16</v>
       </c>
-      <c r="AX2" s="185">
+      <c r="AX2" s="186">
         <v>17</v>
       </c>
-      <c r="AY2" s="185">
+      <c r="AY2" s="186">
         <v>18</v>
       </c>
-      <c r="AZ2" s="185">
+      <c r="AZ2" s="186">
         <v>19</v>
       </c>
-      <c r="BA2" s="185">
+      <c r="BA2" s="186">
         <v>20</v>
       </c>
-      <c r="BB2" s="185"/>
-      <c r="BC2" s="185"/>
-      <c r="BD2" s="186" t="s">
-        <v>314</v>
-      </c>
-      <c r="BE2" s="186" t="s">
-        <v>315</v>
-      </c>
-      <c r="BF2" s="186" t="s">
-        <v>316</v>
-      </c>
-      <c r="BG2" s="186" t="s">
-        <v>317</v>
-      </c>
-      <c r="BH2" s="187" t="s">
-        <v>318</v>
-      </c>
-      <c r="BI2" s="187" t="s">
+      <c r="BB2" s="186"/>
+      <c r="BC2" s="186"/>
+      <c r="BD2" s="187" t="s">
         <v>319</v>
       </c>
-      <c r="BJ2" s="187" t="s">
+      <c r="BE2" s="187" t="s">
         <v>320</v>
+      </c>
+      <c r="BF2" s="187" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG2" s="187" t="s">
+        <v>322</v>
+      </c>
+      <c r="BH2" s="188" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI2" s="188" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ2" s="188" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9625,31 +9730,31 @@
       <c r="BA3" s="120"/>
       <c r="BB3" s="120"/>
       <c r="BC3" s="120"/>
-      <c r="BD3" s="188">
+      <c r="BD3" s="189">
         <f t="shared" ref="BD3:BD53" si="0">SUM(B3:BC3)</f>
         <v>1</v>
       </c>
-      <c r="BE3" s="188" cm="1">
+      <c r="BE3" s="189" cm="1">
         <f t="array" ref="BE3">SUMPRODUCT(--(B3:BC3=INT(B3:BC3)),--(B3:BC3&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF3" s="188" cm="1">
+      <c r="BF3" s="189" cm="1">
         <f t="array" ref="BF3">MAX(FREQUENCY(IF((B3:BC3=INT(B3:BC3))*(B3:BC3&gt;0),COLUMN(B3:BC3)),IF((B3:BC3&lt;&gt;INT(B3:BC3))+(B3:BC3&lt;=0),COLUMN(B3:BC3))))</f>
         <v>1</v>
       </c>
-      <c r="BG3" s="189" cm="1">
+      <c r="BG3" s="190" cm="1">
         <f t="array" ref="BG3">SUMPRODUCT(--(B3:AI3=INT(B3:AI3)),--(B3:AI3&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH3" s="190">
+      <c r="BH3" s="191">
         <f t="shared" ref="BH3:BH53" si="1">RANK(BD3,BD$3:BD$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BI3" s="190">
+      <c r="BI3" s="191">
         <f t="shared" ref="BI3:BI53" si="2">RANK(BE3,BE$3:BE$53,0)</f>
         <v>34</v>
       </c>
-      <c r="BJ3" s="190">
+      <c r="BJ3" s="191">
         <f t="shared" ref="BJ3:BJ53" si="3">RANK(BF3,BF$3:BF$53,0)</f>
         <v>22</v>
       </c>
@@ -9736,7 +9841,9 @@
       <c r="AU4" s="120">
         <v>2</v>
       </c>
-      <c r="AV4" s="120"/>
+      <c r="AV4" s="120">
+        <v>1</v>
+      </c>
       <c r="AW4" s="120"/>
       <c r="AX4" s="120"/>
       <c r="AY4" s="120"/>
@@ -9744,33 +9851,33 @@
       <c r="BA4" s="120"/>
       <c r="BB4" s="120"/>
       <c r="BC4" s="120"/>
-      <c r="BD4" s="188">
+      <c r="BD4" s="189">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="BE4" s="188" cm="1">
+        <v>19</v>
+      </c>
+      <c r="BE4" s="189" cm="1">
         <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>16</v>
-      </c>
-      <c r="BF4" s="188" cm="1">
+        <v>17</v>
+      </c>
+      <c r="BF4" s="189" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
-        <v>4</v>
-      </c>
-      <c r="BG4" s="189" cm="1">
+        <v>5</v>
+      </c>
+      <c r="BG4" s="190" cm="1">
         <f t="array" ref="BG4">SUMPRODUCT(--(B4:AI4=INT(B4:AI4)),--(B4:AI4&gt;0))/34*100%</f>
         <v>0.323529411764706</v>
       </c>
-      <c r="BH4" s="190">
+      <c r="BH4" s="191">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="BI4" s="190">
+      <c r="BI4" s="191">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="BJ4" s="190">
+      <c r="BJ4" s="191">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:62">
@@ -9835,31 +9942,31 @@
       <c r="BA5" s="120"/>
       <c r="BB5" s="120"/>
       <c r="BC5" s="120"/>
-      <c r="BD5" s="188">
+      <c r="BD5" s="189">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE5" s="188" cm="1">
+      <c r="BE5" s="189" cm="1">
         <f t="array" ref="BE5">SUMPRODUCT(--(B5:BC5=INT(B5:BC5)),--(B5:BC5&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF5" s="188" cm="1">
+      <c r="BF5" s="189" cm="1">
         <f t="array" ref="BF5">MAX(FREQUENCY(IF((B5:BC5=INT(B5:BC5))*(B5:BC5&gt;0),COLUMN(B5:BC5)),IF((B5:BC5&lt;&gt;INT(B5:BC5))+(B5:BC5&lt;=0),COLUMN(B5:BC5))))</f>
         <v>1</v>
       </c>
-      <c r="BG5" s="189" cm="1">
+      <c r="BG5" s="190" cm="1">
         <f t="array" ref="BG5">SUMPRODUCT(--(B5:AI5=INT(B5:AI5)),--(B5:AI5&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH5" s="190">
+      <c r="BH5" s="191">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI5" s="190">
+      <c r="BI5" s="191">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ5" s="190">
+      <c r="BJ5" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -9936,31 +10043,31 @@
       <c r="BA6" s="120"/>
       <c r="BB6" s="120"/>
       <c r="BC6" s="120"/>
-      <c r="BD6" s="188">
+      <c r="BD6" s="189">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="BE6" s="188" cm="1">
+      <c r="BE6" s="189" cm="1">
         <f t="array" ref="BE6">SUMPRODUCT(--(B6:BC6=INT(B6:BC6)),--(B6:BC6&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF6" s="188" cm="1">
+      <c r="BF6" s="189" cm="1">
         <f t="array" ref="BF6">MAX(FREQUENCY(IF((B6:BC6=INT(B6:BC6))*(B6:BC6&gt;0),COLUMN(B6:BC6)),IF((B6:BC6&lt;&gt;INT(B6:BC6))+(B6:BC6&lt;=0),COLUMN(B6:BC6))))</f>
         <v>3</v>
       </c>
-      <c r="BG6" s="189" cm="1">
+      <c r="BG6" s="190" cm="1">
         <f t="array" ref="BG6">SUMPRODUCT(--(B6:AI6=INT(B6:AI6)),--(B6:AI6&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH6" s="190">
+      <c r="BH6" s="191">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="BI6" s="190">
+        <v>22</v>
+      </c>
+      <c r="BI6" s="191">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="BJ6" s="190">
+      <c r="BJ6" s="191">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -10029,31 +10136,31 @@
       <c r="BA7" s="120"/>
       <c r="BB7" s="120"/>
       <c r="BC7" s="120"/>
-      <c r="BD7" s="188">
+      <c r="BD7" s="189">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE7" s="188" cm="1">
+      <c r="BE7" s="189" cm="1">
         <f t="array" ref="BE7">SUMPRODUCT(--(B7:BC7=INT(B7:BC7)),--(B7:BC7&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF7" s="188" cm="1">
+      <c r="BF7" s="189" cm="1">
         <f t="array" ref="BF7">MAX(FREQUENCY(IF((B7:BC7=INT(B7:BC7))*(B7:BC7&gt;0),COLUMN(B7:BC7)),IF((B7:BC7&lt;&gt;INT(B7:BC7))+(B7:BC7&lt;=0),COLUMN(B7:BC7))))</f>
         <v>1</v>
       </c>
-      <c r="BG7" s="189" cm="1">
+      <c r="BG7" s="190" cm="1">
         <f t="array" ref="BG7">SUMPRODUCT(--(B7:AI7=INT(B7:AI7)),--(B7:AI7&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH7" s="190">
+      <c r="BH7" s="191">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="BI7" s="190">
+      <c r="BI7" s="191">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="BJ7" s="190">
+      <c r="BJ7" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10156,7 +10263,9 @@
       <c r="AU8" s="120">
         <v>1</v>
       </c>
-      <c r="AV8" s="120"/>
+      <c r="AV8" s="120">
+        <v>1</v>
+      </c>
       <c r="AW8" s="120"/>
       <c r="AX8" s="120"/>
       <c r="AY8" s="120"/>
@@ -10164,31 +10273,31 @@
       <c r="BA8" s="120"/>
       <c r="BB8" s="120"/>
       <c r="BC8" s="120"/>
-      <c r="BD8" s="188">
+      <c r="BD8" s="189">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="BE8" s="188" cm="1">
+        <v>25</v>
+      </c>
+      <c r="BE8" s="189" cm="1">
         <f t="array" ref="BE8">SUMPRODUCT(--(B8:BC8=INT(B8:BC8)),--(B8:BC8&gt;0))</f>
-        <v>24</v>
-      </c>
-      <c r="BF8" s="188" cm="1">
+        <v>25</v>
+      </c>
+      <c r="BF8" s="189" cm="1">
         <f t="array" ref="BF8">MAX(FREQUENCY(IF((B8:BC8=INT(B8:BC8))*(B8:BC8&gt;0),COLUMN(B8:BC8)),IF((B8:BC8&lt;&gt;INT(B8:BC8))+(B8:BC8&lt;=0),COLUMN(B8:BC8))))</f>
         <v>5</v>
       </c>
-      <c r="BG8" s="189" cm="1">
+      <c r="BG8" s="190" cm="1">
         <f t="array" ref="BG8">SUMPRODUCT(--(B8:AI8=INT(B8:AI8)),--(B8:AI8&gt;0))/34*100%</f>
         <v>0.470588235294118</v>
       </c>
-      <c r="BH8" s="190">
+      <c r="BH8" s="191">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="BI8" s="190">
+      <c r="BI8" s="191">
         <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="BJ8" s="190">
+        <v>2</v>
+      </c>
+      <c r="BJ8" s="191">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -10275,7 +10384,9 @@
       <c r="AU9" s="120">
         <v>1</v>
       </c>
-      <c r="AV9" s="120"/>
+      <c r="AV9" s="120">
+        <v>1</v>
+      </c>
       <c r="AW9" s="120"/>
       <c r="AX9" s="120"/>
       <c r="AY9" s="120"/>
@@ -10283,31 +10394,31 @@
       <c r="BA9" s="120"/>
       <c r="BB9" s="120"/>
       <c r="BC9" s="120"/>
-      <c r="BD9" s="188">
+      <c r="BD9" s="189">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="BE9" s="188" cm="1">
+        <v>17</v>
+      </c>
+      <c r="BE9" s="189" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
-        <v>16</v>
-      </c>
-      <c r="BF9" s="188" cm="1">
+        <v>17</v>
+      </c>
+      <c r="BF9" s="189" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
         <v>3</v>
       </c>
-      <c r="BG9" s="189" cm="1">
+      <c r="BG9" s="190" cm="1">
         <f t="array" ref="BG9">SUMPRODUCT(--(B9:AI9=INT(B9:AI9)),--(B9:AI9&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH9" s="190">
+      <c r="BH9" s="191">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="BI9" s="190">
+        <v>9</v>
+      </c>
+      <c r="BI9" s="191">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="BJ9" s="190">
+      <c r="BJ9" s="191">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -10372,31 +10483,31 @@
       <c r="BA10" s="120"/>
       <c r="BB10" s="120"/>
       <c r="BC10" s="120"/>
-      <c r="BD10" s="188">
+      <c r="BD10" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE10" s="188" cm="1">
+      <c r="BE10" s="189" cm="1">
         <f t="array" ref="BE10">SUMPRODUCT(--(B10:BC10=INT(B10:BC10)),--(B10:BC10&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF10" s="188" cm="1">
+      <c r="BF10" s="189" cm="1">
         <f t="array" ref="BF10">MAX(FREQUENCY(IF((B10:BC10=INT(B10:BC10))*(B10:BC10&gt;0),COLUMN(B10:BC10)),IF((B10:BC10&lt;&gt;INT(B10:BC10))+(B10:BC10&lt;=0),COLUMN(B10:BC10))))</f>
         <v>1</v>
       </c>
-      <c r="BG10" s="189" cm="1">
+      <c r="BG10" s="190" cm="1">
         <f t="array" ref="BG10">SUMPRODUCT(--(B10:AI10=INT(B10:AI10)),--(B10:AI10&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH10" s="190">
+      <c r="BH10" s="191">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI10" s="190">
+      <c r="BI10" s="191">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ10" s="190">
+      <c r="BJ10" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10479,31 +10590,31 @@
       <c r="BA11" s="120"/>
       <c r="BB11" s="120"/>
       <c r="BC11" s="120"/>
-      <c r="BD11" s="188">
+      <c r="BD11" s="189">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="BE11" s="188" cm="1">
+      <c r="BE11" s="189" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(--(B11:BC11=INT(B11:BC11)),--(B11:BC11&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="BF11" s="188" cm="1">
+      <c r="BF11" s="189" cm="1">
         <f t="array" ref="BF11">MAX(FREQUENCY(IF((B11:BC11=INT(B11:BC11))*(B11:BC11&gt;0),COLUMN(B11:BC11)),IF((B11:BC11&lt;&gt;INT(B11:BC11))+(B11:BC11&lt;=0),COLUMN(B11:BC11))))</f>
         <v>2</v>
       </c>
-      <c r="BG11" s="189" cm="1">
+      <c r="BG11" s="190" cm="1">
         <f t="array" ref="BG11">SUMPRODUCT(--(B11:AI11=INT(B11:AI11)),--(B11:AI11&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH11" s="190">
+      <c r="BH11" s="191">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="BI11" s="190">
+      <c r="BI11" s="191">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="BJ11" s="190">
+      <c r="BJ11" s="191">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -10570,31 +10681,31 @@
       <c r="BA12" s="120"/>
       <c r="BB12" s="120"/>
       <c r="BC12" s="120"/>
-      <c r="BD12" s="188">
+      <c r="BD12" s="189">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE12" s="188" cm="1">
+      <c r="BE12" s="189" cm="1">
         <f t="array" ref="BE12">SUMPRODUCT(--(B12:BC12=INT(B12:BC12)),--(B12:BC12&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF12" s="188" cm="1">
+      <c r="BF12" s="189" cm="1">
         <f t="array" ref="BF12">MAX(FREQUENCY(IF((B12:BC12=INT(B12:BC12))*(B12:BC12&gt;0),COLUMN(B12:BC12)),IF((B12:BC12&lt;&gt;INT(B12:BC12))+(B12:BC12&lt;=0),COLUMN(B12:BC12))))</f>
         <v>1</v>
       </c>
-      <c r="BG12" s="189" cm="1">
+      <c r="BG12" s="190" cm="1">
         <f t="array" ref="BG12">SUMPRODUCT(--(B12:AI12=INT(B12:AI12)),--(B12:AI12&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH12" s="190">
+      <c r="BH12" s="191">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI12" s="190">
+      <c r="BI12" s="191">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ12" s="190">
+      <c r="BJ12" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10679,31 +10790,31 @@
       <c r="BA13" s="120"/>
       <c r="BB13" s="120"/>
       <c r="BC13" s="120"/>
-      <c r="BD13" s="188">
+      <c r="BD13" s="189">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="BE13" s="188" cm="1">
+      <c r="BE13" s="189" cm="1">
         <f t="array" ref="BE13">SUMPRODUCT(--(B13:BC13=INT(B13:BC13)),--(B13:BC13&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF13" s="188" cm="1">
+      <c r="BF13" s="189" cm="1">
         <f t="array" ref="BF13">MAX(FREQUENCY(IF((B13:BC13=INT(B13:BC13))*(B13:BC13&gt;0),COLUMN(B13:BC13)),IF((B13:BC13&lt;&gt;INT(B13:BC13))+(B13:BC13&lt;=0),COLUMN(B13:BC13))))</f>
         <v>1</v>
       </c>
-      <c r="BG13" s="189" cm="1">
+      <c r="BG13" s="190" cm="1">
         <f t="array" ref="BG13">SUMPRODUCT(--(B13:AI13=INT(B13:AI13)),--(B13:AI13&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH13" s="190">
+      <c r="BH13" s="191">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="BI13" s="190">
+      <c r="BI13" s="191">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ13" s="190">
+      <c r="BJ13" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10774,31 +10885,31 @@
       <c r="BA14" s="120"/>
       <c r="BB14" s="120"/>
       <c r="BC14" s="120"/>
-      <c r="BD14" s="188">
+      <c r="BD14" s="189">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE14" s="188" cm="1">
+      <c r="BE14" s="189" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(--(B14:BC14=INT(B14:BC14)),--(B14:BC14&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF14" s="188" cm="1">
+      <c r="BF14" s="189" cm="1">
         <f t="array" ref="BF14">MAX(FREQUENCY(IF((B14:BC14=INT(B14:BC14))*(B14:BC14&gt;0),COLUMN(B14:BC14)),IF((B14:BC14&lt;&gt;INT(B14:BC14))+(B14:BC14&lt;=0),COLUMN(B14:BC14))))</f>
         <v>1</v>
       </c>
-      <c r="BG14" s="189" cm="1">
+      <c r="BG14" s="190" cm="1">
         <f t="array" ref="BG14">SUMPRODUCT(--(B14:AI14=INT(B14:AI14)),--(B14:AI14&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH14" s="190">
+      <c r="BH14" s="191">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="BI14" s="190">
+      <c r="BI14" s="191">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ14" s="190">
+      <c r="BJ14" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -10893,31 +11004,31 @@
       <c r="BA15" s="120"/>
       <c r="BB15" s="120"/>
       <c r="BC15" s="120"/>
-      <c r="BD15" s="188">
+      <c r="BD15" s="189">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="BE15" s="188" cm="1">
+      <c r="BE15" s="189" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
         <v>16</v>
       </c>
-      <c r="BF15" s="188" cm="1">
+      <c r="BF15" s="189" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
         <v>3</v>
       </c>
-      <c r="BG15" s="189" cm="1">
+      <c r="BG15" s="190" cm="1">
         <f t="array" ref="BG15">SUMPRODUCT(--(B15:AI15=INT(B15:AI15)),--(B15:AI15&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH15" s="190">
+      <c r="BH15" s="191">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="BI15" s="190">
+        <v>8</v>
+      </c>
+      <c r="BI15" s="191">
         <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="BJ15" s="190">
+        <v>8</v>
+      </c>
+      <c r="BJ15" s="191">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -10984,31 +11095,31 @@
       <c r="BA16" s="120"/>
       <c r="BB16" s="120"/>
       <c r="BC16" s="120"/>
-      <c r="BD16" s="188">
+      <c r="BD16" s="189">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="BE16" s="188" cm="1">
+      <c r="BE16" s="189" cm="1">
         <f t="array" ref="BE16">SUMPRODUCT(--(B16:BC16=INT(B16:BC16)),--(B16:BC16&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="BF16" s="188" cm="1">
+      <c r="BF16" s="189" cm="1">
         <f t="array" ref="BF16">MAX(FREQUENCY(IF((B16:BC16=INT(B16:BC16))*(B16:BC16&gt;0),COLUMN(B16:BC16)),IF((B16:BC16&lt;&gt;INT(B16:BC16))+(B16:BC16&lt;=0),COLUMN(B16:BC16))))</f>
         <v>1</v>
       </c>
-      <c r="BG16" s="189" cm="1">
+      <c r="BG16" s="190" cm="1">
         <f t="array" ref="BG16">SUMPRODUCT(--(B16:AI16=INT(B16:AI16)),--(B16:AI16&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH16" s="190">
+      <c r="BH16" s="191">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="BI16" s="190">
+      <c r="BI16" s="191">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="BJ16" s="190">
+      <c r="BJ16" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11079,31 +11190,31 @@
       <c r="BA17" s="120"/>
       <c r="BB17" s="120"/>
       <c r="BC17" s="120"/>
-      <c r="BD17" s="188">
+      <c r="BD17" s="189">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE17" s="188" cm="1">
+      <c r="BE17" s="189" cm="1">
         <f t="array" ref="BE17">SUMPRODUCT(--(B17:BC17=INT(B17:BC17)),--(B17:BC17&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF17" s="188" cm="1">
+      <c r="BF17" s="189" cm="1">
         <f t="array" ref="BF17">MAX(FREQUENCY(IF((B17:BC17=INT(B17:BC17))*(B17:BC17&gt;0),COLUMN(B17:BC17)),IF((B17:BC17&lt;&gt;INT(B17:BC17))+(B17:BC17&lt;=0),COLUMN(B17:BC17))))</f>
         <v>1</v>
       </c>
-      <c r="BG17" s="189" cm="1">
+      <c r="BG17" s="190" cm="1">
         <f t="array" ref="BG17">SUMPRODUCT(--(B17:AI17=INT(B17:AI17)),--(B17:AI17&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH17" s="190">
+      <c r="BH17" s="191">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="BI17" s="190">
+      <c r="BI17" s="191">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ17" s="190">
+      <c r="BJ17" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11168,31 +11279,31 @@
       <c r="BA18" s="120"/>
       <c r="BB18" s="120"/>
       <c r="BC18" s="120"/>
-      <c r="BD18" s="188">
+      <c r="BD18" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE18" s="188" cm="1">
+      <c r="BE18" s="189" cm="1">
         <f t="array" ref="BE18">SUMPRODUCT(--(B18:BC18=INT(B18:BC18)),--(B18:BC18&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF18" s="188" cm="1">
+      <c r="BF18" s="189" cm="1">
         <f t="array" ref="BF18">MAX(FREQUENCY(IF((B18:BC18=INT(B18:BC18))*(B18:BC18&gt;0),COLUMN(B18:BC18)),IF((B18:BC18&lt;&gt;INT(B18:BC18))+(B18:BC18&lt;=0),COLUMN(B18:BC18))))</f>
         <v>1</v>
       </c>
-      <c r="BG18" s="189" cm="1">
+      <c r="BG18" s="190" cm="1">
         <f t="array" ref="BG18">SUMPRODUCT(--(B18:AI18=INT(B18:AI18)),--(B18:AI18&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH18" s="190">
+      <c r="BH18" s="191">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI18" s="190">
+      <c r="BI18" s="191">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ18" s="190">
+      <c r="BJ18" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11259,7 +11370,9 @@
       <c r="AU19" s="120">
         <v>2</v>
       </c>
-      <c r="AV19" s="120"/>
+      <c r="AV19" s="120">
+        <v>1</v>
+      </c>
       <c r="AW19" s="120"/>
       <c r="AX19" s="120"/>
       <c r="AY19" s="120"/>
@@ -11267,31 +11380,31 @@
       <c r="BA19" s="120"/>
       <c r="BB19" s="120"/>
       <c r="BC19" s="120"/>
-      <c r="BD19" s="188">
+      <c r="BD19" s="189">
         <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="BE19" s="189" cm="1">
+        <f t="array" ref="BE19">SUMPRODUCT(--(B19:BC19=INT(B19:BC19)),--(B19:BC19&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BE19" s="188" cm="1">
-        <f t="array" ref="BE19">SUMPRODUCT(--(B19:BC19=INT(B19:BC19)),--(B19:BC19&gt;0))</f>
-        <v>6</v>
-      </c>
-      <c r="BF19" s="188" cm="1">
+      <c r="BF19" s="189" cm="1">
         <f t="array" ref="BF19">MAX(FREQUENCY(IF((B19:BC19=INT(B19:BC19))*(B19:BC19&gt;0),COLUMN(B19:BC19)),IF((B19:BC19&lt;&gt;INT(B19:BC19))+(B19:BC19&lt;=0),COLUMN(B19:BC19))))</f>
         <v>2</v>
       </c>
-      <c r="BG19" s="189" cm="1">
+      <c r="BG19" s="190" cm="1">
         <f t="array" ref="BG19">SUMPRODUCT(--(B19:AI19=INT(B19:AI19)),--(B19:AI19&gt;0))/34*100%</f>
         <v>0.147058823529412</v>
       </c>
-      <c r="BH19" s="190">
+      <c r="BH19" s="191">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="BI19" s="190">
+        <v>19</v>
+      </c>
+      <c r="BI19" s="191">
         <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="BJ19" s="190">
+        <v>20</v>
+      </c>
+      <c r="BJ19" s="191">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -11356,31 +11469,31 @@
       <c r="BA20" s="120"/>
       <c r="BB20" s="120"/>
       <c r="BC20" s="120"/>
-      <c r="BD20" s="188">
+      <c r="BD20" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE20" s="188" cm="1">
+      <c r="BE20" s="189" cm="1">
         <f t="array" ref="BE20">SUMPRODUCT(--(B20:BC20=INT(B20:BC20)),--(B20:BC20&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF20" s="188" cm="1">
+      <c r="BF20" s="189" cm="1">
         <f t="array" ref="BF20">MAX(FREQUENCY(IF((B20:BC20=INT(B20:BC20))*(B20:BC20&gt;0),COLUMN(B20:BC20)),IF((B20:BC20&lt;&gt;INT(B20:BC20))+(B20:BC20&lt;=0),COLUMN(B20:BC20))))</f>
         <v>1</v>
       </c>
-      <c r="BG20" s="189" cm="1">
+      <c r="BG20" s="190" cm="1">
         <f t="array" ref="BG20">SUMPRODUCT(--(B20:AI20=INT(B20:AI20)),--(B20:AI20&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH20" s="190">
+      <c r="BH20" s="191">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI20" s="190">
+      <c r="BI20" s="191">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ20" s="190">
+      <c r="BJ20" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11451,31 +11564,31 @@
       <c r="BA21" s="120"/>
       <c r="BB21" s="120"/>
       <c r="BC21" s="120"/>
-      <c r="BD21" s="188">
+      <c r="BD21" s="189">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE21" s="188" cm="1">
+      <c r="BE21" s="189" cm="1">
         <f t="array" ref="BE21">SUMPRODUCT(--(B21:BC21=INT(B21:BC21)),--(B21:BC21&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF21" s="188" cm="1">
+      <c r="BF21" s="189" cm="1">
         <f t="array" ref="BF21">MAX(FREQUENCY(IF((B21:BC21=INT(B21:BC21))*(B21:BC21&gt;0),COLUMN(B21:BC21)),IF((B21:BC21&lt;&gt;INT(B21:BC21))+(B21:BC21&lt;=0),COLUMN(B21:BC21))))</f>
         <v>1</v>
       </c>
-      <c r="BG21" s="189" cm="1">
+      <c r="BG21" s="190" cm="1">
         <f t="array" ref="BG21">SUMPRODUCT(--(B21:AI21=INT(B21:AI21)),--(B21:AI21&gt;0))/34*100%</f>
         <v>0.0588235294117647</v>
       </c>
-      <c r="BH21" s="190">
+      <c r="BH21" s="191">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="BI21" s="190">
+      <c r="BI21" s="191">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ21" s="190">
+      <c r="BJ21" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11564,33 +11677,33 @@
       <c r="BA22" s="120"/>
       <c r="BB22" s="120"/>
       <c r="BC22" s="120"/>
-      <c r="BD22" s="188">
+      <c r="BD22" s="189">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="BE22" s="188" cm="1">
+      <c r="BE22" s="189" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
         <v>13</v>
       </c>
-      <c r="BF22" s="188" cm="1">
+      <c r="BF22" s="189" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
         <v>4</v>
       </c>
-      <c r="BG22" s="189" cm="1">
+      <c r="BG22" s="190" cm="1">
         <f t="array" ref="BG22">SUMPRODUCT(--(B22:AI22=INT(B22:AI22)),--(B22:AI22&gt;0))/34*100%</f>
         <v>0.294117647058824</v>
       </c>
-      <c r="BH22" s="190">
+      <c r="BH22" s="191">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="BI22" s="190">
+        <v>11</v>
+      </c>
+      <c r="BI22" s="191">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="BJ22" s="190">
+      <c r="BJ22" s="191">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:62">
@@ -11653,31 +11766,31 @@
       <c r="BA23" s="120"/>
       <c r="BB23" s="120"/>
       <c r="BC23" s="120"/>
-      <c r="BD23" s="188">
+      <c r="BD23" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE23" s="188" cm="1">
+      <c r="BE23" s="189" cm="1">
         <f t="array" ref="BE23">SUMPRODUCT(--(B23:BC23=INT(B23:BC23)),--(B23:BC23&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF23" s="188" cm="1">
+      <c r="BF23" s="189" cm="1">
         <f t="array" ref="BF23">MAX(FREQUENCY(IF((B23:BC23=INT(B23:BC23))*(B23:BC23&gt;0),COLUMN(B23:BC23)),IF((B23:BC23&lt;&gt;INT(B23:BC23))+(B23:BC23&lt;=0),COLUMN(B23:BC23))))</f>
         <v>1</v>
       </c>
-      <c r="BG23" s="189" cm="1">
+      <c r="BG23" s="190" cm="1">
         <f t="array" ref="BG23">SUMPRODUCT(--(B23:AI23=INT(B23:AI23)),--(B23:AI23&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH23" s="190">
+      <c r="BH23" s="191">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI23" s="190">
+      <c r="BI23" s="191">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ23" s="190">
+      <c r="BJ23" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -11756,31 +11869,31 @@
       <c r="BA24" s="120"/>
       <c r="BB24" s="120"/>
       <c r="BC24" s="120"/>
-      <c r="BD24" s="188">
+      <c r="BD24" s="189">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="BE24" s="188" cm="1">
+      <c r="BE24" s="189" cm="1">
         <f t="array" ref="BE24">SUMPRODUCT(--(B24:BC24=INT(B24:BC24)),--(B24:BC24&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="BF24" s="188" cm="1">
+      <c r="BF24" s="189" cm="1">
         <f t="array" ref="BF24">MAX(FREQUENCY(IF((B24:BC24=INT(B24:BC24))*(B24:BC24&gt;0),COLUMN(B24:BC24)),IF((B24:BC24&lt;&gt;INT(B24:BC24))+(B24:BC24&lt;=0),COLUMN(B24:BC24))))</f>
         <v>3</v>
       </c>
-      <c r="BG24" s="189" cm="1">
+      <c r="BG24" s="190" cm="1">
         <f t="array" ref="BG24">SUMPRODUCT(--(B24:AI24=INT(B24:AI24)),--(B24:AI24&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH24" s="190">
+      <c r="BH24" s="191">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="BI24" s="190">
+      <c r="BI24" s="191">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="BJ24" s="190">
+      <c r="BJ24" s="191">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -11845,37 +11958,37 @@
       <c r="BA25" s="120"/>
       <c r="BB25" s="120"/>
       <c r="BC25" s="120"/>
-      <c r="BD25" s="188">
+      <c r="BD25" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE25" s="188" cm="1">
+      <c r="BE25" s="189" cm="1">
         <f t="array" ref="BE25">SUMPRODUCT(--(B25:BC25=INT(B25:BC25)),--(B25:BC25&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF25" s="188" cm="1">
+      <c r="BF25" s="189" cm="1">
         <f t="array" ref="BF25">MAX(FREQUENCY(IF((B25:BC25=INT(B25:BC25))*(B25:BC25&gt;0),COLUMN(B25:BC25)),IF((B25:BC25&lt;&gt;INT(B25:BC25))+(B25:BC25&lt;=0),COLUMN(B25:BC25))))</f>
         <v>1</v>
       </c>
-      <c r="BG25" s="189" cm="1">
+      <c r="BG25" s="190" cm="1">
         <f t="array" ref="BG25">SUMPRODUCT(--(B25:AI25=INT(B25:AI25)),--(B25:AI25&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH25" s="190">
+      <c r="BH25" s="191">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI25" s="190">
+      <c r="BI25" s="191">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ25" s="190">
+      <c r="BJ25" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:62">
-      <c r="A26" s="191">
+      <c r="A26" s="117">
         <v>24</v>
       </c>
       <c r="B26" s="120"/>
@@ -11932,37 +12045,37 @@
       <c r="BA26" s="120"/>
       <c r="BB26" s="120"/>
       <c r="BC26" s="120"/>
-      <c r="BD26" s="188">
+      <c r="BD26" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE26" s="188" cm="1">
+      <c r="BE26" s="189" cm="1">
         <f t="array" ref="BE26">SUMPRODUCT(--(B26:BC26=INT(B26:BC26)),--(B26:BC26&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF26" s="188" cm="1">
+      <c r="BF26" s="189" cm="1">
         <f t="array" ref="BF26">MAX(FREQUENCY(IF((B26:BC26=INT(B26:BC26))*(B26:BC26&gt;0),COLUMN(B26:BC26)),IF((B26:BC26&lt;&gt;INT(B26:BC26))+(B26:BC26&lt;=0),COLUMN(B26:BC26))))</f>
         <v>0</v>
       </c>
-      <c r="BG26" s="189" cm="1">
+      <c r="BG26" s="190" cm="1">
         <f t="array" ref="BG26">SUMPRODUCT(--(B26:AI26=INT(B26:AI26)),--(B26:AI26&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH26" s="190">
+      <c r="BH26" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI26" s="190">
+      <c r="BI26" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ26" s="190">
+      <c r="BJ26" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:62">
-      <c r="A27" s="191">
+      <c r="A27" s="117">
         <v>25</v>
       </c>
       <c r="B27" s="120"/>
@@ -12019,31 +12132,31 @@
       <c r="BA27" s="120"/>
       <c r="BB27" s="120"/>
       <c r="BC27" s="120"/>
-      <c r="BD27" s="188">
+      <c r="BD27" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE27" s="188" cm="1">
+      <c r="BE27" s="189" cm="1">
         <f t="array" ref="BE27">SUMPRODUCT(--(B27:BC27=INT(B27:BC27)),--(B27:BC27&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF27" s="188" cm="1">
+      <c r="BF27" s="189" cm="1">
         <f t="array" ref="BF27">MAX(FREQUENCY(IF((B27:BC27=INT(B27:BC27))*(B27:BC27&gt;0),COLUMN(B27:BC27)),IF((B27:BC27&lt;&gt;INT(B27:BC27))+(B27:BC27&lt;=0),COLUMN(B27:BC27))))</f>
         <v>0</v>
       </c>
-      <c r="BG27" s="189" cm="1">
+      <c r="BG27" s="190" cm="1">
         <f t="array" ref="BG27">SUMPRODUCT(--(B27:AI27=INT(B27:AI27)),--(B27:AI27&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH27" s="190">
+      <c r="BH27" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI27" s="190">
+      <c r="BI27" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ27" s="190">
+      <c r="BJ27" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -12128,31 +12241,31 @@
       <c r="BA28" s="120"/>
       <c r="BB28" s="120"/>
       <c r="BC28" s="120"/>
-      <c r="BD28" s="188">
+      <c r="BD28" s="189">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="BE28" s="188" cm="1">
+      <c r="BE28" s="189" cm="1">
         <f t="array" ref="BE28">SUMPRODUCT(--(B28:BC28=INT(B28:BC28)),--(B28:BC28&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF28" s="188" cm="1">
+      <c r="BF28" s="189" cm="1">
         <f t="array" ref="BF28">MAX(FREQUENCY(IF((B28:BC28=INT(B28:BC28))*(B28:BC28&gt;0),COLUMN(B28:BC28)),IF((B28:BC28&lt;&gt;INT(B28:BC28))+(B28:BC28&lt;=0),COLUMN(B28:BC28))))</f>
         <v>2</v>
       </c>
-      <c r="BG28" s="189" cm="1">
+      <c r="BG28" s="190" cm="1">
         <f t="array" ref="BG28">SUMPRODUCT(--(B28:AI28=INT(B28:AI28)),--(B28:AI28&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH28" s="190">
+      <c r="BH28" s="191">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="BI28" s="190">
+      <c r="BI28" s="191">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ28" s="190">
+      <c r="BJ28" s="191">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -12237,31 +12350,31 @@
       <c r="BA29" s="120"/>
       <c r="BB29" s="120"/>
       <c r="BC29" s="120"/>
-      <c r="BD29" s="188">
+      <c r="BD29" s="189">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="BE29" s="188" cm="1">
+      <c r="BE29" s="189" cm="1">
         <f t="array" ref="BE29">SUMPRODUCT(--(B29:BC29=INT(B29:BC29)),--(B29:BC29&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF29" s="188" cm="1">
+      <c r="BF29" s="189" cm="1">
         <f t="array" ref="BF29">MAX(FREQUENCY(IF((B29:BC29=INT(B29:BC29))*(B29:BC29&gt;0),COLUMN(B29:BC29)),IF((B29:BC29&lt;&gt;INT(B29:BC29))+(B29:BC29&lt;=0),COLUMN(B29:BC29))))</f>
         <v>5</v>
       </c>
-      <c r="BG29" s="189" cm="1">
+      <c r="BG29" s="190" cm="1">
         <f t="array" ref="BG29">SUMPRODUCT(--(B29:AI29=INT(B29:AI29)),--(B29:AI29&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH29" s="190">
+      <c r="BH29" s="191">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="BI29" s="190">
+      <c r="BI29" s="191">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ29" s="190">
+      <c r="BJ29" s="191">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -12338,33 +12451,33 @@
       <c r="BA30" s="120"/>
       <c r="BB30" s="120"/>
       <c r="BC30" s="120"/>
-      <c r="BD30" s="188">
+      <c r="BD30" s="189">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="BE30" s="188" cm="1">
+      <c r="BE30" s="189" cm="1">
         <f t="array" ref="BE30">SUMPRODUCT(--(B30:BC30=INT(B30:BC30)),--(B30:BC30&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="BF30" s="188" cm="1">
+      <c r="BF30" s="189" cm="1">
         <f t="array" ref="BF30">MAX(FREQUENCY(IF((B30:BC30=INT(B30:BC30))*(B30:BC30&gt;0),COLUMN(B30:BC30)),IF((B30:BC30&lt;&gt;INT(B30:BC30))+(B30:BC30&lt;=0),COLUMN(B30:BC30))))</f>
         <v>4</v>
       </c>
-      <c r="BG30" s="189" cm="1">
+      <c r="BG30" s="190" cm="1">
         <f t="array" ref="BG30">SUMPRODUCT(--(B30:AI30=INT(B30:AI30)),--(B30:AI30&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH30" s="190">
+      <c r="BH30" s="191">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="BI30" s="190">
+      <c r="BI30" s="191">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="BJ30" s="190">
+      <c r="BJ30" s="191">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:62">
@@ -12447,31 +12560,31 @@
       <c r="BA31" s="120"/>
       <c r="BB31" s="120"/>
       <c r="BC31" s="120"/>
-      <c r="BD31" s="188">
+      <c r="BD31" s="189">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="BE31" s="188" cm="1">
+      <c r="BE31" s="189" cm="1">
         <f t="array" ref="BE31">SUMPRODUCT(--(B31:BC31=INT(B31:BC31)),--(B31:BC31&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF31" s="188" cm="1">
+      <c r="BF31" s="189" cm="1">
         <f t="array" ref="BF31">MAX(FREQUENCY(IF((B31:BC31=INT(B31:BC31))*(B31:BC31&gt;0),COLUMN(B31:BC31)),IF((B31:BC31&lt;&gt;INT(B31:BC31))+(B31:BC31&lt;=0),COLUMN(B31:BC31))))</f>
         <v>2</v>
       </c>
-      <c r="BG31" s="189" cm="1">
+      <c r="BG31" s="190" cm="1">
         <f t="array" ref="BG31">SUMPRODUCT(--(B31:AI31=INT(B31:AI31)),--(B31:AI31&gt;0))/34*100%</f>
         <v>0.205882352941176</v>
       </c>
-      <c r="BH31" s="190">
+      <c r="BH31" s="191">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="BI31" s="190">
+      <c r="BI31" s="191">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ31" s="190">
+      <c r="BJ31" s="191">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -12556,31 +12669,31 @@
       <c r="BA32" s="120"/>
       <c r="BB32" s="120"/>
       <c r="BC32" s="120"/>
-      <c r="BD32" s="188">
+      <c r="BD32" s="189">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="BE32" s="188" cm="1">
+      <c r="BE32" s="189" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="BF32" s="188" cm="1">
+      <c r="BF32" s="189" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
         <v>3</v>
       </c>
-      <c r="BG32" s="189" cm="1">
+      <c r="BG32" s="190" cm="1">
         <f t="array" ref="BG32">SUMPRODUCT(--(B32:AI32=INT(B32:AI32)),--(B32:AI32&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH32" s="190">
+      <c r="BH32" s="191">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="BI32" s="190">
+      <c r="BI32" s="191">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="BJ32" s="190">
+      <c r="BJ32" s="191">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -12653,37 +12766,37 @@
       <c r="BA33" s="120"/>
       <c r="BB33" s="120"/>
       <c r="BC33" s="120"/>
-      <c r="BD33" s="188">
+      <c r="BD33" s="189">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE33" s="188" cm="1">
+      <c r="BE33" s="189" cm="1">
         <f t="array" ref="BE33">SUMPRODUCT(--(B33:BC33=INT(B33:BC33)),--(B33:BC33&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF33" s="188" cm="1">
+      <c r="BF33" s="189" cm="1">
         <f t="array" ref="BF33">MAX(FREQUENCY(IF((B33:BC33=INT(B33:BC33))*(B33:BC33&gt;0),COLUMN(B33:BC33)),IF((B33:BC33&lt;&gt;INT(B33:BC33))+(B33:BC33&lt;=0),COLUMN(B33:BC33))))</f>
         <v>1</v>
       </c>
-      <c r="BG33" s="189" cm="1">
+      <c r="BG33" s="190" cm="1">
         <f t="array" ref="BG33">SUMPRODUCT(--(B33:AI33=INT(B33:AI33)),--(B33:AI33&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH33" s="190">
+      <c r="BH33" s="191">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="BI33" s="190">
+      <c r="BI33" s="191">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="BJ33" s="190">
+      <c r="BJ33" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:62">
-      <c r="A34" s="191">
+      <c r="A34" s="117">
         <v>32</v>
       </c>
       <c r="B34" s="120"/>
@@ -12740,31 +12853,31 @@
       <c r="BA34" s="120"/>
       <c r="BB34" s="120"/>
       <c r="BC34" s="120"/>
-      <c r="BD34" s="188">
+      <c r="BD34" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE34" s="188" cm="1">
+      <c r="BE34" s="189" cm="1">
         <f t="array" ref="BE34">SUMPRODUCT(--(B34:BC34=INT(B34:BC34)),--(B34:BC34&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF34" s="188" cm="1">
+      <c r="BF34" s="189" cm="1">
         <f t="array" ref="BF34">MAX(FREQUENCY(IF((B34:BC34=INT(B34:BC34))*(B34:BC34&gt;0),COLUMN(B34:BC34)),IF((B34:BC34&lt;&gt;INT(B34:BC34))+(B34:BC34&lt;=0),COLUMN(B34:BC34))))</f>
         <v>0</v>
       </c>
-      <c r="BG34" s="189" cm="1">
+      <c r="BG34" s="190" cm="1">
         <f t="array" ref="BG34">SUMPRODUCT(--(B34:AI34=INT(B34:AI34)),--(B34:AI34&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH34" s="190">
+      <c r="BH34" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI34" s="190">
+      <c r="BI34" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ34" s="190">
+      <c r="BJ34" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -12827,31 +12940,31 @@
       <c r="BA35" s="192"/>
       <c r="BB35" s="192"/>
       <c r="BC35" s="192"/>
-      <c r="BD35" s="188">
+      <c r="BD35" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE35" s="188" cm="1">
+      <c r="BE35" s="189" cm="1">
         <f t="array" ref="BE35">SUMPRODUCT(--(B35:BC35=INT(B35:BC35)),--(B35:BC35&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF35" s="188" cm="1">
+      <c r="BF35" s="189" cm="1">
         <f t="array" ref="BF35">MAX(FREQUENCY(IF((B35:BC35=INT(B35:BC35))*(B35:BC35&gt;0),COLUMN(B35:BC35)),IF((B35:BC35&lt;&gt;INT(B35:BC35))+(B35:BC35&lt;=0),COLUMN(B35:BC35))))</f>
         <v>0</v>
       </c>
-      <c r="BG35" s="189" cm="1">
+      <c r="BG35" s="190" cm="1">
         <f t="array" ref="BG35">SUMPRODUCT(--(B35:AI35=INT(B35:AI35)),--(B35:AI35&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH35" s="190">
+      <c r="BH35" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI35" s="190">
+      <c r="BI35" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ35" s="190">
+      <c r="BJ35" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -12916,31 +13029,31 @@
       <c r="BA36" s="120"/>
       <c r="BB36" s="120"/>
       <c r="BC36" s="120"/>
-      <c r="BD36" s="188">
+      <c r="BD36" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE36" s="188" cm="1">
+      <c r="BE36" s="189" cm="1">
         <f t="array" ref="BE36">SUMPRODUCT(--(B36:BC36=INT(B36:BC36)),--(B36:BC36&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF36" s="188" cm="1">
+      <c r="BF36" s="189" cm="1">
         <f t="array" ref="BF36">MAX(FREQUENCY(IF((B36:BC36=INT(B36:BC36))*(B36:BC36&gt;0),COLUMN(B36:BC36)),IF((B36:BC36&lt;&gt;INT(B36:BC36))+(B36:BC36&lt;=0),COLUMN(B36:BC36))))</f>
         <v>1</v>
       </c>
-      <c r="BG36" s="189" cm="1">
+      <c r="BG36" s="190" cm="1">
         <f t="array" ref="BG36">SUMPRODUCT(--(B36:AI36=INT(B36:AI36)),--(B36:AI36&gt;0))/34*100%</f>
         <v>0.0294117647058824</v>
       </c>
-      <c r="BH36" s="190">
+      <c r="BH36" s="191">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI36" s="190">
+      <c r="BI36" s="191">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ36" s="190">
+      <c r="BJ36" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -13019,31 +13132,31 @@
       <c r="BA37" s="120"/>
       <c r="BB37" s="120"/>
       <c r="BC37" s="120"/>
-      <c r="BD37" s="188">
+      <c r="BD37" s="189">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="BE37" s="188" cm="1">
+      <c r="BE37" s="189" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="BF37" s="188" cm="1">
+      <c r="BF37" s="189" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
         <v>3</v>
       </c>
-      <c r="BG37" s="189" cm="1">
+      <c r="BG37" s="190" cm="1">
         <f t="array" ref="BG37">SUMPRODUCT(--(B37:AI37=INT(B37:AI37)),--(B37:AI37&gt;0))/34*100%</f>
         <v>0.176470588235294</v>
       </c>
-      <c r="BH37" s="190">
+      <c r="BH37" s="191">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="BI37" s="190">
+      <c r="BI37" s="191">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="BJ37" s="190">
+      <c r="BJ37" s="191">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -13112,31 +13225,31 @@
       <c r="BA38" s="120"/>
       <c r="BB38" s="120"/>
       <c r="BC38" s="120"/>
-      <c r="BD38" s="188">
+      <c r="BD38" s="189">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE38" s="188" cm="1">
+      <c r="BE38" s="189" cm="1">
         <f t="array" ref="BE38">SUMPRODUCT(--(B38:BC38=INT(B38:BC38)),--(B38:BC38&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="BF38" s="188" cm="1">
+      <c r="BF38" s="189" cm="1">
         <f t="array" ref="BF38">MAX(FREQUENCY(IF((B38:BC38=INT(B38:BC38))*(B38:BC38&gt;0),COLUMN(B38:BC38)),IF((B38:BC38&lt;&gt;INT(B38:BC38))+(B38:BC38&lt;=0),COLUMN(B38:BC38))))</f>
         <v>1</v>
       </c>
-      <c r="BG38" s="189" cm="1">
+      <c r="BG38" s="190" cm="1">
         <f t="array" ref="BG38">SUMPRODUCT(--(B38:AI38=INT(B38:AI38)),--(B38:AI38&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH38" s="190">
+      <c r="BH38" s="191">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="BI38" s="190">
+      <c r="BI38" s="191">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="BJ38" s="190">
+      <c r="BJ38" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -13199,19 +13312,19 @@
       <c r="BA39" s="192"/>
       <c r="BB39" s="192"/>
       <c r="BC39" s="192"/>
-      <c r="BD39" s="188">
+      <c r="BD39" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE39" s="188" cm="1">
+      <c r="BE39" s="189" cm="1">
         <f t="array" ref="BE39">SUMPRODUCT(--(B39:BC39=INT(B39:BC39)),--(B39:BC39&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF39" s="188" cm="1">
+      <c r="BF39" s="189" cm="1">
         <f t="array" ref="BF39">MAX(FREQUENCY(IF((B39:BC39=INT(B39:BC39))*(B39:BC39&gt;0),COLUMN(B39:BC39)),IF((B39:BC39&lt;&gt;INT(B39:BC39))+(B39:BC39&lt;=0),COLUMN(B39:BC39))))</f>
         <v>0</v>
       </c>
-      <c r="BG39" s="189" cm="1">
+      <c r="BG39" s="190" cm="1">
         <f t="array" ref="BG39">SUMPRODUCT(--(B39:AI39=INT(B39:AI39)),--(B39:AI39&gt;0))/34*100%</f>
         <v>0</v>
       </c>
@@ -13336,31 +13449,31 @@
       <c r="BA40" s="120"/>
       <c r="BB40" s="120"/>
       <c r="BC40" s="120"/>
-      <c r="BD40" s="188">
+      <c r="BD40" s="189">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="BE40" s="188" cm="1">
+      <c r="BE40" s="189" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
         <v>25</v>
       </c>
-      <c r="BF40" s="188" cm="1">
+      <c r="BF40" s="189" cm="1">
         <f t="array" ref="BF40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
         <v>12</v>
       </c>
-      <c r="BG40" s="189" cm="1">
+      <c r="BG40" s="190" cm="1">
         <f t="array" ref="BG40">SUMPRODUCT(--(B40:AI40=INT(B40:AI40)),--(B40:AI40&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH40" s="190">
+      <c r="BH40" s="191">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="BI40" s="190">
+      <c r="BI40" s="191">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="BJ40" s="190">
+      <c r="BJ40" s="191">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -13445,7 +13558,9 @@
       <c r="AU41" s="120">
         <v>1</v>
       </c>
-      <c r="AV41" s="120"/>
+      <c r="AV41" s="120">
+        <v>1</v>
+      </c>
       <c r="AW41" s="120"/>
       <c r="AX41" s="120"/>
       <c r="AY41" s="120"/>
@@ -13453,31 +13568,31 @@
       <c r="BA41" s="120"/>
       <c r="BB41" s="120"/>
       <c r="BC41" s="120"/>
-      <c r="BD41" s="188">
+      <c r="BD41" s="189">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="BE41" s="188" cm="1">
+        <v>20</v>
+      </c>
+      <c r="BE41" s="189" cm="1">
         <f t="array" ref="BE41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
-        <v>15</v>
-      </c>
-      <c r="BF41" s="188" cm="1">
+        <v>16</v>
+      </c>
+      <c r="BF41" s="189" cm="1">
         <f t="array" ref="BF41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
         <v>2</v>
       </c>
-      <c r="BG41" s="189" cm="1">
+      <c r="BG41" s="190" cm="1">
         <f t="array" ref="BG41">SUMPRODUCT(--(B41:AI41=INT(B41:AI41)),--(B41:AI41&gt;0))/34*100%</f>
         <v>0.235294117647059</v>
       </c>
-      <c r="BH41" s="190">
+      <c r="BH41" s="191">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="BI41" s="190">
+      <c r="BI41" s="191">
         <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="BJ41" s="190">
+        <v>8</v>
+      </c>
+      <c r="BJ41" s="191">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -13568,7 +13683,9 @@
       <c r="AU42" s="120">
         <v>3</v>
       </c>
-      <c r="AV42" s="120"/>
+      <c r="AV42" s="120">
+        <v>1</v>
+      </c>
       <c r="AW42" s="120"/>
       <c r="AX42" s="120"/>
       <c r="AY42" s="120"/>
@@ -13576,37 +13693,37 @@
       <c r="BA42" s="120"/>
       <c r="BB42" s="120"/>
       <c r="BC42" s="120"/>
-      <c r="BD42" s="188">
+      <c r="BD42" s="189">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="BE42" s="188" cm="1">
+        <v>25</v>
+      </c>
+      <c r="BE42" s="189" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
-        <v>18</v>
-      </c>
-      <c r="BF42" s="188" cm="1">
+        <v>19</v>
+      </c>
+      <c r="BF42" s="189" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
         <v>5</v>
       </c>
-      <c r="BG42" s="189" cm="1">
+      <c r="BG42" s="190" cm="1">
         <f t="array" ref="BG42">SUMPRODUCT(--(B42:AI42=INT(B42:AI42)),--(B42:AI42&gt;0))/34*100%</f>
         <v>0.352941176470588</v>
       </c>
-      <c r="BH42" s="190">
+      <c r="BH42" s="191">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="BI42" s="190">
+      <c r="BI42" s="191">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="BJ42" s="190">
+      <c r="BJ42" s="191">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:62">
-      <c r="A43" s="191">
+      <c r="A43" s="117">
         <v>41</v>
       </c>
       <c r="B43" s="120"/>
@@ -13663,31 +13780,31 @@
       <c r="BA43" s="120"/>
       <c r="BB43" s="120"/>
       <c r="BC43" s="120"/>
-      <c r="BD43" s="188">
+      <c r="BD43" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE43" s="188" cm="1">
+      <c r="BE43" s="189" cm="1">
         <f t="array" ref="BE43">SUMPRODUCT(--(B43:BC43=INT(B43:BC43)),--(B43:BC43&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF43" s="188" cm="1">
+      <c r="BF43" s="189" cm="1">
         <f t="array" ref="BF43">MAX(FREQUENCY(IF((B43:BC43=INT(B43:BC43))*(B43:BC43&gt;0),COLUMN(B43:BC43)),IF((B43:BC43&lt;&gt;INT(B43:BC43))+(B43:BC43&lt;=0),COLUMN(B43:BC43))))</f>
         <v>0</v>
       </c>
-      <c r="BG43" s="189" cm="1">
+      <c r="BG43" s="190" cm="1">
         <f t="array" ref="BG43">SUMPRODUCT(--(B43:AI43=INT(B43:AI43)),--(B43:AI43&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH43" s="190">
+      <c r="BH43" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI43" s="190">
+      <c r="BI43" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ43" s="190">
+      <c r="BJ43" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -13776,7 +13893,9 @@
       <c r="AU44" s="120">
         <v>2</v>
       </c>
-      <c r="AV44" s="120"/>
+      <c r="AV44" s="120">
+        <v>1</v>
+      </c>
       <c r="AW44" s="120"/>
       <c r="AX44" s="120"/>
       <c r="AY44" s="120"/>
@@ -13784,37 +13903,37 @@
       <c r="BA44" s="120"/>
       <c r="BB44" s="120"/>
       <c r="BC44" s="120"/>
-      <c r="BD44" s="188">
+      <c r="BD44" s="189">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="BE44" s="188" cm="1">
+        <v>22</v>
+      </c>
+      <c r="BE44" s="189" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
-        <v>17</v>
-      </c>
-      <c r="BF44" s="188" cm="1">
+        <v>18</v>
+      </c>
+      <c r="BF44" s="189" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
         <v>5</v>
       </c>
-      <c r="BG44" s="189" cm="1">
+      <c r="BG44" s="190" cm="1">
         <f t="array" ref="BG44">SUMPRODUCT(--(B44:AI44=INT(B44:AI44)),--(B44:AI44&gt;0))/34*100%</f>
         <v>0.411764705882353</v>
       </c>
-      <c r="BH44" s="190">
+      <c r="BH44" s="191">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="BI44" s="190">
+      <c r="BI44" s="191">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="BJ44" s="190">
+      <c r="BJ44" s="191">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:62">
-      <c r="A45" s="191">
+      <c r="A45" s="117">
         <v>43</v>
       </c>
       <c r="B45" s="120"/>
@@ -13871,31 +13990,31 @@
       <c r="BA45" s="120"/>
       <c r="BB45" s="120"/>
       <c r="BC45" s="120"/>
-      <c r="BD45" s="188">
+      <c r="BD45" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE45" s="188" cm="1">
+      <c r="BE45" s="189" cm="1">
         <f t="array" ref="BE45">SUMPRODUCT(--(B45:BC45=INT(B45:BC45)),--(B45:BC45&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF45" s="188" cm="1">
+      <c r="BF45" s="189" cm="1">
         <f t="array" ref="BF45">MAX(FREQUENCY(IF((B45:BC45=INT(B45:BC45))*(B45:BC45&gt;0),COLUMN(B45:BC45)),IF((B45:BC45&lt;&gt;INT(B45:BC45))+(B45:BC45&lt;=0),COLUMN(B45:BC45))))</f>
         <v>0</v>
       </c>
-      <c r="BG45" s="189" cm="1">
+      <c r="BG45" s="190" cm="1">
         <f t="array" ref="BG45">SUMPRODUCT(--(B45:AI45=INT(B45:AI45)),--(B45:AI45&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH45" s="190">
+      <c r="BH45" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI45" s="190">
+      <c r="BI45" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ45" s="190">
+      <c r="BJ45" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -14008,7 +14127,9 @@
       <c r="AU46" s="120">
         <v>2</v>
       </c>
-      <c r="AV46" s="120"/>
+      <c r="AV46" s="120">
+        <v>1</v>
+      </c>
       <c r="AW46" s="120"/>
       <c r="AX46" s="120"/>
       <c r="AY46" s="120"/>
@@ -14016,37 +14137,37 @@
       <c r="BA46" s="120"/>
       <c r="BB46" s="120"/>
       <c r="BC46" s="120"/>
-      <c r="BD46" s="188">
+      <c r="BD46" s="189">
         <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="BE46" s="188" cm="1">
+        <v>41</v>
+      </c>
+      <c r="BE46" s="189" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>29</v>
-      </c>
-      <c r="BF46" s="188" cm="1">
+        <v>30</v>
+      </c>
+      <c r="BF46" s="189" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
         <v>8</v>
       </c>
-      <c r="BG46" s="189" cm="1">
+      <c r="BG46" s="190" cm="1">
         <f t="array" ref="BG46">SUMPRODUCT(--(B46:AI46=INT(B46:AI46)),--(B46:AI46&gt;0))/34*100%</f>
         <v>0.617647058823529</v>
       </c>
-      <c r="BH46" s="190">
+      <c r="BH46" s="191">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="BI46" s="190">
+      <c r="BI46" s="191">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="BJ46" s="190">
+      <c r="BJ46" s="191">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:62">
-      <c r="A47" s="191">
+      <c r="A47" s="117">
         <v>45</v>
       </c>
       <c r="B47" s="120"/>
@@ -14103,31 +14224,31 @@
       <c r="BA47" s="120"/>
       <c r="BB47" s="120"/>
       <c r="BC47" s="120"/>
-      <c r="BD47" s="188">
+      <c r="BD47" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE47" s="188" cm="1">
+      <c r="BE47" s="189" cm="1">
         <f t="array" ref="BE47">SUMPRODUCT(--(B47:BC47=INT(B47:BC47)),--(B47:BC47&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF47" s="188" cm="1">
+      <c r="BF47" s="189" cm="1">
         <f t="array" ref="BF47">MAX(FREQUENCY(IF((B47:BC47=INT(B47:BC47))*(B47:BC47&gt;0),COLUMN(B47:BC47)),IF((B47:BC47&lt;&gt;INT(B47:BC47))+(B47:BC47&lt;=0),COLUMN(B47:BC47))))</f>
         <v>0</v>
       </c>
-      <c r="BG47" s="189" cm="1">
+      <c r="BG47" s="190" cm="1">
         <f t="array" ref="BG47">SUMPRODUCT(--(B47:AI47=INT(B47:AI47)),--(B47:AI47&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH47" s="190">
+      <c r="BH47" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI47" s="190">
+      <c r="BI47" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ47" s="190">
+      <c r="BJ47" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -14218,31 +14339,31 @@
       <c r="BA48" s="120"/>
       <c r="BB48" s="120"/>
       <c r="BC48" s="120"/>
-      <c r="BD48" s="188">
+      <c r="BD48" s="189">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="BE48" s="188" cm="1">
+      <c r="BE48" s="189" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
         <v>14</v>
       </c>
-      <c r="BF48" s="188" cm="1">
+      <c r="BF48" s="189" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
         <v>2</v>
       </c>
-      <c r="BG48" s="189" cm="1">
+      <c r="BG48" s="190" cm="1">
         <f t="array" ref="BG48">SUMPRODUCT(--(B48:AI48=INT(B48:AI48)),--(B48:AI48&gt;0))/34*100%</f>
         <v>0.264705882352941</v>
       </c>
-      <c r="BH48" s="190">
+      <c r="BH48" s="191">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="BI48" s="190">
+      <c r="BI48" s="191">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="BJ48" s="190">
+      <c r="BJ48" s="191">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -14313,31 +14434,31 @@
       <c r="BA49" s="120"/>
       <c r="BB49" s="120"/>
       <c r="BC49" s="120"/>
-      <c r="BD49" s="188">
+      <c r="BD49" s="189">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="BE49" s="188" cm="1">
+      <c r="BE49" s="189" cm="1">
         <f t="array" ref="BE49">SUMPRODUCT(--(B49:BC49=INT(B49:BC49)),--(B49:BC49&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="BF49" s="188" cm="1">
+      <c r="BF49" s="189" cm="1">
         <f t="array" ref="BF49">MAX(FREQUENCY(IF((B49:BC49=INT(B49:BC49))*(B49:BC49&gt;0),COLUMN(B49:BC49)),IF((B49:BC49&lt;&gt;INT(B49:BC49))+(B49:BC49&lt;=0),COLUMN(B49:BC49))))</f>
         <v>1</v>
       </c>
-      <c r="BG49" s="189" cm="1">
+      <c r="BG49" s="190" cm="1">
         <f t="array" ref="BG49">SUMPRODUCT(--(B49:AI49=INT(B49:AI49)),--(B49:AI49&gt;0))/34*100%</f>
         <v>0.0882352941176471</v>
       </c>
-      <c r="BH49" s="190">
+      <c r="BH49" s="191">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="BI49" s="190">
+      <c r="BI49" s="191">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="BJ49" s="190">
+      <c r="BJ49" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
@@ -14410,37 +14531,37 @@
       <c r="BA50" s="120"/>
       <c r="BB50" s="120"/>
       <c r="BC50" s="120"/>
-      <c r="BD50" s="188">
+      <c r="BD50" s="189">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="BE50" s="188" cm="1">
+      <c r="BE50" s="189" cm="1">
         <f t="array" ref="BE50">SUMPRODUCT(--(B50:BC50=INT(B50:BC50)),--(B50:BC50&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="BF50" s="188" cm="1">
+      <c r="BF50" s="189" cm="1">
         <f t="array" ref="BF50">MAX(FREQUENCY(IF((B50:BC50=INT(B50:BC50))*(B50:BC50&gt;0),COLUMN(B50:BC50)),IF((B50:BC50&lt;&gt;INT(B50:BC50))+(B50:BC50&lt;=0),COLUMN(B50:BC50))))</f>
         <v>1</v>
       </c>
-      <c r="BG50" s="189" cm="1">
+      <c r="BG50" s="190" cm="1">
         <f t="array" ref="BG50">SUMPRODUCT(--(B50:AI50=INT(B50:AI50)),--(B50:AI50&gt;0))/34*100%</f>
         <v>0.117647058823529</v>
       </c>
-      <c r="BH50" s="190">
+      <c r="BH50" s="191">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="BI50" s="190">
+      <c r="BI50" s="191">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="BJ50" s="190">
+      <c r="BJ50" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:62">
-      <c r="A51" s="191">
+      <c r="A51" s="117">
         <v>49</v>
       </c>
       <c r="B51" s="120"/>
@@ -14497,37 +14618,37 @@
       <c r="BA51" s="120"/>
       <c r="BB51" s="120"/>
       <c r="BC51" s="120"/>
-      <c r="BD51" s="188">
+      <c r="BD51" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE51" s="188" cm="1">
+      <c r="BE51" s="189" cm="1">
         <f t="array" ref="BE51">SUMPRODUCT(--(B51:BC51=INT(B51:BC51)),--(B51:BC51&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF51" s="188" cm="1">
+      <c r="BF51" s="189" cm="1">
         <f t="array" ref="BF51">MAX(FREQUENCY(IF((B51:BC51=INT(B51:BC51))*(B51:BC51&gt;0),COLUMN(B51:BC51)),IF((B51:BC51&lt;&gt;INT(B51:BC51))+(B51:BC51&lt;=0),COLUMN(B51:BC51))))</f>
         <v>0</v>
       </c>
-      <c r="BG51" s="189" cm="1">
+      <c r="BG51" s="190" cm="1">
         <f t="array" ref="BG51">SUMPRODUCT(--(B51:AI51=INT(B51:AI51)),--(B51:AI51&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH51" s="190">
+      <c r="BH51" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI51" s="190">
+      <c r="BI51" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ51" s="190">
+      <c r="BJ51" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:62">
-      <c r="A52" s="191">
+      <c r="A52" s="117">
         <v>50</v>
       </c>
       <c r="B52" s="120"/>
@@ -14584,31 +14705,31 @@
       <c r="BA52" s="120"/>
       <c r="BB52" s="120"/>
       <c r="BC52" s="120"/>
-      <c r="BD52" s="188">
+      <c r="BD52" s="189">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="BE52" s="188" cm="1">
+      <c r="BE52" s="189" cm="1">
         <f t="array" ref="BE52">SUMPRODUCT(--(B52:BC52=INT(B52:BC52)),--(B52:BC52&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BF52" s="188" cm="1">
+      <c r="BF52" s="189" cm="1">
         <f t="array" ref="BF52">MAX(FREQUENCY(IF((B52:BC52=INT(B52:BC52))*(B52:BC52&gt;0),COLUMN(B52:BC52)),IF((B52:BC52&lt;&gt;INT(B52:BC52))+(B52:BC52&lt;=0),COLUMN(B52:BC52))))</f>
         <v>0</v>
       </c>
-      <c r="BG52" s="189" cm="1">
+      <c r="BG52" s="190" cm="1">
         <f t="array" ref="BG52">SUMPRODUCT(--(B52:AI52=INT(B52:AI52)),--(B52:AI52&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH52" s="190">
+      <c r="BH52" s="191">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="BI52" s="190">
+      <c r="BI52" s="191">
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-      <c r="BJ52" s="190">
+      <c r="BJ52" s="191">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
@@ -14673,46 +14794,543 @@
       <c r="BA53" s="120"/>
       <c r="BB53" s="120"/>
       <c r="BC53" s="120"/>
-      <c r="BD53" s="188">
+      <c r="BD53" s="189">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="BE53" s="188" cm="1">
+      <c r="BE53" s="189" cm="1">
         <f t="array" ref="BE53">SUMPRODUCT(--(B53:BC53=INT(B53:BC53)),--(B53:BC53&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="BF53" s="188" cm="1">
+      <c r="BF53" s="189" cm="1">
         <f t="array" ref="BF53">MAX(FREQUENCY(IF((B53:BC53=INT(B53:BC53))*(B53:BC53&gt;0),COLUMN(B53:BC53)),IF((B53:BC53&lt;&gt;INT(B53:BC53))+(B53:BC53&lt;=0),COLUMN(B53:BC53))))</f>
         <v>1</v>
       </c>
-      <c r="BG53" s="189" cm="1">
+      <c r="BG53" s="190" cm="1">
         <f t="array" ref="BG53">SUMPRODUCT(--(B53:AI53=INT(B53:AI53)),--(B53:AI53&gt;0))/34*100%</f>
         <v>0</v>
       </c>
-      <c r="BH53" s="190">
+      <c r="BH53" s="191">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="BI53" s="190">
+      <c r="BI53" s="191">
         <f t="shared" si="2"/>
         <v>34</v>
       </c>
-      <c r="BJ53" s="190">
+      <c r="BJ53" s="191">
         <f t="shared" si="3"/>
         <v>22</v>
       </c>
     </row>
+    <row r="54" s="175" customFormat="1" ht="28" spans="1:62">
+      <c r="A54" s="194" t="s">
+        <v>326</v>
+      </c>
+      <c r="B54" s="195" cm="1">
+        <f t="array" ref="B54">SUMPRODUCT(--(B3:B53=INT(B3:B53)),--(B3:B53&gt;0))</f>
+        <v>11</v>
+      </c>
+      <c r="C54" s="195" cm="1">
+        <f t="array" ref="C54">SUMPRODUCT(--(C3:C53=INT(C3:C53)),--(C3:C53&gt;0))</f>
+        <v>9</v>
+      </c>
+      <c r="D54" s="195" cm="1">
+        <f t="array" ref="D54">SUMPRODUCT(--(D3:D53=INT(D3:D53)),--(D3:D53&gt;0))</f>
+        <v>10</v>
+      </c>
+      <c r="E54" s="195" cm="1">
+        <f t="array" ref="E54">SUMPRODUCT(--(E3:E53=INT(E3:E53)),--(E3:E53&gt;0))</f>
+        <v>6</v>
+      </c>
+      <c r="F54" s="195" cm="1">
+        <f t="array" ref="F54">SUMPRODUCT(--(F3:F53=INT(F3:F53)),--(F3:F53&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="G54" s="195" cm="1">
+        <f t="array" ref="G54">SUMPRODUCT(--(G3:G53=INT(G3:G53)),--(G3:G53&gt;0))</f>
+        <v>5</v>
+      </c>
+      <c r="H54" s="195" cm="1">
+        <f t="array" ref="H54">SUMPRODUCT(--(H3:H53=INT(H3:H53)),--(H3:H53&gt;0))</f>
+        <v>12</v>
+      </c>
+      <c r="I54" s="195" cm="1">
+        <f t="array" ref="I54">SUMPRODUCT(--(I3:I53=INT(I3:I53)),--(I3:I53&gt;0))</f>
+        <v>13</v>
+      </c>
+      <c r="J54" s="195" cm="1">
+        <f t="array" ref="J54">SUMPRODUCT(--(J3:J53=INT(J3:J53)),--(J3:J53&gt;0))</f>
+        <v>12</v>
+      </c>
+      <c r="K54" s="195" cm="1">
+        <f t="array" ref="K54">SUMPRODUCT(--(K3:K53=INT(K3:K53)),--(K3:K53&gt;0))</f>
+        <v>5</v>
+      </c>
+      <c r="L54" s="195" cm="1">
+        <f t="array" ref="L54">SUMPRODUCT(--(L3:L53=INT(L3:L53)),--(L3:L53&gt;0))</f>
+        <v>12</v>
+      </c>
+      <c r="M54" s="195" cm="1">
+        <f t="array" ref="M54">SUMPRODUCT(--(M3:M53=INT(M3:M53)),--(M3:M53&gt;0))</f>
+        <v>6</v>
+      </c>
+      <c r="N54" s="195" cm="1">
+        <f t="array" ref="N54">SUMPRODUCT(--(N3:N53=INT(N3:N53)),--(N3:N53&gt;0))</f>
+        <v>9</v>
+      </c>
+      <c r="O54" s="195" cm="1">
+        <f t="array" ref="O54">SUMPRODUCT(--(O3:O53=INT(O3:O53)),--(O3:O53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="P54" s="195" cm="1">
+        <f t="array" ref="P54">SUMPRODUCT(--(P3:P53=INT(P3:P53)),--(P3:P53&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="Q54" s="195" cm="1">
+        <f t="array" ref="Q54">SUMPRODUCT(--(Q3:Q53=INT(Q3:Q53)),--(Q3:Q53&gt;0))</f>
+        <v>13</v>
+      </c>
+      <c r="R54" s="195" cm="1">
+        <f t="array" ref="R54">SUMPRODUCT(--(R3:R53=INT(R3:R53)),--(R3:R53&gt;0))</f>
+        <v>11</v>
+      </c>
+      <c r="S54" s="195" cm="1">
+        <f t="array" ref="S54">SUMPRODUCT(--(S3:S53=INT(S3:S53)),--(S3:S53&gt;0))</f>
+        <v>11</v>
+      </c>
+      <c r="T54" s="195" cm="1">
+        <f t="array" ref="T54">SUMPRODUCT(--(T3:T53=INT(T3:T53)),--(T3:T53&gt;0))</f>
+        <v>23</v>
+      </c>
+      <c r="U54" s="195" cm="1">
+        <f t="array" ref="U54">SUMPRODUCT(--(U3:U53=INT(U3:U53)),--(U3:U53&gt;0))</f>
+        <v>4</v>
+      </c>
+      <c r="V54" s="195" cm="1">
+        <f t="array" ref="V54">SUMPRODUCT(--(V3:V53=INT(V3:V53)),--(V3:V53&gt;0))</f>
+        <v>12</v>
+      </c>
+      <c r="W54" s="195" cm="1">
+        <f t="array" ref="W54">SUMPRODUCT(--(W3:W53=INT(W3:W53)),--(W3:W53&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="X54" s="195" cm="1">
+        <f t="array" ref="X54">SUMPRODUCT(--(X3:X53=INT(X3:X53)),--(X3:X53&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="Y54" s="195" cm="1">
+        <f t="array" ref="Y54">SUMPRODUCT(--(Y3:Y53=INT(Y3:Y53)),--(Y3:Y53&gt;0))</f>
+        <v>28</v>
+      </c>
+      <c r="Z54" s="195" cm="1">
+        <f t="array" ref="Z54">SUMPRODUCT(--(Z3:Z53=INT(Z3:Z53)),--(Z3:Z53&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="AA54" s="195" cm="1">
+        <f t="array" ref="AA54">SUMPRODUCT(--(AA3:AA53=INT(AA3:AA53)),--(AA3:AA53&gt;0))</f>
+        <v>4</v>
+      </c>
+      <c r="AB54" s="195" cm="1">
+        <f t="array" ref="AB54">SUMPRODUCT(--(AB3:AB53=INT(AB3:AB53)),--(AB3:AB53&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="AC54" s="195" cm="1">
+        <f t="array" ref="AC54">SUMPRODUCT(--(AC3:AC53=INT(AC3:AC53)),--(AC3:AC53&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="AD54" s="195" cm="1">
+        <f t="array" ref="AD54">SUMPRODUCT(--(AD3:AD53=INT(AD3:AD53)),--(AD3:AD53&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="AE54" s="195" cm="1">
+        <f t="array" ref="AE54">SUMPRODUCT(--(AE3:AE53=INT(AE3:AE53)),--(AE3:AE53&gt;0))</f>
+        <v>5</v>
+      </c>
+      <c r="AF54" s="195" cm="1">
+        <f t="array" ref="AF54">SUMPRODUCT(--(AF3:AF53=INT(AF3:AF53)),--(AF3:AF53&gt;0))</f>
+        <v>7</v>
+      </c>
+      <c r="AG54" s="195" cm="1">
+        <f t="array" ref="AG54">SUMPRODUCT(--(AG3:AG53=INT(AG3:AG53)),--(AG3:AG53&gt;0))</f>
+        <v>1</v>
+      </c>
+      <c r="AH54" s="195" cm="1">
+        <f t="array" ref="AH54">SUMPRODUCT(--(AH3:AH53=INT(AH3:AH53)),--(AH3:AH53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="AI54" s="195" cm="1">
+        <f t="array" ref="AI54">SUMPRODUCT(--(AI3:AI53=INT(AI3:AI53)),--(AI3:AI53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="AJ54" s="195" cm="1">
+        <f t="array" ref="AJ54">SUMPRODUCT(--(AJ3:AJ53=INT(AJ3:AJ53)),--(AJ3:AJ53&gt;0))</f>
+        <v>18</v>
+      </c>
+      <c r="AK54" s="195" cm="1">
+        <f t="array" ref="AK54">SUMPRODUCT(--(AK3:AK53=INT(AK3:AK53)),--(AK3:AK53&gt;0))</f>
+        <v>6</v>
+      </c>
+      <c r="AL54" s="195" cm="1">
+        <f t="array" ref="AL54">SUMPRODUCT(--(AL3:AL53=INT(AL3:AL53)),--(AL3:AL53&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="AM54" s="195" cm="1">
+        <f t="array" ref="AM54">SUMPRODUCT(--(AM3:AM53=INT(AM3:AM53)),--(AM3:AM53&gt;0))</f>
+        <v>3</v>
+      </c>
+      <c r="AN54" s="195" cm="1">
+        <f t="array" ref="AN54">SUMPRODUCT(--(AN3:AN53=INT(AN3:AN53)),--(AN3:AN53&gt;0))</f>
+        <v>9</v>
+      </c>
+      <c r="AO54" s="195" cm="1">
+        <f t="array" ref="AO54">SUMPRODUCT(--(AO3:AO53=INT(AO3:AO53)),--(AO3:AO53&gt;0))</f>
+        <v>8</v>
+      </c>
+      <c r="AP54" s="195" cm="1">
+        <f t="array" ref="AP54">SUMPRODUCT(--(AP3:AP53=INT(AP3:AP53)),--(AP3:AP53&gt;0))</f>
+        <v>2</v>
+      </c>
+      <c r="AQ54" s="195" cm="1">
+        <f t="array" ref="AQ54">SUMPRODUCT(--(AQ3:AQ53=INT(AQ3:AQ53)),--(AQ3:AQ53&gt;0))</f>
+        <v>6</v>
+      </c>
+      <c r="AR54" s="195" cm="1">
+        <f t="array" ref="AR54">SUMPRODUCT(--(AR3:AR53=INT(AR3:AR53)),--(AR3:AR53&gt;0))</f>
+        <v>15</v>
+      </c>
+      <c r="AS54" s="195" cm="1">
+        <f t="array" ref="AS54">SUMPRODUCT(--(AS3:AS53=INT(AS3:AS53)),--(AS3:AS53&gt;0))</f>
+        <v>10</v>
+      </c>
+      <c r="AT54" s="195" cm="1">
+        <f t="array" ref="AT54">SUMPRODUCT(--(AT3:AT53=INT(AT3:AT53)),--(AT3:AT53&gt;0))</f>
+        <v>9</v>
+      </c>
+      <c r="AU54" s="195" cm="1">
+        <f t="array" ref="AU54">SUMPRODUCT(--(AU3:AU53=INT(AU3:AU53)),--(AU3:AU53&gt;0))</f>
+        <v>15</v>
+      </c>
+      <c r="AV54" s="195" cm="1">
+        <f t="array" ref="AV54">SUMPRODUCT(--(AV3:AV53=INT(AV3:AV53)),--(AV3:AV53&gt;0))</f>
+        <v>8</v>
+      </c>
+      <c r="AW54" s="195" cm="1">
+        <f t="array" ref="AW54">SUMPRODUCT(--(AW3:AW53=INT(AW3:AW53)),--(AW3:AW53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="AX54" s="195" cm="1">
+        <f t="array" ref="AX54">SUMPRODUCT(--(AX3:AX53=INT(AX3:AX53)),--(AX3:AX53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="AY54" s="195" cm="1">
+        <f t="array" ref="AY54">SUMPRODUCT(--(AY3:AY53=INT(AY3:AY53)),--(AY3:AY53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="AZ54" s="195" cm="1">
+        <f t="array" ref="AZ54">SUMPRODUCT(--(AZ3:AZ53=INT(AZ3:AZ53)),--(AZ3:AZ53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="BA54" s="195" cm="1">
+        <f t="array" ref="BA54">SUMPRODUCT(--(BA3:BA53=INT(BA3:BA53)),--(BA3:BA53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="BB54" s="195" cm="1">
+        <f t="array" ref="BB54">SUMPRODUCT(--(BB3:BB53=INT(BB3:BB53)),--(BB3:BB53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="BC54" s="195" cm="1">
+        <f t="array" ref="BC54">SUMPRODUCT(--(BC3:BC53=INT(BC3:BC53)),--(BC3:BC53&gt;0))</f>
+        <v>0</v>
+      </c>
+      <c r="BD54" s="196" t="s">
+        <v>327</v>
+      </c>
+      <c r="BE54" s="197"/>
+      <c r="BF54" s="197"/>
+      <c r="BG54" s="197"/>
+      <c r="BH54" s="197"/>
+      <c r="BI54" s="197"/>
+      <c r="BJ54" s="198"/>
+    </row>
+    <row r="55" s="175" customFormat="1" ht="28" spans="1:62">
+      <c r="A55" s="194" t="s">
+        <v>328</v>
+      </c>
+      <c r="B55" s="195">
+        <f>SUM(B3:B53)</f>
+        <v>11</v>
+      </c>
+      <c r="C55" s="195">
+        <f t="shared" ref="C55:AH55" si="4">SUM(C3:C53)</f>
+        <v>9</v>
+      </c>
+      <c r="D55" s="195">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="E55" s="195">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="F55" s="195">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="G55" s="195">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H55" s="195">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="I55" s="195">
+        <f t="shared" si="4"/>
+        <v>16</v>
+      </c>
+      <c r="J55" s="195">
+        <f t="shared" si="4"/>
+        <v>14</v>
+      </c>
+      <c r="K55" s="195">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="L55" s="195">
+        <f t="shared" si="4"/>
+        <v>12</v>
+      </c>
+      <c r="M55" s="195">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="N55" s="195">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="O55" s="195">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P55" s="195">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q55" s="195">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="R55" s="195">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="S55" s="195">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="T55" s="195">
+        <f t="shared" si="4"/>
+        <v>28</v>
+      </c>
+      <c r="U55" s="195">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="V55" s="195">
+        <f t="shared" si="4"/>
+        <v>13</v>
+      </c>
+      <c r="W55" s="195">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="X55" s="195">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Y55" s="195">
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="Z55" s="195">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AA55" s="195">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="AB55" s="195">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AC55" s="195">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AD55" s="195">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AE55" s="195">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AF55" s="195">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="AG55" s="195">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="AH55" s="195">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AI55" s="195">
+        <f t="shared" ref="AI55:BC55" si="5">SUM(AI3:AI53)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="195">
+        <f t="shared" si="5"/>
+        <v>20</v>
+      </c>
+      <c r="AK55" s="195">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="AL55" s="195">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AM55" s="195">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="AN55" s="195">
+        <f t="shared" si="5"/>
+        <v>11</v>
+      </c>
+      <c r="AO55" s="195">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="AP55" s="195">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="AQ55" s="195">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="AR55" s="195">
+        <f t="shared" si="5"/>
+        <v>18</v>
+      </c>
+      <c r="AS55" s="195">
+        <f t="shared" si="5"/>
+        <v>10</v>
+      </c>
+      <c r="AT55" s="195">
+        <f t="shared" si="5"/>
+        <v>9</v>
+      </c>
+      <c r="AU55" s="195">
+        <f t="shared" si="5"/>
+        <v>23</v>
+      </c>
+      <c r="AV55" s="195">
+        <f t="shared" si="5"/>
+        <v>8</v>
+      </c>
+      <c r="AW55" s="195">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AX55" s="195">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AY55" s="195">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AZ55" s="195">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BA55" s="195">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BB55" s="195">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BC55" s="195">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="BD55" s="199"/>
+      <c r="BE55" s="200"/>
+      <c r="BF55" s="200"/>
+      <c r="BG55" s="200"/>
+      <c r="BH55" s="200"/>
+      <c r="BI55" s="200"/>
+      <c r="BJ55" s="201"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B1:S1"/>
     <mergeCell ref="T1:AI1"/>
     <mergeCell ref="AJ1:AL1"/>
     <mergeCell ref="AM1:BC1"/>
     <mergeCell ref="BD1:BJ1"/>
     <mergeCell ref="A1:A2"/>
+    <mergeCell ref="BD54:BJ55"/>
   </mergeCells>
+  <conditionalFormatting sqref="B54:BC54">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="6" tint="0.8"/>
+        <color theme="6" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B55:BC55">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="6" tint="0.8"/>
+        <color theme="6" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="T3:T53">
-    <cfRule type="colorScale" priority="129">
+    <cfRule type="colorScale" priority="131">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="132">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3:U53">
+    <cfRule type="colorScale" priority="118">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -14729,7 +15347,25 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3:U53">
+  <conditionalFormatting sqref="V3:V53">
+    <cfRule type="colorScale" priority="117">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="129">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W3:W53">
     <cfRule type="colorScale" priority="116">
       <colorScale>
         <cfvo type="min"/>
@@ -14747,7 +15383,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V3:V53">
+  <conditionalFormatting sqref="X3:X53">
     <cfRule type="colorScale" priority="115">
       <colorScale>
         <cfvo type="min"/>
@@ -14765,7 +15401,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W3:W53">
+  <conditionalFormatting sqref="Y3:Y53">
     <cfRule type="colorScale" priority="114">
       <colorScale>
         <cfvo type="min"/>
@@ -14783,7 +15419,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X3:X53">
+  <conditionalFormatting sqref="Z3:Z53">
     <cfRule type="colorScale" priority="113">
       <colorScale>
         <cfvo type="min"/>
@@ -14801,7 +15437,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y3:Y53">
+  <conditionalFormatting sqref="AA3:AA53">
     <cfRule type="colorScale" priority="112">
       <colorScale>
         <cfvo type="min"/>
@@ -14819,7 +15455,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z3:Z53">
+  <conditionalFormatting sqref="AB3:AB53">
     <cfRule type="colorScale" priority="111">
       <colorScale>
         <cfvo type="min"/>
@@ -14837,7 +15473,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA3:AA53">
+  <conditionalFormatting sqref="AC3:AC53">
     <cfRule type="colorScale" priority="110">
       <colorScale>
         <cfvo type="min"/>
@@ -14855,7 +15491,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB3:AB53">
+  <conditionalFormatting sqref="AD3:AD53">
     <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
@@ -14873,7 +15509,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC3:AC53">
+  <conditionalFormatting sqref="AE3:AE53">
     <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="min"/>
@@ -14891,7 +15527,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD3:AD53">
+  <conditionalFormatting sqref="AF3:AF53">
     <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
@@ -14909,8 +15545,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE3:AE53">
-    <cfRule type="colorScale" priority="106">
+  <conditionalFormatting sqref="AG3:AG53">
+    <cfRule type="colorScale" priority="100">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -14918,7 +15562,25 @@
         <color theme="4" tint="-0.25"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="118">
+    <cfRule type="colorScale" priority="92">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="88">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH3:AH53">
+    <cfRule type="colorScale" priority="99">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -14926,9 +15588,7 @@
         <color theme="4" tint="0.8"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF3:AF53">
-    <cfRule type="colorScale" priority="105">
+    <cfRule type="colorScale" priority="95">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -14936,21 +15596,37 @@
         <color theme="4" tint="-0.25"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="117">
+    <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color theme="4" tint="-0.25"/>
+        <color theme="4"/>
         <color theme="4" tint="0.8"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG3:AG53">
-    <cfRule type="colorScale" priority="98">
+    <cfRule type="colorScale" priority="87">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI3:AI53">
+    <cfRule type="colorScale" priority="86">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="90">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4"/>
         <color theme="4" tint="0.8"/>
       </colorScale>
     </cfRule>
@@ -14962,83 +15638,7 @@
         <color theme="4" tint="-0.25"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="90">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4"/>
-        <color theme="4" tint="0.8"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="86">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AH3:AH53">
-    <cfRule type="colorScale" priority="97">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="-0.25"/>
-        <color theme="4" tint="0.8"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="93">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4" tint="-0.25"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="89">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4"/>
-        <color theme="4" tint="0.8"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="85">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI3:AI53">
-    <cfRule type="colorScale" priority="84">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="88">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4"/>
-        <color theme="4" tint="0.8"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="92">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4" tint="-0.25"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="96">
+    <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15048,6 +15648,74 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ3:AJ53">
+    <cfRule type="colorScale" priority="84">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="64">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK3:AK53">
+    <cfRule type="colorScale" priority="83">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="-0.25"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="63">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4" tint="-0.25"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4"/>
+        <color theme="4" tint="0.8"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="4" tint="0.8"/>
+        <color theme="4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL3:AL53">
     <cfRule type="colorScale" priority="82">
       <colorScale>
         <cfvo type="min"/>
@@ -15081,7 +15749,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK3:AK53">
+  <conditionalFormatting sqref="AM3:AM53">
     <cfRule type="colorScale" priority="81">
       <colorScale>
         <cfvo type="min"/>
@@ -15115,7 +15783,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL3:AL53">
+  <conditionalFormatting sqref="AN3:AN53">
     <cfRule type="colorScale" priority="80">
       <colorScale>
         <cfvo type="min"/>
@@ -15149,7 +15817,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM3:AM53">
+  <conditionalFormatting sqref="AO3:AO53">
     <cfRule type="colorScale" priority="79">
       <colorScale>
         <cfvo type="min"/>
@@ -15183,7 +15851,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN3:AN53">
+  <conditionalFormatting sqref="AP3:AP53">
     <cfRule type="colorScale" priority="78">
       <colorScale>
         <cfvo type="min"/>
@@ -15217,7 +15885,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO3:AO53">
+  <conditionalFormatting sqref="AQ3:AQ53">
     <cfRule type="colorScale" priority="77">
       <colorScale>
         <cfvo type="min"/>
@@ -15251,7 +15919,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AP3:AP53">
+  <conditionalFormatting sqref="AR3:AR53">
     <cfRule type="colorScale" priority="76">
       <colorScale>
         <cfvo type="min"/>
@@ -15285,7 +15953,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AQ3:AQ53">
+  <conditionalFormatting sqref="AS3:AS53">
     <cfRule type="colorScale" priority="75">
       <colorScale>
         <cfvo type="min"/>
@@ -15319,7 +15987,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AR3:AR53">
+  <conditionalFormatting sqref="AT3:AT53">
     <cfRule type="colorScale" priority="74">
       <colorScale>
         <cfvo type="min"/>
@@ -15353,7 +16021,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AS3:AS53">
+  <conditionalFormatting sqref="AU3:AU53">
     <cfRule type="colorScale" priority="73">
       <colorScale>
         <cfvo type="min"/>
@@ -15387,7 +16055,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AT3:AT53">
+  <conditionalFormatting sqref="AV3:AV53">
     <cfRule type="colorScale" priority="72">
       <colorScale>
         <cfvo type="min"/>
@@ -15421,7 +16089,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AU3:AU53">
+  <conditionalFormatting sqref="AW3:AW53">
     <cfRule type="colorScale" priority="71">
       <colorScale>
         <cfvo type="min"/>
@@ -15455,7 +16123,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV3:AV53">
+  <conditionalFormatting sqref="AX3:AX53">
     <cfRule type="colorScale" priority="70">
       <colorScale>
         <cfvo type="min"/>
@@ -15489,7 +16157,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AW3:AW53">
+  <conditionalFormatting sqref="AY3:AY53">
     <cfRule type="colorScale" priority="69">
       <colorScale>
         <cfvo type="min"/>
@@ -15523,7 +16191,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AX3:AX53">
+  <conditionalFormatting sqref="AZ3:AZ53">
     <cfRule type="colorScale" priority="68">
       <colorScale>
         <cfvo type="min"/>
@@ -15557,7 +16225,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AY3:AY53">
+  <conditionalFormatting sqref="BA3:BA53">
     <cfRule type="colorScale" priority="67">
       <colorScale>
         <cfvo type="min"/>
@@ -15591,7 +16259,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AZ3:AZ53">
+  <conditionalFormatting sqref="BB3:BB53">
     <cfRule type="colorScale" priority="66">
       <colorScale>
         <cfvo type="min"/>
@@ -15625,7 +16293,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BA3:BA53">
+  <conditionalFormatting sqref="BC3:BC53">
     <cfRule type="colorScale" priority="65">
       <colorScale>
         <cfvo type="min"/>
@@ -15659,76 +16327,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BB3:BB53">
-    <cfRule type="colorScale" priority="64">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="-0.25"/>
-        <color theme="4" tint="0.8"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4" tint="-0.25"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4"/>
-        <color theme="4" tint="0.8"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="BC3:BC53">
-    <cfRule type="colorScale" priority="63">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="-0.25"/>
-        <color theme="4" tint="0.8"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="43">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4" tint="-0.25"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4"/>
-        <color theme="4" tint="0.8"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color theme="4" tint="0.8"/>
-        <color theme="4"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="BH3:BH53">
-    <cfRule type="colorScale" priority="103">
+    <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15736,7 +16336,7 @@
         <color theme="9" tint="0.8"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="104">
+    <cfRule type="colorScale" priority="106">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15746,7 +16346,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI3:BI53">
-    <cfRule type="colorScale" priority="102">
+    <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15756,7 +16356,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ3:BJ53">
-    <cfRule type="colorScale" priority="101">
+    <cfRule type="colorScale" priority="103">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15766,7 +16366,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:S53">
-    <cfRule type="colorScale" priority="131">
+    <cfRule type="colorScale" priority="133">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15774,7 +16374,7 @@
         <color theme="4" tint="-0.25"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="132">
+    <cfRule type="colorScale" priority="134">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15784,7 +16384,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:AF53">
-    <cfRule type="colorScale" priority="99">
+    <cfRule type="colorScale" priority="101">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15792,7 +16392,7 @@
         <color theme="4"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="100">
+    <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15802,7 +16402,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:BC53">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="1"/>
         <cfvo type="num" val="3"/>
@@ -15812,7 +16412,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:BC53">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -15825,8 +16425,8 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BJ8 Y9:BJ10 A11:BJ53" formulaRange="1"/>
-    <ignoredError sqref="A9:X10 Z3:AF3 A2:AF2 A39:AF39 A37:AF37 A12:X15 Z49:AF49 BH23:BJ29 BI35:BJ35 BH36:BJ39 BH24:BJ28 BH11:BJ14 Z10:AF10 BI9:BJ9 BH6:BJ8 BH4:BJ5 Z41:AE42 Z4:AE4 A5:AF7 A8:V8 X8:AF8 AF50 A50:AD50 A51:AF53 AE48 Z48:AB48 A48:X49 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 A42:X42 A40:V40 AC40:AD40 BI3 BD1:BJ2 A3:X4 AD38:AF38 Z38:AB38 A38:X38 Z36:AF36 A36:X36 A34:AF35 Z29:AF29 A29:X33 A28:X28 A26:AF27 Z24:AF25 A24:X25 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 AE11 AB11:AC11 A11:Z11 U1:AF1 C1:S1 A1 Z9:AB9 AD9:AF9 X41" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A1:BJ40 A41:W41 Y41:BJ41 A42:BJ55" formulaRange="1"/>
+    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 A1 C1:S1 U1:AF1 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z29:AF29 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 A3:X4 BD1:BJ2 BI3 AC40:AD40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 A48:X49 Z48:AB48 AE48 A51:AF53 A50:AD50 AF50 X8:AF8 A8:V8 A5:AF7 Z4:AE4 Z41:AE42 BH4:BJ8 BI9:BJ9 Z10:AF10 BH11:BJ14 BH36:BJ39 BI35:BJ35 BH24:BJ28 Z49:AF49 A12:X15 A37:AF37 A39:AF39 A2:AF2 Z3:AF3 A9:X10" formulaRange="1" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -15873,21 +16473,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="149" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B2" s="153" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C2" s="154" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D2" s="155"/>
       <c r="E2" s="153" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="F2" s="153"/>
       <c r="G2" s="156" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="H2" s="148"/>
       <c r="I2" s="148"/>
@@ -15895,10 +16495,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="149" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B3" s="158" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C3" s="158"/>
       <c r="D3" s="158"/>
@@ -15911,7 +16511,7 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="149" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B4" s="159" t="s">
         <v>247</v>
@@ -15927,7 +16527,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="149" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B5" s="160">
         <v>1</v>
@@ -15947,7 +16547,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="149" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="B6" s="162">
         <v>1</v>
@@ -15957,7 +16557,7 @@
       <c r="E6" s="162"/>
       <c r="F6" s="162"/>
       <c r="G6" s="163" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="H6" s="148"/>
       <c r="I6" s="148"/>
@@ -15965,10 +16565,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="149" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B7" s="164" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C7" s="164"/>
       <c r="D7" s="164"/>
@@ -15983,14 +16583,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="149" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B8" s="166">
         <v>1</v>
       </c>
       <c r="C8" s="166"/>
       <c r="D8" s="167" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
@@ -16001,10 +16601,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="149" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B9" s="153" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C9" s="153"/>
       <c r="D9" s="153"/>
@@ -16017,23 +16617,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="149" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B10" s="158">
         <v>1</v>
       </c>
       <c r="C10" s="158"/>
       <c r="D10" s="168" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="E10" s="158">
         <v>1</v>
       </c>
       <c r="F10" s="168" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="G10" s="148" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="H10" s="148"/>
       <c r="I10" s="148"/>
@@ -16041,7 +16641,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="149" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B11" s="159">
         <v>1</v>
@@ -16057,7 +16657,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="149" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B12" s="160">
         <v>1</v>
@@ -16075,17 +16675,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="149" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="169" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -16093,10 +16693,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="149" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B14" s="171" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C14" s="171"/>
       <c r="D14" s="171"/>
@@ -16171,7 +16771,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -16196,10 +16796,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -16212,7 +16812,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -16236,7 +16836,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -16249,7 +16849,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
@@ -16279,7 +16879,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16294,7 +16894,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -16307,7 +16907,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -16320,7 +16920,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>72</v>
@@ -16332,10 +16932,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>91</v>
@@ -16361,10 +16961,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="142"/>
       <c r="B14" s="136" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="D14" s="143"/>
       <c r="E14" s="138"/>
@@ -16376,7 +16976,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="142"/>
       <c r="B15" s="136" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -16400,7 +17000,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="142"/>
       <c r="B17" s="136" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -16413,7 +17013,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="142"/>
       <c r="B18" s="136" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -16426,7 +17026,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="142"/>
       <c r="B19" s="136" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>84</v>
@@ -16439,7 +17039,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="142"/>
       <c r="B20" s="136" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>87</v>
@@ -16452,7 +17052,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="142"/>
       <c r="B21" s="136" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C21" s="144"/>
       <c r="D21" s="145"/>
@@ -16465,7 +17065,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="146"/>
       <c r="B22" s="136" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C22" s="144"/>
       <c r="D22" s="147"/>
@@ -16528,7 +17128,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -16559,7 +17159,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -16751,7 +17351,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -16943,7 +17543,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -17170,10 +17770,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>203</v>
@@ -17184,208 +17784,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -17393,118 +17993,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -17512,138 +18112,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -997,7 +997,7 @@
   <si>
     <t>课件：“Emm,then you will have to take some ()”任务：listen and repeat。
 听完本句录音，学生大声朗读“emm”，空格处说不出来。刘老师：注意力不在重点、刚才崔宇臣/林芷琪笑、不止“emm”，其他也一样、态度
-重来，学生顺利读出“foreign money”。刘老师：都能说出来
+重来，学生顺利读出“foreign cash”。刘老师：都能说出来
 接下来顺利读完。刘老师：集中注意力就不会拖拉停顿、命令执行效率（circle/underline/repeat）、80%学生认识circle（认识的举手），但执行时（第一遍：10个左右成绩好学生完成；第二遍：要去催的人完成；第三遍：提醒蔡华楷、薛阅晨、崔宇臣等人，王淮等人可进行下一步骤）、刚才段长公开课无拖拉，说明是能专心的、课程紧迫，但这样导致无法完成课时、吸收效率（有人90%吸收，有人10%但晚上努力背诵，却无效果）、笔记本不要合上/笔拿手上：频繁拿笔效率低，细节问题不容忽视、注意力集中的方法（take notes/answer the questions aloud）</t>
   </si>
   <si>
@@ -1100,6 +1100,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>数学课情人记录</t>
     </r>
     <r>
@@ -3361,12 +3367,7 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3374,15 +3375,20 @@
       <charset val="134"/>
     </font>
     <font>
+      <strike/>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
-      <strike/>
       <sz val="11"/>
       <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -4169,7 +4175,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4757,9 +4763,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5237,538 +5240,538 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="232" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="233" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="234" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="235"/>
+    <col min="1" max="1" width="7.59090909090909" style="231" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="232" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="233" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="234"/>
   </cols>
   <sheetData>
-    <row r="1" s="231" customFormat="1" spans="1:10">
-      <c r="A1" s="236" t="s">
+    <row r="1" s="230" customFormat="1" spans="1:10">
+      <c r="A1" s="235" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="237" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="237" t="s">
+      <c r="B1" s="236" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="236" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="237" t="s">
+      <c r="D1" s="236" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="237" t="s">
+      <c r="E1" s="236" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="237" t="s">
+      <c r="F1" s="236" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="237" t="s">
+      <c r="G1" s="236" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="238"/>
-      <c r="I1" s="238"/>
-      <c r="J1" s="238"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="237"/>
+      <c r="J1" s="237"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="239" t="s">
+      <c r="A2" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="232" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="232" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="239" t="s">
+      <c r="A3" s="238" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="232" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="233" t="s">
+      <c r="D3" s="232" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="239" t="s">
+      <c r="A4" s="238" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="233" t="s">
+      <c r="D4" s="232" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="239" t="s">
+      <c r="A5" s="238" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="233" t="s">
+      <c r="C5" s="232" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="233" t="s">
+      <c r="D5" s="232" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="239" t="s">
+      <c r="A6" s="238" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="233" t="s">
+      <c r="C6" s="232" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="239" t="s">
+      <c r="A7" s="238" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="233" t="s">
+      <c r="B7" s="232" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="233" t="s">
+      <c r="C7" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="233" t="s">
+      <c r="D7" s="232" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="239" t="s">
+      <c r="A8" s="238" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="233" t="s">
+      <c r="D8" s="232" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="239" t="s">
+      <c r="A9" s="238" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="239" t="s">
+      <c r="A10" s="238" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="233" t="s">
+      <c r="B10" s="232" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="239" t="s">
+      <c r="A11" s="238" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="239" t="s">
+      <c r="A12" s="238" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="239" t="s">
+      <c r="A13" s="238" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="233" t="s">
+      <c r="D13" s="232" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="239" t="s">
+      <c r="A14" s="238" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="233" t="s">
+      <c r="B14" s="232" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="239" t="s">
+      <c r="A15" s="238" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="239" t="s">
+      <c r="A16" s="238" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="233" t="s">
+      <c r="C16" s="232" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:5">
-      <c r="A17" s="239" t="s">
+      <c r="A17" s="238" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="233" t="s">
+      <c r="C17" s="232" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="239" t="s">
+      <c r="A18" s="238" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="233" t="s">
+      <c r="D18" s="232" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:5">
-      <c r="A19" s="239" t="s">
+      <c r="A19" s="238" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="233" t="s">
+      <c r="D19" s="232" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:5">
-      <c r="A20" s="239" t="s">
+      <c r="A20" s="238" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="233" t="s">
+      <c r="B20" s="232" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="233" t="s">
+      <c r="C20" s="232" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:5">
-      <c r="A21" s="239" t="s">
+      <c r="A21" s="238" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="232" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="233" t="s">
+      <c r="C21" s="232" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="233" t="s">
+      <c r="D21" s="232" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="239" t="s">
+      <c r="A22" s="238" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:5">
-      <c r="A23" s="239" t="s">
+      <c r="A23" s="238" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="233" t="s">
+      <c r="B23" s="232" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:5">
-      <c r="A24" s="239" t="s">
+      <c r="A24" s="238" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="233" t="s">
+      <c r="B24" s="232" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="233" t="s">
+      <c r="C24" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="233" t="s">
+      <c r="D24" s="232" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="239" t="s">
+      <c r="A25" s="238" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="239" t="s">
+      <c r="A26" s="238" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="239" t="s">
+      <c r="A27" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="233" t="s">
+      <c r="B27" s="232" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="233" t="s">
+      <c r="C27" s="232" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:5">
-      <c r="A28" s="239" t="s">
+      <c r="A28" s="238" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="233" t="s">
+      <c r="B28" s="232" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="233" t="s">
+      <c r="C28" s="232" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="233" t="s">
+      <c r="D28" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="233" t="s">
+      <c r="E28" s="232" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="239" t="s">
+      <c r="A29" s="238" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="239" t="s">
+      <c r="A30" s="238" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="233" t="s">
+      <c r="B30" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="233" t="s">
+      <c r="C30" s="232" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="239" t="s">
+      <c r="A31" s="238" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="239" t="s">
+      <c r="A32" s="238" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="239" t="s">
+      <c r="A33" s="238" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="239" t="s">
+      <c r="A34" s="238" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="239" t="s">
+      <c r="A35" s="238" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="239" t="s">
+      <c r="A36" s="238" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="233" t="s">
+      <c r="B36" s="232" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="239" t="s">
+      <c r="A37" s="238" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="233" t="s">
+      <c r="C37" s="232" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="233" t="s">
+      <c r="D37" s="232" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="239" t="s">
+      <c r="A38" s="238" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="233" t="s">
+      <c r="B38" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="240"/>
-      <c r="D38" s="240"/>
-      <c r="E38" s="240"/>
-      <c r="F38" s="240"/>
-      <c r="G38" s="240"/>
+      <c r="C38" s="239"/>
+      <c r="D38" s="239"/>
+      <c r="E38" s="239"/>
+      <c r="F38" s="239"/>
+      <c r="G38" s="239"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="239" t="s">
+      <c r="A39" s="238" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="233" t="s">
+      <c r="C39" s="232" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="233" t="s">
+      <c r="D39" s="232" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="239" t="s">
+      <c r="A40" s="238" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="233" t="s">
+      <c r="B40" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="233" t="s">
+      <c r="C40" s="232" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="233" t="s">
+      <c r="D40" s="232" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="239" t="s">
+      <c r="A41" s="238" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="233" t="s">
+      <c r="C41" s="232" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="233" t="s">
+      <c r="D41" s="232" t="s">
         <v>93</v>
       </c>
-      <c r="E41" s="233" t="s">
+      <c r="E41" s="232" t="s">
         <v>94</v>
       </c>
-      <c r="H41" s="234" t="s">
+      <c r="H41" s="233" t="s">
         <v>95</v>
       </c>
-      <c r="I41" s="234" t="s">
+      <c r="I41" s="233" t="s">
         <v>96</v>
       </c>
-      <c r="J41" s="234" t="s">
+      <c r="J41" s="233" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="239" t="s">
+      <c r="A42" s="238" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="239" t="s">
+      <c r="A43" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="233" t="s">
+      <c r="B43" s="232" t="s">
         <v>100</v>
       </c>
-      <c r="H43" s="234" t="s">
+      <c r="H43" s="233" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="239" t="s">
+      <c r="A44" s="238" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="233" t="s">
+      <c r="B44" s="232" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="239" t="s">
+      <c r="A45" s="238" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="233" t="s">
+      <c r="C45" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="233" t="s">
+      <c r="D45" s="232" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="239" t="s">
+      <c r="A46" s="238" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="239" t="s">
+      <c r="A47" s="238" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="233" t="s">
+      <c r="D47" s="232" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="239" t="s">
+      <c r="A48" s="238" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="233" t="s">
+      <c r="C48" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="D48" s="233" t="s">
+      <c r="D48" s="232" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="239" t="s">
+      <c r="A49" s="238" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="239" t="s">
+      <c r="A50" s="238" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="233" t="s">
+      <c r="C50" s="232" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="239" t="s">
+      <c r="A51" s="238" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="239" t="s">
+      <c r="A52" s="238" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="233" t="s">
+      <c r="B52" s="232" t="s">
         <v>118</v>
       </c>
-      <c r="C52" s="233" t="s">
+      <c r="C52" s="232" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="233" t="s">
+      <c r="E52" s="232" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="232" t="s">
+      <c r="A53" s="231" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="233" t="s">
+      <c r="B53" s="232" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="240"/>
-      <c r="E53" s="240"/>
-      <c r="F53" s="240"/>
-      <c r="G53" s="240"/>
+      <c r="D53" s="239"/>
+      <c r="E53" s="239"/>
+      <c r="F53" s="239"/>
+      <c r="G53" s="239"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="232" t="s">
+      <c r="A54" s="231" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="233" t="s">
+      <c r="B54" s="232" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="233" t="s">
+      <c r="C54" s="232" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="240"/>
-      <c r="E54" s="240"/>
-      <c r="F54" s="240"/>
-      <c r="G54" s="240"/>
+      <c r="D54" s="239"/>
+      <c r="E54" s="239"/>
+      <c r="F54" s="239"/>
+      <c r="G54" s="239"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="232" t="s">
+      <c r="A55" s="231" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="240"/>
-      <c r="C55" s="240"/>
-      <c r="D55" s="233" t="s">
+      <c r="B55" s="239"/>
+      <c r="C55" s="239"/>
+      <c r="D55" s="232" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="232" t="s">
+      <c r="A56" s="231" t="s">
         <v>128</v>
       </c>
       <c r="B56" s="78" t="s">
         <v>129</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="233" t="s">
+      <c r="D56" s="232" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="232" t="s">
+      <c r="A57" s="231" t="s">
         <v>131</v>
       </c>
       <c r="B57" s="78" t="s">
@@ -5777,76 +5780,76 @@
       <c r="C57" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="233" t="s">
+      <c r="D57" s="232" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="232" t="s">
+      <c r="A58" s="231" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="233" t="s">
+      <c r="B58" s="232" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="240"/>
-      <c r="D58" s="240"/>
-      <c r="E58" s="240"/>
-      <c r="F58" s="240"/>
-      <c r="G58" s="240"/>
+      <c r="C58" s="239"/>
+      <c r="D58" s="239"/>
+      <c r="E58" s="239"/>
+      <c r="F58" s="239"/>
+      <c r="G58" s="239"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="232" t="s">
+      <c r="A59" s="231" t="s">
         <v>137</v>
       </c>
-      <c r="B59" s="240"/>
-      <c r="C59" s="233" t="s">
+      <c r="B59" s="239"/>
+      <c r="C59" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="D59" s="240"/>
-      <c r="E59" s="240"/>
-      <c r="F59" s="240"/>
-      <c r="G59" s="240"/>
+      <c r="D59" s="239"/>
+      <c r="E59" s="239"/>
+      <c r="F59" s="239"/>
+      <c r="G59" s="239"/>
     </row>
     <row r="60" ht="65" spans="1:7">
-      <c r="A60" s="232" t="s">
+      <c r="A60" s="231" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="240" t="s">
+      <c r="B60" s="239" t="s">
         <v>140</v>
       </c>
-      <c r="C60" s="240"/>
-      <c r="D60" s="233" t="s">
+      <c r="C60" s="239"/>
+      <c r="D60" s="232" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="232" t="s">
+      <c r="A61" s="231" t="s">
         <v>142</v>
       </c>
       <c r="B61" s="78" t="s">
         <v>143</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="240"/>
-      <c r="E61" s="240"/>
-      <c r="F61" s="240"/>
-      <c r="G61" s="240"/>
+      <c r="D61" s="239"/>
+      <c r="E61" s="239"/>
+      <c r="F61" s="239"/>
+      <c r="G61" s="239"/>
     </row>
     <row r="62" ht="52" spans="1:7">
-      <c r="A62" s="232" t="s">
+      <c r="A62" s="231" t="s">
         <v>144</v>
       </c>
-      <c r="B62" s="240"/>
-      <c r="C62" s="240"/>
-      <c r="D62" s="233" t="s">
+      <c r="B62" s="239"/>
+      <c r="C62" s="239"/>
+      <c r="D62" s="232" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="233" t="s">
+      <c r="E62" s="232" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="232" t="s">
+      <c r="A63" s="231" t="s">
         <v>147</v>
       </c>
       <c r="B63" s="78" t="s">
@@ -5855,66 +5858,66 @@
       <c r="C63" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="240"/>
-      <c r="E63" s="240"/>
-      <c r="F63" s="240"/>
-      <c r="G63" s="240"/>
+      <c r="D63" s="239"/>
+      <c r="E63" s="239"/>
+      <c r="F63" s="239"/>
+      <c r="G63" s="239"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="232" t="s">
+      <c r="A64" s="231" t="s">
         <v>150</v>
       </c>
-      <c r="B64" s="240"/>
-      <c r="C64" s="240"/>
-      <c r="D64" s="233" t="s">
+      <c r="B64" s="239"/>
+      <c r="C64" s="239"/>
+      <c r="D64" s="232" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="232" t="s">
+      <c r="A65" s="231" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="241" t="s">
+      <c r="B65" s="240" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="240"/>
-      <c r="D65" s="240"/>
-      <c r="E65" s="240"/>
-      <c r="F65" s="240"/>
-      <c r="G65" s="240"/>
+      <c r="C65" s="239"/>
+      <c r="D65" s="239"/>
+      <c r="E65" s="239"/>
+      <c r="F65" s="239"/>
+      <c r="G65" s="239"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="232" t="s">
+      <c r="A66" s="231" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="240"/>
-      <c r="C66" s="233" t="s">
+      <c r="B66" s="239"/>
+      <c r="C66" s="232" t="s">
         <v>155</v>
       </c>
-      <c r="D66" s="240"/>
-      <c r="E66" s="240"/>
-      <c r="F66" s="240"/>
-      <c r="G66" s="240"/>
+      <c r="D66" s="239"/>
+      <c r="E66" s="239"/>
+      <c r="F66" s="239"/>
+      <c r="G66" s="239"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="232" t="s">
+      <c r="A67" s="231" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="240"/>
-      <c r="C67" s="240"/>
+      <c r="B67" s="239"/>
+      <c r="C67" s="239"/>
     </row>
     <row r="68" ht="78" spans="1:7">
-      <c r="A68" s="232" t="s">
+      <c r="A68" s="231" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="240"/>
-      <c r="C68" s="240"/>
-      <c r="D68" s="233" t="s">
+      <c r="B68" s="239"/>
+      <c r="C68" s="239"/>
+      <c r="D68" s="232" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="232" t="s">
+      <c r="A69" s="231" t="s">
         <v>159</v>
       </c>
       <c r="B69" s="78" t="s">
@@ -5923,89 +5926,89 @@
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="232" t="s">
+      <c r="A70" s="231" t="s">
         <v>161</v>
       </c>
       <c r="B70" s="78" t="s">
         <v>162</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="240"/>
-      <c r="E70" s="240"/>
-      <c r="F70" s="240"/>
-      <c r="G70" s="240"/>
+      <c r="D70" s="239"/>
+      <c r="E70" s="239"/>
+      <c r="F70" s="239"/>
+      <c r="G70" s="239"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="232" t="s">
+      <c r="A71" s="231" t="s">
         <v>163</v>
       </c>
-      <c r="B71" s="240"/>
-      <c r="C71" s="240"/>
+      <c r="B71" s="239"/>
+      <c r="C71" s="239"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="232" t="s">
+      <c r="A72" s="231" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="233" t="s">
+      <c r="B72" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="C72" s="233" t="s">
+      <c r="C72" s="232" t="s">
         <v>166</v>
       </c>
-      <c r="D72" s="240"/>
-      <c r="E72" s="240"/>
-      <c r="F72" s="240"/>
-      <c r="G72" s="240"/>
+      <c r="D72" s="239"/>
+      <c r="E72" s="239"/>
+      <c r="F72" s="239"/>
+      <c r="G72" s="239"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="232" t="s">
+      <c r="A73" s="231" t="s">
         <v>167</v>
       </c>
-      <c r="B73" s="240"/>
-      <c r="C73" s="233" t="s">
+      <c r="B73" s="239"/>
+      <c r="C73" s="232" t="s">
         <v>168</v>
       </c>
-      <c r="D73" s="240"/>
-      <c r="E73" s="240"/>
-      <c r="F73" s="240"/>
-      <c r="G73" s="240"/>
+      <c r="D73" s="239"/>
+      <c r="E73" s="239"/>
+      <c r="F73" s="239"/>
+      <c r="G73" s="239"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="232" t="s">
+      <c r="A74" s="231" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="232" t="s">
+      <c r="A75" s="231" t="s">
         <v>170</v>
       </c>
-      <c r="D75" s="240"/>
-      <c r="E75" s="240"/>
-      <c r="F75" s="240"/>
-      <c r="G75" s="240"/>
+      <c r="D75" s="239"/>
+      <c r="E75" s="239"/>
+      <c r="F75" s="239"/>
+      <c r="G75" s="239"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="232" t="s">
+      <c r="A76" s="231" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="240"/>
-      <c r="C76" s="240"/>
-      <c r="D76" s="233" t="s">
+      <c r="B76" s="239"/>
+      <c r="C76" s="239"/>
+      <c r="D76" s="232" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="232" t="s">
+      <c r="A77" s="231" t="s">
         <v>173</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="242" t="s">
+      <c r="A78" s="241" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="233" t="s">
+      <c r="B78" s="232" t="s">
         <v>175</v>
       </c>
     </row>
@@ -8355,14 +8358,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="226" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="225" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="227"/>
+    <col min="8" max="16384" width="8.72727272727273" style="226"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="228"/>
+      <c r="A1" s="227"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8382,8 +8385,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="225" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="229" t="s">
+    <row r="2" s="224" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="228" t="s">
         <v>176</v>
       </c>
       <c r="B2" s="78"/>
@@ -8396,7 +8399,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="230" t="s">
+      <c r="A3" s="229" t="s">
         <v>178</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8404,7 +8407,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="230" t="s">
+      <c r="A4" s="229" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8415,7 +8418,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="230" t="s">
+      <c r="A5" s="229" t="s">
         <v>183</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8426,7 +8429,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="230" t="s">
+      <c r="A6" s="229" t="s">
         <v>186</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8437,7 +8440,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="230" t="s">
+      <c r="A7" s="229" t="s">
         <v>189</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8445,127 +8448,127 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="230"/>
+      <c r="A8" s="229"/>
       <c r="D8" s="66" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="230"/>
+      <c r="A9" s="229"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="230"/>
+      <c r="A10" s="229"/>
       <c r="B10" s="66" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="230"/>
+      <c r="A11" s="229"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="230"/>
+      <c r="A12" s="229"/>
       <c r="B12" s="66" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="230"/>
+      <c r="A13" s="229"/>
       <c r="B13" s="66" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="230"/>
+      <c r="A14" s="229"/>
       <c r="B14" s="66" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="230"/>
+      <c r="A15" s="229"/>
       <c r="B15" s="66" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="230"/>
+      <c r="A16" s="229"/>
       <c r="B16" s="66" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="230"/>
+      <c r="A17" s="229"/>
       <c r="B17" s="66" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="230"/>
+      <c r="A18" s="229"/>
       <c r="B18" s="66" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:2">
-      <c r="A19" s="230"/>
+      <c r="A19" s="229"/>
       <c r="B19" s="78" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="230"/>
+      <c r="A20" s="229"/>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="230"/>
+      <c r="A21" s="229"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="230"/>
+      <c r="A22" s="229"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="230"/>
+      <c r="A23" s="229"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="230"/>
+      <c r="A24" s="229"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="230"/>
+      <c r="A25" s="229"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="230"/>
+      <c r="A26" s="229"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="230"/>
+      <c r="A27" s="229"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="230"/>
+      <c r="A28" s="229"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="230"/>
+      <c r="A29" s="229"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="230"/>
+      <c r="A30" s="229"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="230"/>
+      <c r="A31" s="229"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="230"/>
+      <c r="A32" s="229"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="230"/>
+      <c r="A33" s="229"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="230"/>
+      <c r="A34" s="229"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="230"/>
+      <c r="A35" s="229"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="230"/>
+      <c r="A36" s="229"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="230"/>
+      <c r="A37" s="229"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="230"/>
+      <c r="A38" s="229"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8574,7 +8577,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="230"/>
+      <c r="A39" s="229"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8583,40 +8586,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="230"/>
+      <c r="A40" s="229"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="230"/>
+      <c r="A41" s="229"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="230"/>
+      <c r="A42" s="229"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="230"/>
+      <c r="A43" s="229"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="230"/>
+      <c r="A44" s="229"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="230"/>
+      <c r="A45" s="229"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="230"/>
+      <c r="A46" s="229"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="230"/>
+      <c r="A47" s="229"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="230"/>
+      <c r="A48" s="229"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="230"/>
+      <c r="A49" s="229"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="230"/>
+      <c r="A50" s="229"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="230"/>
+      <c r="A51" s="229"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8632,510 +8635,510 @@
   <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="216" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="216" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="216" customWidth="1"/>
+    <col min="1" max="1" width="24" style="215" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="215" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="215" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="215" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="217" t="s">
+    <row r="1" s="214" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="216" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="217" t="s">
+      <c r="B1" s="216" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="217" t="s">
+      <c r="C1" s="216" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="218" t="s">
+      <c r="A2" s="217" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="218" t="s">
+      <c r="B2" s="217" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="218" t="s">
+      <c r="C2" s="217" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="218" t="s">
+      <c r="A3" s="217" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="218" t="s">
+      <c r="B3" s="217" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="218" t="s">
+      <c r="C3" s="217" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="218" t="s">
+      <c r="A4" s="217" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="218" t="s">
+      <c r="B4" s="217" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="218" t="s">
+      <c r="C4" s="217" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="219" t="s">
+      <c r="A5" s="218" t="s">
         <v>212</v>
       </c>
-      <c r="B5" s="218" t="s">
+      <c r="B5" s="217" t="s">
         <v>213</v>
       </c>
-      <c r="C5" s="218" t="s">
+      <c r="C5" s="217" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="220"/>
-      <c r="B6" s="218" t="s">
+      <c r="A6" s="219"/>
+      <c r="B6" s="217" t="s">
         <v>215</v>
       </c>
-      <c r="C6" s="218" t="s">
+      <c r="C6" s="217" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="221" t="s">
+      <c r="A7" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="218" t="s">
+      <c r="B7" s="217" t="s">
         <v>217</v>
       </c>
-      <c r="C7" s="218" t="s">
+      <c r="C7" s="217" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
-      <c r="A8" s="221"/>
-      <c r="B8" s="218" t="s">
+      <c r="A8" s="220"/>
+      <c r="B8" s="217" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="218" t="s">
+      <c r="C8" s="217" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="221"/>
-      <c r="B9" s="218" t="s">
+      <c r="A9" s="220"/>
+      <c r="B9" s="217" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="218" t="s">
+      <c r="C9" s="217" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="221"/>
-      <c r="B10" s="218" t="s">
+      <c r="A10" s="220"/>
+      <c r="B10" s="217" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="218" t="s">
+      <c r="C10" s="217" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="221"/>
-      <c r="B11" s="218"/>
-      <c r="C11" s="218"/>
+      <c r="A11" s="220"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="221"/>
-      <c r="B12" s="218"/>
-      <c r="C12" s="218"/>
+      <c r="A12" s="220"/>
+      <c r="B12" s="217"/>
+      <c r="C12" s="217"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="221"/>
-      <c r="B13" s="218"/>
-      <c r="C13" s="218"/>
+      <c r="A13" s="220"/>
+      <c r="B13" s="217"/>
+      <c r="C13" s="217"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="222"/>
-      <c r="B14" s="218"/>
-      <c r="C14" s="218"/>
+      <c r="A14" s="221"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="218" t="s">
+      <c r="A15" s="217" t="s">
         <v>225</v>
       </c>
-      <c r="B15" s="218" t="s">
+      <c r="B15" s="217" t="s">
         <v>226</v>
       </c>
-      <c r="C15" s="218" t="s">
+      <c r="C15" s="217" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="218" t="s">
+      <c r="A16" s="217" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="218" t="s">
+      <c r="B16" s="217" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="218" t="s">
+      <c r="C16" s="217" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="218" t="s">
+      <c r="A17" s="217" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="218" t="s">
+      <c r="B17" s="217" t="s">
         <v>232</v>
       </c>
-      <c r="C17" s="223">
+      <c r="C17" s="222">
         <v>0.440972222222222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="224" t="s">
+      <c r="A18" s="223" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="218" t="s">
+      <c r="B18" s="217" t="s">
         <v>233</v>
       </c>
-      <c r="C18" s="218" t="s">
+      <c r="C18" s="217" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="221"/>
-      <c r="B19" s="218" t="s">
+      <c r="A19" s="220"/>
+      <c r="B19" s="217" t="s">
         <v>235</v>
       </c>
-      <c r="C19" s="218" t="s">
+      <c r="C19" s="217" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="20" ht="56" spans="1:3">
-      <c r="A20" s="221"/>
-      <c r="B20" s="218" t="s">
+      <c r="A20" s="220"/>
+      <c r="B20" s="217" t="s">
         <v>237</v>
       </c>
-      <c r="C20" s="218" t="s">
+      <c r="C20" s="217" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="221"/>
-      <c r="B21" s="218" t="s">
+      <c r="A21" s="220"/>
+      <c r="B21" s="217" t="s">
         <v>239</v>
       </c>
-      <c r="C21" s="218" t="s">
+      <c r="C21" s="217" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:3">
-      <c r="A22" s="221"/>
-      <c r="B22" s="218" t="s">
+      <c r="A22" s="220"/>
+      <c r="B22" s="217" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="218" t="s">
+      <c r="C22" s="217" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="221"/>
-      <c r="B23" s="218"/>
-      <c r="C23" s="218"/>
+      <c r="A23" s="220"/>
+      <c r="B23" s="217"/>
+      <c r="C23" s="217"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="221"/>
-      <c r="B24" s="218"/>
-      <c r="C24" s="218"/>
+      <c r="A24" s="220"/>
+      <c r="B24" s="217"/>
+      <c r="C24" s="217"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="221"/>
-      <c r="B25" s="218"/>
-      <c r="C25" s="218"/>
+      <c r="A25" s="220"/>
+      <c r="B25" s="217"/>
+      <c r="C25" s="217"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="219" t="s">
+      <c r="A26" s="218" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="218" t="s">
+      <c r="B26" s="217" t="s">
         <v>235</v>
       </c>
-      <c r="C26" s="218" t="s">
+      <c r="C26" s="217" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="220"/>
-      <c r="B27" s="218" t="s">
+      <c r="A27" s="219"/>
+      <c r="B27" s="217" t="s">
         <v>245</v>
       </c>
-      <c r="C27" s="218" t="s">
+      <c r="C27" s="217" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:3">
-      <c r="A28" s="224" t="s">
+      <c r="A28" s="223" t="s">
         <v>247</v>
       </c>
-      <c r="B28" s="218" t="s">
+      <c r="B28" s="217" t="s">
         <v>248</v>
       </c>
-      <c r="C28" s="218" t="s">
+      <c r="C28" s="217" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="221"/>
-      <c r="B29" s="218" t="s">
+      <c r="A29" s="220"/>
+      <c r="B29" s="217" t="s">
         <v>219</v>
       </c>
-      <c r="C29" s="218" t="s">
+      <c r="C29" s="217" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="221"/>
-      <c r="B30" s="218" t="s">
+      <c r="A30" s="220"/>
+      <c r="B30" s="217" t="s">
         <v>251</v>
       </c>
-      <c r="C30" s="218" t="s">
+      <c r="C30" s="217" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="221"/>
-      <c r="B31" s="218"/>
-      <c r="C31" s="218"/>
+      <c r="A31" s="220"/>
+      <c r="B31" s="217"/>
+      <c r="C31" s="217"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="219" t="s">
+      <c r="A32" s="218" t="s">
         <v>253</v>
       </c>
-      <c r="B32" s="218" t="s">
+      <c r="B32" s="217" t="s">
         <v>254</v>
       </c>
-      <c r="C32" s="218" t="s">
+      <c r="C32" s="217" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="220"/>
-      <c r="B33" s="218" t="s">
+      <c r="A33" s="219"/>
+      <c r="B33" s="217" t="s">
         <v>217</v>
       </c>
-      <c r="C33" s="218" t="s">
+      <c r="C33" s="217" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:3">
-      <c r="A34" s="224" t="s">
+      <c r="A34" s="223" t="s">
         <v>47</v>
       </c>
-      <c r="B34" s="218" t="s">
+      <c r="B34" s="217" t="s">
         <v>217</v>
       </c>
-      <c r="C34" s="218" t="s">
+      <c r="C34" s="217" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="221"/>
-      <c r="B35" s="216" t="s">
+      <c r="A35" s="220"/>
+      <c r="B35" s="215" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="216" t="s">
+      <c r="C35" s="215" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="221"/>
-      <c r="B36" s="216" t="s">
+      <c r="A36" s="220"/>
+      <c r="B36" s="215" t="s">
         <v>239</v>
       </c>
-      <c r="C36" s="216" t="s">
+      <c r="C36" s="215" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="37" ht="98" spans="1:3">
-      <c r="A37" s="224" t="s">
+      <c r="A37" s="223" t="s">
         <v>261</v>
       </c>
-      <c r="B37" s="216" t="s">
+      <c r="B37" s="215" t="s">
         <v>217</v>
       </c>
-      <c r="C37" s="216" t="s">
+      <c r="C37" s="215" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="38" ht="84" spans="1:3">
-      <c r="A38" s="221"/>
-      <c r="B38" s="216" t="s">
+      <c r="A38" s="220"/>
+      <c r="B38" s="215" t="s">
         <v>263</v>
       </c>
-      <c r="C38" s="216" t="s">
+      <c r="C38" s="215" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="39" ht="28" spans="1:3">
-      <c r="A39" s="222"/>
-      <c r="B39" s="216" t="s">
+      <c r="A39" s="221"/>
+      <c r="B39" s="215" t="s">
         <v>265</v>
       </c>
-      <c r="C39" s="216" t="s">
+      <c r="C39" s="215" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="216" t="s">
+      <c r="A40" s="215" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="216" t="s">
+      <c r="B40" s="215" t="s">
         <v>267</v>
       </c>
-      <c r="C40" s="216" t="s">
+      <c r="C40" s="215" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="224" t="s">
+      <c r="A41" s="223" t="s">
         <v>269</v>
       </c>
-      <c r="B41" s="216" t="s">
+      <c r="B41" s="215" t="s">
         <v>219</v>
       </c>
-      <c r="C41" s="216" t="s">
+      <c r="C41" s="215" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="222"/>
-      <c r="B42" s="216" t="s">
+      <c r="A42" s="221"/>
+      <c r="B42" s="215" t="s">
         <v>263</v>
       </c>
-      <c r="C42" s="216" t="s">
+      <c r="C42" s="215" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="216" t="s">
+      <c r="A43" s="215" t="s">
         <v>54</v>
       </c>
-      <c r="B43" s="216" t="s">
+      <c r="B43" s="215" t="s">
         <v>221</v>
       </c>
-      <c r="C43" s="216" t="s">
+      <c r="C43" s="215" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="216" t="s">
+      <c r="A44" s="215" t="s">
         <v>273</v>
       </c>
-      <c r="B44" s="216" t="s">
+      <c r="B44" s="215" t="s">
         <v>274</v>
       </c>
-      <c r="C44" s="216" t="s">
+      <c r="C44" s="215" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="216" t="s">
+      <c r="A45" s="215" t="s">
         <v>276</v>
       </c>
-      <c r="B45" s="216" t="s">
+      <c r="B45" s="215" t="s">
         <v>277</v>
       </c>
-      <c r="C45" s="216" t="s">
+      <c r="C45" s="215" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="216" t="s">
+      <c r="A46" s="215" t="s">
         <v>10</v>
       </c>
-      <c r="B46" s="216" t="s">
+      <c r="B46" s="215" t="s">
         <v>263</v>
       </c>
-      <c r="C46" s="216" t="s">
+      <c r="C46" s="215" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="216" t="s">
+      <c r="A47" s="215" t="s">
         <v>280</v>
       </c>
-      <c r="B47" s="216" t="s">
+      <c r="B47" s="215" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="216" t="s">
+      <c r="C47" s="215" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="216" t="s">
+      <c r="A48" s="215" t="s">
         <v>283</v>
       </c>
-      <c r="B48" s="216" t="s">
+      <c r="B48" s="215" t="s">
         <v>284</v>
       </c>
-      <c r="C48" s="216" t="s">
+      <c r="C48" s="215" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="216" t="s">
+      <c r="A49" s="215" t="s">
         <v>286</v>
       </c>
-      <c r="B49" s="216" t="s">
+      <c r="B49" s="215" t="s">
         <v>284</v>
       </c>
-      <c r="C49" s="216" t="s">
+      <c r="C49" s="215" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="216" t="s">
+      <c r="A50" s="215" t="s">
         <v>288</v>
       </c>
-      <c r="B50" s="216" t="s">
+      <c r="B50" s="215" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="216" t="s">
+      <c r="C50" s="215" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="51" ht="28" spans="1:3">
-      <c r="A51" s="216" t="s">
+      <c r="A51" s="215" t="s">
         <v>290</v>
       </c>
-      <c r="B51" s="216" t="s">
+      <c r="B51" s="215" t="s">
         <v>265</v>
       </c>
-      <c r="C51" s="216" t="s">
+      <c r="C51" s="215" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:3">
-      <c r="A52" s="216" t="s">
+      <c r="A52" s="215" t="s">
         <v>292</v>
       </c>
-      <c r="B52" s="216" t="s">
+      <c r="B52" s="215" t="s">
         <v>265</v>
       </c>
-      <c r="C52" s="216" t="s">
+      <c r="C52" s="215" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="53" ht="140" spans="1:3">
-      <c r="A53" s="216" t="s">
+      <c r="A53" s="215" t="s">
         <v>294</v>
       </c>
-      <c r="B53" s="216" t="s">
+      <c r="B53" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C53" s="216" t="s">
+      <c r="C53" s="215" t="s">
         <v>296</v>
       </c>
     </row>
@@ -9168,45 +9171,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="204"/>
+    <col min="5" max="5" width="8.72727272727273" style="203"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="202" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="205" t="s">
+    <row r="1" s="201" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="204" t="s">
         <v>297</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="208"/>
-      <c r="F1" s="202" t="s">
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="201" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="2" s="203" customFormat="1" spans="1:7">
-      <c r="A2" s="209" t="s">
+    <row r="2" s="202" customFormat="1" spans="1:7">
+      <c r="A2" s="208" t="s">
         <v>202</v>
       </c>
-      <c r="B2" s="210"/>
-      <c r="C2" s="203" t="s">
+      <c r="B2" s="209"/>
+      <c r="C2" s="202" t="s">
         <v>299</v>
       </c>
-      <c r="D2" s="203" t="s">
+      <c r="D2" s="202" t="s">
         <v>300</v>
       </c>
       <c r="E2" s="142"/>
-      <c r="F2" s="203" t="s">
+      <c r="F2" s="202" t="s">
         <v>202</v>
       </c>
-      <c r="G2" s="203" t="s">
+      <c r="G2" s="202" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="211">
+      <c r="A3" s="210">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -9224,7 +9227,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="212"/>
+      <c r="A4" s="211"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -9240,7 +9243,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="212"/>
+      <c r="A5" s="211"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -9256,7 +9259,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="212"/>
+      <c r="A6" s="211"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9264,7 +9267,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="213" t="s">
+      <c r="F6" s="212" t="s">
         <v>308</v>
       </c>
       <c r="G6" s="119" t="s">
@@ -9272,7 +9275,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="212"/>
+      <c r="A7" s="211"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9280,13 +9283,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="214"/>
+      <c r="F7" s="213"/>
       <c r="G7" s="119" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="212"/>
+      <c r="A8" s="211"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9302,7 +9305,7 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="214"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9314,7 +9317,7 @@
       <c r="G9" s="119"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="213">
+      <c r="A10" s="212">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9328,7 +9331,7 @@
       <c r="G10" s="119"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="212"/>
+      <c r="A11" s="211"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9340,7 +9343,7 @@
       <c r="G11" s="119"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="214"/>
+      <c r="A12" s="213"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9352,7 +9355,7 @@
       <c r="G12" s="119"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="213">
+      <c r="A13" s="212">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9368,7 +9371,7 @@
       <c r="G13" s="119"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="214"/>
+      <c r="A14" s="213"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -9844,7 +9847,9 @@
       <c r="AV4" s="120">
         <v>1</v>
       </c>
-      <c r="AW4" s="120"/>
+      <c r="AW4" s="120">
+        <v>1</v>
+      </c>
       <c r="AX4" s="120"/>
       <c r="AY4" s="120"/>
       <c r="AZ4" s="120"/>
@@ -9853,15 +9858,15 @@
       <c r="BC4" s="120"/>
       <c r="BD4" s="189">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE4" s="189" cm="1">
         <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF4" s="189" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BG4" s="190" cm="1">
         <f t="array" ref="BG4">SUMPRODUCT(--(B4:AI4=INT(B4:AI4)),--(B4:AI4&gt;0))/34*100%</f>
@@ -9869,11 +9874,11 @@
       </c>
       <c r="BH4" s="191">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BI4" s="191">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BJ4" s="191">
         <f t="shared" si="3"/>
@@ -10299,7 +10304,7 @@
       </c>
       <c r="BJ8" s="191">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:62">
@@ -10387,7 +10392,9 @@
       <c r="AV9" s="120">
         <v>1</v>
       </c>
-      <c r="AW9" s="120"/>
+      <c r="AW9" s="120">
+        <v>1</v>
+      </c>
       <c r="AX9" s="120"/>
       <c r="AY9" s="120"/>
       <c r="AZ9" s="120"/>
@@ -10396,11 +10403,11 @@
       <c r="BC9" s="120"/>
       <c r="BD9" s="189">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE9" s="189" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF9" s="189" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
@@ -10412,11 +10419,11 @@
       </c>
       <c r="BH9" s="191">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI9" s="191">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BJ9" s="191">
         <f t="shared" si="3"/>
@@ -11670,7 +11677,9 @@
         <v>1</v>
       </c>
       <c r="AV22" s="120"/>
-      <c r="AW22" s="120"/>
+      <c r="AW22" s="120">
+        <v>1</v>
+      </c>
       <c r="AX22" s="120"/>
       <c r="AY22" s="120"/>
       <c r="AZ22" s="120"/>
@@ -11679,11 +11688,11 @@
       <c r="BC22" s="120"/>
       <c r="BD22" s="189">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BE22" s="189" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF22" s="189" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
@@ -11695,11 +11704,11 @@
       </c>
       <c r="BH22" s="191">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BI22" s="191">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BJ22" s="191">
         <f t="shared" si="3"/>
@@ -12376,7 +12385,7 @@
       </c>
       <c r="BJ29" s="191">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:62">
@@ -13719,7 +13728,7 @@
       </c>
       <c r="BJ42" s="191">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:62">
@@ -13929,7 +13938,7 @@
       </c>
       <c r="BJ44" s="191">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:62">
@@ -14130,7 +14139,9 @@
       <c r="AV46" s="120">
         <v>1</v>
       </c>
-      <c r="AW46" s="120"/>
+      <c r="AW46" s="120">
+        <v>1</v>
+      </c>
       <c r="AX46" s="120"/>
       <c r="AY46" s="120"/>
       <c r="AZ46" s="120"/>
@@ -14139,11 +14150,11 @@
       <c r="BC46" s="120"/>
       <c r="BD46" s="189">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BE46" s="189" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BF46" s="189" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
@@ -14357,7 +14368,7 @@
       </c>
       <c r="BH48" s="191">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BI48" s="191">
         <f t="shared" si="2"/>
@@ -14827,459 +14838,459 @@
       <c r="A54" s="194" t="s">
         <v>326</v>
       </c>
-      <c r="B54" s="195" cm="1">
+      <c r="B54" s="17" cm="1">
         <f t="array" ref="B54">SUMPRODUCT(--(B3:B53=INT(B3:B53)),--(B3:B53&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="C54" s="195" cm="1">
+      <c r="C54" s="17" cm="1">
         <f t="array" ref="C54">SUMPRODUCT(--(C3:C53=INT(C3:C53)),--(C3:C53&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="D54" s="195" cm="1">
+      <c r="D54" s="17" cm="1">
         <f t="array" ref="D54">SUMPRODUCT(--(D3:D53=INT(D3:D53)),--(D3:D53&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="E54" s="195" cm="1">
+      <c r="E54" s="17" cm="1">
         <f t="array" ref="E54">SUMPRODUCT(--(E3:E53=INT(E3:E53)),--(E3:E53&gt;0))</f>
         <v>6</v>
       </c>
-      <c r="F54" s="195" cm="1">
+      <c r="F54" s="17" cm="1">
         <f t="array" ref="F54">SUMPRODUCT(--(F3:F53=INT(F3:F53)),--(F3:F53&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="G54" s="195" cm="1">
+      <c r="G54" s="17" cm="1">
         <f t="array" ref="G54">SUMPRODUCT(--(G3:G53=INT(G3:G53)),--(G3:G53&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="H54" s="195" cm="1">
+      <c r="H54" s="17" cm="1">
         <f t="array" ref="H54">SUMPRODUCT(--(H3:H53=INT(H3:H53)),--(H3:H53&gt;0))</f>
         <v>12</v>
       </c>
-      <c r="I54" s="195" cm="1">
+      <c r="I54" s="17" cm="1">
         <f t="array" ref="I54">SUMPRODUCT(--(I3:I53=INT(I3:I53)),--(I3:I53&gt;0))</f>
         <v>13</v>
       </c>
-      <c r="J54" s="195" cm="1">
+      <c r="J54" s="17" cm="1">
         <f t="array" ref="J54">SUMPRODUCT(--(J3:J53=INT(J3:J53)),--(J3:J53&gt;0))</f>
         <v>12</v>
       </c>
-      <c r="K54" s="195" cm="1">
+      <c r="K54" s="17" cm="1">
         <f t="array" ref="K54">SUMPRODUCT(--(K3:K53=INT(K3:K53)),--(K3:K53&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="L54" s="195" cm="1">
+      <c r="L54" s="17" cm="1">
         <f t="array" ref="L54">SUMPRODUCT(--(L3:L53=INT(L3:L53)),--(L3:L53&gt;0))</f>
         <v>12</v>
       </c>
-      <c r="M54" s="195" cm="1">
+      <c r="M54" s="17" cm="1">
         <f t="array" ref="M54">SUMPRODUCT(--(M3:M53=INT(M3:M53)),--(M3:M53&gt;0))</f>
         <v>6</v>
       </c>
-      <c r="N54" s="195" cm="1">
+      <c r="N54" s="17" cm="1">
         <f t="array" ref="N54">SUMPRODUCT(--(N3:N53=INT(N3:N53)),--(N3:N53&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="O54" s="195" cm="1">
+      <c r="O54" s="17" cm="1">
         <f t="array" ref="O54">SUMPRODUCT(--(O3:O53=INT(O3:O53)),--(O3:O53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="P54" s="195" cm="1">
+      <c r="P54" s="17" cm="1">
         <f t="array" ref="P54">SUMPRODUCT(--(P3:P53=INT(P3:P53)),--(P3:P53&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="Q54" s="195" cm="1">
+      <c r="Q54" s="17" cm="1">
         <f t="array" ref="Q54">SUMPRODUCT(--(Q3:Q53=INT(Q3:Q53)),--(Q3:Q53&gt;0))</f>
         <v>13</v>
       </c>
-      <c r="R54" s="195" cm="1">
+      <c r="R54" s="17" cm="1">
         <f t="array" ref="R54">SUMPRODUCT(--(R3:R53=INT(R3:R53)),--(R3:R53&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="S54" s="195" cm="1">
+      <c r="S54" s="17" cm="1">
         <f t="array" ref="S54">SUMPRODUCT(--(S3:S53=INT(S3:S53)),--(S3:S53&gt;0))</f>
         <v>11</v>
       </c>
-      <c r="T54" s="195" cm="1">
+      <c r="T54" s="17" cm="1">
         <f t="array" ref="T54">SUMPRODUCT(--(T3:T53=INT(T3:T53)),--(T3:T53&gt;0))</f>
         <v>23</v>
       </c>
-      <c r="U54" s="195" cm="1">
+      <c r="U54" s="17" cm="1">
         <f t="array" ref="U54">SUMPRODUCT(--(U3:U53=INT(U3:U53)),--(U3:U53&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="V54" s="195" cm="1">
+      <c r="V54" s="17" cm="1">
         <f t="array" ref="V54">SUMPRODUCT(--(V3:V53=INT(V3:V53)),--(V3:V53&gt;0))</f>
         <v>12</v>
       </c>
-      <c r="W54" s="195" cm="1">
+      <c r="W54" s="17" cm="1">
         <f t="array" ref="W54">SUMPRODUCT(--(W3:W53=INT(W3:W53)),--(W3:W53&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="X54" s="195" cm="1">
+      <c r="X54" s="17" cm="1">
         <f t="array" ref="X54">SUMPRODUCT(--(X3:X53=INT(X3:X53)),--(X3:X53&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="Y54" s="195" cm="1">
+      <c r="Y54" s="17" cm="1">
         <f t="array" ref="Y54">SUMPRODUCT(--(Y3:Y53=INT(Y3:Y53)),--(Y3:Y53&gt;0))</f>
         <v>28</v>
       </c>
-      <c r="Z54" s="195" cm="1">
+      <c r="Z54" s="17" cm="1">
         <f t="array" ref="Z54">SUMPRODUCT(--(Z3:Z53=INT(Z3:Z53)),--(Z3:Z53&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="AA54" s="195" cm="1">
+      <c r="AA54" s="17" cm="1">
         <f t="array" ref="AA54">SUMPRODUCT(--(AA3:AA53=INT(AA3:AA53)),--(AA3:AA53&gt;0))</f>
         <v>4</v>
       </c>
-      <c r="AB54" s="195" cm="1">
+      <c r="AB54" s="17" cm="1">
         <f t="array" ref="AB54">SUMPRODUCT(--(AB3:AB53=INT(AB3:AB53)),--(AB3:AB53&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AC54" s="195" cm="1">
+      <c r="AC54" s="17" cm="1">
         <f t="array" ref="AC54">SUMPRODUCT(--(AC3:AC53=INT(AC3:AC53)),--(AC3:AC53&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="AD54" s="195" cm="1">
+      <c r="AD54" s="17" cm="1">
         <f t="array" ref="AD54">SUMPRODUCT(--(AD3:AD53=INT(AD3:AD53)),--(AD3:AD53&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AE54" s="195" cm="1">
+      <c r="AE54" s="17" cm="1">
         <f t="array" ref="AE54">SUMPRODUCT(--(AE3:AE53=INT(AE3:AE53)),--(AE3:AE53&gt;0))</f>
         <v>5</v>
       </c>
-      <c r="AF54" s="195" cm="1">
+      <c r="AF54" s="17" cm="1">
         <f t="array" ref="AF54">SUMPRODUCT(--(AF3:AF53=INT(AF3:AF53)),--(AF3:AF53&gt;0))</f>
         <v>7</v>
       </c>
-      <c r="AG54" s="195" cm="1">
+      <c r="AG54" s="17" cm="1">
         <f t="array" ref="AG54">SUMPRODUCT(--(AG3:AG53=INT(AG3:AG53)),--(AG3:AG53&gt;0))</f>
         <v>1</v>
       </c>
-      <c r="AH54" s="195" cm="1">
+      <c r="AH54" s="17" cm="1">
         <f t="array" ref="AH54">SUMPRODUCT(--(AH3:AH53=INT(AH3:AH53)),--(AH3:AH53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AI54" s="195" cm="1">
+      <c r="AI54" s="17" cm="1">
         <f t="array" ref="AI54">SUMPRODUCT(--(AI3:AI53=INT(AI3:AI53)),--(AI3:AI53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AJ54" s="195" cm="1">
+      <c r="AJ54" s="17" cm="1">
         <f t="array" ref="AJ54">SUMPRODUCT(--(AJ3:AJ53=INT(AJ3:AJ53)),--(AJ3:AJ53&gt;0))</f>
         <v>18</v>
       </c>
-      <c r="AK54" s="195" cm="1">
+      <c r="AK54" s="17" cm="1">
         <f t="array" ref="AK54">SUMPRODUCT(--(AK3:AK53=INT(AK3:AK53)),--(AK3:AK53&gt;0))</f>
         <v>6</v>
       </c>
-      <c r="AL54" s="195" cm="1">
+      <c r="AL54" s="17" cm="1">
         <f t="array" ref="AL54">SUMPRODUCT(--(AL3:AL53=INT(AL3:AL53)),--(AL3:AL53&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AM54" s="195" cm="1">
+      <c r="AM54" s="17" cm="1">
         <f t="array" ref="AM54">SUMPRODUCT(--(AM3:AM53=INT(AM3:AM53)),--(AM3:AM53&gt;0))</f>
         <v>3</v>
       </c>
-      <c r="AN54" s="195" cm="1">
+      <c r="AN54" s="17" cm="1">
         <f t="array" ref="AN54">SUMPRODUCT(--(AN3:AN53=INT(AN3:AN53)),--(AN3:AN53&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="AO54" s="195" cm="1">
+      <c r="AO54" s="17" cm="1">
         <f t="array" ref="AO54">SUMPRODUCT(--(AO3:AO53=INT(AO3:AO53)),--(AO3:AO53&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="AP54" s="195" cm="1">
+      <c r="AP54" s="17" cm="1">
         <f t="array" ref="AP54">SUMPRODUCT(--(AP3:AP53=INT(AP3:AP53)),--(AP3:AP53&gt;0))</f>
         <v>2</v>
       </c>
-      <c r="AQ54" s="195" cm="1">
+      <c r="AQ54" s="17" cm="1">
         <f t="array" ref="AQ54">SUMPRODUCT(--(AQ3:AQ53=INT(AQ3:AQ53)),--(AQ3:AQ53&gt;0))</f>
         <v>6</v>
       </c>
-      <c r="AR54" s="195" cm="1">
+      <c r="AR54" s="17" cm="1">
         <f t="array" ref="AR54">SUMPRODUCT(--(AR3:AR53=INT(AR3:AR53)),--(AR3:AR53&gt;0))</f>
         <v>15</v>
       </c>
-      <c r="AS54" s="195" cm="1">
+      <c r="AS54" s="17" cm="1">
         <f t="array" ref="AS54">SUMPRODUCT(--(AS3:AS53=INT(AS3:AS53)),--(AS3:AS53&gt;0))</f>
         <v>10</v>
       </c>
-      <c r="AT54" s="195" cm="1">
+      <c r="AT54" s="17" cm="1">
         <f t="array" ref="AT54">SUMPRODUCT(--(AT3:AT53=INT(AT3:AT53)),--(AT3:AT53&gt;0))</f>
         <v>9</v>
       </c>
-      <c r="AU54" s="195" cm="1">
+      <c r="AU54" s="17" cm="1">
         <f t="array" ref="AU54">SUMPRODUCT(--(AU3:AU53=INT(AU3:AU53)),--(AU3:AU53&gt;0))</f>
         <v>15</v>
       </c>
-      <c r="AV54" s="195" cm="1">
+      <c r="AV54" s="17" cm="1">
         <f t="array" ref="AV54">SUMPRODUCT(--(AV3:AV53=INT(AV3:AV53)),--(AV3:AV53&gt;0))</f>
         <v>8</v>
       </c>
-      <c r="AW54" s="195" cm="1">
+      <c r="AW54" s="17" cm="1">
         <f t="array" ref="AW54">SUMPRODUCT(--(AW3:AW53=INT(AW3:AW53)),--(AW3:AW53&gt;0))</f>
-        <v>0</v>
-      </c>
-      <c r="AX54" s="195" cm="1">
+        <v>4</v>
+      </c>
+      <c r="AX54" s="17" cm="1">
         <f t="array" ref="AX54">SUMPRODUCT(--(AX3:AX53=INT(AX3:AX53)),--(AX3:AX53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AY54" s="195" cm="1">
+      <c r="AY54" s="17" cm="1">
         <f t="array" ref="AY54">SUMPRODUCT(--(AY3:AY53=INT(AY3:AY53)),--(AY3:AY53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="AZ54" s="195" cm="1">
+      <c r="AZ54" s="17" cm="1">
         <f t="array" ref="AZ54">SUMPRODUCT(--(AZ3:AZ53=INT(AZ3:AZ53)),--(AZ3:AZ53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BA54" s="195" cm="1">
+      <c r="BA54" s="17" cm="1">
         <f t="array" ref="BA54">SUMPRODUCT(--(BA3:BA53=INT(BA3:BA53)),--(BA3:BA53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BB54" s="195" cm="1">
+      <c r="BB54" s="17" cm="1">
         <f t="array" ref="BB54">SUMPRODUCT(--(BB3:BB53=INT(BB3:BB53)),--(BB3:BB53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BC54" s="195" cm="1">
+      <c r="BC54" s="17" cm="1">
         <f t="array" ref="BC54">SUMPRODUCT(--(BC3:BC53=INT(BC3:BC53)),--(BC3:BC53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BD54" s="196" t="s">
+      <c r="BD54" s="195" t="s">
         <v>327</v>
       </c>
-      <c r="BE54" s="197"/>
-      <c r="BF54" s="197"/>
-      <c r="BG54" s="197"/>
-      <c r="BH54" s="197"/>
-      <c r="BI54" s="197"/>
-      <c r="BJ54" s="198"/>
+      <c r="BE54" s="196"/>
+      <c r="BF54" s="196"/>
+      <c r="BG54" s="196"/>
+      <c r="BH54" s="196"/>
+      <c r="BI54" s="196"/>
+      <c r="BJ54" s="197"/>
     </row>
     <row r="55" s="175" customFormat="1" ht="28" spans="1:62">
       <c r="A55" s="194" t="s">
         <v>328</v>
       </c>
-      <c r="B55" s="195">
+      <c r="B55" s="17">
         <f>SUM(B3:B53)</f>
         <v>11</v>
       </c>
-      <c r="C55" s="195">
+      <c r="C55" s="17">
         <f t="shared" ref="C55:AH55" si="4">SUM(C3:C53)</f>
         <v>9</v>
       </c>
-      <c r="D55" s="195">
+      <c r="D55" s="17">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="E55" s="195">
+      <c r="E55" s="17">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="F55" s="195">
+      <c r="F55" s="17">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="G55" s="195">
+      <c r="G55" s="17">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="H55" s="195">
+      <c r="H55" s="17">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="I55" s="195">
+      <c r="I55" s="17">
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="J55" s="195">
+      <c r="J55" s="17">
         <f t="shared" si="4"/>
         <v>14</v>
       </c>
-      <c r="K55" s="195">
+      <c r="K55" s="17">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="L55" s="195">
+      <c r="L55" s="17">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
-      <c r="M55" s="195">
+      <c r="M55" s="17">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="N55" s="195">
+      <c r="N55" s="17">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="O55" s="195">
+      <c r="O55" s="17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="P55" s="195">
+      <c r="P55" s="17">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="Q55" s="195">
+      <c r="Q55" s="17">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="R55" s="195">
+      <c r="R55" s="17">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="S55" s="195">
+      <c r="S55" s="17">
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="T55" s="195">
+      <c r="T55" s="17">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="U55" s="195">
+      <c r="U55" s="17">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="V55" s="195">
+      <c r="V55" s="17">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="W55" s="195">
+      <c r="W55" s="17">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="X55" s="195">
+      <c r="X55" s="17">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="Y55" s="195">
+      <c r="Y55" s="17">
         <f t="shared" si="4"/>
         <v>31</v>
       </c>
-      <c r="Z55" s="195">
+      <c r="Z55" s="17">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="AA55" s="195">
+      <c r="AA55" s="17">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="AB55" s="195">
+      <c r="AB55" s="17">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AC55" s="195">
+      <c r="AC55" s="17">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="AD55" s="195">
+      <c r="AD55" s="17">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="AE55" s="195">
+      <c r="AE55" s="17">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="AF55" s="195">
+      <c r="AF55" s="17">
         <f t="shared" si="4"/>
         <v>9</v>
       </c>
-      <c r="AG55" s="195">
+      <c r="AG55" s="17">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="AH55" s="195">
+      <c r="AH55" s="17">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AI55" s="195">
+      <c r="AI55" s="17">
         <f t="shared" ref="AI55:BC55" si="5">SUM(AI3:AI53)</f>
         <v>0</v>
       </c>
-      <c r="AJ55" s="195">
+      <c r="AJ55" s="17">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="AK55" s="195">
+      <c r="AK55" s="17">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="AL55" s="195">
+      <c r="AL55" s="17">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="AM55" s="195">
+      <c r="AM55" s="17">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="AN55" s="195">
+      <c r="AN55" s="17">
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="AO55" s="195">
+      <c r="AO55" s="17">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="AP55" s="195">
+      <c r="AP55" s="17">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="AQ55" s="195">
+      <c r="AQ55" s="17">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="AR55" s="195">
+      <c r="AR55" s="17">
         <f t="shared" si="5"/>
         <v>18</v>
       </c>
-      <c r="AS55" s="195">
+      <c r="AS55" s="17">
         <f t="shared" si="5"/>
         <v>10</v>
       </c>
-      <c r="AT55" s="195">
+      <c r="AT55" s="17">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
-      <c r="AU55" s="195">
+      <c r="AU55" s="17">
         <f t="shared" si="5"/>
         <v>23</v>
       </c>
-      <c r="AV55" s="195">
+      <c r="AV55" s="17">
         <f t="shared" si="5"/>
         <v>8</v>
       </c>
-      <c r="AW55" s="195">
+      <c r="AW55" s="17">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="AX55" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AX55" s="195">
+      <c r="AY55" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AY55" s="195">
+      <c r="AZ55" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AZ55" s="195">
+      <c r="BA55" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BA55" s="195">
+      <c r="BB55" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BB55" s="195">
+      <c r="BC55" s="17">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BC55" s="195">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="BD55" s="199"/>
-      <c r="BE55" s="200"/>
-      <c r="BF55" s="200"/>
-      <c r="BG55" s="200"/>
-      <c r="BH55" s="200"/>
-      <c r="BI55" s="200"/>
-      <c r="BJ55" s="201"/>
+      <c r="BD55" s="198"/>
+      <c r="BE55" s="199"/>
+      <c r="BF55" s="199"/>
+      <c r="BG55" s="199"/>
+      <c r="BH55" s="199"/>
+      <c r="BI55" s="199"/>
+      <c r="BJ55" s="200"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -16425,8 +16436,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:BJ40 A41:W41 Y41:BJ41 A42:BJ55" formulaRange="1"/>
-    <ignoredError sqref="X41 AD9:AF9 Z9:AB9 A1 C1:S1 U1:AF1 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z29:AF29 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 A3:X4 BD1:BJ2 BI3 AC40:AD40 A40:V40 A42:X42 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 A48:X49 Z48:AB48 AE48 A51:AF53 A50:AD50 AF50 X8:AF8 A8:V8 A5:AF7 Z4:AE4 Z41:AE42 BH4:BJ8 BI9:BJ9 Z10:AF10 BH11:BJ14 BH36:BJ39 BI35:BJ35 BH24:BJ28 Z49:AF49 A12:X15 A37:AF37 A39:AF39 A2:AF2 Z3:AF3 A9:X10" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="A41:W41 AX22:BJ22 AF41:BJ42 Y41 Y49 Y42:AE42 A50:BJ50 AG51:BJ53 A54:BJ55 AG49:BJ49 Y4:AV4 AX4:BG4 Z3:BH3 BJ3 B1:BJ1 A2:BJ2 AA11:BJ11 A12:BJ21 Y22:AV22 AG23:BJ23 A24:BJ40 Y9:AC9 AG9:AV9 AX9:BH9 Y10 AG10:BJ10" formulaRange="1"/>
+    <ignoredError sqref="X41 A48:X49 A42:X42 Z42:AE42 A51:AF53 A50:AD50 AF50 Z49:AF49 A49:X49 A4:X4 Z4:AE4 BH4:BJ4 BH5:BJ8 BI3 Z3:AF3 A3:X3 A1 C1:S1 U1:AF1 BD1:BJ2 A2:AF2 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 BH11:BJ14 A12:X15 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z29:AF29 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 AC40:AD40 A40:V40 BH36:BJ39 BI35:BJ35 BH24:BJ28 A37:AF37 A39:AF39 AD9:AF9 Z9:AB9 BI9:BJ9 Z10:AF10 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 Z48:AB48 AE48 A9:X10" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="X8:AF8 A8:V8 A5:AF7 Z41:AE41 A3:X3 BH5:BJ8" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="4"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="665">
   <si>
     <t>姓名</t>
   </si>
@@ -264,7 +264,7 @@
     <t>朋友圈（模糊图片、装）、马克笔写字、挠痒动作、起立时（借口、拖延、不情愿、偷坐）</t>
   </si>
   <si>
-    <t>麦当劳</t>
+    <t>麦当劳、教辅、抄答案</t>
   </si>
   <si>
     <t>林承钰</t>
@@ -671,7 +671,10 @@
   </si>
   <si>
     <t>××住在澎湖湾，天天喝稀饭。
-没有筷子没有碗，只有破烂摊。</t>
+没有筷子没有碗，只有一个破烂摊。</t>
+  </si>
+  <si>
+    <t>拗九节送粥（张桢烨）</t>
   </si>
   <si>
     <t>日常</t>
@@ -999,6 +1002,12 @@
 听完本句录音，学生大声朗读“emm”，空格处说不出来。刘老师：注意力不在重点、刚才崔宇臣/林芷琪笑、不止“emm”，其他也一样、态度
 重来，学生顺利读出“foreign cash”。刘老师：都能说出来
 接下来顺利读完。刘老师：集中注意力就不会拖拉停顿、命令执行效率（circle/underline/repeat）、80%学生认识circle（认识的举手），但执行时（第一遍：10个左右成绩好学生完成；第二遍：要去催的人完成；第三遍：提醒蔡华楷、薛阅晨、崔宇臣等人，王淮等人可进行下一步骤）、刚才段长公开课无拖拉，说明是能专心的、课程紧迫，但这样导致无法完成课时、吸收效率（有人90%吸收，有人10%但晚上努力背诵，却无效果）、笔记本不要合上/笔拿手上：频繁拿笔效率低，细节问题不容忽视、注意力集中的方法（take notes/answer the questions aloud）</t>
+  </si>
+  <si>
+    <t>八下3.17</t>
+  </si>
+  <si>
+    <t>郑致辰！冷静一下！</t>
   </si>
   <si>
     <t>政治课</t>
@@ -3367,7 +3376,18 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3378,17 +3398,6 @@
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -6062,16 +6071,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6085,7 +6094,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6099,7 +6108,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6113,7 +6122,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6141,7 +6150,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6155,7 +6164,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6169,7 +6178,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6183,7 +6192,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6197,7 +6206,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6223,7 +6232,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6237,7 +6246,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6251,7 +6260,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6277,7 +6286,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6291,7 +6300,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6329,7 +6338,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6343,7 +6352,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6369,7 +6378,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6383,7 +6392,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6397,7 +6406,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6411,7 +6420,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6425,7 +6434,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6439,7 +6448,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6465,7 +6474,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6479,7 +6488,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6493,7 +6502,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6519,7 +6528,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6545,7 +6554,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6559,7 +6568,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6573,10 +6582,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E38" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6590,7 +6599,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6604,7 +6613,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6618,10 +6627,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
+        <v>512</v>
+      </c>
+      <c r="E41" t="s">
         <v>509</v>
-      </c>
-      <c r="E41" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6647,7 +6656,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6673,7 +6682,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6699,10 +6708,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E47" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6716,7 +6725,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6742,7 +6751,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6768,7 +6777,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -6801,34 +6810,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6836,10 +6845,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6847,10 +6856,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6858,10 +6867,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6869,23 +6878,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6893,10 +6902,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6904,10 +6913,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6915,10 +6924,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6926,10 +6935,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6937,50 +6946,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6989,24 +6998,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -7014,17 +7023,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -7033,61 +7042,61 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
       <c r="A23" s="42"/>
       <c r="B23" s="43"/>
       <c r="C23" s="31" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -7095,10 +7104,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7106,10 +7115,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7117,27 +7126,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7145,10 +7154,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7156,10 +7165,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7167,53 +7176,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7224,42 +7233,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7267,64 +7276,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7334,16 +7343,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7352,7 +7361,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7361,42 +7370,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7406,10 +7415,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7417,10 +7426,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7432,18 +7441,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -7551,7 +7560,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7565,7 +7574,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7589,7 +7598,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7602,7 +7611,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7615,7 +7624,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7649,7 +7658,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7695,7 +7704,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7731,7 +7740,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7765,10 +7774,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7780,10 +7789,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7806,7 +7815,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7819,10 +7828,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7856,10 +7865,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7871,10 +7880,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7898,7 +7907,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7965,7 +7974,7 @@
         <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7979,7 +7988,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -7991,7 +8000,7 @@
         <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -8005,7 +8014,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -8017,10 +8026,10 @@
         <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -8033,7 +8042,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -8056,7 +8065,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -8080,7 +8089,7 @@
         <v>104</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -8116,7 +8125,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8140,7 +8149,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8163,10 +8172,10 @@
         <v>117</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8202,27 +8211,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8230,13 +8239,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8244,13 +8253,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8258,13 +8267,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8272,13 +8281,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8286,13 +8295,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8300,13 +8309,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8314,7 +8323,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8322,7 +8331,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8330,7 +8339,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8338,7 +8347,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8515,6 +8524,9 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="229"/>
+      <c r="B20" s="66" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="229"/>
@@ -8632,7 +8644,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.8"/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="24" style="215" customWidth="1"/>
@@ -8643,66 +8655,66 @@
   <sheetData>
     <row r="1" s="214" customFormat="1" ht="15" spans="1:3">
       <c r="A1" s="216" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B1" s="216" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C1" s="216" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="217" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B2" s="217" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C2" s="217" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="217" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B3" s="217" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C3" s="217" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="217" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B4" s="217" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C4" s="217" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
       <c r="A5" s="218" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B5" s="217" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C5" s="217" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
       <c r="A6" s="219"/>
       <c r="B6" s="217" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C6" s="217" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8710,37 +8722,37 @@
         <v>91</v>
       </c>
       <c r="B7" s="217" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C7" s="217" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
       <c r="A8" s="220"/>
       <c r="B8" s="217" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C8" s="217" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="220"/>
       <c r="B9" s="217" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C9" s="217" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="220"/>
       <c r="B10" s="217" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C10" s="217" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8765,32 +8777,32 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="217" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B15" s="217" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C15" s="217" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="217" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B16" s="217" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C16" s="217" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="217" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B17" s="217" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C17" s="222">
         <v>0.440972222222222</v>
@@ -8801,46 +8813,46 @@
         <v>63</v>
       </c>
       <c r="B18" s="217" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C18" s="217" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="220"/>
       <c r="B19" s="217" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C19" s="217" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" ht="56" spans="1:3">
       <c r="A20" s="220"/>
       <c r="B20" s="217" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C20" s="217" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="220"/>
       <c r="B21" s="217" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C21" s="217" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:3">
       <c r="A22" s="220"/>
       <c r="B22" s="217" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C22" s="217" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -8860,51 +8872,51 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="218" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" s="217" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C26" s="217" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="219"/>
       <c r="B27" s="217" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C27" s="217" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:3">
       <c r="A28" s="223" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" s="217" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C28" s="217" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="220"/>
       <c r="B29" s="217" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C29" s="217" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="220"/>
       <c r="B30" s="217" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C30" s="217" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -8914,22 +8926,22 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="218" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B32" s="217" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C32" s="217" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="219"/>
       <c r="B33" s="217" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C33" s="217" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" ht="28" spans="1:3">
@@ -8937,57 +8949,57 @@
         <v>47</v>
       </c>
       <c r="B34" s="217" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C34" s="217" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="220"/>
       <c r="B35" s="215" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C35" s="215" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="220"/>
       <c r="B36" s="215" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C36" s="215" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" ht="98" spans="1:3">
       <c r="A37" s="223" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B37" s="215" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C37" s="215" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" ht="84" spans="1:3">
       <c r="A38" s="220"/>
       <c r="B38" s="215" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C38" s="215" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" ht="28" spans="1:3">
       <c r="A39" s="221"/>
       <c r="B39" s="215" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C39" s="215" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -8995,30 +9007,30 @@
         <v>38</v>
       </c>
       <c r="B40" s="215" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C40" s="215" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="223" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B41" s="215" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C41" s="215" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="221"/>
       <c r="B42" s="215" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C42" s="215" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -9026,32 +9038,32 @@
         <v>54</v>
       </c>
       <c r="B43" s="215" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C43" s="215" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="215" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B44" s="215" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C44" s="215" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="215" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B45" s="215" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C45" s="215" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -9059,87 +9071,98 @@
         <v>10</v>
       </c>
       <c r="B46" s="215" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C46" s="215" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="215" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B47" s="215" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C47" s="215" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="215" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B48" s="215" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C48" s="215" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="215" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B49" s="215" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C49" s="215" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="215" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B50" s="215" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C50" s="215" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" ht="28" spans="1:3">
       <c r="A51" s="215" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B51" s="215" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C51" s="215" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" ht="28" spans="1:3">
       <c r="A52" s="215" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B52" s="215" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C52" s="215" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" ht="140" spans="1:3">
       <c r="A53" s="215" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B53" s="215" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C53" s="215" t="s">
-        <v>296</v>
+        <v>297</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" s="215" t="s">
+        <v>10</v>
+      </c>
+      <c r="B54" s="215" t="s">
+        <v>298</v>
+      </c>
+      <c r="C54" s="215" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -9179,33 +9202,33 @@
   <sheetData>
     <row r="1" s="201" customFormat="1" ht="15" spans="1:7">
       <c r="A1" s="204" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B1" s="205"/>
       <c r="C1" s="205"/>
       <c r="D1" s="206"/>
       <c r="E1" s="207"/>
       <c r="F1" s="201" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" s="202" customFormat="1" spans="1:7">
       <c r="A2" s="208" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B2" s="209"/>
       <c r="C2" s="202" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D2" s="202" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E2" s="142"/>
       <c r="F2" s="202" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G2" s="202" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -9220,10 +9243,10 @@
       </c>
       <c r="D3" s="119"/>
       <c r="F3" s="119" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G3" s="119" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -9236,10 +9259,10 @@
       </c>
       <c r="D4" s="119"/>
       <c r="F4" s="119" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G4" s="119" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -9252,10 +9275,10 @@
       </c>
       <c r="D5" s="119"/>
       <c r="F5" s="119" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G5" s="119" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -9268,10 +9291,10 @@
       </c>
       <c r="D6" s="119"/>
       <c r="F6" s="212" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G6" s="119" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -9285,7 +9308,7 @@
       <c r="D7" s="119"/>
       <c r="F7" s="213"/>
       <c r="G7" s="119" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -9298,10 +9321,10 @@
       </c>
       <c r="D8" s="119"/>
       <c r="F8" s="119" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="G8" s="119" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -9417,10 +9440,10 @@
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" s="177" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B1" s="178" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C1" s="179"/>
       <c r="D1" s="179"/>
@@ -9440,7 +9463,7 @@
       <c r="R1" s="179"/>
       <c r="S1" s="179"/>
       <c r="T1" s="180" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="U1" s="181"/>
       <c r="V1" s="181"/>
@@ -9458,12 +9481,12 @@
       <c r="AH1" s="181"/>
       <c r="AI1" s="181"/>
       <c r="AJ1" s="180" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AK1" s="181"/>
       <c r="AL1" s="181"/>
       <c r="AM1" s="180" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AN1" s="181"/>
       <c r="AO1" s="181"/>
@@ -9482,7 +9505,7 @@
       <c r="BB1" s="181"/>
       <c r="BC1" s="182"/>
       <c r="BD1" s="183" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="BE1" s="184"/>
       <c r="BF1" s="184"/>
@@ -9652,25 +9675,25 @@
       <c r="BB2" s="186"/>
       <c r="BC2" s="186"/>
       <c r="BD2" s="187" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="BE2" s="187" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="BF2" s="187" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="BG2" s="187" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="BH2" s="188" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="BI2" s="188" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="BJ2" s="188" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -10296,11 +10319,11 @@
       </c>
       <c r="BH8" s="191">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BI8" s="191">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ8" s="191">
         <f t="shared" si="3"/>
@@ -10419,7 +10442,7 @@
       </c>
       <c r="BH9" s="191">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BI9" s="191">
         <f t="shared" si="2"/>
@@ -10815,11 +10838,11 @@
       </c>
       <c r="BH13" s="191">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BI13" s="191">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BJ13" s="191">
         <f t="shared" si="3"/>
@@ -11005,7 +11028,9 @@
       </c>
       <c r="AV15" s="120"/>
       <c r="AW15" s="120"/>
-      <c r="AX15" s="120"/>
+      <c r="AX15" s="120">
+        <v>2</v>
+      </c>
       <c r="AY15" s="120"/>
       <c r="AZ15" s="120"/>
       <c r="BA15" s="120"/>
@@ -11013,11 +11038,11 @@
       <c r="BC15" s="120"/>
       <c r="BD15" s="189">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BE15" s="189" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BF15" s="189" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
@@ -11029,7 +11054,7 @@
       </c>
       <c r="BH15" s="191">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BI15" s="191">
         <f t="shared" si="2"/>
@@ -11405,7 +11430,7 @@
       </c>
       <c r="BH19" s="191">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BI19" s="191">
         <f t="shared" si="2"/>
@@ -11680,7 +11705,9 @@
       <c r="AW22" s="120">
         <v>1</v>
       </c>
-      <c r="AX22" s="120"/>
+      <c r="AX22" s="120">
+        <v>1</v>
+      </c>
       <c r="AY22" s="120"/>
       <c r="AZ22" s="120"/>
       <c r="BA22" s="120"/>
@@ -11688,11 +11715,11 @@
       <c r="BC22" s="120"/>
       <c r="BD22" s="189">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE22" s="189" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF22" s="189" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
@@ -11704,7 +11731,7 @@
       </c>
       <c r="BH22" s="191">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BI22" s="191">
         <f t="shared" si="2"/>
@@ -11872,7 +11899,9 @@
       <c r="AU24" s="120"/>
       <c r="AV24" s="120"/>
       <c r="AW24" s="120"/>
-      <c r="AX24" s="120"/>
+      <c r="AX24" s="120">
+        <v>1</v>
+      </c>
       <c r="AY24" s="120"/>
       <c r="AZ24" s="120"/>
       <c r="BA24" s="120"/>
@@ -11880,11 +11909,11 @@
       <c r="BC24" s="120"/>
       <c r="BD24" s="189">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE24" s="189" cm="1">
         <f t="array" ref="BE24">SUMPRODUCT(--(B24:BC24=INT(B24:BC24)),--(B24:BC24&gt;0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF24" s="189" cm="1">
         <f t="array" ref="BF24">MAX(FREQUENCY(IF((B24:BC24=INT(B24:BC24))*(B24:BC24&gt;0),COLUMN(B24:BC24)),IF((B24:BC24&lt;&gt;INT(B24:BC24))+(B24:BC24&lt;=0),COLUMN(B24:BC24))))</f>
@@ -12244,7 +12273,9 @@
       </c>
       <c r="AV28" s="120"/>
       <c r="AW28" s="120"/>
-      <c r="AX28" s="120"/>
+      <c r="AX28" s="120">
+        <v>2</v>
+      </c>
       <c r="AY28" s="120"/>
       <c r="AZ28" s="120"/>
       <c r="BA28" s="120"/>
@@ -12252,11 +12283,11 @@
       <c r="BC28" s="120"/>
       <c r="BD28" s="189">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE28" s="189" cm="1">
         <f t="array" ref="BE28">SUMPRODUCT(--(B28:BC28=INT(B28:BC28)),--(B28:BC28&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF28" s="189" cm="1">
         <f t="array" ref="BF28">MAX(FREQUENCY(IF((B28:BC28=INT(B28:BC28))*(B28:BC28&gt;0),COLUMN(B28:BC28)),IF((B28:BC28&lt;&gt;INT(B28:BC28))+(B28:BC28&lt;=0),COLUMN(B28:BC28))))</f>
@@ -12268,7 +12299,7 @@
       </c>
       <c r="BH28" s="191">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BI28" s="191">
         <f t="shared" si="2"/>
@@ -12377,11 +12408,11 @@
       </c>
       <c r="BH29" s="191">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BI29" s="191">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BJ29" s="191">
         <f t="shared" si="3"/>
@@ -12478,7 +12509,7 @@
       </c>
       <c r="BH30" s="191">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BI30" s="191">
         <f t="shared" si="2"/>
@@ -12587,11 +12618,11 @@
       </c>
       <c r="BH31" s="191">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BI31" s="191">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BJ31" s="191">
         <f t="shared" si="3"/>
@@ -12672,7 +12703,9 @@
       <c r="AU32" s="120"/>
       <c r="AV32" s="120"/>
       <c r="AW32" s="120"/>
-      <c r="AX32" s="120"/>
+      <c r="AX32" s="120">
+        <v>1</v>
+      </c>
       <c r="AY32" s="120"/>
       <c r="AZ32" s="120"/>
       <c r="BA32" s="120"/>
@@ -12680,11 +12713,11 @@
       <c r="BC32" s="120"/>
       <c r="BD32" s="189">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BE32" s="189" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF32" s="189" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
@@ -13135,7 +13168,9 @@
       <c r="AU37" s="120"/>
       <c r="AV37" s="120"/>
       <c r="AW37" s="120"/>
-      <c r="AX37" s="120"/>
+      <c r="AX37" s="120">
+        <v>1</v>
+      </c>
       <c r="AY37" s="120"/>
       <c r="AZ37" s="120"/>
       <c r="BA37" s="120"/>
@@ -13143,11 +13178,11 @@
       <c r="BC37" s="120"/>
       <c r="BD37" s="189">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE37" s="189" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF37" s="189" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
@@ -13159,7 +13194,7 @@
       </c>
       <c r="BH37" s="191">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BI37" s="191">
         <f t="shared" si="2"/>
@@ -13452,7 +13487,9 @@
       </c>
       <c r="AV40" s="120"/>
       <c r="AW40" s="120"/>
-      <c r="AX40" s="120"/>
+      <c r="AX40" s="120">
+        <v>2</v>
+      </c>
       <c r="AY40" s="120"/>
       <c r="AZ40" s="120"/>
       <c r="BA40" s="120"/>
@@ -13460,11 +13497,11 @@
       <c r="BC40" s="120"/>
       <c r="BD40" s="189">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BE40" s="189" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF40" s="189" cm="1">
         <f t="array" ref="BF40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
@@ -13599,7 +13636,7 @@
       </c>
       <c r="BI41" s="191">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BJ41" s="191">
         <f t="shared" si="3"/>
@@ -13696,7 +13733,9 @@
         <v>1</v>
       </c>
       <c r="AW42" s="120"/>
-      <c r="AX42" s="120"/>
+      <c r="AX42" s="120">
+        <v>2</v>
+      </c>
       <c r="AY42" s="120"/>
       <c r="AZ42" s="120"/>
       <c r="BA42" s="120"/>
@@ -13704,11 +13743,11 @@
       <c r="BC42" s="120"/>
       <c r="BD42" s="189">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE42" s="189" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BF42" s="189" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
@@ -14142,7 +14181,9 @@
       <c r="AW46" s="120">
         <v>1</v>
       </c>
-      <c r="AX46" s="120"/>
+      <c r="AX46" s="120">
+        <v>1</v>
+      </c>
       <c r="AY46" s="120"/>
       <c r="AZ46" s="120"/>
       <c r="BA46" s="120"/>
@@ -14150,11 +14191,11 @@
       <c r="BC46" s="120"/>
       <c r="BD46" s="189">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BE46" s="189" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BF46" s="189" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
@@ -14344,7 +14385,9 @@
       </c>
       <c r="AV48" s="120"/>
       <c r="AW48" s="120"/>
-      <c r="AX48" s="120"/>
+      <c r="AX48" s="120">
+        <v>1</v>
+      </c>
       <c r="AY48" s="120"/>
       <c r="AZ48" s="120"/>
       <c r="BA48" s="120"/>
@@ -14352,11 +14395,11 @@
       <c r="BC48" s="120"/>
       <c r="BD48" s="189">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE48" s="189" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF48" s="189" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
@@ -14368,7 +14411,7 @@
       </c>
       <c r="BH48" s="191">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BI48" s="191">
         <f t="shared" si="2"/>
@@ -14836,7 +14879,7 @@
     </row>
     <row r="54" s="175" customFormat="1" ht="28" spans="1:62">
       <c r="A54" s="194" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B54" s="17" cm="1">
         <f t="array" ref="B54">SUMPRODUCT(--(B3:B53=INT(B3:B53)),--(B3:B53&gt;0))</f>
@@ -15032,7 +15075,7 @@
       </c>
       <c r="AX54" s="17" cm="1">
         <f t="array" ref="AX54">SUMPRODUCT(--(AX3:AX53=INT(AX3:AX53)),--(AX3:AX53&gt;0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY54" s="17" cm="1">
         <f t="array" ref="AY54">SUMPRODUCT(--(AY3:AY53=INT(AY3:AY53)),--(AY3:AY53&gt;0))</f>
@@ -15055,7 +15098,7 @@
         <v>0</v>
       </c>
       <c r="BD54" s="195" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="BE54" s="196"/>
       <c r="BF54" s="196"/>
@@ -15066,7 +15109,7 @@
     </row>
     <row r="55" s="175" customFormat="1" ht="28" spans="1:62">
       <c r="A55" s="194" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B55" s="17">
         <f>SUM(B3:B53)</f>
@@ -15262,7 +15305,7 @@
       </c>
       <c r="AX55" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY55" s="17">
         <f t="shared" si="5"/>
@@ -16436,9 +16479,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A41:W41 AX22:BJ22 AF41:BJ42 Y41 Y49 Y42:AE42 A50:BJ50 AG51:BJ53 A54:BJ55 AG49:BJ49 Y4:AV4 AX4:BG4 Z3:BH3 BJ3 B1:BJ1 A2:BJ2 AA11:BJ11 A12:BJ21 Y22:AV22 AG23:BJ23 A24:BJ40 Y9:AC9 AG9:AV9 AX9:BH9 Y10 AG10:BJ10" formulaRange="1"/>
-    <ignoredError sqref="X41 A48:X49 A42:X42 Z42:AE42 A51:AF53 A50:AD50 AF50 Z49:AF49 A49:X49 A4:X4 Z4:AE4 BH4:BJ4 BH5:BJ8 BI3 Z3:AF3 A3:X3 A1 C1:S1 U1:AF1 BD1:BJ2 A2:AF2 A11:Z11 AB11:AC11 AE11 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A16:AF16 A17:X18 Z17:AF18 A19:AF21 BH11:BJ14 A12:X15 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X25 Z24:AF25 A26:AF27 A28:X33 Z29:AF29 A34:AF35 A36:X36 Z36:AF36 A38:X38 Z38:AB38 AD38:AF38 AC40:AD40 A40:V40 BH36:BJ39 BI35:BJ35 BH24:BJ28 A37:AF37 A39:AF39 AD9:AF9 Z9:AB9 BI9:BJ9 Z10:AF10 A45:AF45 A44:W44 Z44:AD44 AF44 A43:AF43 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 Z48:AB48 AE48 A9:X10" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="X8:AF8 A8:V8 A5:AF7 Z41:AE41 A3:X3 BH5:BJ8" unlockedFormula="1"/>
+    <ignoredError sqref="A5:AF7 A8:V8 X8:AF8 Z41:AE41 BH36:BJ38 A34:AF34 A28:X32 Z24:AF24 A24:X24 BH11:BJ11 BD1:BJ1" unlockedFormula="1"/>
+    <ignoredError sqref="BH4:BJ8 A3:X4 Z42:AE42 A9:X10 AE48 Z48:AB48 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 Z10:AF10 BI9:BJ9 Z9:AB9 AD9:AF9 A39:AF39 A37:AF37 BH24:BJ28 BI35:BJ35 BH39:BJ39 BH36:BJ36 BH38:BJ38 A40:V40 AC40:AD40 AC40:AD40 AD38:AF38 AD38:AF38 Z38:AB38 Z38:AB38 A38:X38 A38:X38 Z36:AF36 Z36:AF36 A36:X36 A36:X36 A35:AF35 A34:AF34 Z29:AF29 A33:X33 A29:X31 A28:X33 A26:AF27 Z25:AF25 Z24:AF25 A25:X25 A24:X24 A23:AF23 AF22 AA22:AD22 AA22:AD22 A22:X22 A12:X15 BH12:BJ14 A19:AF21 Z17:AF18 A17:X18 A17:X18 A16:AF16 A16:AF16 Z12:AF12 Z12:AF12 Z13 Z13 AB13:AF13 AB13:AF13 Z14:AF14 Z14:AF14 Z15 AB15:AE15 AB15:AE15 AE11 AB11:AC11 AB11:AC11 A11:Z11 A2:AF2 BD2:BJ2 BD1:BJ2 U1:AF1 C1:S1 C1:S1 A1 Z3:AF3 BI3 Z4:AE4 Z49:AF49 AF50 A50:AD50 A50:AD50 A51:AF53 A42:X42 A49:X49 X41" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="Y24:AW24 AY24:BG24 Y28:AW28 AY28:BG28 Y32:AW32 AY32:BJ32 AY37:BG37 AY40:BJ40 AY15:BJ15 AX4:BG4 A54:BJ55 AF41:BJ41 AY42:BJ42 AY22:BJ22 Y41:Y42 AF42:AW42 Y9:Y10 AG10:BJ10 AX9:BH9 AC9 AG9:AV9 AG39:BJ39 AG37:AW37 A35:BH35 A36:BJ36 A38:BG38 W40:AW40 A33:BJ33 AG34:BJ34 A28:X32 AG29:BJ29 A30:BJ31 A25:BG25 AG26:BG27 AG23:BJ23 Y22:AE22 AG22:AV22 Y12:BG14 AG17:BJ21 A16:BJ16 A17:Y18 Y15 AA15:AW15 AA11:AD11 AF11:BG11 AG2:BJ2 AG1:BJ1 B1:T1 AG3:BH3 BJ3 Y4 AF4:AV4 Y49 AG49:BJ53 A50:AE50 A41:W41" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -16485,21 +16528,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="149" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B2" s="153" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C2" s="154" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="D2" s="155"/>
       <c r="E2" s="153" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F2" s="153"/>
       <c r="G2" s="156" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H2" s="148"/>
       <c r="I2" s="148"/>
@@ -16507,10 +16550,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="149" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B3" s="158" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C3" s="158"/>
       <c r="D3" s="158"/>
@@ -16523,10 +16566,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="149" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B4" s="159" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C4" s="159"/>
       <c r="D4" s="159"/>
@@ -16539,7 +16582,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="149" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B5" s="160">
         <v>1</v>
@@ -16559,7 +16602,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="149" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B6" s="162">
         <v>1</v>
@@ -16569,7 +16612,7 @@
       <c r="E6" s="162"/>
       <c r="F6" s="162"/>
       <c r="G6" s="163" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H6" s="148"/>
       <c r="I6" s="148"/>
@@ -16577,10 +16620,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="149" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B7" s="164" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C7" s="164"/>
       <c r="D7" s="164"/>
@@ -16595,14 +16638,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="149" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B8" s="166">
         <v>1</v>
       </c>
       <c r="C8" s="166"/>
       <c r="D8" s="167" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
@@ -16613,10 +16656,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="149" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B9" s="153" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C9" s="153"/>
       <c r="D9" s="153"/>
@@ -16629,23 +16672,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="149" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B10" s="158">
         <v>1</v>
       </c>
       <c r="C10" s="158"/>
       <c r="D10" s="168" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E10" s="158">
         <v>1</v>
       </c>
       <c r="F10" s="168" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G10" s="148" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H10" s="148"/>
       <c r="I10" s="148"/>
@@ -16653,7 +16696,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="149" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B11" s="159">
         <v>1</v>
@@ -16669,7 +16712,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="149" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B12" s="160">
         <v>1</v>
@@ -16687,17 +16730,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="149" t="s">
+        <v>353</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="169" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -16705,10 +16748,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="149" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B14" s="171" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C14" s="171"/>
       <c r="D14" s="171"/>
@@ -16783,7 +16826,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -16808,10 +16851,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -16824,7 +16867,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -16848,7 +16891,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -16861,7 +16904,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
@@ -16891,7 +16934,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16906,7 +16949,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -16919,7 +16962,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -16932,7 +16975,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>72</v>
@@ -16944,10 +16987,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>91</v>
@@ -16973,10 +17016,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="142"/>
       <c r="B14" s="136" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D14" s="143"/>
       <c r="E14" s="138"/>
@@ -16988,7 +17031,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="142"/>
       <c r="B15" s="136" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -17012,7 +17055,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="142"/>
       <c r="B17" s="136" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -17025,7 +17068,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="142"/>
       <c r="B18" s="136" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -17038,7 +17081,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="142"/>
       <c r="B19" s="136" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>84</v>
@@ -17051,7 +17094,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="142"/>
       <c r="B20" s="136" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>87</v>
@@ -17064,7 +17107,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="142"/>
       <c r="B21" s="136" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C21" s="144"/>
       <c r="D21" s="145"/>
@@ -17077,7 +17120,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="146"/>
       <c r="B22" s="136" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C22" s="144"/>
       <c r="D22" s="147"/>
@@ -17140,7 +17183,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -17171,7 +17214,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -17363,7 +17406,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -17555,7 +17598,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -17782,13 +17825,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C1" s="84" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -17796,208 +17839,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -18005,118 +18048,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -18124,138 +18167,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="2"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="667">
   <si>
     <t>姓名</t>
   </si>
@@ -1056,6 +1056,12 @@
   </si>
   <si>
     <t>下午第二节语文</t>
+  </si>
+  <si>
+    <t>2026.3.18</t>
+  </si>
+  <si>
+    <t>上午第三节政治</t>
   </si>
   <si>
     <t>座号</t>
@@ -3373,18 +3379,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="major"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -3395,10 +3389,22 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="57">
@@ -6071,16 +6077,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6094,7 +6100,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6108,7 +6114,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6122,7 +6128,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6150,7 +6156,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6164,7 +6170,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6178,7 +6184,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6192,7 +6198,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6206,7 +6212,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6232,7 +6238,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6246,7 +6252,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6260,7 +6266,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6286,7 +6292,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6300,7 +6306,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6338,7 +6344,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6352,7 +6358,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6378,7 +6384,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6392,7 +6398,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6406,7 +6412,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6420,7 +6426,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6434,7 +6440,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6448,7 +6454,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6474,7 +6480,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6488,7 +6494,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6502,7 +6508,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6528,7 +6534,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6554,7 +6560,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6568,7 +6574,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6582,10 +6588,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E38" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6599,7 +6605,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6613,7 +6619,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6627,10 +6633,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E41" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6656,7 +6662,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6682,7 +6688,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6708,10 +6714,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E47" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6725,7 +6731,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6751,7 +6757,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6777,7 +6783,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -6810,34 +6816,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>248</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6845,10 +6851,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6856,10 +6862,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6867,10 +6873,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6878,23 +6884,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6902,10 +6908,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6913,10 +6919,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6924,10 +6930,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6935,10 +6941,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6946,50 +6952,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -6998,24 +7004,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -7023,17 +7029,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -7042,22 +7048,22 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
@@ -7068,35 +7074,35 @@
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -7104,10 +7110,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7115,10 +7121,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7126,27 +7132,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7154,10 +7160,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7165,10 +7171,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7176,53 +7182,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7233,42 +7239,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7276,64 +7282,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7343,16 +7349,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7361,7 +7367,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7370,42 +7376,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7415,10 +7421,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7426,10 +7432,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7441,18 +7447,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -7560,7 +7566,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7574,7 +7580,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7598,7 +7604,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7611,7 +7617,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7624,7 +7630,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7658,7 +7664,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7704,7 +7710,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7740,7 +7746,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7774,10 +7780,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7789,10 +7795,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7815,7 +7821,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7828,10 +7834,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7865,10 +7871,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7880,10 +7886,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7907,7 +7913,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7974,7 +7980,7 @@
         <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7988,7 +7994,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -8000,7 +8006,7 @@
         <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -8014,7 +8020,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -8026,10 +8032,10 @@
         <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -8042,7 +8048,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -8065,7 +8071,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -8089,7 +8095,7 @@
         <v>104</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -8125,7 +8131,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8149,7 +8155,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8172,10 +8178,10 @@
         <v>117</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8211,27 +8217,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8239,13 +8245,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8253,13 +8259,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8267,13 +8273,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8281,13 +8287,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8295,13 +8301,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8309,13 +8315,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8323,7 +8329,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8331,7 +8337,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8339,7 +8345,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8347,7 +8353,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -9336,8 +9342,12 @@
         <v>89</v>
       </c>
       <c r="D9" s="119"/>
-      <c r="F9" s="119"/>
-      <c r="G9" s="119"/>
+      <c r="F9" s="119" t="s">
+        <v>316</v>
+      </c>
+      <c r="G9" s="119" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="212">
@@ -9440,10 +9450,10 @@
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" s="177" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B1" s="178" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C1" s="179"/>
       <c r="D1" s="179"/>
@@ -9463,7 +9473,7 @@
       <c r="R1" s="179"/>
       <c r="S1" s="179"/>
       <c r="T1" s="180" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="U1" s="181"/>
       <c r="V1" s="181"/>
@@ -9481,12 +9491,12 @@
       <c r="AH1" s="181"/>
       <c r="AI1" s="181"/>
       <c r="AJ1" s="180" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AK1" s="181"/>
       <c r="AL1" s="181"/>
       <c r="AM1" s="180" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AN1" s="181"/>
       <c r="AO1" s="181"/>
@@ -9505,7 +9515,7 @@
       <c r="BB1" s="181"/>
       <c r="BC1" s="182"/>
       <c r="BD1" s="183" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="BE1" s="184"/>
       <c r="BF1" s="184"/>
@@ -9675,25 +9685,25 @@
       <c r="BB2" s="186"/>
       <c r="BC2" s="186"/>
       <c r="BD2" s="187" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="BE2" s="187" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BF2" s="187" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BG2" s="187" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BH2" s="188" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BI2" s="188" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BJ2" s="188" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9874,18 +9884,20 @@
         <v>1</v>
       </c>
       <c r="AX4" s="120"/>
-      <c r="AY4" s="120"/>
+      <c r="AY4" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ4" s="120"/>
       <c r="BA4" s="120"/>
       <c r="BB4" s="120"/>
       <c r="BC4" s="120"/>
       <c r="BD4" s="189">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE4" s="189" cm="1">
         <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF4" s="189" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
@@ -10066,18 +10078,20 @@
       <c r="AV6" s="120"/>
       <c r="AW6" s="120"/>
       <c r="AX6" s="120"/>
-      <c r="AY6" s="120"/>
+      <c r="AY6" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ6" s="120"/>
       <c r="BA6" s="120"/>
       <c r="BB6" s="120"/>
       <c r="BC6" s="120"/>
       <c r="BD6" s="189">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE6" s="189" cm="1">
         <f t="array" ref="BE6">SUMPRODUCT(--(B6:BC6=INT(B6:BC6)),--(B6:BC6&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF6" s="189" cm="1">
         <f t="array" ref="BF6">MAX(FREQUENCY(IF((B6:BC6=INT(B6:BC6))*(B6:BC6&gt;0),COLUMN(B6:BC6)),IF((B6:BC6&lt;&gt;INT(B6:BC6))+(B6:BC6&lt;=0),COLUMN(B6:BC6))))</f>
@@ -10089,7 +10103,7 @@
       </c>
       <c r="BH6" s="191">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BI6" s="191">
         <f t="shared" si="2"/>
@@ -10159,18 +10173,20 @@
       <c r="AV7" s="120"/>
       <c r="AW7" s="120"/>
       <c r="AX7" s="120"/>
-      <c r="AY7" s="120"/>
+      <c r="AY7" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ7" s="120"/>
       <c r="BA7" s="120"/>
       <c r="BB7" s="120"/>
       <c r="BC7" s="120"/>
       <c r="BD7" s="189">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE7" s="189" cm="1">
         <f t="array" ref="BE7">SUMPRODUCT(--(B7:BC7=INT(B7:BC7)),--(B7:BC7&gt;0))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BF7" s="189" cm="1">
         <f t="array" ref="BF7">MAX(FREQUENCY(IF((B7:BC7=INT(B7:BC7))*(B7:BC7&gt;0),COLUMN(B7:BC7)),IF((B7:BC7&lt;&gt;INT(B7:BC7))+(B7:BC7&lt;=0),COLUMN(B7:BC7))))</f>
@@ -10182,11 +10198,11 @@
       </c>
       <c r="BH7" s="191">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BI7" s="191">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BJ7" s="191">
         <f t="shared" si="3"/>
@@ -10296,18 +10312,20 @@
       </c>
       <c r="AW8" s="120"/>
       <c r="AX8" s="120"/>
-      <c r="AY8" s="120"/>
+      <c r="AY8" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ8" s="120"/>
       <c r="BA8" s="120"/>
       <c r="BB8" s="120"/>
       <c r="BC8" s="120"/>
       <c r="BD8" s="189">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE8" s="189" cm="1">
         <f t="array" ref="BE8">SUMPRODUCT(--(B8:BC8=INT(B8:BC8)),--(B8:BC8&gt;0))</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BF8" s="189" cm="1">
         <f t="array" ref="BF8">MAX(FREQUENCY(IF((B8:BC8=INT(B8:BC8))*(B8:BC8&gt;0),COLUMN(B8:BC8)),IF((B8:BC8&lt;&gt;INT(B8:BC8))+(B8:BC8&lt;=0),COLUMN(B8:BC8))))</f>
@@ -10442,11 +10460,11 @@
       </c>
       <c r="BH9" s="191">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BI9" s="191">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BJ9" s="191">
         <f t="shared" si="3"/>
@@ -10638,7 +10656,7 @@
       </c>
       <c r="BH11" s="191">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BI11" s="191">
         <f t="shared" si="2"/>
@@ -10815,18 +10833,20 @@
       <c r="AV13" s="120"/>
       <c r="AW13" s="120"/>
       <c r="AX13" s="120"/>
-      <c r="AY13" s="120"/>
+      <c r="AY13" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ13" s="120"/>
       <c r="BA13" s="120"/>
       <c r="BB13" s="120"/>
       <c r="BC13" s="120"/>
       <c r="BD13" s="189">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE13" s="189" cm="1">
         <f t="array" ref="BE13">SUMPRODUCT(--(B13:BC13=INT(B13:BC13)),--(B13:BC13&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF13" s="189" cm="1">
         <f t="array" ref="BF13">MAX(FREQUENCY(IF((B13:BC13=INT(B13:BC13))*(B13:BC13&gt;0),COLUMN(B13:BC13)),IF((B13:BC13&lt;&gt;INT(B13:BC13))+(B13:BC13&lt;=0),COLUMN(B13:BC13))))</f>
@@ -10838,7 +10858,7 @@
       </c>
       <c r="BH13" s="191">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BI13" s="191">
         <f t="shared" si="2"/>
@@ -10910,18 +10930,20 @@
       <c r="AV14" s="120"/>
       <c r="AW14" s="120"/>
       <c r="AX14" s="120"/>
-      <c r="AY14" s="120"/>
+      <c r="AY14" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ14" s="120"/>
       <c r="BA14" s="120"/>
       <c r="BB14" s="120"/>
       <c r="BC14" s="120"/>
       <c r="BD14" s="189">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BE14" s="189" cm="1">
         <f t="array" ref="BE14">SUMPRODUCT(--(B14:BC14=INT(B14:BC14)),--(B14:BC14&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BF14" s="189" cm="1">
         <f t="array" ref="BF14">MAX(FREQUENCY(IF((B14:BC14=INT(B14:BC14))*(B14:BC14&gt;0),COLUMN(B14:BC14)),IF((B14:BC14&lt;&gt;INT(B14:BC14))+(B14:BC14&lt;=0),COLUMN(B14:BC14))))</f>
@@ -10933,11 +10955,11 @@
       </c>
       <c r="BH14" s="191">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BI14" s="191">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BJ14" s="191">
         <f t="shared" si="3"/>
@@ -11031,18 +11053,20 @@
       <c r="AX15" s="120">
         <v>2</v>
       </c>
-      <c r="AY15" s="120"/>
+      <c r="AY15" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ15" s="120"/>
       <c r="BA15" s="120"/>
       <c r="BB15" s="120"/>
       <c r="BC15" s="120"/>
       <c r="BD15" s="189">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE15" s="189" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BF15" s="189" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
@@ -11058,7 +11082,7 @@
       </c>
       <c r="BI15" s="191">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BJ15" s="191">
         <f t="shared" si="3"/>
@@ -11240,11 +11264,11 @@
       </c>
       <c r="BH17" s="191">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BI17" s="191">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BJ17" s="191">
         <f t="shared" si="3"/>
@@ -11407,18 +11431,20 @@
       </c>
       <c r="AW19" s="120"/>
       <c r="AX19" s="120"/>
-      <c r="AY19" s="120"/>
+      <c r="AY19" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ19" s="120"/>
       <c r="BA19" s="120"/>
       <c r="BB19" s="120"/>
       <c r="BC19" s="120"/>
       <c r="BD19" s="189">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE19" s="189" cm="1">
         <f t="array" ref="BE19">SUMPRODUCT(--(B19:BC19=INT(B19:BC19)),--(B19:BC19&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF19" s="189" cm="1">
         <f t="array" ref="BF19">MAX(FREQUENCY(IF((B19:BC19=INT(B19:BC19))*(B19:BC19&gt;0),COLUMN(B19:BC19)),IF((B19:BC19&lt;&gt;INT(B19:BC19))+(B19:BC19&lt;=0),COLUMN(B19:BC19))))</f>
@@ -11430,7 +11456,7 @@
       </c>
       <c r="BH19" s="191">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BI19" s="191">
         <f t="shared" si="2"/>
@@ -11618,7 +11644,7 @@
       </c>
       <c r="BI21" s="191">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BJ21" s="191">
         <f t="shared" si="3"/>
@@ -11708,18 +11734,20 @@
       <c r="AX22" s="120">
         <v>1</v>
       </c>
-      <c r="AY22" s="120"/>
+      <c r="AY22" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ22" s="120"/>
       <c r="BA22" s="120"/>
       <c r="BB22" s="120"/>
       <c r="BC22" s="120"/>
       <c r="BD22" s="189">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE22" s="189" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BF22" s="189" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
@@ -11735,7 +11763,7 @@
       </c>
       <c r="BI22" s="191">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BJ22" s="191">
         <f t="shared" si="3"/>
@@ -11929,7 +11957,7 @@
       </c>
       <c r="BI24" s="191">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BJ24" s="191">
         <f t="shared" si="3"/>
@@ -12276,18 +12304,20 @@
       <c r="AX28" s="120">
         <v>2</v>
       </c>
-      <c r="AY28" s="120"/>
+      <c r="AY28" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ28" s="120"/>
       <c r="BA28" s="120"/>
       <c r="BB28" s="120"/>
       <c r="BC28" s="120"/>
       <c r="BD28" s="189">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE28" s="189" cm="1">
         <f t="array" ref="BE28">SUMPRODUCT(--(B28:BC28=INT(B28:BC28)),--(B28:BC28&gt;0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF28" s="189" cm="1">
         <f t="array" ref="BF28">MAX(FREQUENCY(IF((B28:BC28=INT(B28:BC28))*(B28:BC28&gt;0),COLUMN(B28:BC28)),IF((B28:BC28&lt;&gt;INT(B28:BC28))+(B28:BC28&lt;=0),COLUMN(B28:BC28))))</f>
@@ -12408,11 +12438,11 @@
       </c>
       <c r="BH29" s="191">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BI29" s="191">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BJ29" s="191">
         <f t="shared" si="3"/>
@@ -12509,11 +12539,11 @@
       </c>
       <c r="BH30" s="191">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BI30" s="191">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BJ30" s="191">
         <f t="shared" si="3"/>
@@ -12622,7 +12652,7 @@
       </c>
       <c r="BI31" s="191">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BJ31" s="191">
         <f t="shared" si="3"/>
@@ -12706,18 +12736,20 @@
       <c r="AX32" s="120">
         <v>1</v>
       </c>
-      <c r="AY32" s="120"/>
+      <c r="AY32" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ32" s="120"/>
       <c r="BA32" s="120"/>
       <c r="BB32" s="120"/>
       <c r="BC32" s="120"/>
       <c r="BD32" s="189">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE32" s="189" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF32" s="189" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
@@ -13171,18 +13203,20 @@
       <c r="AX37" s="120">
         <v>1</v>
       </c>
-      <c r="AY37" s="120"/>
+      <c r="AY37" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ37" s="120"/>
       <c r="BA37" s="120"/>
       <c r="BB37" s="120"/>
       <c r="BC37" s="120"/>
       <c r="BD37" s="189">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE37" s="189" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF37" s="189" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
@@ -13194,11 +13228,11 @@
       </c>
       <c r="BH37" s="191">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BI37" s="191">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BJ37" s="191">
         <f t="shared" si="3"/>
@@ -13287,11 +13321,11 @@
       </c>
       <c r="BH38" s="191">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BI38" s="191">
         <f t="shared" si="2"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BJ38" s="191">
         <f t="shared" si="3"/>
@@ -13490,18 +13524,20 @@
       <c r="AX40" s="120">
         <v>2</v>
       </c>
-      <c r="AY40" s="120"/>
+      <c r="AY40" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ40" s="120"/>
       <c r="BA40" s="120"/>
       <c r="BB40" s="120"/>
       <c r="BC40" s="120"/>
       <c r="BD40" s="189">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BE40" s="189" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BF40" s="189" cm="1">
         <f t="array" ref="BF40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
@@ -13632,7 +13668,7 @@
       </c>
       <c r="BH41" s="191">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BI41" s="191">
         <f t="shared" si="2"/>
@@ -13736,18 +13772,20 @@
       <c r="AX42" s="120">
         <v>2</v>
       </c>
-      <c r="AY42" s="120"/>
+      <c r="AY42" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ42" s="120"/>
       <c r="BA42" s="120"/>
       <c r="BB42" s="120"/>
       <c r="BC42" s="120"/>
       <c r="BD42" s="189">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE42" s="189" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BF42" s="189" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
@@ -13946,18 +13984,20 @@
       </c>
       <c r="AW44" s="120"/>
       <c r="AX44" s="120"/>
-      <c r="AY44" s="120"/>
+      <c r="AY44" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ44" s="120"/>
       <c r="BA44" s="120"/>
       <c r="BB44" s="120"/>
       <c r="BC44" s="120"/>
       <c r="BD44" s="189">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE44" s="189" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF44" s="189" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
@@ -14184,22 +14224,24 @@
       <c r="AX46" s="120">
         <v>1</v>
       </c>
-      <c r="AY46" s="120"/>
+      <c r="AY46" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ46" s="120"/>
       <c r="BA46" s="120"/>
       <c r="BB46" s="120"/>
       <c r="BC46" s="120"/>
       <c r="BD46" s="189">
         <f t="shared" si="0"/>
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="BE46" s="189" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BF46" s="189" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BG46" s="190" cm="1">
         <f t="array" ref="BG46">SUMPRODUCT(--(B46:AI46=INT(B46:AI46)),--(B46:AI46&gt;0))/34*100%</f>
@@ -14388,18 +14430,20 @@
       <c r="AX48" s="120">
         <v>1</v>
       </c>
-      <c r="AY48" s="120"/>
+      <c r="AY48" s="120">
+        <v>1</v>
+      </c>
       <c r="AZ48" s="120"/>
       <c r="BA48" s="120"/>
       <c r="BB48" s="120"/>
       <c r="BC48" s="120"/>
       <c r="BD48" s="189">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE48" s="189" cm="1">
         <f t="array" ref="BE48">SUMPRODUCT(--(B48:BC48=INT(B48:BC48)),--(B48:BC48&gt;0))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BF48" s="189" cm="1">
         <f t="array" ref="BF48">MAX(FREQUENCY(IF((B48:BC48=INT(B48:BC48))*(B48:BC48&gt;0),COLUMN(B48:BC48)),IF((B48:BC48&lt;&gt;INT(B48:BC48))+(B48:BC48&lt;=0),COLUMN(B48:BC48))))</f>
@@ -14415,7 +14459,7 @@
       </c>
       <c r="BI48" s="191">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BJ48" s="191">
         <f t="shared" si="3"/>
@@ -14506,11 +14550,11 @@
       </c>
       <c r="BH49" s="191">
         <f t="shared" si="1"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BI49" s="191">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BJ49" s="191">
         <f t="shared" si="3"/>
@@ -14879,7 +14923,7 @@
     </row>
     <row r="54" s="175" customFormat="1" ht="28" spans="1:62">
       <c r="A54" s="194" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B54" s="17" cm="1">
         <f t="array" ref="B54">SUMPRODUCT(--(B3:B53=INT(B3:B53)),--(B3:B53&gt;0))</f>
@@ -15079,7 +15123,7 @@
       </c>
       <c r="AY54" s="17" cm="1">
         <f t="array" ref="AY54">SUMPRODUCT(--(AY3:AY53=INT(AY3:AY53)),--(AY3:AY53&gt;0))</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ54" s="17" cm="1">
         <f t="array" ref="AZ54">SUMPRODUCT(--(AZ3:AZ53=INT(AZ3:AZ53)),--(AZ3:AZ53&gt;0))</f>
@@ -15098,7 +15142,7 @@
         <v>0</v>
       </c>
       <c r="BD54" s="195" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BE54" s="196"/>
       <c r="BF54" s="196"/>
@@ -15109,7 +15153,7 @@
     </row>
     <row r="55" s="175" customFormat="1" ht="28" spans="1:62">
       <c r="A55" s="194" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B55" s="17">
         <f>SUM(B3:B53)</f>
@@ -15309,7 +15353,7 @@
       </c>
       <c r="AY55" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ55" s="17">
         <f t="shared" si="5"/>
@@ -16479,9 +16523,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A5:AF7 A8:V8 X8:AF8 Z41:AE41 BH36:BJ38 A34:AF34 A28:X32 Z24:AF24 A24:X24 BH11:BJ11 BD1:BJ1" unlockedFormula="1"/>
-    <ignoredError sqref="BH4:BJ8 A3:X4 Z42:AE42 A9:X10 AE48 Z48:AB48 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A43:AF43 AF44 Z44:AD44 A44:W44 A45:AF45 Z10:AF10 BI9:BJ9 Z9:AB9 AD9:AF9 A39:AF39 A37:AF37 BH24:BJ28 BI35:BJ35 BH39:BJ39 BH36:BJ36 BH38:BJ38 A40:V40 AC40:AD40 AC40:AD40 AD38:AF38 AD38:AF38 Z38:AB38 Z38:AB38 A38:X38 A38:X38 Z36:AF36 Z36:AF36 A36:X36 A36:X36 A35:AF35 A34:AF34 Z29:AF29 A33:X33 A29:X31 A28:X33 A26:AF27 Z25:AF25 Z24:AF25 A25:X25 A24:X24 A23:AF23 AF22 AA22:AD22 AA22:AD22 A22:X22 A12:X15 BH12:BJ14 A19:AF21 Z17:AF18 A17:X18 A17:X18 A16:AF16 A16:AF16 Z12:AF12 Z12:AF12 Z13 Z13 AB13:AF13 AB13:AF13 Z14:AF14 Z14:AF14 Z15 AB15:AE15 AB15:AE15 AE11 AB11:AC11 AB11:AC11 A11:Z11 A2:AF2 BD2:BJ2 BD1:BJ2 U1:AF1 C1:S1 C1:S1 A1 Z3:AF3 BI3 Z4:AE4 Z49:AF49 AF50 A50:AD50 A50:AD50 A51:AF53 A42:X42 A49:X49 X41" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="Y24:AW24 AY24:BG24 Y28:AW28 AY28:BG28 Y32:AW32 AY32:BJ32 AY37:BG37 AY40:BJ40 AY15:BJ15 AX4:BG4 A54:BJ55 AF41:BJ41 AY42:BJ42 AY22:BJ22 Y41:Y42 AF42:AW42 Y9:Y10 AG10:BJ10 AX9:BH9 AC9 AG9:AV9 AG39:BJ39 AG37:AW37 A35:BH35 A36:BJ36 A38:BG38 W40:AW40 A33:BJ33 AG34:BJ34 A28:X32 AG29:BJ29 A30:BJ31 A25:BG25 AG26:BG27 AG23:BJ23 Y22:AE22 AG22:AV22 Y12:BG14 AG17:BJ21 A16:BJ16 A17:Y18 Y15 AA15:AW15 AA11:AD11 AF11:BG11 AG2:BJ2 AG1:BJ1 B1:T1 AG3:BH3 BJ3 Y4 AF4:AV4 Y49 AG49:BJ53 A50:AE50 A41:W41" formulaRange="1"/>
+    <ignoredError sqref="BH4:BJ4" unlockedFormula="1"/>
+    <ignoredError sqref="BH38:BJ39 BH38:BJ39 A5:AF7 A8:V8 A8:V8 X8:AF8 X8:AF8 A32:X32 A32:X32 BH5:BJ8 BH4:BJ4 A3:X4 A3:X4 Z41:AE42 A9:X10 A9:X10 AE48 Z48:AB48 Z48:AB48 A47:AF47 A47:AF47 AF46 AF46 AC46:AD46 AC46:AD46 AA46 AA46 A46:X46 A46:X46 A43:AF43 A43:AF43 AF44 AF44 Z44:AD44 Z44:AD44 A44:W44 A44:W44 A45:AF45 A45:AF45 Z10:AF10 Z10:AF10 BI9:BJ9 BI9:BJ9 Z9:AB9 Z9:AB9 AD9:AF9 AD9:AF9 A39:AF39 A39:AF39 A37:AF37 A37:AF37 BH24:BJ28 BH24:BJ28 BI35:BJ35 BI35:BJ35 A40:V40 A40:V40 AC40:AD40 AC40:AD40 AD38:AF38 AD38:AF38 Z38:AB38 Z38:AB38 A38:X38 A38:X38 Z36:AF36 Z36:AF36 A36:X36 A36:X36 A34:AF35 A34:AF35 Z29:AF29 Z29:AF29 A28:X28 A28:X28 A26:AF27 A26:AF27 Z24:AF25 Z24:AF25 A24:X25 A24:X25 A23:AF23 A23:AF23 AF22 AF22 AA22:AD22 AA22:AD22 A22:X22 A22:X22 A12:X15 A12:X15 BH11:BJ14 BH11:BJ14 A19:AF21 A19:AF21 Z17:AF18 Z17:AF18 A17:X18 A17:X18 A16:AF16 A16:AF16 Z12:AF12 Z12:AF12 Z13 Z13 AB13:AF13 AB13:AF13 Z14:AF14 Z14:AF14 Z15 Z15 AB15:AE15 AB15:AE15 AE11 AE11 AB11:AC11 AB11:AC11 A11:Z11 A11:Z11 A2:AF2 A2:AF2 BD1:BJ2 BD1:BJ2 U1:AF1 U1:AF1 C1:S1 C1:S1 A1 A1 Z3:AF3 Z3:AF3 BI3 BI3 Z4:AE4 Z4:AE4 Z49:AF49 Z49:AF49 AF50 AF50 A50:AD50 A50:AD50 A51:AF53 A51:AF53 A42:X42 A49:X49 A49:X49 X41" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="AF41:BJ42 A5:BJ37 A38:BG39 A40:BJ40 A1:BJ3 A4:BG4 A43:BJ47 A48:AD48 AF48:BJ48 A49:BJ55 Y41:Y42 A41:W41" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -16528,21 +16572,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="149" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B2" s="153" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C2" s="154" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D2" s="155"/>
       <c r="E2" s="153" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="F2" s="153"/>
       <c r="G2" s="156" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H2" s="148"/>
       <c r="I2" s="148"/>
@@ -16550,10 +16594,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="149" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B3" s="158" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C3" s="158"/>
       <c r="D3" s="158"/>
@@ -16566,7 +16610,7 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="149" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B4" s="159" t="s">
         <v>248</v>
@@ -16582,7 +16626,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="149" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B5" s="160">
         <v>1</v>
@@ -16602,7 +16646,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="149" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B6" s="162">
         <v>1</v>
@@ -16612,7 +16656,7 @@
       <c r="E6" s="162"/>
       <c r="F6" s="162"/>
       <c r="G6" s="163" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H6" s="148"/>
       <c r="I6" s="148"/>
@@ -16620,10 +16664,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="149" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B7" s="164" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C7" s="164"/>
       <c r="D7" s="164"/>
@@ -16638,14 +16682,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="149" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B8" s="166">
         <v>1</v>
       </c>
       <c r="C8" s="166"/>
       <c r="D8" s="167" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
@@ -16656,10 +16700,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="149" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B9" s="153" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C9" s="153"/>
       <c r="D9" s="153"/>
@@ -16672,23 +16716,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="149" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B10" s="158">
         <v>1</v>
       </c>
       <c r="C10" s="158"/>
       <c r="D10" s="168" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E10" s="158">
         <v>1</v>
       </c>
       <c r="F10" s="168" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G10" s="148" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H10" s="148"/>
       <c r="I10" s="148"/>
@@ -16696,7 +16740,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="149" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B11" s="159">
         <v>1</v>
@@ -16712,7 +16756,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="149" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B12" s="160">
         <v>1</v>
@@ -16730,17 +16774,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="149" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="169" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -16748,10 +16792,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="149" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B14" s="171" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C14" s="171"/>
       <c r="D14" s="171"/>
@@ -16826,7 +16870,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -16851,10 +16895,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -16867,7 +16911,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -16891,7 +16935,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -16904,7 +16948,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
@@ -16934,7 +16978,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16949,7 +16993,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -16962,7 +17006,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -16975,7 +17019,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>72</v>
@@ -16987,10 +17031,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>91</v>
@@ -17016,10 +17060,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="142"/>
       <c r="B14" s="136" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D14" s="143"/>
       <c r="E14" s="138"/>
@@ -17031,7 +17075,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="142"/>
       <c r="B15" s="136" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -17055,7 +17099,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="142"/>
       <c r="B17" s="136" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -17068,7 +17112,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="142"/>
       <c r="B18" s="136" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -17081,7 +17125,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="142"/>
       <c r="B19" s="136" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>84</v>
@@ -17094,7 +17138,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="142"/>
       <c r="B20" s="136" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>87</v>
@@ -17107,7 +17151,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="142"/>
       <c r="B21" s="136" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C21" s="144"/>
       <c r="D21" s="145"/>
@@ -17120,7 +17164,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="146"/>
       <c r="B22" s="136" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C22" s="144"/>
       <c r="D22" s="147"/>
@@ -17183,7 +17227,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -17214,7 +17258,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -17406,7 +17450,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -17598,7 +17642,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -17825,10 +17869,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>204</v>
@@ -17839,208 +17883,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -18048,118 +18092,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -18167,138 +18211,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="3"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="669">
   <si>
     <t>姓名</t>
   </si>
@@ -1062,6 +1062,12 @@
   </si>
   <si>
     <t>上午第三节政治</t>
+  </si>
+  <si>
+    <t>2026.3.19</t>
+  </si>
+  <si>
+    <t>下午第二节地理</t>
   </si>
   <si>
     <t>座号</t>
@@ -3385,14 +3391,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="华文仿宋"/>
+      <name val="黑体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="黑体"/>
+      <name val="华文仿宋"/>
       <charset val="134"/>
-      <scheme val="major"/>
     </font>
     <font>
       <strike/>
@@ -3404,7 +3410,7 @@
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="57">
@@ -6077,16 +6083,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="67" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B1" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6100,7 +6106,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6114,7 +6120,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6128,7 +6134,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6156,7 +6162,7 @@
         <v>20120504</v>
       </c>
       <c r="D6" s="66" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6170,7 +6176,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6184,7 +6190,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6198,7 +6204,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6212,7 +6218,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6238,7 +6244,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6252,7 +6258,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6266,7 +6272,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6292,7 +6298,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6306,7 +6312,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6344,7 +6350,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6358,7 +6364,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6384,7 +6390,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6398,7 +6404,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6412,7 +6418,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6426,7 +6432,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6440,7 +6446,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6454,7 +6460,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6480,7 +6486,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6494,7 +6500,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6508,7 +6514,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6534,7 +6540,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6560,7 +6566,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6574,7 +6580,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6588,10 +6594,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E38" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6605,7 +6611,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6619,7 +6625,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6633,10 +6639,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E41" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6662,7 +6668,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6688,7 +6694,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6714,10 +6720,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E47" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6731,7 +6737,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6757,7 +6763,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6783,7 +6789,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -6816,34 +6822,34 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
       <c r="A2" s="39" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B2" s="40" t="s">
         <v>248</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6851,10 +6857,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6862,10 +6868,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6873,10 +6879,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6884,23 +6890,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6908,10 +6914,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6919,10 +6925,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6930,10 +6936,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6941,10 +6947,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6952,50 +6958,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -7004,24 +7010,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -7029,17 +7035,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -7048,22 +7054,22 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
@@ -7074,35 +7080,35 @@
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A25" s="39" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -7110,10 +7116,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7121,10 +7127,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7132,27 +7138,27 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A29" s="39" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7160,10 +7166,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7171,10 +7177,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7182,53 +7188,53 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
       <c r="A36" s="39" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7239,42 +7245,42 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
       <c r="A38" s="29" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
       <c r="A39" s="39" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7282,64 +7288,64 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
       <c r="A43" s="39" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7349,16 +7355,16 @@
     </row>
     <row r="46" s="28" customFormat="1" spans="1:5">
       <c r="A46" s="39" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7367,7 +7373,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7376,42 +7382,42 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
       <c r="A49" s="29" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B49" s="58" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
       <c r="A50" s="39" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7421,10 +7427,10 @@
     </row>
     <row r="52" s="28" customFormat="1" spans="1:5">
       <c r="A52" s="29" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7432,10 +7438,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7447,18 +7453,18 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
       <c r="A55" s="29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B55" s="30"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -7566,7 +7572,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7580,7 +7586,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7604,7 +7610,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7617,7 +7623,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7630,7 +7636,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7664,7 +7670,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7710,7 +7716,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7746,7 +7752,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7780,10 +7786,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7795,10 +7801,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7821,7 +7827,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7834,10 +7840,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7871,10 +7877,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7886,10 +7892,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7913,7 +7919,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -7980,7 +7986,7 @@
         <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -7994,7 +8000,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -8006,7 +8012,7 @@
         <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -8020,7 +8026,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -8032,10 +8038,10 @@
         <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -8048,7 +8054,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -8071,7 +8077,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -8095,7 +8101,7 @@
         <v>104</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -8131,7 +8137,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8155,7 +8161,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8178,10 +8184,10 @@
         <v>117</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8217,27 +8223,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8245,13 +8251,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8259,13 +8265,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8273,13 +8279,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8287,13 +8293,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8301,13 +8307,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8315,13 +8321,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8329,7 +8335,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8337,7 +8343,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8345,7 +8351,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8353,7 +8359,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -9360,8 +9366,12 @@
         <v>118</v>
       </c>
       <c r="D10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="119"/>
+      <c r="F10" s="119" t="s">
+        <v>318</v>
+      </c>
+      <c r="G10" s="119" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="211"/>
@@ -9450,10 +9460,10 @@
   <sheetData>
     <row r="1" spans="1:62">
       <c r="A1" s="177" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B1" s="178" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C1" s="179"/>
       <c r="D1" s="179"/>
@@ -9473,7 +9483,7 @@
       <c r="R1" s="179"/>
       <c r="S1" s="179"/>
       <c r="T1" s="180" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="U1" s="181"/>
       <c r="V1" s="181"/>
@@ -9491,12 +9501,12 @@
       <c r="AH1" s="181"/>
       <c r="AI1" s="181"/>
       <c r="AJ1" s="180" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AK1" s="181"/>
       <c r="AL1" s="181"/>
       <c r="AM1" s="180" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AN1" s="181"/>
       <c r="AO1" s="181"/>
@@ -9515,7 +9525,7 @@
       <c r="BB1" s="181"/>
       <c r="BC1" s="182"/>
       <c r="BD1" s="183" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BE1" s="184"/>
       <c r="BF1" s="184"/>
@@ -9685,25 +9695,25 @@
       <c r="BB2" s="186"/>
       <c r="BC2" s="186"/>
       <c r="BD2" s="187" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BE2" s="187" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BF2" s="187" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BG2" s="187" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BH2" s="188" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="BI2" s="188" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="BJ2" s="188" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:62">
@@ -9887,17 +9897,19 @@
       <c r="AY4" s="120">
         <v>1</v>
       </c>
-      <c r="AZ4" s="120"/>
+      <c r="AZ4" s="120">
+        <v>1</v>
+      </c>
       <c r="BA4" s="120"/>
       <c r="BB4" s="120"/>
       <c r="BC4" s="120"/>
       <c r="BD4" s="189">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE4" s="189" cm="1">
         <f t="array" ref="BE4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BF4" s="189" cm="1">
         <f t="array" ref="BF4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
@@ -10315,17 +10327,19 @@
       <c r="AY8" s="120">
         <v>1</v>
       </c>
-      <c r="AZ8" s="120"/>
+      <c r="AZ8" s="120">
+        <v>1</v>
+      </c>
       <c r="BA8" s="120"/>
       <c r="BB8" s="120"/>
       <c r="BC8" s="120"/>
       <c r="BD8" s="189">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE8" s="189" cm="1">
         <f t="array" ref="BE8">SUMPRODUCT(--(B8:BC8=INT(B8:BC8)),--(B8:BC8&gt;0))</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BF8" s="189" cm="1">
         <f t="array" ref="BF8">MAX(FREQUENCY(IF((B8:BC8=INT(B8:BC8))*(B8:BC8&gt;0),COLUMN(B8:BC8)),IF((B8:BC8&lt;&gt;INT(B8:BC8))+(B8:BC8&lt;=0),COLUMN(B8:BC8))))</f>
@@ -10438,17 +10452,19 @@
       </c>
       <c r="AX9" s="120"/>
       <c r="AY9" s="120"/>
-      <c r="AZ9" s="120"/>
+      <c r="AZ9" s="120">
+        <v>1</v>
+      </c>
       <c r="BA9" s="120"/>
       <c r="BB9" s="120"/>
       <c r="BC9" s="120"/>
       <c r="BD9" s="189">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE9" s="189" cm="1">
         <f t="array" ref="BE9">SUMPRODUCT(--(B9:BC9=INT(B9:BC9)),--(B9:BC9&gt;0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF9" s="189" cm="1">
         <f t="array" ref="BF9">MAX(FREQUENCY(IF((B9:BC9=INT(B9:BC9))*(B9:BC9&gt;0),COLUMN(B9:BC9)),IF((B9:BC9&lt;&gt;INT(B9:BC9))+(B9:BC9&lt;=0),COLUMN(B9:BC9))))</f>
@@ -10460,7 +10476,7 @@
       </c>
       <c r="BH9" s="191">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BI9" s="191">
         <f t="shared" si="2"/>
@@ -10634,17 +10650,19 @@
       <c r="AW11" s="120"/>
       <c r="AX11" s="120"/>
       <c r="AY11" s="120"/>
-      <c r="AZ11" s="120"/>
+      <c r="AZ11" s="120">
+        <v>1</v>
+      </c>
       <c r="BA11" s="120"/>
       <c r="BB11" s="120"/>
       <c r="BC11" s="120"/>
       <c r="BD11" s="189">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE11" s="189" cm="1">
         <f t="array" ref="BE11">SUMPRODUCT(--(B11:BC11=INT(B11:BC11)),--(B11:BC11&gt;0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF11" s="189" cm="1">
         <f t="array" ref="BF11">MAX(FREQUENCY(IF((B11:BC11=INT(B11:BC11))*(B11:BC11&gt;0),COLUMN(B11:BC11)),IF((B11:BC11&lt;&gt;INT(B11:BC11))+(B11:BC11&lt;=0),COLUMN(B11:BC11))))</f>
@@ -10656,11 +10674,11 @@
       </c>
       <c r="BH11" s="191">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BI11" s="191">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BJ11" s="191">
         <f t="shared" si="3"/>
@@ -11056,17 +11074,19 @@
       <c r="AY15" s="120">
         <v>1</v>
       </c>
-      <c r="AZ15" s="120"/>
+      <c r="AZ15" s="120">
+        <v>1</v>
+      </c>
       <c r="BA15" s="120"/>
       <c r="BB15" s="120"/>
       <c r="BC15" s="120"/>
       <c r="BD15" s="189">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE15" s="189" cm="1">
         <f t="array" ref="BE15">SUMPRODUCT(--(B15:BC15=INT(B15:BC15)),--(B15:BC15&gt;0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF15" s="189" cm="1">
         <f t="array" ref="BF15">MAX(FREQUENCY(IF((B15:BC15=INT(B15:BC15))*(B15:BC15&gt;0),COLUMN(B15:BC15)),IF((B15:BC15&lt;&gt;INT(B15:BC15))+(B15:BC15&lt;=0),COLUMN(B15:BC15))))</f>
@@ -11456,7 +11476,7 @@
       </c>
       <c r="BH19" s="191">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BI19" s="191">
         <f t="shared" si="2"/>
@@ -11737,17 +11757,19 @@
       <c r="AY22" s="120">
         <v>1</v>
       </c>
-      <c r="AZ22" s="120"/>
+      <c r="AZ22" s="120">
+        <v>1</v>
+      </c>
       <c r="BA22" s="120"/>
       <c r="BB22" s="120"/>
       <c r="BC22" s="120"/>
       <c r="BD22" s="189">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE22" s="189" cm="1">
         <f t="array" ref="BE22">SUMPRODUCT(--(B22:BC22=INT(B22:BC22)),--(B22:BC22&gt;0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BF22" s="189" cm="1">
         <f t="array" ref="BF22">MAX(FREQUENCY(IF((B22:BC22=INT(B22:BC22))*(B22:BC22&gt;0),COLUMN(B22:BC22)),IF((B22:BC22&lt;&gt;INT(B22:BC22))+(B22:BC22&lt;=0),COLUMN(B22:BC22))))</f>
@@ -11931,17 +11953,19 @@
         <v>1</v>
       </c>
       <c r="AY24" s="120"/>
-      <c r="AZ24" s="120"/>
+      <c r="AZ24" s="120">
+        <v>1</v>
+      </c>
       <c r="BA24" s="120"/>
       <c r="BB24" s="120"/>
       <c r="BC24" s="120"/>
       <c r="BD24" s="189">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BE24" s="189" cm="1">
         <f t="array" ref="BE24">SUMPRODUCT(--(B24:BC24=INT(B24:BC24)),--(B24:BC24&gt;0))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BF24" s="189" cm="1">
         <f t="array" ref="BF24">MAX(FREQUENCY(IF((B24:BC24=INT(B24:BC24))*(B24:BC24&gt;0),COLUMN(B24:BC24)),IF((B24:BC24&lt;&gt;INT(B24:BC24))+(B24:BC24&lt;=0),COLUMN(B24:BC24))))</f>
@@ -12329,11 +12353,11 @@
       </c>
       <c r="BH28" s="191">
         <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BI28" s="191">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BJ28" s="191">
         <f t="shared" si="3"/>
@@ -12438,7 +12462,7 @@
       </c>
       <c r="BH29" s="191">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BI29" s="191">
         <f t="shared" si="2"/>
@@ -12739,17 +12763,19 @@
       <c r="AY32" s="120">
         <v>1</v>
       </c>
-      <c r="AZ32" s="120"/>
+      <c r="AZ32" s="120">
+        <v>1</v>
+      </c>
       <c r="BA32" s="120"/>
       <c r="BB32" s="120"/>
       <c r="BC32" s="120"/>
       <c r="BD32" s="189">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE32" s="189" cm="1">
         <f t="array" ref="BE32">SUMPRODUCT(--(B32:BC32=INT(B32:BC32)),--(B32:BC32&gt;0))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF32" s="189" cm="1">
         <f t="array" ref="BF32">MAX(FREQUENCY(IF((B32:BC32=INT(B32:BC32))*(B32:BC32&gt;0),COLUMN(B32:BC32)),IF((B32:BC32&lt;&gt;INT(B32:BC32))+(B32:BC32&lt;=0),COLUMN(B32:BC32))))</f>
@@ -13206,17 +13232,19 @@
       <c r="AY37" s="120">
         <v>1</v>
       </c>
-      <c r="AZ37" s="120"/>
+      <c r="AZ37" s="120">
+        <v>1</v>
+      </c>
       <c r="BA37" s="120"/>
       <c r="BB37" s="120"/>
       <c r="BC37" s="120"/>
       <c r="BD37" s="189">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE37" s="189" cm="1">
         <f t="array" ref="BE37">SUMPRODUCT(--(B37:BC37=INT(B37:BC37)),--(B37:BC37&gt;0))</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF37" s="189" cm="1">
         <f t="array" ref="BF37">MAX(FREQUENCY(IF((B37:BC37=INT(B37:BC37))*(B37:BC37&gt;0),COLUMN(B37:BC37)),IF((B37:BC37&lt;&gt;INT(B37:BC37))+(B37:BC37&lt;=0),COLUMN(B37:BC37))))</f>
@@ -13228,11 +13256,11 @@
       </c>
       <c r="BH37" s="191">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BI37" s="191">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BJ37" s="191">
         <f t="shared" si="3"/>
@@ -13527,17 +13555,19 @@
       <c r="AY40" s="120">
         <v>1</v>
       </c>
-      <c r="AZ40" s="120"/>
+      <c r="AZ40" s="120">
+        <v>1</v>
+      </c>
       <c r="BA40" s="120"/>
       <c r="BB40" s="120"/>
       <c r="BC40" s="120"/>
       <c r="BD40" s="189">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BE40" s="189" cm="1">
         <f t="array" ref="BE40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BF40" s="189" cm="1">
         <f t="array" ref="BF40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
@@ -13646,17 +13676,19 @@
       <c r="AW41" s="120"/>
       <c r="AX41" s="120"/>
       <c r="AY41" s="120"/>
-      <c r="AZ41" s="120"/>
+      <c r="AZ41" s="120">
+        <v>2</v>
+      </c>
       <c r="BA41" s="120"/>
       <c r="BB41" s="120"/>
       <c r="BC41" s="120"/>
       <c r="BD41" s="189">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE41" s="189" cm="1">
         <f t="array" ref="BE41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BF41" s="189" cm="1">
         <f t="array" ref="BF41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
@@ -13668,7 +13700,7 @@
       </c>
       <c r="BH41" s="191">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BI41" s="191">
         <f t="shared" si="2"/>
@@ -13775,17 +13807,19 @@
       <c r="AY42" s="120">
         <v>1</v>
       </c>
-      <c r="AZ42" s="120"/>
+      <c r="AZ42" s="120">
+        <v>1</v>
+      </c>
       <c r="BA42" s="120"/>
       <c r="BB42" s="120"/>
       <c r="BC42" s="120"/>
       <c r="BD42" s="189">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE42" s="189" cm="1">
         <f t="array" ref="BE42">SUMPRODUCT(--(B42:BC42=INT(B42:BC42)),--(B42:BC42&gt;0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BF42" s="189" cm="1">
         <f t="array" ref="BF42">MAX(FREQUENCY(IF((B42:BC42=INT(B42:BC42))*(B42:BC42&gt;0),COLUMN(B42:BC42)),IF((B42:BC42&lt;&gt;INT(B42:BC42))+(B42:BC42&lt;=0),COLUMN(B42:BC42))))</f>
@@ -13987,17 +14021,19 @@
       <c r="AY44" s="120">
         <v>1</v>
       </c>
-      <c r="AZ44" s="120"/>
+      <c r="AZ44" s="120">
+        <v>1</v>
+      </c>
       <c r="BA44" s="120"/>
       <c r="BB44" s="120"/>
       <c r="BC44" s="120"/>
       <c r="BD44" s="189">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE44" s="189" cm="1">
         <f t="array" ref="BE44">SUMPRODUCT(--(B44:BC44=INT(B44:BC44)),--(B44:BC44&gt;0))</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BF44" s="189" cm="1">
         <f t="array" ref="BF44">MAX(FREQUENCY(IF((B44:BC44=INT(B44:BC44))*(B44:BC44&gt;0),COLUMN(B44:BC44)),IF((B44:BC44&lt;&gt;INT(B44:BC44))+(B44:BC44&lt;=0),COLUMN(B44:BC44))))</f>
@@ -14227,21 +14263,23 @@
       <c r="AY46" s="120">
         <v>1</v>
       </c>
-      <c r="AZ46" s="120"/>
+      <c r="AZ46" s="120">
+        <v>1</v>
+      </c>
       <c r="BA46" s="120"/>
       <c r="BB46" s="120"/>
       <c r="BC46" s="120"/>
       <c r="BD46" s="189">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BE46" s="189" cm="1">
         <f t="array" ref="BE46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BF46" s="189" cm="1">
         <f t="array" ref="BF46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG46" s="190" cm="1">
         <f t="array" ref="BG46">SUMPRODUCT(--(B46:AI46=INT(B46:AI46)),--(B46:AI46&gt;0))/34*100%</f>
@@ -14455,11 +14493,11 @@
       </c>
       <c r="BH48" s="191">
         <f t="shared" si="1"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BI48" s="191">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BJ48" s="191">
         <f t="shared" si="3"/>
@@ -14923,7 +14961,7 @@
     </row>
     <row r="54" s="175" customFormat="1" ht="28" spans="1:62">
       <c r="A54" s="194" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B54" s="17" cm="1">
         <f t="array" ref="B54">SUMPRODUCT(--(B3:B53=INT(B3:B53)),--(B3:B53&gt;0))</f>
@@ -15127,7 +15165,7 @@
       </c>
       <c r="AZ54" s="17" cm="1">
         <f t="array" ref="AZ54">SUMPRODUCT(--(AZ3:AZ53=INT(AZ3:AZ53)),--(AZ3:AZ53&gt;0))</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA54" s="17" cm="1">
         <f t="array" ref="BA54">SUMPRODUCT(--(BA3:BA53=INT(BA3:BA53)),--(BA3:BA53&gt;0))</f>
@@ -15142,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="BD54" s="195" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BE54" s="196"/>
       <c r="BF54" s="196"/>
@@ -15153,7 +15191,7 @@
     </row>
     <row r="55" s="175" customFormat="1" ht="28" spans="1:62">
       <c r="A55" s="194" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B55" s="17">
         <f>SUM(B3:B53)</f>
@@ -15357,7 +15395,7 @@
       </c>
       <c r="AZ55" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA55" s="17">
         <f t="shared" si="5"/>
@@ -16523,9 +16561,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="BH4:BJ4" unlockedFormula="1"/>
-    <ignoredError sqref="BH38:BJ39 BH38:BJ39 A5:AF7 A8:V8 A8:V8 X8:AF8 X8:AF8 A32:X32 A32:X32 BH5:BJ8 BH4:BJ4 A3:X4 A3:X4 Z41:AE42 A9:X10 A9:X10 AE48 Z48:AB48 Z48:AB48 A47:AF47 A47:AF47 AF46 AF46 AC46:AD46 AC46:AD46 AA46 AA46 A46:X46 A46:X46 A43:AF43 A43:AF43 AF44 AF44 Z44:AD44 Z44:AD44 A44:W44 A44:W44 A45:AF45 A45:AF45 Z10:AF10 Z10:AF10 BI9:BJ9 BI9:BJ9 Z9:AB9 Z9:AB9 AD9:AF9 AD9:AF9 A39:AF39 A39:AF39 A37:AF37 A37:AF37 BH24:BJ28 BH24:BJ28 BI35:BJ35 BI35:BJ35 A40:V40 A40:V40 AC40:AD40 AC40:AD40 AD38:AF38 AD38:AF38 Z38:AB38 Z38:AB38 A38:X38 A38:X38 Z36:AF36 Z36:AF36 A36:X36 A36:X36 A34:AF35 A34:AF35 Z29:AF29 Z29:AF29 A28:X28 A28:X28 A26:AF27 A26:AF27 Z24:AF25 Z24:AF25 A24:X25 A24:X25 A23:AF23 A23:AF23 AF22 AF22 AA22:AD22 AA22:AD22 A22:X22 A22:X22 A12:X15 A12:X15 BH11:BJ14 BH11:BJ14 A19:AF21 A19:AF21 Z17:AF18 Z17:AF18 A17:X18 A17:X18 A16:AF16 A16:AF16 Z12:AF12 Z12:AF12 Z13 Z13 AB13:AF13 AB13:AF13 Z14:AF14 Z14:AF14 Z15 Z15 AB15:AE15 AB15:AE15 AE11 AE11 AB11:AC11 AB11:AC11 A11:Z11 A11:Z11 A2:AF2 A2:AF2 BD1:BJ2 BD1:BJ2 U1:AF1 U1:AF1 C1:S1 C1:S1 A1 A1 Z3:AF3 Z3:AF3 BI3 BI3 Z4:AE4 Z4:AE4 Z49:AF49 Z49:AF49 AF50 AF50 A50:AD50 A50:AD50 A51:AF53 A51:AF53 A42:X42 A49:X49 A49:X49 X41" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="AF41:BJ42 A5:BJ37 A38:BG39 A40:BJ40 A1:BJ3 A4:BG4 A43:BJ47 A48:AD48 AF48:BJ48 A49:BJ55 Y41:Y42 A41:W41" formulaRange="1"/>
+    <ignoredError sqref="BA44:BJ44 BA46:BJ46 BA40:BJ42 BA15:BJ15 BA22:BJ22 BA32:BJ32 BA37:BJ37 AF41:AY42 A41:W41 A42:X42 Y41:Y42 Y49:BJ49 A50:BJ55 AF48:BJ48 A48:Y48 AC48:AD48 AG43:BJ43 X44:AY44 AG45:BJ45 Y46:AY46 AG47:BJ47 A4:Y4 AF4:AY4 BA4:BG4 A40:AB40 AE40:AY40 Y38:BJ38 A39:BJ39 A5:BG7 A8:AY8 A9:AC9 AG9:AY9 AA11:AY11 BA11:BG11 AG16:BJ16 A17:BJ21 Y22:AY22 AG23:BJ23 Y24:AY24 BA24:BG24 Y32:AY32 A33:BJ33 AG34:BJ35 A36:BJ36 AG37:AY37" formulaRange="1"/>
+    <ignoredError sqref="X41 A42:X42 Z41:AE42 A49:X49 A51:AF53 A50:AD50 AF50 Z49:AF49 AE48 Z48:AB48 A43:AF43 A44:W44 Z44:AD44 AF44 A45:AF45 A46:X46 AA46 AC46:AD46 AF46 A47:AF47 Z4:AE4 A4:X4 BH4:BJ4 A3:X3 AC40:AD40 A40:V40 A38:X38 Z38:AB38 AD38:AF38 A39:AF39 BH38:BJ39 BH5:BJ7 A5:AF7 AD9:AF9 Z9:AB9 A9:X9 X8:AF8 A8:V8 BH8:BJ8 A10:X10 A11:Z11 AB11:AC11 AE11 BH11:BJ11 BH12:BJ14 A15:X15 A16:AF16 A17:X18 Z17:AF18 A19:AF21 A22:X22 AA22:AD22 AF22 A23:AF23 A24:X24 Z24:AF24 BH24:BJ24 A25:X25 A32:X32 A34:AF35 A36:X36 Z36:AF36 BI35:BJ35 A37:AF37 Z25:AF25 BH25:BJ28" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="BI3 Z3:AF3 A1 C1:S1 U1:AF1 BD1:BJ2 A2:AF2 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 A26:AF27 A28:X28 Z29:AF29 BI9:BJ9 Z10:AF10 A3:X3 BH5:BJ8 A10:X10 BH12:BJ14 A12:X14 A25:X25 Z25:AF25 BH25:BJ28" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -16572,21 +16610,21 @@
     </row>
     <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="149" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B2" s="153" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C2" s="154" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D2" s="155"/>
       <c r="E2" s="153" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F2" s="153"/>
       <c r="G2" s="156" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="H2" s="148"/>
       <c r="I2" s="148"/>
@@ -16594,10 +16632,10 @@
     </row>
     <row r="3" ht="16.5" spans="1:10">
       <c r="A3" s="149" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B3" s="158" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C3" s="158"/>
       <c r="D3" s="158"/>
@@ -16610,7 +16648,7 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="149" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B4" s="159" t="s">
         <v>248</v>
@@ -16626,7 +16664,7 @@
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="149" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B5" s="160">
         <v>1</v>
@@ -16646,7 +16684,7 @@
     </row>
     <row r="6" ht="16.5" spans="1:10">
       <c r="A6" s="149" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B6" s="162">
         <v>1</v>
@@ -16656,7 +16694,7 @@
       <c r="E6" s="162"/>
       <c r="F6" s="162"/>
       <c r="G6" s="163" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H6" s="148"/>
       <c r="I6" s="148"/>
@@ -16664,10 +16702,10 @@
     </row>
     <row r="7" ht="16.5" spans="1:10">
       <c r="A7" s="149" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B7" s="164" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C7" s="164"/>
       <c r="D7" s="164"/>
@@ -16682,14 +16720,14 @@
     </row>
     <row r="8" ht="16.5" spans="1:10">
       <c r="A8" s="149" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B8" s="166">
         <v>1</v>
       </c>
       <c r="C8" s="166"/>
       <c r="D8" s="167" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E8" s="167"/>
       <c r="F8" s="167"/>
@@ -16700,10 +16738,10 @@
     </row>
     <row r="9" ht="16.5" spans="1:10">
       <c r="A9" s="149" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B9" s="153" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C9" s="153"/>
       <c r="D9" s="153"/>
@@ -16716,23 +16754,23 @@
     </row>
     <row r="10" ht="16.5" spans="1:10">
       <c r="A10" s="149" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B10" s="158">
         <v>1</v>
       </c>
       <c r="C10" s="158"/>
       <c r="D10" s="168" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E10" s="158">
         <v>1</v>
       </c>
       <c r="F10" s="168" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G10" s="148" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H10" s="148"/>
       <c r="I10" s="148"/>
@@ -16740,7 +16778,7 @@
     </row>
     <row r="11" ht="16.5" spans="1:10">
       <c r="A11" s="149" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B11" s="159">
         <v>1</v>
@@ -16756,7 +16794,7 @@
     </row>
     <row r="12" ht="16.5" spans="1:10">
       <c r="A12" s="149" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B12" s="160">
         <v>1</v>
@@ -16774,17 +16812,17 @@
     </row>
     <row r="13" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A13" s="149" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="169" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -16792,10 +16830,10 @@
     </row>
     <row r="14" s="1" customFormat="1" ht="16.5" spans="1:10">
       <c r="A14" s="149" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B14" s="171" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C14" s="171"/>
       <c r="D14" s="171"/>
@@ -16870,7 +16908,7 @@
   <sheetData>
     <row r="1" s="117" customFormat="1" spans="1:9">
       <c r="A1" s="121" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B1" s="122"/>
       <c r="C1" s="117" t="s">
@@ -16895,10 +16933,10 @@
     </row>
     <row r="2" s="118" customFormat="1" spans="1:9">
       <c r="A2" s="125" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B2" s="126" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C2" s="127" t="s">
         <v>7</v>
@@ -16911,7 +16949,7 @@
     <row r="3" s="118" customFormat="1" spans="1:9">
       <c r="A3" s="130"/>
       <c r="B3" s="126" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C3" s="127" t="s">
         <v>30</v>
@@ -16935,7 +16973,7 @@
     <row r="5" s="118" customFormat="1" spans="1:9">
       <c r="A5" s="130"/>
       <c r="B5" s="126" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C5" s="127" t="s">
         <v>33</v>
@@ -16948,7 +16986,7 @@
     <row r="6" s="118" customFormat="1" spans="1:9">
       <c r="A6" s="130"/>
       <c r="B6" s="126" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>20</v>
@@ -16978,7 +17016,7 @@
     <row r="8" s="118" customFormat="1" spans="1:9">
       <c r="A8" s="130"/>
       <c r="B8" s="126" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>15</v>
@@ -16993,7 +17031,7 @@
     <row r="9" s="118" customFormat="1" spans="1:9">
       <c r="A9" s="130"/>
       <c r="B9" s="126" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C9" s="127" t="s">
         <v>26</v>
@@ -17006,7 +17044,7 @@
     <row r="10" s="118" customFormat="1" spans="1:9">
       <c r="A10" s="130"/>
       <c r="B10" s="126" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C10" s="127" t="s">
         <v>36</v>
@@ -17019,7 +17057,7 @@
     <row r="11" s="118" customFormat="1" spans="1:9">
       <c r="A11" s="134"/>
       <c r="B11" s="126" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C11" s="127" t="s">
         <v>72</v>
@@ -17031,10 +17069,10 @@
     </row>
     <row r="12" s="119" customFormat="1" spans="1:9">
       <c r="A12" s="135" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B12" s="136" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C12" s="137" t="s">
         <v>91</v>
@@ -17060,10 +17098,10 @@
     <row r="14" s="119" customFormat="1" spans="1:9">
       <c r="A14" s="142"/>
       <c r="B14" s="136" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C14" s="137" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D14" s="143"/>
       <c r="E14" s="138"/>
@@ -17075,7 +17113,7 @@
     <row r="15" s="119" customFormat="1" spans="1:9">
       <c r="A15" s="142"/>
       <c r="B15" s="136" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C15" s="137" t="s">
         <v>10</v>
@@ -17099,7 +17137,7 @@
     <row r="17" s="119" customFormat="1" spans="1:7">
       <c r="A17" s="142"/>
       <c r="B17" s="136" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C17" s="137" t="s">
         <v>29</v>
@@ -17112,7 +17150,7 @@
     <row r="18" s="119" customFormat="1" spans="1:7">
       <c r="A18" s="142"/>
       <c r="B18" s="136" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C18" s="137" t="s">
         <v>44</v>
@@ -17125,7 +17163,7 @@
     <row r="19" s="119" customFormat="1" spans="1:7">
       <c r="A19" s="142"/>
       <c r="B19" s="136" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C19" s="137" t="s">
         <v>84</v>
@@ -17138,7 +17176,7 @@
     <row r="20" s="119" customFormat="1" spans="1:7">
       <c r="A20" s="142"/>
       <c r="B20" s="136" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C20" s="137" t="s">
         <v>87</v>
@@ -17151,7 +17189,7 @@
     <row r="21" s="119" customFormat="1" spans="1:7">
       <c r="A21" s="142"/>
       <c r="B21" s="136" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C21" s="144"/>
       <c r="D21" s="145"/>
@@ -17164,7 +17202,7 @@
     <row r="22" s="119" customFormat="1" spans="1:7">
       <c r="A22" s="146"/>
       <c r="B22" s="136" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C22" s="144"/>
       <c r="D22" s="147"/>
@@ -17227,7 +17265,7 @@
   <sheetData>
     <row r="1" s="91" customFormat="1" customHeight="1" spans="1:16">
       <c r="A1" s="94" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B1" s="95"/>
       <c r="C1" s="95"/>
@@ -17258,7 +17296,7 @@
     </row>
     <row r="3" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A3" s="100" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B3" s="101"/>
       <c r="C3" s="102"/>
@@ -17450,7 +17488,7 @@
     </row>
     <row r="11" s="93" customFormat="1" customHeight="1" spans="1:16">
       <c r="A11" s="100" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -17642,7 +17680,7 @@
     </row>
     <row r="19" s="93" customFormat="1" customHeight="1" spans="1:9">
       <c r="A19" s="100" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -17869,10 +17907,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="82" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B1" s="83" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C1" s="84" t="s">
         <v>204</v>
@@ -17883,208 +17921,208 @@
         <v>1</v>
       </c>
       <c r="B2" s="80" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C2" s="81" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="85"/>
       <c r="B3" s="80" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C3" s="81" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="85"/>
       <c r="B4" s="80" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="85"/>
       <c r="B5" s="80" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C5" s="81" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="85"/>
       <c r="B6" s="80" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="85"/>
       <c r="B7" s="80" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="85"/>
       <c r="B8" s="80" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="85"/>
       <c r="B9" s="80" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="85"/>
       <c r="B10" s="80" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="85"/>
       <c r="B11" s="80" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="85"/>
       <c r="B12" s="80" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="85"/>
       <c r="B13" s="80" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="85"/>
       <c r="B14" s="80" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="85"/>
       <c r="B15" s="80" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="85"/>
       <c r="B16" s="80" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="85"/>
       <c r="B17" s="80" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="85"/>
       <c r="B18" s="80" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="85"/>
       <c r="B19" s="80" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="85"/>
       <c r="B20" s="80" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="85"/>
       <c r="B21" s="80" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="85"/>
       <c r="B22" s="80" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="85"/>
       <c r="B23" s="80" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="85"/>
       <c r="B24" s="80" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -18092,118 +18130,118 @@
         <v>2</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="86"/>
       <c r="B26" s="80" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="86"/>
       <c r="B27" s="80" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="86"/>
       <c r="B28" s="80" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="86"/>
       <c r="B29" s="80" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="86"/>
       <c r="B30" s="80" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="86"/>
       <c r="B31" s="80" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="86"/>
       <c r="B32" s="80" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="86"/>
       <c r="B33" s="80" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="86"/>
       <c r="B34" s="80" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C34" s="81" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="86"/>
       <c r="B35" s="80" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C35" s="81" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="86"/>
       <c r="B36" s="80" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C36" s="81" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="87"/>
       <c r="B37" s="80" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C37" s="81" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -18211,138 +18249,138 @@
         <v>3</v>
       </c>
       <c r="B38" s="80" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C38" s="81" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="89"/>
       <c r="B39" s="80" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C39" s="81" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="89"/>
       <c r="B40" s="80" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C40" s="81" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="89"/>
       <c r="B41" s="80" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C41" s="81" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="89"/>
       <c r="B42" s="80" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C42" s="81" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="89"/>
       <c r="B43" s="80" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C43" s="81" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="89"/>
       <c r="B44" s="80" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C44" s="81" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="89"/>
       <c r="B45" s="80" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C45" s="81" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="89"/>
       <c r="B46" s="80" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C46" s="81" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="89"/>
       <c r="B47" s="80" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C47" s="81" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="89"/>
       <c r="B48" s="80" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C48" s="81" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="89"/>
       <c r="B49" s="80" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C49" s="81" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="90"/>
       <c r="B50" s="80" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C50" s="81" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:3">
       <c r="A51" s="79"/>
       <c r="B51" s="80" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C51" s="81"/>
     </row>
     <row r="52" customFormat="1" spans="1:3">
       <c r="A52" s="79"/>
       <c r="B52" s="80" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C52" s="81"/>
     </row>
     <row r="53" customFormat="1" spans="1:3">
       <c r="A53" s="79"/>
       <c r="B53" s="80" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C53" s="81"/>
     </row>

--- a/c/materials.xlsx
+++ b/c/materials.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724"/>
+    <workbookView windowWidth="20750" windowHeight="10480" tabRatio="724" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="师生" sheetId="5" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="682">
   <si>
     <t>姓名</t>
   </si>
@@ -1154,13 +1154,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>数学课情人记录</t>
+      <t>数学课请人记录</t>
     </r>
     <r>
       <rPr>
@@ -1322,6 +1316,12 @@
   </si>
   <si>
     <t>第三轮</t>
+  </si>
+  <si>
+    <t>第四轮</t>
+  </si>
+  <si>
+    <t>第五轮</t>
   </si>
   <si>
     <t>年级</t>
@@ -3418,16 +3418,16 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <strike/>
       <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4229,7 +4229,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4812,6 +4812,9 @@
     <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4902,15 +4905,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5300,538 +5294,538 @@
   <dimension ref="A1:J78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.59090909090909" style="233" customWidth="1"/>
-    <col min="2" max="7" width="25.8727272727273" style="234" customWidth="1"/>
-    <col min="8" max="10" width="16.6818181818182" style="235" customWidth="1"/>
-    <col min="11" max="16384" width="8.72727272727273" style="236"/>
+    <col min="1" max="1" width="7.59090909090909" style="231" customWidth="1"/>
+    <col min="2" max="7" width="25.8727272727273" style="232" customWidth="1"/>
+    <col min="8" max="10" width="16.6818181818182" style="233" customWidth="1"/>
+    <col min="11" max="16384" width="8.72727272727273" style="234"/>
   </cols>
   <sheetData>
-    <row r="1" s="232" customFormat="1" spans="1:10">
-      <c r="A1" s="237" t="s">
+    <row r="1" s="230" customFormat="1" spans="1:10">
+      <c r="A1" s="235" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="238" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="238" t="s">
+      <c r="B1" s="236" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="236" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="238" t="s">
+      <c r="D1" s="236" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="238" t="s">
+      <c r="E1" s="236" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="238" t="s">
+      <c r="F1" s="236" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="238" t="s">
+      <c r="G1" s="236" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="239"/>
-      <c r="I1" s="239"/>
-      <c r="J1" s="239"/>
+      <c r="H1" s="237"/>
+      <c r="I1" s="237"/>
+      <c r="J1" s="237"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="240" t="s">
+      <c r="A2" s="238" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="234" t="s">
+      <c r="B2" s="232" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="232" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="52" spans="1:10">
-      <c r="A3" s="240" t="s">
+      <c r="A3" s="238" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="232" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="234" t="s">
+      <c r="D3" s="232" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="26" spans="1:10">
-      <c r="A4" s="240" t="s">
+      <c r="A4" s="238" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="234" t="s">
+      <c r="D4" s="232" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="240" t="s">
+      <c r="A5" s="238" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="234" t="s">
+      <c r="C5" s="232" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="234" t="s">
+      <c r="D5" s="232" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="240" t="s">
+      <c r="A6" s="238" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="234" t="s">
+      <c r="C6" s="232" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" ht="221" spans="1:10">
-      <c r="A7" s="240" t="s">
+      <c r="A7" s="238" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="234" t="s">
+      <c r="B7" s="232" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="234" t="s">
+      <c r="C7" s="232" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="234" t="s">
+      <c r="D7" s="232" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="26" spans="1:10">
-      <c r="A8" s="240" t="s">
+      <c r="A8" s="238" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="234" t="s">
+      <c r="D8" s="232" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="240" t="s">
+      <c r="A9" s="238" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="240" t="s">
+      <c r="A10" s="238" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="234" t="s">
+      <c r="B10" s="232" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="240" t="s">
+      <c r="A11" s="238" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="240" t="s">
+      <c r="A12" s="238" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="39" spans="1:10">
-      <c r="A13" s="240" t="s">
+      <c r="A13" s="238" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="234" t="s">
+      <c r="D13" s="232" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="240" t="s">
+      <c r="A14" s="238" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="234" t="s">
+      <c r="B14" s="232" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="240" t="s">
+      <c r="A15" s="238" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="240" t="s">
+      <c r="A16" s="238" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="234" t="s">
+      <c r="C16" s="232" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="17" ht="26" spans="1:5">
-      <c r="A17" s="240" t="s">
+      <c r="A17" s="238" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="234" t="s">
+      <c r="C17" s="232" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="240" t="s">
+      <c r="A18" s="238" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="234" t="s">
+      <c r="D18" s="232" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:5">
-      <c r="A19" s="240" t="s">
+      <c r="A19" s="238" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="234" t="s">
+      <c r="D19" s="232" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" ht="26" spans="1:5">
-      <c r="A20" s="240" t="s">
+      <c r="A20" s="238" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="234" t="s">
+      <c r="B20" s="232" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="234" t="s">
+      <c r="C20" s="232" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="21" ht="52" spans="1:5">
-      <c r="A21" s="240" t="s">
+      <c r="A21" s="238" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="234" t="s">
+      <c r="B21" s="232" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="234" t="s">
+      <c r="C21" s="232" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="234" t="s">
+      <c r="D21" s="232" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="240" t="s">
+      <c r="A22" s="238" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="23" ht="26" spans="1:5">
-      <c r="A23" s="240" t="s">
+      <c r="A23" s="238" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="234" t="s">
+      <c r="B23" s="232" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="52" spans="1:5">
-      <c r="A24" s="240" t="s">
+      <c r="A24" s="238" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="234" t="s">
+      <c r="B24" s="232" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="234" t="s">
+      <c r="C24" s="232" t="s">
         <v>56</v>
       </c>
-      <c r="D24" s="234" t="s">
+      <c r="D24" s="232" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="240" t="s">
+      <c r="A25" s="238" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="240" t="s">
+      <c r="A26" s="238" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="240" t="s">
+      <c r="A27" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="234" t="s">
+      <c r="B27" s="232" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="234" t="s">
+      <c r="C27" s="232" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="28" ht="91" spans="1:5">
-      <c r="A28" s="240" t="s">
+      <c r="A28" s="238" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="234" t="s">
+      <c r="B28" s="232" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="234" t="s">
+      <c r="C28" s="232" t="s">
         <v>65</v>
       </c>
-      <c r="D28" s="234" t="s">
+      <c r="D28" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="234" t="s">
+      <c r="E28" s="232" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="240" t="s">
+      <c r="A29" s="238" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="240" t="s">
+      <c r="A30" s="238" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="234" t="s">
+      <c r="B30" s="232" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="234" t="s">
+      <c r="C30" s="232" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="240" t="s">
+      <c r="A31" s="238" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="240" t="s">
+      <c r="A32" s="238" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="240" t="s">
+      <c r="A33" s="238" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="240" t="s">
+      <c r="A34" s="238" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="240" t="s">
+      <c r="A35" s="238" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="240" t="s">
+      <c r="A36" s="238" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="234" t="s">
+      <c r="B36" s="232" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="37" ht="26" spans="1:10">
-      <c r="A37" s="240" t="s">
+      <c r="A37" s="238" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="234" t="s">
+      <c r="C37" s="232" t="s">
         <v>80</v>
       </c>
-      <c r="D37" s="234" t="s">
+      <c r="D37" s="232" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="240" t="s">
+      <c r="A38" s="238" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="234" t="s">
+      <c r="B38" s="232" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="241"/>
-      <c r="D38" s="241"/>
-      <c r="E38" s="241"/>
-      <c r="F38" s="241"/>
-      <c r="G38" s="241"/>
+      <c r="C38" s="239"/>
+      <c r="D38" s="239"/>
+      <c r="E38" s="239"/>
+      <c r="F38" s="239"/>
+      <c r="G38" s="239"/>
     </row>
     <row r="39" ht="26" spans="1:10">
-      <c r="A39" s="240" t="s">
+      <c r="A39" s="238" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="234" t="s">
+      <c r="C39" s="232" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="234" t="s">
+      <c r="D39" s="232" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="240" t="s">
+      <c r="A40" s="238" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="234" t="s">
+      <c r="B40" s="232" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="234" t="s">
+      <c r="C40" s="232" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="234" t="s">
+      <c r="D40" s="232" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="41" ht="208" spans="1:10">
-      <c r="A41" s="240" t="s">
+      <c r="A41" s="238" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="234" t="s">
+      <c r="C41" s="232" t="s">
         <v>92</v>
       </c>
-      <c r="D41" s="234" t="s">
+      <c r="D41" s="232" t="s">
         <v>93</v>
       </c>
-      <c r="E41" s="234" t="s">
+      <c r="E41" s="232" t="s">
         <v>94</v>
       </c>
-      <c r="H41" s="235" t="s">
+      <c r="H41" s="233" t="s">
         <v>95</v>
       </c>
-      <c r="I41" s="235" t="s">
+      <c r="I41" s="233" t="s">
         <v>96</v>
       </c>
-      <c r="J41" s="235" t="s">
+      <c r="J41" s="233" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="240" t="s">
+      <c r="A42" s="238" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="43" ht="28" spans="1:10">
-      <c r="A43" s="240" t="s">
+      <c r="A43" s="238" t="s">
         <v>99</v>
       </c>
-      <c r="B43" s="234" t="s">
+      <c r="B43" s="232" t="s">
         <v>100</v>
       </c>
-      <c r="H43" s="235" t="s">
+      <c r="H43" s="233" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="44" ht="26" spans="1:10">
-      <c r="A44" s="240" t="s">
+      <c r="A44" s="238" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="234" t="s">
+      <c r="B44" s="232" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="45" ht="26" spans="1:10">
-      <c r="A45" s="240" t="s">
+      <c r="A45" s="238" t="s">
         <v>104</v>
       </c>
-      <c r="C45" s="234" t="s">
+      <c r="C45" s="232" t="s">
         <v>105</v>
       </c>
-      <c r="D45" s="234" t="s">
+      <c r="D45" s="232" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="240" t="s">
+      <c r="A46" s="238" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="240" t="s">
+      <c r="A47" s="238" t="s">
         <v>108</v>
       </c>
-      <c r="D47" s="234" t="s">
+      <c r="D47" s="232" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="240" t="s">
+      <c r="A48" s="238" t="s">
         <v>110</v>
       </c>
-      <c r="C48" s="234" t="s">
+      <c r="C48" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="D48" s="234" t="s">
+      <c r="D48" s="232" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="240" t="s">
+      <c r="A49" s="238" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="50" ht="78" spans="1:7">
-      <c r="A50" s="240" t="s">
+      <c r="A50" s="238" t="s">
         <v>114</v>
       </c>
-      <c r="C50" s="234" t="s">
+      <c r="C50" s="232" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="240" t="s">
+      <c r="A51" s="238" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="52" ht="26" spans="1:7">
-      <c r="A52" s="240" t="s">
+      <c r="A52" s="238" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="234" t="s">
+      <c r="B52" s="232" t="s">
         <v>118</v>
       </c>
-      <c r="C52" s="234" t="s">
+      <c r="C52" s="232" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="234" t="s">
+      <c r="E52" s="232" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="53" ht="26" spans="1:7">
-      <c r="A53" s="233" t="s">
+      <c r="A53" s="231" t="s">
         <v>121</v>
       </c>
-      <c r="B53" s="234" t="s">
+      <c r="B53" s="232" t="s">
         <v>122</v>
       </c>
-      <c r="D53" s="241"/>
-      <c r="E53" s="241"/>
-      <c r="F53" s="241"/>
-      <c r="G53" s="241"/>
+      <c r="D53" s="239"/>
+      <c r="E53" s="239"/>
+      <c r="F53" s="239"/>
+      <c r="G53" s="239"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="233" t="s">
+      <c r="A54" s="231" t="s">
         <v>123</v>
       </c>
-      <c r="B54" s="234" t="s">
+      <c r="B54" s="232" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="234" t="s">
+      <c r="C54" s="232" t="s">
         <v>125</v>
       </c>
-      <c r="D54" s="241"/>
-      <c r="E54" s="241"/>
-      <c r="F54" s="241"/>
-      <c r="G54" s="241"/>
+      <c r="D54" s="239"/>
+      <c r="E54" s="239"/>
+      <c r="F54" s="239"/>
+      <c r="G54" s="239"/>
     </row>
     <row r="55" ht="65" spans="1:7">
-      <c r="A55" s="233" t="s">
+      <c r="A55" s="231" t="s">
         <v>126</v>
       </c>
-      <c r="B55" s="241"/>
-      <c r="C55" s="241"/>
-      <c r="D55" s="234" t="s">
+      <c r="B55" s="239"/>
+      <c r="C55" s="239"/>
+      <c r="D55" s="232" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="56" ht="65" spans="1:7">
-      <c r="A56" s="233" t="s">
+      <c r="A56" s="231" t="s">
         <v>128</v>
       </c>
       <c r="B56" s="78" t="s">
         <v>129</v>
       </c>
       <c r="C56" s="78"/>
-      <c r="D56" s="234" t="s">
+      <c r="D56" s="232" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="57" ht="117" spans="1:7">
-      <c r="A57" s="233" t="s">
+      <c r="A57" s="231" t="s">
         <v>131</v>
       </c>
       <c r="B57" s="78" t="s">
@@ -5840,76 +5834,76 @@
       <c r="C57" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="D57" s="234" t="s">
+      <c r="D57" s="232" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="233" t="s">
+      <c r="A58" s="231" t="s">
         <v>135</v>
       </c>
-      <c r="B58" s="234" t="s">
+      <c r="B58" s="232" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="241"/>
-      <c r="D58" s="241"/>
-      <c r="E58" s="241"/>
-      <c r="F58" s="241"/>
-      <c r="G58" s="241"/>
+      <c r="C58" s="239"/>
+      <c r="D58" s="239"/>
+      <c r="E58" s="239"/>
+      <c r="F58" s="239"/>
+      <c r="G58" s="239"/>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="233" t="s">
+      <c r="A59" s="231" t="s">
         <v>137</v>
       </c>
-      <c r="B59" s="241"/>
-      <c r="C59" s="234" t="s">
+      <c r="B59" s="239"/>
+      <c r="C59" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="D59" s="241"/>
-      <c r="E59" s="241"/>
-      <c r="F59" s="241"/>
-      <c r="G59" s="241"/>
+      <c r="D59" s="239"/>
+      <c r="E59" s="239"/>
+      <c r="F59" s="239"/>
+      <c r="G59" s="239"/>
     </row>
     <row r="60" ht="65" spans="1:7">
-      <c r="A60" s="233" t="s">
+      <c r="A60" s="231" t="s">
         <v>139</v>
       </c>
-      <c r="B60" s="241" t="s">
+      <c r="B60" s="239" t="s">
         <v>140</v>
       </c>
-      <c r="C60" s="241"/>
-      <c r="D60" s="234" t="s">
+      <c r="C60" s="239"/>
+      <c r="D60" s="232" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="233" t="s">
+      <c r="A61" s="231" t="s">
         <v>142</v>
       </c>
       <c r="B61" s="78" t="s">
         <v>143</v>
       </c>
       <c r="C61" s="78"/>
-      <c r="D61" s="241"/>
-      <c r="E61" s="241"/>
-      <c r="F61" s="241"/>
-      <c r="G61" s="241"/>
+      <c r="D61" s="239"/>
+      <c r="E61" s="239"/>
+      <c r="F61" s="239"/>
+      <c r="G61" s="239"/>
     </row>
     <row r="62" ht="52" spans="1:7">
-      <c r="A62" s="233" t="s">
+      <c r="A62" s="231" t="s">
         <v>144</v>
       </c>
-      <c r="B62" s="241"/>
-      <c r="C62" s="241"/>
-      <c r="D62" s="234" t="s">
+      <c r="B62" s="239"/>
+      <c r="C62" s="239"/>
+      <c r="D62" s="232" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="234" t="s">
+      <c r="E62" s="232" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="63" ht="26" spans="1:7">
-      <c r="A63" s="233" t="s">
+      <c r="A63" s="231" t="s">
         <v>147</v>
       </c>
       <c r="B63" s="78" t="s">
@@ -5918,66 +5912,66 @@
       <c r="C63" s="78" t="s">
         <v>149</v>
       </c>
-      <c r="D63" s="241"/>
-      <c r="E63" s="241"/>
-      <c r="F63" s="241"/>
-      <c r="G63" s="241"/>
+      <c r="D63" s="239"/>
+      <c r="E63" s="239"/>
+      <c r="F63" s="239"/>
+      <c r="G63" s="239"/>
     </row>
     <row r="64" ht="26" spans="1:7">
-      <c r="A64" s="233" t="s">
+      <c r="A64" s="231" t="s">
         <v>150</v>
       </c>
-      <c r="B64" s="241"/>
-      <c r="C64" s="241"/>
-      <c r="D64" s="234" t="s">
+      <c r="B64" s="239"/>
+      <c r="C64" s="239"/>
+      <c r="D64" s="232" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="65" ht="26" spans="1:7">
-      <c r="A65" s="233" t="s">
+      <c r="A65" s="231" t="s">
         <v>152</v>
       </c>
-      <c r="B65" s="242" t="s">
+      <c r="B65" s="240" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="241"/>
-      <c r="D65" s="241"/>
-      <c r="E65" s="241"/>
-      <c r="F65" s="241"/>
-      <c r="G65" s="241"/>
+      <c r="C65" s="239"/>
+      <c r="D65" s="239"/>
+      <c r="E65" s="239"/>
+      <c r="F65" s="239"/>
+      <c r="G65" s="239"/>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="233" t="s">
+      <c r="A66" s="231" t="s">
         <v>154</v>
       </c>
-      <c r="B66" s="241"/>
-      <c r="C66" s="234" t="s">
+      <c r="B66" s="239"/>
+      <c r="C66" s="232" t="s">
         <v>155</v>
       </c>
-      <c r="D66" s="241"/>
-      <c r="E66" s="241"/>
-      <c r="F66" s="241"/>
-      <c r="G66" s="241"/>
+      <c r="D66" s="239"/>
+      <c r="E66" s="239"/>
+      <c r="F66" s="239"/>
+      <c r="G66" s="239"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="233" t="s">
+      <c r="A67" s="231" t="s">
         <v>156</v>
       </c>
-      <c r="B67" s="241"/>
-      <c r="C67" s="241"/>
+      <c r="B67" s="239"/>
+      <c r="C67" s="239"/>
     </row>
     <row r="68" ht="78" spans="1:7">
-      <c r="A68" s="233" t="s">
+      <c r="A68" s="231" t="s">
         <v>157</v>
       </c>
-      <c r="B68" s="241"/>
-      <c r="C68" s="241"/>
-      <c r="D68" s="234" t="s">
+      <c r="B68" s="239"/>
+      <c r="C68" s="239"/>
+      <c r="D68" s="232" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="233" t="s">
+      <c r="A69" s="231" t="s">
         <v>159</v>
       </c>
       <c r="B69" s="78" t="s">
@@ -5986,89 +5980,89 @@
       <c r="C69" s="78"/>
     </row>
     <row r="70" ht="26" spans="1:7">
-      <c r="A70" s="233" t="s">
+      <c r="A70" s="231" t="s">
         <v>161</v>
       </c>
       <c r="B70" s="78" t="s">
         <v>162</v>
       </c>
       <c r="C70" s="78"/>
-      <c r="D70" s="241"/>
-      <c r="E70" s="241"/>
-      <c r="F70" s="241"/>
-      <c r="G70" s="241"/>
+      <c r="D70" s="239"/>
+      <c r="E70" s="239"/>
+      <c r="F70" s="239"/>
+      <c r="G70" s="239"/>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="233" t="s">
+      <c r="A71" s="231" t="s">
         <v>163</v>
       </c>
-      <c r="B71" s="241"/>
-      <c r="C71" s="241"/>
+      <c r="B71" s="239"/>
+      <c r="C71" s="239"/>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="233" t="s">
+      <c r="A72" s="231" t="s">
         <v>164</v>
       </c>
-      <c r="B72" s="234" t="s">
+      <c r="B72" s="232" t="s">
         <v>165</v>
       </c>
-      <c r="C72" s="234" t="s">
+      <c r="C72" s="232" t="s">
         <v>166</v>
       </c>
-      <c r="D72" s="241"/>
-      <c r="E72" s="241"/>
-      <c r="F72" s="241"/>
-      <c r="G72" s="241"/>
+      <c r="D72" s="239"/>
+      <c r="E72" s="239"/>
+      <c r="F72" s="239"/>
+      <c r="G72" s="239"/>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="233" t="s">
+      <c r="A73" s="231" t="s">
         <v>167</v>
       </c>
-      <c r="B73" s="241"/>
-      <c r="C73" s="234" t="s">
+      <c r="B73" s="239"/>
+      <c r="C73" s="232" t="s">
         <v>168</v>
       </c>
-      <c r="D73" s="241"/>
-      <c r="E73" s="241"/>
-      <c r="F73" s="241"/>
-      <c r="G73" s="241"/>
+      <c r="D73" s="239"/>
+      <c r="E73" s="239"/>
+      <c r="F73" s="239"/>
+      <c r="G73" s="239"/>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="233" t="s">
+      <c r="A74" s="231" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="233" t="s">
+      <c r="A75" s="231" t="s">
         <v>170</v>
       </c>
-      <c r="D75" s="241"/>
-      <c r="E75" s="241"/>
-      <c r="F75" s="241"/>
-      <c r="G75" s="241"/>
+      <c r="D75" s="239"/>
+      <c r="E75" s="239"/>
+      <c r="F75" s="239"/>
+      <c r="G75" s="239"/>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="233" t="s">
+      <c r="A76" s="231" t="s">
         <v>171</v>
       </c>
-      <c r="B76" s="241"/>
-      <c r="C76" s="241"/>
-      <c r="D76" s="234" t="s">
+      <c r="B76" s="239"/>
+      <c r="C76" s="239"/>
+      <c r="D76" s="232" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="233" t="s">
+      <c r="A77" s="231" t="s">
         <v>173</v>
       </c>
       <c r="B77" s="78"/>
       <c r="C77" s="78"/>
     </row>
     <row r="78" ht="26" spans="1:7">
-      <c r="A78" s="243" t="s">
+      <c r="A78" s="241" t="s">
         <v>174</v>
       </c>
-      <c r="B78" s="234" t="s">
+      <c r="B78" s="232" t="s">
         <v>175</v>
       </c>
     </row>
@@ -6128,10 +6122,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="69" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D1" s="70" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6145,7 +6139,7 @@
         <v>20111216</v>
       </c>
       <c r="D2" s="66" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6159,7 +6153,7 @@
         <v>20111227</v>
       </c>
       <c r="D3" s="66" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6173,7 +6167,7 @@
         <v>20120518</v>
       </c>
       <c r="D4" s="66" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:4">
@@ -6215,7 +6209,7 @@
         <v>20120809</v>
       </c>
       <c r="D7" s="66" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6229,7 +6223,7 @@
         <v>20120227</v>
       </c>
       <c r="D8" s="66" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6243,7 +6237,7 @@
         <v>20120127</v>
       </c>
       <c r="D9" s="66" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6257,7 +6251,7 @@
         <v>20111202</v>
       </c>
       <c r="D10" s="66" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:4">
@@ -6283,7 +6277,7 @@
         <v>20111024</v>
       </c>
       <c r="D12" s="66" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6297,7 +6291,7 @@
         <v>20110908</v>
       </c>
       <c r="D13" s="66" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6311,7 +6305,7 @@
         <v>20120228</v>
       </c>
       <c r="D14" s="66" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:4">
@@ -6337,7 +6331,7 @@
         <v>20111201</v>
       </c>
       <c r="D16" s="66" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -6351,7 +6345,7 @@
         <v>20120722</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:4">
@@ -6389,7 +6383,7 @@
         <v>20120530</v>
       </c>
       <c r="D20" s="66" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -6403,7 +6397,7 @@
         <v>20120827</v>
       </c>
       <c r="D21" s="66" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:4">
@@ -6429,7 +6423,7 @@
         <v>20120518</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -6443,7 +6437,7 @@
         <v>20120413</v>
       </c>
       <c r="D24" s="66" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -6457,7 +6451,7 @@
         <v>20120629</v>
       </c>
       <c r="D25" s="66" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -6471,7 +6465,7 @@
         <v>20111105</v>
       </c>
       <c r="D26" s="66" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -6485,7 +6479,7 @@
         <v>20120112</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -6499,7 +6493,7 @@
         <v>20111119</v>
       </c>
       <c r="D28" s="66" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:4">
@@ -6525,7 +6519,7 @@
         <v>20120331</v>
       </c>
       <c r="D30" s="66" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -6539,7 +6533,7 @@
         <v>20111109</v>
       </c>
       <c r="D31" s="66" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -6553,7 +6547,7 @@
         <v>20120824</v>
       </c>
       <c r="D32" s="66" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:5">
@@ -6579,7 +6573,7 @@
         <v>20120624</v>
       </c>
       <c r="D34" s="66" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:5">
@@ -6605,7 +6599,7 @@
         <v>20120603</v>
       </c>
       <c r="D36" s="66" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6619,7 +6613,7 @@
         <v>20120326</v>
       </c>
       <c r="D37" s="66" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6633,10 +6627,10 @@
         <v>20111106</v>
       </c>
       <c r="D38" s="77" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E38" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6650,7 +6644,7 @@
         <v>20120811</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6664,7 +6658,7 @@
         <v>20111217</v>
       </c>
       <c r="D40" s="78" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6678,10 +6672,10 @@
         <v>20111013</v>
       </c>
       <c r="D41" s="66" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E41" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:5">
@@ -6707,7 +6701,7 @@
         <v>20120207</v>
       </c>
       <c r="D43" s="66" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:5">
@@ -6733,7 +6727,7 @@
         <v>20110929</v>
       </c>
       <c r="D45" s="66" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:5">
@@ -6759,10 +6753,10 @@
         <v>20120108</v>
       </c>
       <c r="D47" s="66" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E47" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -6776,7 +6770,7 @@
         <v>20120311</v>
       </c>
       <c r="D48" s="66" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:4">
@@ -6802,7 +6796,7 @@
         <v>20120723</v>
       </c>
       <c r="D50" s="66" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:4">
@@ -6828,7 +6822,7 @@
         <v>20111220</v>
       </c>
       <c r="D52" s="66" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
   </sheetData>
@@ -6861,17 +6855,17 @@
   <sheetData>
     <row r="1" s="27" customFormat="1" spans="1:5">
       <c r="A1" s="34" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B1" s="35" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D1" s="37"/>
       <c r="E1" s="38" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" s="28" customFormat="1" ht="409" customHeight="1" spans="1:5">
@@ -6882,13 +6876,13 @@
         <v>255</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D2" s="32" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6896,10 +6890,10 @@
       <c r="B3" s="43"/>
       <c r="C3" s="44"/>
       <c r="D3" s="32" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" s="28" customFormat="1" spans="1:5">
@@ -6907,10 +6901,10 @@
       <c r="B4" s="43"/>
       <c r="C4" s="44"/>
       <c r="D4" s="32" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6918,10 +6912,10 @@
       <c r="B5" s="43"/>
       <c r="C5" s="44"/>
       <c r="D5" s="32" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" s="28" customFormat="1" ht="238" spans="1:5">
@@ -6929,23 +6923,23 @@
       <c r="B6" s="43"/>
       <c r="C6" s="44"/>
       <c r="D6" s="32" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" s="28" customFormat="1" ht="238" spans="1:5">
       <c r="A7" s="42"/>
       <c r="B7" s="43"/>
       <c r="C7" s="41" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8" s="28" customFormat="1" ht="56" spans="1:5">
@@ -6953,10 +6947,10 @@
       <c r="B8" s="43"/>
       <c r="C8" s="44"/>
       <c r="D8" s="32" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" s="28" customFormat="1" ht="84" spans="1:5">
@@ -6964,10 +6958,10 @@
       <c r="B9" s="43"/>
       <c r="C9" s="44"/>
       <c r="D9" s="32" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="E9" s="33" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="10" s="28" customFormat="1" ht="28" spans="1:5">
@@ -6975,10 +6969,10 @@
       <c r="B10" s="43"/>
       <c r="C10" s="44"/>
       <c r="D10" s="32" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E10" s="33" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11" s="28" customFormat="1" spans="1:5">
@@ -6986,10 +6980,10 @@
       <c r="B11" s="43"/>
       <c r="C11" s="45"/>
       <c r="D11" s="32" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="12" s="28" customFormat="1" ht="154" spans="1:5">
@@ -6997,50 +6991,50 @@
       <c r="B12" s="43"/>
       <c r="C12" s="31"/>
       <c r="D12" s="32" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E12" s="33" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="13" s="28" customFormat="1" ht="56" spans="1:5">
       <c r="A13" s="42"/>
       <c r="B13" s="43"/>
       <c r="C13" s="46" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="33" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14" s="28" customFormat="1" ht="84" spans="1:5">
       <c r="A14" s="42"/>
       <c r="B14" s="43"/>
       <c r="C14" s="46" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="33" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="15" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A15" s="42"/>
       <c r="B15" s="43"/>
       <c r="C15" s="46" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D15" s="37"/>
       <c r="E15" s="33" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16" s="28" customFormat="1" spans="1:5">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="46" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="33"/>
@@ -7049,24 +7043,24 @@
       <c r="A17" s="42"/>
       <c r="B17" s="43"/>
       <c r="C17" s="46" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="33" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" s="28" customFormat="1" spans="1:5">
       <c r="A18" s="42"/>
       <c r="B18" s="43"/>
       <c r="C18" s="41" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="19" s="28" customFormat="1" spans="1:5">
@@ -7074,17 +7068,17 @@
       <c r="B19" s="43"/>
       <c r="C19" s="45"/>
       <c r="D19" s="32" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="20" s="28" customFormat="1" spans="1:5">
       <c r="A20" s="42"/>
       <c r="B20" s="43"/>
       <c r="C20" s="46" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="33"/>
@@ -7093,22 +7087,22 @@
       <c r="A21" s="42"/>
       <c r="B21" s="43"/>
       <c r="C21" s="46" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="33" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A22" s="42"/>
       <c r="B22" s="43"/>
       <c r="C22" s="46" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D22" s="47"/>
       <c r="E22" s="33" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" s="28" customFormat="1" spans="1:5">
@@ -7119,18 +7113,18 @@
       </c>
       <c r="D23" s="31"/>
       <c r="E23" s="33" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="24" s="28" customFormat="1" spans="1:5">
       <c r="A24" s="42"/>
       <c r="B24" s="43"/>
       <c r="C24" s="31" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="33" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="25" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7141,13 +7135,13 @@
         <v>352</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="26" s="28" customFormat="1" spans="1:5">
@@ -7155,10 +7149,10 @@
       <c r="B26" s="43"/>
       <c r="C26" s="44"/>
       <c r="D26" s="32" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="27" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7166,10 +7160,10 @@
       <c r="B27" s="43"/>
       <c r="C27" s="44"/>
       <c r="D27" s="32" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="28" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7177,10 +7171,10 @@
       <c r="B28" s="43"/>
       <c r="C28" s="44"/>
       <c r="D28" s="32" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="29" s="28" customFormat="1" ht="42" spans="1:5">
@@ -7191,13 +7185,13 @@
         <v>348</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="30" s="28" customFormat="1" ht="70" spans="1:5">
@@ -7205,10 +7199,10 @@
       <c r="B30" s="43"/>
       <c r="C30" s="44"/>
       <c r="D30" s="32" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="31" s="28" customFormat="1" spans="1:5">
@@ -7216,10 +7210,10 @@
       <c r="B31" s="43"/>
       <c r="C31" s="44"/>
       <c r="D31" s="32" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="32" s="28" customFormat="1" ht="28" spans="1:5">
@@ -7227,45 +7221,45 @@
       <c r="B32" s="43"/>
       <c r="C32" s="45"/>
       <c r="D32" s="32" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="33" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A33" s="42"/>
       <c r="B33" s="49"/>
       <c r="C33" s="46" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D33" s="47"/>
       <c r="E33" s="33" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A34" s="42"/>
       <c r="B34" s="50" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D34" s="51"/>
       <c r="E34" s="52" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="35" s="28" customFormat="1" ht="42" spans="1:5">
       <c r="A35" s="53"/>
       <c r="B35" s="54"/>
       <c r="C35" s="36" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D35" s="51"/>
       <c r="E35" s="52" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="36" s="28" customFormat="1" spans="1:5">
@@ -7273,7 +7267,7 @@
         <v>354</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="57"/>
@@ -7284,12 +7278,12 @@
     <row r="37" s="28" customFormat="1" spans="1:5">
       <c r="A37" s="53"/>
       <c r="B37" s="58" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C37" s="59"/>
       <c r="D37" s="60"/>
       <c r="E37" s="33" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="38" s="28" customFormat="1" spans="1:5">
@@ -7297,12 +7291,12 @@
         <v>355</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C38" s="59"/>
       <c r="D38" s="60"/>
       <c r="E38" s="33" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="39" s="28" customFormat="1" spans="1:5">
@@ -7310,16 +7304,16 @@
         <v>357</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C39" s="41" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="40" s="28" customFormat="1" spans="1:5">
@@ -7327,32 +7321,32 @@
       <c r="B40" s="43"/>
       <c r="C40" s="45"/>
       <c r="D40" s="32" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" s="28" customFormat="1" spans="1:5">
       <c r="A41" s="42"/>
       <c r="B41" s="43"/>
       <c r="C41" s="46" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D41" s="47"/>
       <c r="E41" s="33" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="42" s="28" customFormat="1" spans="1:5">
       <c r="A42" s="53"/>
       <c r="B42" s="49"/>
       <c r="C42" s="46" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D42" s="47"/>
       <c r="E42" s="33" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="43" s="28" customFormat="1" spans="1:5">
@@ -7360,31 +7354,31 @@
         <v>359</v>
       </c>
       <c r="B43" s="50" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C43" s="61" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D43" s="62"/>
       <c r="E43" s="52" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="44" s="28" customFormat="1" ht="28" spans="1:5">
       <c r="A44" s="42"/>
       <c r="B44" s="54"/>
       <c r="C44" s="61" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D44" s="62"/>
       <c r="E44" s="52" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="45" s="28" customFormat="1" spans="1:5">
       <c r="A45" s="53"/>
       <c r="B45" s="58" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C45" s="59"/>
       <c r="D45" s="60"/>
@@ -7397,13 +7391,13 @@
         <v>367</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="E46" s="33"/>
     </row>
@@ -7412,7 +7406,7 @@
       <c r="B47" s="43"/>
       <c r="C47" s="44"/>
       <c r="D47" s="32" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="E47" s="33"/>
     </row>
@@ -7421,10 +7415,10 @@
       <c r="B48" s="49"/>
       <c r="C48" s="45"/>
       <c r="D48" s="32" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="49" s="28" customFormat="1" spans="1:5">
@@ -7437,7 +7431,7 @@
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="33" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="50" s="28" customFormat="1" spans="1:5">
@@ -7445,18 +7439,18 @@
         <v>363</v>
       </c>
       <c r="B50" s="58" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C50" s="59"/>
       <c r="D50" s="60"/>
       <c r="E50" s="33" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="51" s="28" customFormat="1" spans="1:5">
       <c r="A51" s="53"/>
       <c r="B51" s="58" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C51" s="59"/>
       <c r="D51" s="60"/>
@@ -7469,7 +7463,7 @@
         <v>366</v>
       </c>
       <c r="B52" s="58" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C52" s="59"/>
       <c r="D52" s="60"/>
@@ -7477,10 +7471,10 @@
     </row>
     <row r="53" s="28" customFormat="1" spans="1:5">
       <c r="A53" s="39" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B53" s="58" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="C53" s="59"/>
       <c r="D53" s="60"/>
@@ -7492,7 +7486,7 @@
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="33" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="55" s="28" customFormat="1" spans="1:5">
@@ -7503,7 +7497,7 @@
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
       <c r="E55" s="33" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -7611,7 +7605,7 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="10"/>
@@ -7625,7 +7619,7 @@
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
@@ -7649,7 +7643,7 @@
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="11"/>
@@ -7662,7 +7656,7 @@
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="22" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="11"/>
@@ -7675,7 +7669,7 @@
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="11"/>
@@ -7709,7 +7703,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
@@ -7755,7 +7749,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="10"/>
@@ -7791,7 +7785,7 @@
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="22" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="11"/>
@@ -7825,10 +7819,10 @@
         <v>44</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="11"/>
@@ -7840,10 +7834,10 @@
         <v>47</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D21" s="10"/>
       <c r="E21" s="11"/>
@@ -7866,7 +7860,7 @@
         <v>52</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -7879,10 +7873,10 @@
         <v>54</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="D24" s="10"/>
       <c r="E24" s="11"/>
@@ -7916,10 +7910,10 @@
         <v>60</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D27" s="10"/>
       <c r="E27" s="11"/>
@@ -7931,10 +7925,10 @@
         <v>63</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="11"/>
@@ -7958,7 +7952,7 @@
       </c>
       <c r="B30" s="8"/>
       <c r="C30" s="22" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="11"/>
@@ -8025,7 +8019,7 @@
         <v>77</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -8039,7 +8033,7 @@
       </c>
       <c r="B37" s="8"/>
       <c r="C37" s="22" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="11"/>
@@ -8051,7 +8045,7 @@
         <v>82</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C38" s="25"/>
       <c r="D38" s="26"/>
@@ -8065,7 +8059,7 @@
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="11"/>
@@ -8077,10 +8071,10 @@
         <v>87</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C40" s="22" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="11"/>
@@ -8093,7 +8087,7 @@
       </c>
       <c r="B41" s="8"/>
       <c r="C41" s="22" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="11"/>
@@ -8116,7 +8110,7 @@
         <v>99</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="10"/>
@@ -8140,7 +8134,7 @@
         <v>104</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="10"/>
@@ -8176,7 +8170,7 @@
       </c>
       <c r="B48" s="8"/>
       <c r="C48" s="22" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="11"/>
@@ -8200,7 +8194,7 @@
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="22" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="11"/>
@@ -8223,10 +8217,10 @@
         <v>117</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="11"/>
@@ -8262,27 +8256,27 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="4" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C2" s="4">
         <v>13</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
@@ -8290,13 +8284,13 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="C3" s="4">
         <v>13</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F3" s="4">
         <v>13</v>
@@ -8304,13 +8298,13 @@
     </row>
     <row r="4" spans="2:6">
       <c r="B4" s="4" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="C4" s="4">
         <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F4" s="4">
         <v>4</v>
@@ -8318,13 +8312,13 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="4" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="F5" s="4">
         <v>6</v>
@@ -8332,13 +8326,13 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C6" s="4">
         <v>2</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F6" s="4">
         <v>4</v>
@@ -8346,13 +8340,13 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C7" s="4">
         <v>1</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="F7" s="4">
         <v>1</v>
@@ -8360,13 +8354,13 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F8" s="4">
         <v>3</v>
@@ -8374,7 +8368,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="E9" s="4" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -8382,7 +8376,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="E10" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="F10" s="4">
         <v>5</v>
@@ -8390,7 +8384,7 @@
     </row>
     <row r="11" spans="2:6">
       <c r="E11" s="4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="F11" s="4">
         <v>1</v>
@@ -8398,7 +8392,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="E12" s="4" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -8418,14 +8412,14 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.64545454545455" style="227" customWidth="1"/>
+    <col min="1" max="1" width="6.64545454545455" style="225" customWidth="1"/>
     <col min="2" max="2" width="32.6181818181818" style="66" customWidth="1"/>
     <col min="3" max="7" width="16.4909090909091" style="66" customWidth="1"/>
-    <col min="8" max="16384" width="8.72727272727273" style="228"/>
+    <col min="8" max="16384" width="8.72727272727273" style="226"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="229"/>
+      <c r="A1" s="227"/>
       <c r="B1" s="70" t="s">
         <v>1</v>
       </c>
@@ -8445,8 +8439,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="226" customFormat="1" ht="39" spans="1:7">
-      <c r="A2" s="230" t="s">
+    <row r="2" s="224" customFormat="1" ht="39" spans="1:7">
+      <c r="A2" s="228" t="s">
         <v>176</v>
       </c>
       <c r="B2" s="78"/>
@@ -8459,7 +8453,7 @@
       <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="231" t="s">
+      <c r="A3" s="229" t="s">
         <v>178</v>
       </c>
       <c r="C3" s="66" t="s">
@@ -8467,7 +8461,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="231" t="s">
+      <c r="A4" s="229" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="66" t="s">
@@ -8478,7 +8472,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="231" t="s">
+      <c r="A5" s="229" t="s">
         <v>183</v>
       </c>
       <c r="C5" s="66" t="s">
@@ -8489,7 +8483,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="231" t="s">
+      <c r="A6" s="229" t="s">
         <v>186</v>
       </c>
       <c r="B6" s="66" t="s">
@@ -8500,7 +8494,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="231" t="s">
+      <c r="A7" s="229" t="s">
         <v>189</v>
       </c>
       <c r="B7" s="66" t="s">
@@ -8508,130 +8502,130 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="231"/>
+      <c r="A8" s="229"/>
       <c r="D8" s="66" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="231"/>
+      <c r="A9" s="229"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="231"/>
+      <c r="A10" s="229"/>
       <c r="B10" s="66" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="231"/>
+      <c r="A11" s="229"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="231"/>
+      <c r="A12" s="229"/>
       <c r="B12" s="66" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="231"/>
+      <c r="A13" s="229"/>
       <c r="B13" s="66" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="231"/>
+      <c r="A14" s="229"/>
       <c r="B14" s="66" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="231"/>
+      <c r="A15" s="229"/>
       <c r="B15" s="66" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="231"/>
+      <c r="A16" s="229"/>
       <c r="B16" s="66" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="231"/>
+      <c r="A17" s="229"/>
       <c r="B17" s="66" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="231"/>
+      <c r="A18" s="229"/>
       <c r="B18" s="66" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="19" ht="26" spans="1:2">
-      <c r="A19" s="231"/>
+      <c r="A19" s="229"/>
       <c r="B19" s="78" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="231"/>
+      <c r="A20" s="229"/>
       <c r="B20" s="66" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="231"/>
+      <c r="A21" s="229"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="231"/>
+      <c r="A22" s="229"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="231"/>
+      <c r="A23" s="229"/>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="231"/>
+      <c r="A24" s="229"/>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="231"/>
+      <c r="A25" s="229"/>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="231"/>
+      <c r="A26" s="229"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="231"/>
+      <c r="A27" s="229"/>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="231"/>
+      <c r="A28" s="229"/>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="231"/>
+      <c r="A29" s="229"/>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="231"/>
+      <c r="A30" s="229"/>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="231"/>
+      <c r="A31" s="229"/>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="231"/>
+      <c r="A32" s="229"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="231"/>
+      <c r="A33" s="229"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="231"/>
+      <c r="A34" s="229"/>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="231"/>
+      <c r="A35" s="229"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="231"/>
+      <c r="A36" s="229"/>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="231"/>
+      <c r="A37" s="229"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="231"/>
+      <c r="A38" s="229"/>
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
       <c r="D38" s="78"/>
@@ -8640,7 +8634,7 @@
       <c r="G38" s="78"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="231"/>
+      <c r="A39" s="229"/>
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
       <c r="D39" s="78"/>
@@ -8649,40 +8643,40 @@
       <c r="G39" s="78"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="231"/>
+      <c r="A40" s="229"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="231"/>
+      <c r="A41" s="229"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="231"/>
+      <c r="A42" s="229"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="231"/>
+      <c r="A43" s="229"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="231"/>
+      <c r="A44" s="229"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="231"/>
+      <c r="A45" s="229"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="231"/>
+      <c r="A46" s="229"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="231"/>
+      <c r="A47" s="229"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="231"/>
+      <c r="A48" s="229"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="231"/>
+      <c r="A49" s="229"/>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="231"/>
+      <c r="A50" s="229"/>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="231"/>
+      <c r="A51" s="229"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8698,607 +8692,607 @@
   <dimension ref="A1:C66"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="24" style="214" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="214" customWidth="1"/>
-    <col min="3" max="3" width="91.3636363636364" style="214" customWidth="1"/>
+    <col min="1" max="1" width="24" style="215" customWidth="1"/>
+    <col min="2" max="2" width="10.6363636363636" style="215" customWidth="1"/>
+    <col min="3" max="3" width="91.3636363636364" style="215" customWidth="1"/>
     <col min="4" max="16384" width="8.72727272727273" style="93"/>
   </cols>
   <sheetData>
-    <row r="1" s="213" customFormat="1" ht="15" spans="1:3">
-      <c r="A1" s="215" t="s">
+    <row r="1" s="214" customFormat="1" ht="15" spans="1:3">
+      <c r="A1" s="216" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="215" t="s">
+      <c r="B1" s="216" t="s">
         <v>203</v>
       </c>
-      <c r="C1" s="215" t="s">
+      <c r="C1" s="216" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="216" t="s">
+      <c r="A2" s="217" t="s">
         <v>205</v>
       </c>
-      <c r="B2" s="216" t="s">
+      <c r="B2" s="217" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="216" t="s">
+      <c r="C2" s="217" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="216" t="s">
+      <c r="A3" s="217" t="s">
         <v>208</v>
       </c>
-      <c r="B3" s="216" t="s">
+      <c r="B3" s="217" t="s">
         <v>209</v>
       </c>
-      <c r="C3" s="216" t="s">
+      <c r="C3" s="217" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="216" t="s">
+      <c r="A4" s="217" t="s">
         <v>211</v>
       </c>
-      <c r="B4" s="216" t="s">
+      <c r="B4" s="217" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="216" t="s">
+      <c r="C4" s="217" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="5" ht="56" spans="1:3">
-      <c r="A5" s="217" t="s">
+      <c r="A5" s="218" t="s">
         <v>213</v>
       </c>
-      <c r="B5" s="216" t="s">
+      <c r="B5" s="217" t="s">
         <v>214</v>
       </c>
-      <c r="C5" s="216" t="s">
+      <c r="C5" s="217" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="6" ht="28" spans="1:3">
-      <c r="A6" s="218"/>
-      <c r="B6" s="216" t="s">
+      <c r="A6" s="219"/>
+      <c r="B6" s="217" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="216" t="s">
+      <c r="C6" s="217" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="219" t="s">
+      <c r="A7" s="220" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="217" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="216" t="s">
+      <c r="C7" s="217" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="8" ht="140" spans="1:3">
-      <c r="A8" s="219"/>
-      <c r="B8" s="216" t="s">
+      <c r="A8" s="220"/>
+      <c r="B8" s="217" t="s">
         <v>220</v>
       </c>
-      <c r="C8" s="216" t="s">
+      <c r="C8" s="217" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="219"/>
-      <c r="B9" s="216" t="s">
+      <c r="A9" s="220"/>
+      <c r="B9" s="217" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="216" t="s">
+      <c r="C9" s="217" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="219"/>
-      <c r="B10" s="216" t="s">
+      <c r="A10" s="220"/>
+      <c r="B10" s="217" t="s">
         <v>224</v>
       </c>
-      <c r="C10" s="216" t="s">
+      <c r="C10" s="217" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="219"/>
-      <c r="B11" s="216"/>
-      <c r="C11" s="216"/>
+      <c r="A11" s="220"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="219"/>
-      <c r="B12" s="216"/>
-      <c r="C12" s="216"/>
+      <c r="A12" s="220"/>
+      <c r="B12" s="217"/>
+      <c r="C12" s="217"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="219"/>
-      <c r="B13" s="216"/>
-      <c r="C13" s="216"/>
+      <c r="A13" s="220"/>
+      <c r="B13" s="217"/>
+      <c r="C13" s="217"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="220"/>
-      <c r="B14" s="216"/>
-      <c r="C14" s="216"/>
+      <c r="A14" s="221"/>
+      <c r="B14" s="217"/>
+      <c r="C14" s="217"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="216" t="s">
+      <c r="A15" s="217" t="s">
         <v>226</v>
       </c>
-      <c r="B15" s="216" t="s">
+      <c r="B15" s="217" t="s">
         <v>227</v>
       </c>
-      <c r="C15" s="216" t="s">
+      <c r="C15" s="217" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="216" t="s">
+      <c r="A16" s="217" t="s">
         <v>229</v>
       </c>
-      <c r="B16" s="216" t="s">
+      <c r="B16" s="217" t="s">
         <v>230</v>
       </c>
-      <c r="C16" s="216" t="s">
+      <c r="C16" s="217" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="216" t="s">
+      <c r="A17" s="217" t="s">
         <v>232</v>
       </c>
-      <c r="B17" s="216" t="s">
+      <c r="B17" s="217" t="s">
         <v>233</v>
       </c>
-      <c r="C17" s="221">
+      <c r="C17" s="222">
         <v>0.440972222222222</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="222" t="s">
+      <c r="A18" s="223" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="216" t="s">
+      <c r="B18" s="217" t="s">
         <v>234</v>
       </c>
-      <c r="C18" s="216" t="s">
+      <c r="C18" s="217" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="223"/>
-      <c r="B19" s="216" t="s">
+      <c r="A19" s="220"/>
+      <c r="B19" s="217" t="s">
         <v>236</v>
       </c>
-      <c r="C19" s="216" t="s">
+      <c r="C19" s="217" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="20" ht="56" spans="1:3">
-      <c r="A20" s="223"/>
-      <c r="B20" s="216" t="s">
+      <c r="A20" s="220"/>
+      <c r="B20" s="217" t="s">
         <v>238</v>
       </c>
-      <c r="C20" s="216" t="s">
+      <c r="C20" s="217" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="223"/>
-      <c r="B21" s="216" t="s">
+      <c r="A21" s="220"/>
+      <c r="B21" s="217" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="216" t="s">
+      <c r="C21" s="217" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:3">
-      <c r="A22" s="223"/>
-      <c r="B22" s="216" t="s">
+      <c r="A22" s="220"/>
+      <c r="B22" s="217" t="s">
         <v>242</v>
       </c>
-      <c r="C22" s="216" t="s">
+      <c r="C22" s="217" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="223"/>
-      <c r="B23" s="216" t="s">
+      <c r="A23" s="220"/>
+      <c r="B23" s="217" t="s">
         <v>244</v>
       </c>
-      <c r="C23" s="216" t="s">
+      <c r="C23" s="217" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="223"/>
-      <c r="B24" s="216" t="s">
+      <c r="A24" s="220"/>
+      <c r="B24" s="217" t="s">
         <v>246</v>
       </c>
-      <c r="C24" s="216" t="s">
+      <c r="C24" s="217" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="223"/>
-      <c r="B25" s="216" t="s">
+      <c r="A25" s="220"/>
+      <c r="B25" s="217" t="s">
         <v>248</v>
       </c>
-      <c r="C25" s="216" t="s">
+      <c r="C25" s="217" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="223"/>
-      <c r="B26" s="216" t="s">
+      <c r="A26" s="220"/>
+      <c r="B26" s="217" t="s">
         <v>246</v>
       </c>
-      <c r="C26" s="216" t="s">
+      <c r="C26" s="217" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="223"/>
-      <c r="B27" s="216"/>
-      <c r="C27" s="216"/>
+      <c r="A27" s="220"/>
+      <c r="B27" s="217"/>
+      <c r="C27" s="217"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="223"/>
-      <c r="B28" s="216"/>
-      <c r="C28" s="216"/>
+      <c r="A28" s="220"/>
+      <c r="B28" s="217"/>
+      <c r="C28" s="217"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="223"/>
-      <c r="B29" s="216"/>
-      <c r="C29" s="216"/>
+      <c r="A29" s="220"/>
+      <c r="B29" s="217"/>
+      <c r="C29" s="217"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="223"/>
-      <c r="B30" s="216"/>
-      <c r="C30" s="216"/>
+      <c r="A30" s="220"/>
+      <c r="B30" s="217"/>
+      <c r="C30" s="217"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="223"/>
-      <c r="B31" s="216"/>
-      <c r="C31" s="216"/>
+      <c r="A31" s="220"/>
+      <c r="B31" s="217"/>
+      <c r="C31" s="217"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="223"/>
-      <c r="B32" s="216"/>
-      <c r="C32" s="216"/>
+      <c r="A32" s="220"/>
+      <c r="B32" s="217"/>
+      <c r="C32" s="217"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="223"/>
-      <c r="B33" s="216"/>
-      <c r="C33" s="216"/>
+      <c r="A33" s="220"/>
+      <c r="B33" s="217"/>
+      <c r="C33" s="217"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="217" t="s">
+      <c r="A34" s="218" t="s">
         <v>251</v>
       </c>
-      <c r="B34" s="216" t="s">
+      <c r="B34" s="217" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="216" t="s">
+      <c r="C34" s="217" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="218"/>
-      <c r="B35" s="216" t="s">
+      <c r="A35" s="219"/>
+      <c r="B35" s="217" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="216" t="s">
+      <c r="C35" s="217" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="36" ht="28" spans="1:3">
-      <c r="A36" s="224" t="s">
+      <c r="A36" s="223" t="s">
         <v>255</v>
       </c>
-      <c r="B36" s="216" t="s">
+      <c r="B36" s="217" t="s">
         <v>256</v>
       </c>
-      <c r="C36" s="216" t="s">
+      <c r="C36" s="217" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="219"/>
-      <c r="B37" s="216" t="s">
+      <c r="A37" s="220"/>
+      <c r="B37" s="217" t="s">
         <v>220</v>
       </c>
-      <c r="C37" s="216" t="s">
+      <c r="C37" s="217" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="219"/>
-      <c r="B38" s="216" t="s">
+      <c r="A38" s="220"/>
+      <c r="B38" s="217" t="s">
         <v>259</v>
       </c>
-      <c r="C38" s="216" t="s">
+      <c r="C38" s="217" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="219"/>
-      <c r="B39" s="216"/>
-      <c r="C39" s="216"/>
+      <c r="A39" s="220"/>
+      <c r="B39" s="217"/>
+      <c r="C39" s="217"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="217" t="s">
+      <c r="A40" s="218" t="s">
         <v>261</v>
       </c>
-      <c r="B40" s="216" t="s">
+      <c r="B40" s="217" t="s">
         <v>262</v>
       </c>
-      <c r="C40" s="216" t="s">
+      <c r="C40" s="217" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="218"/>
-      <c r="B41" s="216" t="s">
+      <c r="A41" s="219"/>
+      <c r="B41" s="217" t="s">
         <v>218</v>
       </c>
-      <c r="C41" s="216" t="s">
+      <c r="C41" s="217" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="42" ht="28" spans="1:3">
-      <c r="A42" s="222" t="s">
+      <c r="A42" s="223" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="216" t="s">
+      <c r="B42" s="217" t="s">
         <v>218</v>
       </c>
-      <c r="C42" s="216" t="s">
+      <c r="C42" s="217" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="223"/>
-      <c r="B43" s="214" t="s">
+      <c r="A43" s="220"/>
+      <c r="B43" s="215" t="s">
         <v>266</v>
       </c>
-      <c r="C43" s="214" t="s">
+      <c r="C43" s="215" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="223"/>
-      <c r="B44" s="214" t="s">
+      <c r="A44" s="220"/>
+      <c r="B44" s="215" t="s">
         <v>240</v>
       </c>
-      <c r="C44" s="214" t="s">
+      <c r="C44" s="215" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="223"/>
-      <c r="B45" s="214" t="s">
+      <c r="A45" s="220"/>
+      <c r="B45" s="215" t="s">
         <v>246</v>
       </c>
-      <c r="C45" s="214" t="s">
+      <c r="C45" s="215" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="46" ht="28" spans="1:3">
-      <c r="A46" s="223"/>
-      <c r="B46" s="214" t="s">
+      <c r="A46" s="220"/>
+      <c r="B46" s="215" t="s">
         <v>246</v>
       </c>
-      <c r="C46" s="214" t="s">
+      <c r="C46" s="215" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="223"/>
+      <c r="A47" s="220"/>
     </row>
     <row r="48" ht="98" spans="1:3">
-      <c r="A48" s="224" t="s">
+      <c r="A48" s="223" t="s">
         <v>271</v>
       </c>
-      <c r="B48" s="214" t="s">
+      <c r="B48" s="215" t="s">
         <v>218</v>
       </c>
-      <c r="C48" s="214" t="s">
+      <c r="C48" s="215" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="49" ht="84" spans="1:3">
-      <c r="A49" s="219"/>
-      <c r="B49" s="214" t="s">
+      <c r="A49" s="220"/>
+      <c r="B49" s="215" t="s">
         <v>273</v>
       </c>
-      <c r="C49" s="214" t="s">
+      <c r="C49" s="215" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="50" ht="28" spans="1:3">
-      <c r="A50" s="220"/>
-      <c r="B50" s="214" t="s">
+      <c r="A50" s="221"/>
+      <c r="B50" s="215" t="s">
         <v>275</v>
       </c>
-      <c r="C50" s="214" t="s">
+      <c r="C50" s="215" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="214" t="s">
+      <c r="A51" s="215" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="214" t="s">
+      <c r="B51" s="215" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="214" t="s">
+      <c r="C51" s="215" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="224" t="s">
+      <c r="A52" s="223" t="s">
         <v>279</v>
       </c>
-      <c r="B52" s="214" t="s">
+      <c r="B52" s="215" t="s">
         <v>220</v>
       </c>
-      <c r="C52" s="214" t="s">
+      <c r="C52" s="215" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="220"/>
-      <c r="B53" s="214" t="s">
+      <c r="A53" s="221"/>
+      <c r="B53" s="215" t="s">
         <v>273</v>
       </c>
-      <c r="C53" s="214" t="s">
+      <c r="C53" s="215" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="214" t="s">
+      <c r="A54" s="215" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="214" t="s">
+      <c r="B54" s="215" t="s">
         <v>222</v>
       </c>
-      <c r="C54" s="214" t="s">
+      <c r="C54" s="215" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="222" t="s">
+      <c r="A55" s="223" t="s">
         <v>283</v>
       </c>
-      <c r="B55" s="214" t="s">
+      <c r="B55" s="215" t="s">
         <v>284</v>
       </c>
-      <c r="C55" s="214" t="s">
+      <c r="C55" s="215" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="225"/>
-      <c r="B56" s="214" t="s">
+      <c r="A56" s="221"/>
+      <c r="B56" s="215" t="s">
         <v>246</v>
       </c>
-      <c r="C56" s="214" t="s">
+      <c r="C56" s="215" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="214" t="s">
+      <c r="A57" s="215" t="s">
         <v>287</v>
       </c>
-      <c r="B57" s="214" t="s">
+      <c r="B57" s="215" t="s">
         <v>288</v>
       </c>
-      <c r="C57" s="214" t="s">
+      <c r="C57" s="215" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="214" t="s">
+      <c r="A58" s="215" t="s">
         <v>10</v>
       </c>
-      <c r="B58" s="214" t="s">
+      <c r="B58" s="215" t="s">
         <v>273</v>
       </c>
-      <c r="C58" s="214" t="s">
+      <c r="C58" s="215" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="214" t="s">
+      <c r="A59" s="215" t="s">
         <v>291</v>
       </c>
-      <c r="B59" s="214" t="s">
+      <c r="B59" s="215" t="s">
         <v>292</v>
       </c>
-      <c r="C59" s="214" t="s">
+      <c r="C59" s="215" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="214" t="s">
+      <c r="A60" s="215" t="s">
         <v>294</v>
       </c>
-      <c r="B60" s="214" t="s">
+      <c r="B60" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C60" s="214" t="s">
+      <c r="C60" s="215" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="214" t="s">
+      <c r="A61" s="215" t="s">
         <v>297</v>
       </c>
-      <c r="B61" s="214" t="s">
+      <c r="B61" s="215" t="s">
         <v>295</v>
       </c>
-      <c r="C61" s="214" t="s">
+      <c r="C61" s="215" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="214" t="s">
+      <c r="A62" s="215" t="s">
         <v>299</v>
       </c>
-      <c r="B62" s="214" t="s">
+      <c r="B62" s="215" t="s">
         <v>242</v>
       </c>
-      <c r="C62" s="214" t="s">
+      <c r="C62" s="215" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="63" ht="28" spans="1:3">
-      <c r="A63" s="214" t="s">
+      <c r="A63" s="215" t="s">
         <v>301</v>
       </c>
-      <c r="B63" s="214" t="s">
+      <c r="B63" s="215" t="s">
         <v>275</v>
       </c>
-      <c r="C63" s="214" t="s">
+      <c r="C63" s="215" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="64" ht="28" spans="1:3">
-      <c r="A64" s="214" t="s">
+      <c r="A64" s="215" t="s">
         <v>303</v>
       </c>
-      <c r="B64" s="214" t="s">
+      <c r="B64" s="215" t="s">
         <v>275</v>
       </c>
-      <c r="C64" s="214" t="s">
+      <c r="C64" s="215" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="65" ht="140" spans="1:3">
-      <c r="A65" s="214" t="s">
+      <c r="A65" s="215" t="s">
         <v>305</v>
       </c>
-      <c r="B65" s="214" t="s">
+      <c r="B65" s="215" t="s">
         <v>306</v>
       </c>
-      <c r="C65" s="214" t="s">
+      <c r="C65" s="215" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="214" t="s">
+      <c r="A66" s="215" t="s">
         <v>10</v>
       </c>
-      <c r="B66" s="214" t="s">
+      <c r="B66" s="215" t="s">
         <v>244</v>
       </c>
-      <c r="C66" s="214" t="s">
+      <c r="C66" s="215" t="s">
         <v>308</v>
       </c>
     </row>
@@ -9332,45 +9326,45 @@
     <col min="2" max="2" width="3.54545454545455" style="4" customWidth="1"/>
     <col min="3" max="3" width="4.27272727272727" style="4" customWidth="1"/>
     <col min="4" max="4" width="3.45454545454545" style="4" customWidth="1"/>
-    <col min="5" max="5" width="8.72727272727273" style="202"/>
+    <col min="5" max="5" width="8.72727272727273" style="203"/>
     <col min="6" max="6" width="9.52727272727273" style="4" customWidth="1"/>
     <col min="7" max="7" width="22.8181818181818" style="4" customWidth="1"/>
     <col min="8" max="16384" width="8.72727272727273" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="200" customFormat="1" ht="15" spans="1:7">
-      <c r="A1" s="203" t="s">
+    <row r="1" s="201" customFormat="1" ht="15" spans="1:7">
+      <c r="A1" s="204" t="s">
         <v>309</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="205"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="200" t="s">
+      <c r="B1" s="205"/>
+      <c r="C1" s="205"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="201" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="2" s="201" customFormat="1" spans="1:7">
-      <c r="A2" s="207" t="s">
+    <row r="2" s="202" customFormat="1" spans="1:7">
+      <c r="A2" s="208" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="208"/>
-      <c r="C2" s="201" t="s">
+      <c r="B2" s="209"/>
+      <c r="C2" s="202" t="s">
         <v>311</v>
       </c>
-      <c r="D2" s="201" t="s">
+      <c r="D2" s="202" t="s">
         <v>312</v>
       </c>
       <c r="E2" s="142"/>
-      <c r="F2" s="201" t="s">
+      <c r="F2" s="202" t="s">
         <v>203</v>
       </c>
-      <c r="G2" s="201" t="s">
+      <c r="G2" s="202" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="209">
+      <c r="A3" s="210">
         <v>2025.1</v>
       </c>
       <c r="B3" s="119">
@@ -9388,7 +9382,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="210"/>
+      <c r="A4" s="211"/>
       <c r="B4" s="119">
         <v>15</v>
       </c>
@@ -9404,7 +9398,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="210"/>
+      <c r="A5" s="211"/>
       <c r="B5" s="119">
         <v>17</v>
       </c>
@@ -9420,7 +9414,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="210"/>
+      <c r="A6" s="211"/>
       <c r="B6" s="119">
         <v>22</v>
       </c>
@@ -9428,7 +9422,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="119"/>
-      <c r="F6" s="211" t="s">
+      <c r="F6" s="212" t="s">
         <v>320</v>
       </c>
       <c r="G6" s="119" t="s">
@@ -9436,7 +9430,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="210"/>
+      <c r="A7" s="211"/>
       <c r="B7" s="119">
         <v>24</v>
       </c>
@@ -9444,13 +9438,13 @@
         <v>180</v>
       </c>
       <c r="D7" s="119"/>
-      <c r="F7" s="212"/>
+      <c r="F7" s="213"/>
       <c r="G7" s="119" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="210"/>
+      <c r="A8" s="211"/>
       <c r="B8" s="119">
         <v>29</v>
       </c>
@@ -9466,7 +9460,7 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="212"/>
+      <c r="A9" s="213"/>
       <c r="B9" s="119">
         <v>31</v>
       </c>
@@ -9482,7 +9476,7 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="211">
+      <c r="A10" s="212">
         <v>2025.11</v>
       </c>
       <c r="B10" s="119">
@@ -9500,7 +9494,7 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="210"/>
+      <c r="A11" s="211"/>
       <c r="B11" s="119">
         <v>7</v>
       </c>
@@ -9508,7 +9502,7 @@
         <v>119</v>
       </c>
       <c r="D11" s="119"/>
-      <c r="F11" s="211" t="s">
+      <c r="F11" s="212" t="s">
         <v>329</v>
       </c>
       <c r="G11" s="119" t="s">
@@ -9516,7 +9510,7 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="212"/>
+      <c r="A12" s="213"/>
       <c r="B12" s="119">
         <v>14</v>
       </c>
@@ -9524,13 +9518,13 @@
         <v>63</v>
       </c>
       <c r="D12" s="119"/>
-      <c r="F12" s="210"/>
+      <c r="F12" s="211"/>
       <c r="G12" s="119" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="211">
+      <c r="A13" s="212">
         <v>2025.12</v>
       </c>
       <c r="B13" s="119">
@@ -9542,13 +9536,13 @@
       <c r="D13" s="119">
         <v>74</v>
       </c>
-      <c r="F13" s="212"/>
+      <c r="F13" s="213"/>
       <c r="G13" s="119" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="212"/>
+      <c r="A14" s="213"/>
       <c r="B14" s="119">
         <v>31</v>
       </c>
@@ -10077,7 +10071,9 @@
       <c r="BA4" s="120">
         <v>1</v>
       </c>
-      <c r="BB4" s="120"/>
+      <c r="BB4" s="120">
+        <v>1</v>
+      </c>
       <c r="BC4" s="120"/>
       <c r="BD4" s="120"/>
       <c r="BE4" s="120"/>
@@ -10086,11 +10082,11 @@
       <c r="BH4" s="120"/>
       <c r="BI4" s="188">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BJ4" s="188" cm="1">
         <f t="array" ref="BJ4">SUMPRODUCT(--(B4:BC4=INT(B4:BC4)),--(B4:BC4&gt;0))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BK4" s="188" cm="1">
         <f t="array" ref="BK4">MAX(FREQUENCY(IF((B4:BC4=INT(B4:BC4))*(B4:BC4&gt;0),COLUMN(B4:BC4)),IF((B4:BC4&lt;&gt;INT(B4:BC4))+(B4:BC4&lt;=0),COLUMN(B4:BC4))))</f>
@@ -10102,7 +10098,7 @@
       </c>
       <c r="BM4" s="190">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BN4" s="190">
         <f t="shared" si="2"/>
@@ -10383,7 +10379,9 @@
       </c>
       <c r="AZ7" s="120"/>
       <c r="BA7" s="120"/>
-      <c r="BB7" s="120"/>
+      <c r="BB7" s="120">
+        <v>1</v>
+      </c>
       <c r="BC7" s="120"/>
       <c r="BD7" s="120"/>
       <c r="BE7" s="120"/>
@@ -10392,11 +10390,11 @@
       <c r="BH7" s="120"/>
       <c r="BI7" s="188">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BJ7" s="188" cm="1">
         <f t="array" ref="BJ7">SUMPRODUCT(--(B7:BC7=INT(B7:BC7)),--(B7:BC7&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BK7" s="188" cm="1">
         <f t="array" ref="BK7">MAX(FREQUENCY(IF((B7:BC7=INT(B7:BC7))*(B7:BC7&gt;0),COLUMN(B7:BC7)),IF((B7:BC7&lt;&gt;INT(B7:BC7))+(B7:BC7&lt;=0),COLUMN(B7:BC7))))</f>
@@ -10412,7 +10410,7 @@
       </c>
       <c r="BN7" s="190">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BO7" s="190">
         <f t="shared" si="3"/>
@@ -10904,7 +10902,7 @@
       </c>
       <c r="BO11" s="190">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:67">
@@ -11212,11 +11210,11 @@
       </c>
       <c r="BM14" s="190">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BN14" s="190">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BO14" s="190">
         <f t="shared" si="3"/>
@@ -11344,7 +11342,7 @@
       </c>
       <c r="BM15" s="190">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BN15" s="190">
         <f t="shared" si="2"/>
@@ -11546,7 +11544,7 @@
       </c>
       <c r="BN17" s="190">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BO17" s="190">
         <f t="shared" si="3"/>
@@ -11752,7 +11750,7 @@
       </c>
       <c r="BO19" s="190">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:67">
@@ -11913,7 +11911,9 @@
       <c r="AY21" s="120"/>
       <c r="AZ21" s="120"/>
       <c r="BA21" s="120"/>
-      <c r="BB21" s="120"/>
+      <c r="BB21" s="120">
+        <v>1</v>
+      </c>
       <c r="BC21" s="120"/>
       <c r="BD21" s="120"/>
       <c r="BE21" s="120"/>
@@ -11922,11 +11922,11 @@
       <c r="BH21" s="120"/>
       <c r="BI21" s="188">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BJ21" s="188" cm="1">
         <f t="array" ref="BJ21">SUMPRODUCT(--(B21:BC21=INT(B21:BC21)),--(B21:BC21&gt;0))</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BK21" s="188" cm="1">
         <f t="array" ref="BK21">MAX(FREQUENCY(IF((B21:BC21=INT(B21:BC21))*(B21:BC21&gt;0),COLUMN(B21:BC21)),IF((B21:BC21&lt;&gt;INT(B21:BC21))+(B21:BC21&lt;=0),COLUMN(B21:BC21))))</f>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="BN21" s="190">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BO21" s="190">
         <f t="shared" si="3"/>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="BN22" s="190">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BO22" s="190">
         <f t="shared" si="3"/>
@@ -12249,7 +12249,9 @@
       <c r="BA24" s="120">
         <v>1</v>
       </c>
-      <c r="BB24" s="120"/>
+      <c r="BB24" s="120">
+        <v>1</v>
+      </c>
       <c r="BC24" s="120"/>
       <c r="BD24" s="120"/>
       <c r="BE24" s="120"/>
@@ -12258,11 +12260,11 @@
       <c r="BH24" s="120"/>
       <c r="BI24" s="188">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BJ24" s="188" cm="1">
         <f t="array" ref="BJ24">SUMPRODUCT(--(B24:BC24=INT(B24:BC24)),--(B24:BC24&gt;0))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BK24" s="188" cm="1">
         <f t="array" ref="BK24">MAX(FREQUENCY(IF((B24:BC24=INT(B24:BC24))*(B24:BC24&gt;0),COLUMN(B24:BC24)),IF((B24:BC24&lt;&gt;INT(B24:BC24))+(B24:BC24&lt;=0),COLUMN(B24:BC24))))</f>
@@ -12274,11 +12276,11 @@
       </c>
       <c r="BM24" s="190">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BN24" s="190">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BO24" s="190">
         <f t="shared" si="3"/>
@@ -12460,15 +12462,15 @@
       </c>
       <c r="BM26" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN26" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO26" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:67">
@@ -12552,15 +12554,15 @@
       </c>
       <c r="BM27" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN27" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO27" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:67">
@@ -12680,7 +12682,7 @@
       </c>
       <c r="BO28" s="190">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:67">
@@ -12786,11 +12788,11 @@
       </c>
       <c r="BM29" s="190">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BN29" s="190">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BO29" s="190">
         <f t="shared" si="3"/>
@@ -12867,7 +12869,9 @@
       <c r="AY30" s="120"/>
       <c r="AZ30" s="120"/>
       <c r="BA30" s="120"/>
-      <c r="BB30" s="120"/>
+      <c r="BB30" s="120">
+        <v>1</v>
+      </c>
       <c r="BC30" s="120"/>
       <c r="BD30" s="120"/>
       <c r="BE30" s="120"/>
@@ -12876,11 +12880,11 @@
       <c r="BH30" s="120"/>
       <c r="BI30" s="188">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BJ30" s="188" cm="1">
         <f t="array" ref="BJ30">SUMPRODUCT(--(B30:BC30=INT(B30:BC30)),--(B30:BC30&gt;0))</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BK30" s="188" cm="1">
         <f t="array" ref="BK30">MAX(FREQUENCY(IF((B30:BC30=INT(B30:BC30))*(B30:BC30&gt;0),COLUMN(B30:BC30)),IF((B30:BC30&lt;&gt;INT(B30:BC30))+(B30:BC30&lt;=0),COLUMN(B30:BC30))))</f>
@@ -12892,11 +12896,11 @@
       </c>
       <c r="BM30" s="190">
         <f t="shared" si="1"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BN30" s="190">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BO30" s="190">
         <f t="shared" si="3"/>
@@ -13016,7 +13020,7 @@
       </c>
       <c r="BO31" s="190">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:67">
@@ -13205,7 +13209,9 @@
       <c r="AY33" s="120"/>
       <c r="AZ33" s="120"/>
       <c r="BA33" s="120"/>
-      <c r="BB33" s="120"/>
+      <c r="BB33" s="120">
+        <v>1</v>
+      </c>
       <c r="BC33" s="120"/>
       <c r="BD33" s="120"/>
       <c r="BE33" s="120"/>
@@ -13214,11 +13220,11 @@
       <c r="BH33" s="120"/>
       <c r="BI33" s="188">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BJ33" s="188" cm="1">
         <f t="array" ref="BJ33">SUMPRODUCT(--(B33:BC33=INT(B33:BC33)),--(B33:BC33&gt;0))</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BK33" s="188" cm="1">
         <f t="array" ref="BK33">MAX(FREQUENCY(IF((B33:BC33=INT(B33:BC33))*(B33:BC33&gt;0),COLUMN(B33:BC33)),IF((B33:BC33&lt;&gt;INT(B33:BC33))+(B33:BC33&lt;=0),COLUMN(B33:BC33))))</f>
@@ -13322,15 +13328,15 @@
       </c>
       <c r="BM34" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN34" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO34" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:67">
@@ -13414,15 +13420,15 @@
       </c>
       <c r="BM35" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN35" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO35" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:67">
@@ -13626,7 +13632,7 @@
       </c>
       <c r="BN37" s="190">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BO37" s="190">
         <f t="shared" si="3"/>
@@ -13812,15 +13818,15 @@
       </c>
       <c r="BM39" s="192">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN39" s="192">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO39" s="192">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:67">
@@ -13935,7 +13941,9 @@
         <v>1</v>
       </c>
       <c r="BA40" s="120"/>
-      <c r="BB40" s="120"/>
+      <c r="BB40" s="120">
+        <v>1</v>
+      </c>
       <c r="BC40" s="120"/>
       <c r="BD40" s="120"/>
       <c r="BE40" s="120"/>
@@ -13944,11 +13952,11 @@
       <c r="BH40" s="120"/>
       <c r="BI40" s="188">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BJ40" s="188" cm="1">
         <f t="array" ref="BJ40">SUMPRODUCT(--(B40:BC40=INT(B40:BC40)),--(B40:BC40&gt;0))</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BK40" s="188" cm="1">
         <f t="array" ref="BK40">MAX(FREQUENCY(IF((B40:BC40=INT(B40:BC40))*(B40:BC40&gt;0),COLUMN(B40:BC40)),IF((B40:BC40&lt;&gt;INT(B40:BC40))+(B40:BC40&lt;=0),COLUMN(B40:BC40))))</f>
@@ -14063,7 +14071,9 @@
       <c r="BA41" s="120">
         <v>1</v>
       </c>
-      <c r="BB41" s="120"/>
+      <c r="BB41" s="120">
+        <v>2</v>
+      </c>
       <c r="BC41" s="120"/>
       <c r="BD41" s="120"/>
       <c r="BE41" s="120"/>
@@ -14072,15 +14082,15 @@
       <c r="BH41" s="120"/>
       <c r="BI41" s="188">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BJ41" s="188" cm="1">
         <f t="array" ref="BJ41">SUMPRODUCT(--(B41:BC41=INT(B41:BC41)),--(B41:BC41&gt;0))</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BK41" s="188" cm="1">
         <f t="array" ref="BK41">MAX(FREQUENCY(IF((B41:BC41=INT(B41:BC41))*(B41:BC41&gt;0),COLUMN(B41:BC41)),IF((B41:BC41&lt;&gt;INT(B41:BC41))+(B41:BC41&lt;=0),COLUMN(B41:BC41))))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL41" s="189" cm="1">
         <f t="array" ref="BL41">SUMPRODUCT(--(B41:BA41=INT(B41:BA41)),--(B41:BA41&gt;0))/52*100%</f>
@@ -14088,7 +14098,7 @@
       </c>
       <c r="BM41" s="190">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN41" s="190">
         <f t="shared" si="2"/>
@@ -14096,7 +14106,7 @@
       </c>
       <c r="BO41" s="190">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:67">
@@ -14318,15 +14328,15 @@
       </c>
       <c r="BM43" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN43" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO43" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:67">
@@ -14456,7 +14466,7 @@
       </c>
       <c r="BN44" s="190">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BO44" s="190">
         <f t="shared" si="3"/>
@@ -14544,15 +14554,15 @@
       </c>
       <c r="BM45" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN45" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO45" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:67">
@@ -14681,7 +14691,9 @@
       <c r="BA46" s="120">
         <v>1</v>
       </c>
-      <c r="BB46" s="120"/>
+      <c r="BB46" s="120">
+        <v>2</v>
+      </c>
       <c r="BC46" s="120"/>
       <c r="BD46" s="120"/>
       <c r="BE46" s="120"/>
@@ -14690,15 +14702,15 @@
       <c r="BH46" s="120"/>
       <c r="BI46" s="188">
         <f t="shared" si="0"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BJ46" s="188" cm="1">
         <f t="array" ref="BJ46">SUMPRODUCT(--(B46:BC46=INT(B46:BC46)),--(B46:BC46&gt;0))</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BK46" s="188" cm="1">
         <f t="array" ref="BK46">MAX(FREQUENCY(IF((B46:BC46=INT(B46:BC46))*(B46:BC46&gt;0),COLUMN(B46:BC46)),IF((B46:BC46&lt;&gt;INT(B46:BC46))+(B46:BC46&lt;=0),COLUMN(B46:BC46))))</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BL46" s="189" cm="1">
         <f t="array" ref="BL46">SUMPRODUCT(--(B46:BA46=INT(B46:BA46)),--(B46:BA46&gt;0))/52*100%</f>
@@ -14714,7 +14726,7 @@
       </c>
       <c r="BO46" s="190">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:67">
@@ -14798,15 +14810,15 @@
       </c>
       <c r="BM47" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN47" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO47" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:67">
@@ -14932,7 +14944,7 @@
       </c>
       <c r="BO48" s="190">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:67">
@@ -15028,7 +15040,7 @@
       </c>
       <c r="BN49" s="190">
         <f t="shared" si="2"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BO49" s="190">
         <f t="shared" si="3"/>
@@ -15126,11 +15138,11 @@
       </c>
       <c r="BM50" s="190">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BN50" s="190">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BO50" s="190">
         <f t="shared" si="3"/>
@@ -15138,7 +15150,7 @@
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:67">
-      <c r="A51" s="117">
+      <c r="A51" s="193">
         <v>49</v>
       </c>
       <c r="B51" s="120"/>
@@ -15193,7 +15205,9 @@
       <c r="AY51" s="120"/>
       <c r="AZ51" s="120"/>
       <c r="BA51" s="120"/>
-      <c r="BB51" s="120"/>
+      <c r="BB51" s="120">
+        <v>1</v>
+      </c>
       <c r="BC51" s="120"/>
       <c r="BD51" s="120"/>
       <c r="BE51" s="120"/>
@@ -15202,15 +15216,15 @@
       <c r="BH51" s="120"/>
       <c r="BI51" s="188">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ51" s="188" cm="1">
         <f t="array" ref="BJ51">SUMPRODUCT(--(B51:BC51=INT(B51:BC51)),--(B51:BC51&gt;0))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BK51" s="188" cm="1">
         <f t="array" ref="BK51">MAX(FREQUENCY(IF((B51:BC51=INT(B51:BC51))*(B51:BC51&gt;0),COLUMN(B51:BC51)),IF((B51:BC51&lt;&gt;INT(B51:BC51))+(B51:BC51&lt;=0),COLUMN(B51:BC51))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BL51" s="189" cm="1">
         <f t="array" ref="BL51">SUMPRODUCT(--(B51:BA51=INT(B51:BA51)),--(B51:BA51&gt;0))/52*100%</f>
@@ -15218,15 +15232,15 @@
       </c>
       <c r="BM51" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="BN51" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="BO51" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:67">
@@ -15310,15 +15324,15 @@
       </c>
       <c r="BM52" s="190">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BN52" s="190">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="BO52" s="190">
         <f t="shared" si="3"/>
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:67">
@@ -15416,7 +15430,7 @@
       </c>
     </row>
     <row r="54" s="175" customFormat="1" ht="28" spans="1:67">
-      <c r="A54" s="193" t="s">
+      <c r="A54" s="194" t="s">
         <v>344</v>
       </c>
       <c r="B54" s="17" cm="1">
@@ -15629,7 +15643,7 @@
       </c>
       <c r="BB54" s="17" cm="1">
         <f t="array" ref="BB54">SUMPRODUCT(--(BB3:BB53=INT(BB3:BB53)),--(BB3:BB53&gt;0))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BC54" s="17" cm="1">
         <f t="array" ref="BC54">SUMPRODUCT(--(BC3:BC53=INT(BC3:BC53)),--(BC3:BC53&gt;0))</f>
@@ -15655,18 +15669,18 @@
         <f t="array" ref="BH54">SUMPRODUCT(--(BH3:BH53=INT(BH3:BH53)),--(BH3:BH53&gt;0))</f>
         <v>0</v>
       </c>
-      <c r="BI54" s="194" t="s">
+      <c r="BI54" s="195" t="s">
         <v>345</v>
       </c>
-      <c r="BJ54" s="195"/>
-      <c r="BK54" s="195"/>
-      <c r="BL54" s="195"/>
-      <c r="BM54" s="195"/>
-      <c r="BN54" s="195"/>
-      <c r="BO54" s="196"/>
+      <c r="BJ54" s="196"/>
+      <c r="BK54" s="196"/>
+      <c r="BL54" s="196"/>
+      <c r="BM54" s="196"/>
+      <c r="BN54" s="196"/>
+      <c r="BO54" s="197"/>
     </row>
     <row r="55" s="175" customFormat="1" ht="28" spans="1:67">
-      <c r="A55" s="193" t="s">
+      <c r="A55" s="194" t="s">
         <v>346</v>
       </c>
       <c r="B55" s="17">
@@ -15879,7 +15893,7 @@
       </c>
       <c r="BB55" s="17">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC55" s="17">
         <f t="shared" si="5"/>
@@ -15905,13 +15919,13 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="BI55" s="197"/>
-      <c r="BJ55" s="198"/>
-      <c r="BK55" s="198"/>
-      <c r="BL55" s="198"/>
-      <c r="BM55" s="198"/>
-      <c r="BN55" s="198"/>
-      <c r="BO55" s="199"/>
+      <c r="BI55" s="198"/>
+      <c r="BJ55" s="199"/>
+      <c r="BK55" s="199"/>
+      <c r="BL55" s="199"/>
+      <c r="BM55" s="199"/>
+      <c r="BN55" s="199"/>
+      <c r="BO55" s="200"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -17295,9 +17309,9 @@
   <pageSetup paperSize="9" scale="80" orientation="landscape"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A54:BO55 AG52:BO53 A5:BO23 A24:BL28 A29:BO40 Y4:AE4 A52:Z52 A53:AF53 A42:BO46 AG47:BO47 A48:BO51 A41:W41" formulaRange="1"/>
-    <ignoredError sqref="BM24:BO28 Z24:AF25 A24:X25 A12:X15 BM11:BO14 A9:X10 BM5:BO8 Z10:AF10 BN9:BO9 Z29:AF29 A28:X28 A26:AF27 Z12:AF12 Z13 AB13:AF13 Z14:AF14 Z15 AB15:AE15 A37:AF37 BN35:BO35 Z36:AF36 A36:X36 A34:AF35 A32:X32 A23:AF23 AF22 AA22:AD22 A22:X22 A19:AF21 Z17:AF18 A17:X18 A16:AF16 AE11 AB11:AC11 A11:Z11 A8:V8 X8:AF8 Z9:AB9 AD9:AF9 A5:AF7 BM38:BO39 A39:AF39 AD38:AF38 Z38:AB38 A38:X38 A40:V40 AC40:AD40 BM4:BO4 A4:X4 Z4:AE4 A3:X3 AA52:AF52 Y52 V52 P52 A52 A53:AF53 A47:AF47 AF46 AC46:AD46 AA46 A46:X46 A45:AF45 AF44 Z44:AD44 A44:W44 A43:AF43 Z48:AB48 AE48 Z49:AF49 AF50 A50:AD50 A51:AF51 A49:X49 Z42:AE42 A42:X42 Z41:AE41 X41" formulaRange="1" unlockedFormula="1"/>
-    <ignoredError sqref="A2:AF2 BI1:BO2 U1:AF1 C1:S1 A1 Z3:AF3 BN3 BM4:BO4 A3:X3 Z41:AE41" unlockedFormula="1"/>
+    <ignoredError sqref="A55:BO55 BJ54:BO54 A54:BH54 BC51:BO51 BC46:BO46 BC30:BO30 BC33:BO33 BC40:BO40 BC24:BL24 BC21:BO21 AG52:BO53 A30:BA30 A33:BA33 A48:BO48 Y49:BO49 A50:BO50 AG47:BO47 A42:Y42 AF42:BO42 A43:BO45 A29:Y29 AG29:BO29 A31:BO31 Y32:BO32 A34:BO37 Y38:BO38 A39:BO39 A25:BL25 AG26:BL27 A28:BL28 A5:BL6 A8:BL8 A9:BO20 Y22:BO22 A23:BO23 A41:W41 AG51:BA51 Y46:BA46 B52:Z52 Y4 A40:AB40 AE40:BA40 AG7:BA7 AG21:BA21 Y24:BA24" formulaRange="1"/>
+    <ignoredError sqref="A49:X49 A50:AD50 AF50 Z49:AF49 AE48 Z48:AB48 A47:AF47 Z42:AE42 A42:X42 A43:AF43 A44:W44 Z44:AD44 AF44 A45:AF45 Z29:AF29 A32:X32 A38:X38 Z38:AB38 AD38:AF38 A39:AF39 BM38:BO39 A34:AF35 A36:X36 Z36:AF36 BN35:BO35 A37:AF37 A26:AF27 A28:X28 A25:X25 Z25:AF25 BM5:BO6 A5:AF6 BM7:BO8 BM8:BO8 AD9:AF9 Z9:AB9 X8:AF8 A8:V8 A11:Z11 AB11:AC11 AE11 A16:AF16 A17:X18 Z17:AF18 A19:AF20 AB15:AE15 Z15 Z14:AF14 AB13:AF13 Z13 Z12:AF12 BN9:BO9 Z10:AF10 A9:X10 BM11:BO14 A12:X15 A22:X22 AA22:AD22 AF22 A23:AF23 X41 Z41:AE41 A51:AF51 A46:X46 AA46 AC46:AD46 AF46 AA46 AC46:AD46 AF46 A53:AF53 A52 P52 V52 Y52 P52 V52 Y52 AA52:AF52 Z4:AE4 A3:X4 AC40:AD40 A40:V40 A40:V40 A7:AF7 A21:AF21 BM4:BO4 A24:X24 Z24:AF24 Z24:AF24 BM24:BO28" formulaRange="1" unlockedFormula="1"/>
+    <ignoredError sqref="BN3 Z3:AF3 A1 C1:S1 U1:AF1 BI1:BO2 A2:AF2 Z41:AE41 A24:X24 Z24:AF24 BM4:BO4 BM7:BO8 A7:AF7 A21:AF21" unlockedFormula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -17989,7 +18003,7 @@
   <sheetPr>
     <tabColor theme="0" tint="-0.05"/>
   </sheetPr>
-  <dimension ref="A1:XFD26"/>
+  <dimension ref="A1:XFD42"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="19" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.72727272727273" style="93"/>
@@ -18604,8 +18618,188 @@
       <c r="H26" s="112"/>
       <c r="I26" s="113"/>
     </row>
+    <row r="27" customHeight="1" spans="1:9">
+      <c r="A27" s="100" t="s">
+        <v>396</v>
+      </c>
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+    </row>
+    <row r="28" customHeight="1" spans="1:9">
+      <c r="A28" s="106"/>
+      <c r="B28" s="114"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="104"/>
+      <c r="G28" s="104"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:9">
+      <c r="A29" s="106"/>
+      <c r="B29" s="102"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="103"/>
+      <c r="F29" s="104"/>
+      <c r="G29" s="104"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+    </row>
+    <row r="30" customHeight="1" spans="1:9">
+      <c r="A30" s="106"/>
+      <c r="B30" s="102"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="104"/>
+      <c r="G30" s="104"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="105"/>
+    </row>
+    <row r="31" customHeight="1" spans="1:9">
+      <c r="A31" s="106"/>
+      <c r="B31" s="102"/>
+      <c r="C31" s="102"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="105"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:9">
+      <c r="A32" s="106"/>
+      <c r="B32" s="102"/>
+      <c r="C32" s="102"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="104"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+    </row>
+    <row r="33" customHeight="1" spans="1:9">
+      <c r="A33" s="106"/>
+      <c r="B33" s="102"/>
+      <c r="C33" s="102"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="104"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="105"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:9">
+      <c r="A34" s="107"/>
+      <c r="B34" s="115"/>
+      <c r="C34" s="116"/>
+      <c r="D34" s="110"/>
+      <c r="E34" s="111"/>
+      <c r="F34" s="112"/>
+      <c r="G34" s="112"/>
+      <c r="H34" s="112"/>
+      <c r="I34" s="113"/>
+    </row>
+    <row r="35" customHeight="1" spans="1:9">
+      <c r="A35" s="100" t="s">
+        <v>397</v>
+      </c>
+      <c r="B35" s="101"/>
+      <c r="C35" s="102"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
+    </row>
+    <row r="36" customHeight="1" spans="1:9"